--- a/datos/vistas_negocio/Fact_Global_Master.xlsx
+++ b/datos/vistas_negocio/Fact_Global_Master.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,47 +429,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ID_Futmondo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Jornada</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Temporada</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Puntos</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Puntos_Acumulados</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Acumulado_Total</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Ranking_Jornada</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Ranking_Temporada</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Ranking_General</t>
         </is>

--- a/datos/vistas_negocio/Fact_Global_Master.xlsx
+++ b/datos/vistas_negocio/Fact_Global_Master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1465"/>
+  <dimension ref="A1:I1473"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48787,6 +48787,270 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1466">
+      <c r="A1466" t="inlineStr">
+        <is>
+          <t>5f452f5e66dd374930eb2b71</t>
+        </is>
+      </c>
+      <c r="B1466" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="C1466" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1466" t="n">
+        <v>76.3</v>
+      </c>
+      <c r="E1466" t="n">
+        <v>2289</v>
+      </c>
+      <c r="F1466" t="n">
+        <v>13000.1</v>
+      </c>
+      <c r="G1466" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1466" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1466" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1467">
+      <c r="A1467" t="inlineStr">
+        <is>
+          <t>5f453062ec331549297ee6b8</t>
+        </is>
+      </c>
+      <c r="B1467" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="C1467" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1467" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="E1467" t="n">
+        <v>2200.4</v>
+      </c>
+      <c r="F1467" t="n">
+        <v>12891.4</v>
+      </c>
+      <c r="G1467" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1467" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1467" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1468">
+      <c r="A1468" t="inlineStr">
+        <is>
+          <t>5f4530beec331549297ee6d6</t>
+        </is>
+      </c>
+      <c r="B1468" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="C1468" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1468" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="E1468" t="n">
+        <v>2144.6</v>
+      </c>
+      <c r="F1468" t="n">
+        <v>12009.7</v>
+      </c>
+      <c r="G1468" t="n">
+        <v>7</v>
+      </c>
+      <c r="H1468" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1468" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1469">
+      <c r="A1469" t="inlineStr">
+        <is>
+          <t>5f4531e9764e7d491e029746</t>
+        </is>
+      </c>
+      <c r="B1469" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="C1469" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1469" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="E1469" t="n">
+        <v>1963.8</v>
+      </c>
+      <c r="F1469" t="n">
+        <v>11628.4</v>
+      </c>
+      <c r="G1469" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1469" t="n">
+        <v>7</v>
+      </c>
+      <c r="I1469" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1470">
+      <c r="A1470" t="inlineStr">
+        <is>
+          <t>5f45324dec331549297ee971</t>
+        </is>
+      </c>
+      <c r="B1470" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="C1470" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1470" t="n">
+        <v>69.7</v>
+      </c>
+      <c r="E1470" t="n">
+        <v>2297.3</v>
+      </c>
+      <c r="F1470" t="n">
+        <v>13232.1</v>
+      </c>
+      <c r="G1470" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1470" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1470" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1471">
+      <c r="A1471" t="inlineStr">
+        <is>
+          <t>5f47ab5b9e2edb0bb831c703</t>
+        </is>
+      </c>
+      <c r="B1471" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="C1471" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1471" t="n">
+        <v>80.09999999999999</v>
+      </c>
+      <c r="E1471" t="n">
+        <v>1848.3</v>
+      </c>
+      <c r="F1471" t="n">
+        <v>10682.2</v>
+      </c>
+      <c r="G1471" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1471" t="n">
+        <v>8</v>
+      </c>
+      <c r="I1471" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1472">
+      <c r="A1472" t="inlineStr">
+        <is>
+          <t>5f47aeb6c387a50bca03dd55</t>
+        </is>
+      </c>
+      <c r="B1472" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="C1472" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1472" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="E1472" t="n">
+        <v>2051.2</v>
+      </c>
+      <c r="F1472" t="n">
+        <v>11655.3</v>
+      </c>
+      <c r="G1472" t="n">
+        <v>8</v>
+      </c>
+      <c r="H1472" t="n">
+        <v>6</v>
+      </c>
+      <c r="I1472" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1473">
+      <c r="A1473" t="inlineStr">
+        <is>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
+        </is>
+      </c>
+      <c r="B1473" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="C1473" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1473" t="n">
+        <v>82.40000000000001</v>
+      </c>
+      <c r="E1473" t="n">
+        <v>2272.3</v>
+      </c>
+      <c r="F1473" t="n">
+        <v>9807.299999999999</v>
+      </c>
+      <c r="G1473" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1473" t="n">
+        <v>3</v>
+      </c>
+      <c r="I1473" t="n">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/vistas_negocio/Fact_Global_Master.xlsx
+++ b/datos/vistas_negocio/Fact_Global_Master.xlsx
@@ -40882,13 +40882,13 @@
         </is>
       </c>
       <c r="D1226" t="n">
-        <v>44.2</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="E1226" t="n">
-        <v>85.2</v>
+        <v>129.4</v>
       </c>
       <c r="F1226" t="n">
-        <v>10796.3</v>
+        <v>10840.5</v>
       </c>
       <c r="G1226" t="n">
         <v>8</v>
@@ -40915,19 +40915,19 @@
         </is>
       </c>
       <c r="D1227" t="n">
-        <v>93.3</v>
+        <v>186.6</v>
       </c>
       <c r="E1227" t="n">
-        <v>125.3</v>
+        <v>218.6</v>
       </c>
       <c r="F1227" t="n">
-        <v>10816.3</v>
+        <v>10909.6</v>
       </c>
       <c r="G1227" t="n">
         <v>2</v>
       </c>
       <c r="H1227" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I1227" t="n">
         <v>2</v>
@@ -40948,19 +40948,19 @@
         </is>
       </c>
       <c r="D1228" t="n">
-        <v>63.40000000000001</v>
+        <v>126.8</v>
       </c>
       <c r="E1228" t="n">
-        <v>134.4</v>
+        <v>197.8</v>
       </c>
       <c r="F1228" t="n">
-        <v>9999.5</v>
+        <v>10062.9</v>
       </c>
       <c r="G1228" t="n">
         <v>4</v>
       </c>
       <c r="H1228" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1228" t="n">
         <v>4</v>
@@ -40981,13 +40981,13 @@
         </is>
       </c>
       <c r="D1229" t="n">
-        <v>103</v>
+        <v>206</v>
       </c>
       <c r="E1229" t="n">
-        <v>146</v>
+        <v>249</v>
       </c>
       <c r="F1229" t="n">
-        <v>9810.6</v>
+        <v>9913.6</v>
       </c>
       <c r="G1229" t="n">
         <v>1</v>
@@ -41014,19 +41014,19 @@
         </is>
       </c>
       <c r="D1230" t="n">
-        <v>60.2</v>
+        <v>120.4</v>
       </c>
       <c r="E1230" t="n">
-        <v>139.2</v>
+        <v>199.4</v>
       </c>
       <c r="F1230" t="n">
-        <v>11074</v>
+        <v>11134.2</v>
       </c>
       <c r="G1230" t="n">
         <v>5</v>
       </c>
       <c r="H1230" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I1230" t="n">
         <v>1</v>
@@ -41047,13 +41047,13 @@
         </is>
       </c>
       <c r="D1231" t="n">
-        <v>44.6</v>
+        <v>89.2</v>
       </c>
       <c r="E1231" t="n">
-        <v>99.59999999999999</v>
+        <v>144.2</v>
       </c>
       <c r="F1231" t="n">
-        <v>8933.5</v>
+        <v>8978.1</v>
       </c>
       <c r="G1231" t="n">
         <v>7</v>
@@ -41080,19 +41080,19 @@
         </is>
       </c>
       <c r="D1232" t="n">
-        <v>70.10000000000001</v>
+        <v>140.2</v>
       </c>
       <c r="E1232" t="n">
-        <v>121.1</v>
+        <v>191.2</v>
       </c>
       <c r="F1232" t="n">
-        <v>9725.200000000001</v>
+        <v>9795.299999999999</v>
       </c>
       <c r="G1232" t="n">
         <v>3</v>
       </c>
       <c r="H1232" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I1232" t="n">
         <v>6</v>
@@ -41113,19 +41113,19 @@
         </is>
       </c>
       <c r="D1233" t="n">
-        <v>57.8</v>
+        <v>115.6</v>
       </c>
       <c r="E1233" t="n">
-        <v>126.8</v>
+        <v>184.6</v>
       </c>
       <c r="F1233" t="n">
-        <v>7661.8</v>
+        <v>7719.6</v>
       </c>
       <c r="G1233" t="n">
         <v>6</v>
       </c>
       <c r="H1233" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I1233" t="n">
         <v>8</v>
@@ -41146,13 +41146,13 @@
         </is>
       </c>
       <c r="D1234" t="n">
-        <v>62.4</v>
+        <v>124.8</v>
       </c>
       <c r="E1234" t="n">
-        <v>147.6</v>
+        <v>254.2</v>
       </c>
       <c r="F1234" t="n">
-        <v>10858.7</v>
+        <v>10965.3</v>
       </c>
       <c r="G1234" t="n">
         <v>5</v>
@@ -41179,19 +41179,19 @@
         </is>
       </c>
       <c r="D1235" t="n">
-        <v>66.8</v>
+        <v>133.6</v>
       </c>
       <c r="E1235" t="n">
-        <v>192.1</v>
+        <v>352.2</v>
       </c>
       <c r="F1235" t="n">
-        <v>10883.1</v>
+        <v>11043.2</v>
       </c>
       <c r="G1235" t="n">
         <v>3</v>
       </c>
       <c r="H1235" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I1235" t="n">
         <v>2</v>
@@ -41212,13 +41212,13 @@
         </is>
       </c>
       <c r="D1236" t="n">
-        <v>73</v>
+        <v>146</v>
       </c>
       <c r="E1236" t="n">
-        <v>207.4</v>
+        <v>343.8</v>
       </c>
       <c r="F1236" t="n">
-        <v>10072.5</v>
+        <v>10208.9</v>
       </c>
       <c r="G1236" t="n">
         <v>1</v>
@@ -41245,13 +41245,13 @@
         </is>
       </c>
       <c r="D1237" t="n">
-        <v>63.6</v>
+        <v>127.2</v>
       </c>
       <c r="E1237" t="n">
-        <v>209.6</v>
+        <v>376.2</v>
       </c>
       <c r="F1237" t="n">
-        <v>9874.200000000001</v>
+        <v>10040.8</v>
       </c>
       <c r="G1237" t="n">
         <v>4</v>
@@ -41278,19 +41278,19 @@
         </is>
       </c>
       <c r="D1238" t="n">
-        <v>70</v>
+        <v>140</v>
       </c>
       <c r="E1238" t="n">
-        <v>209.2</v>
+        <v>339.4</v>
       </c>
       <c r="F1238" t="n">
-        <v>11144</v>
+        <v>11274.2</v>
       </c>
       <c r="G1238" t="n">
         <v>2</v>
       </c>
       <c r="H1238" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I1238" t="n">
         <v>1</v>
@@ -41311,13 +41311,13 @@
         </is>
       </c>
       <c r="D1239" t="n">
-        <v>40.5</v>
+        <v>81</v>
       </c>
       <c r="E1239" t="n">
-        <v>140.1</v>
+        <v>225.2</v>
       </c>
       <c r="F1239" t="n">
-        <v>8974</v>
+        <v>9059.1</v>
       </c>
       <c r="G1239" t="n">
         <v>8</v>
@@ -41344,13 +41344,13 @@
         </is>
       </c>
       <c r="D1240" t="n">
-        <v>59.8</v>
+        <v>119.6</v>
       </c>
       <c r="E1240" t="n">
-        <v>180.9</v>
+        <v>310.8</v>
       </c>
       <c r="F1240" t="n">
-        <v>9785</v>
+        <v>9914.9</v>
       </c>
       <c r="G1240" t="n">
         <v>6</v>
@@ -41377,13 +41377,13 @@
         </is>
       </c>
       <c r="D1241" t="n">
-        <v>43.5</v>
+        <v>87</v>
       </c>
       <c r="E1241" t="n">
-        <v>170.3</v>
+        <v>271.6</v>
       </c>
       <c r="F1241" t="n">
-        <v>7705.3</v>
+        <v>7806.6</v>
       </c>
       <c r="G1241" t="n">
         <v>7</v>
@@ -41410,13 +41410,13 @@
         </is>
       </c>
       <c r="D1242" t="n">
-        <v>56.9</v>
+        <v>113.8</v>
       </c>
       <c r="E1242" t="n">
-        <v>204.5</v>
+        <v>368</v>
       </c>
       <c r="F1242" t="n">
-        <v>10915.6</v>
+        <v>11079.1</v>
       </c>
       <c r="G1242" t="n">
         <v>4</v>
@@ -41443,19 +41443,19 @@
         </is>
       </c>
       <c r="D1243" t="n">
-        <v>55.1</v>
+        <v>110.2</v>
       </c>
       <c r="E1243" t="n">
-        <v>247.2</v>
+        <v>462.4</v>
       </c>
       <c r="F1243" t="n">
-        <v>10938.2</v>
+        <v>11153.4</v>
       </c>
       <c r="G1243" t="n">
         <v>6</v>
       </c>
       <c r="H1243" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I1243" t="n">
         <v>2</v>
@@ -41476,19 +41476,19 @@
         </is>
       </c>
       <c r="D1244" t="n">
-        <v>58.8</v>
+        <v>117.6</v>
       </c>
       <c r="E1244" t="n">
-        <v>266.2</v>
+        <v>461.4</v>
       </c>
       <c r="F1244" t="n">
-        <v>10131.3</v>
+        <v>10326.5</v>
       </c>
       <c r="G1244" t="n">
         <v>3</v>
       </c>
       <c r="H1244" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I1244" t="n">
         <v>4</v>
@@ -41509,13 +41509,13 @@
         </is>
       </c>
       <c r="D1245" t="n">
-        <v>86.2</v>
+        <v>172.4</v>
       </c>
       <c r="E1245" t="n">
-        <v>295.8</v>
+        <v>548.6</v>
       </c>
       <c r="F1245" t="n">
-        <v>9960.4</v>
+        <v>10213.2</v>
       </c>
       <c r="G1245" t="n">
         <v>1</v>
@@ -41542,19 +41542,19 @@
         </is>
       </c>
       <c r="D1246" t="n">
-        <v>56.8</v>
+        <v>113.6</v>
       </c>
       <c r="E1246" t="n">
-        <v>266</v>
+        <v>453</v>
       </c>
       <c r="F1246" t="n">
-        <v>11200.8</v>
+        <v>11387.8</v>
       </c>
       <c r="G1246" t="n">
         <v>5</v>
       </c>
       <c r="H1246" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1246" t="n">
         <v>1</v>
@@ -41575,13 +41575,13 @@
         </is>
       </c>
       <c r="D1247" t="n">
-        <v>53.5</v>
+        <v>107</v>
       </c>
       <c r="E1247" t="n">
-        <v>193.6</v>
+        <v>332.2</v>
       </c>
       <c r="F1247" t="n">
-        <v>9027.5</v>
+        <v>9166.1</v>
       </c>
       <c r="G1247" t="n">
         <v>7</v>
@@ -41608,13 +41608,13 @@
         </is>
       </c>
       <c r="D1248" t="n">
-        <v>44.2</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="E1248" t="n">
-        <v>225.1</v>
+        <v>399.2</v>
       </c>
       <c r="F1248" t="n">
-        <v>9829.200000000001</v>
+        <v>10003.3</v>
       </c>
       <c r="G1248" t="n">
         <v>8</v>
@@ -41641,13 +41641,13 @@
         </is>
       </c>
       <c r="D1249" t="n">
-        <v>71.5</v>
+        <v>143</v>
       </c>
       <c r="E1249" t="n">
-        <v>241.8</v>
+        <v>414.6</v>
       </c>
       <c r="F1249" t="n">
-        <v>7776.8</v>
+        <v>7949.6</v>
       </c>
       <c r="G1249" t="n">
         <v>2</v>
@@ -41674,13 +41674,13 @@
         </is>
       </c>
       <c r="D1250" t="n">
-        <v>49.90000000000001</v>
+        <v>99.80000000000001</v>
       </c>
       <c r="E1250" t="n">
-        <v>254.4</v>
+        <v>467.8</v>
       </c>
       <c r="F1250" t="n">
-        <v>10965.5</v>
+        <v>11178.9</v>
       </c>
       <c r="G1250" t="n">
         <v>8</v>
@@ -41707,19 +41707,19 @@
         </is>
       </c>
       <c r="D1251" t="n">
-        <v>70.40000000000001</v>
+        <v>140.8</v>
       </c>
       <c r="E1251" t="n">
-        <v>317.6</v>
+        <v>603.2</v>
       </c>
       <c r="F1251" t="n">
-        <v>11008.6</v>
+        <v>11294.2</v>
       </c>
       <c r="G1251" t="n">
         <v>5</v>
       </c>
       <c r="H1251" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1251" t="n">
         <v>2</v>
@@ -41740,19 +41740,19 @@
         </is>
       </c>
       <c r="D1252" t="n">
-        <v>57.1</v>
+        <v>114.2</v>
       </c>
       <c r="E1252" t="n">
-        <v>323.3</v>
+        <v>575.6</v>
       </c>
       <c r="F1252" t="n">
-        <v>10188.4</v>
+        <v>10440.7</v>
       </c>
       <c r="G1252" t="n">
         <v>6</v>
       </c>
       <c r="H1252" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1252" t="n">
         <v>4</v>
@@ -41773,13 +41773,13 @@
         </is>
       </c>
       <c r="D1253" t="n">
-        <v>82.7</v>
+        <v>165.4</v>
       </c>
       <c r="E1253" t="n">
-        <v>378.5</v>
+        <v>714</v>
       </c>
       <c r="F1253" t="n">
-        <v>10043.1</v>
+        <v>10378.6</v>
       </c>
       <c r="G1253" t="n">
         <v>2</v>
@@ -41806,13 +41806,13 @@
         </is>
       </c>
       <c r="D1254" t="n">
-        <v>86.5</v>
+        <v>173</v>
       </c>
       <c r="E1254" t="n">
-        <v>352.5</v>
+        <v>626</v>
       </c>
       <c r="F1254" t="n">
-        <v>11287.3</v>
+        <v>11560.8</v>
       </c>
       <c r="G1254" t="n">
         <v>1</v>
@@ -41839,13 +41839,13 @@
         </is>
       </c>
       <c r="D1255" t="n">
-        <v>75.8</v>
+        <v>151.6</v>
       </c>
       <c r="E1255" t="n">
-        <v>269.4</v>
+        <v>483.8</v>
       </c>
       <c r="F1255" t="n">
-        <v>9103.299999999999</v>
+        <v>9317.700000000001</v>
       </c>
       <c r="G1255" t="n">
         <v>4</v>
@@ -41872,13 +41872,13 @@
         </is>
       </c>
       <c r="D1256" t="n">
-        <v>77.7</v>
+        <v>155.4</v>
       </c>
       <c r="E1256" t="n">
-        <v>302.8</v>
+        <v>554.6</v>
       </c>
       <c r="F1256" t="n">
-        <v>9906.9</v>
+        <v>10158.7</v>
       </c>
       <c r="G1256" t="n">
         <v>3</v>
@@ -41905,13 +41905,13 @@
         </is>
       </c>
       <c r="D1257" t="n">
-        <v>55.6</v>
+        <v>111.2</v>
       </c>
       <c r="E1257" t="n">
-        <v>297.4</v>
+        <v>525.8</v>
       </c>
       <c r="F1257" t="n">
-        <v>7832.4</v>
+        <v>8060.8</v>
       </c>
       <c r="G1257" t="n">
         <v>7</v>
@@ -41938,13 +41938,13 @@
         </is>
       </c>
       <c r="D1258" t="n">
-        <v>34.2</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="E1258" t="n">
-        <v>288.6</v>
+        <v>536.2</v>
       </c>
       <c r="F1258" t="n">
-        <v>10999.7</v>
+        <v>11247.3</v>
       </c>
       <c r="G1258" t="n">
         <v>6</v>
@@ -41971,19 +41971,19 @@
         </is>
       </c>
       <c r="D1259" t="n">
-        <v>45.6</v>
+        <v>91.2</v>
       </c>
       <c r="E1259" t="n">
-        <v>363.2</v>
+        <v>694.4</v>
       </c>
       <c r="F1259" t="n">
-        <v>11054.2</v>
+        <v>11385.4</v>
       </c>
       <c r="G1259" t="n">
         <v>5</v>
       </c>
       <c r="H1259" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1259" t="n">
         <v>2</v>
@@ -42004,19 +42004,19 @@
         </is>
       </c>
       <c r="D1260" t="n">
-        <v>56.1</v>
+        <v>112.2</v>
       </c>
       <c r="E1260" t="n">
-        <v>379.4</v>
+        <v>687.8</v>
       </c>
       <c r="F1260" t="n">
-        <v>10244.5</v>
+        <v>10552.9</v>
       </c>
       <c r="G1260" t="n">
         <v>3</v>
       </c>
       <c r="H1260" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1260" t="n">
         <v>4</v>
@@ -42037,13 +42037,13 @@
         </is>
       </c>
       <c r="D1261" t="n">
-        <v>61.7</v>
+        <v>123.4</v>
       </c>
       <c r="E1261" t="n">
-        <v>440.2</v>
+        <v>837.4000000000001</v>
       </c>
       <c r="F1261" t="n">
-        <v>10104.8</v>
+        <v>10502</v>
       </c>
       <c r="G1261" t="n">
         <v>1</v>
@@ -42070,13 +42070,13 @@
         </is>
       </c>
       <c r="D1262" t="n">
-        <v>58.3</v>
+        <v>116.6</v>
       </c>
       <c r="E1262" t="n">
-        <v>410.8</v>
+        <v>742.6</v>
       </c>
       <c r="F1262" t="n">
-        <v>11345.6</v>
+        <v>11677.4</v>
       </c>
       <c r="G1262" t="n">
         <v>2</v>
@@ -42103,13 +42103,13 @@
         </is>
       </c>
       <c r="D1263" t="n">
-        <v>47.9</v>
+        <v>95.8</v>
       </c>
       <c r="E1263" t="n">
-        <v>317.3</v>
+        <v>579.6</v>
       </c>
       <c r="F1263" t="n">
-        <v>9151.200000000001</v>
+        <v>9413.5</v>
       </c>
       <c r="G1263" t="n">
         <v>4</v>
@@ -42136,13 +42136,13 @@
         </is>
       </c>
       <c r="D1264" t="n">
-        <v>32.4</v>
+        <v>64.8</v>
       </c>
       <c r="E1264" t="n">
-        <v>335.2</v>
+        <v>619.4</v>
       </c>
       <c r="F1264" t="n">
-        <v>9939.299999999999</v>
+        <v>10223.5</v>
       </c>
       <c r="G1264" t="n">
         <v>8</v>
@@ -42169,13 +42169,13 @@
         </is>
       </c>
       <c r="D1265" t="n">
-        <v>34.2</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="E1265" t="n">
-        <v>331.6</v>
+        <v>594.2</v>
       </c>
       <c r="F1265" t="n">
-        <v>7866.6</v>
+        <v>8129.2</v>
       </c>
       <c r="G1265" t="n">
         <v>6</v>
@@ -42202,13 +42202,13 @@
         </is>
       </c>
       <c r="D1266" t="n">
-        <v>73.59999999999999</v>
+        <v>147.2</v>
       </c>
       <c r="E1266" t="n">
-        <v>362.2</v>
+        <v>683.4</v>
       </c>
       <c r="F1266" t="n">
-        <v>11073.3</v>
+        <v>11394.5</v>
       </c>
       <c r="G1266" t="n">
         <v>3</v>
@@ -42235,13 +42235,13 @@
         </is>
       </c>
       <c r="D1267" t="n">
-        <v>59.40000000000001</v>
+        <v>118.8</v>
       </c>
       <c r="E1267" t="n">
-        <v>422.6</v>
+        <v>813.2</v>
       </c>
       <c r="F1267" t="n">
-        <v>11113.6</v>
+        <v>11504.2</v>
       </c>
       <c r="G1267" t="n">
         <v>5</v>
@@ -42268,13 +42268,13 @@
         </is>
       </c>
       <c r="D1268" t="n">
-        <v>78.59999999999999</v>
+        <v>157.2</v>
       </c>
       <c r="E1268" t="n">
-        <v>458</v>
+        <v>845</v>
       </c>
       <c r="F1268" t="n">
-        <v>10323.1</v>
+        <v>10710.1</v>
       </c>
       <c r="G1268" t="n">
         <v>1</v>
@@ -42301,13 +42301,13 @@
         </is>
       </c>
       <c r="D1269" t="n">
-        <v>46</v>
+        <v>92</v>
       </c>
       <c r="E1269" t="n">
-        <v>486.2</v>
+        <v>929.4000000000001</v>
       </c>
       <c r="F1269" t="n">
-        <v>10150.8</v>
+        <v>10594</v>
       </c>
       <c r="G1269" t="n">
         <v>8</v>
@@ -42334,13 +42334,13 @@
         </is>
       </c>
       <c r="D1270" t="n">
-        <v>70.09999999999999</v>
+        <v>140.2</v>
       </c>
       <c r="E1270" t="n">
-        <v>480.9</v>
+        <v>882.8</v>
       </c>
       <c r="F1270" t="n">
-        <v>11415.7</v>
+        <v>11817.6</v>
       </c>
       <c r="G1270" t="n">
         <v>4</v>
@@ -42367,13 +42367,13 @@
         </is>
       </c>
       <c r="D1271" t="n">
-        <v>52.5</v>
+        <v>105</v>
       </c>
       <c r="E1271" t="n">
-        <v>369.8</v>
+        <v>684.6</v>
       </c>
       <c r="F1271" t="n">
-        <v>9203.700000000001</v>
+        <v>9518.5</v>
       </c>
       <c r="G1271" t="n">
         <v>7</v>
@@ -42400,13 +42400,13 @@
         </is>
       </c>
       <c r="D1272" t="n">
-        <v>74.90000000000001</v>
+        <v>149.8</v>
       </c>
       <c r="E1272" t="n">
-        <v>410.1</v>
+        <v>769.2</v>
       </c>
       <c r="F1272" t="n">
-        <v>10014.2</v>
+        <v>10373.3</v>
       </c>
       <c r="G1272" t="n">
         <v>2</v>
@@ -42433,13 +42433,13 @@
         </is>
       </c>
       <c r="D1273" t="n">
-        <v>58.2</v>
+        <v>116.4</v>
       </c>
       <c r="E1273" t="n">
-        <v>389.8</v>
+        <v>710.6</v>
       </c>
       <c r="F1273" t="n">
-        <v>7924.8</v>
+        <v>8245.6</v>
       </c>
       <c r="G1273" t="n">
         <v>6</v>
@@ -42466,13 +42466,13 @@
         </is>
       </c>
       <c r="D1274" t="n">
-        <v>53.8</v>
+        <v>107.6</v>
       </c>
       <c r="E1274" t="n">
-        <v>416</v>
+        <v>791</v>
       </c>
       <c r="F1274" t="n">
-        <v>11127.1</v>
+        <v>11502.1</v>
       </c>
       <c r="G1274" t="n">
         <v>7</v>
@@ -42499,19 +42499,19 @@
         </is>
       </c>
       <c r="D1275" t="n">
-        <v>51.1</v>
+        <v>102.2</v>
       </c>
       <c r="E1275" t="n">
-        <v>473.7</v>
+        <v>915.4</v>
       </c>
       <c r="F1275" t="n">
-        <v>11164.7</v>
+        <v>11606.4</v>
       </c>
       <c r="G1275" t="n">
         <v>8</v>
       </c>
       <c r="H1275" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I1275" t="n">
         <v>2</v>
@@ -42532,13 +42532,13 @@
         </is>
       </c>
       <c r="D1276" t="n">
-        <v>62.1</v>
+        <v>124.2</v>
       </c>
       <c r="E1276" t="n">
-        <v>520.1</v>
+        <v>969.2</v>
       </c>
       <c r="F1276" t="n">
-        <v>10385.2</v>
+        <v>10834.3</v>
       </c>
       <c r="G1276" t="n">
         <v>3</v>
@@ -42565,13 +42565,13 @@
         </is>
       </c>
       <c r="D1277" t="n">
-        <v>69.5</v>
+        <v>139</v>
       </c>
       <c r="E1277" t="n">
-        <v>555.7</v>
+        <v>1068.4</v>
       </c>
       <c r="F1277" t="n">
-        <v>10220.3</v>
+        <v>10733</v>
       </c>
       <c r="G1277" t="n">
         <v>1</v>
@@ -42598,13 +42598,13 @@
         </is>
       </c>
       <c r="D1278" t="n">
-        <v>59.5</v>
+        <v>119</v>
       </c>
       <c r="E1278" t="n">
-        <v>540.4</v>
+        <v>1001.8</v>
       </c>
       <c r="F1278" t="n">
-        <v>11475.2</v>
+        <v>11936.6</v>
       </c>
       <c r="G1278" t="n">
         <v>5</v>
@@ -42631,13 +42631,13 @@
         </is>
       </c>
       <c r="D1279" t="n">
-        <v>54.1</v>
+        <v>108.2</v>
       </c>
       <c r="E1279" t="n">
-        <v>423.9</v>
+        <v>792.8</v>
       </c>
       <c r="F1279" t="n">
-        <v>9257.799999999999</v>
+        <v>9626.700000000001</v>
       </c>
       <c r="G1279" t="n">
         <v>6</v>
@@ -42664,19 +42664,19 @@
         </is>
       </c>
       <c r="D1280" t="n">
-        <v>69.2</v>
+        <v>138.4</v>
       </c>
       <c r="E1280" t="n">
-        <v>479.3</v>
+        <v>907.6</v>
       </c>
       <c r="F1280" t="n">
-        <v>10083.4</v>
+        <v>10511.7</v>
       </c>
       <c r="G1280" t="n">
         <v>2</v>
       </c>
       <c r="H1280" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I1280" t="n">
         <v>6</v>
@@ -42697,13 +42697,13 @@
         </is>
       </c>
       <c r="D1281" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="E1281" t="n">
-        <v>449.8</v>
+        <v>830.6</v>
       </c>
       <c r="F1281" t="n">
-        <v>7984.8</v>
+        <v>8365.6</v>
       </c>
       <c r="G1281" t="n">
         <v>4</v>
@@ -42730,13 +42730,13 @@
         </is>
       </c>
       <c r="D1282" t="n">
-        <v>87.8</v>
+        <v>175.6</v>
       </c>
       <c r="E1282" t="n">
-        <v>503.8</v>
+        <v>966.6</v>
       </c>
       <c r="F1282" t="n">
-        <v>11214.9</v>
+        <v>11677.7</v>
       </c>
       <c r="G1282" t="n">
         <v>1</v>
@@ -42763,13 +42763,13 @@
         </is>
       </c>
       <c r="D1283" t="n">
-        <v>67</v>
+        <v>134</v>
       </c>
       <c r="E1283" t="n">
-        <v>540.7</v>
+        <v>1049.4</v>
       </c>
       <c r="F1283" t="n">
-        <v>11231.7</v>
+        <v>11740.4</v>
       </c>
       <c r="G1283" t="n">
         <v>4</v>
@@ -42796,13 +42796,13 @@
         </is>
       </c>
       <c r="D1284" t="n">
-        <v>55.4</v>
+        <v>110.8</v>
       </c>
       <c r="E1284" t="n">
-        <v>575.5</v>
+        <v>1080</v>
       </c>
       <c r="F1284" t="n">
-        <v>10440.6</v>
+        <v>10945.1</v>
       </c>
       <c r="G1284" t="n">
         <v>7</v>
@@ -42829,13 +42829,13 @@
         </is>
       </c>
       <c r="D1285" t="n">
-        <v>57.6</v>
+        <v>115.2</v>
       </c>
       <c r="E1285" t="n">
-        <v>613.3000000000001</v>
+        <v>1183.6</v>
       </c>
       <c r="F1285" t="n">
-        <v>10277.9</v>
+        <v>10848.2</v>
       </c>
       <c r="G1285" t="n">
         <v>6</v>
@@ -42862,13 +42862,13 @@
         </is>
       </c>
       <c r="D1286" t="n">
-        <v>66.3</v>
+        <v>132.6</v>
       </c>
       <c r="E1286" t="n">
-        <v>606.7</v>
+        <v>1134.4</v>
       </c>
       <c r="F1286" t="n">
-        <v>11541.5</v>
+        <v>12069.2</v>
       </c>
       <c r="G1286" t="n">
         <v>5</v>
@@ -42895,13 +42895,13 @@
         </is>
       </c>
       <c r="D1287" t="n">
-        <v>52.1</v>
+        <v>104.2</v>
       </c>
       <c r="E1287" t="n">
-        <v>476</v>
+        <v>897</v>
       </c>
       <c r="F1287" t="n">
-        <v>9309.9</v>
+        <v>9730.9</v>
       </c>
       <c r="G1287" t="n">
         <v>8</v>
@@ -42928,13 +42928,13 @@
         </is>
       </c>
       <c r="D1288" t="n">
-        <v>81.09999999999999</v>
+        <v>162.2</v>
       </c>
       <c r="E1288" t="n">
-        <v>560.4</v>
+        <v>1069.8</v>
       </c>
       <c r="F1288" t="n">
-        <v>10164.5</v>
+        <v>10673.9</v>
       </c>
       <c r="G1288" t="n">
         <v>2</v>
@@ -42961,13 +42961,13 @@
         </is>
       </c>
       <c r="D1289" t="n">
-        <v>76.89999999999999</v>
+        <v>153.8</v>
       </c>
       <c r="E1289" t="n">
-        <v>526.7</v>
+        <v>984.4</v>
       </c>
       <c r="F1289" t="n">
-        <v>8061.7</v>
+        <v>8519.4</v>
       </c>
       <c r="G1289" t="n">
         <v>3</v>
@@ -42994,22 +42994,22 @@
         </is>
       </c>
       <c r="D1290" t="n">
-        <v>77.90000000000001</v>
+        <v>155.8</v>
       </c>
       <c r="E1290" t="n">
-        <v>581.7</v>
+        <v>1122.4</v>
       </c>
       <c r="F1290" t="n">
-        <v>11292.8</v>
+        <v>11833.5</v>
       </c>
       <c r="G1290" t="n">
         <v>1</v>
       </c>
       <c r="H1290" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I1290" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1291">
@@ -43027,13 +43027,13 @@
         </is>
       </c>
       <c r="D1291" t="n">
-        <v>54.8</v>
+        <v>109.6</v>
       </c>
       <c r="E1291" t="n">
-        <v>595.5</v>
+        <v>1159</v>
       </c>
       <c r="F1291" t="n">
-        <v>11286.5</v>
+        <v>11850</v>
       </c>
       <c r="G1291" t="n">
         <v>7</v>
@@ -43042,7 +43042,7 @@
         <v>5</v>
       </c>
       <c r="I1291" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1292">
@@ -43060,13 +43060,13 @@
         </is>
       </c>
       <c r="D1292" t="n">
-        <v>68.8</v>
+        <v>137.6</v>
       </c>
       <c r="E1292" t="n">
-        <v>644.3</v>
+        <v>1217.6</v>
       </c>
       <c r="F1292" t="n">
-        <v>10509.4</v>
+        <v>11082.7</v>
       </c>
       <c r="G1292" t="n">
         <v>3</v>
@@ -43093,13 +43093,13 @@
         </is>
       </c>
       <c r="D1293" t="n">
-        <v>60.2</v>
+        <v>120.4</v>
       </c>
       <c r="E1293" t="n">
-        <v>673.5</v>
+        <v>1304</v>
       </c>
       <c r="F1293" t="n">
-        <v>10338.1</v>
+        <v>10968.6</v>
       </c>
       <c r="G1293" t="n">
         <v>6</v>
@@ -43126,13 +43126,13 @@
         </is>
       </c>
       <c r="D1294" t="n">
-        <v>62.8</v>
+        <v>125.6</v>
       </c>
       <c r="E1294" t="n">
-        <v>669.5</v>
+        <v>1260</v>
       </c>
       <c r="F1294" t="n">
-        <v>11604.3</v>
+        <v>12194.8</v>
       </c>
       <c r="G1294" t="n">
         <v>5</v>
@@ -43159,13 +43159,13 @@
         </is>
       </c>
       <c r="D1295" t="n">
-        <v>50.9</v>
+        <v>101.8</v>
       </c>
       <c r="E1295" t="n">
-        <v>526.9</v>
+        <v>998.8</v>
       </c>
       <c r="F1295" t="n">
-        <v>9360.799999999999</v>
+        <v>9832.700000000001</v>
       </c>
       <c r="G1295" t="n">
         <v>8</v>
@@ -43192,13 +43192,13 @@
         </is>
       </c>
       <c r="D1296" t="n">
-        <v>69.40000000000001</v>
+        <v>138.8</v>
       </c>
       <c r="E1296" t="n">
-        <v>629.8000000000001</v>
+        <v>1208.6</v>
       </c>
       <c r="F1296" t="n">
-        <v>10233.9</v>
+        <v>10812.7</v>
       </c>
       <c r="G1296" t="n">
         <v>2</v>
@@ -43225,19 +43225,19 @@
         </is>
       </c>
       <c r="D1297" t="n">
-        <v>66.3</v>
+        <v>132.6</v>
       </c>
       <c r="E1297" t="n">
-        <v>593</v>
+        <v>1117</v>
       </c>
       <c r="F1297" t="n">
-        <v>8128</v>
+        <v>8652</v>
       </c>
       <c r="G1297" t="n">
         <v>4</v>
       </c>
       <c r="H1297" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1297" t="n">
         <v>8</v>
@@ -43258,13 +43258,13 @@
         </is>
       </c>
       <c r="D1298" t="n">
-        <v>68</v>
+        <v>136</v>
       </c>
       <c r="E1298" t="n">
-        <v>649.7</v>
+        <v>1258.4</v>
       </c>
       <c r="F1298" t="n">
-        <v>11360.8</v>
+        <v>11969.5</v>
       </c>
       <c r="G1298" t="n">
         <v>5</v>
@@ -43291,19 +43291,19 @@
         </is>
       </c>
       <c r="D1299" t="n">
-        <v>89.2</v>
+        <v>178.4</v>
       </c>
       <c r="E1299" t="n">
-        <v>684.7</v>
+        <v>1337.4</v>
       </c>
       <c r="F1299" t="n">
-        <v>11375.7</v>
+        <v>12028.4</v>
       </c>
       <c r="G1299" t="n">
         <v>2</v>
       </c>
       <c r="H1299" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I1299" t="n">
         <v>2</v>
@@ -43324,19 +43324,19 @@
         </is>
       </c>
       <c r="D1300" t="n">
-        <v>79.3</v>
+        <v>158.6</v>
       </c>
       <c r="E1300" t="n">
-        <v>723.6</v>
+        <v>1376.2</v>
       </c>
       <c r="F1300" t="n">
-        <v>10588.7</v>
+        <v>11241.3</v>
       </c>
       <c r="G1300" t="n">
         <v>3</v>
       </c>
       <c r="H1300" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I1300" t="n">
         <v>4</v>
@@ -43357,13 +43357,13 @@
         </is>
       </c>
       <c r="D1301" t="n">
-        <v>61</v>
+        <v>122</v>
       </c>
       <c r="E1301" t="n">
-        <v>734.5</v>
+        <v>1426</v>
       </c>
       <c r="F1301" t="n">
-        <v>10399.1</v>
+        <v>11090.6</v>
       </c>
       <c r="G1301" t="n">
         <v>6</v>
@@ -43390,19 +43390,19 @@
         </is>
       </c>
       <c r="D1302" t="n">
-        <v>57.4</v>
+        <v>114.8</v>
       </c>
       <c r="E1302" t="n">
-        <v>726.9</v>
+        <v>1374.8</v>
       </c>
       <c r="F1302" t="n">
-        <v>11661.7</v>
+        <v>12309.6</v>
       </c>
       <c r="G1302" t="n">
         <v>7</v>
       </c>
       <c r="H1302" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I1302" t="n">
         <v>1</v>
@@ -43423,13 +43423,13 @@
         </is>
       </c>
       <c r="D1303" t="n">
-        <v>46.4</v>
+        <v>92.8</v>
       </c>
       <c r="E1303" t="n">
-        <v>573.3</v>
+        <v>1091.6</v>
       </c>
       <c r="F1303" t="n">
-        <v>9407.200000000001</v>
+        <v>9925.5</v>
       </c>
       <c r="G1303" t="n">
         <v>8</v>
@@ -43456,13 +43456,13 @@
         </is>
       </c>
       <c r="D1304" t="n">
-        <v>77.2</v>
+        <v>154.4</v>
       </c>
       <c r="E1304" t="n">
-        <v>707</v>
+        <v>1363</v>
       </c>
       <c r="F1304" t="n">
-        <v>10311.1</v>
+        <v>10967.1</v>
       </c>
       <c r="G1304" t="n">
         <v>4</v>
@@ -43489,19 +43489,19 @@
         </is>
       </c>
       <c r="D1305" t="n">
-        <v>95.2</v>
+        <v>190.4</v>
       </c>
       <c r="E1305" t="n">
-        <v>688.2</v>
+        <v>1307.4</v>
       </c>
       <c r="F1305" t="n">
-        <v>8223.200000000001</v>
+        <v>8842.4</v>
       </c>
       <c r="G1305" t="n">
         <v>1</v>
       </c>
       <c r="H1305" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I1305" t="n">
         <v>8</v>
@@ -43522,13 +43522,13 @@
         </is>
       </c>
       <c r="D1306" t="n">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="E1306" t="n">
-        <v>727.7</v>
+        <v>1414.4</v>
       </c>
       <c r="F1306" t="n">
-        <v>11438.8</v>
+        <v>12125.5</v>
       </c>
       <c r="G1306" t="n">
         <v>3</v>
@@ -43555,19 +43555,19 @@
         </is>
       </c>
       <c r="D1307" t="n">
-        <v>78.59999999999999</v>
+        <v>157.2</v>
       </c>
       <c r="E1307" t="n">
-        <v>763.3</v>
+        <v>1494.6</v>
       </c>
       <c r="F1307" t="n">
-        <v>11454.3</v>
+        <v>12185.6</v>
       </c>
       <c r="G1307" t="n">
         <v>2</v>
       </c>
       <c r="H1307" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I1307" t="n">
         <v>2</v>
@@ -43588,13 +43588,13 @@
         </is>
       </c>
       <c r="D1308" t="n">
-        <v>76.90000000000001</v>
+        <v>153.8</v>
       </c>
       <c r="E1308" t="n">
-        <v>800.5</v>
+        <v>1530</v>
       </c>
       <c r="F1308" t="n">
-        <v>10665.6</v>
+        <v>11395.1</v>
       </c>
       <c r="G1308" t="n">
         <v>4</v>
@@ -43621,19 +43621,19 @@
         </is>
       </c>
       <c r="D1309" t="n">
-        <v>48.40000000000001</v>
+        <v>96.8</v>
       </c>
       <c r="E1309" t="n">
-        <v>782.9</v>
+        <v>1522.8</v>
       </c>
       <c r="F1309" t="n">
-        <v>10447.5</v>
+        <v>11187.4</v>
       </c>
       <c r="G1309" t="n">
         <v>8</v>
       </c>
       <c r="H1309" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I1309" t="n">
         <v>5</v>
@@ -43654,19 +43654,19 @@
         </is>
       </c>
       <c r="D1310" t="n">
-        <v>67.59999999999999</v>
+        <v>135.2</v>
       </c>
       <c r="E1310" t="n">
-        <v>794.5</v>
+        <v>1510</v>
       </c>
       <c r="F1310" t="n">
-        <v>11729.3</v>
+        <v>12444.8</v>
       </c>
       <c r="G1310" t="n">
         <v>5</v>
       </c>
       <c r="H1310" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I1310" t="n">
         <v>1</v>
@@ -43687,13 +43687,13 @@
         </is>
       </c>
       <c r="D1311" t="n">
-        <v>58.1</v>
+        <v>116.2</v>
       </c>
       <c r="E1311" t="n">
-        <v>631.4</v>
+        <v>1207.8</v>
       </c>
       <c r="F1311" t="n">
-        <v>9465.299999999999</v>
+        <v>10041.7</v>
       </c>
       <c r="G1311" t="n">
         <v>7</v>
@@ -43720,13 +43720,13 @@
         </is>
       </c>
       <c r="D1312" t="n">
-        <v>61.4</v>
+        <v>122.8</v>
       </c>
       <c r="E1312" t="n">
-        <v>768.4</v>
+        <v>1485.8</v>
       </c>
       <c r="F1312" t="n">
-        <v>10372.5</v>
+        <v>11089.9</v>
       </c>
       <c r="G1312" t="n">
         <v>6</v>
@@ -43753,19 +43753,19 @@
         </is>
       </c>
       <c r="D1313" t="n">
-        <v>81.59999999999999</v>
+        <v>163.2</v>
       </c>
       <c r="E1313" t="n">
-        <v>769.8</v>
+        <v>1470.6</v>
       </c>
       <c r="F1313" t="n">
-        <v>8304.799999999999</v>
+        <v>9005.6</v>
       </c>
       <c r="G1313" t="n">
         <v>1</v>
       </c>
       <c r="H1313" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I1313" t="n">
         <v>8</v>
@@ -43786,13 +43786,13 @@
         </is>
       </c>
       <c r="D1314" t="n">
-        <v>67.5</v>
+        <v>135</v>
       </c>
       <c r="E1314" t="n">
-        <v>795.2</v>
+        <v>1549.4</v>
       </c>
       <c r="F1314" t="n">
-        <v>11506.3</v>
+        <v>12260.5</v>
       </c>
       <c r="G1314" t="n">
         <v>5</v>
@@ -43819,19 +43819,19 @@
         </is>
       </c>
       <c r="D1315" t="n">
-        <v>69.8</v>
+        <v>139.6</v>
       </c>
       <c r="E1315" t="n">
-        <v>833.1</v>
+        <v>1634.2</v>
       </c>
       <c r="F1315" t="n">
-        <v>11524.1</v>
+        <v>12325.2</v>
       </c>
       <c r="G1315" t="n">
         <v>2</v>
       </c>
       <c r="H1315" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I1315" t="n">
         <v>2</v>
@@ -43852,13 +43852,13 @@
         </is>
       </c>
       <c r="D1316" t="n">
-        <v>68.3</v>
+        <v>136.6</v>
       </c>
       <c r="E1316" t="n">
-        <v>868.8</v>
+        <v>1666.6</v>
       </c>
       <c r="F1316" t="n">
-        <v>10733.9</v>
+        <v>11531.7</v>
       </c>
       <c r="G1316" t="n">
         <v>3</v>
@@ -43885,13 +43885,13 @@
         </is>
       </c>
       <c r="D1317" t="n">
-        <v>52.1</v>
+        <v>104.2</v>
       </c>
       <c r="E1317" t="n">
-        <v>835</v>
+        <v>1627</v>
       </c>
       <c r="F1317" t="n">
-        <v>10499.6</v>
+        <v>11291.6</v>
       </c>
       <c r="G1317" t="n">
         <v>8</v>
@@ -43918,13 +43918,13 @@
         </is>
       </c>
       <c r="D1318" t="n">
-        <v>79.7</v>
+        <v>159.4</v>
       </c>
       <c r="E1318" t="n">
-        <v>874.2</v>
+        <v>1669.4</v>
       </c>
       <c r="F1318" t="n">
-        <v>11809</v>
+        <v>12604.2</v>
       </c>
       <c r="G1318" t="n">
         <v>1</v>
@@ -43951,13 +43951,13 @@
         </is>
       </c>
       <c r="D1319" t="n">
-        <v>58</v>
+        <v>116</v>
       </c>
       <c r="E1319" t="n">
-        <v>689.4</v>
+        <v>1323.8</v>
       </c>
       <c r="F1319" t="n">
-        <v>9523.299999999999</v>
+        <v>10157.7</v>
       </c>
       <c r="G1319" t="n">
         <v>7</v>
@@ -43984,13 +43984,13 @@
         </is>
       </c>
       <c r="D1320" t="n">
-        <v>59.5</v>
+        <v>119</v>
       </c>
       <c r="E1320" t="n">
-        <v>827.9</v>
+        <v>1604.8</v>
       </c>
       <c r="F1320" t="n">
-        <v>10432</v>
+        <v>11208.9</v>
       </c>
       <c r="G1320" t="n">
         <v>6</v>
@@ -44017,19 +44017,19 @@
         </is>
       </c>
       <c r="D1321" t="n">
-        <v>68.10000000000001</v>
+        <v>136.2</v>
       </c>
       <c r="E1321" t="n">
-        <v>837.9</v>
+        <v>1606.8</v>
       </c>
       <c r="F1321" t="n">
-        <v>8372.9</v>
+        <v>9141.799999999999</v>
       </c>
       <c r="G1321" t="n">
         <v>4</v>
       </c>
       <c r="H1321" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I1321" t="n">
         <v>8</v>
@@ -44050,13 +44050,13 @@
         </is>
       </c>
       <c r="D1322" t="n">
-        <v>58.6</v>
+        <v>117.2</v>
       </c>
       <c r="E1322" t="n">
-        <v>853.8</v>
+        <v>1666.6</v>
       </c>
       <c r="F1322" t="n">
-        <v>11564.9</v>
+        <v>12377.7</v>
       </c>
       <c r="G1322" t="n">
         <v>6</v>
@@ -44083,19 +44083,19 @@
         </is>
       </c>
       <c r="D1323" t="n">
-        <v>105.7</v>
+        <v>211.4</v>
       </c>
       <c r="E1323" t="n">
-        <v>938.8</v>
+        <v>1845.6</v>
       </c>
       <c r="F1323" t="n">
-        <v>11629.8</v>
+        <v>12536.6</v>
       </c>
       <c r="G1323" t="n">
         <v>1</v>
       </c>
       <c r="H1323" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1323" t="n">
         <v>2</v>
@@ -44116,13 +44116,13 @@
         </is>
       </c>
       <c r="D1324" t="n">
-        <v>58.4</v>
+        <v>116.8</v>
       </c>
       <c r="E1324" t="n">
-        <v>927.2</v>
+        <v>1783.4</v>
       </c>
       <c r="F1324" t="n">
-        <v>10792.3</v>
+        <v>11648.5</v>
       </c>
       <c r="G1324" t="n">
         <v>7</v>
@@ -44149,13 +44149,13 @@
         </is>
       </c>
       <c r="D1325" t="n">
-        <v>57.4</v>
+        <v>114.8</v>
       </c>
       <c r="E1325" t="n">
-        <v>892.4</v>
+        <v>1741.8</v>
       </c>
       <c r="F1325" t="n">
-        <v>10557</v>
+        <v>11406.4</v>
       </c>
       <c r="G1325" t="n">
         <v>8</v>
@@ -44182,19 +44182,19 @@
         </is>
       </c>
       <c r="D1326" t="n">
-        <v>83.40000000000001</v>
+        <v>166.8</v>
       </c>
       <c r="E1326" t="n">
-        <v>957.6</v>
+        <v>1836.2</v>
       </c>
       <c r="F1326" t="n">
-        <v>11892.4</v>
+        <v>12771</v>
       </c>
       <c r="G1326" t="n">
         <v>3</v>
       </c>
       <c r="H1326" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1326" t="n">
         <v>1</v>
@@ -44215,13 +44215,13 @@
         </is>
       </c>
       <c r="D1327" t="n">
-        <v>74.3</v>
+        <v>148.6</v>
       </c>
       <c r="E1327" t="n">
-        <v>763.7</v>
+        <v>1472.4</v>
       </c>
       <c r="F1327" t="n">
-        <v>9597.6</v>
+        <v>10306.3</v>
       </c>
       <c r="G1327" t="n">
         <v>4</v>
@@ -44248,13 +44248,13 @@
         </is>
       </c>
       <c r="D1328" t="n">
-        <v>72</v>
+        <v>144</v>
       </c>
       <c r="E1328" t="n">
-        <v>899.9000000000001</v>
+        <v>1748.8</v>
       </c>
       <c r="F1328" t="n">
-        <v>10504</v>
+        <v>11352.9</v>
       </c>
       <c r="G1328" t="n">
         <v>5</v>
@@ -44281,13 +44281,13 @@
         </is>
       </c>
       <c r="D1329" t="n">
-        <v>87.09999999999999</v>
+        <v>174.2</v>
       </c>
       <c r="E1329" t="n">
-        <v>925</v>
+        <v>1781</v>
       </c>
       <c r="F1329" t="n">
-        <v>8460</v>
+        <v>9316</v>
       </c>
       <c r="G1329" t="n">
         <v>2</v>
@@ -44314,13 +44314,13 @@
         </is>
       </c>
       <c r="D1330" t="n">
-        <v>61.2</v>
+        <v>122.4</v>
       </c>
       <c r="E1330" t="n">
-        <v>915</v>
+        <v>1789</v>
       </c>
       <c r="F1330" t="n">
-        <v>11626.1</v>
+        <v>12500.1</v>
       </c>
       <c r="G1330" t="n">
         <v>5</v>
@@ -44347,13 +44347,13 @@
         </is>
       </c>
       <c r="D1331" t="n">
-        <v>55.6</v>
+        <v>111.2</v>
       </c>
       <c r="E1331" t="n">
-        <v>994.4</v>
+        <v>1956.8</v>
       </c>
       <c r="F1331" t="n">
-        <v>11685.4</v>
+        <v>12647.8</v>
       </c>
       <c r="G1331" t="n">
         <v>7</v>
@@ -44380,13 +44380,13 @@
         </is>
       </c>
       <c r="D1332" t="n">
-        <v>50.59999999999999</v>
+        <v>101.2</v>
       </c>
       <c r="E1332" t="n">
-        <v>977.8</v>
+        <v>1884.6</v>
       </c>
       <c r="F1332" t="n">
-        <v>10842.9</v>
+        <v>11749.7</v>
       </c>
       <c r="G1332" t="n">
         <v>8</v>
@@ -44413,13 +44413,13 @@
         </is>
       </c>
       <c r="D1333" t="n">
-        <v>62.4</v>
+        <v>124.8</v>
       </c>
       <c r="E1333" t="n">
-        <v>954.8000000000001</v>
+        <v>1866.6</v>
       </c>
       <c r="F1333" t="n">
-        <v>10619.4</v>
+        <v>11531.2</v>
       </c>
       <c r="G1333" t="n">
         <v>4</v>
@@ -44446,13 +44446,13 @@
         </is>
       </c>
       <c r="D1334" t="n">
-        <v>81.90000000000001</v>
+        <v>163.8</v>
       </c>
       <c r="E1334" t="n">
-        <v>1039.5</v>
+        <v>2000</v>
       </c>
       <c r="F1334" t="n">
-        <v>11974.3</v>
+        <v>12934.8</v>
       </c>
       <c r="G1334" t="n">
         <v>2</v>
@@ -44479,13 +44479,13 @@
         </is>
       </c>
       <c r="D1335" t="n">
-        <v>63.3</v>
+        <v>126.6</v>
       </c>
       <c r="E1335" t="n">
-        <v>827</v>
+        <v>1599</v>
       </c>
       <c r="F1335" t="n">
-        <v>9660.9</v>
+        <v>10432.9</v>
       </c>
       <c r="G1335" t="n">
         <v>3</v>
@@ -44512,13 +44512,13 @@
         </is>
       </c>
       <c r="D1336" t="n">
-        <v>86</v>
+        <v>172</v>
       </c>
       <c r="E1336" t="n">
-        <v>985.9000000000001</v>
+        <v>1920.8</v>
       </c>
       <c r="F1336" t="n">
-        <v>10590</v>
+        <v>11524.9</v>
       </c>
       <c r="G1336" t="n">
         <v>1</v>
@@ -44545,13 +44545,13 @@
         </is>
       </c>
       <c r="D1337" t="n">
-        <v>58.1</v>
+        <v>116.2</v>
       </c>
       <c r="E1337" t="n">
-        <v>983.1</v>
+        <v>1897.2</v>
       </c>
       <c r="F1337" t="n">
-        <v>8518.1</v>
+        <v>9432.200000000001</v>
       </c>
       <c r="G1337" t="n">
         <v>6</v>
@@ -44578,13 +44578,13 @@
         </is>
       </c>
       <c r="D1338" t="n">
-        <v>64.2</v>
+        <v>128.4</v>
       </c>
       <c r="E1338" t="n">
-        <v>979.2</v>
+        <v>1917.4</v>
       </c>
       <c r="F1338" t="n">
-        <v>11690.3</v>
+        <v>12628.5</v>
       </c>
       <c r="G1338" t="n">
         <v>5</v>
@@ -44611,13 +44611,13 @@
         </is>
       </c>
       <c r="D1339" t="n">
-        <v>88.7</v>
+        <v>177.4</v>
       </c>
       <c r="E1339" t="n">
-        <v>1083.1</v>
+        <v>2134.2</v>
       </c>
       <c r="F1339" t="n">
-        <v>11774.1</v>
+        <v>12825.2</v>
       </c>
       <c r="G1339" t="n">
         <v>1</v>
@@ -44644,19 +44644,19 @@
         </is>
       </c>
       <c r="D1340" t="n">
-        <v>76.8</v>
+        <v>153.6</v>
       </c>
       <c r="E1340" t="n">
-        <v>1054.6</v>
+        <v>2038.2</v>
       </c>
       <c r="F1340" t="n">
-        <v>10919.7</v>
+        <v>11903.3</v>
       </c>
       <c r="G1340" t="n">
         <v>3</v>
       </c>
       <c r="H1340" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1340" t="n">
         <v>4</v>
@@ -44677,13 +44677,13 @@
         </is>
       </c>
       <c r="D1341" t="n">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="E1341" t="n">
-        <v>999.8000000000001</v>
+        <v>1956.6</v>
       </c>
       <c r="F1341" t="n">
-        <v>10664.4</v>
+        <v>11621.2</v>
       </c>
       <c r="G1341" t="n">
         <v>8</v>
@@ -44692,7 +44692,7 @@
         <v>6</v>
       </c>
       <c r="I1341" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1342">
@@ -44710,13 +44710,13 @@
         </is>
       </c>
       <c r="D1342" t="n">
-        <v>81.2</v>
+        <v>162.4</v>
       </c>
       <c r="E1342" t="n">
-        <v>1120.7</v>
+        <v>2162.4</v>
       </c>
       <c r="F1342" t="n">
-        <v>12055.5</v>
+        <v>13097.2</v>
       </c>
       <c r="G1342" t="n">
         <v>2</v>
@@ -44743,13 +44743,13 @@
         </is>
       </c>
       <c r="D1343" t="n">
-        <v>63.7</v>
+        <v>127.4</v>
       </c>
       <c r="E1343" t="n">
-        <v>890.7</v>
+        <v>1726.4</v>
       </c>
       <c r="F1343" t="n">
-        <v>9724.6</v>
+        <v>10560.3</v>
       </c>
       <c r="G1343" t="n">
         <v>6</v>
@@ -44776,22 +44776,22 @@
         </is>
       </c>
       <c r="D1344" t="n">
-        <v>67.7</v>
+        <v>135.4</v>
       </c>
       <c r="E1344" t="n">
-        <v>1053.6</v>
+        <v>2056.2</v>
       </c>
       <c r="F1344" t="n">
-        <v>10657.7</v>
+        <v>11660.3</v>
       </c>
       <c r="G1344" t="n">
         <v>4</v>
       </c>
       <c r="H1344" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1344" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1345">
@@ -44809,13 +44809,13 @@
         </is>
       </c>
       <c r="D1345" t="n">
-        <v>60.2</v>
+        <v>120.4</v>
       </c>
       <c r="E1345" t="n">
-        <v>1043.3</v>
+        <v>2017.6</v>
       </c>
       <c r="F1345" t="n">
-        <v>8578.299999999999</v>
+        <v>9552.6</v>
       </c>
       <c r="G1345" t="n">
         <v>7</v>
@@ -44842,13 +44842,13 @@
         </is>
       </c>
       <c r="D1346" t="n">
-        <v>88.09999999999999</v>
+        <v>176.2</v>
       </c>
       <c r="E1346" t="n">
-        <v>1067.3</v>
+        <v>2093.6</v>
       </c>
       <c r="F1346" t="n">
-        <v>11778.4</v>
+        <v>12804.7</v>
       </c>
       <c r="G1346" t="n">
         <v>3</v>
@@ -44875,13 +44875,13 @@
         </is>
       </c>
       <c r="D1347" t="n">
-        <v>59.9</v>
+        <v>119.8</v>
       </c>
       <c r="E1347" t="n">
-        <v>1143</v>
+        <v>2254</v>
       </c>
       <c r="F1347" t="n">
-        <v>11834</v>
+        <v>12945</v>
       </c>
       <c r="G1347" t="n">
         <v>6</v>
@@ -44908,13 +44908,13 @@
         </is>
       </c>
       <c r="D1348" t="n">
-        <v>70.2</v>
+        <v>140.4</v>
       </c>
       <c r="E1348" t="n">
-        <v>1124.8</v>
+        <v>2178.6</v>
       </c>
       <c r="F1348" t="n">
-        <v>10989.9</v>
+        <v>12043.7</v>
       </c>
       <c r="G1348" t="n">
         <v>4</v>
@@ -44944,10 +44944,10 @@
         <v>0</v>
       </c>
       <c r="E1349" t="n">
-        <v>999.8000000000001</v>
+        <v>1956.6</v>
       </c>
       <c r="F1349" t="n">
-        <v>10664.4</v>
+        <v>11621.2</v>
       </c>
       <c r="G1349" t="n">
         <v>8</v>
@@ -44974,13 +44974,13 @@
         </is>
       </c>
       <c r="D1350" t="n">
-        <v>94</v>
+        <v>188</v>
       </c>
       <c r="E1350" t="n">
-        <v>1214.7</v>
+        <v>2350.4</v>
       </c>
       <c r="F1350" t="n">
-        <v>12149.5</v>
+        <v>13285.2</v>
       </c>
       <c r="G1350" t="n">
         <v>1</v>
@@ -45007,13 +45007,13 @@
         </is>
       </c>
       <c r="D1351" t="n">
-        <v>61.6</v>
+        <v>123.2</v>
       </c>
       <c r="E1351" t="n">
-        <v>952.3</v>
+        <v>1849.6</v>
       </c>
       <c r="F1351" t="n">
-        <v>9786.200000000001</v>
+        <v>10683.5</v>
       </c>
       <c r="G1351" t="n">
         <v>5</v>
@@ -45040,13 +45040,13 @@
         </is>
       </c>
       <c r="D1352" t="n">
-        <v>58.6</v>
+        <v>117.2</v>
       </c>
       <c r="E1352" t="n">
-        <v>1112.2</v>
+        <v>2173.4</v>
       </c>
       <c r="F1352" t="n">
-        <v>10716.3</v>
+        <v>11777.5</v>
       </c>
       <c r="G1352" t="n">
         <v>7</v>
@@ -45073,13 +45073,13 @@
         </is>
       </c>
       <c r="D1353" t="n">
-        <v>89.5</v>
+        <v>179</v>
       </c>
       <c r="E1353" t="n">
-        <v>1132.8</v>
+        <v>2196.6</v>
       </c>
       <c r="F1353" t="n">
-        <v>8667.799999999999</v>
+        <v>9731.6</v>
       </c>
       <c r="G1353" t="n">
         <v>2</v>
@@ -45106,13 +45106,13 @@
         </is>
       </c>
       <c r="D1354" t="n">
-        <v>66.7</v>
+        <v>133.4</v>
       </c>
       <c r="E1354" t="n">
-        <v>1134</v>
+        <v>2227</v>
       </c>
       <c r="F1354" t="n">
-        <v>11845.1</v>
+        <v>12938.1</v>
       </c>
       <c r="G1354" t="n">
         <v>4</v>
@@ -45139,19 +45139,19 @@
         </is>
       </c>
       <c r="D1355" t="n">
-        <v>35.8</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="E1355" t="n">
-        <v>1178.8</v>
+        <v>2325.6</v>
       </c>
       <c r="F1355" t="n">
-        <v>11869.8</v>
+        <v>13016.6</v>
       </c>
       <c r="G1355" t="n">
         <v>8</v>
       </c>
       <c r="H1355" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I1355" t="n">
         <v>2</v>
@@ -45172,19 +45172,19 @@
         </is>
       </c>
       <c r="D1356" t="n">
-        <v>59.2</v>
+        <v>118.4</v>
       </c>
       <c r="E1356" t="n">
-        <v>1184</v>
+        <v>2297</v>
       </c>
       <c r="F1356" t="n">
-        <v>11049.1</v>
+        <v>12162.1</v>
       </c>
       <c r="G1356" t="n">
         <v>6</v>
       </c>
       <c r="H1356" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I1356" t="n">
         <v>4</v>
@@ -45205,13 +45205,13 @@
         </is>
       </c>
       <c r="D1357" t="n">
-        <v>82.2</v>
+        <v>164.4</v>
       </c>
       <c r="E1357" t="n">
-        <v>1082</v>
+        <v>2121</v>
       </c>
       <c r="F1357" t="n">
-        <v>10746.6</v>
+        <v>11785.6</v>
       </c>
       <c r="G1357" t="n">
         <v>2</v>
@@ -45238,13 +45238,13 @@
         </is>
       </c>
       <c r="D1358" t="n">
-        <v>63</v>
+        <v>126</v>
       </c>
       <c r="E1358" t="n">
-        <v>1277.7</v>
+        <v>2476.4</v>
       </c>
       <c r="F1358" t="n">
-        <v>12212.5</v>
+        <v>13411.2</v>
       </c>
       <c r="G1358" t="n">
         <v>5</v>
@@ -45271,13 +45271,13 @@
         </is>
       </c>
       <c r="D1359" t="n">
-        <v>56.6</v>
+        <v>113.2</v>
       </c>
       <c r="E1359" t="n">
-        <v>1008.9</v>
+        <v>1962.8</v>
       </c>
       <c r="F1359" t="n">
-        <v>9842.799999999999</v>
+        <v>10796.7</v>
       </c>
       <c r="G1359" t="n">
         <v>7</v>
@@ -45304,13 +45304,13 @@
         </is>
       </c>
       <c r="D1360" t="n">
-        <v>78.59999999999999</v>
+        <v>157.2</v>
       </c>
       <c r="E1360" t="n">
-        <v>1190.8</v>
+        <v>2330.6</v>
       </c>
       <c r="F1360" t="n">
-        <v>10794.9</v>
+        <v>11934.7</v>
       </c>
       <c r="G1360" t="n">
         <v>3</v>
@@ -45337,13 +45337,13 @@
         </is>
       </c>
       <c r="D1361" t="n">
-        <v>87.3</v>
+        <v>174.6</v>
       </c>
       <c r="E1361" t="n">
-        <v>1220.1</v>
+        <v>2371.2</v>
       </c>
       <c r="F1361" t="n">
-        <v>8755.1</v>
+        <v>9906.200000000001</v>
       </c>
       <c r="G1361" t="n">
         <v>1</v>
@@ -45370,13 +45370,13 @@
         </is>
       </c>
       <c r="D1362" t="n">
-        <v>70.8</v>
+        <v>141.6</v>
       </c>
       <c r="E1362" t="n">
-        <v>1204.8</v>
+        <v>2368.6</v>
       </c>
       <c r="F1362" t="n">
-        <v>11915.9</v>
+        <v>13079.7</v>
       </c>
       <c r="G1362" t="n">
         <v>4</v>
@@ -45403,19 +45403,19 @@
         </is>
       </c>
       <c r="D1363" t="n">
-        <v>76.5</v>
+        <v>153</v>
       </c>
       <c r="E1363" t="n">
-        <v>1255.3</v>
+        <v>2478.6</v>
       </c>
       <c r="F1363" t="n">
-        <v>11946.3</v>
+        <v>13169.6</v>
       </c>
       <c r="G1363" t="n">
         <v>2</v>
       </c>
       <c r="H1363" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I1363" t="n">
         <v>2</v>
@@ -45436,19 +45436,19 @@
         </is>
       </c>
       <c r="D1364" t="n">
-        <v>75.2</v>
+        <v>150.4</v>
       </c>
       <c r="E1364" t="n">
-        <v>1259.2</v>
+        <v>2447.4</v>
       </c>
       <c r="F1364" t="n">
-        <v>11124.3</v>
+        <v>12312.5</v>
       </c>
       <c r="G1364" t="n">
         <v>3</v>
       </c>
       <c r="H1364" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I1364" t="n">
         <v>4</v>
@@ -45469,13 +45469,13 @@
         </is>
       </c>
       <c r="D1365" t="n">
-        <v>46.7</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="E1365" t="n">
-        <v>1128.7</v>
+        <v>2214.4</v>
       </c>
       <c r="F1365" t="n">
-        <v>10793.3</v>
+        <v>11879</v>
       </c>
       <c r="G1365" t="n">
         <v>8</v>
@@ -45502,13 +45502,13 @@
         </is>
       </c>
       <c r="D1366" t="n">
-        <v>79.40000000000001</v>
+        <v>158.8</v>
       </c>
       <c r="E1366" t="n">
-        <v>1357.1</v>
+        <v>2635.2</v>
       </c>
       <c r="F1366" t="n">
-        <v>12291.9</v>
+        <v>13570</v>
       </c>
       <c r="G1366" t="n">
         <v>1</v>
@@ -45535,13 +45535,13 @@
         </is>
       </c>
       <c r="D1367" t="n">
-        <v>56.59999999999999</v>
+        <v>113.2</v>
       </c>
       <c r="E1367" t="n">
-        <v>1065.5</v>
+        <v>2076</v>
       </c>
       <c r="F1367" t="n">
-        <v>9899.4</v>
+        <v>10909.9</v>
       </c>
       <c r="G1367" t="n">
         <v>6</v>
@@ -45568,13 +45568,13 @@
         </is>
       </c>
       <c r="D1368" t="n">
-        <v>65.2</v>
+        <v>130.4</v>
       </c>
       <c r="E1368" t="n">
-        <v>1256</v>
+        <v>2461</v>
       </c>
       <c r="F1368" t="n">
-        <v>10860.1</v>
+        <v>12065.1</v>
       </c>
       <c r="G1368" t="n">
         <v>5</v>
@@ -45601,13 +45601,13 @@
         </is>
       </c>
       <c r="D1369" t="n">
-        <v>54.8</v>
+        <v>109.6</v>
       </c>
       <c r="E1369" t="n">
-        <v>1274.9</v>
+        <v>2480.8</v>
       </c>
       <c r="F1369" t="n">
-        <v>8809.9</v>
+        <v>10015.8</v>
       </c>
       <c r="G1369" t="n">
         <v>7</v>
@@ -45634,13 +45634,13 @@
         </is>
       </c>
       <c r="D1370" t="n">
-        <v>93.8</v>
+        <v>187.6</v>
       </c>
       <c r="E1370" t="n">
-        <v>1298.6</v>
+        <v>2556.2</v>
       </c>
       <c r="F1370" t="n">
-        <v>12009.7</v>
+        <v>13267.3</v>
       </c>
       <c r="G1370" t="n">
         <v>2</v>
@@ -45667,19 +45667,19 @@
         </is>
       </c>
       <c r="D1371" t="n">
-        <v>65.2</v>
+        <v>130.4</v>
       </c>
       <c r="E1371" t="n">
-        <v>1320.5</v>
+        <v>2609</v>
       </c>
       <c r="F1371" t="n">
-        <v>12011.5</v>
+        <v>13300</v>
       </c>
       <c r="G1371" t="n">
         <v>7</v>
       </c>
       <c r="H1371" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I1371" t="n">
         <v>2</v>
@@ -45700,13 +45700,13 @@
         </is>
       </c>
       <c r="D1372" t="n">
-        <v>97.59999999999999</v>
+        <v>195.2</v>
       </c>
       <c r="E1372" t="n">
-        <v>1356.8</v>
+        <v>2642.6</v>
       </c>
       <c r="F1372" t="n">
-        <v>11221.9</v>
+        <v>12507.7</v>
       </c>
       <c r="G1372" t="n">
         <v>1</v>
@@ -45733,13 +45733,13 @@
         </is>
       </c>
       <c r="D1373" t="n">
-        <v>63.3</v>
+        <v>126.6</v>
       </c>
       <c r="E1373" t="n">
-        <v>1192</v>
+        <v>2341</v>
       </c>
       <c r="F1373" t="n">
-        <v>10856.6</v>
+        <v>12005.6</v>
       </c>
       <c r="G1373" t="n">
         <v>8</v>
@@ -45766,13 +45766,13 @@
         </is>
       </c>
       <c r="D1374" t="n">
-        <v>79.3</v>
+        <v>158.6</v>
       </c>
       <c r="E1374" t="n">
-        <v>1436.4</v>
+        <v>2793.8</v>
       </c>
       <c r="F1374" t="n">
-        <v>12371.2</v>
+        <v>13728.6</v>
       </c>
       <c r="G1374" t="n">
         <v>5</v>
@@ -45799,13 +45799,13 @@
         </is>
       </c>
       <c r="D1375" t="n">
-        <v>81.7</v>
+        <v>163.4</v>
       </c>
       <c r="E1375" t="n">
-        <v>1147.2</v>
+        <v>2239.4</v>
       </c>
       <c r="F1375" t="n">
-        <v>9981.1</v>
+        <v>11073.3</v>
       </c>
       <c r="G1375" t="n">
         <v>4</v>
@@ -45832,19 +45832,19 @@
         </is>
       </c>
       <c r="D1376" t="n">
-        <v>67.40000000000001</v>
+        <v>134.8</v>
       </c>
       <c r="E1376" t="n">
-        <v>1323.4</v>
+        <v>2595.8</v>
       </c>
       <c r="F1376" t="n">
-        <v>10927.5</v>
+        <v>12199.9</v>
       </c>
       <c r="G1376" t="n">
         <v>6</v>
       </c>
       <c r="H1376" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I1376" t="n">
         <v>5</v>
@@ -45865,13 +45865,13 @@
         </is>
       </c>
       <c r="D1377" t="n">
-        <v>82.59999999999999</v>
+        <v>165.2</v>
       </c>
       <c r="E1377" t="n">
-        <v>1357.5</v>
+        <v>2646</v>
       </c>
       <c r="F1377" t="n">
-        <v>8892.5</v>
+        <v>10181</v>
       </c>
       <c r="G1377" t="n">
         <v>3</v>
@@ -45898,13 +45898,13 @@
         </is>
       </c>
       <c r="D1378" t="n">
-        <v>100.5</v>
+        <v>201</v>
       </c>
       <c r="E1378" t="n">
-        <v>1399.1</v>
+        <v>2757.2</v>
       </c>
       <c r="F1378" t="n">
-        <v>12110.2</v>
+        <v>13468.3</v>
       </c>
       <c r="G1378" t="n">
         <v>1</v>
@@ -45931,19 +45931,19 @@
         </is>
       </c>
       <c r="D1379" t="n">
-        <v>80.3</v>
+        <v>160.6</v>
       </c>
       <c r="E1379" t="n">
-        <v>1400.8</v>
+        <v>2769.6</v>
       </c>
       <c r="F1379" t="n">
-        <v>12091.8</v>
+        <v>13460.6</v>
       </c>
       <c r="G1379" t="n">
         <v>2</v>
       </c>
       <c r="H1379" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I1379" t="n">
         <v>3</v>
@@ -45964,19 +45964,19 @@
         </is>
       </c>
       <c r="D1380" t="n">
-        <v>60.3</v>
+        <v>120.6</v>
       </c>
       <c r="E1380" t="n">
-        <v>1417.1</v>
+        <v>2763.2</v>
       </c>
       <c r="F1380" t="n">
-        <v>11282.2</v>
+        <v>12628.3</v>
       </c>
       <c r="G1380" t="n">
         <v>6</v>
       </c>
       <c r="H1380" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I1380" t="n">
         <v>4</v>
@@ -45997,13 +45997,13 @@
         </is>
       </c>
       <c r="D1381" t="n">
-        <v>67.59999999999999</v>
+        <v>135.2</v>
       </c>
       <c r="E1381" t="n">
-        <v>1259.6</v>
+        <v>2476.2</v>
       </c>
       <c r="F1381" t="n">
-        <v>10924.2</v>
+        <v>12140.8</v>
       </c>
       <c r="G1381" t="n">
         <v>4</v>
@@ -46030,13 +46030,13 @@
         </is>
       </c>
       <c r="D1382" t="n">
-        <v>70.2</v>
+        <v>140.4</v>
       </c>
       <c r="E1382" t="n">
-        <v>1506.6</v>
+        <v>2934.2</v>
       </c>
       <c r="F1382" t="n">
-        <v>12441.4</v>
+        <v>13869</v>
       </c>
       <c r="G1382" t="n">
         <v>3</v>
@@ -46063,13 +46063,13 @@
         </is>
       </c>
       <c r="D1383" t="n">
-        <v>61.2</v>
+        <v>122.4</v>
       </c>
       <c r="E1383" t="n">
-        <v>1208.4</v>
+        <v>2361.8</v>
       </c>
       <c r="F1383" t="n">
-        <v>10042.3</v>
+        <v>11195.7</v>
       </c>
       <c r="G1383" t="n">
         <v>5</v>
@@ -46096,13 +46096,13 @@
         </is>
       </c>
       <c r="D1384" t="n">
-        <v>50.8</v>
+        <v>101.6</v>
       </c>
       <c r="E1384" t="n">
-        <v>1374.2</v>
+        <v>2697.4</v>
       </c>
       <c r="F1384" t="n">
-        <v>10978.3</v>
+        <v>12301.5</v>
       </c>
       <c r="G1384" t="n">
         <v>8</v>
@@ -46129,13 +46129,13 @@
         </is>
       </c>
       <c r="D1385" t="n">
-        <v>58.9</v>
+        <v>117.8</v>
       </c>
       <c r="E1385" t="n">
-        <v>1416.4</v>
+        <v>2763.8</v>
       </c>
       <c r="F1385" t="n">
-        <v>8951.4</v>
+        <v>10298.8</v>
       </c>
       <c r="G1385" t="n">
         <v>7</v>
@@ -46162,19 +46162,19 @@
         </is>
       </c>
       <c r="D1386" t="n">
-        <v>92</v>
+        <v>184</v>
       </c>
       <c r="E1386" t="n">
-        <v>1491.1</v>
+        <v>2941.2</v>
       </c>
       <c r="F1386" t="n">
-        <v>12202.2</v>
+        <v>13652.3</v>
       </c>
       <c r="G1386" t="n">
         <v>2</v>
       </c>
       <c r="H1386" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I1386" t="n">
         <v>2</v>
@@ -46195,19 +46195,19 @@
         </is>
       </c>
       <c r="D1387" t="n">
-        <v>77.2</v>
+        <v>154.4</v>
       </c>
       <c r="E1387" t="n">
-        <v>1478</v>
+        <v>2924</v>
       </c>
       <c r="F1387" t="n">
-        <v>12169</v>
+        <v>13615</v>
       </c>
       <c r="G1387" t="n">
         <v>4</v>
       </c>
       <c r="H1387" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I1387" t="n">
         <v>3</v>
@@ -46228,19 +46228,19 @@
         </is>
       </c>
       <c r="D1388" t="n">
-        <v>80.3</v>
+        <v>160.6</v>
       </c>
       <c r="E1388" t="n">
-        <v>1497.4</v>
+        <v>2923.8</v>
       </c>
       <c r="F1388" t="n">
-        <v>11362.5</v>
+        <v>12788.9</v>
       </c>
       <c r="G1388" t="n">
         <v>3</v>
       </c>
       <c r="H1388" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I1388" t="n">
         <v>4</v>
@@ -46261,13 +46261,13 @@
         </is>
       </c>
       <c r="D1389" t="n">
-        <v>50.6</v>
+        <v>101.2</v>
       </c>
       <c r="E1389" t="n">
-        <v>1310.2</v>
+        <v>2577.4</v>
       </c>
       <c r="F1389" t="n">
-        <v>10974.8</v>
+        <v>12242</v>
       </c>
       <c r="G1389" t="n">
         <v>7</v>
@@ -46294,13 +46294,13 @@
         </is>
       </c>
       <c r="D1390" t="n">
-        <v>76.7</v>
+        <v>153.4</v>
       </c>
       <c r="E1390" t="n">
-        <v>1583.3</v>
+        <v>3087.6</v>
       </c>
       <c r="F1390" t="n">
-        <v>12518.1</v>
+        <v>14022.4</v>
       </c>
       <c r="G1390" t="n">
         <v>5</v>
@@ -46327,13 +46327,13 @@
         </is>
       </c>
       <c r="D1391" t="n">
-        <v>48.7</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="E1391" t="n">
-        <v>1257.1</v>
+        <v>2459.2</v>
       </c>
       <c r="F1391" t="n">
-        <v>10091</v>
+        <v>11293.1</v>
       </c>
       <c r="G1391" t="n">
         <v>8</v>
@@ -46360,13 +46360,13 @@
         </is>
       </c>
       <c r="D1392" t="n">
-        <v>92.5</v>
+        <v>185</v>
       </c>
       <c r="E1392" t="n">
-        <v>1466.7</v>
+        <v>2882.4</v>
       </c>
       <c r="F1392" t="n">
-        <v>11070.8</v>
+        <v>12486.5</v>
       </c>
       <c r="G1392" t="n">
         <v>1</v>
@@ -46393,19 +46393,19 @@
         </is>
       </c>
       <c r="D1393" t="n">
-        <v>73.10000000000001</v>
+        <v>146.2</v>
       </c>
       <c r="E1393" t="n">
-        <v>1489.5</v>
+        <v>2910</v>
       </c>
       <c r="F1393" t="n">
-        <v>9024.5</v>
+        <v>10445</v>
       </c>
       <c r="G1393" t="n">
         <v>6</v>
       </c>
       <c r="H1393" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I1393" t="n">
         <v>8</v>
@@ -46426,19 +46426,19 @@
         </is>
       </c>
       <c r="D1394" t="n">
-        <v>75.59999999999999</v>
+        <v>151.2</v>
       </c>
       <c r="E1394" t="n">
-        <v>1566.7</v>
+        <v>3092.4</v>
       </c>
       <c r="F1394" t="n">
-        <v>12277.8</v>
+        <v>13803.5</v>
       </c>
       <c r="G1394" t="n">
         <v>3</v>
       </c>
       <c r="H1394" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I1394" t="n">
         <v>2</v>
@@ -46459,19 +46459,19 @@
         </is>
       </c>
       <c r="D1395" t="n">
-        <v>84.09999999999999</v>
+        <v>168.2</v>
       </c>
       <c r="E1395" t="n">
-        <v>1562.1</v>
+        <v>3092.2</v>
       </c>
       <c r="F1395" t="n">
-        <v>12253.1</v>
+        <v>13783.2</v>
       </c>
       <c r="G1395" t="n">
         <v>1</v>
       </c>
       <c r="H1395" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1395" t="n">
         <v>3</v>
@@ -46492,13 +46492,13 @@
         </is>
       </c>
       <c r="D1396" t="n">
-        <v>59.3</v>
+        <v>118.6</v>
       </c>
       <c r="E1396" t="n">
-        <v>1556.7</v>
+        <v>3042.4</v>
       </c>
       <c r="F1396" t="n">
-        <v>11421.8</v>
+        <v>12907.5</v>
       </c>
       <c r="G1396" t="n">
         <v>8</v>
@@ -46525,13 +46525,13 @@
         </is>
       </c>
       <c r="D1397" t="n">
-        <v>71.5</v>
+        <v>143</v>
       </c>
       <c r="E1397" t="n">
-        <v>1381.7</v>
+        <v>2720.4</v>
       </c>
       <c r="F1397" t="n">
-        <v>11046.3</v>
+        <v>12385</v>
       </c>
       <c r="G1397" t="n">
         <v>6</v>
@@ -46558,13 +46558,13 @@
         </is>
       </c>
       <c r="D1398" t="n">
-        <v>75.39999999999999</v>
+        <v>150.8</v>
       </c>
       <c r="E1398" t="n">
-        <v>1658.7</v>
+        <v>3238.4</v>
       </c>
       <c r="F1398" t="n">
-        <v>12593.5</v>
+        <v>14173.2</v>
       </c>
       <c r="G1398" t="n">
         <v>4</v>
@@ -46591,13 +46591,13 @@
         </is>
       </c>
       <c r="D1399" t="n">
-        <v>62.7</v>
+        <v>125.4</v>
       </c>
       <c r="E1399" t="n">
-        <v>1319.8</v>
+        <v>2584.6</v>
       </c>
       <c r="F1399" t="n">
-        <v>10153.7</v>
+        <v>11418.5</v>
       </c>
       <c r="G1399" t="n">
         <v>7</v>
@@ -46624,13 +46624,13 @@
         </is>
       </c>
       <c r="D1400" t="n">
-        <v>72</v>
+        <v>144</v>
       </c>
       <c r="E1400" t="n">
-        <v>1538.7</v>
+        <v>3026.4</v>
       </c>
       <c r="F1400" t="n">
-        <v>11142.8</v>
+        <v>12630.5</v>
       </c>
       <c r="G1400" t="n">
         <v>5</v>
@@ -46657,19 +46657,19 @@
         </is>
       </c>
       <c r="D1401" t="n">
-        <v>79.09999999999999</v>
+        <v>158.2</v>
       </c>
       <c r="E1401" t="n">
-        <v>1568.6</v>
+        <v>3068.2</v>
       </c>
       <c r="F1401" t="n">
-        <v>9103.6</v>
+        <v>10603.2</v>
       </c>
       <c r="G1401" t="n">
         <v>2</v>
       </c>
       <c r="H1401" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I1401" t="n">
         <v>8</v>
@@ -46690,19 +46690,19 @@
         </is>
       </c>
       <c r="D1402" t="n">
-        <v>73.2</v>
+        <v>146.4</v>
       </c>
       <c r="E1402" t="n">
-        <v>1639.9</v>
+        <v>3238.8</v>
       </c>
       <c r="F1402" t="n">
-        <v>12351</v>
+        <v>13949.9</v>
       </c>
       <c r="G1402" t="n">
         <v>2</v>
       </c>
       <c r="H1402" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I1402" t="n">
         <v>2</v>
@@ -46723,19 +46723,19 @@
         </is>
       </c>
       <c r="D1403" t="n">
-        <v>62.7</v>
+        <v>125.4</v>
       </c>
       <c r="E1403" t="n">
-        <v>1624.8</v>
+        <v>3217.6</v>
       </c>
       <c r="F1403" t="n">
-        <v>12315.8</v>
+        <v>13908.6</v>
       </c>
       <c r="G1403" t="n">
         <v>5</v>
       </c>
       <c r="H1403" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1403" t="n">
         <v>3</v>
@@ -46756,13 +46756,13 @@
         </is>
       </c>
       <c r="D1404" t="n">
-        <v>49.2</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="E1404" t="n">
-        <v>1605.9</v>
+        <v>3140.8</v>
       </c>
       <c r="F1404" t="n">
-        <v>11471</v>
+        <v>13005.9</v>
       </c>
       <c r="G1404" t="n">
         <v>6</v>
@@ -46789,13 +46789,13 @@
         </is>
       </c>
       <c r="D1405" t="n">
-        <v>43.9</v>
+        <v>87.8</v>
       </c>
       <c r="E1405" t="n">
-        <v>1425.6</v>
+        <v>2808.2</v>
       </c>
       <c r="F1405" t="n">
-        <v>11090.2</v>
+        <v>12472.8</v>
       </c>
       <c r="G1405" t="n">
         <v>7</v>
@@ -46822,13 +46822,13 @@
         </is>
       </c>
       <c r="D1406" t="n">
-        <v>71.2</v>
+        <v>142.4</v>
       </c>
       <c r="E1406" t="n">
-        <v>1729.9</v>
+        <v>3380.8</v>
       </c>
       <c r="F1406" t="n">
-        <v>12664.7</v>
+        <v>14315.6</v>
       </c>
       <c r="G1406" t="n">
         <v>3</v>
@@ -46855,13 +46855,13 @@
         </is>
       </c>
       <c r="D1407" t="n">
-        <v>64.09999999999999</v>
+        <v>128.2</v>
       </c>
       <c r="E1407" t="n">
-        <v>1383.9</v>
+        <v>2712.8</v>
       </c>
       <c r="F1407" t="n">
-        <v>10217.8</v>
+        <v>11546.7</v>
       </c>
       <c r="G1407" t="n">
         <v>4</v>
@@ -46888,13 +46888,13 @@
         </is>
       </c>
       <c r="D1408" t="n">
-        <v>42.9</v>
+        <v>85.8</v>
       </c>
       <c r="E1408" t="n">
-        <v>1581.6</v>
+        <v>3112.2</v>
       </c>
       <c r="F1408" t="n">
-        <v>11185.7</v>
+        <v>12716.3</v>
       </c>
       <c r="G1408" t="n">
         <v>8</v>
@@ -46921,19 +46921,19 @@
         </is>
       </c>
       <c r="D1409" t="n">
-        <v>73.8</v>
+        <v>147.6</v>
       </c>
       <c r="E1409" t="n">
-        <v>1642.4</v>
+        <v>3215.8</v>
       </c>
       <c r="F1409" t="n">
-        <v>9177.4</v>
+        <v>10750.8</v>
       </c>
       <c r="G1409" t="n">
         <v>1</v>
       </c>
       <c r="H1409" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I1409" t="n">
         <v>8</v>
@@ -46954,13 +46954,13 @@
         </is>
       </c>
       <c r="D1410" t="n">
-        <v>79.3</v>
+        <v>158.6</v>
       </c>
       <c r="E1410" t="n">
-        <v>1719.2</v>
+        <v>3397.4</v>
       </c>
       <c r="F1410" t="n">
-        <v>12430.3</v>
+        <v>14108.5</v>
       </c>
       <c r="G1410" t="n">
         <v>1</v>
@@ -46987,19 +46987,19 @@
         </is>
       </c>
       <c r="D1411" t="n">
-        <v>62.3</v>
+        <v>124.6</v>
       </c>
       <c r="E1411" t="n">
-        <v>1687.1</v>
+        <v>3342.2</v>
       </c>
       <c r="F1411" t="n">
-        <v>12378.1</v>
+        <v>14033.2</v>
       </c>
       <c r="G1411" t="n">
         <v>4</v>
       </c>
       <c r="H1411" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1411" t="n">
         <v>3</v>
@@ -47020,13 +47020,13 @@
         </is>
       </c>
       <c r="D1412" t="n">
-        <v>50.4</v>
+        <v>100.8</v>
       </c>
       <c r="E1412" t="n">
-        <v>1656.3</v>
+        <v>3241.6</v>
       </c>
       <c r="F1412" t="n">
-        <v>11521.4</v>
+        <v>13106.7</v>
       </c>
       <c r="G1412" t="n">
         <v>7</v>
@@ -47053,13 +47053,13 @@
         </is>
       </c>
       <c r="D1413" t="n">
-        <v>48.8</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="E1413" t="n">
-        <v>1474.4</v>
+        <v>2905.8</v>
       </c>
       <c r="F1413" t="n">
-        <v>11139</v>
+        <v>12570.4</v>
       </c>
       <c r="G1413" t="n">
         <v>8</v>
@@ -47086,13 +47086,13 @@
         </is>
       </c>
       <c r="D1414" t="n">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="E1414" t="n">
-        <v>1804.9</v>
+        <v>3530.8</v>
       </c>
       <c r="F1414" t="n">
-        <v>12739.7</v>
+        <v>14465.6</v>
       </c>
       <c r="G1414" t="n">
         <v>2</v>
@@ -47119,13 +47119,13 @@
         </is>
       </c>
       <c r="D1415" t="n">
-        <v>64.5</v>
+        <v>129</v>
       </c>
       <c r="E1415" t="n">
-        <v>1448.4</v>
+        <v>2841.8</v>
       </c>
       <c r="F1415" t="n">
-        <v>10282.3</v>
+        <v>11675.7</v>
       </c>
       <c r="G1415" t="n">
         <v>3</v>
@@ -47152,13 +47152,13 @@
         </is>
       </c>
       <c r="D1416" t="n">
-        <v>59.7</v>
+        <v>119.4</v>
       </c>
       <c r="E1416" t="n">
-        <v>1641.3</v>
+        <v>3231.6</v>
       </c>
       <c r="F1416" t="n">
-        <v>11245.4</v>
+        <v>12835.7</v>
       </c>
       <c r="G1416" t="n">
         <v>5</v>
@@ -47185,19 +47185,19 @@
         </is>
       </c>
       <c r="D1417" t="n">
-        <v>57.7</v>
+        <v>115.4</v>
       </c>
       <c r="E1417" t="n">
-        <v>1700.1</v>
+        <v>3331.2</v>
       </c>
       <c r="F1417" t="n">
-        <v>9235.1</v>
+        <v>10866.2</v>
       </c>
       <c r="G1417" t="n">
         <v>6</v>
       </c>
       <c r="H1417" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1417" t="n">
         <v>8</v>
@@ -47218,13 +47218,13 @@
         </is>
       </c>
       <c r="D1418" t="n">
-        <v>86.3</v>
+        <v>172.6</v>
       </c>
       <c r="E1418" t="n">
-        <v>1805.5</v>
+        <v>3570</v>
       </c>
       <c r="F1418" t="n">
-        <v>12516.6</v>
+        <v>14281.1</v>
       </c>
       <c r="G1418" t="n">
         <v>2</v>
@@ -47251,13 +47251,13 @@
         </is>
       </c>
       <c r="D1419" t="n">
-        <v>75.59999999999999</v>
+        <v>151.2</v>
       </c>
       <c r="E1419" t="n">
-        <v>1762.7</v>
+        <v>3493.4</v>
       </c>
       <c r="F1419" t="n">
-        <v>12453.7</v>
+        <v>14184.4</v>
       </c>
       <c r="G1419" t="n">
         <v>3</v>
@@ -47284,13 +47284,13 @@
         </is>
       </c>
       <c r="D1420" t="n">
-        <v>50.9</v>
+        <v>101.8</v>
       </c>
       <c r="E1420" t="n">
-        <v>1707.2</v>
+        <v>3343.4</v>
       </c>
       <c r="F1420" t="n">
-        <v>11572.3</v>
+        <v>13208.5</v>
       </c>
       <c r="G1420" t="n">
         <v>8</v>
@@ -47317,13 +47317,13 @@
         </is>
       </c>
       <c r="D1421" t="n">
-        <v>65.3</v>
+        <v>130.6</v>
       </c>
       <c r="E1421" t="n">
-        <v>1539.7</v>
+        <v>3036.4</v>
       </c>
       <c r="F1421" t="n">
-        <v>11204.3</v>
+        <v>12701</v>
       </c>
       <c r="G1421" t="n">
         <v>4</v>
@@ -47350,13 +47350,13 @@
         </is>
       </c>
       <c r="D1422" t="n">
-        <v>58.4</v>
+        <v>116.8</v>
       </c>
       <c r="E1422" t="n">
-        <v>1863.3</v>
+        <v>3647.6</v>
       </c>
       <c r="F1422" t="n">
-        <v>12798.1</v>
+        <v>14582.4</v>
       </c>
       <c r="G1422" t="n">
         <v>6</v>
@@ -47383,13 +47383,13 @@
         </is>
       </c>
       <c r="D1423" t="n">
-        <v>58.6</v>
+        <v>117.2</v>
       </c>
       <c r="E1423" t="n">
-        <v>1507</v>
+        <v>2959</v>
       </c>
       <c r="F1423" t="n">
-        <v>10340.9</v>
+        <v>11792.9</v>
       </c>
       <c r="G1423" t="n">
         <v>5</v>
@@ -47416,13 +47416,13 @@
         </is>
       </c>
       <c r="D1424" t="n">
-        <v>55.3</v>
+        <v>110.6</v>
       </c>
       <c r="E1424" t="n">
-        <v>1696.6</v>
+        <v>3342.2</v>
       </c>
       <c r="F1424" t="n">
-        <v>11300.7</v>
+        <v>12946.3</v>
       </c>
       <c r="G1424" t="n">
         <v>7</v>
@@ -47449,13 +47449,13 @@
         </is>
       </c>
       <c r="D1425" t="n">
-        <v>96</v>
+        <v>192</v>
       </c>
       <c r="E1425" t="n">
-        <v>1796.1</v>
+        <v>3523.2</v>
       </c>
       <c r="F1425" t="n">
-        <v>9331.1</v>
+        <v>11058.2</v>
       </c>
       <c r="G1425" t="n">
         <v>1</v>
@@ -47482,13 +47482,13 @@
         </is>
       </c>
       <c r="D1426" t="n">
-        <v>84.5</v>
+        <v>169</v>
       </c>
       <c r="E1426" t="n">
-        <v>1890</v>
+        <v>3739</v>
       </c>
       <c r="F1426" t="n">
-        <v>12601.1</v>
+        <v>14450.1</v>
       </c>
       <c r="G1426" t="n">
         <v>1</v>
@@ -47515,13 +47515,13 @@
         </is>
       </c>
       <c r="D1427" t="n">
-        <v>66.59999999999999</v>
+        <v>133.2</v>
       </c>
       <c r="E1427" t="n">
-        <v>1829.3</v>
+        <v>3626.6</v>
       </c>
       <c r="F1427" t="n">
-        <v>12520.3</v>
+        <v>14317.6</v>
       </c>
       <c r="G1427" t="n">
         <v>4</v>
@@ -47548,19 +47548,19 @@
         </is>
       </c>
       <c r="D1428" t="n">
-        <v>60.1</v>
+        <v>120.2</v>
       </c>
       <c r="E1428" t="n">
-        <v>1767.3</v>
+        <v>3463.6</v>
       </c>
       <c r="F1428" t="n">
-        <v>11632.4</v>
+        <v>13328.7</v>
       </c>
       <c r="G1428" t="n">
         <v>6</v>
       </c>
       <c r="H1428" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I1428" t="n">
         <v>4</v>
@@ -47581,13 +47581,13 @@
         </is>
       </c>
       <c r="D1429" t="n">
-        <v>74.09999999999999</v>
+        <v>148.2</v>
       </c>
       <c r="E1429" t="n">
-        <v>1613.8</v>
+        <v>3184.6</v>
       </c>
       <c r="F1429" t="n">
-        <v>11278.4</v>
+        <v>12849.2</v>
       </c>
       <c r="G1429" t="n">
         <v>3</v>
@@ -47614,13 +47614,13 @@
         </is>
       </c>
       <c r="D1430" t="n">
-        <v>57.4</v>
+        <v>114.8</v>
       </c>
       <c r="E1430" t="n">
-        <v>1920.7</v>
+        <v>3762.4</v>
       </c>
       <c r="F1430" t="n">
-        <v>12855.5</v>
+        <v>14697.2</v>
       </c>
       <c r="G1430" t="n">
         <v>7</v>
@@ -47650,10 +47650,10 @@
         <v>0</v>
       </c>
       <c r="E1431" t="n">
-        <v>1507</v>
+        <v>2959</v>
       </c>
       <c r="F1431" t="n">
-        <v>10340.9</v>
+        <v>11792.9</v>
       </c>
       <c r="G1431" t="n">
         <v>8</v>
@@ -47680,19 +47680,19 @@
         </is>
       </c>
       <c r="D1432" t="n">
-        <v>65.90000000000001</v>
+        <v>131.8</v>
       </c>
       <c r="E1432" t="n">
-        <v>1762.5</v>
+        <v>3474</v>
       </c>
       <c r="F1432" t="n">
-        <v>11366.6</v>
+        <v>13078.1</v>
       </c>
       <c r="G1432" t="n">
         <v>5</v>
       </c>
       <c r="H1432" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I1432" t="n">
         <v>5</v>
@@ -47713,13 +47713,13 @@
         </is>
       </c>
       <c r="D1433" t="n">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="E1433" t="n">
-        <v>1872.1</v>
+        <v>3675.2</v>
       </c>
       <c r="F1433" t="n">
-        <v>9407.1</v>
+        <v>11210.2</v>
       </c>
       <c r="G1433" t="n">
         <v>2</v>
@@ -47746,19 +47746,19 @@
         </is>
       </c>
       <c r="D1434" t="n">
-        <v>73.09999999999999</v>
+        <v>146.2</v>
       </c>
       <c r="E1434" t="n">
-        <v>1963.1</v>
+        <v>3885.2</v>
       </c>
       <c r="F1434" t="n">
-        <v>12674.2</v>
+        <v>14596.3</v>
       </c>
       <c r="G1434" t="n">
         <v>6</v>
       </c>
       <c r="H1434" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I1434" t="n">
         <v>2</v>
@@ -47779,13 +47779,13 @@
         </is>
       </c>
       <c r="D1435" t="n">
-        <v>92.90000000000001</v>
+        <v>185.8</v>
       </c>
       <c r="E1435" t="n">
-        <v>1922.2</v>
+        <v>3812.4</v>
       </c>
       <c r="F1435" t="n">
-        <v>12613.2</v>
+        <v>14503.4</v>
       </c>
       <c r="G1435" t="n">
         <v>2</v>
@@ -47812,13 +47812,13 @@
         </is>
       </c>
       <c r="D1436" t="n">
-        <v>51.6</v>
+        <v>103.2</v>
       </c>
       <c r="E1436" t="n">
-        <v>1818.9</v>
+        <v>3566.8</v>
       </c>
       <c r="F1436" t="n">
-        <v>11684</v>
+        <v>13431.9</v>
       </c>
       <c r="G1436" t="n">
         <v>8</v>
@@ -47845,13 +47845,13 @@
         </is>
       </c>
       <c r="D1437" t="n">
-        <v>62.1</v>
+        <v>124.2</v>
       </c>
       <c r="E1437" t="n">
-        <v>1675.9</v>
+        <v>3308.8</v>
       </c>
       <c r="F1437" t="n">
-        <v>11340.5</v>
+        <v>12973.4</v>
       </c>
       <c r="G1437" t="n">
         <v>7</v>
@@ -47878,13 +47878,13 @@
         </is>
       </c>
       <c r="D1438" t="n">
-        <v>86.7</v>
+        <v>173.4</v>
       </c>
       <c r="E1438" t="n">
-        <v>2007.4</v>
+        <v>3935.8</v>
       </c>
       <c r="F1438" t="n">
-        <v>12942.2</v>
+        <v>14870.6</v>
       </c>
       <c r="G1438" t="n">
         <v>4</v>
@@ -47911,13 +47911,13 @@
         </is>
       </c>
       <c r="D1439" t="n">
-        <v>88.2</v>
+        <v>176.4</v>
       </c>
       <c r="E1439" t="n">
-        <v>1595.2</v>
+        <v>3135.4</v>
       </c>
       <c r="F1439" t="n">
-        <v>10429.1</v>
+        <v>11969.3</v>
       </c>
       <c r="G1439" t="n">
         <v>3</v>
@@ -47944,13 +47944,13 @@
         </is>
       </c>
       <c r="D1440" t="n">
-        <v>73.3</v>
+        <v>146.6</v>
       </c>
       <c r="E1440" t="n">
-        <v>1835.8</v>
+        <v>3620.6</v>
       </c>
       <c r="F1440" t="n">
-        <v>11439.9</v>
+        <v>13224.7</v>
       </c>
       <c r="G1440" t="n">
         <v>5</v>
@@ -47977,19 +47977,19 @@
         </is>
       </c>
       <c r="D1441" t="n">
-        <v>100.9</v>
+        <v>201.8</v>
       </c>
       <c r="E1441" t="n">
-        <v>1973</v>
+        <v>3877</v>
       </c>
       <c r="F1441" t="n">
-        <v>9508</v>
+        <v>11412</v>
       </c>
       <c r="G1441" t="n">
         <v>1</v>
       </c>
       <c r="H1441" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I1441" t="n">
         <v>8</v>
@@ -48010,19 +48010,19 @@
         </is>
       </c>
       <c r="D1442" t="n">
-        <v>82.5</v>
+        <v>165</v>
       </c>
       <c r="E1442" t="n">
-        <v>2045.6</v>
+        <v>4050.2</v>
       </c>
       <c r="F1442" t="n">
-        <v>12756.7</v>
+        <v>14761.3</v>
       </c>
       <c r="G1442" t="n">
         <v>3</v>
       </c>
       <c r="H1442" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1442" t="n">
         <v>2</v>
@@ -48043,13 +48043,13 @@
         </is>
       </c>
       <c r="D1443" t="n">
-        <v>73.5</v>
+        <v>147</v>
       </c>
       <c r="E1443" t="n">
-        <v>1995.7</v>
+        <v>3959.4</v>
       </c>
       <c r="F1443" t="n">
-        <v>12686.7</v>
+        <v>14650.4</v>
       </c>
       <c r="G1443" t="n">
         <v>4</v>
@@ -48076,13 +48076,13 @@
         </is>
       </c>
       <c r="D1444" t="n">
-        <v>114.5</v>
+        <v>229</v>
       </c>
       <c r="E1444" t="n">
-        <v>1933.4</v>
+        <v>3795.8</v>
       </c>
       <c r="F1444" t="n">
-        <v>11798.5</v>
+        <v>13660.9</v>
       </c>
       <c r="G1444" t="n">
         <v>1</v>
@@ -48109,13 +48109,13 @@
         </is>
       </c>
       <c r="D1445" t="n">
-        <v>85.90000000000001</v>
+        <v>171.8</v>
       </c>
       <c r="E1445" t="n">
-        <v>1761.8</v>
+        <v>3480.6</v>
       </c>
       <c r="F1445" t="n">
-        <v>11426.4</v>
+        <v>13145.2</v>
       </c>
       <c r="G1445" t="n">
         <v>2</v>
@@ -48142,19 +48142,19 @@
         </is>
       </c>
       <c r="D1446" t="n">
-        <v>48.6</v>
+        <v>97.2</v>
       </c>
       <c r="E1446" t="n">
-        <v>2056</v>
+        <v>4033</v>
       </c>
       <c r="F1446" t="n">
-        <v>12990.8</v>
+        <v>14967.8</v>
       </c>
       <c r="G1446" t="n">
         <v>6</v>
       </c>
       <c r="H1446" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1446" t="n">
         <v>1</v>
@@ -48175,13 +48175,13 @@
         </is>
       </c>
       <c r="D1447" t="n">
-        <v>52.8</v>
+        <v>105.6</v>
       </c>
       <c r="E1447" t="n">
-        <v>1648</v>
+        <v>3241</v>
       </c>
       <c r="F1447" t="n">
-        <v>10481.9</v>
+        <v>12074.9</v>
       </c>
       <c r="G1447" t="n">
         <v>5</v>
@@ -48208,13 +48208,13 @@
         </is>
       </c>
       <c r="D1448" t="n">
-        <v>47.9</v>
+        <v>95.8</v>
       </c>
       <c r="E1448" t="n">
-        <v>1883.7</v>
+        <v>3716.4</v>
       </c>
       <c r="F1448" t="n">
-        <v>11487.8</v>
+        <v>13320.5</v>
       </c>
       <c r="G1448" t="n">
         <v>7</v>
@@ -48241,13 +48241,13 @@
         </is>
       </c>
       <c r="D1449" t="n">
-        <v>43.3</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="E1449" t="n">
-        <v>2016.3</v>
+        <v>3963.6</v>
       </c>
       <c r="F1449" t="n">
-        <v>9551.299999999999</v>
+        <v>11498.6</v>
       </c>
       <c r="G1449" t="n">
         <v>8</v>
@@ -48274,13 +48274,13 @@
         </is>
       </c>
       <c r="D1450" t="n">
-        <v>66.5</v>
+        <v>133</v>
       </c>
       <c r="E1450" t="n">
-        <v>2112.1</v>
+        <v>4183.2</v>
       </c>
       <c r="F1450" t="n">
-        <v>12823.2</v>
+        <v>14894.3</v>
       </c>
       <c r="G1450" t="n">
         <v>5</v>
@@ -48307,13 +48307,13 @@
         </is>
       </c>
       <c r="D1451" t="n">
-        <v>65.5</v>
+        <v>131</v>
       </c>
       <c r="E1451" t="n">
-        <v>2061.2</v>
+        <v>4090.4</v>
       </c>
       <c r="F1451" t="n">
-        <v>12752.2</v>
+        <v>14781.4</v>
       </c>
       <c r="G1451" t="n">
         <v>7</v>
@@ -48340,13 +48340,13 @@
         </is>
       </c>
       <c r="D1452" t="n">
-        <v>83.90000000000001</v>
+        <v>167.8</v>
       </c>
       <c r="E1452" t="n">
-        <v>2017.3</v>
+        <v>3963.6</v>
       </c>
       <c r="F1452" t="n">
-        <v>11882.4</v>
+        <v>13828.7</v>
       </c>
       <c r="G1452" t="n">
         <v>3</v>
@@ -48373,13 +48373,13 @@
         </is>
       </c>
       <c r="D1453" t="n">
-        <v>66.40000000000001</v>
+        <v>132.8</v>
       </c>
       <c r="E1453" t="n">
-        <v>1828.2</v>
+        <v>3613.4</v>
       </c>
       <c r="F1453" t="n">
-        <v>11492.8</v>
+        <v>13278</v>
       </c>
       <c r="G1453" t="n">
         <v>6</v>
@@ -48406,13 +48406,13 @@
         </is>
       </c>
       <c r="D1454" t="n">
-        <v>107</v>
+        <v>214</v>
       </c>
       <c r="E1454" t="n">
-        <v>2163</v>
+        <v>4247</v>
       </c>
       <c r="F1454" t="n">
-        <v>13097.8</v>
+        <v>15181.8</v>
       </c>
       <c r="G1454" t="n">
         <v>1</v>
@@ -48439,13 +48439,13 @@
         </is>
       </c>
       <c r="D1455" t="n">
-        <v>46.5</v>
+        <v>93</v>
       </c>
       <c r="E1455" t="n">
-        <v>1694.5</v>
+        <v>3334</v>
       </c>
       <c r="F1455" t="n">
-        <v>10528.4</v>
+        <v>12167.9</v>
       </c>
       <c r="G1455" t="n">
         <v>8</v>
@@ -48472,13 +48472,13 @@
         </is>
       </c>
       <c r="D1456" t="n">
-        <v>67.40000000000001</v>
+        <v>134.8</v>
       </c>
       <c r="E1456" t="n">
-        <v>1951.1</v>
+        <v>3851.2</v>
       </c>
       <c r="F1456" t="n">
-        <v>11555.2</v>
+        <v>13455.3</v>
       </c>
       <c r="G1456" t="n">
         <v>4</v>
@@ -48505,13 +48505,13 @@
         </is>
       </c>
       <c r="D1457" t="n">
-        <v>85.59999999999999</v>
+        <v>171.2</v>
       </c>
       <c r="E1457" t="n">
-        <v>2101.9</v>
+        <v>4134.8</v>
       </c>
       <c r="F1457" t="n">
-        <v>9636.9</v>
+        <v>11669.8</v>
       </c>
       <c r="G1457" t="n">
         <v>2</v>
@@ -48538,19 +48538,19 @@
         </is>
       </c>
       <c r="D1458" t="n">
-        <v>100.6</v>
+        <v>201.2</v>
       </c>
       <c r="E1458" t="n">
-        <v>2212.7</v>
+        <v>4384.4</v>
       </c>
       <c r="F1458" t="n">
-        <v>12923.8</v>
+        <v>15095.5</v>
       </c>
       <c r="G1458" t="n">
         <v>1</v>
       </c>
       <c r="H1458" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1458" t="n">
         <v>2</v>
@@ -48571,13 +48571,13 @@
         </is>
       </c>
       <c r="D1459" t="n">
-        <v>65.90000000000001</v>
+        <v>131.8</v>
       </c>
       <c r="E1459" t="n">
-        <v>2127.1</v>
+        <v>4222.2</v>
       </c>
       <c r="F1459" t="n">
-        <v>12818.1</v>
+        <v>14913.2</v>
       </c>
       <c r="G1459" t="n">
         <v>5</v>
@@ -48604,13 +48604,13 @@
         </is>
       </c>
       <c r="D1460" t="n">
-        <v>70.8</v>
+        <v>141.6</v>
       </c>
       <c r="E1460" t="n">
-        <v>2088.1</v>
+        <v>4105.2</v>
       </c>
       <c r="F1460" t="n">
-        <v>11953.2</v>
+        <v>13970.3</v>
       </c>
       <c r="G1460" t="n">
         <v>4</v>
@@ -48637,13 +48637,13 @@
         </is>
       </c>
       <c r="D1461" t="n">
-        <v>60.5</v>
+        <v>121</v>
       </c>
       <c r="E1461" t="n">
-        <v>1888.7</v>
+        <v>3734.4</v>
       </c>
       <c r="F1461" t="n">
-        <v>11553.3</v>
+        <v>13399</v>
       </c>
       <c r="G1461" t="n">
         <v>7</v>
@@ -48670,19 +48670,19 @@
         </is>
       </c>
       <c r="D1462" t="n">
-        <v>64.59999999999999</v>
+        <v>129.2</v>
       </c>
       <c r="E1462" t="n">
-        <v>2227.6</v>
+        <v>4376.2</v>
       </c>
       <c r="F1462" t="n">
-        <v>13162.4</v>
+        <v>15311</v>
       </c>
       <c r="G1462" t="n">
         <v>6</v>
       </c>
       <c r="H1462" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1462" t="n">
         <v>1</v>
@@ -48703,13 +48703,13 @@
         </is>
       </c>
       <c r="D1463" t="n">
-        <v>73.7</v>
+        <v>147.4</v>
       </c>
       <c r="E1463" t="n">
-        <v>1768.2</v>
+        <v>3481.4</v>
       </c>
       <c r="F1463" t="n">
-        <v>10602.1</v>
+        <v>12315.3</v>
       </c>
       <c r="G1463" t="n">
         <v>3</v>
@@ -48736,13 +48736,13 @@
         </is>
       </c>
       <c r="D1464" t="n">
-        <v>55.2</v>
+        <v>110.4</v>
       </c>
       <c r="E1464" t="n">
-        <v>2006.3</v>
+        <v>3961.6</v>
       </c>
       <c r="F1464" t="n">
-        <v>11610.4</v>
+        <v>13565.7</v>
       </c>
       <c r="G1464" t="n">
         <v>8</v>
@@ -48769,13 +48769,13 @@
         </is>
       </c>
       <c r="D1465" t="n">
-        <v>88</v>
+        <v>176</v>
       </c>
       <c r="E1465" t="n">
-        <v>2189.9</v>
+        <v>4310.8</v>
       </c>
       <c r="F1465" t="n">
-        <v>9724.9</v>
+        <v>11845.8</v>
       </c>
       <c r="G1465" t="n">
         <v>2</v>
@@ -48805,16 +48805,16 @@
         <v>76.3</v>
       </c>
       <c r="E1466" t="n">
-        <v>2289</v>
+        <v>4460.7</v>
       </c>
       <c r="F1466" t="n">
-        <v>13000.1</v>
+        <v>15171.8</v>
       </c>
       <c r="G1466" t="n">
         <v>3</v>
       </c>
       <c r="H1466" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1466" t="n">
         <v>2</v>
@@ -48838,10 +48838,10 @@
         <v>73.3</v>
       </c>
       <c r="E1467" t="n">
-        <v>2200.4</v>
+        <v>4295.5</v>
       </c>
       <c r="F1467" t="n">
-        <v>12891.4</v>
+        <v>14986.5</v>
       </c>
       <c r="G1467" t="n">
         <v>5</v>
@@ -48871,10 +48871,10 @@
         <v>56.5</v>
       </c>
       <c r="E1468" t="n">
-        <v>2144.6</v>
+        <v>4161.7</v>
       </c>
       <c r="F1468" t="n">
-        <v>12009.7</v>
+        <v>14026.8</v>
       </c>
       <c r="G1468" t="n">
         <v>7</v>
@@ -48904,10 +48904,10 @@
         <v>75.09999999999999</v>
       </c>
       <c r="E1469" t="n">
-        <v>1963.8</v>
+        <v>3809.5</v>
       </c>
       <c r="F1469" t="n">
-        <v>11628.4</v>
+        <v>13474.1</v>
       </c>
       <c r="G1469" t="n">
         <v>4</v>
@@ -48937,16 +48937,16 @@
         <v>69.7</v>
       </c>
       <c r="E1470" t="n">
-        <v>2297.3</v>
+        <v>4445.9</v>
       </c>
       <c r="F1470" t="n">
-        <v>13232.1</v>
+        <v>15380.7</v>
       </c>
       <c r="G1470" t="n">
         <v>6</v>
       </c>
       <c r="H1470" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1470" t="n">
         <v>1</v>
@@ -48970,10 +48970,10 @@
         <v>80.09999999999999</v>
       </c>
       <c r="E1471" t="n">
-        <v>1848.3</v>
+        <v>3561.5</v>
       </c>
       <c r="F1471" t="n">
-        <v>10682.2</v>
+        <v>12395.4</v>
       </c>
       <c r="G1471" t="n">
         <v>2</v>
@@ -49003,10 +49003,10 @@
         <v>44.9</v>
       </c>
       <c r="E1472" t="n">
-        <v>2051.2</v>
+        <v>4006.5</v>
       </c>
       <c r="F1472" t="n">
-        <v>11655.3</v>
+        <v>13610.6</v>
       </c>
       <c r="G1472" t="n">
         <v>8</v>
@@ -49036,10 +49036,10 @@
         <v>82.40000000000001</v>
       </c>
       <c r="E1473" t="n">
-        <v>2272.3</v>
+        <v>4393.2</v>
       </c>
       <c r="F1473" t="n">
-        <v>9807.299999999999</v>
+        <v>11928.2</v>
       </c>
       <c r="G1473" t="n">
         <v>1</v>

--- a/datos/vistas_negocio/Fact_Global_Master.xlsx
+++ b/datos/vistas_negocio/Fact_Global_Master.xlsx
@@ -40882,13 +40882,13 @@
         </is>
       </c>
       <c r="D1226" t="n">
-        <v>88.40000000000001</v>
+        <v>132.6</v>
       </c>
       <c r="E1226" t="n">
-        <v>129.4</v>
+        <v>173.6</v>
       </c>
       <c r="F1226" t="n">
-        <v>10840.5</v>
+        <v>10884.7</v>
       </c>
       <c r="G1226" t="n">
         <v>8</v>
@@ -40915,13 +40915,13 @@
         </is>
       </c>
       <c r="D1227" t="n">
-        <v>186.6</v>
+        <v>279.9</v>
       </c>
       <c r="E1227" t="n">
-        <v>218.6</v>
+        <v>311.9</v>
       </c>
       <c r="F1227" t="n">
-        <v>10909.6</v>
+        <v>11002.9</v>
       </c>
       <c r="G1227" t="n">
         <v>2</v>
@@ -40948,13 +40948,13 @@
         </is>
       </c>
       <c r="D1228" t="n">
-        <v>126.8</v>
+        <v>190.2</v>
       </c>
       <c r="E1228" t="n">
-        <v>197.8</v>
+        <v>261.2</v>
       </c>
       <c r="F1228" t="n">
-        <v>10062.9</v>
+        <v>10126.3</v>
       </c>
       <c r="G1228" t="n">
         <v>4</v>
@@ -40981,13 +40981,13 @@
         </is>
       </c>
       <c r="D1229" t="n">
-        <v>206</v>
+        <v>309</v>
       </c>
       <c r="E1229" t="n">
-        <v>249</v>
+        <v>352</v>
       </c>
       <c r="F1229" t="n">
-        <v>9913.6</v>
+        <v>10016.6</v>
       </c>
       <c r="G1229" t="n">
         <v>1</v>
@@ -41014,19 +41014,19 @@
         </is>
       </c>
       <c r="D1230" t="n">
-        <v>120.4</v>
+        <v>180.6</v>
       </c>
       <c r="E1230" t="n">
-        <v>199.4</v>
+        <v>259.6</v>
       </c>
       <c r="F1230" t="n">
-        <v>11134.2</v>
+        <v>11194.4</v>
       </c>
       <c r="G1230" t="n">
         <v>5</v>
       </c>
       <c r="H1230" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I1230" t="n">
         <v>1</v>
@@ -41047,13 +41047,13 @@
         </is>
       </c>
       <c r="D1231" t="n">
-        <v>89.2</v>
+        <v>133.8</v>
       </c>
       <c r="E1231" t="n">
-        <v>144.2</v>
+        <v>188.8</v>
       </c>
       <c r="F1231" t="n">
-        <v>8978.1</v>
+        <v>9022.700000000001</v>
       </c>
       <c r="G1231" t="n">
         <v>7</v>
@@ -41080,19 +41080,19 @@
         </is>
       </c>
       <c r="D1232" t="n">
-        <v>140.2</v>
+        <v>210.3</v>
       </c>
       <c r="E1232" t="n">
-        <v>191.2</v>
+        <v>261.3</v>
       </c>
       <c r="F1232" t="n">
-        <v>9795.299999999999</v>
+        <v>9865.4</v>
       </c>
       <c r="G1232" t="n">
         <v>3</v>
       </c>
       <c r="H1232" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I1232" t="n">
         <v>6</v>
@@ -41113,13 +41113,13 @@
         </is>
       </c>
       <c r="D1233" t="n">
-        <v>115.6</v>
+        <v>173.4</v>
       </c>
       <c r="E1233" t="n">
-        <v>184.6</v>
+        <v>242.4</v>
       </c>
       <c r="F1233" t="n">
-        <v>7719.6</v>
+        <v>7777.4</v>
       </c>
       <c r="G1233" t="n">
         <v>6</v>
@@ -41146,13 +41146,13 @@
         </is>
       </c>
       <c r="D1234" t="n">
-        <v>124.8</v>
+        <v>187.2</v>
       </c>
       <c r="E1234" t="n">
-        <v>254.2</v>
+        <v>360.8</v>
       </c>
       <c r="F1234" t="n">
-        <v>10965.3</v>
+        <v>11071.9</v>
       </c>
       <c r="G1234" t="n">
         <v>5</v>
@@ -41179,13 +41179,13 @@
         </is>
       </c>
       <c r="D1235" t="n">
-        <v>133.6</v>
+        <v>200.4</v>
       </c>
       <c r="E1235" t="n">
-        <v>352.2</v>
+        <v>512.3000000000001</v>
       </c>
       <c r="F1235" t="n">
-        <v>11043.2</v>
+        <v>11203.3</v>
       </c>
       <c r="G1235" t="n">
         <v>3</v>
@@ -41212,13 +41212,13 @@
         </is>
       </c>
       <c r="D1236" t="n">
-        <v>146</v>
+        <v>219</v>
       </c>
       <c r="E1236" t="n">
-        <v>343.8</v>
+        <v>480.2</v>
       </c>
       <c r="F1236" t="n">
-        <v>10208.9</v>
+        <v>10345.3</v>
       </c>
       <c r="G1236" t="n">
         <v>1</v>
@@ -41245,13 +41245,13 @@
         </is>
       </c>
       <c r="D1237" t="n">
-        <v>127.2</v>
+        <v>190.8</v>
       </c>
       <c r="E1237" t="n">
-        <v>376.2</v>
+        <v>542.8</v>
       </c>
       <c r="F1237" t="n">
-        <v>10040.8</v>
+        <v>10207.4</v>
       </c>
       <c r="G1237" t="n">
         <v>4</v>
@@ -41278,13 +41278,13 @@
         </is>
       </c>
       <c r="D1238" t="n">
-        <v>140</v>
+        <v>210</v>
       </c>
       <c r="E1238" t="n">
-        <v>339.4</v>
+        <v>469.6</v>
       </c>
       <c r="F1238" t="n">
-        <v>11274.2</v>
+        <v>11404.4</v>
       </c>
       <c r="G1238" t="n">
         <v>2</v>
@@ -41311,13 +41311,13 @@
         </is>
       </c>
       <c r="D1239" t="n">
-        <v>81</v>
+        <v>121.5</v>
       </c>
       <c r="E1239" t="n">
-        <v>225.2</v>
+        <v>310.3</v>
       </c>
       <c r="F1239" t="n">
-        <v>9059.1</v>
+        <v>9144.200000000001</v>
       </c>
       <c r="G1239" t="n">
         <v>8</v>
@@ -41344,13 +41344,13 @@
         </is>
       </c>
       <c r="D1240" t="n">
-        <v>119.6</v>
+        <v>179.4</v>
       </c>
       <c r="E1240" t="n">
-        <v>310.8</v>
+        <v>440.7</v>
       </c>
       <c r="F1240" t="n">
-        <v>9914.9</v>
+        <v>10044.8</v>
       </c>
       <c r="G1240" t="n">
         <v>6</v>
@@ -41377,13 +41377,13 @@
         </is>
       </c>
       <c r="D1241" t="n">
-        <v>87</v>
+        <v>130.5</v>
       </c>
       <c r="E1241" t="n">
-        <v>271.6</v>
+        <v>372.9</v>
       </c>
       <c r="F1241" t="n">
-        <v>7806.6</v>
+        <v>7907.9</v>
       </c>
       <c r="G1241" t="n">
         <v>7</v>
@@ -41410,13 +41410,13 @@
         </is>
       </c>
       <c r="D1242" t="n">
-        <v>113.8</v>
+        <v>170.7</v>
       </c>
       <c r="E1242" t="n">
-        <v>368</v>
+        <v>531.5</v>
       </c>
       <c r="F1242" t="n">
-        <v>11079.1</v>
+        <v>11242.6</v>
       </c>
       <c r="G1242" t="n">
         <v>4</v>
@@ -41443,13 +41443,13 @@
         </is>
       </c>
       <c r="D1243" t="n">
-        <v>110.2</v>
+        <v>165.3</v>
       </c>
       <c r="E1243" t="n">
-        <v>462.4</v>
+        <v>677.6</v>
       </c>
       <c r="F1243" t="n">
-        <v>11153.4</v>
+        <v>11368.6</v>
       </c>
       <c r="G1243" t="n">
         <v>6</v>
@@ -41476,13 +41476,13 @@
         </is>
       </c>
       <c r="D1244" t="n">
-        <v>117.6</v>
+        <v>176.4</v>
       </c>
       <c r="E1244" t="n">
-        <v>461.4</v>
+        <v>656.6</v>
       </c>
       <c r="F1244" t="n">
-        <v>10326.5</v>
+        <v>10521.7</v>
       </c>
       <c r="G1244" t="n">
         <v>3</v>
@@ -41509,13 +41509,13 @@
         </is>
       </c>
       <c r="D1245" t="n">
-        <v>172.4</v>
+        <v>258.6</v>
       </c>
       <c r="E1245" t="n">
-        <v>548.6</v>
+        <v>801.4000000000001</v>
       </c>
       <c r="F1245" t="n">
-        <v>10213.2</v>
+        <v>10466</v>
       </c>
       <c r="G1245" t="n">
         <v>1</v>
@@ -41542,13 +41542,13 @@
         </is>
       </c>
       <c r="D1246" t="n">
-        <v>113.6</v>
+        <v>170.4</v>
       </c>
       <c r="E1246" t="n">
-        <v>453</v>
+        <v>640</v>
       </c>
       <c r="F1246" t="n">
-        <v>11387.8</v>
+        <v>11574.8</v>
       </c>
       <c r="G1246" t="n">
         <v>5</v>
@@ -41575,13 +41575,13 @@
         </is>
       </c>
       <c r="D1247" t="n">
-        <v>107</v>
+        <v>160.5</v>
       </c>
       <c r="E1247" t="n">
-        <v>332.2</v>
+        <v>470.8</v>
       </c>
       <c r="F1247" t="n">
-        <v>9166.1</v>
+        <v>9304.700000000001</v>
       </c>
       <c r="G1247" t="n">
         <v>7</v>
@@ -41608,13 +41608,13 @@
         </is>
       </c>
       <c r="D1248" t="n">
-        <v>88.40000000000001</v>
+        <v>132.6</v>
       </c>
       <c r="E1248" t="n">
-        <v>399.2</v>
+        <v>573.3</v>
       </c>
       <c r="F1248" t="n">
-        <v>10003.3</v>
+        <v>10177.4</v>
       </c>
       <c r="G1248" t="n">
         <v>8</v>
@@ -41641,13 +41641,13 @@
         </is>
       </c>
       <c r="D1249" t="n">
-        <v>143</v>
+        <v>214.5</v>
       </c>
       <c r="E1249" t="n">
-        <v>414.6</v>
+        <v>587.4</v>
       </c>
       <c r="F1249" t="n">
-        <v>7949.6</v>
+        <v>8122.4</v>
       </c>
       <c r="G1249" t="n">
         <v>2</v>
@@ -41674,13 +41674,13 @@
         </is>
       </c>
       <c r="D1250" t="n">
-        <v>99.80000000000001</v>
+        <v>149.7</v>
       </c>
       <c r="E1250" t="n">
-        <v>467.8</v>
+        <v>681.2</v>
       </c>
       <c r="F1250" t="n">
-        <v>11178.9</v>
+        <v>11392.3</v>
       </c>
       <c r="G1250" t="n">
         <v>8</v>
@@ -41707,13 +41707,13 @@
         </is>
       </c>
       <c r="D1251" t="n">
-        <v>140.8</v>
+        <v>211.2</v>
       </c>
       <c r="E1251" t="n">
-        <v>603.2</v>
+        <v>888.8</v>
       </c>
       <c r="F1251" t="n">
-        <v>11294.2</v>
+        <v>11579.8</v>
       </c>
       <c r="G1251" t="n">
         <v>5</v>
@@ -41740,13 +41740,13 @@
         </is>
       </c>
       <c r="D1252" t="n">
-        <v>114.2</v>
+        <v>171.3</v>
       </c>
       <c r="E1252" t="n">
-        <v>575.6</v>
+        <v>827.9000000000001</v>
       </c>
       <c r="F1252" t="n">
-        <v>10440.7</v>
+        <v>10693</v>
       </c>
       <c r="G1252" t="n">
         <v>6</v>
@@ -41755,7 +41755,7 @@
         <v>4</v>
       </c>
       <c r="I1252" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1253">
@@ -41773,13 +41773,13 @@
         </is>
       </c>
       <c r="D1253" t="n">
-        <v>165.4</v>
+        <v>248.1</v>
       </c>
       <c r="E1253" t="n">
-        <v>714</v>
+        <v>1049.5</v>
       </c>
       <c r="F1253" t="n">
-        <v>10378.6</v>
+        <v>10714.1</v>
       </c>
       <c r="G1253" t="n">
         <v>2</v>
@@ -41788,7 +41788,7 @@
         <v>1</v>
       </c>
       <c r="I1253" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1254">
@@ -41806,13 +41806,13 @@
         </is>
       </c>
       <c r="D1254" t="n">
-        <v>173</v>
+        <v>259.5</v>
       </c>
       <c r="E1254" t="n">
-        <v>626</v>
+        <v>899.5</v>
       </c>
       <c r="F1254" t="n">
-        <v>11560.8</v>
+        <v>11834.3</v>
       </c>
       <c r="G1254" t="n">
         <v>1</v>
@@ -41839,13 +41839,13 @@
         </is>
       </c>
       <c r="D1255" t="n">
-        <v>151.6</v>
+        <v>227.4</v>
       </c>
       <c r="E1255" t="n">
-        <v>483.8</v>
+        <v>698.2</v>
       </c>
       <c r="F1255" t="n">
-        <v>9317.700000000001</v>
+        <v>9532.1</v>
       </c>
       <c r="G1255" t="n">
         <v>4</v>
@@ -41872,13 +41872,13 @@
         </is>
       </c>
       <c r="D1256" t="n">
-        <v>155.4</v>
+        <v>233.1</v>
       </c>
       <c r="E1256" t="n">
-        <v>554.6</v>
+        <v>806.4</v>
       </c>
       <c r="F1256" t="n">
-        <v>10158.7</v>
+        <v>10410.5</v>
       </c>
       <c r="G1256" t="n">
         <v>3</v>
@@ -41905,13 +41905,13 @@
         </is>
       </c>
       <c r="D1257" t="n">
-        <v>111.2</v>
+        <v>166.8</v>
       </c>
       <c r="E1257" t="n">
-        <v>525.8</v>
+        <v>754.2</v>
       </c>
       <c r="F1257" t="n">
-        <v>8060.8</v>
+        <v>8289.200000000001</v>
       </c>
       <c r="G1257" t="n">
         <v>7</v>
@@ -41938,13 +41938,13 @@
         </is>
       </c>
       <c r="D1258" t="n">
-        <v>68.40000000000001</v>
+        <v>102.6</v>
       </c>
       <c r="E1258" t="n">
-        <v>536.2</v>
+        <v>783.8</v>
       </c>
       <c r="F1258" t="n">
-        <v>11247.3</v>
+        <v>11494.9</v>
       </c>
       <c r="G1258" t="n">
         <v>6</v>
@@ -41971,13 +41971,13 @@
         </is>
       </c>
       <c r="D1259" t="n">
-        <v>91.2</v>
+        <v>136.8</v>
       </c>
       <c r="E1259" t="n">
-        <v>694.4</v>
+        <v>1025.6</v>
       </c>
       <c r="F1259" t="n">
-        <v>11385.4</v>
+        <v>11716.6</v>
       </c>
       <c r="G1259" t="n">
         <v>5</v>
@@ -42004,13 +42004,13 @@
         </is>
       </c>
       <c r="D1260" t="n">
-        <v>112.2</v>
+        <v>168.3</v>
       </c>
       <c r="E1260" t="n">
-        <v>687.8</v>
+        <v>996.2</v>
       </c>
       <c r="F1260" t="n">
-        <v>10552.9</v>
+        <v>10861.3</v>
       </c>
       <c r="G1260" t="n">
         <v>3</v>
@@ -42019,7 +42019,7 @@
         <v>4</v>
       </c>
       <c r="I1260" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1261">
@@ -42037,13 +42037,13 @@
         </is>
       </c>
       <c r="D1261" t="n">
-        <v>123.4</v>
+        <v>185.1</v>
       </c>
       <c r="E1261" t="n">
-        <v>837.4000000000001</v>
+        <v>1234.6</v>
       </c>
       <c r="F1261" t="n">
-        <v>10502</v>
+        <v>10899.2</v>
       </c>
       <c r="G1261" t="n">
         <v>1</v>
@@ -42052,7 +42052,7 @@
         <v>1</v>
       </c>
       <c r="I1261" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1262">
@@ -42070,13 +42070,13 @@
         </is>
       </c>
       <c r="D1262" t="n">
-        <v>116.6</v>
+        <v>174.9</v>
       </c>
       <c r="E1262" t="n">
-        <v>742.6</v>
+        <v>1074.4</v>
       </c>
       <c r="F1262" t="n">
-        <v>11677.4</v>
+        <v>12009.2</v>
       </c>
       <c r="G1262" t="n">
         <v>2</v>
@@ -42103,13 +42103,13 @@
         </is>
       </c>
       <c r="D1263" t="n">
-        <v>95.8</v>
+        <v>143.7</v>
       </c>
       <c r="E1263" t="n">
-        <v>579.6</v>
+        <v>841.9</v>
       </c>
       <c r="F1263" t="n">
-        <v>9413.5</v>
+        <v>9675.799999999999</v>
       </c>
       <c r="G1263" t="n">
         <v>4</v>
@@ -42136,13 +42136,13 @@
         </is>
       </c>
       <c r="D1264" t="n">
-        <v>64.8</v>
+        <v>97.2</v>
       </c>
       <c r="E1264" t="n">
-        <v>619.4</v>
+        <v>903.6</v>
       </c>
       <c r="F1264" t="n">
-        <v>10223.5</v>
+        <v>10507.7</v>
       </c>
       <c r="G1264" t="n">
         <v>8</v>
@@ -42169,13 +42169,13 @@
         </is>
       </c>
       <c r="D1265" t="n">
-        <v>68.40000000000001</v>
+        <v>102.6</v>
       </c>
       <c r="E1265" t="n">
-        <v>594.2</v>
+        <v>856.8</v>
       </c>
       <c r="F1265" t="n">
-        <v>8129.2</v>
+        <v>8391.799999999999</v>
       </c>
       <c r="G1265" t="n">
         <v>6</v>
@@ -42202,19 +42202,19 @@
         </is>
       </c>
       <c r="D1266" t="n">
-        <v>147.2</v>
+        <v>220.8</v>
       </c>
       <c r="E1266" t="n">
-        <v>683.4</v>
+        <v>1004.6</v>
       </c>
       <c r="F1266" t="n">
-        <v>11394.5</v>
+        <v>11715.7</v>
       </c>
       <c r="G1266" t="n">
         <v>3</v>
       </c>
       <c r="H1266" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I1266" t="n">
         <v>3</v>
@@ -42235,13 +42235,13 @@
         </is>
       </c>
       <c r="D1267" t="n">
-        <v>118.8</v>
+        <v>178.2</v>
       </c>
       <c r="E1267" t="n">
-        <v>813.2</v>
+        <v>1203.8</v>
       </c>
       <c r="F1267" t="n">
-        <v>11504.2</v>
+        <v>11894.8</v>
       </c>
       <c r="G1267" t="n">
         <v>5</v>
@@ -42268,13 +42268,13 @@
         </is>
       </c>
       <c r="D1268" t="n">
-        <v>157.2</v>
+        <v>235.8</v>
       </c>
       <c r="E1268" t="n">
-        <v>845</v>
+        <v>1232</v>
       </c>
       <c r="F1268" t="n">
-        <v>10710.1</v>
+        <v>11097.1</v>
       </c>
       <c r="G1268" t="n">
         <v>1</v>
@@ -42301,13 +42301,13 @@
         </is>
       </c>
       <c r="D1269" t="n">
-        <v>92</v>
+        <v>138</v>
       </c>
       <c r="E1269" t="n">
-        <v>929.4000000000001</v>
+        <v>1372.6</v>
       </c>
       <c r="F1269" t="n">
-        <v>10594</v>
+        <v>11037.2</v>
       </c>
       <c r="G1269" t="n">
         <v>8</v>
@@ -42334,13 +42334,13 @@
         </is>
       </c>
       <c r="D1270" t="n">
-        <v>140.2</v>
+        <v>210.3</v>
       </c>
       <c r="E1270" t="n">
-        <v>882.8</v>
+        <v>1284.7</v>
       </c>
       <c r="F1270" t="n">
-        <v>11817.6</v>
+        <v>12219.5</v>
       </c>
       <c r="G1270" t="n">
         <v>4</v>
@@ -42367,19 +42367,19 @@
         </is>
       </c>
       <c r="D1271" t="n">
-        <v>105</v>
+        <v>157.5</v>
       </c>
       <c r="E1271" t="n">
-        <v>684.6</v>
+        <v>999.4</v>
       </c>
       <c r="F1271" t="n">
-        <v>9518.5</v>
+        <v>9833.299999999999</v>
       </c>
       <c r="G1271" t="n">
         <v>7</v>
       </c>
       <c r="H1271" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I1271" t="n">
         <v>7</v>
@@ -42400,13 +42400,13 @@
         </is>
       </c>
       <c r="D1272" t="n">
-        <v>149.8</v>
+        <v>224.7</v>
       </c>
       <c r="E1272" t="n">
-        <v>769.2</v>
+        <v>1128.3</v>
       </c>
       <c r="F1272" t="n">
-        <v>10373.3</v>
+        <v>10732.4</v>
       </c>
       <c r="G1272" t="n">
         <v>2</v>
@@ -42433,13 +42433,13 @@
         </is>
       </c>
       <c r="D1273" t="n">
-        <v>116.4</v>
+        <v>174.6</v>
       </c>
       <c r="E1273" t="n">
-        <v>710.6</v>
+        <v>1031.4</v>
       </c>
       <c r="F1273" t="n">
-        <v>8245.6</v>
+        <v>8566.4</v>
       </c>
       <c r="G1273" t="n">
         <v>6</v>
@@ -42466,19 +42466,19 @@
         </is>
       </c>
       <c r="D1274" t="n">
-        <v>107.6</v>
+        <v>161.4</v>
       </c>
       <c r="E1274" t="n">
-        <v>791</v>
+        <v>1166</v>
       </c>
       <c r="F1274" t="n">
-        <v>11502.1</v>
+        <v>11877.1</v>
       </c>
       <c r="G1274" t="n">
         <v>7</v>
       </c>
       <c r="H1274" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I1274" t="n">
         <v>3</v>
@@ -42499,13 +42499,13 @@
         </is>
       </c>
       <c r="D1275" t="n">
-        <v>102.2</v>
+        <v>153.3</v>
       </c>
       <c r="E1275" t="n">
-        <v>915.4</v>
+        <v>1357.1</v>
       </c>
       <c r="F1275" t="n">
-        <v>11606.4</v>
+        <v>12048.1</v>
       </c>
       <c r="G1275" t="n">
         <v>8</v>
@@ -42532,13 +42532,13 @@
         </is>
       </c>
       <c r="D1276" t="n">
-        <v>124.2</v>
+        <v>186.3</v>
       </c>
       <c r="E1276" t="n">
-        <v>969.2</v>
+        <v>1418.3</v>
       </c>
       <c r="F1276" t="n">
-        <v>10834.3</v>
+        <v>11283.4</v>
       </c>
       <c r="G1276" t="n">
         <v>3</v>
@@ -42565,13 +42565,13 @@
         </is>
       </c>
       <c r="D1277" t="n">
-        <v>139</v>
+        <v>208.5</v>
       </c>
       <c r="E1277" t="n">
-        <v>1068.4</v>
+        <v>1581.1</v>
       </c>
       <c r="F1277" t="n">
-        <v>10733</v>
+        <v>11245.7</v>
       </c>
       <c r="G1277" t="n">
         <v>1</v>
@@ -42598,13 +42598,13 @@
         </is>
       </c>
       <c r="D1278" t="n">
-        <v>119</v>
+        <v>178.5</v>
       </c>
       <c r="E1278" t="n">
-        <v>1001.8</v>
+        <v>1463.2</v>
       </c>
       <c r="F1278" t="n">
-        <v>11936.6</v>
+        <v>12398</v>
       </c>
       <c r="G1278" t="n">
         <v>5</v>
@@ -42631,19 +42631,19 @@
         </is>
       </c>
       <c r="D1279" t="n">
-        <v>108.2</v>
+        <v>162.3</v>
       </c>
       <c r="E1279" t="n">
-        <v>792.8</v>
+        <v>1161.7</v>
       </c>
       <c r="F1279" t="n">
-        <v>9626.700000000001</v>
+        <v>9995.6</v>
       </c>
       <c r="G1279" t="n">
         <v>6</v>
       </c>
       <c r="H1279" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I1279" t="n">
         <v>7</v>
@@ -42664,13 +42664,13 @@
         </is>
       </c>
       <c r="D1280" t="n">
-        <v>138.4</v>
+        <v>207.6</v>
       </c>
       <c r="E1280" t="n">
-        <v>907.6</v>
+        <v>1335.9</v>
       </c>
       <c r="F1280" t="n">
-        <v>10511.7</v>
+        <v>10940</v>
       </c>
       <c r="G1280" t="n">
         <v>2</v>
@@ -42697,13 +42697,13 @@
         </is>
       </c>
       <c r="D1281" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="E1281" t="n">
-        <v>830.6</v>
+        <v>1211.4</v>
       </c>
       <c r="F1281" t="n">
-        <v>8365.6</v>
+        <v>8746.4</v>
       </c>
       <c r="G1281" t="n">
         <v>4</v>
@@ -42730,13 +42730,13 @@
         </is>
       </c>
       <c r="D1282" t="n">
-        <v>175.6</v>
+        <v>263.4</v>
       </c>
       <c r="E1282" t="n">
-        <v>966.6</v>
+        <v>1429.4</v>
       </c>
       <c r="F1282" t="n">
-        <v>11677.7</v>
+        <v>12140.5</v>
       </c>
       <c r="G1282" t="n">
         <v>1</v>
@@ -42763,13 +42763,13 @@
         </is>
       </c>
       <c r="D1283" t="n">
-        <v>134</v>
+        <v>201</v>
       </c>
       <c r="E1283" t="n">
-        <v>1049.4</v>
+        <v>1558.1</v>
       </c>
       <c r="F1283" t="n">
-        <v>11740.4</v>
+        <v>12249.1</v>
       </c>
       <c r="G1283" t="n">
         <v>4</v>
@@ -42796,13 +42796,13 @@
         </is>
       </c>
       <c r="D1284" t="n">
-        <v>110.8</v>
+        <v>166.2</v>
       </c>
       <c r="E1284" t="n">
-        <v>1080</v>
+        <v>1584.5</v>
       </c>
       <c r="F1284" t="n">
-        <v>10945.1</v>
+        <v>11449.6</v>
       </c>
       <c r="G1284" t="n">
         <v>7</v>
@@ -42829,13 +42829,13 @@
         </is>
       </c>
       <c r="D1285" t="n">
-        <v>115.2</v>
+        <v>172.8</v>
       </c>
       <c r="E1285" t="n">
-        <v>1183.6</v>
+        <v>1753.9</v>
       </c>
       <c r="F1285" t="n">
-        <v>10848.2</v>
+        <v>11418.5</v>
       </c>
       <c r="G1285" t="n">
         <v>6</v>
@@ -42862,13 +42862,13 @@
         </is>
       </c>
       <c r="D1286" t="n">
-        <v>132.6</v>
+        <v>198.9</v>
       </c>
       <c r="E1286" t="n">
-        <v>1134.4</v>
+        <v>1662.1</v>
       </c>
       <c r="F1286" t="n">
-        <v>12069.2</v>
+        <v>12596.9</v>
       </c>
       <c r="G1286" t="n">
         <v>5</v>
@@ -42895,13 +42895,13 @@
         </is>
       </c>
       <c r="D1287" t="n">
-        <v>104.2</v>
+        <v>156.3</v>
       </c>
       <c r="E1287" t="n">
-        <v>897</v>
+        <v>1318</v>
       </c>
       <c r="F1287" t="n">
-        <v>9730.9</v>
+        <v>10151.9</v>
       </c>
       <c r="G1287" t="n">
         <v>8</v>
@@ -42928,13 +42928,13 @@
         </is>
       </c>
       <c r="D1288" t="n">
-        <v>162.2</v>
+        <v>243.3</v>
       </c>
       <c r="E1288" t="n">
-        <v>1069.8</v>
+        <v>1579.2</v>
       </c>
       <c r="F1288" t="n">
-        <v>10673.9</v>
+        <v>11183.3</v>
       </c>
       <c r="G1288" t="n">
         <v>2</v>
@@ -42961,13 +42961,13 @@
         </is>
       </c>
       <c r="D1289" t="n">
-        <v>153.8</v>
+        <v>230.7</v>
       </c>
       <c r="E1289" t="n">
-        <v>984.4</v>
+        <v>1442.1</v>
       </c>
       <c r="F1289" t="n">
-        <v>8519.4</v>
+        <v>8977.1</v>
       </c>
       <c r="G1289" t="n">
         <v>3</v>
@@ -42994,13 +42994,13 @@
         </is>
       </c>
       <c r="D1290" t="n">
-        <v>155.8</v>
+        <v>233.7</v>
       </c>
       <c r="E1290" t="n">
-        <v>1122.4</v>
+        <v>1663.1</v>
       </c>
       <c r="F1290" t="n">
-        <v>11833.5</v>
+        <v>12374.2</v>
       </c>
       <c r="G1290" t="n">
         <v>1</v>
@@ -43027,13 +43027,13 @@
         </is>
       </c>
       <c r="D1291" t="n">
-        <v>109.6</v>
+        <v>164.4</v>
       </c>
       <c r="E1291" t="n">
-        <v>1159</v>
+        <v>1722.5</v>
       </c>
       <c r="F1291" t="n">
-        <v>11850</v>
+        <v>12413.5</v>
       </c>
       <c r="G1291" t="n">
         <v>7</v>
@@ -43060,13 +43060,13 @@
         </is>
       </c>
       <c r="D1292" t="n">
-        <v>137.6</v>
+        <v>206.4</v>
       </c>
       <c r="E1292" t="n">
-        <v>1217.6</v>
+        <v>1790.9</v>
       </c>
       <c r="F1292" t="n">
-        <v>11082.7</v>
+        <v>11656</v>
       </c>
       <c r="G1292" t="n">
         <v>3</v>
@@ -43093,13 +43093,13 @@
         </is>
       </c>
       <c r="D1293" t="n">
-        <v>120.4</v>
+        <v>180.6</v>
       </c>
       <c r="E1293" t="n">
-        <v>1304</v>
+        <v>1934.5</v>
       </c>
       <c r="F1293" t="n">
-        <v>10968.6</v>
+        <v>11599.1</v>
       </c>
       <c r="G1293" t="n">
         <v>6</v>
@@ -43126,13 +43126,13 @@
         </is>
       </c>
       <c r="D1294" t="n">
-        <v>125.6</v>
+        <v>188.4</v>
       </c>
       <c r="E1294" t="n">
-        <v>1260</v>
+        <v>1850.5</v>
       </c>
       <c r="F1294" t="n">
-        <v>12194.8</v>
+        <v>12785.3</v>
       </c>
       <c r="G1294" t="n">
         <v>5</v>
@@ -43159,13 +43159,13 @@
         </is>
       </c>
       <c r="D1295" t="n">
-        <v>101.8</v>
+        <v>152.7</v>
       </c>
       <c r="E1295" t="n">
-        <v>998.8</v>
+        <v>1470.7</v>
       </c>
       <c r="F1295" t="n">
-        <v>9832.700000000001</v>
+        <v>10304.6</v>
       </c>
       <c r="G1295" t="n">
         <v>8</v>
@@ -43192,13 +43192,13 @@
         </is>
       </c>
       <c r="D1296" t="n">
-        <v>138.8</v>
+        <v>208.2</v>
       </c>
       <c r="E1296" t="n">
-        <v>1208.6</v>
+        <v>1787.4</v>
       </c>
       <c r="F1296" t="n">
-        <v>10812.7</v>
+        <v>11391.5</v>
       </c>
       <c r="G1296" t="n">
         <v>2</v>
@@ -43225,13 +43225,13 @@
         </is>
       </c>
       <c r="D1297" t="n">
-        <v>132.6</v>
+        <v>198.9</v>
       </c>
       <c r="E1297" t="n">
-        <v>1117</v>
+        <v>1641</v>
       </c>
       <c r="F1297" t="n">
-        <v>8652</v>
+        <v>9176</v>
       </c>
       <c r="G1297" t="n">
         <v>4</v>
@@ -43258,13 +43258,13 @@
         </is>
       </c>
       <c r="D1298" t="n">
-        <v>136</v>
+        <v>204</v>
       </c>
       <c r="E1298" t="n">
-        <v>1258.4</v>
+        <v>1867.1</v>
       </c>
       <c r="F1298" t="n">
-        <v>11969.5</v>
+        <v>12578.2</v>
       </c>
       <c r="G1298" t="n">
         <v>5</v>
@@ -43291,13 +43291,13 @@
         </is>
       </c>
       <c r="D1299" t="n">
-        <v>178.4</v>
+        <v>267.6</v>
       </c>
       <c r="E1299" t="n">
-        <v>1337.4</v>
+        <v>1990.1</v>
       </c>
       <c r="F1299" t="n">
-        <v>12028.4</v>
+        <v>12681.1</v>
       </c>
       <c r="G1299" t="n">
         <v>2</v>
@@ -43324,13 +43324,13 @@
         </is>
       </c>
       <c r="D1300" t="n">
-        <v>158.6</v>
+        <v>237.9</v>
       </c>
       <c r="E1300" t="n">
-        <v>1376.2</v>
+        <v>2028.8</v>
       </c>
       <c r="F1300" t="n">
-        <v>11241.3</v>
+        <v>11893.9</v>
       </c>
       <c r="G1300" t="n">
         <v>3</v>
@@ -43357,13 +43357,13 @@
         </is>
       </c>
       <c r="D1301" t="n">
-        <v>122</v>
+        <v>183</v>
       </c>
       <c r="E1301" t="n">
-        <v>1426</v>
+        <v>2117.5</v>
       </c>
       <c r="F1301" t="n">
-        <v>11090.6</v>
+        <v>11782.1</v>
       </c>
       <c r="G1301" t="n">
         <v>6</v>
@@ -43390,13 +43390,13 @@
         </is>
       </c>
       <c r="D1302" t="n">
-        <v>114.8</v>
+        <v>172.2</v>
       </c>
       <c r="E1302" t="n">
-        <v>1374.8</v>
+        <v>2022.7</v>
       </c>
       <c r="F1302" t="n">
-        <v>12309.6</v>
+        <v>12957.5</v>
       </c>
       <c r="G1302" t="n">
         <v>7</v>
@@ -43423,13 +43423,13 @@
         </is>
       </c>
       <c r="D1303" t="n">
-        <v>92.8</v>
+        <v>139.2</v>
       </c>
       <c r="E1303" t="n">
-        <v>1091.6</v>
+        <v>1609.9</v>
       </c>
       <c r="F1303" t="n">
-        <v>9925.5</v>
+        <v>10443.8</v>
       </c>
       <c r="G1303" t="n">
         <v>8</v>
@@ -43456,13 +43456,13 @@
         </is>
       </c>
       <c r="D1304" t="n">
-        <v>154.4</v>
+        <v>231.6</v>
       </c>
       <c r="E1304" t="n">
-        <v>1363</v>
+        <v>2019</v>
       </c>
       <c r="F1304" t="n">
-        <v>10967.1</v>
+        <v>11623.1</v>
       </c>
       <c r="G1304" t="n">
         <v>4</v>
@@ -43489,13 +43489,13 @@
         </is>
       </c>
       <c r="D1305" t="n">
-        <v>190.4</v>
+        <v>285.6</v>
       </c>
       <c r="E1305" t="n">
-        <v>1307.4</v>
+        <v>1926.6</v>
       </c>
       <c r="F1305" t="n">
-        <v>8842.4</v>
+        <v>9461.6</v>
       </c>
       <c r="G1305" t="n">
         <v>1</v>
@@ -43522,13 +43522,13 @@
         </is>
       </c>
       <c r="D1306" t="n">
-        <v>156</v>
+        <v>234</v>
       </c>
       <c r="E1306" t="n">
-        <v>1414.4</v>
+        <v>2101.1</v>
       </c>
       <c r="F1306" t="n">
-        <v>12125.5</v>
+        <v>12812.2</v>
       </c>
       <c r="G1306" t="n">
         <v>3</v>
@@ -43555,19 +43555,19 @@
         </is>
       </c>
       <c r="D1307" t="n">
-        <v>157.2</v>
+        <v>235.8</v>
       </c>
       <c r="E1307" t="n">
-        <v>1494.6</v>
+        <v>2225.9</v>
       </c>
       <c r="F1307" t="n">
-        <v>12185.6</v>
+        <v>12916.9</v>
       </c>
       <c r="G1307" t="n">
         <v>2</v>
       </c>
       <c r="H1307" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1307" t="n">
         <v>2</v>
@@ -43588,19 +43588,19 @@
         </is>
       </c>
       <c r="D1308" t="n">
-        <v>153.8</v>
+        <v>230.7</v>
       </c>
       <c r="E1308" t="n">
-        <v>1530</v>
+        <v>2259.5</v>
       </c>
       <c r="F1308" t="n">
-        <v>11395.1</v>
+        <v>12124.6</v>
       </c>
       <c r="G1308" t="n">
         <v>4</v>
       </c>
       <c r="H1308" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1308" t="n">
         <v>4</v>
@@ -43621,19 +43621,19 @@
         </is>
       </c>
       <c r="D1309" t="n">
-        <v>96.8</v>
+        <v>145.2</v>
       </c>
       <c r="E1309" t="n">
-        <v>1522.8</v>
+        <v>2262.7</v>
       </c>
       <c r="F1309" t="n">
-        <v>11187.4</v>
+        <v>11927.3</v>
       </c>
       <c r="G1309" t="n">
         <v>8</v>
       </c>
       <c r="H1309" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1309" t="n">
         <v>5</v>
@@ -43654,19 +43654,19 @@
         </is>
       </c>
       <c r="D1310" t="n">
-        <v>135.2</v>
+        <v>202.8</v>
       </c>
       <c r="E1310" t="n">
-        <v>1510</v>
+        <v>2225.5</v>
       </c>
       <c r="F1310" t="n">
-        <v>12444.8</v>
+        <v>13160.3</v>
       </c>
       <c r="G1310" t="n">
         <v>5</v>
       </c>
       <c r="H1310" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1310" t="n">
         <v>1</v>
@@ -43687,13 +43687,13 @@
         </is>
       </c>
       <c r="D1311" t="n">
-        <v>116.2</v>
+        <v>174.3</v>
       </c>
       <c r="E1311" t="n">
-        <v>1207.8</v>
+        <v>1784.2</v>
       </c>
       <c r="F1311" t="n">
-        <v>10041.7</v>
+        <v>10618.1</v>
       </c>
       <c r="G1311" t="n">
         <v>7</v>
@@ -43720,13 +43720,13 @@
         </is>
       </c>
       <c r="D1312" t="n">
-        <v>122.8</v>
+        <v>184.2</v>
       </c>
       <c r="E1312" t="n">
-        <v>1485.8</v>
+        <v>2203.2</v>
       </c>
       <c r="F1312" t="n">
-        <v>11089.9</v>
+        <v>11807.3</v>
       </c>
       <c r="G1312" t="n">
         <v>6</v>
@@ -43753,13 +43753,13 @@
         </is>
       </c>
       <c r="D1313" t="n">
-        <v>163.2</v>
+        <v>244.8</v>
       </c>
       <c r="E1313" t="n">
-        <v>1470.6</v>
+        <v>2171.4</v>
       </c>
       <c r="F1313" t="n">
-        <v>9005.6</v>
+        <v>9706.4</v>
       </c>
       <c r="G1313" t="n">
         <v>1</v>
@@ -43786,13 +43786,13 @@
         </is>
       </c>
       <c r="D1314" t="n">
-        <v>135</v>
+        <v>202.5</v>
       </c>
       <c r="E1314" t="n">
-        <v>1549.4</v>
+        <v>2303.6</v>
       </c>
       <c r="F1314" t="n">
-        <v>12260.5</v>
+        <v>13014.7</v>
       </c>
       <c r="G1314" t="n">
         <v>5</v>
@@ -43819,13 +43819,13 @@
         </is>
       </c>
       <c r="D1315" t="n">
-        <v>139.6</v>
+        <v>209.4</v>
       </c>
       <c r="E1315" t="n">
-        <v>1634.2</v>
+        <v>2435.3</v>
       </c>
       <c r="F1315" t="n">
-        <v>12325.2</v>
+        <v>13126.3</v>
       </c>
       <c r="G1315" t="n">
         <v>2</v>
@@ -43852,13 +43852,13 @@
         </is>
       </c>
       <c r="D1316" t="n">
-        <v>136.6</v>
+        <v>204.9</v>
       </c>
       <c r="E1316" t="n">
-        <v>1666.6</v>
+        <v>2464.4</v>
       </c>
       <c r="F1316" t="n">
-        <v>11531.7</v>
+        <v>12329.5</v>
       </c>
       <c r="G1316" t="n">
         <v>3</v>
@@ -43885,13 +43885,13 @@
         </is>
       </c>
       <c r="D1317" t="n">
-        <v>104.2</v>
+        <v>156.3</v>
       </c>
       <c r="E1317" t="n">
-        <v>1627</v>
+        <v>2419</v>
       </c>
       <c r="F1317" t="n">
-        <v>11291.6</v>
+        <v>12083.6</v>
       </c>
       <c r="G1317" t="n">
         <v>8</v>
@@ -43918,13 +43918,13 @@
         </is>
       </c>
       <c r="D1318" t="n">
-        <v>159.4</v>
+        <v>239.1</v>
       </c>
       <c r="E1318" t="n">
-        <v>1669.4</v>
+        <v>2464.6</v>
       </c>
       <c r="F1318" t="n">
-        <v>12604.2</v>
+        <v>13399.4</v>
       </c>
       <c r="G1318" t="n">
         <v>1</v>
@@ -43951,13 +43951,13 @@
         </is>
       </c>
       <c r="D1319" t="n">
-        <v>116</v>
+        <v>174</v>
       </c>
       <c r="E1319" t="n">
-        <v>1323.8</v>
+        <v>1958.2</v>
       </c>
       <c r="F1319" t="n">
-        <v>10157.7</v>
+        <v>10792.1</v>
       </c>
       <c r="G1319" t="n">
         <v>7</v>
@@ -43984,19 +43984,19 @@
         </is>
       </c>
       <c r="D1320" t="n">
-        <v>119</v>
+        <v>178.5</v>
       </c>
       <c r="E1320" t="n">
-        <v>1604.8</v>
+        <v>2381.7</v>
       </c>
       <c r="F1320" t="n">
-        <v>11208.9</v>
+        <v>11985.8</v>
       </c>
       <c r="G1320" t="n">
         <v>6</v>
       </c>
       <c r="H1320" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I1320" t="n">
         <v>6</v>
@@ -44017,19 +44017,19 @@
         </is>
       </c>
       <c r="D1321" t="n">
-        <v>136.2</v>
+        <v>204.3</v>
       </c>
       <c r="E1321" t="n">
-        <v>1606.8</v>
+        <v>2375.7</v>
       </c>
       <c r="F1321" t="n">
-        <v>9141.799999999999</v>
+        <v>9910.700000000001</v>
       </c>
       <c r="G1321" t="n">
         <v>4</v>
       </c>
       <c r="H1321" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I1321" t="n">
         <v>8</v>
@@ -44050,13 +44050,13 @@
         </is>
       </c>
       <c r="D1322" t="n">
-        <v>117.2</v>
+        <v>175.8</v>
       </c>
       <c r="E1322" t="n">
-        <v>1666.6</v>
+        <v>2479.4</v>
       </c>
       <c r="F1322" t="n">
-        <v>12377.7</v>
+        <v>13190.5</v>
       </c>
       <c r="G1322" t="n">
         <v>6</v>
@@ -44083,13 +44083,13 @@
         </is>
       </c>
       <c r="D1323" t="n">
-        <v>211.4</v>
+        <v>317.1</v>
       </c>
       <c r="E1323" t="n">
-        <v>1845.6</v>
+        <v>2752.4</v>
       </c>
       <c r="F1323" t="n">
-        <v>12536.6</v>
+        <v>13443.4</v>
       </c>
       <c r="G1323" t="n">
         <v>1</v>
@@ -44116,13 +44116,13 @@
         </is>
       </c>
       <c r="D1324" t="n">
-        <v>116.8</v>
+        <v>175.2</v>
       </c>
       <c r="E1324" t="n">
-        <v>1783.4</v>
+        <v>2639.6</v>
       </c>
       <c r="F1324" t="n">
-        <v>11648.5</v>
+        <v>12504.7</v>
       </c>
       <c r="G1324" t="n">
         <v>7</v>
@@ -44149,13 +44149,13 @@
         </is>
       </c>
       <c r="D1325" t="n">
-        <v>114.8</v>
+        <v>172.2</v>
       </c>
       <c r="E1325" t="n">
-        <v>1741.8</v>
+        <v>2591.2</v>
       </c>
       <c r="F1325" t="n">
-        <v>11406.4</v>
+        <v>12255.8</v>
       </c>
       <c r="G1325" t="n">
         <v>8</v>
@@ -44182,13 +44182,13 @@
         </is>
       </c>
       <c r="D1326" t="n">
-        <v>166.8</v>
+        <v>250.2</v>
       </c>
       <c r="E1326" t="n">
-        <v>1836.2</v>
+        <v>2714.8</v>
       </c>
       <c r="F1326" t="n">
-        <v>12771</v>
+        <v>13649.6</v>
       </c>
       <c r="G1326" t="n">
         <v>3</v>
@@ -44215,13 +44215,13 @@
         </is>
       </c>
       <c r="D1327" t="n">
-        <v>148.6</v>
+        <v>222.9</v>
       </c>
       <c r="E1327" t="n">
-        <v>1472.4</v>
+        <v>2181.1</v>
       </c>
       <c r="F1327" t="n">
-        <v>10306.3</v>
+        <v>11015</v>
       </c>
       <c r="G1327" t="n">
         <v>4</v>
@@ -44248,13 +44248,13 @@
         </is>
       </c>
       <c r="D1328" t="n">
-        <v>144</v>
+        <v>216</v>
       </c>
       <c r="E1328" t="n">
-        <v>1748.8</v>
+        <v>2597.7</v>
       </c>
       <c r="F1328" t="n">
-        <v>11352.9</v>
+        <v>12201.8</v>
       </c>
       <c r="G1328" t="n">
         <v>5</v>
@@ -44281,13 +44281,13 @@
         </is>
       </c>
       <c r="D1329" t="n">
-        <v>174.2</v>
+        <v>261.3</v>
       </c>
       <c r="E1329" t="n">
-        <v>1781</v>
+        <v>2637</v>
       </c>
       <c r="F1329" t="n">
-        <v>9316</v>
+        <v>10172</v>
       </c>
       <c r="G1329" t="n">
         <v>2</v>
@@ -44314,13 +44314,13 @@
         </is>
       </c>
       <c r="D1330" t="n">
-        <v>122.4</v>
+        <v>183.6</v>
       </c>
       <c r="E1330" t="n">
-        <v>1789</v>
+        <v>2663</v>
       </c>
       <c r="F1330" t="n">
-        <v>12500.1</v>
+        <v>13374.1</v>
       </c>
       <c r="G1330" t="n">
         <v>5</v>
@@ -44347,13 +44347,13 @@
         </is>
       </c>
       <c r="D1331" t="n">
-        <v>111.2</v>
+        <v>166.8</v>
       </c>
       <c r="E1331" t="n">
-        <v>1956.8</v>
+        <v>2919.2</v>
       </c>
       <c r="F1331" t="n">
-        <v>12647.8</v>
+        <v>13610.2</v>
       </c>
       <c r="G1331" t="n">
         <v>7</v>
@@ -44380,13 +44380,13 @@
         </is>
       </c>
       <c r="D1332" t="n">
-        <v>101.2</v>
+        <v>151.8</v>
       </c>
       <c r="E1332" t="n">
-        <v>1884.6</v>
+        <v>2791.4</v>
       </c>
       <c r="F1332" t="n">
-        <v>11749.7</v>
+        <v>12656.5</v>
       </c>
       <c r="G1332" t="n">
         <v>8</v>
@@ -44413,13 +44413,13 @@
         </is>
       </c>
       <c r="D1333" t="n">
-        <v>124.8</v>
+        <v>187.2</v>
       </c>
       <c r="E1333" t="n">
-        <v>1866.6</v>
+        <v>2778.4</v>
       </c>
       <c r="F1333" t="n">
-        <v>11531.2</v>
+        <v>12443</v>
       </c>
       <c r="G1333" t="n">
         <v>4</v>
@@ -44428,7 +44428,7 @@
         <v>6</v>
       </c>
       <c r="I1333" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1334">
@@ -44446,13 +44446,13 @@
         </is>
       </c>
       <c r="D1334" t="n">
-        <v>163.8</v>
+        <v>245.7</v>
       </c>
       <c r="E1334" t="n">
-        <v>2000</v>
+        <v>2960.5</v>
       </c>
       <c r="F1334" t="n">
-        <v>12934.8</v>
+        <v>13895.3</v>
       </c>
       <c r="G1334" t="n">
         <v>2</v>
@@ -44479,13 +44479,13 @@
         </is>
       </c>
       <c r="D1335" t="n">
-        <v>126.6</v>
+        <v>189.9</v>
       </c>
       <c r="E1335" t="n">
-        <v>1599</v>
+        <v>2371</v>
       </c>
       <c r="F1335" t="n">
-        <v>10432.9</v>
+        <v>11204.9</v>
       </c>
       <c r="G1335" t="n">
         <v>3</v>
@@ -44512,13 +44512,13 @@
         </is>
       </c>
       <c r="D1336" t="n">
-        <v>172</v>
+        <v>258</v>
       </c>
       <c r="E1336" t="n">
-        <v>1920.8</v>
+        <v>2855.7</v>
       </c>
       <c r="F1336" t="n">
-        <v>11524.9</v>
+        <v>12459.8</v>
       </c>
       <c r="G1336" t="n">
         <v>1</v>
@@ -44527,7 +44527,7 @@
         <v>3</v>
       </c>
       <c r="I1336" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1337">
@@ -44545,13 +44545,13 @@
         </is>
       </c>
       <c r="D1337" t="n">
-        <v>116.2</v>
+        <v>174.3</v>
       </c>
       <c r="E1337" t="n">
-        <v>1897.2</v>
+        <v>2811.3</v>
       </c>
       <c r="F1337" t="n">
-        <v>9432.200000000001</v>
+        <v>10346.3</v>
       </c>
       <c r="G1337" t="n">
         <v>6</v>
@@ -44578,13 +44578,13 @@
         </is>
       </c>
       <c r="D1338" t="n">
-        <v>128.4</v>
+        <v>192.6</v>
       </c>
       <c r="E1338" t="n">
-        <v>1917.4</v>
+        <v>2855.6</v>
       </c>
       <c r="F1338" t="n">
-        <v>12628.5</v>
+        <v>13566.7</v>
       </c>
       <c r="G1338" t="n">
         <v>5</v>
@@ -44611,13 +44611,13 @@
         </is>
       </c>
       <c r="D1339" t="n">
-        <v>177.4</v>
+        <v>266.1</v>
       </c>
       <c r="E1339" t="n">
-        <v>2134.2</v>
+        <v>3185.3</v>
       </c>
       <c r="F1339" t="n">
-        <v>12825.2</v>
+        <v>13876.3</v>
       </c>
       <c r="G1339" t="n">
         <v>1</v>
@@ -44644,13 +44644,13 @@
         </is>
       </c>
       <c r="D1340" t="n">
-        <v>153.6</v>
+        <v>230.4</v>
       </c>
       <c r="E1340" t="n">
-        <v>2038.2</v>
+        <v>3021.8</v>
       </c>
       <c r="F1340" t="n">
-        <v>11903.3</v>
+        <v>12886.9</v>
       </c>
       <c r="G1340" t="n">
         <v>3</v>
@@ -44677,13 +44677,13 @@
         </is>
       </c>
       <c r="D1341" t="n">
-        <v>90</v>
+        <v>135</v>
       </c>
       <c r="E1341" t="n">
-        <v>1956.6</v>
+        <v>2913.4</v>
       </c>
       <c r="F1341" t="n">
-        <v>11621.2</v>
+        <v>12578</v>
       </c>
       <c r="G1341" t="n">
         <v>8</v>
@@ -44710,13 +44710,13 @@
         </is>
       </c>
       <c r="D1342" t="n">
-        <v>162.4</v>
+        <v>243.6</v>
       </c>
       <c r="E1342" t="n">
-        <v>2162.4</v>
+        <v>3204.1</v>
       </c>
       <c r="F1342" t="n">
-        <v>13097.2</v>
+        <v>14138.9</v>
       </c>
       <c r="G1342" t="n">
         <v>2</v>
@@ -44743,13 +44743,13 @@
         </is>
       </c>
       <c r="D1343" t="n">
-        <v>127.4</v>
+        <v>191.1</v>
       </c>
       <c r="E1343" t="n">
-        <v>1726.4</v>
+        <v>2562.1</v>
       </c>
       <c r="F1343" t="n">
-        <v>10560.3</v>
+        <v>11396</v>
       </c>
       <c r="G1343" t="n">
         <v>6</v>
@@ -44776,13 +44776,13 @@
         </is>
       </c>
       <c r="D1344" t="n">
-        <v>135.4</v>
+        <v>203.1</v>
       </c>
       <c r="E1344" t="n">
-        <v>2056.2</v>
+        <v>3058.8</v>
       </c>
       <c r="F1344" t="n">
-        <v>11660.3</v>
+        <v>12662.9</v>
       </c>
       <c r="G1344" t="n">
         <v>4</v>
@@ -44809,13 +44809,13 @@
         </is>
       </c>
       <c r="D1345" t="n">
-        <v>120.4</v>
+        <v>180.6</v>
       </c>
       <c r="E1345" t="n">
-        <v>2017.6</v>
+        <v>2991.9</v>
       </c>
       <c r="F1345" t="n">
-        <v>9552.6</v>
+        <v>10526.9</v>
       </c>
       <c r="G1345" t="n">
         <v>7</v>
@@ -44842,13 +44842,13 @@
         </is>
       </c>
       <c r="D1346" t="n">
-        <v>176.2</v>
+        <v>264.3</v>
       </c>
       <c r="E1346" t="n">
-        <v>2093.6</v>
+        <v>3119.9</v>
       </c>
       <c r="F1346" t="n">
-        <v>12804.7</v>
+        <v>13831</v>
       </c>
       <c r="G1346" t="n">
         <v>3</v>
@@ -44875,13 +44875,13 @@
         </is>
       </c>
       <c r="D1347" t="n">
-        <v>119.8</v>
+        <v>179.7</v>
       </c>
       <c r="E1347" t="n">
-        <v>2254</v>
+        <v>3365</v>
       </c>
       <c r="F1347" t="n">
-        <v>12945</v>
+        <v>14056</v>
       </c>
       <c r="G1347" t="n">
         <v>6</v>
@@ -44908,19 +44908,19 @@
         </is>
       </c>
       <c r="D1348" t="n">
-        <v>140.4</v>
+        <v>210.6</v>
       </c>
       <c r="E1348" t="n">
-        <v>2178.6</v>
+        <v>3232.4</v>
       </c>
       <c r="F1348" t="n">
-        <v>12043.7</v>
+        <v>13097.5</v>
       </c>
       <c r="G1348" t="n">
         <v>4</v>
       </c>
       <c r="H1348" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I1348" t="n">
         <v>4</v>
@@ -44944,10 +44944,10 @@
         <v>0</v>
       </c>
       <c r="E1349" t="n">
-        <v>1956.6</v>
+        <v>2913.4</v>
       </c>
       <c r="F1349" t="n">
-        <v>11621.2</v>
+        <v>12578</v>
       </c>
       <c r="G1349" t="n">
         <v>8</v>
@@ -44974,13 +44974,13 @@
         </is>
       </c>
       <c r="D1350" t="n">
-        <v>188</v>
+        <v>282</v>
       </c>
       <c r="E1350" t="n">
-        <v>2350.4</v>
+        <v>3486.1</v>
       </c>
       <c r="F1350" t="n">
-        <v>13285.2</v>
+        <v>14420.9</v>
       </c>
       <c r="G1350" t="n">
         <v>1</v>
@@ -45007,13 +45007,13 @@
         </is>
       </c>
       <c r="D1351" t="n">
-        <v>123.2</v>
+        <v>184.8</v>
       </c>
       <c r="E1351" t="n">
-        <v>1849.6</v>
+        <v>2746.9</v>
       </c>
       <c r="F1351" t="n">
-        <v>10683.5</v>
+        <v>11580.8</v>
       </c>
       <c r="G1351" t="n">
         <v>5</v>
@@ -45040,19 +45040,19 @@
         </is>
       </c>
       <c r="D1352" t="n">
-        <v>117.2</v>
+        <v>175.8</v>
       </c>
       <c r="E1352" t="n">
-        <v>2173.4</v>
+        <v>3234.6</v>
       </c>
       <c r="F1352" t="n">
-        <v>11777.5</v>
+        <v>12838.7</v>
       </c>
       <c r="G1352" t="n">
         <v>7</v>
       </c>
       <c r="H1352" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I1352" t="n">
         <v>5</v>
@@ -45073,13 +45073,13 @@
         </is>
       </c>
       <c r="D1353" t="n">
-        <v>179</v>
+        <v>268.5</v>
       </c>
       <c r="E1353" t="n">
-        <v>2196.6</v>
+        <v>3260.4</v>
       </c>
       <c r="F1353" t="n">
-        <v>9731.6</v>
+        <v>10795.4</v>
       </c>
       <c r="G1353" t="n">
         <v>2</v>
@@ -45106,13 +45106,13 @@
         </is>
       </c>
       <c r="D1354" t="n">
-        <v>133.4</v>
+        <v>200.1</v>
       </c>
       <c r="E1354" t="n">
-        <v>2227</v>
+        <v>3320</v>
       </c>
       <c r="F1354" t="n">
-        <v>12938.1</v>
+        <v>14031.1</v>
       </c>
       <c r="G1354" t="n">
         <v>4</v>
@@ -45139,19 +45139,19 @@
         </is>
       </c>
       <c r="D1355" t="n">
-        <v>71.59999999999999</v>
+        <v>107.4</v>
       </c>
       <c r="E1355" t="n">
-        <v>2325.6</v>
+        <v>3472.4</v>
       </c>
       <c r="F1355" t="n">
-        <v>13016.6</v>
+        <v>14163.4</v>
       </c>
       <c r="G1355" t="n">
         <v>8</v>
       </c>
       <c r="H1355" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1355" t="n">
         <v>2</v>
@@ -45172,13 +45172,13 @@
         </is>
       </c>
       <c r="D1356" t="n">
-        <v>118.4</v>
+        <v>177.6</v>
       </c>
       <c r="E1356" t="n">
-        <v>2297</v>
+        <v>3410</v>
       </c>
       <c r="F1356" t="n">
-        <v>12162.1</v>
+        <v>13275.1</v>
       </c>
       <c r="G1356" t="n">
         <v>6</v>
@@ -45205,13 +45205,13 @@
         </is>
       </c>
       <c r="D1357" t="n">
-        <v>164.4</v>
+        <v>246.6</v>
       </c>
       <c r="E1357" t="n">
-        <v>2121</v>
+        <v>3160</v>
       </c>
       <c r="F1357" t="n">
-        <v>11785.6</v>
+        <v>12824.6</v>
       </c>
       <c r="G1357" t="n">
         <v>2</v>
@@ -45238,13 +45238,13 @@
         </is>
       </c>
       <c r="D1358" t="n">
-        <v>126</v>
+        <v>189</v>
       </c>
       <c r="E1358" t="n">
-        <v>2476.4</v>
+        <v>3675.1</v>
       </c>
       <c r="F1358" t="n">
-        <v>13411.2</v>
+        <v>14609.9</v>
       </c>
       <c r="G1358" t="n">
         <v>5</v>
@@ -45271,13 +45271,13 @@
         </is>
       </c>
       <c r="D1359" t="n">
-        <v>113.2</v>
+        <v>169.8</v>
       </c>
       <c r="E1359" t="n">
-        <v>1962.8</v>
+        <v>2916.7</v>
       </c>
       <c r="F1359" t="n">
-        <v>10796.7</v>
+        <v>11750.6</v>
       </c>
       <c r="G1359" t="n">
         <v>7</v>
@@ -45304,19 +45304,19 @@
         </is>
       </c>
       <c r="D1360" t="n">
-        <v>157.2</v>
+        <v>235.8</v>
       </c>
       <c r="E1360" t="n">
-        <v>2330.6</v>
+        <v>3470.4</v>
       </c>
       <c r="F1360" t="n">
-        <v>11934.7</v>
+        <v>13074.5</v>
       </c>
       <c r="G1360" t="n">
         <v>3</v>
       </c>
       <c r="H1360" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1360" t="n">
         <v>5</v>
@@ -45337,13 +45337,13 @@
         </is>
       </c>
       <c r="D1361" t="n">
-        <v>174.6</v>
+        <v>261.9</v>
       </c>
       <c r="E1361" t="n">
-        <v>2371.2</v>
+        <v>3522.3</v>
       </c>
       <c r="F1361" t="n">
-        <v>9906.200000000001</v>
+        <v>11057.3</v>
       </c>
       <c r="G1361" t="n">
         <v>1</v>
@@ -45370,13 +45370,13 @@
         </is>
       </c>
       <c r="D1362" t="n">
-        <v>141.6</v>
+        <v>212.4</v>
       </c>
       <c r="E1362" t="n">
-        <v>2368.6</v>
+        <v>3532.4</v>
       </c>
       <c r="F1362" t="n">
-        <v>13079.7</v>
+        <v>14243.5</v>
       </c>
       <c r="G1362" t="n">
         <v>4</v>
@@ -45403,19 +45403,19 @@
         </is>
       </c>
       <c r="D1363" t="n">
-        <v>153</v>
+        <v>229.5</v>
       </c>
       <c r="E1363" t="n">
-        <v>2478.6</v>
+        <v>3701.9</v>
       </c>
       <c r="F1363" t="n">
-        <v>13169.6</v>
+        <v>14392.9</v>
       </c>
       <c r="G1363" t="n">
         <v>2</v>
       </c>
       <c r="H1363" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I1363" t="n">
         <v>2</v>
@@ -45436,13 +45436,13 @@
         </is>
       </c>
       <c r="D1364" t="n">
-        <v>150.4</v>
+        <v>225.6</v>
       </c>
       <c r="E1364" t="n">
-        <v>2447.4</v>
+        <v>3635.6</v>
       </c>
       <c r="F1364" t="n">
-        <v>12312.5</v>
+        <v>13500.7</v>
       </c>
       <c r="G1364" t="n">
         <v>3</v>
@@ -45469,13 +45469,13 @@
         </is>
       </c>
       <c r="D1365" t="n">
-        <v>93.40000000000001</v>
+        <v>140.1</v>
       </c>
       <c r="E1365" t="n">
-        <v>2214.4</v>
+        <v>3300.1</v>
       </c>
       <c r="F1365" t="n">
-        <v>11879</v>
+        <v>12964.7</v>
       </c>
       <c r="G1365" t="n">
         <v>8</v>
@@ -45502,13 +45502,13 @@
         </is>
       </c>
       <c r="D1366" t="n">
-        <v>158.8</v>
+        <v>238.2</v>
       </c>
       <c r="E1366" t="n">
-        <v>2635.2</v>
+        <v>3913.3</v>
       </c>
       <c r="F1366" t="n">
-        <v>13570</v>
+        <v>14848.1</v>
       </c>
       <c r="G1366" t="n">
         <v>1</v>
@@ -45535,13 +45535,13 @@
         </is>
       </c>
       <c r="D1367" t="n">
-        <v>113.2</v>
+        <v>169.8</v>
       </c>
       <c r="E1367" t="n">
-        <v>2076</v>
+        <v>3086.5</v>
       </c>
       <c r="F1367" t="n">
-        <v>10909.9</v>
+        <v>11920.4</v>
       </c>
       <c r="G1367" t="n">
         <v>6</v>
@@ -45568,13 +45568,13 @@
         </is>
       </c>
       <c r="D1368" t="n">
-        <v>130.4</v>
+        <v>195.6</v>
       </c>
       <c r="E1368" t="n">
-        <v>2461</v>
+        <v>3666</v>
       </c>
       <c r="F1368" t="n">
-        <v>12065.1</v>
+        <v>13270.1</v>
       </c>
       <c r="G1368" t="n">
         <v>5</v>
@@ -45601,19 +45601,19 @@
         </is>
       </c>
       <c r="D1369" t="n">
-        <v>109.6</v>
+        <v>164.4</v>
       </c>
       <c r="E1369" t="n">
-        <v>2480.8</v>
+        <v>3686.7</v>
       </c>
       <c r="F1369" t="n">
-        <v>10015.8</v>
+        <v>11221.7</v>
       </c>
       <c r="G1369" t="n">
         <v>7</v>
       </c>
       <c r="H1369" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I1369" t="n">
         <v>8</v>
@@ -45634,13 +45634,13 @@
         </is>
       </c>
       <c r="D1370" t="n">
-        <v>187.6</v>
+        <v>281.4</v>
       </c>
       <c r="E1370" t="n">
-        <v>2556.2</v>
+        <v>3813.8</v>
       </c>
       <c r="F1370" t="n">
-        <v>13267.3</v>
+        <v>14524.9</v>
       </c>
       <c r="G1370" t="n">
         <v>2</v>
@@ -45667,13 +45667,13 @@
         </is>
       </c>
       <c r="D1371" t="n">
-        <v>130.4</v>
+        <v>195.6</v>
       </c>
       <c r="E1371" t="n">
-        <v>2609</v>
+        <v>3897.5</v>
       </c>
       <c r="F1371" t="n">
-        <v>13300</v>
+        <v>14588.5</v>
       </c>
       <c r="G1371" t="n">
         <v>7</v>
@@ -45700,13 +45700,13 @@
         </is>
       </c>
       <c r="D1372" t="n">
-        <v>195.2</v>
+        <v>292.8</v>
       </c>
       <c r="E1372" t="n">
-        <v>2642.6</v>
+        <v>3928.4</v>
       </c>
       <c r="F1372" t="n">
-        <v>12507.7</v>
+        <v>13793.5</v>
       </c>
       <c r="G1372" t="n">
         <v>1</v>
@@ -45733,13 +45733,13 @@
         </is>
       </c>
       <c r="D1373" t="n">
-        <v>126.6</v>
+        <v>189.9</v>
       </c>
       <c r="E1373" t="n">
-        <v>2341</v>
+        <v>3490</v>
       </c>
       <c r="F1373" t="n">
-        <v>12005.6</v>
+        <v>13154.6</v>
       </c>
       <c r="G1373" t="n">
         <v>8</v>
@@ -45766,13 +45766,13 @@
         </is>
       </c>
       <c r="D1374" t="n">
-        <v>158.6</v>
+        <v>237.9</v>
       </c>
       <c r="E1374" t="n">
-        <v>2793.8</v>
+        <v>4151.2</v>
       </c>
       <c r="F1374" t="n">
-        <v>13728.6</v>
+        <v>15086</v>
       </c>
       <c r="G1374" t="n">
         <v>5</v>
@@ -45799,13 +45799,13 @@
         </is>
       </c>
       <c r="D1375" t="n">
-        <v>163.4</v>
+        <v>245.1</v>
       </c>
       <c r="E1375" t="n">
-        <v>2239.4</v>
+        <v>3331.6</v>
       </c>
       <c r="F1375" t="n">
-        <v>11073.3</v>
+        <v>12165.5</v>
       </c>
       <c r="G1375" t="n">
         <v>4</v>
@@ -45832,13 +45832,13 @@
         </is>
       </c>
       <c r="D1376" t="n">
-        <v>134.8</v>
+        <v>202.2</v>
       </c>
       <c r="E1376" t="n">
-        <v>2595.8</v>
+        <v>3868.2</v>
       </c>
       <c r="F1376" t="n">
-        <v>12199.9</v>
+        <v>13472.3</v>
       </c>
       <c r="G1376" t="n">
         <v>6</v>
@@ -45865,13 +45865,13 @@
         </is>
       </c>
       <c r="D1377" t="n">
-        <v>165.2</v>
+        <v>247.8</v>
       </c>
       <c r="E1377" t="n">
-        <v>2646</v>
+        <v>3934.5</v>
       </c>
       <c r="F1377" t="n">
-        <v>10181</v>
+        <v>11469.5</v>
       </c>
       <c r="G1377" t="n">
         <v>3</v>
@@ -45898,22 +45898,22 @@
         </is>
       </c>
       <c r="D1378" t="n">
-        <v>201</v>
+        <v>301.5</v>
       </c>
       <c r="E1378" t="n">
-        <v>2757.2</v>
+        <v>4115.3</v>
       </c>
       <c r="F1378" t="n">
-        <v>13468.3</v>
+        <v>14826.4</v>
       </c>
       <c r="G1378" t="n">
         <v>1</v>
       </c>
       <c r="H1378" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I1378" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1379">
@@ -45931,13 +45931,13 @@
         </is>
       </c>
       <c r="D1379" t="n">
-        <v>160.6</v>
+        <v>240.9</v>
       </c>
       <c r="E1379" t="n">
-        <v>2769.6</v>
+        <v>4138.400000000001</v>
       </c>
       <c r="F1379" t="n">
-        <v>13460.6</v>
+        <v>14829.4</v>
       </c>
       <c r="G1379" t="n">
         <v>2</v>
@@ -45946,7 +45946,7 @@
         <v>2</v>
       </c>
       <c r="I1379" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1380">
@@ -45964,19 +45964,19 @@
         </is>
       </c>
       <c r="D1380" t="n">
-        <v>120.6</v>
+        <v>180.9</v>
       </c>
       <c r="E1380" t="n">
-        <v>2763.2</v>
+        <v>4109.3</v>
       </c>
       <c r="F1380" t="n">
-        <v>12628.3</v>
+        <v>13974.4</v>
       </c>
       <c r="G1380" t="n">
         <v>6</v>
       </c>
       <c r="H1380" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I1380" t="n">
         <v>4</v>
@@ -45997,13 +45997,13 @@
         </is>
       </c>
       <c r="D1381" t="n">
-        <v>135.2</v>
+        <v>202.8</v>
       </c>
       <c r="E1381" t="n">
-        <v>2476.2</v>
+        <v>3692.8</v>
       </c>
       <c r="F1381" t="n">
-        <v>12140.8</v>
+        <v>13357.4</v>
       </c>
       <c r="G1381" t="n">
         <v>4</v>
@@ -46030,13 +46030,13 @@
         </is>
       </c>
       <c r="D1382" t="n">
-        <v>140.4</v>
+        <v>210.6</v>
       </c>
       <c r="E1382" t="n">
-        <v>2934.2</v>
+        <v>4361.8</v>
       </c>
       <c r="F1382" t="n">
-        <v>13869</v>
+        <v>15296.6</v>
       </c>
       <c r="G1382" t="n">
         <v>3</v>
@@ -46063,13 +46063,13 @@
         </is>
       </c>
       <c r="D1383" t="n">
-        <v>122.4</v>
+        <v>183.6</v>
       </c>
       <c r="E1383" t="n">
-        <v>2361.8</v>
+        <v>3515.2</v>
       </c>
       <c r="F1383" t="n">
-        <v>11195.7</v>
+        <v>12349.1</v>
       </c>
       <c r="G1383" t="n">
         <v>5</v>
@@ -46096,13 +46096,13 @@
         </is>
       </c>
       <c r="D1384" t="n">
-        <v>101.6</v>
+        <v>152.4</v>
       </c>
       <c r="E1384" t="n">
-        <v>2697.4</v>
+        <v>4020.6</v>
       </c>
       <c r="F1384" t="n">
-        <v>12301.5</v>
+        <v>13624.7</v>
       </c>
       <c r="G1384" t="n">
         <v>8</v>
@@ -46129,19 +46129,19 @@
         </is>
       </c>
       <c r="D1385" t="n">
-        <v>117.8</v>
+        <v>176.7</v>
       </c>
       <c r="E1385" t="n">
-        <v>2763.8</v>
+        <v>4111.2</v>
       </c>
       <c r="F1385" t="n">
-        <v>10298.8</v>
+        <v>11646.2</v>
       </c>
       <c r="G1385" t="n">
         <v>7</v>
       </c>
       <c r="H1385" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1385" t="n">
         <v>8</v>
@@ -46162,13 +46162,13 @@
         </is>
       </c>
       <c r="D1386" t="n">
-        <v>184</v>
+        <v>276</v>
       </c>
       <c r="E1386" t="n">
-        <v>2941.2</v>
+        <v>4391.3</v>
       </c>
       <c r="F1386" t="n">
-        <v>13652.3</v>
+        <v>15102.4</v>
       </c>
       <c r="G1386" t="n">
         <v>2</v>
@@ -46195,13 +46195,13 @@
         </is>
       </c>
       <c r="D1387" t="n">
-        <v>154.4</v>
+        <v>231.6</v>
       </c>
       <c r="E1387" t="n">
-        <v>2924</v>
+        <v>4370</v>
       </c>
       <c r="F1387" t="n">
-        <v>13615</v>
+        <v>15061</v>
       </c>
       <c r="G1387" t="n">
         <v>4</v>
@@ -46228,13 +46228,13 @@
         </is>
       </c>
       <c r="D1388" t="n">
-        <v>160.6</v>
+        <v>240.9</v>
       </c>
       <c r="E1388" t="n">
-        <v>2923.8</v>
+        <v>4350.2</v>
       </c>
       <c r="F1388" t="n">
-        <v>12788.9</v>
+        <v>14215.3</v>
       </c>
       <c r="G1388" t="n">
         <v>3</v>
@@ -46261,13 +46261,13 @@
         </is>
       </c>
       <c r="D1389" t="n">
-        <v>101.2</v>
+        <v>151.8</v>
       </c>
       <c r="E1389" t="n">
-        <v>2577.4</v>
+        <v>3844.6</v>
       </c>
       <c r="F1389" t="n">
-        <v>12242</v>
+        <v>13509.2</v>
       </c>
       <c r="G1389" t="n">
         <v>7</v>
@@ -46294,13 +46294,13 @@
         </is>
       </c>
       <c r="D1390" t="n">
-        <v>153.4</v>
+        <v>230.1</v>
       </c>
       <c r="E1390" t="n">
-        <v>3087.6</v>
+        <v>4591.9</v>
       </c>
       <c r="F1390" t="n">
-        <v>14022.4</v>
+        <v>15526.7</v>
       </c>
       <c r="G1390" t="n">
         <v>5</v>
@@ -46327,13 +46327,13 @@
         </is>
       </c>
       <c r="D1391" t="n">
-        <v>97.40000000000001</v>
+        <v>146.1</v>
       </c>
       <c r="E1391" t="n">
-        <v>2459.2</v>
+        <v>3661.3</v>
       </c>
       <c r="F1391" t="n">
-        <v>11293.1</v>
+        <v>12495.2</v>
       </c>
       <c r="G1391" t="n">
         <v>8</v>
@@ -46360,13 +46360,13 @@
         </is>
       </c>
       <c r="D1392" t="n">
-        <v>185</v>
+        <v>277.5</v>
       </c>
       <c r="E1392" t="n">
-        <v>2882.4</v>
+        <v>4298.1</v>
       </c>
       <c r="F1392" t="n">
-        <v>12486.5</v>
+        <v>13902.2</v>
       </c>
       <c r="G1392" t="n">
         <v>1</v>
@@ -46393,13 +46393,13 @@
         </is>
       </c>
       <c r="D1393" t="n">
-        <v>146.2</v>
+        <v>219.3</v>
       </c>
       <c r="E1393" t="n">
-        <v>2910</v>
+        <v>4330.5</v>
       </c>
       <c r="F1393" t="n">
-        <v>10445</v>
+        <v>11865.5</v>
       </c>
       <c r="G1393" t="n">
         <v>6</v>
@@ -46426,19 +46426,19 @@
         </is>
       </c>
       <c r="D1394" t="n">
-        <v>151.2</v>
+        <v>226.8</v>
       </c>
       <c r="E1394" t="n">
-        <v>3092.4</v>
+        <v>4618.1</v>
       </c>
       <c r="F1394" t="n">
-        <v>13803.5</v>
+        <v>15329.2</v>
       </c>
       <c r="G1394" t="n">
         <v>3</v>
       </c>
       <c r="H1394" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I1394" t="n">
         <v>2</v>
@@ -46459,19 +46459,19 @@
         </is>
       </c>
       <c r="D1395" t="n">
-        <v>168.2</v>
+        <v>252.3</v>
       </c>
       <c r="E1395" t="n">
-        <v>3092.2</v>
+        <v>4622.3</v>
       </c>
       <c r="F1395" t="n">
-        <v>13783.2</v>
+        <v>15313.3</v>
       </c>
       <c r="G1395" t="n">
         <v>1</v>
       </c>
       <c r="H1395" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I1395" t="n">
         <v>3</v>
@@ -46492,13 +46492,13 @@
         </is>
       </c>
       <c r="D1396" t="n">
-        <v>118.6</v>
+        <v>177.9</v>
       </c>
       <c r="E1396" t="n">
-        <v>3042.4</v>
+        <v>4528.1</v>
       </c>
       <c r="F1396" t="n">
-        <v>12907.5</v>
+        <v>14393.2</v>
       </c>
       <c r="G1396" t="n">
         <v>8</v>
@@ -46525,13 +46525,13 @@
         </is>
       </c>
       <c r="D1397" t="n">
-        <v>143</v>
+        <v>214.5</v>
       </c>
       <c r="E1397" t="n">
-        <v>2720.4</v>
+        <v>4059.1</v>
       </c>
       <c r="F1397" t="n">
-        <v>12385</v>
+        <v>13723.7</v>
       </c>
       <c r="G1397" t="n">
         <v>6</v>
@@ -46558,13 +46558,13 @@
         </is>
       </c>
       <c r="D1398" t="n">
-        <v>150.8</v>
+        <v>226.2</v>
       </c>
       <c r="E1398" t="n">
-        <v>3238.4</v>
+        <v>4818.1</v>
       </c>
       <c r="F1398" t="n">
-        <v>14173.2</v>
+        <v>15752.9</v>
       </c>
       <c r="G1398" t="n">
         <v>4</v>
@@ -46591,13 +46591,13 @@
         </is>
       </c>
       <c r="D1399" t="n">
-        <v>125.4</v>
+        <v>188.1</v>
       </c>
       <c r="E1399" t="n">
-        <v>2584.6</v>
+        <v>3849.4</v>
       </c>
       <c r="F1399" t="n">
-        <v>11418.5</v>
+        <v>12683.3</v>
       </c>
       <c r="G1399" t="n">
         <v>7</v>
@@ -46624,13 +46624,13 @@
         </is>
       </c>
       <c r="D1400" t="n">
-        <v>144</v>
+        <v>216</v>
       </c>
       <c r="E1400" t="n">
-        <v>3026.4</v>
+        <v>4514.1</v>
       </c>
       <c r="F1400" t="n">
-        <v>12630.5</v>
+        <v>14118.2</v>
       </c>
       <c r="G1400" t="n">
         <v>5</v>
@@ -46657,13 +46657,13 @@
         </is>
       </c>
       <c r="D1401" t="n">
-        <v>158.2</v>
+        <v>237.3</v>
       </c>
       <c r="E1401" t="n">
-        <v>3068.2</v>
+        <v>4567.8</v>
       </c>
       <c r="F1401" t="n">
-        <v>10603.2</v>
+        <v>12102.8</v>
       </c>
       <c r="G1401" t="n">
         <v>2</v>
@@ -46690,13 +46690,13 @@
         </is>
       </c>
       <c r="D1402" t="n">
-        <v>146.4</v>
+        <v>219.6</v>
       </c>
       <c r="E1402" t="n">
-        <v>3238.8</v>
+        <v>4837.7</v>
       </c>
       <c r="F1402" t="n">
-        <v>13949.9</v>
+        <v>15548.8</v>
       </c>
       <c r="G1402" t="n">
         <v>2</v>
@@ -46723,13 +46723,13 @@
         </is>
       </c>
       <c r="D1403" t="n">
-        <v>125.4</v>
+        <v>188.1</v>
       </c>
       <c r="E1403" t="n">
-        <v>3217.6</v>
+        <v>4810.400000000001</v>
       </c>
       <c r="F1403" t="n">
-        <v>13908.6</v>
+        <v>15501.4</v>
       </c>
       <c r="G1403" t="n">
         <v>5</v>
@@ -46756,13 +46756,13 @@
         </is>
       </c>
       <c r="D1404" t="n">
-        <v>98.40000000000001</v>
+        <v>147.6</v>
       </c>
       <c r="E1404" t="n">
-        <v>3140.8</v>
+        <v>4675.7</v>
       </c>
       <c r="F1404" t="n">
-        <v>13005.9</v>
+        <v>14540.8</v>
       </c>
       <c r="G1404" t="n">
         <v>6</v>
@@ -46789,13 +46789,13 @@
         </is>
       </c>
       <c r="D1405" t="n">
-        <v>87.8</v>
+        <v>131.7</v>
       </c>
       <c r="E1405" t="n">
-        <v>2808.2</v>
+        <v>4190.8</v>
       </c>
       <c r="F1405" t="n">
-        <v>12472.8</v>
+        <v>13855.4</v>
       </c>
       <c r="G1405" t="n">
         <v>7</v>
@@ -46822,13 +46822,13 @@
         </is>
       </c>
       <c r="D1406" t="n">
-        <v>142.4</v>
+        <v>213.6</v>
       </c>
       <c r="E1406" t="n">
-        <v>3380.8</v>
+        <v>5031.7</v>
       </c>
       <c r="F1406" t="n">
-        <v>14315.6</v>
+        <v>15966.5</v>
       </c>
       <c r="G1406" t="n">
         <v>3</v>
@@ -46855,13 +46855,13 @@
         </is>
       </c>
       <c r="D1407" t="n">
-        <v>128.2</v>
+        <v>192.3</v>
       </c>
       <c r="E1407" t="n">
-        <v>2712.8</v>
+        <v>4041.7</v>
       </c>
       <c r="F1407" t="n">
-        <v>11546.7</v>
+        <v>12875.6</v>
       </c>
       <c r="G1407" t="n">
         <v>4</v>
@@ -46888,13 +46888,13 @@
         </is>
       </c>
       <c r="D1408" t="n">
-        <v>85.8</v>
+        <v>128.7</v>
       </c>
       <c r="E1408" t="n">
-        <v>3112.2</v>
+        <v>4642.8</v>
       </c>
       <c r="F1408" t="n">
-        <v>12716.3</v>
+        <v>14246.9</v>
       </c>
       <c r="G1408" t="n">
         <v>8</v>
@@ -46921,13 +46921,13 @@
         </is>
       </c>
       <c r="D1409" t="n">
-        <v>147.6</v>
+        <v>221.4</v>
       </c>
       <c r="E1409" t="n">
-        <v>3215.8</v>
+        <v>4789.2</v>
       </c>
       <c r="F1409" t="n">
-        <v>10750.8</v>
+        <v>12324.2</v>
       </c>
       <c r="G1409" t="n">
         <v>1</v>
@@ -46954,13 +46954,13 @@
         </is>
       </c>
       <c r="D1410" t="n">
-        <v>158.6</v>
+        <v>237.9</v>
       </c>
       <c r="E1410" t="n">
-        <v>3397.4</v>
+        <v>5075.6</v>
       </c>
       <c r="F1410" t="n">
-        <v>14108.5</v>
+        <v>15786.7</v>
       </c>
       <c r="G1410" t="n">
         <v>1</v>
@@ -46987,13 +46987,13 @@
         </is>
       </c>
       <c r="D1411" t="n">
-        <v>124.6</v>
+        <v>186.9</v>
       </c>
       <c r="E1411" t="n">
-        <v>3342.2</v>
+        <v>4997.3</v>
       </c>
       <c r="F1411" t="n">
-        <v>14033.2</v>
+        <v>15688.3</v>
       </c>
       <c r="G1411" t="n">
         <v>4</v>
@@ -47020,13 +47020,13 @@
         </is>
       </c>
       <c r="D1412" t="n">
-        <v>100.8</v>
+        <v>151.2</v>
       </c>
       <c r="E1412" t="n">
-        <v>3241.6</v>
+        <v>4826.9</v>
       </c>
       <c r="F1412" t="n">
-        <v>13106.7</v>
+        <v>14692</v>
       </c>
       <c r="G1412" t="n">
         <v>7</v>
@@ -47053,13 +47053,13 @@
         </is>
       </c>
       <c r="D1413" t="n">
-        <v>97.59999999999999</v>
+        <v>146.4</v>
       </c>
       <c r="E1413" t="n">
-        <v>2905.8</v>
+        <v>4337.2</v>
       </c>
       <c r="F1413" t="n">
-        <v>12570.4</v>
+        <v>14001.8</v>
       </c>
       <c r="G1413" t="n">
         <v>8</v>
@@ -47086,13 +47086,13 @@
         </is>
       </c>
       <c r="D1414" t="n">
-        <v>150</v>
+        <v>225</v>
       </c>
       <c r="E1414" t="n">
-        <v>3530.8</v>
+        <v>5256.7</v>
       </c>
       <c r="F1414" t="n">
-        <v>14465.6</v>
+        <v>16191.5</v>
       </c>
       <c r="G1414" t="n">
         <v>2</v>
@@ -47119,13 +47119,13 @@
         </is>
       </c>
       <c r="D1415" t="n">
-        <v>129</v>
+        <v>193.5</v>
       </c>
       <c r="E1415" t="n">
-        <v>2841.8</v>
+        <v>4235.2</v>
       </c>
       <c r="F1415" t="n">
-        <v>11675.7</v>
+        <v>13069.1</v>
       </c>
       <c r="G1415" t="n">
         <v>3</v>
@@ -47152,13 +47152,13 @@
         </is>
       </c>
       <c r="D1416" t="n">
-        <v>119.4</v>
+        <v>179.1</v>
       </c>
       <c r="E1416" t="n">
-        <v>3231.6</v>
+        <v>4821.9</v>
       </c>
       <c r="F1416" t="n">
-        <v>12835.7</v>
+        <v>14426</v>
       </c>
       <c r="G1416" t="n">
         <v>5</v>
@@ -47185,13 +47185,13 @@
         </is>
       </c>
       <c r="D1417" t="n">
-        <v>115.4</v>
+        <v>173.1</v>
       </c>
       <c r="E1417" t="n">
-        <v>3331.2</v>
+        <v>4962.3</v>
       </c>
       <c r="F1417" t="n">
-        <v>10866.2</v>
+        <v>12497.3</v>
       </c>
       <c r="G1417" t="n">
         <v>6</v>
@@ -47218,13 +47218,13 @@
         </is>
       </c>
       <c r="D1418" t="n">
-        <v>172.6</v>
+        <v>258.9</v>
       </c>
       <c r="E1418" t="n">
-        <v>3570</v>
+        <v>5334.5</v>
       </c>
       <c r="F1418" t="n">
-        <v>14281.1</v>
+        <v>16045.6</v>
       </c>
       <c r="G1418" t="n">
         <v>2</v>
@@ -47251,13 +47251,13 @@
         </is>
       </c>
       <c r="D1419" t="n">
-        <v>151.2</v>
+        <v>226.8</v>
       </c>
       <c r="E1419" t="n">
-        <v>3493.4</v>
+        <v>5224.1</v>
       </c>
       <c r="F1419" t="n">
-        <v>14184.4</v>
+        <v>15915.1</v>
       </c>
       <c r="G1419" t="n">
         <v>3</v>
@@ -47284,19 +47284,19 @@
         </is>
       </c>
       <c r="D1420" t="n">
-        <v>101.8</v>
+        <v>152.7</v>
       </c>
       <c r="E1420" t="n">
-        <v>3343.4</v>
+        <v>4979.6</v>
       </c>
       <c r="F1420" t="n">
-        <v>13208.5</v>
+        <v>14844.7</v>
       </c>
       <c r="G1420" t="n">
         <v>8</v>
       </c>
       <c r="H1420" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I1420" t="n">
         <v>4</v>
@@ -47317,13 +47317,13 @@
         </is>
       </c>
       <c r="D1421" t="n">
-        <v>130.6</v>
+        <v>195.9</v>
       </c>
       <c r="E1421" t="n">
-        <v>3036.4</v>
+        <v>4533.1</v>
       </c>
       <c r="F1421" t="n">
-        <v>12701</v>
+        <v>14197.7</v>
       </c>
       <c r="G1421" t="n">
         <v>4</v>
@@ -47350,13 +47350,13 @@
         </is>
       </c>
       <c r="D1422" t="n">
-        <v>116.8</v>
+        <v>175.2</v>
       </c>
       <c r="E1422" t="n">
-        <v>3647.6</v>
+        <v>5431.9</v>
       </c>
       <c r="F1422" t="n">
-        <v>14582.4</v>
+        <v>16366.7</v>
       </c>
       <c r="G1422" t="n">
         <v>6</v>
@@ -47383,13 +47383,13 @@
         </is>
       </c>
       <c r="D1423" t="n">
-        <v>117.2</v>
+        <v>175.8</v>
       </c>
       <c r="E1423" t="n">
-        <v>2959</v>
+        <v>4411</v>
       </c>
       <c r="F1423" t="n">
-        <v>11792.9</v>
+        <v>13244.9</v>
       </c>
       <c r="G1423" t="n">
         <v>5</v>
@@ -47416,19 +47416,19 @@
         </is>
       </c>
       <c r="D1424" t="n">
-        <v>110.6</v>
+        <v>165.9</v>
       </c>
       <c r="E1424" t="n">
-        <v>3342.2</v>
+        <v>4987.8</v>
       </c>
       <c r="F1424" t="n">
-        <v>12946.3</v>
+        <v>14591.9</v>
       </c>
       <c r="G1424" t="n">
         <v>7</v>
       </c>
       <c r="H1424" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I1424" t="n">
         <v>5</v>
@@ -47449,13 +47449,13 @@
         </is>
       </c>
       <c r="D1425" t="n">
-        <v>192</v>
+        <v>288</v>
       </c>
       <c r="E1425" t="n">
-        <v>3523.2</v>
+        <v>5250.3</v>
       </c>
       <c r="F1425" t="n">
-        <v>11058.2</v>
+        <v>12785.3</v>
       </c>
       <c r="G1425" t="n">
         <v>1</v>
@@ -47482,13 +47482,13 @@
         </is>
       </c>
       <c r="D1426" t="n">
-        <v>169</v>
+        <v>253.5</v>
       </c>
       <c r="E1426" t="n">
-        <v>3739</v>
+        <v>5588</v>
       </c>
       <c r="F1426" t="n">
-        <v>14450.1</v>
+        <v>16299.1</v>
       </c>
       <c r="G1426" t="n">
         <v>1</v>
@@ -47515,13 +47515,13 @@
         </is>
       </c>
       <c r="D1427" t="n">
-        <v>133.2</v>
+        <v>199.8</v>
       </c>
       <c r="E1427" t="n">
-        <v>3626.6</v>
+        <v>5423.900000000001</v>
       </c>
       <c r="F1427" t="n">
-        <v>14317.6</v>
+        <v>16114.9</v>
       </c>
       <c r="G1427" t="n">
         <v>4</v>
@@ -47548,13 +47548,13 @@
         </is>
       </c>
       <c r="D1428" t="n">
-        <v>120.2</v>
+        <v>180.3</v>
       </c>
       <c r="E1428" t="n">
-        <v>3463.6</v>
+        <v>5159.9</v>
       </c>
       <c r="F1428" t="n">
-        <v>13328.7</v>
+        <v>15025</v>
       </c>
       <c r="G1428" t="n">
         <v>6</v>
@@ -47581,13 +47581,13 @@
         </is>
       </c>
       <c r="D1429" t="n">
-        <v>148.2</v>
+        <v>222.3</v>
       </c>
       <c r="E1429" t="n">
-        <v>3184.6</v>
+        <v>4755.4</v>
       </c>
       <c r="F1429" t="n">
-        <v>12849.2</v>
+        <v>14420</v>
       </c>
       <c r="G1429" t="n">
         <v>3</v>
@@ -47614,13 +47614,13 @@
         </is>
       </c>
       <c r="D1430" t="n">
-        <v>114.8</v>
+        <v>172.2</v>
       </c>
       <c r="E1430" t="n">
-        <v>3762.4</v>
+        <v>5604.1</v>
       </c>
       <c r="F1430" t="n">
-        <v>14697.2</v>
+        <v>16538.9</v>
       </c>
       <c r="G1430" t="n">
         <v>7</v>
@@ -47650,10 +47650,10 @@
         <v>0</v>
       </c>
       <c r="E1431" t="n">
-        <v>2959</v>
+        <v>4411</v>
       </c>
       <c r="F1431" t="n">
-        <v>11792.9</v>
+        <v>13244.9</v>
       </c>
       <c r="G1431" t="n">
         <v>8</v>
@@ -47680,13 +47680,13 @@
         </is>
       </c>
       <c r="D1432" t="n">
-        <v>131.8</v>
+        <v>197.7</v>
       </c>
       <c r="E1432" t="n">
-        <v>3474</v>
+        <v>5185.5</v>
       </c>
       <c r="F1432" t="n">
-        <v>13078.1</v>
+        <v>14789.6</v>
       </c>
       <c r="G1432" t="n">
         <v>5</v>
@@ -47713,13 +47713,13 @@
         </is>
       </c>
       <c r="D1433" t="n">
-        <v>152</v>
+        <v>228</v>
       </c>
       <c r="E1433" t="n">
-        <v>3675.2</v>
+        <v>5478.3</v>
       </c>
       <c r="F1433" t="n">
-        <v>11210.2</v>
+        <v>13013.3</v>
       </c>
       <c r="G1433" t="n">
         <v>2</v>
@@ -47746,13 +47746,13 @@
         </is>
       </c>
       <c r="D1434" t="n">
-        <v>146.2</v>
+        <v>219.3</v>
       </c>
       <c r="E1434" t="n">
-        <v>3885.2</v>
+        <v>5807.3</v>
       </c>
       <c r="F1434" t="n">
-        <v>14596.3</v>
+        <v>16518.4</v>
       </c>
       <c r="G1434" t="n">
         <v>6</v>
@@ -47779,13 +47779,13 @@
         </is>
       </c>
       <c r="D1435" t="n">
-        <v>185.8</v>
+        <v>278.7</v>
       </c>
       <c r="E1435" t="n">
-        <v>3812.4</v>
+        <v>5702.6</v>
       </c>
       <c r="F1435" t="n">
-        <v>14503.4</v>
+        <v>16393.6</v>
       </c>
       <c r="G1435" t="n">
         <v>2</v>
@@ -47812,13 +47812,13 @@
         </is>
       </c>
       <c r="D1436" t="n">
-        <v>103.2</v>
+        <v>154.8</v>
       </c>
       <c r="E1436" t="n">
-        <v>3566.8</v>
+        <v>5314.7</v>
       </c>
       <c r="F1436" t="n">
-        <v>13431.9</v>
+        <v>15179.8</v>
       </c>
       <c r="G1436" t="n">
         <v>8</v>
@@ -47845,13 +47845,13 @@
         </is>
       </c>
       <c r="D1437" t="n">
-        <v>124.2</v>
+        <v>186.3</v>
       </c>
       <c r="E1437" t="n">
-        <v>3308.8</v>
+        <v>4941.7</v>
       </c>
       <c r="F1437" t="n">
-        <v>12973.4</v>
+        <v>14606.3</v>
       </c>
       <c r="G1437" t="n">
         <v>7</v>
@@ -47878,13 +47878,13 @@
         </is>
       </c>
       <c r="D1438" t="n">
-        <v>173.4</v>
+        <v>260.1</v>
       </c>
       <c r="E1438" t="n">
-        <v>3935.8</v>
+        <v>5864.2</v>
       </c>
       <c r="F1438" t="n">
-        <v>14870.6</v>
+        <v>16799</v>
       </c>
       <c r="G1438" t="n">
         <v>4</v>
@@ -47911,13 +47911,13 @@
         </is>
       </c>
       <c r="D1439" t="n">
-        <v>176.4</v>
+        <v>264.6</v>
       </c>
       <c r="E1439" t="n">
-        <v>3135.4</v>
+        <v>4675.6</v>
       </c>
       <c r="F1439" t="n">
-        <v>11969.3</v>
+        <v>13509.5</v>
       </c>
       <c r="G1439" t="n">
         <v>3</v>
@@ -47944,13 +47944,13 @@
         </is>
       </c>
       <c r="D1440" t="n">
-        <v>146.6</v>
+        <v>219.9</v>
       </c>
       <c r="E1440" t="n">
-        <v>3620.6</v>
+        <v>5405.4</v>
       </c>
       <c r="F1440" t="n">
-        <v>13224.7</v>
+        <v>15009.5</v>
       </c>
       <c r="G1440" t="n">
         <v>5</v>
@@ -47977,13 +47977,13 @@
         </is>
       </c>
       <c r="D1441" t="n">
-        <v>201.8</v>
+        <v>302.7</v>
       </c>
       <c r="E1441" t="n">
-        <v>3877</v>
+        <v>5781</v>
       </c>
       <c r="F1441" t="n">
-        <v>11412</v>
+        <v>13316</v>
       </c>
       <c r="G1441" t="n">
         <v>1</v>
@@ -48010,13 +48010,13 @@
         </is>
       </c>
       <c r="D1442" t="n">
-        <v>165</v>
+        <v>247.5</v>
       </c>
       <c r="E1442" t="n">
-        <v>4050.2</v>
+        <v>6054.8</v>
       </c>
       <c r="F1442" t="n">
-        <v>14761.3</v>
+        <v>16765.9</v>
       </c>
       <c r="G1442" t="n">
         <v>3</v>
@@ -48043,19 +48043,19 @@
         </is>
       </c>
       <c r="D1443" t="n">
-        <v>147</v>
+        <v>220.5</v>
       </c>
       <c r="E1443" t="n">
-        <v>3959.4</v>
+        <v>5923.1</v>
       </c>
       <c r="F1443" t="n">
-        <v>14650.4</v>
+        <v>16614.1</v>
       </c>
       <c r="G1443" t="n">
         <v>4</v>
       </c>
       <c r="H1443" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1443" t="n">
         <v>3</v>
@@ -48076,13 +48076,13 @@
         </is>
       </c>
       <c r="D1444" t="n">
-        <v>229</v>
+        <v>343.5</v>
       </c>
       <c r="E1444" t="n">
-        <v>3795.8</v>
+        <v>5658.2</v>
       </c>
       <c r="F1444" t="n">
-        <v>13660.9</v>
+        <v>15523.3</v>
       </c>
       <c r="G1444" t="n">
         <v>1</v>
@@ -48109,13 +48109,13 @@
         </is>
       </c>
       <c r="D1445" t="n">
-        <v>171.8</v>
+        <v>257.7</v>
       </c>
       <c r="E1445" t="n">
-        <v>3480.6</v>
+        <v>5199.4</v>
       </c>
       <c r="F1445" t="n">
-        <v>13145.2</v>
+        <v>14864</v>
       </c>
       <c r="G1445" t="n">
         <v>2</v>
@@ -48142,13 +48142,13 @@
         </is>
       </c>
       <c r="D1446" t="n">
-        <v>97.2</v>
+        <v>145.8</v>
       </c>
       <c r="E1446" t="n">
-        <v>4033</v>
+        <v>6010</v>
       </c>
       <c r="F1446" t="n">
-        <v>14967.8</v>
+        <v>16944.8</v>
       </c>
       <c r="G1446" t="n">
         <v>6</v>
@@ -48175,13 +48175,13 @@
         </is>
       </c>
       <c r="D1447" t="n">
-        <v>105.6</v>
+        <v>158.4</v>
       </c>
       <c r="E1447" t="n">
-        <v>3241</v>
+        <v>4834</v>
       </c>
       <c r="F1447" t="n">
-        <v>12074.9</v>
+        <v>13667.9</v>
       </c>
       <c r="G1447" t="n">
         <v>5</v>
@@ -48208,13 +48208,13 @@
         </is>
       </c>
       <c r="D1448" t="n">
-        <v>95.8</v>
+        <v>143.7</v>
       </c>
       <c r="E1448" t="n">
-        <v>3716.4</v>
+        <v>5549.1</v>
       </c>
       <c r="F1448" t="n">
-        <v>13320.5</v>
+        <v>15153.2</v>
       </c>
       <c r="G1448" t="n">
         <v>7</v>
@@ -48241,19 +48241,19 @@
         </is>
       </c>
       <c r="D1449" t="n">
-        <v>86.59999999999999</v>
+        <v>129.9</v>
       </c>
       <c r="E1449" t="n">
-        <v>3963.6</v>
+        <v>5910.9</v>
       </c>
       <c r="F1449" t="n">
-        <v>11498.6</v>
+        <v>13445.9</v>
       </c>
       <c r="G1449" t="n">
         <v>8</v>
       </c>
       <c r="H1449" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1449" t="n">
         <v>8</v>
@@ -48274,13 +48274,13 @@
         </is>
       </c>
       <c r="D1450" t="n">
-        <v>133</v>
+        <v>199.5</v>
       </c>
       <c r="E1450" t="n">
-        <v>4183.2</v>
+        <v>6254.3</v>
       </c>
       <c r="F1450" t="n">
-        <v>14894.3</v>
+        <v>16965.4</v>
       </c>
       <c r="G1450" t="n">
         <v>5</v>
@@ -48307,13 +48307,13 @@
         </is>
       </c>
       <c r="D1451" t="n">
-        <v>131</v>
+        <v>196.5</v>
       </c>
       <c r="E1451" t="n">
-        <v>4090.4</v>
+        <v>6119.6</v>
       </c>
       <c r="F1451" t="n">
-        <v>14781.4</v>
+        <v>16810.6</v>
       </c>
       <c r="G1451" t="n">
         <v>7</v>
@@ -48340,13 +48340,13 @@
         </is>
       </c>
       <c r="D1452" t="n">
-        <v>167.8</v>
+        <v>251.7</v>
       </c>
       <c r="E1452" t="n">
-        <v>3963.6</v>
+        <v>5909.9</v>
       </c>
       <c r="F1452" t="n">
-        <v>13828.7</v>
+        <v>15775</v>
       </c>
       <c r="G1452" t="n">
         <v>3</v>
@@ -48373,13 +48373,13 @@
         </is>
       </c>
       <c r="D1453" t="n">
-        <v>132.8</v>
+        <v>199.2</v>
       </c>
       <c r="E1453" t="n">
-        <v>3613.4</v>
+        <v>5398.6</v>
       </c>
       <c r="F1453" t="n">
-        <v>13278</v>
+        <v>15063.2</v>
       </c>
       <c r="G1453" t="n">
         <v>6</v>
@@ -48406,13 +48406,13 @@
         </is>
       </c>
       <c r="D1454" t="n">
-        <v>214</v>
+        <v>321</v>
       </c>
       <c r="E1454" t="n">
-        <v>4247</v>
+        <v>6331</v>
       </c>
       <c r="F1454" t="n">
-        <v>15181.8</v>
+        <v>17265.8</v>
       </c>
       <c r="G1454" t="n">
         <v>1</v>
@@ -48439,13 +48439,13 @@
         </is>
       </c>
       <c r="D1455" t="n">
-        <v>93</v>
+        <v>139.5</v>
       </c>
       <c r="E1455" t="n">
-        <v>3334</v>
+        <v>4973.5</v>
       </c>
       <c r="F1455" t="n">
-        <v>12167.9</v>
+        <v>13807.4</v>
       </c>
       <c r="G1455" t="n">
         <v>8</v>
@@ -48472,13 +48472,13 @@
         </is>
       </c>
       <c r="D1456" t="n">
-        <v>134.8</v>
+        <v>202.2</v>
       </c>
       <c r="E1456" t="n">
-        <v>3851.2</v>
+        <v>5751.3</v>
       </c>
       <c r="F1456" t="n">
-        <v>13455.3</v>
+        <v>15355.4</v>
       </c>
       <c r="G1456" t="n">
         <v>4</v>
@@ -48505,13 +48505,13 @@
         </is>
       </c>
       <c r="D1457" t="n">
-        <v>171.2</v>
+        <v>256.8</v>
       </c>
       <c r="E1457" t="n">
-        <v>4134.8</v>
+        <v>6167.7</v>
       </c>
       <c r="F1457" t="n">
-        <v>11669.8</v>
+        <v>13702.7</v>
       </c>
       <c r="G1457" t="n">
         <v>2</v>
@@ -48538,13 +48538,13 @@
         </is>
       </c>
       <c r="D1458" t="n">
-        <v>201.2</v>
+        <v>301.8</v>
       </c>
       <c r="E1458" t="n">
-        <v>4384.4</v>
+        <v>6556.1</v>
       </c>
       <c r="F1458" t="n">
-        <v>15095.5</v>
+        <v>17267.2</v>
       </c>
       <c r="G1458" t="n">
         <v>1</v>
@@ -48571,13 +48571,13 @@
         </is>
       </c>
       <c r="D1459" t="n">
-        <v>131.8</v>
+        <v>197.7</v>
       </c>
       <c r="E1459" t="n">
-        <v>4222.2</v>
+        <v>6317.3</v>
       </c>
       <c r="F1459" t="n">
-        <v>14913.2</v>
+        <v>17008.3</v>
       </c>
       <c r="G1459" t="n">
         <v>5</v>
@@ -48604,13 +48604,13 @@
         </is>
       </c>
       <c r="D1460" t="n">
-        <v>141.6</v>
+        <v>212.4</v>
       </c>
       <c r="E1460" t="n">
-        <v>4105.2</v>
+        <v>6122.3</v>
       </c>
       <c r="F1460" t="n">
-        <v>13970.3</v>
+        <v>15987.4</v>
       </c>
       <c r="G1460" t="n">
         <v>4</v>
@@ -48637,13 +48637,13 @@
         </is>
       </c>
       <c r="D1461" t="n">
-        <v>121</v>
+        <v>181.5</v>
       </c>
       <c r="E1461" t="n">
-        <v>3734.4</v>
+        <v>5580.1</v>
       </c>
       <c r="F1461" t="n">
-        <v>13399</v>
+        <v>15244.7</v>
       </c>
       <c r="G1461" t="n">
         <v>7</v>
@@ -48670,13 +48670,13 @@
         </is>
       </c>
       <c r="D1462" t="n">
-        <v>129.2</v>
+        <v>193.8</v>
       </c>
       <c r="E1462" t="n">
-        <v>4376.2</v>
+        <v>6524.8</v>
       </c>
       <c r="F1462" t="n">
-        <v>15311</v>
+        <v>17459.6</v>
       </c>
       <c r="G1462" t="n">
         <v>6</v>
@@ -48703,13 +48703,13 @@
         </is>
       </c>
       <c r="D1463" t="n">
-        <v>147.4</v>
+        <v>221.1</v>
       </c>
       <c r="E1463" t="n">
-        <v>3481.4</v>
+        <v>5194.6</v>
       </c>
       <c r="F1463" t="n">
-        <v>12315.3</v>
+        <v>14028.5</v>
       </c>
       <c r="G1463" t="n">
         <v>3</v>
@@ -48736,13 +48736,13 @@
         </is>
       </c>
       <c r="D1464" t="n">
-        <v>110.4</v>
+        <v>165.6</v>
       </c>
       <c r="E1464" t="n">
-        <v>3961.6</v>
+        <v>5916.9</v>
       </c>
       <c r="F1464" t="n">
-        <v>13565.7</v>
+        <v>15521</v>
       </c>
       <c r="G1464" t="n">
         <v>8</v>
@@ -48769,13 +48769,13 @@
         </is>
       </c>
       <c r="D1465" t="n">
-        <v>176</v>
+        <v>264</v>
       </c>
       <c r="E1465" t="n">
-        <v>4310.8</v>
+        <v>6431.7</v>
       </c>
       <c r="F1465" t="n">
-        <v>11845.8</v>
+        <v>13966.7</v>
       </c>
       <c r="G1465" t="n">
         <v>2</v>
@@ -48805,10 +48805,10 @@
         <v>76.3</v>
       </c>
       <c r="E1466" t="n">
-        <v>4460.7</v>
+        <v>6632.4</v>
       </c>
       <c r="F1466" t="n">
-        <v>15171.8</v>
+        <v>17343.5</v>
       </c>
       <c r="G1466" t="n">
         <v>3</v>
@@ -48838,10 +48838,10 @@
         <v>73.3</v>
       </c>
       <c r="E1467" t="n">
-        <v>4295.5</v>
+        <v>6390.6</v>
       </c>
       <c r="F1467" t="n">
-        <v>14986.5</v>
+        <v>17081.6</v>
       </c>
       <c r="G1467" t="n">
         <v>5</v>
@@ -48871,10 +48871,10 @@
         <v>56.5</v>
       </c>
       <c r="E1468" t="n">
-        <v>4161.7</v>
+        <v>6178.8</v>
       </c>
       <c r="F1468" t="n">
-        <v>14026.8</v>
+        <v>16043.9</v>
       </c>
       <c r="G1468" t="n">
         <v>7</v>
@@ -48904,10 +48904,10 @@
         <v>75.09999999999999</v>
       </c>
       <c r="E1469" t="n">
-        <v>3809.5</v>
+        <v>5655.2</v>
       </c>
       <c r="F1469" t="n">
-        <v>13474.1</v>
+        <v>15319.8</v>
       </c>
       <c r="G1469" t="n">
         <v>4</v>
@@ -48937,10 +48937,10 @@
         <v>69.7</v>
       </c>
       <c r="E1470" t="n">
-        <v>4445.9</v>
+        <v>6594.5</v>
       </c>
       <c r="F1470" t="n">
-        <v>15380.7</v>
+        <v>17529.3</v>
       </c>
       <c r="G1470" t="n">
         <v>6</v>
@@ -48970,10 +48970,10 @@
         <v>80.09999999999999</v>
       </c>
       <c r="E1471" t="n">
-        <v>3561.5</v>
+        <v>5274.7</v>
       </c>
       <c r="F1471" t="n">
-        <v>12395.4</v>
+        <v>14108.6</v>
       </c>
       <c r="G1471" t="n">
         <v>2</v>
@@ -49003,10 +49003,10 @@
         <v>44.9</v>
       </c>
       <c r="E1472" t="n">
-        <v>4006.5</v>
+        <v>5961.8</v>
       </c>
       <c r="F1472" t="n">
-        <v>13610.6</v>
+        <v>15565.9</v>
       </c>
       <c r="G1472" t="n">
         <v>8</v>
@@ -49036,10 +49036,10 @@
         <v>82.40000000000001</v>
       </c>
       <c r="E1473" t="n">
-        <v>4393.2</v>
+        <v>6514.1</v>
       </c>
       <c r="F1473" t="n">
-        <v>11928.2</v>
+        <v>14049.1</v>
       </c>
       <c r="G1473" t="n">
         <v>1</v>

--- a/datos/vistas_negocio/Fact_Global_Master.xlsx
+++ b/datos/vistas_negocio/Fact_Global_Master.xlsx
@@ -40882,13 +40882,13 @@
         </is>
       </c>
       <c r="D1226" t="n">
-        <v>132.6</v>
+        <v>176.8</v>
       </c>
       <c r="E1226" t="n">
-        <v>173.6</v>
+        <v>217.8</v>
       </c>
       <c r="F1226" t="n">
-        <v>10884.7</v>
+        <v>10928.9</v>
       </c>
       <c r="G1226" t="n">
         <v>8</v>
@@ -40915,13 +40915,13 @@
         </is>
       </c>
       <c r="D1227" t="n">
-        <v>279.9</v>
+        <v>373.2</v>
       </c>
       <c r="E1227" t="n">
-        <v>311.9</v>
+        <v>405.2</v>
       </c>
       <c r="F1227" t="n">
-        <v>11002.9</v>
+        <v>11096.2</v>
       </c>
       <c r="G1227" t="n">
         <v>2</v>
@@ -40948,13 +40948,13 @@
         </is>
       </c>
       <c r="D1228" t="n">
-        <v>190.2</v>
+        <v>253.6</v>
       </c>
       <c r="E1228" t="n">
-        <v>261.2</v>
+        <v>324.6</v>
       </c>
       <c r="F1228" t="n">
-        <v>10126.3</v>
+        <v>10189.7</v>
       </c>
       <c r="G1228" t="n">
         <v>4</v>
@@ -40981,13 +40981,13 @@
         </is>
       </c>
       <c r="D1229" t="n">
-        <v>309</v>
+        <v>412</v>
       </c>
       <c r="E1229" t="n">
-        <v>352</v>
+        <v>455</v>
       </c>
       <c r="F1229" t="n">
-        <v>10016.6</v>
+        <v>10119.6</v>
       </c>
       <c r="G1229" t="n">
         <v>1</v>
@@ -41014,13 +41014,13 @@
         </is>
       </c>
       <c r="D1230" t="n">
-        <v>180.6</v>
+        <v>240.8</v>
       </c>
       <c r="E1230" t="n">
-        <v>259.6</v>
+        <v>319.8</v>
       </c>
       <c r="F1230" t="n">
-        <v>11194.4</v>
+        <v>11254.6</v>
       </c>
       <c r="G1230" t="n">
         <v>5</v>
@@ -41047,13 +41047,13 @@
         </is>
       </c>
       <c r="D1231" t="n">
-        <v>133.8</v>
+        <v>178.4</v>
       </c>
       <c r="E1231" t="n">
-        <v>188.8</v>
+        <v>233.4</v>
       </c>
       <c r="F1231" t="n">
-        <v>9022.700000000001</v>
+        <v>9067.299999999999</v>
       </c>
       <c r="G1231" t="n">
         <v>7</v>
@@ -41080,13 +41080,13 @@
         </is>
       </c>
       <c r="D1232" t="n">
-        <v>210.3</v>
+        <v>280.4</v>
       </c>
       <c r="E1232" t="n">
-        <v>261.3</v>
+        <v>331.4</v>
       </c>
       <c r="F1232" t="n">
-        <v>9865.4</v>
+        <v>9935.5</v>
       </c>
       <c r="G1232" t="n">
         <v>3</v>
@@ -41113,13 +41113,13 @@
         </is>
       </c>
       <c r="D1233" t="n">
-        <v>173.4</v>
+        <v>231.2</v>
       </c>
       <c r="E1233" t="n">
-        <v>242.4</v>
+        <v>300.2</v>
       </c>
       <c r="F1233" t="n">
-        <v>7777.4</v>
+        <v>7835.2</v>
       </c>
       <c r="G1233" t="n">
         <v>6</v>
@@ -41146,13 +41146,13 @@
         </is>
       </c>
       <c r="D1234" t="n">
-        <v>187.2</v>
+        <v>249.6</v>
       </c>
       <c r="E1234" t="n">
-        <v>360.8</v>
+        <v>467.4</v>
       </c>
       <c r="F1234" t="n">
-        <v>11071.9</v>
+        <v>11178.5</v>
       </c>
       <c r="G1234" t="n">
         <v>5</v>
@@ -41179,13 +41179,13 @@
         </is>
       </c>
       <c r="D1235" t="n">
-        <v>200.4</v>
+        <v>267.2</v>
       </c>
       <c r="E1235" t="n">
-        <v>512.3000000000001</v>
+        <v>672.4</v>
       </c>
       <c r="F1235" t="n">
-        <v>11203.3</v>
+        <v>11363.4</v>
       </c>
       <c r="G1235" t="n">
         <v>3</v>
@@ -41212,13 +41212,13 @@
         </is>
       </c>
       <c r="D1236" t="n">
-        <v>219</v>
+        <v>292</v>
       </c>
       <c r="E1236" t="n">
-        <v>480.2</v>
+        <v>616.6</v>
       </c>
       <c r="F1236" t="n">
-        <v>10345.3</v>
+        <v>10481.7</v>
       </c>
       <c r="G1236" t="n">
         <v>1</v>
@@ -41245,13 +41245,13 @@
         </is>
       </c>
       <c r="D1237" t="n">
-        <v>190.8</v>
+        <v>254.4</v>
       </c>
       <c r="E1237" t="n">
-        <v>542.8</v>
+        <v>709.4</v>
       </c>
       <c r="F1237" t="n">
-        <v>10207.4</v>
+        <v>10374</v>
       </c>
       <c r="G1237" t="n">
         <v>4</v>
@@ -41278,13 +41278,13 @@
         </is>
       </c>
       <c r="D1238" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
       <c r="E1238" t="n">
-        <v>469.6</v>
+        <v>599.8</v>
       </c>
       <c r="F1238" t="n">
-        <v>11404.4</v>
+        <v>11534.6</v>
       </c>
       <c r="G1238" t="n">
         <v>2</v>
@@ -41311,13 +41311,13 @@
         </is>
       </c>
       <c r="D1239" t="n">
-        <v>121.5</v>
+        <v>162</v>
       </c>
       <c r="E1239" t="n">
-        <v>310.3</v>
+        <v>395.4</v>
       </c>
       <c r="F1239" t="n">
-        <v>9144.200000000001</v>
+        <v>9229.299999999999</v>
       </c>
       <c r="G1239" t="n">
         <v>8</v>
@@ -41344,13 +41344,13 @@
         </is>
       </c>
       <c r="D1240" t="n">
-        <v>179.4</v>
+        <v>239.2</v>
       </c>
       <c r="E1240" t="n">
-        <v>440.7</v>
+        <v>570.6</v>
       </c>
       <c r="F1240" t="n">
-        <v>10044.8</v>
+        <v>10174.7</v>
       </c>
       <c r="G1240" t="n">
         <v>6</v>
@@ -41377,13 +41377,13 @@
         </is>
       </c>
       <c r="D1241" t="n">
-        <v>130.5</v>
+        <v>174</v>
       </c>
       <c r="E1241" t="n">
-        <v>372.9</v>
+        <v>474.2</v>
       </c>
       <c r="F1241" t="n">
-        <v>7907.9</v>
+        <v>8009.2</v>
       </c>
       <c r="G1241" t="n">
         <v>7</v>
@@ -41410,13 +41410,13 @@
         </is>
       </c>
       <c r="D1242" t="n">
-        <v>170.7</v>
+        <v>227.6</v>
       </c>
       <c r="E1242" t="n">
-        <v>531.5</v>
+        <v>695</v>
       </c>
       <c r="F1242" t="n">
-        <v>11242.6</v>
+        <v>11406.1</v>
       </c>
       <c r="G1242" t="n">
         <v>4</v>
@@ -41443,13 +41443,13 @@
         </is>
       </c>
       <c r="D1243" t="n">
-        <v>165.3</v>
+        <v>220.4</v>
       </c>
       <c r="E1243" t="n">
-        <v>677.6</v>
+        <v>892.8</v>
       </c>
       <c r="F1243" t="n">
-        <v>11368.6</v>
+        <v>11583.8</v>
       </c>
       <c r="G1243" t="n">
         <v>6</v>
@@ -41476,13 +41476,13 @@
         </is>
       </c>
       <c r="D1244" t="n">
-        <v>176.4</v>
+        <v>235.2</v>
       </c>
       <c r="E1244" t="n">
-        <v>656.6</v>
+        <v>851.8</v>
       </c>
       <c r="F1244" t="n">
-        <v>10521.7</v>
+        <v>10716.9</v>
       </c>
       <c r="G1244" t="n">
         <v>3</v>
@@ -41491,7 +41491,7 @@
         <v>3</v>
       </c>
       <c r="I1244" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1245">
@@ -41509,13 +41509,13 @@
         </is>
       </c>
       <c r="D1245" t="n">
-        <v>258.6</v>
+        <v>344.8</v>
       </c>
       <c r="E1245" t="n">
-        <v>801.4000000000001</v>
+        <v>1054.2</v>
       </c>
       <c r="F1245" t="n">
-        <v>10466</v>
+        <v>10718.8</v>
       </c>
       <c r="G1245" t="n">
         <v>1</v>
@@ -41524,7 +41524,7 @@
         <v>1</v>
       </c>
       <c r="I1245" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1246">
@@ -41542,13 +41542,13 @@
         </is>
       </c>
       <c r="D1246" t="n">
-        <v>170.4</v>
+        <v>227.2</v>
       </c>
       <c r="E1246" t="n">
-        <v>640</v>
+        <v>827</v>
       </c>
       <c r="F1246" t="n">
-        <v>11574.8</v>
+        <v>11761.8</v>
       </c>
       <c r="G1246" t="n">
         <v>5</v>
@@ -41575,13 +41575,13 @@
         </is>
       </c>
       <c r="D1247" t="n">
-        <v>160.5</v>
+        <v>214</v>
       </c>
       <c r="E1247" t="n">
-        <v>470.8</v>
+        <v>609.4</v>
       </c>
       <c r="F1247" t="n">
-        <v>9304.700000000001</v>
+        <v>9443.299999999999</v>
       </c>
       <c r="G1247" t="n">
         <v>7</v>
@@ -41608,13 +41608,13 @@
         </is>
       </c>
       <c r="D1248" t="n">
-        <v>132.6</v>
+        <v>176.8</v>
       </c>
       <c r="E1248" t="n">
-        <v>573.3</v>
+        <v>747.4</v>
       </c>
       <c r="F1248" t="n">
-        <v>10177.4</v>
+        <v>10351.5</v>
       </c>
       <c r="G1248" t="n">
         <v>8</v>
@@ -41641,13 +41641,13 @@
         </is>
       </c>
       <c r="D1249" t="n">
-        <v>214.5</v>
+        <v>286</v>
       </c>
       <c r="E1249" t="n">
-        <v>587.4</v>
+        <v>760.2</v>
       </c>
       <c r="F1249" t="n">
-        <v>8122.4</v>
+        <v>8295.200000000001</v>
       </c>
       <c r="G1249" t="n">
         <v>2</v>
@@ -41674,13 +41674,13 @@
         </is>
       </c>
       <c r="D1250" t="n">
-        <v>149.7</v>
+        <v>199.6</v>
       </c>
       <c r="E1250" t="n">
-        <v>681.2</v>
+        <v>894.6</v>
       </c>
       <c r="F1250" t="n">
-        <v>11392.3</v>
+        <v>11605.7</v>
       </c>
       <c r="G1250" t="n">
         <v>8</v>
@@ -41707,19 +41707,19 @@
         </is>
       </c>
       <c r="D1251" t="n">
-        <v>211.2</v>
+        <v>281.6</v>
       </c>
       <c r="E1251" t="n">
-        <v>888.8</v>
+        <v>1174.4</v>
       </c>
       <c r="F1251" t="n">
-        <v>11579.8</v>
+        <v>11865.4</v>
       </c>
       <c r="G1251" t="n">
         <v>5</v>
       </c>
       <c r="H1251" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I1251" t="n">
         <v>2</v>
@@ -41740,13 +41740,13 @@
         </is>
       </c>
       <c r="D1252" t="n">
-        <v>171.3</v>
+        <v>228.4</v>
       </c>
       <c r="E1252" t="n">
-        <v>827.9000000000001</v>
+        <v>1080.2</v>
       </c>
       <c r="F1252" t="n">
-        <v>10693</v>
+        <v>10945.3</v>
       </c>
       <c r="G1252" t="n">
         <v>6</v>
@@ -41773,13 +41773,13 @@
         </is>
       </c>
       <c r="D1253" t="n">
-        <v>248.1</v>
+        <v>330.8</v>
       </c>
       <c r="E1253" t="n">
-        <v>1049.5</v>
+        <v>1385</v>
       </c>
       <c r="F1253" t="n">
-        <v>10714.1</v>
+        <v>11049.6</v>
       </c>
       <c r="G1253" t="n">
         <v>2</v>
@@ -41806,19 +41806,19 @@
         </is>
       </c>
       <c r="D1254" t="n">
-        <v>259.5</v>
+        <v>346</v>
       </c>
       <c r="E1254" t="n">
-        <v>899.5</v>
+        <v>1173</v>
       </c>
       <c r="F1254" t="n">
-        <v>11834.3</v>
+        <v>12107.8</v>
       </c>
       <c r="G1254" t="n">
         <v>1</v>
       </c>
       <c r="H1254" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I1254" t="n">
         <v>1</v>
@@ -41839,13 +41839,13 @@
         </is>
       </c>
       <c r="D1255" t="n">
-        <v>227.4</v>
+        <v>303.2</v>
       </c>
       <c r="E1255" t="n">
-        <v>698.2</v>
+        <v>912.6</v>
       </c>
       <c r="F1255" t="n">
-        <v>9532.1</v>
+        <v>9746.5</v>
       </c>
       <c r="G1255" t="n">
         <v>4</v>
@@ -41872,13 +41872,13 @@
         </is>
       </c>
       <c r="D1256" t="n">
-        <v>233.1</v>
+        <v>310.8</v>
       </c>
       <c r="E1256" t="n">
-        <v>806.4</v>
+        <v>1058.2</v>
       </c>
       <c r="F1256" t="n">
-        <v>10410.5</v>
+        <v>10662.3</v>
       </c>
       <c r="G1256" t="n">
         <v>3</v>
@@ -41905,13 +41905,13 @@
         </is>
       </c>
       <c r="D1257" t="n">
-        <v>166.8</v>
+        <v>222.4</v>
       </c>
       <c r="E1257" t="n">
-        <v>754.2</v>
+        <v>982.6</v>
       </c>
       <c r="F1257" t="n">
-        <v>8289.200000000001</v>
+        <v>8517.6</v>
       </c>
       <c r="G1257" t="n">
         <v>7</v>
@@ -41938,13 +41938,13 @@
         </is>
       </c>
       <c r="D1258" t="n">
-        <v>102.6</v>
+        <v>136.8</v>
       </c>
       <c r="E1258" t="n">
-        <v>783.8</v>
+        <v>1031.4</v>
       </c>
       <c r="F1258" t="n">
-        <v>11494.9</v>
+        <v>11742.5</v>
       </c>
       <c r="G1258" t="n">
         <v>6</v>
@@ -41971,13 +41971,13 @@
         </is>
       </c>
       <c r="D1259" t="n">
-        <v>136.8</v>
+        <v>182.4</v>
       </c>
       <c r="E1259" t="n">
-        <v>1025.6</v>
+        <v>1356.8</v>
       </c>
       <c r="F1259" t="n">
-        <v>11716.6</v>
+        <v>12047.8</v>
       </c>
       <c r="G1259" t="n">
         <v>5</v>
@@ -42004,13 +42004,13 @@
         </is>
       </c>
       <c r="D1260" t="n">
-        <v>168.3</v>
+        <v>224.4</v>
       </c>
       <c r="E1260" t="n">
-        <v>996.2</v>
+        <v>1304.6</v>
       </c>
       <c r="F1260" t="n">
-        <v>10861.3</v>
+        <v>11169.7</v>
       </c>
       <c r="G1260" t="n">
         <v>3</v>
@@ -42037,13 +42037,13 @@
         </is>
       </c>
       <c r="D1261" t="n">
-        <v>185.1</v>
+        <v>246.8</v>
       </c>
       <c r="E1261" t="n">
-        <v>1234.6</v>
+        <v>1631.8</v>
       </c>
       <c r="F1261" t="n">
-        <v>10899.2</v>
+        <v>11296.4</v>
       </c>
       <c r="G1261" t="n">
         <v>1</v>
@@ -42070,13 +42070,13 @@
         </is>
       </c>
       <c r="D1262" t="n">
-        <v>174.9</v>
+        <v>233.2</v>
       </c>
       <c r="E1262" t="n">
-        <v>1074.4</v>
+        <v>1406.2</v>
       </c>
       <c r="F1262" t="n">
-        <v>12009.2</v>
+        <v>12341</v>
       </c>
       <c r="G1262" t="n">
         <v>2</v>
@@ -42103,13 +42103,13 @@
         </is>
       </c>
       <c r="D1263" t="n">
-        <v>143.7</v>
+        <v>191.6</v>
       </c>
       <c r="E1263" t="n">
-        <v>841.9</v>
+        <v>1104.2</v>
       </c>
       <c r="F1263" t="n">
-        <v>9675.799999999999</v>
+        <v>9938.1</v>
       </c>
       <c r="G1263" t="n">
         <v>4</v>
@@ -42136,13 +42136,13 @@
         </is>
       </c>
       <c r="D1264" t="n">
-        <v>97.2</v>
+        <v>129.6</v>
       </c>
       <c r="E1264" t="n">
-        <v>903.6</v>
+        <v>1187.8</v>
       </c>
       <c r="F1264" t="n">
-        <v>10507.7</v>
+        <v>10791.9</v>
       </c>
       <c r="G1264" t="n">
         <v>8</v>
@@ -42169,13 +42169,13 @@
         </is>
       </c>
       <c r="D1265" t="n">
-        <v>102.6</v>
+        <v>136.8</v>
       </c>
       <c r="E1265" t="n">
-        <v>856.8</v>
+        <v>1119.4</v>
       </c>
       <c r="F1265" t="n">
-        <v>8391.799999999999</v>
+        <v>8654.4</v>
       </c>
       <c r="G1265" t="n">
         <v>6</v>
@@ -42202,13 +42202,13 @@
         </is>
       </c>
       <c r="D1266" t="n">
-        <v>220.8</v>
+        <v>294.4</v>
       </c>
       <c r="E1266" t="n">
-        <v>1004.6</v>
+        <v>1325.8</v>
       </c>
       <c r="F1266" t="n">
-        <v>11715.7</v>
+        <v>12036.9</v>
       </c>
       <c r="G1266" t="n">
         <v>3</v>
@@ -42235,13 +42235,13 @@
         </is>
       </c>
       <c r="D1267" t="n">
-        <v>178.2</v>
+        <v>237.6</v>
       </c>
       <c r="E1267" t="n">
-        <v>1203.8</v>
+        <v>1594.4</v>
       </c>
       <c r="F1267" t="n">
-        <v>11894.8</v>
+        <v>12285.4</v>
       </c>
       <c r="G1267" t="n">
         <v>5</v>
@@ -42268,13 +42268,13 @@
         </is>
       </c>
       <c r="D1268" t="n">
-        <v>235.8</v>
+        <v>314.4</v>
       </c>
       <c r="E1268" t="n">
-        <v>1232</v>
+        <v>1619</v>
       </c>
       <c r="F1268" t="n">
-        <v>11097.1</v>
+        <v>11484.1</v>
       </c>
       <c r="G1268" t="n">
         <v>1</v>
@@ -42301,13 +42301,13 @@
         </is>
       </c>
       <c r="D1269" t="n">
-        <v>138</v>
+        <v>184</v>
       </c>
       <c r="E1269" t="n">
-        <v>1372.6</v>
+        <v>1815.8</v>
       </c>
       <c r="F1269" t="n">
-        <v>11037.2</v>
+        <v>11480.4</v>
       </c>
       <c r="G1269" t="n">
         <v>8</v>
@@ -42334,13 +42334,13 @@
         </is>
       </c>
       <c r="D1270" t="n">
-        <v>210.3</v>
+        <v>280.4</v>
       </c>
       <c r="E1270" t="n">
-        <v>1284.7</v>
+        <v>1686.6</v>
       </c>
       <c r="F1270" t="n">
-        <v>12219.5</v>
+        <v>12621.4</v>
       </c>
       <c r="G1270" t="n">
         <v>4</v>
@@ -42367,13 +42367,13 @@
         </is>
       </c>
       <c r="D1271" t="n">
-        <v>157.5</v>
+        <v>210</v>
       </c>
       <c r="E1271" t="n">
-        <v>999.4</v>
+        <v>1314.2</v>
       </c>
       <c r="F1271" t="n">
-        <v>9833.299999999999</v>
+        <v>10148.1</v>
       </c>
       <c r="G1271" t="n">
         <v>7</v>
@@ -42400,13 +42400,13 @@
         </is>
       </c>
       <c r="D1272" t="n">
-        <v>224.7</v>
+        <v>299.6</v>
       </c>
       <c r="E1272" t="n">
-        <v>1128.3</v>
+        <v>1487.4</v>
       </c>
       <c r="F1272" t="n">
-        <v>10732.4</v>
+        <v>11091.5</v>
       </c>
       <c r="G1272" t="n">
         <v>2</v>
@@ -42433,13 +42433,13 @@
         </is>
       </c>
       <c r="D1273" t="n">
-        <v>174.6</v>
+        <v>232.8</v>
       </c>
       <c r="E1273" t="n">
-        <v>1031.4</v>
+        <v>1352.2</v>
       </c>
       <c r="F1273" t="n">
-        <v>8566.4</v>
+        <v>8887.200000000001</v>
       </c>
       <c r="G1273" t="n">
         <v>6</v>
@@ -42466,13 +42466,13 @@
         </is>
       </c>
       <c r="D1274" t="n">
-        <v>161.4</v>
+        <v>215.2</v>
       </c>
       <c r="E1274" t="n">
-        <v>1166</v>
+        <v>1541</v>
       </c>
       <c r="F1274" t="n">
-        <v>11877.1</v>
+        <v>12252.1</v>
       </c>
       <c r="G1274" t="n">
         <v>7</v>
@@ -42499,13 +42499,13 @@
         </is>
       </c>
       <c r="D1275" t="n">
-        <v>153.3</v>
+        <v>204.4</v>
       </c>
       <c r="E1275" t="n">
-        <v>1357.1</v>
+        <v>1798.8</v>
       </c>
       <c r="F1275" t="n">
-        <v>12048.1</v>
+        <v>12489.8</v>
       </c>
       <c r="G1275" t="n">
         <v>8</v>
@@ -42532,13 +42532,13 @@
         </is>
       </c>
       <c r="D1276" t="n">
-        <v>186.3</v>
+        <v>248.4</v>
       </c>
       <c r="E1276" t="n">
-        <v>1418.3</v>
+        <v>1867.4</v>
       </c>
       <c r="F1276" t="n">
-        <v>11283.4</v>
+        <v>11732.5</v>
       </c>
       <c r="G1276" t="n">
         <v>3</v>
@@ -42547,7 +42547,7 @@
         <v>3</v>
       </c>
       <c r="I1276" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1277">
@@ -42565,13 +42565,13 @@
         </is>
       </c>
       <c r="D1277" t="n">
-        <v>208.5</v>
+        <v>278</v>
       </c>
       <c r="E1277" t="n">
-        <v>1581.1</v>
+        <v>2093.8</v>
       </c>
       <c r="F1277" t="n">
-        <v>11245.7</v>
+        <v>11758.4</v>
       </c>
       <c r="G1277" t="n">
         <v>1</v>
@@ -42580,7 +42580,7 @@
         <v>1</v>
       </c>
       <c r="I1277" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1278">
@@ -42598,13 +42598,13 @@
         </is>
       </c>
       <c r="D1278" t="n">
-        <v>178.5</v>
+        <v>238</v>
       </c>
       <c r="E1278" t="n">
-        <v>1463.2</v>
+        <v>1924.6</v>
       </c>
       <c r="F1278" t="n">
-        <v>12398</v>
+        <v>12859.4</v>
       </c>
       <c r="G1278" t="n">
         <v>5</v>
@@ -42631,13 +42631,13 @@
         </is>
       </c>
       <c r="D1279" t="n">
-        <v>162.3</v>
+        <v>216.4</v>
       </c>
       <c r="E1279" t="n">
-        <v>1161.7</v>
+        <v>1530.6</v>
       </c>
       <c r="F1279" t="n">
-        <v>9995.6</v>
+        <v>10364.5</v>
       </c>
       <c r="G1279" t="n">
         <v>6</v>
@@ -42664,13 +42664,13 @@
         </is>
       </c>
       <c r="D1280" t="n">
-        <v>207.6</v>
+        <v>276.8</v>
       </c>
       <c r="E1280" t="n">
-        <v>1335.9</v>
+        <v>1764.2</v>
       </c>
       <c r="F1280" t="n">
-        <v>10940</v>
+        <v>11368.3</v>
       </c>
       <c r="G1280" t="n">
         <v>2</v>
@@ -42697,13 +42697,13 @@
         </is>
       </c>
       <c r="D1281" t="n">
-        <v>180</v>
+        <v>240</v>
       </c>
       <c r="E1281" t="n">
-        <v>1211.4</v>
+        <v>1592.2</v>
       </c>
       <c r="F1281" t="n">
-        <v>8746.4</v>
+        <v>9127.200000000001</v>
       </c>
       <c r="G1281" t="n">
         <v>4</v>
@@ -42730,13 +42730,13 @@
         </is>
       </c>
       <c r="D1282" t="n">
-        <v>263.4</v>
+        <v>351.2</v>
       </c>
       <c r="E1282" t="n">
-        <v>1429.4</v>
+        <v>1892.2</v>
       </c>
       <c r="F1282" t="n">
-        <v>12140.5</v>
+        <v>12603.3</v>
       </c>
       <c r="G1282" t="n">
         <v>1</v>
@@ -42763,13 +42763,13 @@
         </is>
       </c>
       <c r="D1283" t="n">
-        <v>201</v>
+        <v>268</v>
       </c>
       <c r="E1283" t="n">
-        <v>1558.1</v>
+        <v>2066.8</v>
       </c>
       <c r="F1283" t="n">
-        <v>12249.1</v>
+        <v>12757.8</v>
       </c>
       <c r="G1283" t="n">
         <v>4</v>
@@ -42796,13 +42796,13 @@
         </is>
       </c>
       <c r="D1284" t="n">
-        <v>166.2</v>
+        <v>221.6</v>
       </c>
       <c r="E1284" t="n">
-        <v>1584.5</v>
+        <v>2089</v>
       </c>
       <c r="F1284" t="n">
-        <v>11449.6</v>
+        <v>11954.1</v>
       </c>
       <c r="G1284" t="n">
         <v>7</v>
@@ -42811,7 +42811,7 @@
         <v>3</v>
       </c>
       <c r="I1284" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1285">
@@ -42829,13 +42829,13 @@
         </is>
       </c>
       <c r="D1285" t="n">
-        <v>172.8</v>
+        <v>230.4</v>
       </c>
       <c r="E1285" t="n">
-        <v>1753.9</v>
+        <v>2324.2</v>
       </c>
       <c r="F1285" t="n">
-        <v>11418.5</v>
+        <v>11988.8</v>
       </c>
       <c r="G1285" t="n">
         <v>6</v>
@@ -42844,7 +42844,7 @@
         <v>1</v>
       </c>
       <c r="I1285" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1286">
@@ -42862,13 +42862,13 @@
         </is>
       </c>
       <c r="D1286" t="n">
-        <v>198.9</v>
+        <v>265.2</v>
       </c>
       <c r="E1286" t="n">
-        <v>1662.1</v>
+        <v>2189.8</v>
       </c>
       <c r="F1286" t="n">
-        <v>12596.9</v>
+        <v>13124.6</v>
       </c>
       <c r="G1286" t="n">
         <v>5</v>
@@ -42895,13 +42895,13 @@
         </is>
       </c>
       <c r="D1287" t="n">
-        <v>156.3</v>
+        <v>208.4</v>
       </c>
       <c r="E1287" t="n">
-        <v>1318</v>
+        <v>1739</v>
       </c>
       <c r="F1287" t="n">
-        <v>10151.9</v>
+        <v>10572.9</v>
       </c>
       <c r="G1287" t="n">
         <v>8</v>
@@ -42928,13 +42928,13 @@
         </is>
       </c>
       <c r="D1288" t="n">
-        <v>243.3</v>
+        <v>324.4</v>
       </c>
       <c r="E1288" t="n">
-        <v>1579.2</v>
+        <v>2088.6</v>
       </c>
       <c r="F1288" t="n">
-        <v>11183.3</v>
+        <v>11692.7</v>
       </c>
       <c r="G1288" t="n">
         <v>2</v>
@@ -42961,13 +42961,13 @@
         </is>
       </c>
       <c r="D1289" t="n">
-        <v>230.7</v>
+        <v>307.6</v>
       </c>
       <c r="E1289" t="n">
-        <v>1442.1</v>
+        <v>1899.8</v>
       </c>
       <c r="F1289" t="n">
-        <v>8977.1</v>
+        <v>9434.799999999999</v>
       </c>
       <c r="G1289" t="n">
         <v>3</v>
@@ -42994,13 +42994,13 @@
         </is>
       </c>
       <c r="D1290" t="n">
-        <v>233.7</v>
+        <v>311.6</v>
       </c>
       <c r="E1290" t="n">
-        <v>1663.1</v>
+        <v>2203.8</v>
       </c>
       <c r="F1290" t="n">
-        <v>12374.2</v>
+        <v>12914.9</v>
       </c>
       <c r="G1290" t="n">
         <v>1</v>
@@ -43027,13 +43027,13 @@
         </is>
       </c>
       <c r="D1291" t="n">
-        <v>164.4</v>
+        <v>219.2</v>
       </c>
       <c r="E1291" t="n">
-        <v>1722.5</v>
+        <v>2286</v>
       </c>
       <c r="F1291" t="n">
-        <v>12413.5</v>
+        <v>12977</v>
       </c>
       <c r="G1291" t="n">
         <v>7</v>
@@ -43060,22 +43060,22 @@
         </is>
       </c>
       <c r="D1292" t="n">
-        <v>206.4</v>
+        <v>275.2</v>
       </c>
       <c r="E1292" t="n">
-        <v>1790.9</v>
+        <v>2364.2</v>
       </c>
       <c r="F1292" t="n">
-        <v>11656</v>
+        <v>12229.3</v>
       </c>
       <c r="G1292" t="n">
         <v>3</v>
       </c>
       <c r="H1292" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1292" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1293">
@@ -43093,13 +43093,13 @@
         </is>
       </c>
       <c r="D1293" t="n">
-        <v>180.6</v>
+        <v>240.8</v>
       </c>
       <c r="E1293" t="n">
-        <v>1934.5</v>
+        <v>2565</v>
       </c>
       <c r="F1293" t="n">
-        <v>11599.1</v>
+        <v>12229.6</v>
       </c>
       <c r="G1293" t="n">
         <v>6</v>
@@ -43108,7 +43108,7 @@
         <v>1</v>
       </c>
       <c r="I1293" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1294">
@@ -43126,13 +43126,13 @@
         </is>
       </c>
       <c r="D1294" t="n">
-        <v>188.4</v>
+        <v>251.2</v>
       </c>
       <c r="E1294" t="n">
-        <v>1850.5</v>
+        <v>2441</v>
       </c>
       <c r="F1294" t="n">
-        <v>12785.3</v>
+        <v>13375.8</v>
       </c>
       <c r="G1294" t="n">
         <v>5</v>
@@ -43159,13 +43159,13 @@
         </is>
       </c>
       <c r="D1295" t="n">
-        <v>152.7</v>
+        <v>203.6</v>
       </c>
       <c r="E1295" t="n">
-        <v>1470.7</v>
+        <v>1942.6</v>
       </c>
       <c r="F1295" t="n">
-        <v>10304.6</v>
+        <v>10776.5</v>
       </c>
       <c r="G1295" t="n">
         <v>8</v>
@@ -43192,19 +43192,19 @@
         </is>
       </c>
       <c r="D1296" t="n">
-        <v>208.2</v>
+        <v>277.6</v>
       </c>
       <c r="E1296" t="n">
-        <v>1787.4</v>
+        <v>2366.2</v>
       </c>
       <c r="F1296" t="n">
-        <v>11391.5</v>
+        <v>11970.3</v>
       </c>
       <c r="G1296" t="n">
         <v>2</v>
       </c>
       <c r="H1296" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1296" t="n">
         <v>6</v>
@@ -43225,13 +43225,13 @@
         </is>
       </c>
       <c r="D1297" t="n">
-        <v>198.9</v>
+        <v>265.2</v>
       </c>
       <c r="E1297" t="n">
-        <v>1641</v>
+        <v>2165</v>
       </c>
       <c r="F1297" t="n">
-        <v>9176</v>
+        <v>9700</v>
       </c>
       <c r="G1297" t="n">
         <v>4</v>
@@ -43258,13 +43258,13 @@
         </is>
       </c>
       <c r="D1298" t="n">
-        <v>204</v>
+        <v>272</v>
       </c>
       <c r="E1298" t="n">
-        <v>1867.1</v>
+        <v>2475.8</v>
       </c>
       <c r="F1298" t="n">
-        <v>12578.2</v>
+        <v>13186.9</v>
       </c>
       <c r="G1298" t="n">
         <v>5</v>
@@ -43291,13 +43291,13 @@
         </is>
       </c>
       <c r="D1299" t="n">
-        <v>267.6</v>
+        <v>356.8</v>
       </c>
       <c r="E1299" t="n">
-        <v>1990.1</v>
+        <v>2642.8</v>
       </c>
       <c r="F1299" t="n">
-        <v>12681.1</v>
+        <v>13333.8</v>
       </c>
       <c r="G1299" t="n">
         <v>2</v>
@@ -43324,13 +43324,13 @@
         </is>
       </c>
       <c r="D1300" t="n">
-        <v>237.9</v>
+        <v>317.2</v>
       </c>
       <c r="E1300" t="n">
-        <v>2028.8</v>
+        <v>2681.4</v>
       </c>
       <c r="F1300" t="n">
-        <v>11893.9</v>
+        <v>12546.5</v>
       </c>
       <c r="G1300" t="n">
         <v>3</v>
@@ -43357,13 +43357,13 @@
         </is>
       </c>
       <c r="D1301" t="n">
-        <v>183</v>
+        <v>244</v>
       </c>
       <c r="E1301" t="n">
-        <v>2117.5</v>
+        <v>2809</v>
       </c>
       <c r="F1301" t="n">
-        <v>11782.1</v>
+        <v>12473.6</v>
       </c>
       <c r="G1301" t="n">
         <v>6</v>
@@ -43390,19 +43390,19 @@
         </is>
       </c>
       <c r="D1302" t="n">
-        <v>172.2</v>
+        <v>229.6</v>
       </c>
       <c r="E1302" t="n">
-        <v>2022.7</v>
+        <v>2670.6</v>
       </c>
       <c r="F1302" t="n">
-        <v>12957.5</v>
+        <v>13605.4</v>
       </c>
       <c r="G1302" t="n">
         <v>7</v>
       </c>
       <c r="H1302" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1302" t="n">
         <v>1</v>
@@ -43423,13 +43423,13 @@
         </is>
       </c>
       <c r="D1303" t="n">
-        <v>139.2</v>
+        <v>185.6</v>
       </c>
       <c r="E1303" t="n">
-        <v>1609.9</v>
+        <v>2128.2</v>
       </c>
       <c r="F1303" t="n">
-        <v>10443.8</v>
+        <v>10962.1</v>
       </c>
       <c r="G1303" t="n">
         <v>8</v>
@@ -43456,19 +43456,19 @@
         </is>
       </c>
       <c r="D1304" t="n">
-        <v>231.6</v>
+        <v>308.8</v>
       </c>
       <c r="E1304" t="n">
-        <v>2019</v>
+        <v>2675</v>
       </c>
       <c r="F1304" t="n">
-        <v>11623.1</v>
+        <v>12279.1</v>
       </c>
       <c r="G1304" t="n">
         <v>4</v>
       </c>
       <c r="H1304" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1304" t="n">
         <v>6</v>
@@ -43489,13 +43489,13 @@
         </is>
       </c>
       <c r="D1305" t="n">
-        <v>285.6</v>
+        <v>380.8</v>
       </c>
       <c r="E1305" t="n">
-        <v>1926.6</v>
+        <v>2545.8</v>
       </c>
       <c r="F1305" t="n">
-        <v>9461.6</v>
+        <v>10080.8</v>
       </c>
       <c r="G1305" t="n">
         <v>1</v>
@@ -43522,13 +43522,13 @@
         </is>
       </c>
       <c r="D1306" t="n">
-        <v>234</v>
+        <v>312</v>
       </c>
       <c r="E1306" t="n">
-        <v>2101.1</v>
+        <v>2787.8</v>
       </c>
       <c r="F1306" t="n">
-        <v>12812.2</v>
+        <v>13498.9</v>
       </c>
       <c r="G1306" t="n">
         <v>3</v>
@@ -43555,13 +43555,13 @@
         </is>
       </c>
       <c r="D1307" t="n">
-        <v>235.8</v>
+        <v>314.4</v>
       </c>
       <c r="E1307" t="n">
-        <v>2225.9</v>
+        <v>2957.2</v>
       </c>
       <c r="F1307" t="n">
-        <v>12916.9</v>
+        <v>13648.2</v>
       </c>
       <c r="G1307" t="n">
         <v>2</v>
@@ -43588,13 +43588,13 @@
         </is>
       </c>
       <c r="D1308" t="n">
-        <v>230.7</v>
+        <v>307.6</v>
       </c>
       <c r="E1308" t="n">
-        <v>2259.5</v>
+        <v>2989</v>
       </c>
       <c r="F1308" t="n">
-        <v>12124.6</v>
+        <v>12854.1</v>
       </c>
       <c r="G1308" t="n">
         <v>4</v>
@@ -43621,13 +43621,13 @@
         </is>
       </c>
       <c r="D1309" t="n">
-        <v>145.2</v>
+        <v>193.6</v>
       </c>
       <c r="E1309" t="n">
-        <v>2262.7</v>
+        <v>3002.6</v>
       </c>
       <c r="F1309" t="n">
-        <v>11927.3</v>
+        <v>12667.2</v>
       </c>
       <c r="G1309" t="n">
         <v>8</v>
@@ -43654,13 +43654,13 @@
         </is>
       </c>
       <c r="D1310" t="n">
-        <v>202.8</v>
+        <v>270.4</v>
       </c>
       <c r="E1310" t="n">
-        <v>2225.5</v>
+        <v>2941</v>
       </c>
       <c r="F1310" t="n">
-        <v>13160.3</v>
+        <v>13875.8</v>
       </c>
       <c r="G1310" t="n">
         <v>5</v>
@@ -43687,13 +43687,13 @@
         </is>
       </c>
       <c r="D1311" t="n">
-        <v>174.3</v>
+        <v>232.4</v>
       </c>
       <c r="E1311" t="n">
-        <v>1784.2</v>
+        <v>2360.6</v>
       </c>
       <c r="F1311" t="n">
-        <v>10618.1</v>
+        <v>11194.5</v>
       </c>
       <c r="G1311" t="n">
         <v>7</v>
@@ -43720,13 +43720,13 @@
         </is>
       </c>
       <c r="D1312" t="n">
-        <v>184.2</v>
+        <v>245.6</v>
       </c>
       <c r="E1312" t="n">
-        <v>2203.2</v>
+        <v>2920.6</v>
       </c>
       <c r="F1312" t="n">
-        <v>11807.3</v>
+        <v>12524.7</v>
       </c>
       <c r="G1312" t="n">
         <v>6</v>
@@ -43753,13 +43753,13 @@
         </is>
       </c>
       <c r="D1313" t="n">
-        <v>244.8</v>
+        <v>326.4</v>
       </c>
       <c r="E1313" t="n">
-        <v>2171.4</v>
+        <v>2872.2</v>
       </c>
       <c r="F1313" t="n">
-        <v>9706.4</v>
+        <v>10407.2</v>
       </c>
       <c r="G1313" t="n">
         <v>1</v>
@@ -43786,13 +43786,13 @@
         </is>
       </c>
       <c r="D1314" t="n">
-        <v>202.5</v>
+        <v>270</v>
       </c>
       <c r="E1314" t="n">
-        <v>2303.6</v>
+        <v>3057.8</v>
       </c>
       <c r="F1314" t="n">
-        <v>13014.7</v>
+        <v>13768.9</v>
       </c>
       <c r="G1314" t="n">
         <v>5</v>
@@ -43819,13 +43819,13 @@
         </is>
       </c>
       <c r="D1315" t="n">
-        <v>209.4</v>
+        <v>279.2</v>
       </c>
       <c r="E1315" t="n">
-        <v>2435.3</v>
+        <v>3236.4</v>
       </c>
       <c r="F1315" t="n">
-        <v>13126.3</v>
+        <v>13927.4</v>
       </c>
       <c r="G1315" t="n">
         <v>2</v>
@@ -43852,19 +43852,19 @@
         </is>
       </c>
       <c r="D1316" t="n">
-        <v>204.9</v>
+        <v>273.2</v>
       </c>
       <c r="E1316" t="n">
-        <v>2464.4</v>
+        <v>3262.2</v>
       </c>
       <c r="F1316" t="n">
-        <v>12329.5</v>
+        <v>13127.3</v>
       </c>
       <c r="G1316" t="n">
         <v>3</v>
       </c>
       <c r="H1316" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1316" t="n">
         <v>4</v>
@@ -43885,13 +43885,13 @@
         </is>
       </c>
       <c r="D1317" t="n">
-        <v>156.3</v>
+        <v>208.4</v>
       </c>
       <c r="E1317" t="n">
-        <v>2419</v>
+        <v>3211</v>
       </c>
       <c r="F1317" t="n">
-        <v>12083.6</v>
+        <v>12875.6</v>
       </c>
       <c r="G1317" t="n">
         <v>8</v>
@@ -43918,19 +43918,19 @@
         </is>
       </c>
       <c r="D1318" t="n">
-        <v>239.1</v>
+        <v>318.8</v>
       </c>
       <c r="E1318" t="n">
-        <v>2464.6</v>
+        <v>3259.8</v>
       </c>
       <c r="F1318" t="n">
-        <v>13399.4</v>
+        <v>14194.6</v>
       </c>
       <c r="G1318" t="n">
         <v>1</v>
       </c>
       <c r="H1318" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1318" t="n">
         <v>1</v>
@@ -43951,13 +43951,13 @@
         </is>
       </c>
       <c r="D1319" t="n">
-        <v>174</v>
+        <v>232</v>
       </c>
       <c r="E1319" t="n">
-        <v>1958.2</v>
+        <v>2592.6</v>
       </c>
       <c r="F1319" t="n">
-        <v>10792.1</v>
+        <v>11426.5</v>
       </c>
       <c r="G1319" t="n">
         <v>7</v>
@@ -43984,13 +43984,13 @@
         </is>
       </c>
       <c r="D1320" t="n">
-        <v>178.5</v>
+        <v>238</v>
       </c>
       <c r="E1320" t="n">
-        <v>2381.7</v>
+        <v>3158.6</v>
       </c>
       <c r="F1320" t="n">
-        <v>11985.8</v>
+        <v>12762.7</v>
       </c>
       <c r="G1320" t="n">
         <v>6</v>
@@ -44017,13 +44017,13 @@
         </is>
       </c>
       <c r="D1321" t="n">
-        <v>204.3</v>
+        <v>272.4</v>
       </c>
       <c r="E1321" t="n">
-        <v>2375.7</v>
+        <v>3144.6</v>
       </c>
       <c r="F1321" t="n">
-        <v>9910.700000000001</v>
+        <v>10679.6</v>
       </c>
       <c r="G1321" t="n">
         <v>4</v>
@@ -44050,13 +44050,13 @@
         </is>
       </c>
       <c r="D1322" t="n">
-        <v>175.8</v>
+        <v>234.4</v>
       </c>
       <c r="E1322" t="n">
-        <v>2479.4</v>
+        <v>3292.2</v>
       </c>
       <c r="F1322" t="n">
-        <v>13190.5</v>
+        <v>14003.3</v>
       </c>
       <c r="G1322" t="n">
         <v>6</v>
@@ -44083,13 +44083,13 @@
         </is>
       </c>
       <c r="D1323" t="n">
-        <v>317.1</v>
+        <v>422.8</v>
       </c>
       <c r="E1323" t="n">
-        <v>2752.4</v>
+        <v>3659.2</v>
       </c>
       <c r="F1323" t="n">
-        <v>13443.4</v>
+        <v>14350.2</v>
       </c>
       <c r="G1323" t="n">
         <v>1</v>
@@ -44116,13 +44116,13 @@
         </is>
       </c>
       <c r="D1324" t="n">
-        <v>175.2</v>
+        <v>233.6</v>
       </c>
       <c r="E1324" t="n">
-        <v>2639.6</v>
+        <v>3495.8</v>
       </c>
       <c r="F1324" t="n">
-        <v>12504.7</v>
+        <v>13360.9</v>
       </c>
       <c r="G1324" t="n">
         <v>7</v>
@@ -44149,13 +44149,13 @@
         </is>
       </c>
       <c r="D1325" t="n">
-        <v>172.2</v>
+        <v>229.6</v>
       </c>
       <c r="E1325" t="n">
-        <v>2591.2</v>
+        <v>3440.6</v>
       </c>
       <c r="F1325" t="n">
-        <v>12255.8</v>
+        <v>13105.2</v>
       </c>
       <c r="G1325" t="n">
         <v>8</v>
@@ -44182,13 +44182,13 @@
         </is>
       </c>
       <c r="D1326" t="n">
-        <v>250.2</v>
+        <v>333.6</v>
       </c>
       <c r="E1326" t="n">
-        <v>2714.8</v>
+        <v>3593.4</v>
       </c>
       <c r="F1326" t="n">
-        <v>13649.6</v>
+        <v>14528.2</v>
       </c>
       <c r="G1326" t="n">
         <v>3</v>
@@ -44215,13 +44215,13 @@
         </is>
       </c>
       <c r="D1327" t="n">
-        <v>222.9</v>
+        <v>297.2</v>
       </c>
       <c r="E1327" t="n">
-        <v>2181.1</v>
+        <v>2889.8</v>
       </c>
       <c r="F1327" t="n">
-        <v>11015</v>
+        <v>11723.7</v>
       </c>
       <c r="G1327" t="n">
         <v>4</v>
@@ -44248,13 +44248,13 @@
         </is>
       </c>
       <c r="D1328" t="n">
-        <v>216</v>
+        <v>288</v>
       </c>
       <c r="E1328" t="n">
-        <v>2597.7</v>
+        <v>3446.6</v>
       </c>
       <c r="F1328" t="n">
-        <v>12201.8</v>
+        <v>13050.7</v>
       </c>
       <c r="G1328" t="n">
         <v>5</v>
@@ -44281,13 +44281,13 @@
         </is>
       </c>
       <c r="D1329" t="n">
-        <v>261.3</v>
+        <v>348.4</v>
       </c>
       <c r="E1329" t="n">
-        <v>2637</v>
+        <v>3493</v>
       </c>
       <c r="F1329" t="n">
-        <v>10172</v>
+        <v>11028</v>
       </c>
       <c r="G1329" t="n">
         <v>2</v>
@@ -44314,13 +44314,13 @@
         </is>
       </c>
       <c r="D1330" t="n">
-        <v>183.6</v>
+        <v>244.8</v>
       </c>
       <c r="E1330" t="n">
-        <v>2663</v>
+        <v>3537</v>
       </c>
       <c r="F1330" t="n">
-        <v>13374.1</v>
+        <v>14248.1</v>
       </c>
       <c r="G1330" t="n">
         <v>5</v>
@@ -44347,13 +44347,13 @@
         </is>
       </c>
       <c r="D1331" t="n">
-        <v>166.8</v>
+        <v>222.4</v>
       </c>
       <c r="E1331" t="n">
-        <v>2919.2</v>
+        <v>3881.6</v>
       </c>
       <c r="F1331" t="n">
-        <v>13610.2</v>
+        <v>14572.6</v>
       </c>
       <c r="G1331" t="n">
         <v>7</v>
@@ -44380,13 +44380,13 @@
         </is>
       </c>
       <c r="D1332" t="n">
-        <v>151.8</v>
+        <v>202.4</v>
       </c>
       <c r="E1332" t="n">
-        <v>2791.4</v>
+        <v>3698.2</v>
       </c>
       <c r="F1332" t="n">
-        <v>12656.5</v>
+        <v>13563.3</v>
       </c>
       <c r="G1332" t="n">
         <v>8</v>
@@ -44413,13 +44413,13 @@
         </is>
       </c>
       <c r="D1333" t="n">
-        <v>187.2</v>
+        <v>249.6</v>
       </c>
       <c r="E1333" t="n">
-        <v>2778.4</v>
+        <v>3690.2</v>
       </c>
       <c r="F1333" t="n">
-        <v>12443</v>
+        <v>13354.8</v>
       </c>
       <c r="G1333" t="n">
         <v>4</v>
@@ -44446,13 +44446,13 @@
         </is>
       </c>
       <c r="D1334" t="n">
-        <v>245.7</v>
+        <v>327.6</v>
       </c>
       <c r="E1334" t="n">
-        <v>2960.5</v>
+        <v>3921</v>
       </c>
       <c r="F1334" t="n">
-        <v>13895.3</v>
+        <v>14855.8</v>
       </c>
       <c r="G1334" t="n">
         <v>2</v>
@@ -44479,13 +44479,13 @@
         </is>
       </c>
       <c r="D1335" t="n">
-        <v>189.9</v>
+        <v>253.2</v>
       </c>
       <c r="E1335" t="n">
-        <v>2371</v>
+        <v>3143</v>
       </c>
       <c r="F1335" t="n">
-        <v>11204.9</v>
+        <v>11976.9</v>
       </c>
       <c r="G1335" t="n">
         <v>3</v>
@@ -44512,13 +44512,13 @@
         </is>
       </c>
       <c r="D1336" t="n">
-        <v>258</v>
+        <v>344</v>
       </c>
       <c r="E1336" t="n">
-        <v>2855.7</v>
+        <v>3790.6</v>
       </c>
       <c r="F1336" t="n">
-        <v>12459.8</v>
+        <v>13394.7</v>
       </c>
       <c r="G1336" t="n">
         <v>1</v>
@@ -44545,13 +44545,13 @@
         </is>
       </c>
       <c r="D1337" t="n">
-        <v>174.3</v>
+        <v>232.4</v>
       </c>
       <c r="E1337" t="n">
-        <v>2811.3</v>
+        <v>3725.4</v>
       </c>
       <c r="F1337" t="n">
-        <v>10346.3</v>
+        <v>11260.4</v>
       </c>
       <c r="G1337" t="n">
         <v>6</v>
@@ -44578,13 +44578,13 @@
         </is>
       </c>
       <c r="D1338" t="n">
-        <v>192.6</v>
+        <v>256.8</v>
       </c>
       <c r="E1338" t="n">
-        <v>2855.6</v>
+        <v>3793.8</v>
       </c>
       <c r="F1338" t="n">
-        <v>13566.7</v>
+        <v>14504.9</v>
       </c>
       <c r="G1338" t="n">
         <v>5</v>
@@ -44611,13 +44611,13 @@
         </is>
       </c>
       <c r="D1339" t="n">
-        <v>266.1</v>
+        <v>354.8</v>
       </c>
       <c r="E1339" t="n">
-        <v>3185.3</v>
+        <v>4236.4</v>
       </c>
       <c r="F1339" t="n">
-        <v>13876.3</v>
+        <v>14927.4</v>
       </c>
       <c r="G1339" t="n">
         <v>1</v>
@@ -44644,13 +44644,13 @@
         </is>
       </c>
       <c r="D1340" t="n">
-        <v>230.4</v>
+        <v>307.2</v>
       </c>
       <c r="E1340" t="n">
-        <v>3021.8</v>
+        <v>4005.4</v>
       </c>
       <c r="F1340" t="n">
-        <v>12886.9</v>
+        <v>13870.5</v>
       </c>
       <c r="G1340" t="n">
         <v>3</v>
@@ -44677,13 +44677,13 @@
         </is>
       </c>
       <c r="D1341" t="n">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="E1341" t="n">
-        <v>2913.4</v>
+        <v>3870.2</v>
       </c>
       <c r="F1341" t="n">
-        <v>12578</v>
+        <v>13534.8</v>
       </c>
       <c r="G1341" t="n">
         <v>8</v>
@@ -44710,13 +44710,13 @@
         </is>
       </c>
       <c r="D1342" t="n">
-        <v>243.6</v>
+        <v>324.8</v>
       </c>
       <c r="E1342" t="n">
-        <v>3204.1</v>
+        <v>4245.8</v>
       </c>
       <c r="F1342" t="n">
-        <v>14138.9</v>
+        <v>15180.6</v>
       </c>
       <c r="G1342" t="n">
         <v>2</v>
@@ -44743,13 +44743,13 @@
         </is>
       </c>
       <c r="D1343" t="n">
-        <v>191.1</v>
+        <v>254.8</v>
       </c>
       <c r="E1343" t="n">
-        <v>2562.1</v>
+        <v>3397.8</v>
       </c>
       <c r="F1343" t="n">
-        <v>11396</v>
+        <v>12231.7</v>
       </c>
       <c r="G1343" t="n">
         <v>6</v>
@@ -44776,13 +44776,13 @@
         </is>
       </c>
       <c r="D1344" t="n">
-        <v>203.1</v>
+        <v>270.8</v>
       </c>
       <c r="E1344" t="n">
-        <v>3058.8</v>
+        <v>4061.4</v>
       </c>
       <c r="F1344" t="n">
-        <v>12662.9</v>
+        <v>13665.5</v>
       </c>
       <c r="G1344" t="n">
         <v>4</v>
@@ -44809,13 +44809,13 @@
         </is>
       </c>
       <c r="D1345" t="n">
-        <v>180.6</v>
+        <v>240.8</v>
       </c>
       <c r="E1345" t="n">
-        <v>2991.9</v>
+        <v>3966.2</v>
       </c>
       <c r="F1345" t="n">
-        <v>10526.9</v>
+        <v>11501.2</v>
       </c>
       <c r="G1345" t="n">
         <v>7</v>
@@ -44842,13 +44842,13 @@
         </is>
       </c>
       <c r="D1346" t="n">
-        <v>264.3</v>
+        <v>352.4</v>
       </c>
       <c r="E1346" t="n">
-        <v>3119.9</v>
+        <v>4146.2</v>
       </c>
       <c r="F1346" t="n">
-        <v>13831</v>
+        <v>14857.3</v>
       </c>
       <c r="G1346" t="n">
         <v>3</v>
@@ -44875,13 +44875,13 @@
         </is>
       </c>
       <c r="D1347" t="n">
-        <v>179.7</v>
+        <v>239.6</v>
       </c>
       <c r="E1347" t="n">
-        <v>3365</v>
+        <v>4476</v>
       </c>
       <c r="F1347" t="n">
-        <v>14056</v>
+        <v>15167</v>
       </c>
       <c r="G1347" t="n">
         <v>6</v>
@@ -44908,13 +44908,13 @@
         </is>
       </c>
       <c r="D1348" t="n">
-        <v>210.6</v>
+        <v>280.8</v>
       </c>
       <c r="E1348" t="n">
-        <v>3232.4</v>
+        <v>4286.2</v>
       </c>
       <c r="F1348" t="n">
-        <v>13097.5</v>
+        <v>14151.3</v>
       </c>
       <c r="G1348" t="n">
         <v>4</v>
@@ -44944,10 +44944,10 @@
         <v>0</v>
       </c>
       <c r="E1349" t="n">
-        <v>2913.4</v>
+        <v>3870.2</v>
       </c>
       <c r="F1349" t="n">
-        <v>12578</v>
+        <v>13534.8</v>
       </c>
       <c r="G1349" t="n">
         <v>8</v>
@@ -44974,13 +44974,13 @@
         </is>
       </c>
       <c r="D1350" t="n">
-        <v>282</v>
+        <v>376</v>
       </c>
       <c r="E1350" t="n">
-        <v>3486.1</v>
+        <v>4621.8</v>
       </c>
       <c r="F1350" t="n">
-        <v>14420.9</v>
+        <v>15556.6</v>
       </c>
       <c r="G1350" t="n">
         <v>1</v>
@@ -45007,13 +45007,13 @@
         </is>
       </c>
       <c r="D1351" t="n">
-        <v>184.8</v>
+        <v>246.4</v>
       </c>
       <c r="E1351" t="n">
-        <v>2746.9</v>
+        <v>3644.2</v>
       </c>
       <c r="F1351" t="n">
-        <v>11580.8</v>
+        <v>12478.1</v>
       </c>
       <c r="G1351" t="n">
         <v>5</v>
@@ -45040,13 +45040,13 @@
         </is>
       </c>
       <c r="D1352" t="n">
-        <v>175.8</v>
+        <v>234.4</v>
       </c>
       <c r="E1352" t="n">
-        <v>3234.6</v>
+        <v>4295.8</v>
       </c>
       <c r="F1352" t="n">
-        <v>12838.7</v>
+        <v>13899.9</v>
       </c>
       <c r="G1352" t="n">
         <v>7</v>
@@ -45073,13 +45073,13 @@
         </is>
       </c>
       <c r="D1353" t="n">
-        <v>268.5</v>
+        <v>358</v>
       </c>
       <c r="E1353" t="n">
-        <v>3260.4</v>
+        <v>4324.2</v>
       </c>
       <c r="F1353" t="n">
-        <v>10795.4</v>
+        <v>11859.2</v>
       </c>
       <c r="G1353" t="n">
         <v>2</v>
@@ -45106,13 +45106,13 @@
         </is>
       </c>
       <c r="D1354" t="n">
-        <v>200.1</v>
+        <v>266.8</v>
       </c>
       <c r="E1354" t="n">
-        <v>3320</v>
+        <v>4413</v>
       </c>
       <c r="F1354" t="n">
-        <v>14031.1</v>
+        <v>15124.1</v>
       </c>
       <c r="G1354" t="n">
         <v>4</v>
@@ -45139,13 +45139,13 @@
         </is>
       </c>
       <c r="D1355" t="n">
-        <v>107.4</v>
+        <v>143.2</v>
       </c>
       <c r="E1355" t="n">
-        <v>3472.4</v>
+        <v>4619.2</v>
       </c>
       <c r="F1355" t="n">
-        <v>14163.4</v>
+        <v>15310.2</v>
       </c>
       <c r="G1355" t="n">
         <v>8</v>
@@ -45172,13 +45172,13 @@
         </is>
       </c>
       <c r="D1356" t="n">
-        <v>177.6</v>
+        <v>236.8</v>
       </c>
       <c r="E1356" t="n">
-        <v>3410</v>
+        <v>4523</v>
       </c>
       <c r="F1356" t="n">
-        <v>13275.1</v>
+        <v>14388.1</v>
       </c>
       <c r="G1356" t="n">
         <v>6</v>
@@ -45205,13 +45205,13 @@
         </is>
       </c>
       <c r="D1357" t="n">
-        <v>246.6</v>
+        <v>328.8</v>
       </c>
       <c r="E1357" t="n">
-        <v>3160</v>
+        <v>4199</v>
       </c>
       <c r="F1357" t="n">
-        <v>12824.6</v>
+        <v>13863.6</v>
       </c>
       <c r="G1357" t="n">
         <v>2</v>
@@ -45238,13 +45238,13 @@
         </is>
       </c>
       <c r="D1358" t="n">
-        <v>189</v>
+        <v>252</v>
       </c>
       <c r="E1358" t="n">
-        <v>3675.1</v>
+        <v>4873.8</v>
       </c>
       <c r="F1358" t="n">
-        <v>14609.9</v>
+        <v>15808.6</v>
       </c>
       <c r="G1358" t="n">
         <v>5</v>
@@ -45271,13 +45271,13 @@
         </is>
       </c>
       <c r="D1359" t="n">
-        <v>169.8</v>
+        <v>226.4</v>
       </c>
       <c r="E1359" t="n">
-        <v>2916.7</v>
+        <v>3870.6</v>
       </c>
       <c r="F1359" t="n">
-        <v>11750.6</v>
+        <v>12704.5</v>
       </c>
       <c r="G1359" t="n">
         <v>7</v>
@@ -45304,13 +45304,13 @@
         </is>
       </c>
       <c r="D1360" t="n">
-        <v>235.8</v>
+        <v>314.4</v>
       </c>
       <c r="E1360" t="n">
-        <v>3470.4</v>
+        <v>4610.2</v>
       </c>
       <c r="F1360" t="n">
-        <v>13074.5</v>
+        <v>14214.3</v>
       </c>
       <c r="G1360" t="n">
         <v>3</v>
@@ -45337,13 +45337,13 @@
         </is>
       </c>
       <c r="D1361" t="n">
-        <v>261.9</v>
+        <v>349.2</v>
       </c>
       <c r="E1361" t="n">
-        <v>3522.3</v>
+        <v>4673.4</v>
       </c>
       <c r="F1361" t="n">
-        <v>11057.3</v>
+        <v>12208.4</v>
       </c>
       <c r="G1361" t="n">
         <v>1</v>
@@ -45370,13 +45370,13 @@
         </is>
       </c>
       <c r="D1362" t="n">
-        <v>212.4</v>
+        <v>283.2</v>
       </c>
       <c r="E1362" t="n">
-        <v>3532.4</v>
+        <v>4696.2</v>
       </c>
       <c r="F1362" t="n">
-        <v>14243.5</v>
+        <v>15407.3</v>
       </c>
       <c r="G1362" t="n">
         <v>4</v>
@@ -45403,13 +45403,13 @@
         </is>
       </c>
       <c r="D1363" t="n">
-        <v>229.5</v>
+        <v>306</v>
       </c>
       <c r="E1363" t="n">
-        <v>3701.9</v>
+        <v>4925.2</v>
       </c>
       <c r="F1363" t="n">
-        <v>14392.9</v>
+        <v>15616.2</v>
       </c>
       <c r="G1363" t="n">
         <v>2</v>
@@ -45436,13 +45436,13 @@
         </is>
       </c>
       <c r="D1364" t="n">
-        <v>225.6</v>
+        <v>300.8</v>
       </c>
       <c r="E1364" t="n">
-        <v>3635.6</v>
+        <v>4823.8</v>
       </c>
       <c r="F1364" t="n">
-        <v>13500.7</v>
+        <v>14688.9</v>
       </c>
       <c r="G1364" t="n">
         <v>3</v>
@@ -45469,13 +45469,13 @@
         </is>
       </c>
       <c r="D1365" t="n">
-        <v>140.1</v>
+        <v>186.8</v>
       </c>
       <c r="E1365" t="n">
-        <v>3300.1</v>
+        <v>4385.8</v>
       </c>
       <c r="F1365" t="n">
-        <v>12964.7</v>
+        <v>14050.4</v>
       </c>
       <c r="G1365" t="n">
         <v>8</v>
@@ -45502,13 +45502,13 @@
         </is>
       </c>
       <c r="D1366" t="n">
-        <v>238.2</v>
+        <v>317.6</v>
       </c>
       <c r="E1366" t="n">
-        <v>3913.3</v>
+        <v>5191.4</v>
       </c>
       <c r="F1366" t="n">
-        <v>14848.1</v>
+        <v>16126.2</v>
       </c>
       <c r="G1366" t="n">
         <v>1</v>
@@ -45535,13 +45535,13 @@
         </is>
       </c>
       <c r="D1367" t="n">
-        <v>169.8</v>
+        <v>226.4</v>
       </c>
       <c r="E1367" t="n">
-        <v>3086.5</v>
+        <v>4097</v>
       </c>
       <c r="F1367" t="n">
-        <v>11920.4</v>
+        <v>12930.9</v>
       </c>
       <c r="G1367" t="n">
         <v>6</v>
@@ -45568,13 +45568,13 @@
         </is>
       </c>
       <c r="D1368" t="n">
-        <v>195.6</v>
+        <v>260.8</v>
       </c>
       <c r="E1368" t="n">
-        <v>3666</v>
+        <v>4871</v>
       </c>
       <c r="F1368" t="n">
-        <v>13270.1</v>
+        <v>14475.1</v>
       </c>
       <c r="G1368" t="n">
         <v>5</v>
@@ -45601,13 +45601,13 @@
         </is>
       </c>
       <c r="D1369" t="n">
-        <v>164.4</v>
+        <v>219.2</v>
       </c>
       <c r="E1369" t="n">
-        <v>3686.7</v>
+        <v>4892.599999999999</v>
       </c>
       <c r="F1369" t="n">
-        <v>11221.7</v>
+        <v>12427.6</v>
       </c>
       <c r="G1369" t="n">
         <v>7</v>
@@ -45634,13 +45634,13 @@
         </is>
       </c>
       <c r="D1370" t="n">
-        <v>281.4</v>
+        <v>375.2</v>
       </c>
       <c r="E1370" t="n">
-        <v>3813.8</v>
+        <v>5071.4</v>
       </c>
       <c r="F1370" t="n">
-        <v>14524.9</v>
+        <v>15782.5</v>
       </c>
       <c r="G1370" t="n">
         <v>2</v>
@@ -45667,13 +45667,13 @@
         </is>
       </c>
       <c r="D1371" t="n">
-        <v>195.6</v>
+        <v>260.8</v>
       </c>
       <c r="E1371" t="n">
-        <v>3897.5</v>
+        <v>5186</v>
       </c>
       <c r="F1371" t="n">
-        <v>14588.5</v>
+        <v>15877</v>
       </c>
       <c r="G1371" t="n">
         <v>7</v>
@@ -45700,13 +45700,13 @@
         </is>
       </c>
       <c r="D1372" t="n">
-        <v>292.8</v>
+        <v>390.4</v>
       </c>
       <c r="E1372" t="n">
-        <v>3928.4</v>
+        <v>5214.2</v>
       </c>
       <c r="F1372" t="n">
-        <v>13793.5</v>
+        <v>15079.3</v>
       </c>
       <c r="G1372" t="n">
         <v>1</v>
@@ -45733,13 +45733,13 @@
         </is>
       </c>
       <c r="D1373" t="n">
-        <v>189.9</v>
+        <v>253.2</v>
       </c>
       <c r="E1373" t="n">
-        <v>3490</v>
+        <v>4639</v>
       </c>
       <c r="F1373" t="n">
-        <v>13154.6</v>
+        <v>14303.6</v>
       </c>
       <c r="G1373" t="n">
         <v>8</v>
@@ -45766,13 +45766,13 @@
         </is>
       </c>
       <c r="D1374" t="n">
-        <v>237.9</v>
+        <v>317.2</v>
       </c>
       <c r="E1374" t="n">
-        <v>4151.2</v>
+        <v>5508.6</v>
       </c>
       <c r="F1374" t="n">
-        <v>15086</v>
+        <v>16443.4</v>
       </c>
       <c r="G1374" t="n">
         <v>5</v>
@@ -45799,13 +45799,13 @@
         </is>
       </c>
       <c r="D1375" t="n">
-        <v>245.1</v>
+        <v>326.8</v>
       </c>
       <c r="E1375" t="n">
-        <v>3331.6</v>
+        <v>4423.8</v>
       </c>
       <c r="F1375" t="n">
-        <v>12165.5</v>
+        <v>13257.7</v>
       </c>
       <c r="G1375" t="n">
         <v>4</v>
@@ -45832,13 +45832,13 @@
         </is>
       </c>
       <c r="D1376" t="n">
-        <v>202.2</v>
+        <v>269.6</v>
       </c>
       <c r="E1376" t="n">
-        <v>3868.2</v>
+        <v>5140.6</v>
       </c>
       <c r="F1376" t="n">
-        <v>13472.3</v>
+        <v>14744.7</v>
       </c>
       <c r="G1376" t="n">
         <v>6</v>
@@ -45865,13 +45865,13 @@
         </is>
       </c>
       <c r="D1377" t="n">
-        <v>247.8</v>
+        <v>330.4</v>
       </c>
       <c r="E1377" t="n">
-        <v>3934.5</v>
+        <v>5223</v>
       </c>
       <c r="F1377" t="n">
-        <v>11469.5</v>
+        <v>12758</v>
       </c>
       <c r="G1377" t="n">
         <v>3</v>
@@ -45898,13 +45898,13 @@
         </is>
       </c>
       <c r="D1378" t="n">
-        <v>301.5</v>
+        <v>402</v>
       </c>
       <c r="E1378" t="n">
-        <v>4115.3</v>
+        <v>5473.4</v>
       </c>
       <c r="F1378" t="n">
-        <v>14826.4</v>
+        <v>16184.5</v>
       </c>
       <c r="G1378" t="n">
         <v>1</v>
@@ -45931,13 +45931,13 @@
         </is>
       </c>
       <c r="D1379" t="n">
-        <v>240.9</v>
+        <v>321.2</v>
       </c>
       <c r="E1379" t="n">
-        <v>4138.400000000001</v>
+        <v>5507.2</v>
       </c>
       <c r="F1379" t="n">
-        <v>14829.4</v>
+        <v>16198.2</v>
       </c>
       <c r="G1379" t="n">
         <v>2</v>
@@ -45964,13 +45964,13 @@
         </is>
       </c>
       <c r="D1380" t="n">
-        <v>180.9</v>
+        <v>241.2</v>
       </c>
       <c r="E1380" t="n">
-        <v>4109.3</v>
+        <v>5455.4</v>
       </c>
       <c r="F1380" t="n">
-        <v>13974.4</v>
+        <v>15320.5</v>
       </c>
       <c r="G1380" t="n">
         <v>6</v>
@@ -45997,13 +45997,13 @@
         </is>
       </c>
       <c r="D1381" t="n">
-        <v>202.8</v>
+        <v>270.4</v>
       </c>
       <c r="E1381" t="n">
-        <v>3692.8</v>
+        <v>4909.4</v>
       </c>
       <c r="F1381" t="n">
-        <v>13357.4</v>
+        <v>14574</v>
       </c>
       <c r="G1381" t="n">
         <v>4</v>
@@ -46030,13 +46030,13 @@
         </is>
       </c>
       <c r="D1382" t="n">
-        <v>210.6</v>
+        <v>280.8</v>
       </c>
       <c r="E1382" t="n">
-        <v>4361.8</v>
+        <v>5789.4</v>
       </c>
       <c r="F1382" t="n">
-        <v>15296.6</v>
+        <v>16724.2</v>
       </c>
       <c r="G1382" t="n">
         <v>3</v>
@@ -46063,13 +46063,13 @@
         </is>
       </c>
       <c r="D1383" t="n">
-        <v>183.6</v>
+        <v>244.8</v>
       </c>
       <c r="E1383" t="n">
-        <v>3515.2</v>
+        <v>4668.6</v>
       </c>
       <c r="F1383" t="n">
-        <v>12349.1</v>
+        <v>13502.5</v>
       </c>
       <c r="G1383" t="n">
         <v>5</v>
@@ -46096,13 +46096,13 @@
         </is>
       </c>
       <c r="D1384" t="n">
-        <v>152.4</v>
+        <v>203.2</v>
       </c>
       <c r="E1384" t="n">
-        <v>4020.6</v>
+        <v>5343.8</v>
       </c>
       <c r="F1384" t="n">
-        <v>13624.7</v>
+        <v>14947.9</v>
       </c>
       <c r="G1384" t="n">
         <v>8</v>
@@ -46129,13 +46129,13 @@
         </is>
       </c>
       <c r="D1385" t="n">
-        <v>176.7</v>
+        <v>235.6</v>
       </c>
       <c r="E1385" t="n">
-        <v>4111.2</v>
+        <v>5458.599999999999</v>
       </c>
       <c r="F1385" t="n">
-        <v>11646.2</v>
+        <v>12993.6</v>
       </c>
       <c r="G1385" t="n">
         <v>7</v>
@@ -46162,13 +46162,13 @@
         </is>
       </c>
       <c r="D1386" t="n">
-        <v>276</v>
+        <v>368</v>
       </c>
       <c r="E1386" t="n">
-        <v>4391.3</v>
+        <v>5841.4</v>
       </c>
       <c r="F1386" t="n">
-        <v>15102.4</v>
+        <v>16552.5</v>
       </c>
       <c r="G1386" t="n">
         <v>2</v>
@@ -46195,13 +46195,13 @@
         </is>
       </c>
       <c r="D1387" t="n">
-        <v>231.6</v>
+        <v>308.8</v>
       </c>
       <c r="E1387" t="n">
-        <v>4370</v>
+        <v>5816</v>
       </c>
       <c r="F1387" t="n">
-        <v>15061</v>
+        <v>16507</v>
       </c>
       <c r="G1387" t="n">
         <v>4</v>
@@ -46228,13 +46228,13 @@
         </is>
       </c>
       <c r="D1388" t="n">
-        <v>240.9</v>
+        <v>321.2</v>
       </c>
       <c r="E1388" t="n">
-        <v>4350.2</v>
+        <v>5776.6</v>
       </c>
       <c r="F1388" t="n">
-        <v>14215.3</v>
+        <v>15641.7</v>
       </c>
       <c r="G1388" t="n">
         <v>3</v>
@@ -46261,13 +46261,13 @@
         </is>
       </c>
       <c r="D1389" t="n">
-        <v>151.8</v>
+        <v>202.4</v>
       </c>
       <c r="E1389" t="n">
-        <v>3844.6</v>
+        <v>5111.8</v>
       </c>
       <c r="F1389" t="n">
-        <v>13509.2</v>
+        <v>14776.4</v>
       </c>
       <c r="G1389" t="n">
         <v>7</v>
@@ -46294,13 +46294,13 @@
         </is>
       </c>
       <c r="D1390" t="n">
-        <v>230.1</v>
+        <v>306.8</v>
       </c>
       <c r="E1390" t="n">
-        <v>4591.9</v>
+        <v>6096.2</v>
       </c>
       <c r="F1390" t="n">
-        <v>15526.7</v>
+        <v>17031</v>
       </c>
       <c r="G1390" t="n">
         <v>5</v>
@@ -46327,13 +46327,13 @@
         </is>
       </c>
       <c r="D1391" t="n">
-        <v>146.1</v>
+        <v>194.8</v>
       </c>
       <c r="E1391" t="n">
-        <v>3661.3</v>
+        <v>4863.4</v>
       </c>
       <c r="F1391" t="n">
-        <v>12495.2</v>
+        <v>13697.3</v>
       </c>
       <c r="G1391" t="n">
         <v>8</v>
@@ -46360,13 +46360,13 @@
         </is>
       </c>
       <c r="D1392" t="n">
-        <v>277.5</v>
+        <v>370</v>
       </c>
       <c r="E1392" t="n">
-        <v>4298.1</v>
+        <v>5713.8</v>
       </c>
       <c r="F1392" t="n">
-        <v>13902.2</v>
+        <v>15317.9</v>
       </c>
       <c r="G1392" t="n">
         <v>1</v>
@@ -46393,13 +46393,13 @@
         </is>
       </c>
       <c r="D1393" t="n">
-        <v>219.3</v>
+        <v>292.4</v>
       </c>
       <c r="E1393" t="n">
-        <v>4330.5</v>
+        <v>5751</v>
       </c>
       <c r="F1393" t="n">
-        <v>11865.5</v>
+        <v>13286</v>
       </c>
       <c r="G1393" t="n">
         <v>6</v>
@@ -46426,13 +46426,13 @@
         </is>
       </c>
       <c r="D1394" t="n">
-        <v>226.8</v>
+        <v>302.4</v>
       </c>
       <c r="E1394" t="n">
-        <v>4618.1</v>
+        <v>6143.8</v>
       </c>
       <c r="F1394" t="n">
-        <v>15329.2</v>
+        <v>16854.9</v>
       </c>
       <c r="G1394" t="n">
         <v>3</v>
@@ -46459,13 +46459,13 @@
         </is>
       </c>
       <c r="D1395" t="n">
-        <v>252.3</v>
+        <v>336.4</v>
       </c>
       <c r="E1395" t="n">
-        <v>4622.3</v>
+        <v>6152.4</v>
       </c>
       <c r="F1395" t="n">
-        <v>15313.3</v>
+        <v>16843.4</v>
       </c>
       <c r="G1395" t="n">
         <v>1</v>
@@ -46492,13 +46492,13 @@
         </is>
       </c>
       <c r="D1396" t="n">
-        <v>177.9</v>
+        <v>237.2</v>
       </c>
       <c r="E1396" t="n">
-        <v>4528.1</v>
+        <v>6013.8</v>
       </c>
       <c r="F1396" t="n">
-        <v>14393.2</v>
+        <v>15878.9</v>
       </c>
       <c r="G1396" t="n">
         <v>8</v>
@@ -46525,13 +46525,13 @@
         </is>
       </c>
       <c r="D1397" t="n">
-        <v>214.5</v>
+        <v>286</v>
       </c>
       <c r="E1397" t="n">
-        <v>4059.1</v>
+        <v>5397.8</v>
       </c>
       <c r="F1397" t="n">
-        <v>13723.7</v>
+        <v>15062.4</v>
       </c>
       <c r="G1397" t="n">
         <v>6</v>
@@ -46558,13 +46558,13 @@
         </is>
       </c>
       <c r="D1398" t="n">
-        <v>226.2</v>
+        <v>301.6</v>
       </c>
       <c r="E1398" t="n">
-        <v>4818.1</v>
+        <v>6397.8</v>
       </c>
       <c r="F1398" t="n">
-        <v>15752.9</v>
+        <v>17332.6</v>
       </c>
       <c r="G1398" t="n">
         <v>4</v>
@@ -46591,13 +46591,13 @@
         </is>
       </c>
       <c r="D1399" t="n">
-        <v>188.1</v>
+        <v>250.8</v>
       </c>
       <c r="E1399" t="n">
-        <v>3849.4</v>
+        <v>5114.2</v>
       </c>
       <c r="F1399" t="n">
-        <v>12683.3</v>
+        <v>13948.1</v>
       </c>
       <c r="G1399" t="n">
         <v>7</v>
@@ -46624,13 +46624,13 @@
         </is>
       </c>
       <c r="D1400" t="n">
-        <v>216</v>
+        <v>288</v>
       </c>
       <c r="E1400" t="n">
-        <v>4514.1</v>
+        <v>6001.8</v>
       </c>
       <c r="F1400" t="n">
-        <v>14118.2</v>
+        <v>15605.9</v>
       </c>
       <c r="G1400" t="n">
         <v>5</v>
@@ -46657,13 +46657,13 @@
         </is>
       </c>
       <c r="D1401" t="n">
-        <v>237.3</v>
+        <v>316.4</v>
       </c>
       <c r="E1401" t="n">
-        <v>4567.8</v>
+        <v>6067.4</v>
       </c>
       <c r="F1401" t="n">
-        <v>12102.8</v>
+        <v>13602.4</v>
       </c>
       <c r="G1401" t="n">
         <v>2</v>
@@ -46690,13 +46690,13 @@
         </is>
       </c>
       <c r="D1402" t="n">
-        <v>219.6</v>
+        <v>292.8</v>
       </c>
       <c r="E1402" t="n">
-        <v>4837.7</v>
+        <v>6436.6</v>
       </c>
       <c r="F1402" t="n">
-        <v>15548.8</v>
+        <v>17147.7</v>
       </c>
       <c r="G1402" t="n">
         <v>2</v>
@@ -46723,13 +46723,13 @@
         </is>
       </c>
       <c r="D1403" t="n">
-        <v>188.1</v>
+        <v>250.8</v>
       </c>
       <c r="E1403" t="n">
-        <v>4810.400000000001</v>
+        <v>6403.2</v>
       </c>
       <c r="F1403" t="n">
-        <v>15501.4</v>
+        <v>17094.2</v>
       </c>
       <c r="G1403" t="n">
         <v>5</v>
@@ -46756,13 +46756,13 @@
         </is>
       </c>
       <c r="D1404" t="n">
-        <v>147.6</v>
+        <v>196.8</v>
       </c>
       <c r="E1404" t="n">
-        <v>4675.7</v>
+        <v>6210.6</v>
       </c>
       <c r="F1404" t="n">
-        <v>14540.8</v>
+        <v>16075.7</v>
       </c>
       <c r="G1404" t="n">
         <v>6</v>
@@ -46789,13 +46789,13 @@
         </is>
       </c>
       <c r="D1405" t="n">
-        <v>131.7</v>
+        <v>175.6</v>
       </c>
       <c r="E1405" t="n">
-        <v>4190.8</v>
+        <v>5573.4</v>
       </c>
       <c r="F1405" t="n">
-        <v>13855.4</v>
+        <v>15238</v>
       </c>
       <c r="G1405" t="n">
         <v>7</v>
@@ -46822,13 +46822,13 @@
         </is>
       </c>
       <c r="D1406" t="n">
-        <v>213.6</v>
+        <v>284.8</v>
       </c>
       <c r="E1406" t="n">
-        <v>5031.7</v>
+        <v>6682.6</v>
       </c>
       <c r="F1406" t="n">
-        <v>15966.5</v>
+        <v>17617.4</v>
       </c>
       <c r="G1406" t="n">
         <v>3</v>
@@ -46855,13 +46855,13 @@
         </is>
       </c>
       <c r="D1407" t="n">
-        <v>192.3</v>
+        <v>256.4</v>
       </c>
       <c r="E1407" t="n">
-        <v>4041.7</v>
+        <v>5370.6</v>
       </c>
       <c r="F1407" t="n">
-        <v>12875.6</v>
+        <v>14204.5</v>
       </c>
       <c r="G1407" t="n">
         <v>4</v>
@@ -46888,13 +46888,13 @@
         </is>
       </c>
       <c r="D1408" t="n">
-        <v>128.7</v>
+        <v>171.6</v>
       </c>
       <c r="E1408" t="n">
-        <v>4642.8</v>
+        <v>6173.400000000001</v>
       </c>
       <c r="F1408" t="n">
-        <v>14246.9</v>
+        <v>15777.5</v>
       </c>
       <c r="G1408" t="n">
         <v>8</v>
@@ -46921,13 +46921,13 @@
         </is>
       </c>
       <c r="D1409" t="n">
-        <v>221.4</v>
+        <v>295.2</v>
       </c>
       <c r="E1409" t="n">
-        <v>4789.2</v>
+        <v>6362.599999999999</v>
       </c>
       <c r="F1409" t="n">
-        <v>12324.2</v>
+        <v>13897.6</v>
       </c>
       <c r="G1409" t="n">
         <v>1</v>
@@ -46954,13 +46954,13 @@
         </is>
       </c>
       <c r="D1410" t="n">
-        <v>237.9</v>
+        <v>317.2</v>
       </c>
       <c r="E1410" t="n">
-        <v>5075.6</v>
+        <v>6753.8</v>
       </c>
       <c r="F1410" t="n">
-        <v>15786.7</v>
+        <v>17464.9</v>
       </c>
       <c r="G1410" t="n">
         <v>1</v>
@@ -46987,13 +46987,13 @@
         </is>
       </c>
       <c r="D1411" t="n">
-        <v>186.9</v>
+        <v>249.2</v>
       </c>
       <c r="E1411" t="n">
-        <v>4997.3</v>
+        <v>6652.4</v>
       </c>
       <c r="F1411" t="n">
-        <v>15688.3</v>
+        <v>17343.4</v>
       </c>
       <c r="G1411" t="n">
         <v>4</v>
@@ -47020,13 +47020,13 @@
         </is>
       </c>
       <c r="D1412" t="n">
-        <v>151.2</v>
+        <v>201.6</v>
       </c>
       <c r="E1412" t="n">
-        <v>4826.9</v>
+        <v>6412.2</v>
       </c>
       <c r="F1412" t="n">
-        <v>14692</v>
+        <v>16277.3</v>
       </c>
       <c r="G1412" t="n">
         <v>7</v>
@@ -47053,13 +47053,13 @@
         </is>
       </c>
       <c r="D1413" t="n">
-        <v>146.4</v>
+        <v>195.2</v>
       </c>
       <c r="E1413" t="n">
-        <v>4337.2</v>
+        <v>5768.6</v>
       </c>
       <c r="F1413" t="n">
-        <v>14001.8</v>
+        <v>15433.2</v>
       </c>
       <c r="G1413" t="n">
         <v>8</v>
@@ -47086,13 +47086,13 @@
         </is>
       </c>
       <c r="D1414" t="n">
-        <v>225</v>
+        <v>300</v>
       </c>
       <c r="E1414" t="n">
-        <v>5256.7</v>
+        <v>6982.6</v>
       </c>
       <c r="F1414" t="n">
-        <v>16191.5</v>
+        <v>17917.4</v>
       </c>
       <c r="G1414" t="n">
         <v>2</v>
@@ -47119,13 +47119,13 @@
         </is>
       </c>
       <c r="D1415" t="n">
-        <v>193.5</v>
+        <v>258</v>
       </c>
       <c r="E1415" t="n">
-        <v>4235.2</v>
+        <v>5628.6</v>
       </c>
       <c r="F1415" t="n">
-        <v>13069.1</v>
+        <v>14462.5</v>
       </c>
       <c r="G1415" t="n">
         <v>3</v>
@@ -47152,19 +47152,19 @@
         </is>
       </c>
       <c r="D1416" t="n">
-        <v>179.1</v>
+        <v>238.8</v>
       </c>
       <c r="E1416" t="n">
-        <v>4821.9</v>
+        <v>6412.2</v>
       </c>
       <c r="F1416" t="n">
-        <v>14426</v>
+        <v>16016.3</v>
       </c>
       <c r="G1416" t="n">
         <v>5</v>
       </c>
       <c r="H1416" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I1416" t="n">
         <v>5</v>
@@ -47185,13 +47185,13 @@
         </is>
       </c>
       <c r="D1417" t="n">
-        <v>173.1</v>
+        <v>230.8</v>
       </c>
       <c r="E1417" t="n">
-        <v>4962.3</v>
+        <v>6593.4</v>
       </c>
       <c r="F1417" t="n">
-        <v>12497.3</v>
+        <v>14128.4</v>
       </c>
       <c r="G1417" t="n">
         <v>6</v>
@@ -47218,13 +47218,13 @@
         </is>
       </c>
       <c r="D1418" t="n">
-        <v>258.9</v>
+        <v>345.2</v>
       </c>
       <c r="E1418" t="n">
-        <v>5334.5</v>
+        <v>7099</v>
       </c>
       <c r="F1418" t="n">
-        <v>16045.6</v>
+        <v>17810.1</v>
       </c>
       <c r="G1418" t="n">
         <v>2</v>
@@ -47251,13 +47251,13 @@
         </is>
       </c>
       <c r="D1419" t="n">
-        <v>226.8</v>
+        <v>302.4</v>
       </c>
       <c r="E1419" t="n">
-        <v>5224.1</v>
+        <v>6954.8</v>
       </c>
       <c r="F1419" t="n">
-        <v>15915.1</v>
+        <v>17645.8</v>
       </c>
       <c r="G1419" t="n">
         <v>3</v>
@@ -47284,13 +47284,13 @@
         </is>
       </c>
       <c r="D1420" t="n">
-        <v>152.7</v>
+        <v>203.6</v>
       </c>
       <c r="E1420" t="n">
-        <v>4979.6</v>
+        <v>6615.8</v>
       </c>
       <c r="F1420" t="n">
-        <v>14844.7</v>
+        <v>16480.9</v>
       </c>
       <c r="G1420" t="n">
         <v>8</v>
@@ -47317,13 +47317,13 @@
         </is>
       </c>
       <c r="D1421" t="n">
-        <v>195.9</v>
+        <v>261.2</v>
       </c>
       <c r="E1421" t="n">
-        <v>4533.1</v>
+        <v>6029.8</v>
       </c>
       <c r="F1421" t="n">
-        <v>14197.7</v>
+        <v>15694.4</v>
       </c>
       <c r="G1421" t="n">
         <v>4</v>
@@ -47350,13 +47350,13 @@
         </is>
       </c>
       <c r="D1422" t="n">
-        <v>175.2</v>
+        <v>233.6</v>
       </c>
       <c r="E1422" t="n">
-        <v>5431.9</v>
+        <v>7216.2</v>
       </c>
       <c r="F1422" t="n">
-        <v>16366.7</v>
+        <v>18151</v>
       </c>
       <c r="G1422" t="n">
         <v>6</v>
@@ -47383,13 +47383,13 @@
         </is>
       </c>
       <c r="D1423" t="n">
-        <v>175.8</v>
+        <v>234.4</v>
       </c>
       <c r="E1423" t="n">
-        <v>4411</v>
+        <v>5863</v>
       </c>
       <c r="F1423" t="n">
-        <v>13244.9</v>
+        <v>14696.9</v>
       </c>
       <c r="G1423" t="n">
         <v>5</v>
@@ -47416,13 +47416,13 @@
         </is>
       </c>
       <c r="D1424" t="n">
-        <v>165.9</v>
+        <v>221.2</v>
       </c>
       <c r="E1424" t="n">
-        <v>4987.8</v>
+        <v>6633.400000000001</v>
       </c>
       <c r="F1424" t="n">
-        <v>14591.9</v>
+        <v>16237.5</v>
       </c>
       <c r="G1424" t="n">
         <v>7</v>
@@ -47449,13 +47449,13 @@
         </is>
       </c>
       <c r="D1425" t="n">
-        <v>288</v>
+        <v>384</v>
       </c>
       <c r="E1425" t="n">
-        <v>5250.3</v>
+        <v>6977.4</v>
       </c>
       <c r="F1425" t="n">
-        <v>12785.3</v>
+        <v>14512.4</v>
       </c>
       <c r="G1425" t="n">
         <v>1</v>
@@ -47482,13 +47482,13 @@
         </is>
       </c>
       <c r="D1426" t="n">
-        <v>253.5</v>
+        <v>338</v>
       </c>
       <c r="E1426" t="n">
-        <v>5588</v>
+        <v>7437</v>
       </c>
       <c r="F1426" t="n">
-        <v>16299.1</v>
+        <v>18148.1</v>
       </c>
       <c r="G1426" t="n">
         <v>1</v>
@@ -47515,13 +47515,13 @@
         </is>
       </c>
       <c r="D1427" t="n">
-        <v>199.8</v>
+        <v>266.4</v>
       </c>
       <c r="E1427" t="n">
-        <v>5423.900000000001</v>
+        <v>7221.2</v>
       </c>
       <c r="F1427" t="n">
-        <v>16114.9</v>
+        <v>17912.2</v>
       </c>
       <c r="G1427" t="n">
         <v>4</v>
@@ -47548,13 +47548,13 @@
         </is>
       </c>
       <c r="D1428" t="n">
-        <v>180.3</v>
+        <v>240.4</v>
       </c>
       <c r="E1428" t="n">
-        <v>5159.9</v>
+        <v>6856.2</v>
       </c>
       <c r="F1428" t="n">
-        <v>15025</v>
+        <v>16721.3</v>
       </c>
       <c r="G1428" t="n">
         <v>6</v>
@@ -47581,13 +47581,13 @@
         </is>
       </c>
       <c r="D1429" t="n">
-        <v>222.3</v>
+        <v>296.4</v>
       </c>
       <c r="E1429" t="n">
-        <v>4755.4</v>
+        <v>6326.2</v>
       </c>
       <c r="F1429" t="n">
-        <v>14420</v>
+        <v>15990.8</v>
       </c>
       <c r="G1429" t="n">
         <v>3</v>
@@ -47614,13 +47614,13 @@
         </is>
       </c>
       <c r="D1430" t="n">
-        <v>172.2</v>
+        <v>229.6</v>
       </c>
       <c r="E1430" t="n">
-        <v>5604.1</v>
+        <v>7445.8</v>
       </c>
       <c r="F1430" t="n">
-        <v>16538.9</v>
+        <v>18380.6</v>
       </c>
       <c r="G1430" t="n">
         <v>7</v>
@@ -47650,10 +47650,10 @@
         <v>0</v>
       </c>
       <c r="E1431" t="n">
-        <v>4411</v>
+        <v>5863</v>
       </c>
       <c r="F1431" t="n">
-        <v>13244.9</v>
+        <v>14696.9</v>
       </c>
       <c r="G1431" t="n">
         <v>8</v>
@@ -47662,7 +47662,7 @@
         <v>8</v>
       </c>
       <c r="I1431" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1432">
@@ -47680,13 +47680,13 @@
         </is>
       </c>
       <c r="D1432" t="n">
-        <v>197.7</v>
+        <v>263.6</v>
       </c>
       <c r="E1432" t="n">
-        <v>5185.5</v>
+        <v>6897</v>
       </c>
       <c r="F1432" t="n">
-        <v>14789.6</v>
+        <v>16501.1</v>
       </c>
       <c r="G1432" t="n">
         <v>5</v>
@@ -47713,13 +47713,13 @@
         </is>
       </c>
       <c r="D1433" t="n">
-        <v>228</v>
+        <v>304</v>
       </c>
       <c r="E1433" t="n">
-        <v>5478.3</v>
+        <v>7281.4</v>
       </c>
       <c r="F1433" t="n">
-        <v>13013.3</v>
+        <v>14816.4</v>
       </c>
       <c r="G1433" t="n">
         <v>2</v>
@@ -47728,7 +47728,7 @@
         <v>3</v>
       </c>
       <c r="I1433" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1434">
@@ -47746,13 +47746,13 @@
         </is>
       </c>
       <c r="D1434" t="n">
-        <v>219.3</v>
+        <v>292.4</v>
       </c>
       <c r="E1434" t="n">
-        <v>5807.3</v>
+        <v>7729.4</v>
       </c>
       <c r="F1434" t="n">
-        <v>16518.4</v>
+        <v>18440.5</v>
       </c>
       <c r="G1434" t="n">
         <v>6</v>
@@ -47779,13 +47779,13 @@
         </is>
       </c>
       <c r="D1435" t="n">
-        <v>278.7</v>
+        <v>371.6</v>
       </c>
       <c r="E1435" t="n">
-        <v>5702.6</v>
+        <v>7592.8</v>
       </c>
       <c r="F1435" t="n">
-        <v>16393.6</v>
+        <v>18283.8</v>
       </c>
       <c r="G1435" t="n">
         <v>2</v>
@@ -47812,13 +47812,13 @@
         </is>
       </c>
       <c r="D1436" t="n">
-        <v>154.8</v>
+        <v>206.4</v>
       </c>
       <c r="E1436" t="n">
-        <v>5314.7</v>
+        <v>7062.6</v>
       </c>
       <c r="F1436" t="n">
-        <v>15179.8</v>
+        <v>16927.7</v>
       </c>
       <c r="G1436" t="n">
         <v>8</v>
@@ -47845,13 +47845,13 @@
         </is>
       </c>
       <c r="D1437" t="n">
-        <v>186.3</v>
+        <v>248.4</v>
       </c>
       <c r="E1437" t="n">
-        <v>4941.7</v>
+        <v>6574.6</v>
       </c>
       <c r="F1437" t="n">
-        <v>14606.3</v>
+        <v>16239.2</v>
       </c>
       <c r="G1437" t="n">
         <v>7</v>
@@ -47878,13 +47878,13 @@
         </is>
       </c>
       <c r="D1438" t="n">
-        <v>260.1</v>
+        <v>346.8</v>
       </c>
       <c r="E1438" t="n">
-        <v>5864.2</v>
+        <v>7792.6</v>
       </c>
       <c r="F1438" t="n">
-        <v>16799</v>
+        <v>18727.4</v>
       </c>
       <c r="G1438" t="n">
         <v>4</v>
@@ -47911,13 +47911,13 @@
         </is>
       </c>
       <c r="D1439" t="n">
-        <v>264.6</v>
+        <v>352.8</v>
       </c>
       <c r="E1439" t="n">
-        <v>4675.6</v>
+        <v>6215.8</v>
       </c>
       <c r="F1439" t="n">
-        <v>13509.5</v>
+        <v>15049.7</v>
       </c>
       <c r="G1439" t="n">
         <v>3</v>
@@ -47926,7 +47926,7 @@
         <v>8</v>
       </c>
       <c r="I1439" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1440">
@@ -47944,13 +47944,13 @@
         </is>
       </c>
       <c r="D1440" t="n">
-        <v>219.9</v>
+        <v>293.2</v>
       </c>
       <c r="E1440" t="n">
-        <v>5405.4</v>
+        <v>7190.2</v>
       </c>
       <c r="F1440" t="n">
-        <v>15009.5</v>
+        <v>16794.3</v>
       </c>
       <c r="G1440" t="n">
         <v>5</v>
@@ -47977,13 +47977,13 @@
         </is>
       </c>
       <c r="D1441" t="n">
-        <v>302.7</v>
+        <v>403.6</v>
       </c>
       <c r="E1441" t="n">
-        <v>5781</v>
+        <v>7685</v>
       </c>
       <c r="F1441" t="n">
-        <v>13316</v>
+        <v>15220</v>
       </c>
       <c r="G1441" t="n">
         <v>1</v>
@@ -47992,7 +47992,7 @@
         <v>3</v>
       </c>
       <c r="I1441" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1442">
@@ -48010,13 +48010,13 @@
         </is>
       </c>
       <c r="D1442" t="n">
-        <v>247.5</v>
+        <v>330</v>
       </c>
       <c r="E1442" t="n">
-        <v>6054.8</v>
+        <v>8059.4</v>
       </c>
       <c r="F1442" t="n">
-        <v>16765.9</v>
+        <v>18770.5</v>
       </c>
       <c r="G1442" t="n">
         <v>3</v>
@@ -48043,13 +48043,13 @@
         </is>
       </c>
       <c r="D1443" t="n">
-        <v>220.5</v>
+        <v>294</v>
       </c>
       <c r="E1443" t="n">
-        <v>5923.1</v>
+        <v>7886.8</v>
       </c>
       <c r="F1443" t="n">
-        <v>16614.1</v>
+        <v>18577.8</v>
       </c>
       <c r="G1443" t="n">
         <v>4</v>
@@ -48076,13 +48076,13 @@
         </is>
       </c>
       <c r="D1444" t="n">
-        <v>343.5</v>
+        <v>458</v>
       </c>
       <c r="E1444" t="n">
-        <v>5658.2</v>
+        <v>7520.6</v>
       </c>
       <c r="F1444" t="n">
-        <v>15523.3</v>
+        <v>17385.7</v>
       </c>
       <c r="G1444" t="n">
         <v>1</v>
@@ -48109,13 +48109,13 @@
         </is>
       </c>
       <c r="D1445" t="n">
-        <v>257.7</v>
+        <v>343.6</v>
       </c>
       <c r="E1445" t="n">
-        <v>5199.4</v>
+        <v>6918.2</v>
       </c>
       <c r="F1445" t="n">
-        <v>14864</v>
+        <v>16582.8</v>
       </c>
       <c r="G1445" t="n">
         <v>2</v>
@@ -48142,13 +48142,13 @@
         </is>
       </c>
       <c r="D1446" t="n">
-        <v>145.8</v>
+        <v>194.4</v>
       </c>
       <c r="E1446" t="n">
-        <v>6010</v>
+        <v>7987</v>
       </c>
       <c r="F1446" t="n">
-        <v>16944.8</v>
+        <v>18921.8</v>
       </c>
       <c r="G1446" t="n">
         <v>6</v>
@@ -48175,13 +48175,13 @@
         </is>
       </c>
       <c r="D1447" t="n">
-        <v>158.4</v>
+        <v>211.2</v>
       </c>
       <c r="E1447" t="n">
-        <v>4834</v>
+        <v>6427</v>
       </c>
       <c r="F1447" t="n">
-        <v>13667.9</v>
+        <v>15260.9</v>
       </c>
       <c r="G1447" t="n">
         <v>5</v>
@@ -48190,7 +48190,7 @@
         <v>8</v>
       </c>
       <c r="I1447" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1448">
@@ -48208,13 +48208,13 @@
         </is>
       </c>
       <c r="D1448" t="n">
-        <v>143.7</v>
+        <v>191.6</v>
       </c>
       <c r="E1448" t="n">
-        <v>5549.1</v>
+        <v>7381.8</v>
       </c>
       <c r="F1448" t="n">
-        <v>15153.2</v>
+        <v>16985.9</v>
       </c>
       <c r="G1448" t="n">
         <v>7</v>
@@ -48241,13 +48241,13 @@
         </is>
       </c>
       <c r="D1449" t="n">
-        <v>129.9</v>
+        <v>173.2</v>
       </c>
       <c r="E1449" t="n">
-        <v>5910.9</v>
+        <v>7858.2</v>
       </c>
       <c r="F1449" t="n">
-        <v>13445.9</v>
+        <v>15393.2</v>
       </c>
       <c r="G1449" t="n">
         <v>8</v>
@@ -48256,7 +48256,7 @@
         <v>4</v>
       </c>
       <c r="I1449" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1450">
@@ -48274,13 +48274,13 @@
         </is>
       </c>
       <c r="D1450" t="n">
-        <v>199.5</v>
+        <v>266</v>
       </c>
       <c r="E1450" t="n">
-        <v>6254.3</v>
+        <v>8325.4</v>
       </c>
       <c r="F1450" t="n">
-        <v>16965.4</v>
+        <v>19036.5</v>
       </c>
       <c r="G1450" t="n">
         <v>5</v>
@@ -48307,13 +48307,13 @@
         </is>
       </c>
       <c r="D1451" t="n">
-        <v>196.5</v>
+        <v>262</v>
       </c>
       <c r="E1451" t="n">
-        <v>6119.6</v>
+        <v>8148.8</v>
       </c>
       <c r="F1451" t="n">
-        <v>16810.6</v>
+        <v>18839.8</v>
       </c>
       <c r="G1451" t="n">
         <v>7</v>
@@ -48340,13 +48340,13 @@
         </is>
       </c>
       <c r="D1452" t="n">
-        <v>251.7</v>
+        <v>335.6</v>
       </c>
       <c r="E1452" t="n">
-        <v>5909.9</v>
+        <v>7856.2</v>
       </c>
       <c r="F1452" t="n">
-        <v>15775</v>
+        <v>17721.3</v>
       </c>
       <c r="G1452" t="n">
         <v>3</v>
@@ -48373,13 +48373,13 @@
         </is>
       </c>
       <c r="D1453" t="n">
-        <v>199.2</v>
+        <v>265.6</v>
       </c>
       <c r="E1453" t="n">
-        <v>5398.6</v>
+        <v>7183.8</v>
       </c>
       <c r="F1453" t="n">
-        <v>15063.2</v>
+        <v>16848.4</v>
       </c>
       <c r="G1453" t="n">
         <v>6</v>
@@ -48406,13 +48406,13 @@
         </is>
       </c>
       <c r="D1454" t="n">
-        <v>321</v>
+        <v>428</v>
       </c>
       <c r="E1454" t="n">
-        <v>6331</v>
+        <v>8415</v>
       </c>
       <c r="F1454" t="n">
-        <v>17265.8</v>
+        <v>19349.8</v>
       </c>
       <c r="G1454" t="n">
         <v>1</v>
@@ -48439,13 +48439,13 @@
         </is>
       </c>
       <c r="D1455" t="n">
-        <v>139.5</v>
+        <v>186</v>
       </c>
       <c r="E1455" t="n">
-        <v>4973.5</v>
+        <v>6613</v>
       </c>
       <c r="F1455" t="n">
-        <v>13807.4</v>
+        <v>15446.9</v>
       </c>
       <c r="G1455" t="n">
         <v>8</v>
@@ -48454,7 +48454,7 @@
         <v>8</v>
       </c>
       <c r="I1455" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1456">
@@ -48472,13 +48472,13 @@
         </is>
       </c>
       <c r="D1456" t="n">
-        <v>202.2</v>
+        <v>269.6</v>
       </c>
       <c r="E1456" t="n">
-        <v>5751.3</v>
+        <v>7651.400000000001</v>
       </c>
       <c r="F1456" t="n">
-        <v>15355.4</v>
+        <v>17255.5</v>
       </c>
       <c r="G1456" t="n">
         <v>4</v>
@@ -48505,13 +48505,13 @@
         </is>
       </c>
       <c r="D1457" t="n">
-        <v>256.8</v>
+        <v>342.4</v>
       </c>
       <c r="E1457" t="n">
-        <v>6167.7</v>
+        <v>8200.6</v>
       </c>
       <c r="F1457" t="n">
-        <v>13702.7</v>
+        <v>15735.6</v>
       </c>
       <c r="G1457" t="n">
         <v>2</v>
@@ -48520,7 +48520,7 @@
         <v>3</v>
       </c>
       <c r="I1457" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1458">
@@ -48538,13 +48538,13 @@
         </is>
       </c>
       <c r="D1458" t="n">
-        <v>301.8</v>
+        <v>402.4</v>
       </c>
       <c r="E1458" t="n">
-        <v>6556.1</v>
+        <v>8727.799999999999</v>
       </c>
       <c r="F1458" t="n">
-        <v>17267.2</v>
+        <v>19438.9</v>
       </c>
       <c r="G1458" t="n">
         <v>1</v>
@@ -48571,13 +48571,13 @@
         </is>
       </c>
       <c r="D1459" t="n">
-        <v>197.7</v>
+        <v>263.6</v>
       </c>
       <c r="E1459" t="n">
-        <v>6317.3</v>
+        <v>8412.4</v>
       </c>
       <c r="F1459" t="n">
-        <v>17008.3</v>
+        <v>19103.4</v>
       </c>
       <c r="G1459" t="n">
         <v>5</v>
@@ -48604,13 +48604,13 @@
         </is>
       </c>
       <c r="D1460" t="n">
-        <v>212.4</v>
+        <v>283.2</v>
       </c>
       <c r="E1460" t="n">
-        <v>6122.3</v>
+        <v>8139.4</v>
       </c>
       <c r="F1460" t="n">
-        <v>15987.4</v>
+        <v>18004.5</v>
       </c>
       <c r="G1460" t="n">
         <v>4</v>
@@ -48637,13 +48637,13 @@
         </is>
       </c>
       <c r="D1461" t="n">
-        <v>181.5</v>
+        <v>242</v>
       </c>
       <c r="E1461" t="n">
-        <v>5580.1</v>
+        <v>7425.8</v>
       </c>
       <c r="F1461" t="n">
-        <v>15244.7</v>
+        <v>17090.4</v>
       </c>
       <c r="G1461" t="n">
         <v>7</v>
@@ -48670,13 +48670,13 @@
         </is>
       </c>
       <c r="D1462" t="n">
-        <v>193.8</v>
+        <v>258.4</v>
       </c>
       <c r="E1462" t="n">
-        <v>6524.8</v>
+        <v>8673.4</v>
       </c>
       <c r="F1462" t="n">
-        <v>17459.6</v>
+        <v>19608.2</v>
       </c>
       <c r="G1462" t="n">
         <v>6</v>
@@ -48703,13 +48703,13 @@
         </is>
       </c>
       <c r="D1463" t="n">
-        <v>221.1</v>
+        <v>294.8</v>
       </c>
       <c r="E1463" t="n">
-        <v>5194.6</v>
+        <v>6907.8</v>
       </c>
       <c r="F1463" t="n">
-        <v>14028.5</v>
+        <v>15741.7</v>
       </c>
       <c r="G1463" t="n">
         <v>3</v>
@@ -48718,7 +48718,7 @@
         <v>8</v>
       </c>
       <c r="I1463" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1464">
@@ -48736,13 +48736,13 @@
         </is>
       </c>
       <c r="D1464" t="n">
-        <v>165.6</v>
+        <v>220.8</v>
       </c>
       <c r="E1464" t="n">
-        <v>5916.9</v>
+        <v>7872.2</v>
       </c>
       <c r="F1464" t="n">
-        <v>15521</v>
+        <v>17476.3</v>
       </c>
       <c r="G1464" t="n">
         <v>8</v>
@@ -48769,13 +48769,13 @@
         </is>
       </c>
       <c r="D1465" t="n">
-        <v>264</v>
+        <v>352</v>
       </c>
       <c r="E1465" t="n">
-        <v>6431.7</v>
+        <v>8552.6</v>
       </c>
       <c r="F1465" t="n">
-        <v>13966.7</v>
+        <v>16087.6</v>
       </c>
       <c r="G1465" t="n">
         <v>2</v>
@@ -48784,7 +48784,7 @@
         <v>3</v>
       </c>
       <c r="I1465" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1466">
@@ -48805,10 +48805,10 @@
         <v>76.3</v>
       </c>
       <c r="E1466" t="n">
-        <v>6632.4</v>
+        <v>8804.1</v>
       </c>
       <c r="F1466" t="n">
-        <v>17343.5</v>
+        <v>19515.2</v>
       </c>
       <c r="G1466" t="n">
         <v>3</v>
@@ -48838,10 +48838,10 @@
         <v>73.3</v>
       </c>
       <c r="E1467" t="n">
-        <v>6390.6</v>
+        <v>8485.700000000001</v>
       </c>
       <c r="F1467" t="n">
-        <v>17081.6</v>
+        <v>19176.7</v>
       </c>
       <c r="G1467" t="n">
         <v>5</v>
@@ -48871,10 +48871,10 @@
         <v>56.5</v>
       </c>
       <c r="E1468" t="n">
-        <v>6178.8</v>
+        <v>8195.9</v>
       </c>
       <c r="F1468" t="n">
-        <v>16043.9</v>
+        <v>18061</v>
       </c>
       <c r="G1468" t="n">
         <v>7</v>
@@ -48904,10 +48904,10 @@
         <v>75.09999999999999</v>
       </c>
       <c r="E1469" t="n">
-        <v>5655.2</v>
+        <v>7500.9</v>
       </c>
       <c r="F1469" t="n">
-        <v>15319.8</v>
+        <v>17165.5</v>
       </c>
       <c r="G1469" t="n">
         <v>4</v>
@@ -48937,10 +48937,10 @@
         <v>69.7</v>
       </c>
       <c r="E1470" t="n">
-        <v>6594.5</v>
+        <v>8743.1</v>
       </c>
       <c r="F1470" t="n">
-        <v>17529.3</v>
+        <v>19677.9</v>
       </c>
       <c r="G1470" t="n">
         <v>6</v>
@@ -48970,10 +48970,10 @@
         <v>80.09999999999999</v>
       </c>
       <c r="E1471" t="n">
-        <v>5274.7</v>
+        <v>6987.9</v>
       </c>
       <c r="F1471" t="n">
-        <v>14108.6</v>
+        <v>15821.8</v>
       </c>
       <c r="G1471" t="n">
         <v>2</v>
@@ -48982,7 +48982,7 @@
         <v>8</v>
       </c>
       <c r="I1471" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1472">
@@ -49003,10 +49003,10 @@
         <v>44.9</v>
       </c>
       <c r="E1472" t="n">
-        <v>5961.8</v>
+        <v>7917.1</v>
       </c>
       <c r="F1472" t="n">
-        <v>15565.9</v>
+        <v>17521.2</v>
       </c>
       <c r="G1472" t="n">
         <v>8</v>
@@ -49036,10 +49036,10 @@
         <v>82.40000000000001</v>
       </c>
       <c r="E1473" t="n">
-        <v>6514.1</v>
+        <v>8635</v>
       </c>
       <c r="F1473" t="n">
-        <v>14049.1</v>
+        <v>16170</v>
       </c>
       <c r="G1473" t="n">
         <v>1</v>
@@ -49048,7 +49048,7 @@
         <v>3</v>
       </c>
       <c r="I1473" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/datos/vistas_negocio/Fact_Global_Master.xlsx
+++ b/datos/vistas_negocio/Fact_Global_Master.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,47 +417,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ID_Futmondo</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Jornada</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Temporada</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Puntos</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Puntos_Acumulados</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Acumulado_Total</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Ranking_Jornada</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Ranking_Temporada</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Ranking_General</t>
         </is>
@@ -40882,13 +40870,13 @@
         </is>
       </c>
       <c r="D1226" t="n">
-        <v>88.40000000000001</v>
+        <v>44.2</v>
       </c>
       <c r="E1226" t="n">
-        <v>129.4</v>
+        <v>85.2</v>
       </c>
       <c r="F1226" t="n">
-        <v>10840.5</v>
+        <v>10796.3</v>
       </c>
       <c r="G1226" t="n">
         <v>8</v>
@@ -40915,19 +40903,19 @@
         </is>
       </c>
       <c r="D1227" t="n">
-        <v>186.6</v>
+        <v>93.3</v>
       </c>
       <c r="E1227" t="n">
-        <v>218.6</v>
+        <v>125.3</v>
       </c>
       <c r="F1227" t="n">
-        <v>10909.6</v>
+        <v>10816.3</v>
       </c>
       <c r="G1227" t="n">
         <v>2</v>
       </c>
       <c r="H1227" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I1227" t="n">
         <v>2</v>
@@ -40948,19 +40936,19 @@
         </is>
       </c>
       <c r="D1228" t="n">
-        <v>126.8</v>
+        <v>63.40000000000001</v>
       </c>
       <c r="E1228" t="n">
-        <v>197.8</v>
+        <v>134.4</v>
       </c>
       <c r="F1228" t="n">
-        <v>10062.9</v>
+        <v>9999.5</v>
       </c>
       <c r="G1228" t="n">
         <v>4</v>
       </c>
       <c r="H1228" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1228" t="n">
         <v>4</v>
@@ -40981,13 +40969,13 @@
         </is>
       </c>
       <c r="D1229" t="n">
-        <v>206</v>
+        <v>103</v>
       </c>
       <c r="E1229" t="n">
-        <v>249</v>
+        <v>146</v>
       </c>
       <c r="F1229" t="n">
-        <v>9913.6</v>
+        <v>9810.6</v>
       </c>
       <c r="G1229" t="n">
         <v>1</v>
@@ -41014,19 +41002,19 @@
         </is>
       </c>
       <c r="D1230" t="n">
-        <v>120.4</v>
+        <v>60.2</v>
       </c>
       <c r="E1230" t="n">
-        <v>199.4</v>
+        <v>139.2</v>
       </c>
       <c r="F1230" t="n">
-        <v>11134.2</v>
+        <v>11074</v>
       </c>
       <c r="G1230" t="n">
         <v>5</v>
       </c>
       <c r="H1230" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I1230" t="n">
         <v>1</v>
@@ -41047,13 +41035,13 @@
         </is>
       </c>
       <c r="D1231" t="n">
-        <v>89.2</v>
+        <v>44.6</v>
       </c>
       <c r="E1231" t="n">
-        <v>144.2</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="F1231" t="n">
-        <v>8978.1</v>
+        <v>8933.5</v>
       </c>
       <c r="G1231" t="n">
         <v>7</v>
@@ -41080,19 +41068,19 @@
         </is>
       </c>
       <c r="D1232" t="n">
-        <v>140.2</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="E1232" t="n">
-        <v>191.2</v>
+        <v>121.1</v>
       </c>
       <c r="F1232" t="n">
-        <v>9795.299999999999</v>
+        <v>9725.200000000001</v>
       </c>
       <c r="G1232" t="n">
         <v>3</v>
       </c>
       <c r="H1232" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I1232" t="n">
         <v>6</v>
@@ -41113,19 +41101,19 @@
         </is>
       </c>
       <c r="D1233" t="n">
-        <v>115.6</v>
+        <v>57.8</v>
       </c>
       <c r="E1233" t="n">
-        <v>184.6</v>
+        <v>126.8</v>
       </c>
       <c r="F1233" t="n">
-        <v>7719.6</v>
+        <v>7661.8</v>
       </c>
       <c r="G1233" t="n">
         <v>6</v>
       </c>
       <c r="H1233" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I1233" t="n">
         <v>8</v>
@@ -41146,13 +41134,13 @@
         </is>
       </c>
       <c r="D1234" t="n">
-        <v>124.8</v>
+        <v>62.4</v>
       </c>
       <c r="E1234" t="n">
-        <v>254.2</v>
+        <v>147.6</v>
       </c>
       <c r="F1234" t="n">
-        <v>10965.3</v>
+        <v>10858.7</v>
       </c>
       <c r="G1234" t="n">
         <v>5</v>
@@ -41179,19 +41167,19 @@
         </is>
       </c>
       <c r="D1235" t="n">
-        <v>133.6</v>
+        <v>66.8</v>
       </c>
       <c r="E1235" t="n">
-        <v>352.2</v>
+        <v>192.1</v>
       </c>
       <c r="F1235" t="n">
-        <v>11043.2</v>
+        <v>10883.1</v>
       </c>
       <c r="G1235" t="n">
         <v>3</v>
       </c>
       <c r="H1235" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I1235" t="n">
         <v>2</v>
@@ -41212,13 +41200,13 @@
         </is>
       </c>
       <c r="D1236" t="n">
-        <v>146</v>
+        <v>73</v>
       </c>
       <c r="E1236" t="n">
-        <v>343.8</v>
+        <v>207.4</v>
       </c>
       <c r="F1236" t="n">
-        <v>10208.9</v>
+        <v>10072.5</v>
       </c>
       <c r="G1236" t="n">
         <v>1</v>
@@ -41245,13 +41233,13 @@
         </is>
       </c>
       <c r="D1237" t="n">
-        <v>127.2</v>
+        <v>63.6</v>
       </c>
       <c r="E1237" t="n">
-        <v>376.2</v>
+        <v>209.6</v>
       </c>
       <c r="F1237" t="n">
-        <v>10040.8</v>
+        <v>9874.200000000001</v>
       </c>
       <c r="G1237" t="n">
         <v>4</v>
@@ -41278,19 +41266,19 @@
         </is>
       </c>
       <c r="D1238" t="n">
-        <v>140</v>
+        <v>70</v>
       </c>
       <c r="E1238" t="n">
-        <v>339.4</v>
+        <v>209.2</v>
       </c>
       <c r="F1238" t="n">
-        <v>11274.2</v>
+        <v>11144</v>
       </c>
       <c r="G1238" t="n">
         <v>2</v>
       </c>
       <c r="H1238" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I1238" t="n">
         <v>1</v>
@@ -41311,13 +41299,13 @@
         </is>
       </c>
       <c r="D1239" t="n">
-        <v>81</v>
+        <v>40.5</v>
       </c>
       <c r="E1239" t="n">
-        <v>225.2</v>
+        <v>140.1</v>
       </c>
       <c r="F1239" t="n">
-        <v>9059.1</v>
+        <v>8974</v>
       </c>
       <c r="G1239" t="n">
         <v>8</v>
@@ -41344,13 +41332,13 @@
         </is>
       </c>
       <c r="D1240" t="n">
-        <v>119.6</v>
+        <v>59.8</v>
       </c>
       <c r="E1240" t="n">
-        <v>310.8</v>
+        <v>180.9</v>
       </c>
       <c r="F1240" t="n">
-        <v>9914.9</v>
+        <v>9785</v>
       </c>
       <c r="G1240" t="n">
         <v>6</v>
@@ -41377,13 +41365,13 @@
         </is>
       </c>
       <c r="D1241" t="n">
-        <v>87</v>
+        <v>43.5</v>
       </c>
       <c r="E1241" t="n">
-        <v>271.6</v>
+        <v>170.3</v>
       </c>
       <c r="F1241" t="n">
-        <v>7806.6</v>
+        <v>7705.3</v>
       </c>
       <c r="G1241" t="n">
         <v>7</v>
@@ -41410,13 +41398,13 @@
         </is>
       </c>
       <c r="D1242" t="n">
-        <v>113.8</v>
+        <v>56.9</v>
       </c>
       <c r="E1242" t="n">
-        <v>368</v>
+        <v>204.5</v>
       </c>
       <c r="F1242" t="n">
-        <v>11079.1</v>
+        <v>10915.6</v>
       </c>
       <c r="G1242" t="n">
         <v>4</v>
@@ -41443,19 +41431,19 @@
         </is>
       </c>
       <c r="D1243" t="n">
-        <v>110.2</v>
+        <v>55.1</v>
       </c>
       <c r="E1243" t="n">
-        <v>462.4</v>
+        <v>247.2</v>
       </c>
       <c r="F1243" t="n">
-        <v>11153.4</v>
+        <v>10938.2</v>
       </c>
       <c r="G1243" t="n">
         <v>6</v>
       </c>
       <c r="H1243" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I1243" t="n">
         <v>2</v>
@@ -41476,19 +41464,19 @@
         </is>
       </c>
       <c r="D1244" t="n">
-        <v>117.6</v>
+        <v>58.8</v>
       </c>
       <c r="E1244" t="n">
-        <v>461.4</v>
+        <v>266.2</v>
       </c>
       <c r="F1244" t="n">
-        <v>10326.5</v>
+        <v>10131.3</v>
       </c>
       <c r="G1244" t="n">
         <v>3</v>
       </c>
       <c r="H1244" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I1244" t="n">
         <v>4</v>
@@ -41509,13 +41497,13 @@
         </is>
       </c>
       <c r="D1245" t="n">
-        <v>172.4</v>
+        <v>86.2</v>
       </c>
       <c r="E1245" t="n">
-        <v>548.6</v>
+        <v>295.8</v>
       </c>
       <c r="F1245" t="n">
-        <v>10213.2</v>
+        <v>9960.4</v>
       </c>
       <c r="G1245" t="n">
         <v>1</v>
@@ -41542,19 +41530,19 @@
         </is>
       </c>
       <c r="D1246" t="n">
-        <v>113.6</v>
+        <v>56.8</v>
       </c>
       <c r="E1246" t="n">
-        <v>453</v>
+        <v>266</v>
       </c>
       <c r="F1246" t="n">
-        <v>11387.8</v>
+        <v>11200.8</v>
       </c>
       <c r="G1246" t="n">
         <v>5</v>
       </c>
       <c r="H1246" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1246" t="n">
         <v>1</v>
@@ -41575,13 +41563,13 @@
         </is>
       </c>
       <c r="D1247" t="n">
-        <v>107</v>
+        <v>53.5</v>
       </c>
       <c r="E1247" t="n">
-        <v>332.2</v>
+        <v>193.6</v>
       </c>
       <c r="F1247" t="n">
-        <v>9166.1</v>
+        <v>9027.5</v>
       </c>
       <c r="G1247" t="n">
         <v>7</v>
@@ -41608,13 +41596,13 @@
         </is>
       </c>
       <c r="D1248" t="n">
-        <v>88.40000000000001</v>
+        <v>44.2</v>
       </c>
       <c r="E1248" t="n">
-        <v>399.2</v>
+        <v>225.1</v>
       </c>
       <c r="F1248" t="n">
-        <v>10003.3</v>
+        <v>9829.200000000001</v>
       </c>
       <c r="G1248" t="n">
         <v>8</v>
@@ -41641,13 +41629,13 @@
         </is>
       </c>
       <c r="D1249" t="n">
-        <v>143</v>
+        <v>71.5</v>
       </c>
       <c r="E1249" t="n">
-        <v>414.6</v>
+        <v>241.8</v>
       </c>
       <c r="F1249" t="n">
-        <v>7949.6</v>
+        <v>7776.8</v>
       </c>
       <c r="G1249" t="n">
         <v>2</v>
@@ -41674,13 +41662,13 @@
         </is>
       </c>
       <c r="D1250" t="n">
-        <v>99.80000000000001</v>
+        <v>49.90000000000001</v>
       </c>
       <c r="E1250" t="n">
-        <v>467.8</v>
+        <v>254.4</v>
       </c>
       <c r="F1250" t="n">
-        <v>11178.9</v>
+        <v>10965.5</v>
       </c>
       <c r="G1250" t="n">
         <v>8</v>
@@ -41707,19 +41695,19 @@
         </is>
       </c>
       <c r="D1251" t="n">
-        <v>140.8</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="E1251" t="n">
-        <v>603.2</v>
+        <v>317.6</v>
       </c>
       <c r="F1251" t="n">
-        <v>11294.2</v>
+        <v>11008.6</v>
       </c>
       <c r="G1251" t="n">
         <v>5</v>
       </c>
       <c r="H1251" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1251" t="n">
         <v>2</v>
@@ -41740,19 +41728,19 @@
         </is>
       </c>
       <c r="D1252" t="n">
-        <v>114.2</v>
+        <v>57.1</v>
       </c>
       <c r="E1252" t="n">
-        <v>575.6</v>
+        <v>323.3</v>
       </c>
       <c r="F1252" t="n">
-        <v>10440.7</v>
+        <v>10188.4</v>
       </c>
       <c r="G1252" t="n">
         <v>6</v>
       </c>
       <c r="H1252" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1252" t="n">
         <v>4</v>
@@ -41773,13 +41761,13 @@
         </is>
       </c>
       <c r="D1253" t="n">
-        <v>165.4</v>
+        <v>82.7</v>
       </c>
       <c r="E1253" t="n">
-        <v>714</v>
+        <v>378.5</v>
       </c>
       <c r="F1253" t="n">
-        <v>10378.6</v>
+        <v>10043.1</v>
       </c>
       <c r="G1253" t="n">
         <v>2</v>
@@ -41806,13 +41794,13 @@
         </is>
       </c>
       <c r="D1254" t="n">
-        <v>173</v>
+        <v>86.5</v>
       </c>
       <c r="E1254" t="n">
-        <v>626</v>
+        <v>352.5</v>
       </c>
       <c r="F1254" t="n">
-        <v>11560.8</v>
+        <v>11287.3</v>
       </c>
       <c r="G1254" t="n">
         <v>1</v>
@@ -41839,13 +41827,13 @@
         </is>
       </c>
       <c r="D1255" t="n">
-        <v>151.6</v>
+        <v>75.8</v>
       </c>
       <c r="E1255" t="n">
-        <v>483.8</v>
+        <v>269.4</v>
       </c>
       <c r="F1255" t="n">
-        <v>9317.700000000001</v>
+        <v>9103.299999999999</v>
       </c>
       <c r="G1255" t="n">
         <v>4</v>
@@ -41872,13 +41860,13 @@
         </is>
       </c>
       <c r="D1256" t="n">
-        <v>155.4</v>
+        <v>77.7</v>
       </c>
       <c r="E1256" t="n">
-        <v>554.6</v>
+        <v>302.8</v>
       </c>
       <c r="F1256" t="n">
-        <v>10158.7</v>
+        <v>9906.9</v>
       </c>
       <c r="G1256" t="n">
         <v>3</v>
@@ -41905,13 +41893,13 @@
         </is>
       </c>
       <c r="D1257" t="n">
-        <v>111.2</v>
+        <v>55.6</v>
       </c>
       <c r="E1257" t="n">
-        <v>525.8</v>
+        <v>297.4</v>
       </c>
       <c r="F1257" t="n">
-        <v>8060.8</v>
+        <v>7832.4</v>
       </c>
       <c r="G1257" t="n">
         <v>7</v>
@@ -41938,13 +41926,13 @@
         </is>
       </c>
       <c r="D1258" t="n">
-        <v>68.40000000000001</v>
+        <v>34.2</v>
       </c>
       <c r="E1258" t="n">
-        <v>536.2</v>
+        <v>288.6</v>
       </c>
       <c r="F1258" t="n">
-        <v>11247.3</v>
+        <v>10999.7</v>
       </c>
       <c r="G1258" t="n">
         <v>6</v>
@@ -41971,19 +41959,19 @@
         </is>
       </c>
       <c r="D1259" t="n">
-        <v>91.2</v>
+        <v>45.6</v>
       </c>
       <c r="E1259" t="n">
-        <v>694.4</v>
+        <v>363.2</v>
       </c>
       <c r="F1259" t="n">
-        <v>11385.4</v>
+        <v>11054.2</v>
       </c>
       <c r="G1259" t="n">
         <v>5</v>
       </c>
       <c r="H1259" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1259" t="n">
         <v>2</v>
@@ -42004,19 +41992,19 @@
         </is>
       </c>
       <c r="D1260" t="n">
-        <v>112.2</v>
+        <v>56.1</v>
       </c>
       <c r="E1260" t="n">
-        <v>687.8</v>
+        <v>379.4</v>
       </c>
       <c r="F1260" t="n">
-        <v>10552.9</v>
+        <v>10244.5</v>
       </c>
       <c r="G1260" t="n">
         <v>3</v>
       </c>
       <c r="H1260" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1260" t="n">
         <v>4</v>
@@ -42037,13 +42025,13 @@
         </is>
       </c>
       <c r="D1261" t="n">
-        <v>123.4</v>
+        <v>61.7</v>
       </c>
       <c r="E1261" t="n">
-        <v>837.4000000000001</v>
+        <v>440.2</v>
       </c>
       <c r="F1261" t="n">
-        <v>10502</v>
+        <v>10104.8</v>
       </c>
       <c r="G1261" t="n">
         <v>1</v>
@@ -42070,13 +42058,13 @@
         </is>
       </c>
       <c r="D1262" t="n">
-        <v>116.6</v>
+        <v>58.3</v>
       </c>
       <c r="E1262" t="n">
-        <v>742.6</v>
+        <v>410.8</v>
       </c>
       <c r="F1262" t="n">
-        <v>11677.4</v>
+        <v>11345.6</v>
       </c>
       <c r="G1262" t="n">
         <v>2</v>
@@ -42103,13 +42091,13 @@
         </is>
       </c>
       <c r="D1263" t="n">
-        <v>95.8</v>
+        <v>47.9</v>
       </c>
       <c r="E1263" t="n">
-        <v>579.6</v>
+        <v>317.3</v>
       </c>
       <c r="F1263" t="n">
-        <v>9413.5</v>
+        <v>9151.200000000001</v>
       </c>
       <c r="G1263" t="n">
         <v>4</v>
@@ -42136,13 +42124,13 @@
         </is>
       </c>
       <c r="D1264" t="n">
-        <v>64.8</v>
+        <v>32.4</v>
       </c>
       <c r="E1264" t="n">
-        <v>619.4</v>
+        <v>335.2</v>
       </c>
       <c r="F1264" t="n">
-        <v>10223.5</v>
+        <v>9939.299999999999</v>
       </c>
       <c r="G1264" t="n">
         <v>8</v>
@@ -42169,13 +42157,13 @@
         </is>
       </c>
       <c r="D1265" t="n">
-        <v>68.40000000000001</v>
+        <v>34.2</v>
       </c>
       <c r="E1265" t="n">
-        <v>594.2</v>
+        <v>331.6</v>
       </c>
       <c r="F1265" t="n">
-        <v>8129.2</v>
+        <v>7866.6</v>
       </c>
       <c r="G1265" t="n">
         <v>6</v>
@@ -42202,13 +42190,13 @@
         </is>
       </c>
       <c r="D1266" t="n">
-        <v>147.2</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="E1266" t="n">
-        <v>683.4</v>
+        <v>362.2</v>
       </c>
       <c r="F1266" t="n">
-        <v>11394.5</v>
+        <v>11073.3</v>
       </c>
       <c r="G1266" t="n">
         <v>3</v>
@@ -42235,13 +42223,13 @@
         </is>
       </c>
       <c r="D1267" t="n">
-        <v>118.8</v>
+        <v>59.40000000000001</v>
       </c>
       <c r="E1267" t="n">
-        <v>813.2</v>
+        <v>422.6</v>
       </c>
       <c r="F1267" t="n">
-        <v>11504.2</v>
+        <v>11113.6</v>
       </c>
       <c r="G1267" t="n">
         <v>5</v>
@@ -42268,13 +42256,13 @@
         </is>
       </c>
       <c r="D1268" t="n">
-        <v>157.2</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="E1268" t="n">
-        <v>845</v>
+        <v>458</v>
       </c>
       <c r="F1268" t="n">
-        <v>10710.1</v>
+        <v>10323.1</v>
       </c>
       <c r="G1268" t="n">
         <v>1</v>
@@ -42301,13 +42289,13 @@
         </is>
       </c>
       <c r="D1269" t="n">
-        <v>92</v>
+        <v>46</v>
       </c>
       <c r="E1269" t="n">
-        <v>929.4000000000001</v>
+        <v>486.2</v>
       </c>
       <c r="F1269" t="n">
-        <v>10594</v>
+        <v>10150.8</v>
       </c>
       <c r="G1269" t="n">
         <v>8</v>
@@ -42334,13 +42322,13 @@
         </is>
       </c>
       <c r="D1270" t="n">
-        <v>140.2</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="E1270" t="n">
-        <v>882.8</v>
+        <v>480.9</v>
       </c>
       <c r="F1270" t="n">
-        <v>11817.6</v>
+        <v>11415.7</v>
       </c>
       <c r="G1270" t="n">
         <v>4</v>
@@ -42367,13 +42355,13 @@
         </is>
       </c>
       <c r="D1271" t="n">
-        <v>105</v>
+        <v>52.5</v>
       </c>
       <c r="E1271" t="n">
-        <v>684.6</v>
+        <v>369.8</v>
       </c>
       <c r="F1271" t="n">
-        <v>9518.5</v>
+        <v>9203.700000000001</v>
       </c>
       <c r="G1271" t="n">
         <v>7</v>
@@ -42400,13 +42388,13 @@
         </is>
       </c>
       <c r="D1272" t="n">
-        <v>149.8</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="E1272" t="n">
-        <v>769.2</v>
+        <v>410.1</v>
       </c>
       <c r="F1272" t="n">
-        <v>10373.3</v>
+        <v>10014.2</v>
       </c>
       <c r="G1272" t="n">
         <v>2</v>
@@ -42433,13 +42421,13 @@
         </is>
       </c>
       <c r="D1273" t="n">
-        <v>116.4</v>
+        <v>58.2</v>
       </c>
       <c r="E1273" t="n">
-        <v>710.6</v>
+        <v>389.8</v>
       </c>
       <c r="F1273" t="n">
-        <v>8245.6</v>
+        <v>7924.8</v>
       </c>
       <c r="G1273" t="n">
         <v>6</v>
@@ -42466,13 +42454,13 @@
         </is>
       </c>
       <c r="D1274" t="n">
-        <v>107.6</v>
+        <v>53.8</v>
       </c>
       <c r="E1274" t="n">
-        <v>791</v>
+        <v>416</v>
       </c>
       <c r="F1274" t="n">
-        <v>11502.1</v>
+        <v>11127.1</v>
       </c>
       <c r="G1274" t="n">
         <v>7</v>
@@ -42499,19 +42487,19 @@
         </is>
       </c>
       <c r="D1275" t="n">
-        <v>102.2</v>
+        <v>51.1</v>
       </c>
       <c r="E1275" t="n">
-        <v>915.4</v>
+        <v>473.7</v>
       </c>
       <c r="F1275" t="n">
-        <v>11606.4</v>
+        <v>11164.7</v>
       </c>
       <c r="G1275" t="n">
         <v>8</v>
       </c>
       <c r="H1275" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I1275" t="n">
         <v>2</v>
@@ -42532,13 +42520,13 @@
         </is>
       </c>
       <c r="D1276" t="n">
-        <v>124.2</v>
+        <v>62.1</v>
       </c>
       <c r="E1276" t="n">
-        <v>969.2</v>
+        <v>520.1</v>
       </c>
       <c r="F1276" t="n">
-        <v>10834.3</v>
+        <v>10385.2</v>
       </c>
       <c r="G1276" t="n">
         <v>3</v>
@@ -42565,13 +42553,13 @@
         </is>
       </c>
       <c r="D1277" t="n">
-        <v>139</v>
+        <v>69.5</v>
       </c>
       <c r="E1277" t="n">
-        <v>1068.4</v>
+        <v>555.7</v>
       </c>
       <c r="F1277" t="n">
-        <v>10733</v>
+        <v>10220.3</v>
       </c>
       <c r="G1277" t="n">
         <v>1</v>
@@ -42598,13 +42586,13 @@
         </is>
       </c>
       <c r="D1278" t="n">
-        <v>119</v>
+        <v>59.5</v>
       </c>
       <c r="E1278" t="n">
-        <v>1001.8</v>
+        <v>540.4</v>
       </c>
       <c r="F1278" t="n">
-        <v>11936.6</v>
+        <v>11475.2</v>
       </c>
       <c r="G1278" t="n">
         <v>5</v>
@@ -42631,13 +42619,13 @@
         </is>
       </c>
       <c r="D1279" t="n">
-        <v>108.2</v>
+        <v>54.1</v>
       </c>
       <c r="E1279" t="n">
-        <v>792.8</v>
+        <v>423.9</v>
       </c>
       <c r="F1279" t="n">
-        <v>9626.700000000001</v>
+        <v>9257.799999999999</v>
       </c>
       <c r="G1279" t="n">
         <v>6</v>
@@ -42664,19 +42652,19 @@
         </is>
       </c>
       <c r="D1280" t="n">
-        <v>138.4</v>
+        <v>69.2</v>
       </c>
       <c r="E1280" t="n">
-        <v>907.6</v>
+        <v>479.3</v>
       </c>
       <c r="F1280" t="n">
-        <v>10511.7</v>
+        <v>10083.4</v>
       </c>
       <c r="G1280" t="n">
         <v>2</v>
       </c>
       <c r="H1280" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I1280" t="n">
         <v>6</v>
@@ -42697,13 +42685,13 @@
         </is>
       </c>
       <c r="D1281" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="E1281" t="n">
-        <v>830.6</v>
+        <v>449.8</v>
       </c>
       <c r="F1281" t="n">
-        <v>8365.6</v>
+        <v>7984.8</v>
       </c>
       <c r="G1281" t="n">
         <v>4</v>
@@ -42730,13 +42718,13 @@
         </is>
       </c>
       <c r="D1282" t="n">
-        <v>175.6</v>
+        <v>87.8</v>
       </c>
       <c r="E1282" t="n">
-        <v>966.6</v>
+        <v>503.8</v>
       </c>
       <c r="F1282" t="n">
-        <v>11677.7</v>
+        <v>11214.9</v>
       </c>
       <c r="G1282" t="n">
         <v>1</v>
@@ -42763,13 +42751,13 @@
         </is>
       </c>
       <c r="D1283" t="n">
-        <v>134</v>
+        <v>67</v>
       </c>
       <c r="E1283" t="n">
-        <v>1049.4</v>
+        <v>540.7</v>
       </c>
       <c r="F1283" t="n">
-        <v>11740.4</v>
+        <v>11231.7</v>
       </c>
       <c r="G1283" t="n">
         <v>4</v>
@@ -42796,13 +42784,13 @@
         </is>
       </c>
       <c r="D1284" t="n">
-        <v>110.8</v>
+        <v>55.4</v>
       </c>
       <c r="E1284" t="n">
-        <v>1080</v>
+        <v>575.5</v>
       </c>
       <c r="F1284" t="n">
-        <v>10945.1</v>
+        <v>10440.6</v>
       </c>
       <c r="G1284" t="n">
         <v>7</v>
@@ -42829,13 +42817,13 @@
         </is>
       </c>
       <c r="D1285" t="n">
-        <v>115.2</v>
+        <v>57.6</v>
       </c>
       <c r="E1285" t="n">
-        <v>1183.6</v>
+        <v>613.3000000000001</v>
       </c>
       <c r="F1285" t="n">
-        <v>10848.2</v>
+        <v>10277.9</v>
       </c>
       <c r="G1285" t="n">
         <v>6</v>
@@ -42862,13 +42850,13 @@
         </is>
       </c>
       <c r="D1286" t="n">
-        <v>132.6</v>
+        <v>66.3</v>
       </c>
       <c r="E1286" t="n">
-        <v>1134.4</v>
+        <v>606.7</v>
       </c>
       <c r="F1286" t="n">
-        <v>12069.2</v>
+        <v>11541.5</v>
       </c>
       <c r="G1286" t="n">
         <v>5</v>
@@ -42895,13 +42883,13 @@
         </is>
       </c>
       <c r="D1287" t="n">
-        <v>104.2</v>
+        <v>52.1</v>
       </c>
       <c r="E1287" t="n">
-        <v>897</v>
+        <v>476</v>
       </c>
       <c r="F1287" t="n">
-        <v>9730.9</v>
+        <v>9309.9</v>
       </c>
       <c r="G1287" t="n">
         <v>8</v>
@@ -42928,13 +42916,13 @@
         </is>
       </c>
       <c r="D1288" t="n">
-        <v>162.2</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="E1288" t="n">
-        <v>1069.8</v>
+        <v>560.4</v>
       </c>
       <c r="F1288" t="n">
-        <v>10673.9</v>
+        <v>10164.5</v>
       </c>
       <c r="G1288" t="n">
         <v>2</v>
@@ -42961,13 +42949,13 @@
         </is>
       </c>
       <c r="D1289" t="n">
-        <v>153.8</v>
+        <v>76.89999999999999</v>
       </c>
       <c r="E1289" t="n">
-        <v>984.4</v>
+        <v>526.7</v>
       </c>
       <c r="F1289" t="n">
-        <v>8519.4</v>
+        <v>8061.7</v>
       </c>
       <c r="G1289" t="n">
         <v>3</v>
@@ -42994,22 +42982,22 @@
         </is>
       </c>
       <c r="D1290" t="n">
-        <v>155.8</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="E1290" t="n">
-        <v>1122.4</v>
+        <v>581.7</v>
       </c>
       <c r="F1290" t="n">
-        <v>11833.5</v>
+        <v>11292.8</v>
       </c>
       <c r="G1290" t="n">
         <v>1</v>
       </c>
       <c r="H1290" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1290" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1291">
@@ -43027,13 +43015,13 @@
         </is>
       </c>
       <c r="D1291" t="n">
-        <v>109.6</v>
+        <v>54.8</v>
       </c>
       <c r="E1291" t="n">
-        <v>1159</v>
+        <v>595.5</v>
       </c>
       <c r="F1291" t="n">
-        <v>11850</v>
+        <v>11286.5</v>
       </c>
       <c r="G1291" t="n">
         <v>7</v>
@@ -43042,7 +43030,7 @@
         <v>5</v>
       </c>
       <c r="I1291" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1292">
@@ -43060,13 +43048,13 @@
         </is>
       </c>
       <c r="D1292" t="n">
-        <v>137.6</v>
+        <v>68.8</v>
       </c>
       <c r="E1292" t="n">
-        <v>1217.6</v>
+        <v>644.3</v>
       </c>
       <c r="F1292" t="n">
-        <v>11082.7</v>
+        <v>10509.4</v>
       </c>
       <c r="G1292" t="n">
         <v>3</v>
@@ -43093,13 +43081,13 @@
         </is>
       </c>
       <c r="D1293" t="n">
-        <v>120.4</v>
+        <v>60.2</v>
       </c>
       <c r="E1293" t="n">
-        <v>1304</v>
+        <v>673.5</v>
       </c>
       <c r="F1293" t="n">
-        <v>10968.6</v>
+        <v>10338.1</v>
       </c>
       <c r="G1293" t="n">
         <v>6</v>
@@ -43126,13 +43114,13 @@
         </is>
       </c>
       <c r="D1294" t="n">
-        <v>125.6</v>
+        <v>62.8</v>
       </c>
       <c r="E1294" t="n">
-        <v>1260</v>
+        <v>669.5</v>
       </c>
       <c r="F1294" t="n">
-        <v>12194.8</v>
+        <v>11604.3</v>
       </c>
       <c r="G1294" t="n">
         <v>5</v>
@@ -43159,13 +43147,13 @@
         </is>
       </c>
       <c r="D1295" t="n">
-        <v>101.8</v>
+        <v>50.9</v>
       </c>
       <c r="E1295" t="n">
-        <v>998.8</v>
+        <v>526.9</v>
       </c>
       <c r="F1295" t="n">
-        <v>9832.700000000001</v>
+        <v>9360.799999999999</v>
       </c>
       <c r="G1295" t="n">
         <v>8</v>
@@ -43192,13 +43180,13 @@
         </is>
       </c>
       <c r="D1296" t="n">
-        <v>138.8</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="E1296" t="n">
-        <v>1208.6</v>
+        <v>629.8</v>
       </c>
       <c r="F1296" t="n">
-        <v>10812.7</v>
+        <v>10233.9</v>
       </c>
       <c r="G1296" t="n">
         <v>2</v>
@@ -43225,19 +43213,19 @@
         </is>
       </c>
       <c r="D1297" t="n">
-        <v>132.6</v>
+        <v>66.3</v>
       </c>
       <c r="E1297" t="n">
-        <v>1117</v>
+        <v>593</v>
       </c>
       <c r="F1297" t="n">
-        <v>8652</v>
+        <v>8128</v>
       </c>
       <c r="G1297" t="n">
         <v>4</v>
       </c>
       <c r="H1297" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I1297" t="n">
         <v>8</v>
@@ -43258,13 +43246,13 @@
         </is>
       </c>
       <c r="D1298" t="n">
-        <v>136</v>
+        <v>68</v>
       </c>
       <c r="E1298" t="n">
-        <v>1258.4</v>
+        <v>649.7</v>
       </c>
       <c r="F1298" t="n">
-        <v>11969.5</v>
+        <v>11360.8</v>
       </c>
       <c r="G1298" t="n">
         <v>5</v>
@@ -43291,19 +43279,19 @@
         </is>
       </c>
       <c r="D1299" t="n">
-        <v>178.4</v>
+        <v>89.2</v>
       </c>
       <c r="E1299" t="n">
-        <v>1337.4</v>
+        <v>684.7</v>
       </c>
       <c r="F1299" t="n">
-        <v>12028.4</v>
+        <v>11375.7</v>
       </c>
       <c r="G1299" t="n">
         <v>2</v>
       </c>
       <c r="H1299" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I1299" t="n">
         <v>2</v>
@@ -43324,19 +43312,19 @@
         </is>
       </c>
       <c r="D1300" t="n">
-        <v>158.6</v>
+        <v>79.3</v>
       </c>
       <c r="E1300" t="n">
-        <v>1376.2</v>
+        <v>723.6</v>
       </c>
       <c r="F1300" t="n">
-        <v>11241.3</v>
+        <v>10588.7</v>
       </c>
       <c r="G1300" t="n">
         <v>3</v>
       </c>
       <c r="H1300" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I1300" t="n">
         <v>4</v>
@@ -43357,13 +43345,13 @@
         </is>
       </c>
       <c r="D1301" t="n">
-        <v>122</v>
+        <v>61</v>
       </c>
       <c r="E1301" t="n">
-        <v>1426</v>
+        <v>734.5</v>
       </c>
       <c r="F1301" t="n">
-        <v>11090.6</v>
+        <v>10399.1</v>
       </c>
       <c r="G1301" t="n">
         <v>6</v>
@@ -43390,19 +43378,19 @@
         </is>
       </c>
       <c r="D1302" t="n">
-        <v>114.8</v>
+        <v>57.4</v>
       </c>
       <c r="E1302" t="n">
-        <v>1374.8</v>
+        <v>726.9</v>
       </c>
       <c r="F1302" t="n">
-        <v>12309.6</v>
+        <v>11661.7</v>
       </c>
       <c r="G1302" t="n">
         <v>7</v>
       </c>
       <c r="H1302" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I1302" t="n">
         <v>1</v>
@@ -43423,13 +43411,13 @@
         </is>
       </c>
       <c r="D1303" t="n">
-        <v>92.8</v>
+        <v>46.4</v>
       </c>
       <c r="E1303" t="n">
-        <v>1091.6</v>
+        <v>573.3</v>
       </c>
       <c r="F1303" t="n">
-        <v>9925.5</v>
+        <v>9407.200000000001</v>
       </c>
       <c r="G1303" t="n">
         <v>8</v>
@@ -43456,13 +43444,13 @@
         </is>
       </c>
       <c r="D1304" t="n">
-        <v>154.4</v>
+        <v>77.2</v>
       </c>
       <c r="E1304" t="n">
-        <v>1363</v>
+        <v>707</v>
       </c>
       <c r="F1304" t="n">
-        <v>10967.1</v>
+        <v>10311.1</v>
       </c>
       <c r="G1304" t="n">
         <v>4</v>
@@ -43489,19 +43477,19 @@
         </is>
       </c>
       <c r="D1305" t="n">
-        <v>190.4</v>
+        <v>95.2</v>
       </c>
       <c r="E1305" t="n">
-        <v>1307.4</v>
+        <v>688.2</v>
       </c>
       <c r="F1305" t="n">
-        <v>8842.4</v>
+        <v>8223.200000000001</v>
       </c>
       <c r="G1305" t="n">
         <v>1</v>
       </c>
       <c r="H1305" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I1305" t="n">
         <v>8</v>
@@ -43522,13 +43510,13 @@
         </is>
       </c>
       <c r="D1306" t="n">
-        <v>156</v>
+        <v>78</v>
       </c>
       <c r="E1306" t="n">
-        <v>1414.4</v>
+        <v>727.7</v>
       </c>
       <c r="F1306" t="n">
-        <v>12125.5</v>
+        <v>11438.8</v>
       </c>
       <c r="G1306" t="n">
         <v>3</v>
@@ -43555,19 +43543,19 @@
         </is>
       </c>
       <c r="D1307" t="n">
-        <v>157.2</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="E1307" t="n">
-        <v>1494.6</v>
+        <v>763.3</v>
       </c>
       <c r="F1307" t="n">
-        <v>12185.6</v>
+        <v>11454.3</v>
       </c>
       <c r="G1307" t="n">
         <v>2</v>
       </c>
       <c r="H1307" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I1307" t="n">
         <v>2</v>
@@ -43588,13 +43576,13 @@
         </is>
       </c>
       <c r="D1308" t="n">
-        <v>153.8</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="E1308" t="n">
-        <v>1530</v>
+        <v>800.5</v>
       </c>
       <c r="F1308" t="n">
-        <v>11395.1</v>
+        <v>10665.6</v>
       </c>
       <c r="G1308" t="n">
         <v>4</v>
@@ -43621,19 +43609,19 @@
         </is>
       </c>
       <c r="D1309" t="n">
-        <v>96.8</v>
+        <v>48.4</v>
       </c>
       <c r="E1309" t="n">
-        <v>1522.8</v>
+        <v>782.9</v>
       </c>
       <c r="F1309" t="n">
-        <v>11187.4</v>
+        <v>10447.5</v>
       </c>
       <c r="G1309" t="n">
         <v>8</v>
       </c>
       <c r="H1309" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I1309" t="n">
         <v>5</v>
@@ -43654,19 +43642,19 @@
         </is>
       </c>
       <c r="D1310" t="n">
-        <v>135.2</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="E1310" t="n">
-        <v>1510</v>
+        <v>794.5</v>
       </c>
       <c r="F1310" t="n">
-        <v>12444.8</v>
+        <v>11729.3</v>
       </c>
       <c r="G1310" t="n">
         <v>5</v>
       </c>
       <c r="H1310" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I1310" t="n">
         <v>1</v>
@@ -43687,13 +43675,13 @@
         </is>
       </c>
       <c r="D1311" t="n">
-        <v>116.2</v>
+        <v>58.1</v>
       </c>
       <c r="E1311" t="n">
-        <v>1207.8</v>
+        <v>631.4</v>
       </c>
       <c r="F1311" t="n">
-        <v>10041.7</v>
+        <v>9465.299999999999</v>
       </c>
       <c r="G1311" t="n">
         <v>7</v>
@@ -43720,13 +43708,13 @@
         </is>
       </c>
       <c r="D1312" t="n">
-        <v>122.8</v>
+        <v>61.4</v>
       </c>
       <c r="E1312" t="n">
-        <v>1485.8</v>
+        <v>768.4</v>
       </c>
       <c r="F1312" t="n">
-        <v>11089.9</v>
+        <v>10372.5</v>
       </c>
       <c r="G1312" t="n">
         <v>6</v>
@@ -43753,19 +43741,19 @@
         </is>
       </c>
       <c r="D1313" t="n">
-        <v>163.2</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="E1313" t="n">
-        <v>1470.6</v>
+        <v>769.8</v>
       </c>
       <c r="F1313" t="n">
-        <v>9005.6</v>
+        <v>8304.799999999999</v>
       </c>
       <c r="G1313" t="n">
         <v>1</v>
       </c>
       <c r="H1313" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I1313" t="n">
         <v>8</v>
@@ -43786,13 +43774,13 @@
         </is>
       </c>
       <c r="D1314" t="n">
-        <v>135</v>
+        <v>67.5</v>
       </c>
       <c r="E1314" t="n">
-        <v>1549.4</v>
+        <v>795.2</v>
       </c>
       <c r="F1314" t="n">
-        <v>12260.5</v>
+        <v>11506.3</v>
       </c>
       <c r="G1314" t="n">
         <v>5</v>
@@ -43819,19 +43807,19 @@
         </is>
       </c>
       <c r="D1315" t="n">
-        <v>139.6</v>
+        <v>69.8</v>
       </c>
       <c r="E1315" t="n">
-        <v>1634.2</v>
+        <v>833.1</v>
       </c>
       <c r="F1315" t="n">
-        <v>12325.2</v>
+        <v>11524.1</v>
       </c>
       <c r="G1315" t="n">
         <v>2</v>
       </c>
       <c r="H1315" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I1315" t="n">
         <v>2</v>
@@ -43852,13 +43840,13 @@
         </is>
       </c>
       <c r="D1316" t="n">
-        <v>136.6</v>
+        <v>68.3</v>
       </c>
       <c r="E1316" t="n">
-        <v>1666.6</v>
+        <v>868.8</v>
       </c>
       <c r="F1316" t="n">
-        <v>11531.7</v>
+        <v>10733.9</v>
       </c>
       <c r="G1316" t="n">
         <v>3</v>
@@ -43885,13 +43873,13 @@
         </is>
       </c>
       <c r="D1317" t="n">
-        <v>104.2</v>
+        <v>52.1</v>
       </c>
       <c r="E1317" t="n">
-        <v>1627</v>
+        <v>835</v>
       </c>
       <c r="F1317" t="n">
-        <v>11291.6</v>
+        <v>10499.6</v>
       </c>
       <c r="G1317" t="n">
         <v>8</v>
@@ -43918,13 +43906,13 @@
         </is>
       </c>
       <c r="D1318" t="n">
-        <v>159.4</v>
+        <v>79.7</v>
       </c>
       <c r="E1318" t="n">
-        <v>1669.4</v>
+        <v>874.1999999999999</v>
       </c>
       <c r="F1318" t="n">
-        <v>12604.2</v>
+        <v>11809</v>
       </c>
       <c r="G1318" t="n">
         <v>1</v>
@@ -43951,13 +43939,13 @@
         </is>
       </c>
       <c r="D1319" t="n">
-        <v>116</v>
+        <v>58</v>
       </c>
       <c r="E1319" t="n">
-        <v>1323.8</v>
+        <v>689.4</v>
       </c>
       <c r="F1319" t="n">
-        <v>10157.7</v>
+        <v>9523.299999999999</v>
       </c>
       <c r="G1319" t="n">
         <v>7</v>
@@ -43984,13 +43972,13 @@
         </is>
       </c>
       <c r="D1320" t="n">
-        <v>119</v>
+        <v>59.5</v>
       </c>
       <c r="E1320" t="n">
-        <v>1604.8</v>
+        <v>827.9</v>
       </c>
       <c r="F1320" t="n">
-        <v>11208.9</v>
+        <v>10432</v>
       </c>
       <c r="G1320" t="n">
         <v>6</v>
@@ -44017,19 +44005,19 @@
         </is>
       </c>
       <c r="D1321" t="n">
-        <v>136.2</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="E1321" t="n">
-        <v>1606.8</v>
+        <v>837.9</v>
       </c>
       <c r="F1321" t="n">
-        <v>9141.799999999999</v>
+        <v>8372.9</v>
       </c>
       <c r="G1321" t="n">
         <v>4</v>
       </c>
       <c r="H1321" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I1321" t="n">
         <v>8</v>
@@ -44050,13 +44038,13 @@
         </is>
       </c>
       <c r="D1322" t="n">
-        <v>117.2</v>
+        <v>58.6</v>
       </c>
       <c r="E1322" t="n">
-        <v>1666.6</v>
+        <v>853.8</v>
       </c>
       <c r="F1322" t="n">
-        <v>12377.7</v>
+        <v>11564.9</v>
       </c>
       <c r="G1322" t="n">
         <v>6</v>
@@ -44083,19 +44071,19 @@
         </is>
       </c>
       <c r="D1323" t="n">
-        <v>211.4</v>
+        <v>105.7</v>
       </c>
       <c r="E1323" t="n">
-        <v>1845.6</v>
+        <v>938.8</v>
       </c>
       <c r="F1323" t="n">
-        <v>12536.6</v>
+        <v>11629.8</v>
       </c>
       <c r="G1323" t="n">
         <v>1</v>
       </c>
       <c r="H1323" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1323" t="n">
         <v>2</v>
@@ -44116,13 +44104,13 @@
         </is>
       </c>
       <c r="D1324" t="n">
-        <v>116.8</v>
+        <v>58.4</v>
       </c>
       <c r="E1324" t="n">
-        <v>1783.4</v>
+        <v>927.2</v>
       </c>
       <c r="F1324" t="n">
-        <v>11648.5</v>
+        <v>10792.3</v>
       </c>
       <c r="G1324" t="n">
         <v>7</v>
@@ -44149,13 +44137,13 @@
         </is>
       </c>
       <c r="D1325" t="n">
-        <v>114.8</v>
+        <v>57.4</v>
       </c>
       <c r="E1325" t="n">
-        <v>1741.8</v>
+        <v>892.4</v>
       </c>
       <c r="F1325" t="n">
-        <v>11406.4</v>
+        <v>10557</v>
       </c>
       <c r="G1325" t="n">
         <v>8</v>
@@ -44182,19 +44170,19 @@
         </is>
       </c>
       <c r="D1326" t="n">
-        <v>166.8</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="E1326" t="n">
-        <v>1836.2</v>
+        <v>957.6</v>
       </c>
       <c r="F1326" t="n">
-        <v>12771</v>
+        <v>11892.4</v>
       </c>
       <c r="G1326" t="n">
         <v>3</v>
       </c>
       <c r="H1326" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1326" t="n">
         <v>1</v>
@@ -44215,13 +44203,13 @@
         </is>
       </c>
       <c r="D1327" t="n">
-        <v>148.6</v>
+        <v>74.3</v>
       </c>
       <c r="E1327" t="n">
-        <v>1472.4</v>
+        <v>763.7</v>
       </c>
       <c r="F1327" t="n">
-        <v>10306.3</v>
+        <v>9597.6</v>
       </c>
       <c r="G1327" t="n">
         <v>4</v>
@@ -44248,13 +44236,13 @@
         </is>
       </c>
       <c r="D1328" t="n">
-        <v>144</v>
+        <v>72</v>
       </c>
       <c r="E1328" t="n">
-        <v>1748.8</v>
+        <v>899.9</v>
       </c>
       <c r="F1328" t="n">
-        <v>11352.9</v>
+        <v>10504</v>
       </c>
       <c r="G1328" t="n">
         <v>5</v>
@@ -44281,13 +44269,13 @@
         </is>
       </c>
       <c r="D1329" t="n">
-        <v>174.2</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="E1329" t="n">
-        <v>1781</v>
+        <v>925</v>
       </c>
       <c r="F1329" t="n">
-        <v>9316</v>
+        <v>8460</v>
       </c>
       <c r="G1329" t="n">
         <v>2</v>
@@ -44314,13 +44302,13 @@
         </is>
       </c>
       <c r="D1330" t="n">
-        <v>122.4</v>
+        <v>61.2</v>
       </c>
       <c r="E1330" t="n">
-        <v>1789</v>
+        <v>915</v>
       </c>
       <c r="F1330" t="n">
-        <v>12500.1</v>
+        <v>11626.1</v>
       </c>
       <c r="G1330" t="n">
         <v>5</v>
@@ -44347,13 +44335,13 @@
         </is>
       </c>
       <c r="D1331" t="n">
-        <v>111.2</v>
+        <v>55.59999999999999</v>
       </c>
       <c r="E1331" t="n">
-        <v>1956.8</v>
+        <v>994.4</v>
       </c>
       <c r="F1331" t="n">
-        <v>12647.8</v>
+        <v>11685.4</v>
       </c>
       <c r="G1331" t="n">
         <v>7</v>
@@ -44380,13 +44368,13 @@
         </is>
       </c>
       <c r="D1332" t="n">
-        <v>101.2</v>
+        <v>50.59999999999999</v>
       </c>
       <c r="E1332" t="n">
-        <v>1884.6</v>
+        <v>977.8</v>
       </c>
       <c r="F1332" t="n">
-        <v>11749.7</v>
+        <v>10842.9</v>
       </c>
       <c r="G1332" t="n">
         <v>8</v>
@@ -44413,13 +44401,13 @@
         </is>
       </c>
       <c r="D1333" t="n">
-        <v>124.8</v>
+        <v>62.40000000000001</v>
       </c>
       <c r="E1333" t="n">
-        <v>1866.6</v>
+        <v>954.8000000000001</v>
       </c>
       <c r="F1333" t="n">
-        <v>11531.2</v>
+        <v>10619.4</v>
       </c>
       <c r="G1333" t="n">
         <v>4</v>
@@ -44446,13 +44434,13 @@
         </is>
       </c>
       <c r="D1334" t="n">
-        <v>163.8</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="E1334" t="n">
-        <v>2000</v>
+        <v>1039.5</v>
       </c>
       <c r="F1334" t="n">
-        <v>12934.8</v>
+        <v>11974.3</v>
       </c>
       <c r="G1334" t="n">
         <v>2</v>
@@ -44479,13 +44467,13 @@
         </is>
       </c>
       <c r="D1335" t="n">
-        <v>126.6</v>
+        <v>63.3</v>
       </c>
       <c r="E1335" t="n">
-        <v>1599</v>
+        <v>827</v>
       </c>
       <c r="F1335" t="n">
-        <v>10432.9</v>
+        <v>9660.9</v>
       </c>
       <c r="G1335" t="n">
         <v>3</v>
@@ -44512,13 +44500,13 @@
         </is>
       </c>
       <c r="D1336" t="n">
-        <v>172</v>
+        <v>86</v>
       </c>
       <c r="E1336" t="n">
-        <v>1920.8</v>
+        <v>985.9</v>
       </c>
       <c r="F1336" t="n">
-        <v>11524.9</v>
+        <v>10590</v>
       </c>
       <c r="G1336" t="n">
         <v>1</v>
@@ -44545,13 +44533,13 @@
         </is>
       </c>
       <c r="D1337" t="n">
-        <v>116.2</v>
+        <v>58.1</v>
       </c>
       <c r="E1337" t="n">
-        <v>1897.2</v>
+        <v>983.1</v>
       </c>
       <c r="F1337" t="n">
-        <v>9432.200000000001</v>
+        <v>8518.1</v>
       </c>
       <c r="G1337" t="n">
         <v>6</v>
@@ -44578,13 +44566,13 @@
         </is>
       </c>
       <c r="D1338" t="n">
-        <v>128.4</v>
+        <v>64.2</v>
       </c>
       <c r="E1338" t="n">
-        <v>1917.4</v>
+        <v>979.2</v>
       </c>
       <c r="F1338" t="n">
-        <v>12628.5</v>
+        <v>11690.3</v>
       </c>
       <c r="G1338" t="n">
         <v>5</v>
@@ -44611,13 +44599,13 @@
         </is>
       </c>
       <c r="D1339" t="n">
-        <v>177.4</v>
+        <v>88.7</v>
       </c>
       <c r="E1339" t="n">
-        <v>2134.2</v>
+        <v>1083.1</v>
       </c>
       <c r="F1339" t="n">
-        <v>12825.2</v>
+        <v>11774.1</v>
       </c>
       <c r="G1339" t="n">
         <v>1</v>
@@ -44644,19 +44632,19 @@
         </is>
       </c>
       <c r="D1340" t="n">
-        <v>153.6</v>
+        <v>76.8</v>
       </c>
       <c r="E1340" t="n">
-        <v>2038.2</v>
+        <v>1054.6</v>
       </c>
       <c r="F1340" t="n">
-        <v>11903.3</v>
+        <v>10919.7</v>
       </c>
       <c r="G1340" t="n">
         <v>3</v>
       </c>
       <c r="H1340" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1340" t="n">
         <v>4</v>
@@ -44677,13 +44665,13 @@
         </is>
       </c>
       <c r="D1341" t="n">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="E1341" t="n">
-        <v>1956.6</v>
+        <v>999.8000000000001</v>
       </c>
       <c r="F1341" t="n">
-        <v>11621.2</v>
+        <v>10664.4</v>
       </c>
       <c r="G1341" t="n">
         <v>8</v>
@@ -44692,7 +44680,7 @@
         <v>6</v>
       </c>
       <c r="I1341" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1342">
@@ -44710,13 +44698,13 @@
         </is>
       </c>
       <c r="D1342" t="n">
-        <v>162.4</v>
+        <v>81.2</v>
       </c>
       <c r="E1342" t="n">
-        <v>2162.4</v>
+        <v>1120.7</v>
       </c>
       <c r="F1342" t="n">
-        <v>13097.2</v>
+        <v>12055.5</v>
       </c>
       <c r="G1342" t="n">
         <v>2</v>
@@ -44743,13 +44731,13 @@
         </is>
       </c>
       <c r="D1343" t="n">
-        <v>127.4</v>
+        <v>63.7</v>
       </c>
       <c r="E1343" t="n">
-        <v>1726.4</v>
+        <v>890.7</v>
       </c>
       <c r="F1343" t="n">
-        <v>10560.3</v>
+        <v>9724.6</v>
       </c>
       <c r="G1343" t="n">
         <v>6</v>
@@ -44776,22 +44764,22 @@
         </is>
       </c>
       <c r="D1344" t="n">
-        <v>135.4</v>
+        <v>67.7</v>
       </c>
       <c r="E1344" t="n">
-        <v>2056.2</v>
+        <v>1053.6</v>
       </c>
       <c r="F1344" t="n">
-        <v>11660.3</v>
+        <v>10657.7</v>
       </c>
       <c r="G1344" t="n">
         <v>4</v>
       </c>
       <c r="H1344" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1344" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1345">
@@ -44809,13 +44797,13 @@
         </is>
       </c>
       <c r="D1345" t="n">
-        <v>120.4</v>
+        <v>60.2</v>
       </c>
       <c r="E1345" t="n">
-        <v>2017.6</v>
+        <v>1043.3</v>
       </c>
       <c r="F1345" t="n">
-        <v>9552.6</v>
+        <v>8578.299999999999</v>
       </c>
       <c r="G1345" t="n">
         <v>7</v>
@@ -44842,13 +44830,13 @@
         </is>
       </c>
       <c r="D1346" t="n">
-        <v>176.2</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="E1346" t="n">
-        <v>2093.6</v>
+        <v>1067.3</v>
       </c>
       <c r="F1346" t="n">
-        <v>12804.7</v>
+        <v>11778.4</v>
       </c>
       <c r="G1346" t="n">
         <v>3</v>
@@ -44875,13 +44863,13 @@
         </is>
       </c>
       <c r="D1347" t="n">
-        <v>119.8</v>
+        <v>59.9</v>
       </c>
       <c r="E1347" t="n">
-        <v>2254</v>
+        <v>1143</v>
       </c>
       <c r="F1347" t="n">
-        <v>12945</v>
+        <v>11834</v>
       </c>
       <c r="G1347" t="n">
         <v>6</v>
@@ -44908,13 +44896,13 @@
         </is>
       </c>
       <c r="D1348" t="n">
-        <v>140.4</v>
+        <v>70.2</v>
       </c>
       <c r="E1348" t="n">
-        <v>2178.6</v>
+        <v>1124.8</v>
       </c>
       <c r="F1348" t="n">
-        <v>12043.7</v>
+        <v>10989.9</v>
       </c>
       <c r="G1348" t="n">
         <v>4</v>
@@ -44944,10 +44932,10 @@
         <v>0</v>
       </c>
       <c r="E1349" t="n">
-        <v>1956.6</v>
+        <v>999.8000000000001</v>
       </c>
       <c r="F1349" t="n">
-        <v>11621.2</v>
+        <v>10664.4</v>
       </c>
       <c r="G1349" t="n">
         <v>8</v>
@@ -44974,13 +44962,13 @@
         </is>
       </c>
       <c r="D1350" t="n">
-        <v>188</v>
+        <v>94</v>
       </c>
       <c r="E1350" t="n">
-        <v>2350.4</v>
+        <v>1214.7</v>
       </c>
       <c r="F1350" t="n">
-        <v>13285.2</v>
+        <v>12149.5</v>
       </c>
       <c r="G1350" t="n">
         <v>1</v>
@@ -45007,13 +44995,13 @@
         </is>
       </c>
       <c r="D1351" t="n">
-        <v>123.2</v>
+        <v>61.6</v>
       </c>
       <c r="E1351" t="n">
-        <v>1849.6</v>
+        <v>952.3</v>
       </c>
       <c r="F1351" t="n">
-        <v>10683.5</v>
+        <v>9786.200000000001</v>
       </c>
       <c r="G1351" t="n">
         <v>5</v>
@@ -45040,13 +45028,13 @@
         </is>
       </c>
       <c r="D1352" t="n">
-        <v>117.2</v>
+        <v>58.6</v>
       </c>
       <c r="E1352" t="n">
-        <v>2173.4</v>
+        <v>1112.2</v>
       </c>
       <c r="F1352" t="n">
-        <v>11777.5</v>
+        <v>10716.3</v>
       </c>
       <c r="G1352" t="n">
         <v>7</v>
@@ -45073,13 +45061,13 @@
         </is>
       </c>
       <c r="D1353" t="n">
-        <v>179</v>
+        <v>89.5</v>
       </c>
       <c r="E1353" t="n">
-        <v>2196.6</v>
+        <v>1132.8</v>
       </c>
       <c r="F1353" t="n">
-        <v>9731.6</v>
+        <v>8667.799999999999</v>
       </c>
       <c r="G1353" t="n">
         <v>2</v>
@@ -45106,13 +45094,13 @@
         </is>
       </c>
       <c r="D1354" t="n">
-        <v>133.4</v>
+        <v>66.7</v>
       </c>
       <c r="E1354" t="n">
-        <v>2227</v>
+        <v>1134</v>
       </c>
       <c r="F1354" t="n">
-        <v>12938.1</v>
+        <v>11845.1</v>
       </c>
       <c r="G1354" t="n">
         <v>4</v>
@@ -45139,13 +45127,13 @@
         </is>
       </c>
       <c r="D1355" t="n">
-        <v>71.59999999999999</v>
+        <v>45.8</v>
       </c>
       <c r="E1355" t="n">
-        <v>2325.6</v>
+        <v>1188.8</v>
       </c>
       <c r="F1355" t="n">
-        <v>13016.6</v>
+        <v>11879.8</v>
       </c>
       <c r="G1355" t="n">
         <v>8</v>
@@ -45172,13 +45160,13 @@
         </is>
       </c>
       <c r="D1356" t="n">
-        <v>118.4</v>
+        <v>59.2</v>
       </c>
       <c r="E1356" t="n">
-        <v>2297</v>
+        <v>1184</v>
       </c>
       <c r="F1356" t="n">
-        <v>12162.1</v>
+        <v>11049.1</v>
       </c>
       <c r="G1356" t="n">
         <v>6</v>
@@ -45205,13 +45193,13 @@
         </is>
       </c>
       <c r="D1357" t="n">
-        <v>164.4</v>
+        <v>82.2</v>
       </c>
       <c r="E1357" t="n">
-        <v>2121</v>
+        <v>1082</v>
       </c>
       <c r="F1357" t="n">
-        <v>11785.6</v>
+        <v>10746.6</v>
       </c>
       <c r="G1357" t="n">
         <v>2</v>
@@ -45238,13 +45226,13 @@
         </is>
       </c>
       <c r="D1358" t="n">
-        <v>126</v>
+        <v>63</v>
       </c>
       <c r="E1358" t="n">
-        <v>2476.4</v>
+        <v>1277.7</v>
       </c>
       <c r="F1358" t="n">
-        <v>13411.2</v>
+        <v>12212.5</v>
       </c>
       <c r="G1358" t="n">
         <v>5</v>
@@ -45271,13 +45259,13 @@
         </is>
       </c>
       <c r="D1359" t="n">
-        <v>113.2</v>
+        <v>56.6</v>
       </c>
       <c r="E1359" t="n">
-        <v>1962.8</v>
+        <v>1008.9</v>
       </c>
       <c r="F1359" t="n">
-        <v>10796.7</v>
+        <v>9842.799999999999</v>
       </c>
       <c r="G1359" t="n">
         <v>7</v>
@@ -45304,13 +45292,13 @@
         </is>
       </c>
       <c r="D1360" t="n">
-        <v>157.2</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="E1360" t="n">
-        <v>2330.6</v>
+        <v>1190.8</v>
       </c>
       <c r="F1360" t="n">
-        <v>11934.7</v>
+        <v>10794.9</v>
       </c>
       <c r="G1360" t="n">
         <v>3</v>
@@ -45337,13 +45325,13 @@
         </is>
       </c>
       <c r="D1361" t="n">
-        <v>174.6</v>
+        <v>87.3</v>
       </c>
       <c r="E1361" t="n">
-        <v>2371.2</v>
+        <v>1220.1</v>
       </c>
       <c r="F1361" t="n">
-        <v>9906.200000000001</v>
+        <v>8755.1</v>
       </c>
       <c r="G1361" t="n">
         <v>1</v>
@@ -45370,13 +45358,13 @@
         </is>
       </c>
       <c r="D1362" t="n">
-        <v>141.6</v>
+        <v>70.8</v>
       </c>
       <c r="E1362" t="n">
-        <v>2368.6</v>
+        <v>1204.8</v>
       </c>
       <c r="F1362" t="n">
-        <v>13079.7</v>
+        <v>11915.9</v>
       </c>
       <c r="G1362" t="n">
         <v>4</v>
@@ -45403,13 +45391,13 @@
         </is>
       </c>
       <c r="D1363" t="n">
-        <v>153</v>
+        <v>76.5</v>
       </c>
       <c r="E1363" t="n">
-        <v>2478.6</v>
+        <v>1265.3</v>
       </c>
       <c r="F1363" t="n">
-        <v>13169.6</v>
+        <v>11956.3</v>
       </c>
       <c r="G1363" t="n">
         <v>2</v>
@@ -45436,19 +45424,19 @@
         </is>
       </c>
       <c r="D1364" t="n">
-        <v>150.4</v>
+        <v>75.2</v>
       </c>
       <c r="E1364" t="n">
-        <v>2447.4</v>
+        <v>1259.2</v>
       </c>
       <c r="F1364" t="n">
-        <v>12312.5</v>
+        <v>11124.3</v>
       </c>
       <c r="G1364" t="n">
         <v>3</v>
       </c>
       <c r="H1364" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I1364" t="n">
         <v>4</v>
@@ -45469,13 +45457,13 @@
         </is>
       </c>
       <c r="D1365" t="n">
-        <v>93.40000000000001</v>
+        <v>46.7</v>
       </c>
       <c r="E1365" t="n">
-        <v>2214.4</v>
+        <v>1128.7</v>
       </c>
       <c r="F1365" t="n">
-        <v>11879</v>
+        <v>10793.3</v>
       </c>
       <c r="G1365" t="n">
         <v>8</v>
@@ -45502,13 +45490,13 @@
         </is>
       </c>
       <c r="D1366" t="n">
-        <v>158.8</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="E1366" t="n">
-        <v>2635.2</v>
+        <v>1357.1</v>
       </c>
       <c r="F1366" t="n">
-        <v>13570</v>
+        <v>12291.9</v>
       </c>
       <c r="G1366" t="n">
         <v>1</v>
@@ -45535,13 +45523,13 @@
         </is>
       </c>
       <c r="D1367" t="n">
-        <v>113.2</v>
+        <v>56.59999999999999</v>
       </c>
       <c r="E1367" t="n">
-        <v>2076</v>
+        <v>1065.5</v>
       </c>
       <c r="F1367" t="n">
-        <v>10909.9</v>
+        <v>9899.4</v>
       </c>
       <c r="G1367" t="n">
         <v>6</v>
@@ -45568,19 +45556,19 @@
         </is>
       </c>
       <c r="D1368" t="n">
-        <v>130.4</v>
+        <v>65.2</v>
       </c>
       <c r="E1368" t="n">
-        <v>2461</v>
+        <v>1256</v>
       </c>
       <c r="F1368" t="n">
-        <v>12065.1</v>
+        <v>10860.1</v>
       </c>
       <c r="G1368" t="n">
         <v>5</v>
       </c>
       <c r="H1368" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I1368" t="n">
         <v>5</v>
@@ -45601,13 +45589,13 @@
         </is>
       </c>
       <c r="D1369" t="n">
-        <v>109.6</v>
+        <v>54.8</v>
       </c>
       <c r="E1369" t="n">
-        <v>2480.8</v>
+        <v>1274.9</v>
       </c>
       <c r="F1369" t="n">
-        <v>10015.8</v>
+        <v>8809.9</v>
       </c>
       <c r="G1369" t="n">
         <v>7</v>
@@ -45634,13 +45622,13 @@
         </is>
       </c>
       <c r="D1370" t="n">
-        <v>187.6</v>
+        <v>93.8</v>
       </c>
       <c r="E1370" t="n">
-        <v>2556.2</v>
+        <v>1298.6</v>
       </c>
       <c r="F1370" t="n">
-        <v>13267.3</v>
+        <v>12009.7</v>
       </c>
       <c r="G1370" t="n">
         <v>2</v>
@@ -45667,13 +45655,13 @@
         </is>
       </c>
       <c r="D1371" t="n">
-        <v>130.4</v>
+        <v>65.2</v>
       </c>
       <c r="E1371" t="n">
-        <v>2609</v>
+        <v>1330.5</v>
       </c>
       <c r="F1371" t="n">
-        <v>13300</v>
+        <v>12021.5</v>
       </c>
       <c r="G1371" t="n">
         <v>7</v>
@@ -45700,13 +45688,13 @@
         </is>
       </c>
       <c r="D1372" t="n">
-        <v>195.2</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="E1372" t="n">
-        <v>2642.6</v>
+        <v>1356.8</v>
       </c>
       <c r="F1372" t="n">
-        <v>12507.7</v>
+        <v>11221.9</v>
       </c>
       <c r="G1372" t="n">
         <v>1</v>
@@ -45733,13 +45721,13 @@
         </is>
       </c>
       <c r="D1373" t="n">
-        <v>126.6</v>
+        <v>63.3</v>
       </c>
       <c r="E1373" t="n">
-        <v>2341</v>
+        <v>1192</v>
       </c>
       <c r="F1373" t="n">
-        <v>12005.6</v>
+        <v>10856.6</v>
       </c>
       <c r="G1373" t="n">
         <v>8</v>
@@ -45766,13 +45754,13 @@
         </is>
       </c>
       <c r="D1374" t="n">
-        <v>158.6</v>
+        <v>79.3</v>
       </c>
       <c r="E1374" t="n">
-        <v>2793.8</v>
+        <v>1436.4</v>
       </c>
       <c r="F1374" t="n">
-        <v>13728.6</v>
+        <v>12371.2</v>
       </c>
       <c r="G1374" t="n">
         <v>5</v>
@@ -45799,13 +45787,13 @@
         </is>
       </c>
       <c r="D1375" t="n">
-        <v>163.4</v>
+        <v>81.7</v>
       </c>
       <c r="E1375" t="n">
-        <v>2239.4</v>
+        <v>1147.2</v>
       </c>
       <c r="F1375" t="n">
-        <v>11073.3</v>
+        <v>9981.1</v>
       </c>
       <c r="G1375" t="n">
         <v>4</v>
@@ -45832,13 +45820,13 @@
         </is>
       </c>
       <c r="D1376" t="n">
-        <v>134.8</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="E1376" t="n">
-        <v>2595.8</v>
+        <v>1323.4</v>
       </c>
       <c r="F1376" t="n">
-        <v>12199.9</v>
+        <v>10927.5</v>
       </c>
       <c r="G1376" t="n">
         <v>6</v>
@@ -45865,13 +45853,13 @@
         </is>
       </c>
       <c r="D1377" t="n">
-        <v>165.2</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="E1377" t="n">
-        <v>2646</v>
+        <v>1357.5</v>
       </c>
       <c r="F1377" t="n">
-        <v>10181</v>
+        <v>8892.5</v>
       </c>
       <c r="G1377" t="n">
         <v>3</v>
@@ -45898,13 +45886,13 @@
         </is>
       </c>
       <c r="D1378" t="n">
-        <v>201</v>
+        <v>100.5</v>
       </c>
       <c r="E1378" t="n">
-        <v>2757.2</v>
+        <v>1399.1</v>
       </c>
       <c r="F1378" t="n">
-        <v>13468.3</v>
+        <v>12110.2</v>
       </c>
       <c r="G1378" t="n">
         <v>1</v>
@@ -45931,19 +45919,19 @@
         </is>
       </c>
       <c r="D1379" t="n">
-        <v>160.6</v>
+        <v>80.3</v>
       </c>
       <c r="E1379" t="n">
-        <v>2769.6</v>
+        <v>1410.8</v>
       </c>
       <c r="F1379" t="n">
-        <v>13460.6</v>
+        <v>12101.8</v>
       </c>
       <c r="G1379" t="n">
         <v>2</v>
       </c>
       <c r="H1379" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I1379" t="n">
         <v>3</v>
@@ -45964,19 +45952,19 @@
         </is>
       </c>
       <c r="D1380" t="n">
-        <v>120.6</v>
+        <v>60.3</v>
       </c>
       <c r="E1380" t="n">
-        <v>2763.2</v>
+        <v>1417.1</v>
       </c>
       <c r="F1380" t="n">
-        <v>12628.3</v>
+        <v>11282.2</v>
       </c>
       <c r="G1380" t="n">
         <v>6</v>
       </c>
       <c r="H1380" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I1380" t="n">
         <v>4</v>
@@ -45997,13 +45985,13 @@
         </is>
       </c>
       <c r="D1381" t="n">
-        <v>135.2</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="E1381" t="n">
-        <v>2476.2</v>
+        <v>1259.6</v>
       </c>
       <c r="F1381" t="n">
-        <v>12140.8</v>
+        <v>10924.2</v>
       </c>
       <c r="G1381" t="n">
         <v>4</v>
@@ -46030,13 +46018,13 @@
         </is>
       </c>
       <c r="D1382" t="n">
-        <v>140.4</v>
+        <v>70.2</v>
       </c>
       <c r="E1382" t="n">
-        <v>2934.2</v>
+        <v>1506.6</v>
       </c>
       <c r="F1382" t="n">
-        <v>13869</v>
+        <v>12441.4</v>
       </c>
       <c r="G1382" t="n">
         <v>3</v>
@@ -46063,13 +46051,13 @@
         </is>
       </c>
       <c r="D1383" t="n">
-        <v>122.4</v>
+        <v>61.2</v>
       </c>
       <c r="E1383" t="n">
-        <v>2361.8</v>
+        <v>1208.4</v>
       </c>
       <c r="F1383" t="n">
-        <v>11195.7</v>
+        <v>10042.3</v>
       </c>
       <c r="G1383" t="n">
         <v>5</v>
@@ -46096,13 +46084,13 @@
         </is>
       </c>
       <c r="D1384" t="n">
-        <v>101.6</v>
+        <v>50.8</v>
       </c>
       <c r="E1384" t="n">
-        <v>2697.4</v>
+        <v>1374.2</v>
       </c>
       <c r="F1384" t="n">
-        <v>12301.5</v>
+        <v>10978.3</v>
       </c>
       <c r="G1384" t="n">
         <v>8</v>
@@ -46129,13 +46117,13 @@
         </is>
       </c>
       <c r="D1385" t="n">
-        <v>117.8</v>
+        <v>58.9</v>
       </c>
       <c r="E1385" t="n">
-        <v>2763.8</v>
+        <v>1416.4</v>
       </c>
       <c r="F1385" t="n">
-        <v>10298.8</v>
+        <v>8951.4</v>
       </c>
       <c r="G1385" t="n">
         <v>7</v>
@@ -46162,19 +46150,19 @@
         </is>
       </c>
       <c r="D1386" t="n">
-        <v>184</v>
+        <v>92</v>
       </c>
       <c r="E1386" t="n">
-        <v>2941.2</v>
+        <v>1491.1</v>
       </c>
       <c r="F1386" t="n">
-        <v>13652.3</v>
+        <v>12202.2</v>
       </c>
       <c r="G1386" t="n">
         <v>2</v>
       </c>
       <c r="H1386" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I1386" t="n">
         <v>2</v>
@@ -46195,19 +46183,19 @@
         </is>
       </c>
       <c r="D1387" t="n">
-        <v>154.4</v>
+        <v>77.2</v>
       </c>
       <c r="E1387" t="n">
-        <v>2924</v>
+        <v>1488</v>
       </c>
       <c r="F1387" t="n">
-        <v>13615</v>
+        <v>12179</v>
       </c>
       <c r="G1387" t="n">
         <v>4</v>
       </c>
       <c r="H1387" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I1387" t="n">
         <v>3</v>
@@ -46228,19 +46216,19 @@
         </is>
       </c>
       <c r="D1388" t="n">
-        <v>160.6</v>
+        <v>80.3</v>
       </c>
       <c r="E1388" t="n">
-        <v>2923.8</v>
+        <v>1497.4</v>
       </c>
       <c r="F1388" t="n">
-        <v>12788.9</v>
+        <v>11362.5</v>
       </c>
       <c r="G1388" t="n">
         <v>3</v>
       </c>
       <c r="H1388" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I1388" t="n">
         <v>4</v>
@@ -46261,13 +46249,13 @@
         </is>
       </c>
       <c r="D1389" t="n">
-        <v>101.2</v>
+        <v>50.6</v>
       </c>
       <c r="E1389" t="n">
-        <v>2577.4</v>
+        <v>1310.2</v>
       </c>
       <c r="F1389" t="n">
-        <v>12242</v>
+        <v>10974.8</v>
       </c>
       <c r="G1389" t="n">
         <v>7</v>
@@ -46294,13 +46282,13 @@
         </is>
       </c>
       <c r="D1390" t="n">
-        <v>153.4</v>
+        <v>76.7</v>
       </c>
       <c r="E1390" t="n">
-        <v>3087.6</v>
+        <v>1583.3</v>
       </c>
       <c r="F1390" t="n">
-        <v>14022.4</v>
+        <v>12518.1</v>
       </c>
       <c r="G1390" t="n">
         <v>5</v>
@@ -46327,13 +46315,13 @@
         </is>
       </c>
       <c r="D1391" t="n">
-        <v>97.40000000000001</v>
+        <v>48.7</v>
       </c>
       <c r="E1391" t="n">
-        <v>2459.2</v>
+        <v>1257.1</v>
       </c>
       <c r="F1391" t="n">
-        <v>11293.1</v>
+        <v>10091</v>
       </c>
       <c r="G1391" t="n">
         <v>8</v>
@@ -46360,13 +46348,13 @@
         </is>
       </c>
       <c r="D1392" t="n">
-        <v>185</v>
+        <v>92.5</v>
       </c>
       <c r="E1392" t="n">
-        <v>2882.4</v>
+        <v>1466.7</v>
       </c>
       <c r="F1392" t="n">
-        <v>12486.5</v>
+        <v>11070.8</v>
       </c>
       <c r="G1392" t="n">
         <v>1</v>
@@ -46393,19 +46381,19 @@
         </is>
       </c>
       <c r="D1393" t="n">
-        <v>146.2</v>
+        <v>73.10000000000001</v>
       </c>
       <c r="E1393" t="n">
-        <v>2910</v>
+        <v>1489.5</v>
       </c>
       <c r="F1393" t="n">
-        <v>10445</v>
+        <v>9024.5</v>
       </c>
       <c r="G1393" t="n">
         <v>6</v>
       </c>
       <c r="H1393" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I1393" t="n">
         <v>8</v>
@@ -46426,19 +46414,19 @@
         </is>
       </c>
       <c r="D1394" t="n">
-        <v>151.2</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="E1394" t="n">
-        <v>3092.4</v>
+        <v>1566.7</v>
       </c>
       <c r="F1394" t="n">
-        <v>13803.5</v>
+        <v>12277.8</v>
       </c>
       <c r="G1394" t="n">
         <v>3</v>
       </c>
       <c r="H1394" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I1394" t="n">
         <v>2</v>
@@ -46459,19 +46447,19 @@
         </is>
       </c>
       <c r="D1395" t="n">
-        <v>168.2</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="E1395" t="n">
-        <v>3092.2</v>
+        <v>1572.1</v>
       </c>
       <c r="F1395" t="n">
-        <v>13783.2</v>
+        <v>12263.1</v>
       </c>
       <c r="G1395" t="n">
         <v>1</v>
       </c>
       <c r="H1395" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I1395" t="n">
         <v>3</v>
@@ -46492,13 +46480,13 @@
         </is>
       </c>
       <c r="D1396" t="n">
-        <v>118.6</v>
+        <v>59.3</v>
       </c>
       <c r="E1396" t="n">
-        <v>3042.4</v>
+        <v>1556.7</v>
       </c>
       <c r="F1396" t="n">
-        <v>12907.5</v>
+        <v>11421.8</v>
       </c>
       <c r="G1396" t="n">
         <v>8</v>
@@ -46525,13 +46513,13 @@
         </is>
       </c>
       <c r="D1397" t="n">
-        <v>143</v>
+        <v>71.5</v>
       </c>
       <c r="E1397" t="n">
-        <v>2720.4</v>
+        <v>1381.7</v>
       </c>
       <c r="F1397" t="n">
-        <v>12385</v>
+        <v>11046.3</v>
       </c>
       <c r="G1397" t="n">
         <v>6</v>
@@ -46558,13 +46546,13 @@
         </is>
       </c>
       <c r="D1398" t="n">
-        <v>150.8</v>
+        <v>75.39999999999999</v>
       </c>
       <c r="E1398" t="n">
-        <v>3238.4</v>
+        <v>1658.7</v>
       </c>
       <c r="F1398" t="n">
-        <v>14173.2</v>
+        <v>12593.5</v>
       </c>
       <c r="G1398" t="n">
         <v>4</v>
@@ -46591,13 +46579,13 @@
         </is>
       </c>
       <c r="D1399" t="n">
-        <v>125.4</v>
+        <v>62.7</v>
       </c>
       <c r="E1399" t="n">
-        <v>2584.6</v>
+        <v>1319.8</v>
       </c>
       <c r="F1399" t="n">
-        <v>11418.5</v>
+        <v>10153.7</v>
       </c>
       <c r="G1399" t="n">
         <v>7</v>
@@ -46624,13 +46612,13 @@
         </is>
       </c>
       <c r="D1400" t="n">
-        <v>144</v>
+        <v>72</v>
       </c>
       <c r="E1400" t="n">
-        <v>3026.4</v>
+        <v>1538.7</v>
       </c>
       <c r="F1400" t="n">
-        <v>12630.5</v>
+        <v>11142.8</v>
       </c>
       <c r="G1400" t="n">
         <v>5</v>
@@ -46657,19 +46645,19 @@
         </is>
       </c>
       <c r="D1401" t="n">
-        <v>158.2</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="E1401" t="n">
-        <v>3068.2</v>
+        <v>1568.6</v>
       </c>
       <c r="F1401" t="n">
-        <v>10603.2</v>
+        <v>9103.6</v>
       </c>
       <c r="G1401" t="n">
         <v>2</v>
       </c>
       <c r="H1401" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1401" t="n">
         <v>8</v>
@@ -46690,19 +46678,19 @@
         </is>
       </c>
       <c r="D1402" t="n">
-        <v>146.4</v>
+        <v>73.2</v>
       </c>
       <c r="E1402" t="n">
-        <v>3238.8</v>
+        <v>1639.9</v>
       </c>
       <c r="F1402" t="n">
-        <v>13949.9</v>
+        <v>12351</v>
       </c>
       <c r="G1402" t="n">
         <v>2</v>
       </c>
       <c r="H1402" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I1402" t="n">
         <v>2</v>
@@ -46723,19 +46711,19 @@
         </is>
       </c>
       <c r="D1403" t="n">
-        <v>125.4</v>
+        <v>62.7</v>
       </c>
       <c r="E1403" t="n">
-        <v>3217.6</v>
+        <v>1634.8</v>
       </c>
       <c r="F1403" t="n">
-        <v>13908.6</v>
+        <v>12325.8</v>
       </c>
       <c r="G1403" t="n">
         <v>5</v>
       </c>
       <c r="H1403" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1403" t="n">
         <v>3</v>
@@ -46756,13 +46744,13 @@
         </is>
       </c>
       <c r="D1404" t="n">
-        <v>98.40000000000001</v>
+        <v>49.2</v>
       </c>
       <c r="E1404" t="n">
-        <v>3140.8</v>
+        <v>1605.9</v>
       </c>
       <c r="F1404" t="n">
-        <v>13005.9</v>
+        <v>11471</v>
       </c>
       <c r="G1404" t="n">
         <v>6</v>
@@ -46789,13 +46777,13 @@
         </is>
       </c>
       <c r="D1405" t="n">
-        <v>87.8</v>
+        <v>43.9</v>
       </c>
       <c r="E1405" t="n">
-        <v>2808.2</v>
+        <v>1425.6</v>
       </c>
       <c r="F1405" t="n">
-        <v>12472.8</v>
+        <v>11090.2</v>
       </c>
       <c r="G1405" t="n">
         <v>7</v>
@@ -46822,13 +46810,13 @@
         </is>
       </c>
       <c r="D1406" t="n">
-        <v>142.4</v>
+        <v>71.2</v>
       </c>
       <c r="E1406" t="n">
-        <v>3380.8</v>
+        <v>1729.9</v>
       </c>
       <c r="F1406" t="n">
-        <v>14315.6</v>
+        <v>12664.7</v>
       </c>
       <c r="G1406" t="n">
         <v>3</v>
@@ -46855,13 +46843,13 @@
         </is>
       </c>
       <c r="D1407" t="n">
-        <v>128.2</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="E1407" t="n">
-        <v>2712.8</v>
+        <v>1383.9</v>
       </c>
       <c r="F1407" t="n">
-        <v>11546.7</v>
+        <v>10217.8</v>
       </c>
       <c r="G1407" t="n">
         <v>4</v>
@@ -46888,13 +46876,13 @@
         </is>
       </c>
       <c r="D1408" t="n">
-        <v>85.8</v>
+        <v>42.9</v>
       </c>
       <c r="E1408" t="n">
-        <v>3112.2</v>
+        <v>1581.6</v>
       </c>
       <c r="F1408" t="n">
-        <v>12716.3</v>
+        <v>11185.7</v>
       </c>
       <c r="G1408" t="n">
         <v>8</v>
@@ -46921,19 +46909,19 @@
         </is>
       </c>
       <c r="D1409" t="n">
-        <v>147.6</v>
+        <v>73.8</v>
       </c>
       <c r="E1409" t="n">
-        <v>3215.8</v>
+        <v>1642.4</v>
       </c>
       <c r="F1409" t="n">
-        <v>10750.8</v>
+        <v>9177.4</v>
       </c>
       <c r="G1409" t="n">
         <v>1</v>
       </c>
       <c r="H1409" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I1409" t="n">
         <v>8</v>
@@ -46954,13 +46942,13 @@
         </is>
       </c>
       <c r="D1410" t="n">
-        <v>158.6</v>
+        <v>79.3</v>
       </c>
       <c r="E1410" t="n">
-        <v>3397.4</v>
+        <v>1719.2</v>
       </c>
       <c r="F1410" t="n">
-        <v>14108.5</v>
+        <v>12430.3</v>
       </c>
       <c r="G1410" t="n">
         <v>1</v>
@@ -46987,19 +46975,19 @@
         </is>
       </c>
       <c r="D1411" t="n">
-        <v>124.6</v>
+        <v>62.3</v>
       </c>
       <c r="E1411" t="n">
-        <v>3342.2</v>
+        <v>1697.1</v>
       </c>
       <c r="F1411" t="n">
-        <v>14033.2</v>
+        <v>12388.1</v>
       </c>
       <c r="G1411" t="n">
         <v>4</v>
       </c>
       <c r="H1411" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1411" t="n">
         <v>3</v>
@@ -47020,13 +47008,13 @@
         </is>
       </c>
       <c r="D1412" t="n">
-        <v>100.8</v>
+        <v>50.4</v>
       </c>
       <c r="E1412" t="n">
-        <v>3241.6</v>
+        <v>1656.3</v>
       </c>
       <c r="F1412" t="n">
-        <v>13106.7</v>
+        <v>11521.4</v>
       </c>
       <c r="G1412" t="n">
         <v>7</v>
@@ -47053,13 +47041,13 @@
         </is>
       </c>
       <c r="D1413" t="n">
-        <v>97.59999999999999</v>
+        <v>48.8</v>
       </c>
       <c r="E1413" t="n">
-        <v>2905.8</v>
+        <v>1474.4</v>
       </c>
       <c r="F1413" t="n">
-        <v>12570.4</v>
+        <v>11139</v>
       </c>
       <c r="G1413" t="n">
         <v>8</v>
@@ -47086,13 +47074,13 @@
         </is>
       </c>
       <c r="D1414" t="n">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="E1414" t="n">
-        <v>3530.8</v>
+        <v>1804.9</v>
       </c>
       <c r="F1414" t="n">
-        <v>14465.6</v>
+        <v>12739.7</v>
       </c>
       <c r="G1414" t="n">
         <v>2</v>
@@ -47119,13 +47107,13 @@
         </is>
       </c>
       <c r="D1415" t="n">
-        <v>129</v>
+        <v>64.5</v>
       </c>
       <c r="E1415" t="n">
-        <v>2841.8</v>
+        <v>1448.4</v>
       </c>
       <c r="F1415" t="n">
-        <v>11675.7</v>
+        <v>10282.3</v>
       </c>
       <c r="G1415" t="n">
         <v>3</v>
@@ -47152,13 +47140,13 @@
         </is>
       </c>
       <c r="D1416" t="n">
-        <v>119.4</v>
+        <v>59.7</v>
       </c>
       <c r="E1416" t="n">
-        <v>3231.6</v>
+        <v>1641.3</v>
       </c>
       <c r="F1416" t="n">
-        <v>12835.7</v>
+        <v>11245.4</v>
       </c>
       <c r="G1416" t="n">
         <v>5</v>
@@ -47185,19 +47173,19 @@
         </is>
       </c>
       <c r="D1417" t="n">
-        <v>115.4</v>
+        <v>57.7</v>
       </c>
       <c r="E1417" t="n">
-        <v>3331.2</v>
+        <v>1700.1</v>
       </c>
       <c r="F1417" t="n">
-        <v>10866.2</v>
+        <v>9235.1</v>
       </c>
       <c r="G1417" t="n">
         <v>6</v>
       </c>
       <c r="H1417" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1417" t="n">
         <v>8</v>
@@ -47218,13 +47206,13 @@
         </is>
       </c>
       <c r="D1418" t="n">
-        <v>172.6</v>
+        <v>86.3</v>
       </c>
       <c r="E1418" t="n">
-        <v>3570</v>
+        <v>1805.5</v>
       </c>
       <c r="F1418" t="n">
-        <v>14281.1</v>
+        <v>12516.6</v>
       </c>
       <c r="G1418" t="n">
         <v>2</v>
@@ -47251,13 +47239,13 @@
         </is>
       </c>
       <c r="D1419" t="n">
-        <v>151.2</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="E1419" t="n">
-        <v>3493.4</v>
+        <v>1772.7</v>
       </c>
       <c r="F1419" t="n">
-        <v>14184.4</v>
+        <v>12463.7</v>
       </c>
       <c r="G1419" t="n">
         <v>3</v>
@@ -47284,13 +47272,13 @@
         </is>
       </c>
       <c r="D1420" t="n">
-        <v>101.8</v>
+        <v>50.9</v>
       </c>
       <c r="E1420" t="n">
-        <v>3343.4</v>
+        <v>1707.2</v>
       </c>
       <c r="F1420" t="n">
-        <v>13208.5</v>
+        <v>11572.3</v>
       </c>
       <c r="G1420" t="n">
         <v>8</v>
@@ -47317,13 +47305,13 @@
         </is>
       </c>
       <c r="D1421" t="n">
-        <v>130.6</v>
+        <v>65.3</v>
       </c>
       <c r="E1421" t="n">
-        <v>3036.4</v>
+        <v>1539.7</v>
       </c>
       <c r="F1421" t="n">
-        <v>12701</v>
+        <v>11204.3</v>
       </c>
       <c r="G1421" t="n">
         <v>4</v>
@@ -47350,13 +47338,13 @@
         </is>
       </c>
       <c r="D1422" t="n">
-        <v>116.8</v>
+        <v>58.4</v>
       </c>
       <c r="E1422" t="n">
-        <v>3647.6</v>
+        <v>1863.3</v>
       </c>
       <c r="F1422" t="n">
-        <v>14582.4</v>
+        <v>12798.1</v>
       </c>
       <c r="G1422" t="n">
         <v>6</v>
@@ -47383,13 +47371,13 @@
         </is>
       </c>
       <c r="D1423" t="n">
-        <v>117.2</v>
+        <v>58.6</v>
       </c>
       <c r="E1423" t="n">
-        <v>2959</v>
+        <v>1507</v>
       </c>
       <c r="F1423" t="n">
-        <v>11792.9</v>
+        <v>10340.9</v>
       </c>
       <c r="G1423" t="n">
         <v>5</v>
@@ -47416,13 +47404,13 @@
         </is>
       </c>
       <c r="D1424" t="n">
-        <v>110.6</v>
+        <v>55.3</v>
       </c>
       <c r="E1424" t="n">
-        <v>3342.2</v>
+        <v>1696.6</v>
       </c>
       <c r="F1424" t="n">
-        <v>12946.3</v>
+        <v>11300.7</v>
       </c>
       <c r="G1424" t="n">
         <v>7</v>
@@ -47449,13 +47437,13 @@
         </is>
       </c>
       <c r="D1425" t="n">
-        <v>192</v>
+        <v>96</v>
       </c>
       <c r="E1425" t="n">
-        <v>3523.2</v>
+        <v>1796.1</v>
       </c>
       <c r="F1425" t="n">
-        <v>11058.2</v>
+        <v>9331.1</v>
       </c>
       <c r="G1425" t="n">
         <v>1</v>
@@ -47482,13 +47470,13 @@
         </is>
       </c>
       <c r="D1426" t="n">
-        <v>169</v>
+        <v>84.5</v>
       </c>
       <c r="E1426" t="n">
-        <v>3739</v>
+        <v>1890</v>
       </c>
       <c r="F1426" t="n">
-        <v>14450.1</v>
+        <v>12601.1</v>
       </c>
       <c r="G1426" t="n">
         <v>1</v>
@@ -47515,13 +47503,13 @@
         </is>
       </c>
       <c r="D1427" t="n">
-        <v>133.2</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="E1427" t="n">
-        <v>3626.6</v>
+        <v>1839.3</v>
       </c>
       <c r="F1427" t="n">
-        <v>14317.6</v>
+        <v>12530.3</v>
       </c>
       <c r="G1427" t="n">
         <v>4</v>
@@ -47548,19 +47536,19 @@
         </is>
       </c>
       <c r="D1428" t="n">
-        <v>120.2</v>
+        <v>60.1</v>
       </c>
       <c r="E1428" t="n">
-        <v>3463.6</v>
+        <v>1767.3</v>
       </c>
       <c r="F1428" t="n">
-        <v>13328.7</v>
+        <v>11632.4</v>
       </c>
       <c r="G1428" t="n">
         <v>6</v>
       </c>
       <c r="H1428" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I1428" t="n">
         <v>4</v>
@@ -47581,13 +47569,13 @@
         </is>
       </c>
       <c r="D1429" t="n">
-        <v>148.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="E1429" t="n">
-        <v>3184.6</v>
+        <v>1613.8</v>
       </c>
       <c r="F1429" t="n">
-        <v>12849.2</v>
+        <v>11278.4</v>
       </c>
       <c r="G1429" t="n">
         <v>3</v>
@@ -47614,13 +47602,13 @@
         </is>
       </c>
       <c r="D1430" t="n">
-        <v>114.8</v>
+        <v>57.4</v>
       </c>
       <c r="E1430" t="n">
-        <v>3762.4</v>
+        <v>1920.7</v>
       </c>
       <c r="F1430" t="n">
-        <v>14697.2</v>
+        <v>12855.5</v>
       </c>
       <c r="G1430" t="n">
         <v>7</v>
@@ -47650,10 +47638,10 @@
         <v>0</v>
       </c>
       <c r="E1431" t="n">
-        <v>2959</v>
+        <v>1507</v>
       </c>
       <c r="F1431" t="n">
-        <v>11792.9</v>
+        <v>10340.9</v>
       </c>
       <c r="G1431" t="n">
         <v>8</v>
@@ -47680,19 +47668,19 @@
         </is>
       </c>
       <c r="D1432" t="n">
-        <v>131.8</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="E1432" t="n">
-        <v>3474</v>
+        <v>1762.5</v>
       </c>
       <c r="F1432" t="n">
-        <v>13078.1</v>
+        <v>11366.6</v>
       </c>
       <c r="G1432" t="n">
         <v>5</v>
       </c>
       <c r="H1432" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I1432" t="n">
         <v>5</v>
@@ -47713,13 +47701,13 @@
         </is>
       </c>
       <c r="D1433" t="n">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="E1433" t="n">
-        <v>3675.2</v>
+        <v>1872.1</v>
       </c>
       <c r="F1433" t="n">
-        <v>11210.2</v>
+        <v>9407.1</v>
       </c>
       <c r="G1433" t="n">
         <v>2</v>
@@ -47746,19 +47734,19 @@
         </is>
       </c>
       <c r="D1434" t="n">
-        <v>146.2</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="E1434" t="n">
-        <v>3885.2</v>
+        <v>1963.1</v>
       </c>
       <c r="F1434" t="n">
-        <v>14596.3</v>
+        <v>12674.2</v>
       </c>
       <c r="G1434" t="n">
         <v>6</v>
       </c>
       <c r="H1434" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I1434" t="n">
         <v>2</v>
@@ -47779,13 +47767,13 @@
         </is>
       </c>
       <c r="D1435" t="n">
-        <v>185.8</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="E1435" t="n">
-        <v>3812.4</v>
+        <v>1932.2</v>
       </c>
       <c r="F1435" t="n">
-        <v>14503.4</v>
+        <v>12623.2</v>
       </c>
       <c r="G1435" t="n">
         <v>2</v>
@@ -47812,13 +47800,13 @@
         </is>
       </c>
       <c r="D1436" t="n">
-        <v>103.2</v>
+        <v>51.6</v>
       </c>
       <c r="E1436" t="n">
-        <v>3566.8</v>
+        <v>1818.9</v>
       </c>
       <c r="F1436" t="n">
-        <v>13431.9</v>
+        <v>11684</v>
       </c>
       <c r="G1436" t="n">
         <v>8</v>
@@ -47845,13 +47833,13 @@
         </is>
       </c>
       <c r="D1437" t="n">
-        <v>124.2</v>
+        <v>62.09999999999999</v>
       </c>
       <c r="E1437" t="n">
-        <v>3308.8</v>
+        <v>1675.9</v>
       </c>
       <c r="F1437" t="n">
-        <v>12973.4</v>
+        <v>11340.5</v>
       </c>
       <c r="G1437" t="n">
         <v>7</v>
@@ -47878,13 +47866,13 @@
         </is>
       </c>
       <c r="D1438" t="n">
-        <v>173.4</v>
+        <v>86.7</v>
       </c>
       <c r="E1438" t="n">
-        <v>3935.8</v>
+        <v>2007.4</v>
       </c>
       <c r="F1438" t="n">
-        <v>14870.6</v>
+        <v>12942.2</v>
       </c>
       <c r="G1438" t="n">
         <v>4</v>
@@ -47911,13 +47899,13 @@
         </is>
       </c>
       <c r="D1439" t="n">
-        <v>176.4</v>
+        <v>88.2</v>
       </c>
       <c r="E1439" t="n">
-        <v>3135.4</v>
+        <v>1595.2</v>
       </c>
       <c r="F1439" t="n">
-        <v>11969.3</v>
+        <v>10429.1</v>
       </c>
       <c r="G1439" t="n">
         <v>3</v>
@@ -47944,13 +47932,13 @@
         </is>
       </c>
       <c r="D1440" t="n">
-        <v>146.6</v>
+        <v>73.3</v>
       </c>
       <c r="E1440" t="n">
-        <v>3620.6</v>
+        <v>1835.8</v>
       </c>
       <c r="F1440" t="n">
-        <v>13224.7</v>
+        <v>11439.9</v>
       </c>
       <c r="G1440" t="n">
         <v>5</v>
@@ -47977,19 +47965,19 @@
         </is>
       </c>
       <c r="D1441" t="n">
-        <v>201.8</v>
+        <v>100.9</v>
       </c>
       <c r="E1441" t="n">
-        <v>3877</v>
+        <v>1973</v>
       </c>
       <c r="F1441" t="n">
-        <v>11412</v>
+        <v>9508</v>
       </c>
       <c r="G1441" t="n">
         <v>1</v>
       </c>
       <c r="H1441" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I1441" t="n">
         <v>8</v>
@@ -48010,19 +47998,19 @@
         </is>
       </c>
       <c r="D1442" t="n">
-        <v>165</v>
+        <v>82.5</v>
       </c>
       <c r="E1442" t="n">
-        <v>4050.2</v>
+        <v>2045.6</v>
       </c>
       <c r="F1442" t="n">
-        <v>14761.3</v>
+        <v>12756.7</v>
       </c>
       <c r="G1442" t="n">
         <v>3</v>
       </c>
       <c r="H1442" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1442" t="n">
         <v>2</v>
@@ -48043,13 +48031,13 @@
         </is>
       </c>
       <c r="D1443" t="n">
-        <v>147</v>
+        <v>73.5</v>
       </c>
       <c r="E1443" t="n">
-        <v>3959.4</v>
+        <v>2005.7</v>
       </c>
       <c r="F1443" t="n">
-        <v>14650.4</v>
+        <v>12696.7</v>
       </c>
       <c r="G1443" t="n">
         <v>4</v>
@@ -48076,13 +48064,13 @@
         </is>
       </c>
       <c r="D1444" t="n">
-        <v>229</v>
+        <v>114.5</v>
       </c>
       <c r="E1444" t="n">
-        <v>3795.8</v>
+        <v>1933.4</v>
       </c>
       <c r="F1444" t="n">
-        <v>13660.9</v>
+        <v>11798.5</v>
       </c>
       <c r="G1444" t="n">
         <v>1</v>
@@ -48109,13 +48097,13 @@
         </is>
       </c>
       <c r="D1445" t="n">
-        <v>171.8</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="E1445" t="n">
-        <v>3480.6</v>
+        <v>1761.8</v>
       </c>
       <c r="F1445" t="n">
-        <v>13145.2</v>
+        <v>11426.4</v>
       </c>
       <c r="G1445" t="n">
         <v>2</v>
@@ -48142,19 +48130,19 @@
         </is>
       </c>
       <c r="D1446" t="n">
-        <v>97.2</v>
+        <v>48.6</v>
       </c>
       <c r="E1446" t="n">
-        <v>4033</v>
+        <v>2056</v>
       </c>
       <c r="F1446" t="n">
-        <v>14967.8</v>
+        <v>12990.8</v>
       </c>
       <c r="G1446" t="n">
         <v>6</v>
       </c>
       <c r="H1446" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1446" t="n">
         <v>1</v>
@@ -48175,13 +48163,13 @@
         </is>
       </c>
       <c r="D1447" t="n">
-        <v>105.6</v>
+        <v>52.8</v>
       </c>
       <c r="E1447" t="n">
-        <v>3241</v>
+        <v>1648</v>
       </c>
       <c r="F1447" t="n">
-        <v>12074.9</v>
+        <v>10481.9</v>
       </c>
       <c r="G1447" t="n">
         <v>5</v>
@@ -48208,13 +48196,13 @@
         </is>
       </c>
       <c r="D1448" t="n">
-        <v>95.8</v>
+        <v>47.9</v>
       </c>
       <c r="E1448" t="n">
-        <v>3716.4</v>
+        <v>1883.7</v>
       </c>
       <c r="F1448" t="n">
-        <v>13320.5</v>
+        <v>11487.8</v>
       </c>
       <c r="G1448" t="n">
         <v>7</v>
@@ -48241,13 +48229,13 @@
         </is>
       </c>
       <c r="D1449" t="n">
-        <v>86.59999999999999</v>
+        <v>43.3</v>
       </c>
       <c r="E1449" t="n">
-        <v>3963.6</v>
+        <v>2016.3</v>
       </c>
       <c r="F1449" t="n">
-        <v>11498.6</v>
+        <v>9551.299999999999</v>
       </c>
       <c r="G1449" t="n">
         <v>8</v>
@@ -48274,13 +48262,13 @@
         </is>
       </c>
       <c r="D1450" t="n">
-        <v>133</v>
+        <v>66.5</v>
       </c>
       <c r="E1450" t="n">
-        <v>4183.2</v>
+        <v>2112.1</v>
       </c>
       <c r="F1450" t="n">
-        <v>14894.3</v>
+        <v>12823.2</v>
       </c>
       <c r="G1450" t="n">
         <v>5</v>
@@ -48307,13 +48295,13 @@
         </is>
       </c>
       <c r="D1451" t="n">
-        <v>131</v>
+        <v>65.5</v>
       </c>
       <c r="E1451" t="n">
-        <v>4090.4</v>
+        <v>2071.2</v>
       </c>
       <c r="F1451" t="n">
-        <v>14781.4</v>
+        <v>12762.2</v>
       </c>
       <c r="G1451" t="n">
         <v>7</v>
@@ -48340,13 +48328,13 @@
         </is>
       </c>
       <c r="D1452" t="n">
-        <v>167.8</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="E1452" t="n">
-        <v>3963.6</v>
+        <v>2017.3</v>
       </c>
       <c r="F1452" t="n">
-        <v>13828.7</v>
+        <v>11882.4</v>
       </c>
       <c r="G1452" t="n">
         <v>3</v>
@@ -48373,13 +48361,13 @@
         </is>
       </c>
       <c r="D1453" t="n">
-        <v>132.8</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="E1453" t="n">
-        <v>3613.4</v>
+        <v>1828.2</v>
       </c>
       <c r="F1453" t="n">
-        <v>13278</v>
+        <v>11492.8</v>
       </c>
       <c r="G1453" t="n">
         <v>6</v>
@@ -48406,13 +48394,13 @@
         </is>
       </c>
       <c r="D1454" t="n">
-        <v>214</v>
+        <v>107</v>
       </c>
       <c r="E1454" t="n">
-        <v>4247</v>
+        <v>2163</v>
       </c>
       <c r="F1454" t="n">
-        <v>15181.8</v>
+        <v>13097.8</v>
       </c>
       <c r="G1454" t="n">
         <v>1</v>
@@ -48439,13 +48427,13 @@
         </is>
       </c>
       <c r="D1455" t="n">
-        <v>93</v>
+        <v>46.5</v>
       </c>
       <c r="E1455" t="n">
-        <v>3334</v>
+        <v>1694.5</v>
       </c>
       <c r="F1455" t="n">
-        <v>12167.9</v>
+        <v>10528.4</v>
       </c>
       <c r="G1455" t="n">
         <v>8</v>
@@ -48472,13 +48460,13 @@
         </is>
       </c>
       <c r="D1456" t="n">
-        <v>134.8</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="E1456" t="n">
-        <v>3851.2</v>
+        <v>1951.1</v>
       </c>
       <c r="F1456" t="n">
-        <v>13455.3</v>
+        <v>11555.2</v>
       </c>
       <c r="G1456" t="n">
         <v>4</v>
@@ -48505,13 +48493,13 @@
         </is>
       </c>
       <c r="D1457" t="n">
-        <v>171.2</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="E1457" t="n">
-        <v>4134.8</v>
+        <v>2101.9</v>
       </c>
       <c r="F1457" t="n">
-        <v>11669.8</v>
+        <v>9636.9</v>
       </c>
       <c r="G1457" t="n">
         <v>2</v>
@@ -48538,19 +48526,19 @@
         </is>
       </c>
       <c r="D1458" t="n">
-        <v>201.2</v>
+        <v>100.6</v>
       </c>
       <c r="E1458" t="n">
-        <v>4384.4</v>
+        <v>2212.7</v>
       </c>
       <c r="F1458" t="n">
-        <v>15095.5</v>
+        <v>12923.8</v>
       </c>
       <c r="G1458" t="n">
         <v>1</v>
       </c>
       <c r="H1458" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1458" t="n">
         <v>2</v>
@@ -48571,13 +48559,13 @@
         </is>
       </c>
       <c r="D1459" t="n">
-        <v>131.8</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="E1459" t="n">
-        <v>4222.2</v>
+        <v>2137.1</v>
       </c>
       <c r="F1459" t="n">
-        <v>14913.2</v>
+        <v>12828.1</v>
       </c>
       <c r="G1459" t="n">
         <v>5</v>
@@ -48604,13 +48592,13 @@
         </is>
       </c>
       <c r="D1460" t="n">
-        <v>141.6</v>
+        <v>70.8</v>
       </c>
       <c r="E1460" t="n">
-        <v>4105.2</v>
+        <v>2088.1</v>
       </c>
       <c r="F1460" t="n">
-        <v>13970.3</v>
+        <v>11953.2</v>
       </c>
       <c r="G1460" t="n">
         <v>4</v>
@@ -48637,13 +48625,13 @@
         </is>
       </c>
       <c r="D1461" t="n">
-        <v>121</v>
+        <v>60.5</v>
       </c>
       <c r="E1461" t="n">
-        <v>3734.4</v>
+        <v>1888.7</v>
       </c>
       <c r="F1461" t="n">
-        <v>13399</v>
+        <v>11553.3</v>
       </c>
       <c r="G1461" t="n">
         <v>7</v>
@@ -48670,19 +48658,19 @@
         </is>
       </c>
       <c r="D1462" t="n">
-        <v>129.2</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="E1462" t="n">
-        <v>4376.2</v>
+        <v>2227.6</v>
       </c>
       <c r="F1462" t="n">
-        <v>15311</v>
+        <v>13162.4</v>
       </c>
       <c r="G1462" t="n">
         <v>6</v>
       </c>
       <c r="H1462" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1462" t="n">
         <v>1</v>
@@ -48703,13 +48691,13 @@
         </is>
       </c>
       <c r="D1463" t="n">
-        <v>147.4</v>
+        <v>73.7</v>
       </c>
       <c r="E1463" t="n">
-        <v>3481.4</v>
+        <v>1768.2</v>
       </c>
       <c r="F1463" t="n">
-        <v>12315.3</v>
+        <v>10602.1</v>
       </c>
       <c r="G1463" t="n">
         <v>3</v>
@@ -48736,13 +48724,13 @@
         </is>
       </c>
       <c r="D1464" t="n">
-        <v>110.4</v>
+        <v>55.2</v>
       </c>
       <c r="E1464" t="n">
-        <v>3961.6</v>
+        <v>2006.3</v>
       </c>
       <c r="F1464" t="n">
-        <v>13565.7</v>
+        <v>11610.4</v>
       </c>
       <c r="G1464" t="n">
         <v>8</v>
@@ -48769,13 +48757,13 @@
         </is>
       </c>
       <c r="D1465" t="n">
-        <v>176</v>
+        <v>88</v>
       </c>
       <c r="E1465" t="n">
-        <v>4310.8</v>
+        <v>2189.9</v>
       </c>
       <c r="F1465" t="n">
-        <v>11845.8</v>
+        <v>9724.9</v>
       </c>
       <c r="G1465" t="n">
         <v>2</v>
@@ -48805,16 +48793,16 @@
         <v>76.3</v>
       </c>
       <c r="E1466" t="n">
-        <v>4460.7</v>
+        <v>2289</v>
       </c>
       <c r="F1466" t="n">
-        <v>15171.8</v>
+        <v>13000.1</v>
       </c>
       <c r="G1466" t="n">
         <v>3</v>
       </c>
       <c r="H1466" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1466" t="n">
         <v>2</v>
@@ -48838,10 +48826,10 @@
         <v>73.3</v>
       </c>
       <c r="E1467" t="n">
-        <v>4295.5</v>
+        <v>2210.4</v>
       </c>
       <c r="F1467" t="n">
-        <v>14986.5</v>
+        <v>12901.4</v>
       </c>
       <c r="G1467" t="n">
         <v>5</v>
@@ -48871,10 +48859,10 @@
         <v>56.5</v>
       </c>
       <c r="E1468" t="n">
-        <v>4161.7</v>
+        <v>2144.6</v>
       </c>
       <c r="F1468" t="n">
-        <v>14026.8</v>
+        <v>12009.7</v>
       </c>
       <c r="G1468" t="n">
         <v>7</v>
@@ -48904,10 +48892,10 @@
         <v>75.09999999999999</v>
       </c>
       <c r="E1469" t="n">
-        <v>3809.5</v>
+        <v>1963.8</v>
       </c>
       <c r="F1469" t="n">
-        <v>13474.1</v>
+        <v>11628.4</v>
       </c>
       <c r="G1469" t="n">
         <v>4</v>
@@ -48937,16 +48925,16 @@
         <v>69.7</v>
       </c>
       <c r="E1470" t="n">
-        <v>4445.9</v>
+        <v>2297.3</v>
       </c>
       <c r="F1470" t="n">
-        <v>15380.7</v>
+        <v>13232.1</v>
       </c>
       <c r="G1470" t="n">
         <v>6</v>
       </c>
       <c r="H1470" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1470" t="n">
         <v>1</v>
@@ -48970,10 +48958,10 @@
         <v>80.09999999999999</v>
       </c>
       <c r="E1471" t="n">
-        <v>3561.5</v>
+        <v>1848.3</v>
       </c>
       <c r="F1471" t="n">
-        <v>12395.4</v>
+        <v>10682.2</v>
       </c>
       <c r="G1471" t="n">
         <v>2</v>
@@ -49003,10 +48991,10 @@
         <v>44.9</v>
       </c>
       <c r="E1472" t="n">
-        <v>4006.5</v>
+        <v>2051.2</v>
       </c>
       <c r="F1472" t="n">
-        <v>13610.6</v>
+        <v>11655.3</v>
       </c>
       <c r="G1472" t="n">
         <v>8</v>
@@ -49036,10 +49024,10 @@
         <v>82.40000000000001</v>
       </c>
       <c r="E1473" t="n">
-        <v>4393.2</v>
+        <v>2272.3</v>
       </c>
       <c r="F1473" t="n">
-        <v>11928.2</v>
+        <v>9807.299999999999</v>
       </c>
       <c r="G1473" t="n">
         <v>1</v>

--- a/datos/vistas_negocio/Fact_Global_Master.xlsx
+++ b/datos/vistas_negocio/Fact_Global_Master.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,47 +429,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ID_Futmondo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Jornada</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Temporada</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Puntos</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Puntos_Acumulados</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Acumulado_Total</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Ranking_Jornada</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Ranking_Temporada</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Ranking_General</t>
         </is>
@@ -43909,7 +43921,7 @@
         <v>79.7</v>
       </c>
       <c r="E1318" t="n">
-        <v>874.1999999999999</v>
+        <v>874.2</v>
       </c>
       <c r="F1318" t="n">
         <v>11809</v>
@@ -44335,7 +44347,7 @@
         </is>
       </c>
       <c r="D1331" t="n">
-        <v>55.59999999999999</v>
+        <v>55.6</v>
       </c>
       <c r="E1331" t="n">
         <v>994.4</v>
@@ -45127,19 +45139,19 @@
         </is>
       </c>
       <c r="D1355" t="n">
-        <v>45.8</v>
+        <v>35.8</v>
       </c>
       <c r="E1355" t="n">
-        <v>1188.8</v>
+        <v>1178.8</v>
       </c>
       <c r="F1355" t="n">
-        <v>11879.8</v>
+        <v>11869.8</v>
       </c>
       <c r="G1355" t="n">
         <v>8</v>
       </c>
       <c r="H1355" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I1355" t="n">
         <v>2</v>
@@ -45172,7 +45184,7 @@
         <v>6</v>
       </c>
       <c r="H1356" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I1356" t="n">
         <v>4</v>
@@ -45394,16 +45406,16 @@
         <v>76.5</v>
       </c>
       <c r="E1363" t="n">
-        <v>1265.3</v>
+        <v>1255.3</v>
       </c>
       <c r="F1363" t="n">
-        <v>11956.3</v>
+        <v>11946.3</v>
       </c>
       <c r="G1363" t="n">
         <v>2</v>
       </c>
       <c r="H1363" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I1363" t="n">
         <v>2</v>
@@ -45436,7 +45448,7 @@
         <v>3</v>
       </c>
       <c r="H1364" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1364" t="n">
         <v>4</v>
@@ -45568,7 +45580,7 @@
         <v>5</v>
       </c>
       <c r="H1368" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I1368" t="n">
         <v>5</v>
@@ -45658,16 +45670,16 @@
         <v>65.2</v>
       </c>
       <c r="E1371" t="n">
-        <v>1330.5</v>
+        <v>1320.5</v>
       </c>
       <c r="F1371" t="n">
-        <v>12021.5</v>
+        <v>12011.5</v>
       </c>
       <c r="G1371" t="n">
         <v>7</v>
       </c>
       <c r="H1371" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I1371" t="n">
         <v>2</v>
@@ -45832,7 +45844,7 @@
         <v>6</v>
       </c>
       <c r="H1376" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I1376" t="n">
         <v>5</v>
@@ -45922,10 +45934,10 @@
         <v>80.3</v>
       </c>
       <c r="E1379" t="n">
-        <v>1410.8</v>
+        <v>1400.8</v>
       </c>
       <c r="F1379" t="n">
-        <v>12101.8</v>
+        <v>12091.8</v>
       </c>
       <c r="G1379" t="n">
         <v>2</v>
@@ -46186,10 +46198,10 @@
         <v>77.2</v>
       </c>
       <c r="E1387" t="n">
-        <v>1488</v>
+        <v>1478</v>
       </c>
       <c r="F1387" t="n">
-        <v>12179</v>
+        <v>12169</v>
       </c>
       <c r="G1387" t="n">
         <v>4</v>
@@ -46426,7 +46438,7 @@
         <v>3</v>
       </c>
       <c r="H1394" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1394" t="n">
         <v>2</v>
@@ -46450,16 +46462,16 @@
         <v>84.09999999999999</v>
       </c>
       <c r="E1395" t="n">
-        <v>1572.1</v>
+        <v>1562.1</v>
       </c>
       <c r="F1395" t="n">
-        <v>12263.1</v>
+        <v>12253.1</v>
       </c>
       <c r="G1395" t="n">
         <v>1</v>
       </c>
       <c r="H1395" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I1395" t="n">
         <v>3</v>
@@ -46657,7 +46669,7 @@
         <v>2</v>
       </c>
       <c r="H1401" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I1401" t="n">
         <v>8</v>
@@ -46714,10 +46726,10 @@
         <v>62.7</v>
       </c>
       <c r="E1403" t="n">
-        <v>1634.8</v>
+        <v>1624.8</v>
       </c>
       <c r="F1403" t="n">
-        <v>12325.8</v>
+        <v>12315.8</v>
       </c>
       <c r="G1403" t="n">
         <v>5</v>
@@ -46978,10 +46990,10 @@
         <v>62.3</v>
       </c>
       <c r="E1411" t="n">
-        <v>1697.1</v>
+        <v>1687.1</v>
       </c>
       <c r="F1411" t="n">
-        <v>12388.1</v>
+        <v>12378.1</v>
       </c>
       <c r="G1411" t="n">
         <v>4</v>
@@ -47242,10 +47254,10 @@
         <v>75.59999999999999</v>
       </c>
       <c r="E1419" t="n">
-        <v>1772.7</v>
+        <v>1762.7</v>
       </c>
       <c r="F1419" t="n">
-        <v>12463.7</v>
+        <v>12453.7</v>
       </c>
       <c r="G1419" t="n">
         <v>3</v>
@@ -47506,10 +47518,10 @@
         <v>66.59999999999999</v>
       </c>
       <c r="E1427" t="n">
-        <v>1839.3</v>
+        <v>1829.3</v>
       </c>
       <c r="F1427" t="n">
-        <v>12530.3</v>
+        <v>12520.3</v>
       </c>
       <c r="G1427" t="n">
         <v>4</v>
@@ -47770,10 +47782,10 @@
         <v>92.90000000000001</v>
       </c>
       <c r="E1435" t="n">
-        <v>1932.2</v>
+        <v>1922.2</v>
       </c>
       <c r="F1435" t="n">
-        <v>12623.2</v>
+        <v>12613.2</v>
       </c>
       <c r="G1435" t="n">
         <v>2</v>
@@ -48034,10 +48046,10 @@
         <v>73.5</v>
       </c>
       <c r="E1443" t="n">
-        <v>2005.7</v>
+        <v>1995.7</v>
       </c>
       <c r="F1443" t="n">
-        <v>12696.7</v>
+        <v>12686.7</v>
       </c>
       <c r="G1443" t="n">
         <v>4</v>
@@ -48298,10 +48310,10 @@
         <v>65.5</v>
       </c>
       <c r="E1451" t="n">
-        <v>2071.2</v>
+        <v>2061.2</v>
       </c>
       <c r="F1451" t="n">
-        <v>12762.2</v>
+        <v>12752.2</v>
       </c>
       <c r="G1451" t="n">
         <v>7</v>
@@ -48562,10 +48574,10 @@
         <v>65.90000000000001</v>
       </c>
       <c r="E1459" t="n">
-        <v>2137.1</v>
+        <v>2127.1</v>
       </c>
       <c r="F1459" t="n">
-        <v>12828.1</v>
+        <v>12818.1</v>
       </c>
       <c r="G1459" t="n">
         <v>5</v>
@@ -48826,10 +48838,10 @@
         <v>73.3</v>
       </c>
       <c r="E1467" t="n">
-        <v>2210.4</v>
+        <v>2200.4</v>
       </c>
       <c r="F1467" t="n">
-        <v>12901.4</v>
+        <v>12891.4</v>
       </c>
       <c r="G1467" t="n">
         <v>5</v>

--- a/datos/vistas_negocio/Fact_Global_Master.xlsx
+++ b/datos/vistas_negocio/Fact_Global_Master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1473"/>
+  <dimension ref="A1:I1481"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43195,7 +43195,7 @@
         <v>69.40000000000001</v>
       </c>
       <c r="E1296" t="n">
-        <v>629.8</v>
+        <v>629.8000000000001</v>
       </c>
       <c r="F1296" t="n">
         <v>10233.9</v>
@@ -43621,7 +43621,7 @@
         </is>
       </c>
       <c r="D1309" t="n">
-        <v>48.4</v>
+        <v>48.40000000000001</v>
       </c>
       <c r="E1309" t="n">
         <v>782.9</v>
@@ -44017,7 +44017,7 @@
         </is>
       </c>
       <c r="D1321" t="n">
-        <v>68.09999999999999</v>
+        <v>68.10000000000001</v>
       </c>
       <c r="E1321" t="n">
         <v>837.9</v>
@@ -44251,7 +44251,7 @@
         <v>72</v>
       </c>
       <c r="E1328" t="n">
-        <v>899.9</v>
+        <v>899.9000000000001</v>
       </c>
       <c r="F1328" t="n">
         <v>10504</v>
@@ -44347,7 +44347,7 @@
         </is>
       </c>
       <c r="D1331" t="n">
-        <v>55.6</v>
+        <v>55.59999999999999</v>
       </c>
       <c r="E1331" t="n">
         <v>994.4</v>
@@ -44413,7 +44413,7 @@
         </is>
       </c>
       <c r="D1333" t="n">
-        <v>62.40000000000001</v>
+        <v>62.4</v>
       </c>
       <c r="E1333" t="n">
         <v>954.8000000000001</v>
@@ -44515,7 +44515,7 @@
         <v>86</v>
       </c>
       <c r="E1336" t="n">
-        <v>985.9</v>
+        <v>985.9000000000001</v>
       </c>
       <c r="F1336" t="n">
         <v>10590</v>
@@ -46558,7 +46558,7 @@
         </is>
       </c>
       <c r="D1398" t="n">
-        <v>75.39999999999999</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="E1398" t="n">
         <v>1658.7</v>
@@ -47845,7 +47845,7 @@
         </is>
       </c>
       <c r="D1437" t="n">
-        <v>62.09999999999999</v>
+        <v>62.1</v>
       </c>
       <c r="E1437" t="n">
         <v>1675.9</v>
@@ -49048,6 +49048,270 @@
         <v>3</v>
       </c>
       <c r="I1473" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1474">
+      <c r="A1474" t="inlineStr">
+        <is>
+          <t>5f452f5e66dd374930eb2b71</t>
+        </is>
+      </c>
+      <c r="B1474" t="n">
+        <v>32</v>
+      </c>
+      <c r="C1474" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1474" t="n">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="E1474" t="n">
+        <v>2359.1</v>
+      </c>
+      <c r="F1474" t="n">
+        <v>13070.2</v>
+      </c>
+      <c r="G1474" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1474" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1474" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1475">
+      <c r="A1475" t="inlineStr">
+        <is>
+          <t>5f453062ec331549297ee6b8</t>
+        </is>
+      </c>
+      <c r="B1475" t="n">
+        <v>32</v>
+      </c>
+      <c r="C1475" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1475" t="n">
+        <v>77.90000000000001</v>
+      </c>
+      <c r="E1475" t="n">
+        <v>2278.3</v>
+      </c>
+      <c r="F1475" t="n">
+        <v>12969.3</v>
+      </c>
+      <c r="G1475" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1475" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1475" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1476">
+      <c r="A1476" t="inlineStr">
+        <is>
+          <t>5f4530beec331549297ee6d6</t>
+        </is>
+      </c>
+      <c r="B1476" t="n">
+        <v>32</v>
+      </c>
+      <c r="C1476" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1476" t="n">
+        <v>80.8</v>
+      </c>
+      <c r="E1476" t="n">
+        <v>2225.4</v>
+      </c>
+      <c r="F1476" t="n">
+        <v>12090.5</v>
+      </c>
+      <c r="G1476" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1476" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1476" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1477">
+      <c r="A1477" t="inlineStr">
+        <is>
+          <t>5f4531e9764e7d491e029746</t>
+        </is>
+      </c>
+      <c r="B1477" t="n">
+        <v>32</v>
+      </c>
+      <c r="C1477" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1477" t="n">
+        <v>53</v>
+      </c>
+      <c r="E1477" t="n">
+        <v>2016.8</v>
+      </c>
+      <c r="F1477" t="n">
+        <v>11681.4</v>
+      </c>
+      <c r="G1477" t="n">
+        <v>7</v>
+      </c>
+      <c r="H1477" t="n">
+        <v>7</v>
+      </c>
+      <c r="I1477" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1478">
+      <c r="A1478" t="inlineStr">
+        <is>
+          <t>5f45324dec331549297ee971</t>
+        </is>
+      </c>
+      <c r="B1478" t="n">
+        <v>32</v>
+      </c>
+      <c r="C1478" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1478" t="n">
+        <v>59.8</v>
+      </c>
+      <c r="E1478" t="n">
+        <v>2357.1</v>
+      </c>
+      <c r="F1478" t="n">
+        <v>13291.9</v>
+      </c>
+      <c r="G1478" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1478" t="n">
+        <v>3</v>
+      </c>
+      <c r="I1478" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1479">
+      <c r="A1479" t="inlineStr">
+        <is>
+          <t>5f47ab5b9e2edb0bb831c703</t>
+        </is>
+      </c>
+      <c r="B1479" t="n">
+        <v>32</v>
+      </c>
+      <c r="C1479" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1479" t="n">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="E1479" t="n">
+        <v>1916.7</v>
+      </c>
+      <c r="F1479" t="n">
+        <v>10750.6</v>
+      </c>
+      <c r="G1479" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1479" t="n">
+        <v>8</v>
+      </c>
+      <c r="I1479" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1480">
+      <c r="A1480" t="inlineStr">
+        <is>
+          <t>5f47aeb6c387a50bca03dd55</t>
+        </is>
+      </c>
+      <c r="B1480" t="n">
+        <v>32</v>
+      </c>
+      <c r="C1480" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1480" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="E1480" t="n">
+        <v>2099.6</v>
+      </c>
+      <c r="F1480" t="n">
+        <v>11703.7</v>
+      </c>
+      <c r="G1480" t="n">
+        <v>8</v>
+      </c>
+      <c r="H1480" t="n">
+        <v>6</v>
+      </c>
+      <c r="I1480" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1481">
+      <c r="A1481" t="inlineStr">
+        <is>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
+        </is>
+      </c>
+      <c r="B1481" t="n">
+        <v>32</v>
+      </c>
+      <c r="C1481" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1481" t="n">
+        <v>104.8</v>
+      </c>
+      <c r="E1481" t="n">
+        <v>2377.1</v>
+      </c>
+      <c r="F1481" t="n">
+        <v>9912.1</v>
+      </c>
+      <c r="G1481" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1481" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1481" t="n">
         <v>8</v>
       </c>
     </row>

--- a/datos/vistas_negocio/Fact_Global_Master.xlsx
+++ b/datos/vistas_negocio/Fact_Global_Master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1481"/>
+  <dimension ref="A1:I1489"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43195,7 +43195,7 @@
         <v>69.40000000000001</v>
       </c>
       <c r="E1296" t="n">
-        <v>629.8000000000001</v>
+        <v>629.8</v>
       </c>
       <c r="F1296" t="n">
         <v>10233.9</v>
@@ -43621,7 +43621,7 @@
         </is>
       </c>
       <c r="D1309" t="n">
-        <v>48.40000000000001</v>
+        <v>48.4</v>
       </c>
       <c r="E1309" t="n">
         <v>782.9</v>
@@ -44251,7 +44251,7 @@
         <v>72</v>
       </c>
       <c r="E1328" t="n">
-        <v>899.9000000000001</v>
+        <v>899.9</v>
       </c>
       <c r="F1328" t="n">
         <v>10504</v>
@@ -44347,7 +44347,7 @@
         </is>
       </c>
       <c r="D1331" t="n">
-        <v>55.59999999999999</v>
+        <v>55.6</v>
       </c>
       <c r="E1331" t="n">
         <v>994.4</v>
@@ -44413,7 +44413,7 @@
         </is>
       </c>
       <c r="D1333" t="n">
-        <v>62.4</v>
+        <v>62.40000000000001</v>
       </c>
       <c r="E1333" t="n">
         <v>954.8000000000001</v>
@@ -44515,7 +44515,7 @@
         <v>86</v>
       </c>
       <c r="E1336" t="n">
-        <v>985.9000000000001</v>
+        <v>985.9</v>
       </c>
       <c r="F1336" t="n">
         <v>10590</v>
@@ -47845,7 +47845,7 @@
         </is>
       </c>
       <c r="D1437" t="n">
-        <v>62.1</v>
+        <v>62.09999999999999</v>
       </c>
       <c r="E1437" t="n">
         <v>1675.9</v>
@@ -49312,6 +49312,270 @@
         <v>1</v>
       </c>
       <c r="I1481" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1482">
+      <c r="A1482" t="inlineStr">
+        <is>
+          <t>5f452f5e66dd374930eb2b71</t>
+        </is>
+      </c>
+      <c r="B1482" t="n">
+        <v>33</v>
+      </c>
+      <c r="C1482" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1482" t="n">
+        <v>76.3</v>
+      </c>
+      <c r="E1482" t="n">
+        <v>2435.4</v>
+      </c>
+      <c r="F1482" t="n">
+        <v>13146.5</v>
+      </c>
+      <c r="G1482" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1482" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1482" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1483">
+      <c r="A1483" t="inlineStr">
+        <is>
+          <t>5f453062ec331549297ee6b8</t>
+        </is>
+      </c>
+      <c r="B1483" t="n">
+        <v>33</v>
+      </c>
+      <c r="C1483" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1483" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="E1483" t="n">
+        <v>2351.6</v>
+      </c>
+      <c r="F1483" t="n">
+        <v>13042.6</v>
+      </c>
+      <c r="G1483" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1483" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1483" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1484">
+      <c r="A1484" t="inlineStr">
+        <is>
+          <t>5f4530beec331549297ee6d6</t>
+        </is>
+      </c>
+      <c r="B1484" t="n">
+        <v>33</v>
+      </c>
+      <c r="C1484" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1484" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="E1484" t="n">
+        <v>2281.9</v>
+      </c>
+      <c r="F1484" t="n">
+        <v>12147</v>
+      </c>
+      <c r="G1484" t="n">
+        <v>7</v>
+      </c>
+      <c r="H1484" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1484" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1485">
+      <c r="A1485" t="inlineStr">
+        <is>
+          <t>5f4531e9764e7d491e029746</t>
+        </is>
+      </c>
+      <c r="B1485" t="n">
+        <v>33</v>
+      </c>
+      <c r="C1485" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1485" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="E1485" t="n">
+        <v>2091.9</v>
+      </c>
+      <c r="F1485" t="n">
+        <v>11756.5</v>
+      </c>
+      <c r="G1485" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1485" t="n">
+        <v>7</v>
+      </c>
+      <c r="I1485" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1486">
+      <c r="A1486" t="inlineStr">
+        <is>
+          <t>5f45324dec331549297ee971</t>
+        </is>
+      </c>
+      <c r="B1486" t="n">
+        <v>33</v>
+      </c>
+      <c r="C1486" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1486" t="n">
+        <v>69.7</v>
+      </c>
+      <c r="E1486" t="n">
+        <v>2426.8</v>
+      </c>
+      <c r="F1486" t="n">
+        <v>13361.6</v>
+      </c>
+      <c r="G1486" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1486" t="n">
+        <v>3</v>
+      </c>
+      <c r="I1486" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1487">
+      <c r="A1487" t="inlineStr">
+        <is>
+          <t>5f47ab5b9e2edb0bb831c703</t>
+        </is>
+      </c>
+      <c r="B1487" t="n">
+        <v>33</v>
+      </c>
+      <c r="C1487" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1487" t="n">
+        <v>80.09999999999999</v>
+      </c>
+      <c r="E1487" t="n">
+        <v>1996.8</v>
+      </c>
+      <c r="F1487" t="n">
+        <v>10830.7</v>
+      </c>
+      <c r="G1487" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1487" t="n">
+        <v>8</v>
+      </c>
+      <c r="I1487" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1488">
+      <c r="A1488" t="inlineStr">
+        <is>
+          <t>5f47aeb6c387a50bca03dd55</t>
+        </is>
+      </c>
+      <c r="B1488" t="n">
+        <v>33</v>
+      </c>
+      <c r="C1488" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1488" t="n">
+        <v>44.90000000000001</v>
+      </c>
+      <c r="E1488" t="n">
+        <v>2144.5</v>
+      </c>
+      <c r="F1488" t="n">
+        <v>11748.6</v>
+      </c>
+      <c r="G1488" t="n">
+        <v>8</v>
+      </c>
+      <c r="H1488" t="n">
+        <v>6</v>
+      </c>
+      <c r="I1488" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1489">
+      <c r="A1489" t="inlineStr">
+        <is>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
+        </is>
+      </c>
+      <c r="B1489" t="n">
+        <v>33</v>
+      </c>
+      <c r="C1489" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1489" t="n">
+        <v>82.40000000000001</v>
+      </c>
+      <c r="E1489" t="n">
+        <v>2459.5</v>
+      </c>
+      <c r="F1489" t="n">
+        <v>9994.5</v>
+      </c>
+      <c r="G1489" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1489" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1489" t="n">
         <v>8</v>
       </c>
     </row>

--- a/datos/vistas_negocio/Fact_Global_Master.xlsx
+++ b/datos/vistas_negocio/Fact_Global_Master.xlsx
@@ -41080,7 +41080,7 @@
         </is>
       </c>
       <c r="D1232" t="n">
-        <v>70.09999999999999</v>
+        <v>70.10000000000001</v>
       </c>
       <c r="E1232" t="n">
         <v>121.1</v>
@@ -43195,7 +43195,7 @@
         <v>69.40000000000001</v>
       </c>
       <c r="E1296" t="n">
-        <v>629.8</v>
+        <v>629.8000000000001</v>
       </c>
       <c r="F1296" t="n">
         <v>10233.9</v>
@@ -43921,7 +43921,7 @@
         <v>79.7</v>
       </c>
       <c r="E1318" t="n">
-        <v>874.2</v>
+        <v>874.1999999999999</v>
       </c>
       <c r="F1318" t="n">
         <v>11809</v>
@@ -44251,7 +44251,7 @@
         <v>72</v>
       </c>
       <c r="E1328" t="n">
-        <v>899.9</v>
+        <v>899.9000000000001</v>
       </c>
       <c r="F1328" t="n">
         <v>10504</v>
@@ -44347,7 +44347,7 @@
         </is>
       </c>
       <c r="D1331" t="n">
-        <v>55.6</v>
+        <v>55.59999999999999</v>
       </c>
       <c r="E1331" t="n">
         <v>994.4</v>
@@ -44515,7 +44515,7 @@
         <v>86</v>
       </c>
       <c r="E1336" t="n">
-        <v>985.9</v>
+        <v>985.9000000000001</v>
       </c>
       <c r="F1336" t="n">
         <v>10590</v>
@@ -46393,7 +46393,7 @@
         </is>
       </c>
       <c r="D1393" t="n">
-        <v>73.10000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="E1393" t="n">
         <v>1489.5</v>
@@ -46558,7 +46558,7 @@
         </is>
       </c>
       <c r="D1398" t="n">
-        <v>75.40000000000001</v>
+        <v>75.39999999999999</v>
       </c>
       <c r="E1398" t="n">
         <v>1658.7</v>
@@ -49231,7 +49231,7 @@
         </is>
       </c>
       <c r="D1479" t="n">
-        <v>68.40000000000001</v>
+        <v>68.39999999999999</v>
       </c>
       <c r="E1479" t="n">
         <v>1916.7</v>
@@ -49528,7 +49528,7 @@
         </is>
       </c>
       <c r="D1488" t="n">
-        <v>44.90000000000001</v>
+        <v>44.9</v>
       </c>
       <c r="E1488" t="n">
         <v>2144.5</v>

--- a/datos/vistas_negocio/Fact_Global_Master.xlsx
+++ b/datos/vistas_negocio/Fact_Global_Master.xlsx
@@ -43621,7 +43621,7 @@
         </is>
       </c>
       <c r="D1309" t="n">
-        <v>48.4</v>
+        <v>48.40000000000001</v>
       </c>
       <c r="E1309" t="n">
         <v>782.9</v>
@@ -43921,7 +43921,7 @@
         <v>79.7</v>
       </c>
       <c r="E1318" t="n">
-        <v>874.1999999999999</v>
+        <v>874.2</v>
       </c>
       <c r="F1318" t="n">
         <v>11809</v>
@@ -44017,7 +44017,7 @@
         </is>
       </c>
       <c r="D1321" t="n">
-        <v>68.10000000000001</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="E1321" t="n">
         <v>837.9</v>
@@ -44347,7 +44347,7 @@
         </is>
       </c>
       <c r="D1331" t="n">
-        <v>55.59999999999999</v>
+        <v>55.6</v>
       </c>
       <c r="E1331" t="n">
         <v>994.4</v>
@@ -46393,7 +46393,7 @@
         </is>
       </c>
       <c r="D1393" t="n">
-        <v>73.09999999999999</v>
+        <v>73.10000000000001</v>
       </c>
       <c r="E1393" t="n">
         <v>1489.5</v>
@@ -46558,7 +46558,7 @@
         </is>
       </c>
       <c r="D1398" t="n">
-        <v>75.39999999999999</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="E1398" t="n">
         <v>1658.7</v>
@@ -47845,7 +47845,7 @@
         </is>
       </c>
       <c r="D1437" t="n">
-        <v>62.09999999999999</v>
+        <v>62.1</v>
       </c>
       <c r="E1437" t="n">
         <v>1675.9</v>
@@ -49231,7 +49231,7 @@
         </is>
       </c>
       <c r="D1479" t="n">
-        <v>68.39999999999999</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="E1479" t="n">
         <v>1916.7</v>
@@ -49528,7 +49528,7 @@
         </is>
       </c>
       <c r="D1488" t="n">
-        <v>44.9</v>
+        <v>44.90000000000001</v>
       </c>
       <c r="E1488" t="n">
         <v>2144.5</v>

--- a/datos/vistas_negocio/Fact_Global_Master.xlsx
+++ b/datos/vistas_negocio/Fact_Global_Master.xlsx
@@ -41080,7 +41080,7 @@
         </is>
       </c>
       <c r="D1232" t="n">
-        <v>70.10000000000001</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="E1232" t="n">
         <v>121.1</v>
@@ -44347,7 +44347,7 @@
         </is>
       </c>
       <c r="D1331" t="n">
-        <v>55.6</v>
+        <v>55.59999999999999</v>
       </c>
       <c r="E1331" t="n">
         <v>994.4</v>
@@ -46558,7 +46558,7 @@
         </is>
       </c>
       <c r="D1398" t="n">
-        <v>75.40000000000001</v>
+        <v>75.39999999999999</v>
       </c>
       <c r="E1398" t="n">
         <v>1658.7</v>
@@ -47845,7 +47845,7 @@
         </is>
       </c>
       <c r="D1437" t="n">
-        <v>62.1</v>
+        <v>62.09999999999999</v>
       </c>
       <c r="E1437" t="n">
         <v>1675.9</v>
@@ -49231,7 +49231,7 @@
         </is>
       </c>
       <c r="D1479" t="n">
-        <v>68.40000000000001</v>
+        <v>68.39999999999999</v>
       </c>
       <c r="E1479" t="n">
         <v>1916.7</v>

--- a/datos/vistas_negocio/Fact_Global_Master.xlsx
+++ b/datos/vistas_negocio/Fact_Global_Master.xlsx
@@ -41080,7 +41080,7 @@
         </is>
       </c>
       <c r="D1232" t="n">
-        <v>70.09999999999999</v>
+        <v>70.10000000000001</v>
       </c>
       <c r="E1232" t="n">
         <v>121.1</v>
@@ -43921,7 +43921,7 @@
         <v>79.7</v>
       </c>
       <c r="E1318" t="n">
-        <v>874.2</v>
+        <v>874.1999999999999</v>
       </c>
       <c r="F1318" t="n">
         <v>11809</v>
@@ -44347,7 +44347,7 @@
         </is>
       </c>
       <c r="D1331" t="n">
-        <v>55.59999999999999</v>
+        <v>55.6</v>
       </c>
       <c r="E1331" t="n">
         <v>994.4</v>
@@ -44413,7 +44413,7 @@
         </is>
       </c>
       <c r="D1333" t="n">
-        <v>62.40000000000001</v>
+        <v>62.4</v>
       </c>
       <c r="E1333" t="n">
         <v>954.8000000000001</v>
@@ -47845,7 +47845,7 @@
         </is>
       </c>
       <c r="D1437" t="n">
-        <v>62.09999999999999</v>
+        <v>62.1</v>
       </c>
       <c r="E1437" t="n">
         <v>1675.9</v>
@@ -49231,7 +49231,7 @@
         </is>
       </c>
       <c r="D1479" t="n">
-        <v>68.39999999999999</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="E1479" t="n">
         <v>1916.7</v>

--- a/datos/vistas_negocio/Fact_Global_Master.xlsx
+++ b/datos/vistas_negocio/Fact_Global_Master.xlsx
@@ -41080,7 +41080,7 @@
         </is>
       </c>
       <c r="D1232" t="n">
-        <v>70.10000000000001</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="E1232" t="n">
         <v>121.1</v>
@@ -43195,7 +43195,7 @@
         <v>69.40000000000001</v>
       </c>
       <c r="E1296" t="n">
-        <v>629.8000000000001</v>
+        <v>629.8</v>
       </c>
       <c r="F1296" t="n">
         <v>10233.9</v>
@@ -43921,7 +43921,7 @@
         <v>79.7</v>
       </c>
       <c r="E1318" t="n">
-        <v>874.1999999999999</v>
+        <v>874.2</v>
       </c>
       <c r="F1318" t="n">
         <v>11809</v>
@@ -44251,7 +44251,7 @@
         <v>72</v>
       </c>
       <c r="E1328" t="n">
-        <v>899.9000000000001</v>
+        <v>899.9</v>
       </c>
       <c r="F1328" t="n">
         <v>10504</v>
@@ -44515,7 +44515,7 @@
         <v>86</v>
       </c>
       <c r="E1336" t="n">
-        <v>985.9000000000001</v>
+        <v>985.9</v>
       </c>
       <c r="F1336" t="n">
         <v>10590</v>
@@ -46393,7 +46393,7 @@
         </is>
       </c>
       <c r="D1393" t="n">
-        <v>73.10000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="E1393" t="n">
         <v>1489.5</v>
@@ -49528,7 +49528,7 @@
         </is>
       </c>
       <c r="D1488" t="n">
-        <v>44.90000000000001</v>
+        <v>44.9</v>
       </c>
       <c r="E1488" t="n">
         <v>2144.5</v>

--- a/datos/vistas_negocio/Fact_Global_Master.xlsx
+++ b/datos/vistas_negocio/Fact_Global_Master.xlsx
@@ -43195,7 +43195,7 @@
         <v>69.40000000000001</v>
       </c>
       <c r="E1296" t="n">
-        <v>629.8</v>
+        <v>629.8000000000001</v>
       </c>
       <c r="F1296" t="n">
         <v>10233.9</v>
@@ -43921,7 +43921,7 @@
         <v>79.7</v>
       </c>
       <c r="E1318" t="n">
-        <v>874.2</v>
+        <v>874.1999999999999</v>
       </c>
       <c r="F1318" t="n">
         <v>11809</v>
@@ -44017,7 +44017,7 @@
         </is>
       </c>
       <c r="D1321" t="n">
-        <v>68.09999999999999</v>
+        <v>68.10000000000001</v>
       </c>
       <c r="E1321" t="n">
         <v>837.9</v>
@@ -44251,7 +44251,7 @@
         <v>72</v>
       </c>
       <c r="E1328" t="n">
-        <v>899.9</v>
+        <v>899.9000000000001</v>
       </c>
       <c r="F1328" t="n">
         <v>10504</v>
@@ -44347,7 +44347,7 @@
         </is>
       </c>
       <c r="D1331" t="n">
-        <v>55.6</v>
+        <v>55.59999999999999</v>
       </c>
       <c r="E1331" t="n">
         <v>994.4</v>
@@ -44515,7 +44515,7 @@
         <v>86</v>
       </c>
       <c r="E1336" t="n">
-        <v>985.9</v>
+        <v>985.9000000000001</v>
       </c>
       <c r="F1336" t="n">
         <v>10590</v>
@@ -46393,7 +46393,7 @@
         </is>
       </c>
       <c r="D1393" t="n">
-        <v>73.09999999999999</v>
+        <v>73.10000000000001</v>
       </c>
       <c r="E1393" t="n">
         <v>1489.5</v>
@@ -49528,7 +49528,7 @@
         </is>
       </c>
       <c r="D1488" t="n">
-        <v>44.9</v>
+        <v>44.90000000000001</v>
       </c>
       <c r="E1488" t="n">
         <v>2144.5</v>

--- a/datos/vistas_negocio/Fact_Global_Master.xlsx
+++ b/datos/vistas_negocio/Fact_Global_Master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1489"/>
+  <dimension ref="A1:I1497"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41080,7 +41080,7 @@
         </is>
       </c>
       <c r="D1232" t="n">
-        <v>70.09999999999999</v>
+        <v>70.10000000000001</v>
       </c>
       <c r="E1232" t="n">
         <v>121.1</v>
@@ -43621,7 +43621,7 @@
         </is>
       </c>
       <c r="D1309" t="n">
-        <v>48.40000000000001</v>
+        <v>48.4</v>
       </c>
       <c r="E1309" t="n">
         <v>782.9</v>
@@ -44347,7 +44347,7 @@
         </is>
       </c>
       <c r="D1331" t="n">
-        <v>55.59999999999999</v>
+        <v>55.6</v>
       </c>
       <c r="E1331" t="n">
         <v>994.4</v>
@@ -44413,7 +44413,7 @@
         </is>
       </c>
       <c r="D1333" t="n">
-        <v>62.4</v>
+        <v>62.40000000000001</v>
       </c>
       <c r="E1333" t="n">
         <v>954.8000000000001</v>
@@ -49576,6 +49576,270 @@
         <v>1</v>
       </c>
       <c r="I1489" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1490">
+      <c r="A1490" t="inlineStr">
+        <is>
+          <t>5f452f5e66dd374930eb2b71</t>
+        </is>
+      </c>
+      <c r="B1490" t="n">
+        <v>34</v>
+      </c>
+      <c r="C1490" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1490" t="n">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="E1490" t="n">
+        <v>2529.5</v>
+      </c>
+      <c r="F1490" t="n">
+        <v>13240.6</v>
+      </c>
+      <c r="G1490" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1490" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1490" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1491">
+      <c r="A1491" t="inlineStr">
+        <is>
+          <t>5f453062ec331549297ee6b8</t>
+        </is>
+      </c>
+      <c r="B1491" t="n">
+        <v>34</v>
+      </c>
+      <c r="C1491" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1491" t="n">
+        <v>94.90000000000001</v>
+      </c>
+      <c r="E1491" t="n">
+        <v>2446.5</v>
+      </c>
+      <c r="F1491" t="n">
+        <v>13137.5</v>
+      </c>
+      <c r="G1491" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1491" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1491" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1492">
+      <c r="A1492" t="inlineStr">
+        <is>
+          <t>5f4530beec331549297ee6d6</t>
+        </is>
+      </c>
+      <c r="B1492" t="n">
+        <v>34</v>
+      </c>
+      <c r="C1492" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1492" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="E1492" t="n">
+        <v>2357.1</v>
+      </c>
+      <c r="F1492" t="n">
+        <v>12222.2</v>
+      </c>
+      <c r="G1492" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1492" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1492" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1493">
+      <c r="A1493" t="inlineStr">
+        <is>
+          <t>5f4531e9764e7d491e029746</t>
+        </is>
+      </c>
+      <c r="B1493" t="n">
+        <v>34</v>
+      </c>
+      <c r="C1493" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1493" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="E1493" t="n">
+        <v>2130.2</v>
+      </c>
+      <c r="F1493" t="n">
+        <v>11794.8</v>
+      </c>
+      <c r="G1493" t="n">
+        <v>8</v>
+      </c>
+      <c r="H1493" t="n">
+        <v>7</v>
+      </c>
+      <c r="I1493" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1494">
+      <c r="A1494" t="inlineStr">
+        <is>
+          <t>5f45324dec331549297ee971</t>
+        </is>
+      </c>
+      <c r="B1494" t="n">
+        <v>34</v>
+      </c>
+      <c r="C1494" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1494" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="E1494" t="n">
+        <v>2479.7</v>
+      </c>
+      <c r="F1494" t="n">
+        <v>13414.5</v>
+      </c>
+      <c r="G1494" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1494" t="n">
+        <v>3</v>
+      </c>
+      <c r="I1494" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1495">
+      <c r="A1495" t="inlineStr">
+        <is>
+          <t>5f47ab5b9e2edb0bb831c703</t>
+        </is>
+      </c>
+      <c r="B1495" t="n">
+        <v>34</v>
+      </c>
+      <c r="C1495" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1495" t="n">
+        <v>78.7</v>
+      </c>
+      <c r="E1495" t="n">
+        <v>2075.5</v>
+      </c>
+      <c r="F1495" t="n">
+        <v>10909.4</v>
+      </c>
+      <c r="G1495" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1495" t="n">
+        <v>8</v>
+      </c>
+      <c r="I1495" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1496">
+      <c r="A1496" t="inlineStr">
+        <is>
+          <t>5f47aeb6c387a50bca03dd55</t>
+        </is>
+      </c>
+      <c r="B1496" t="n">
+        <v>34</v>
+      </c>
+      <c r="C1496" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1496" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="E1496" t="n">
+        <v>2188.9</v>
+      </c>
+      <c r="F1496" t="n">
+        <v>11793</v>
+      </c>
+      <c r="G1496" t="n">
+        <v>7</v>
+      </c>
+      <c r="H1496" t="n">
+        <v>6</v>
+      </c>
+      <c r="I1496" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1497">
+      <c r="A1497" t="inlineStr">
+        <is>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
+        </is>
+      </c>
+      <c r="B1497" t="n">
+        <v>34</v>
+      </c>
+      <c r="C1497" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1497" t="n">
+        <v>95.3</v>
+      </c>
+      <c r="E1497" t="n">
+        <v>2554.8</v>
+      </c>
+      <c r="F1497" t="n">
+        <v>10089.8</v>
+      </c>
+      <c r="G1497" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1497" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1497" t="n">
         <v>8</v>
       </c>
     </row>

--- a/datos/vistas_negocio/Fact_Global_Master.xlsx
+++ b/datos/vistas_negocio/Fact_Global_Master.xlsx
@@ -41080,7 +41080,7 @@
         </is>
       </c>
       <c r="D1232" t="n">
-        <v>70.10000000000001</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="E1232" t="n">
         <v>121.1</v>
@@ -43195,7 +43195,7 @@
         <v>69.40000000000001</v>
       </c>
       <c r="E1296" t="n">
-        <v>629.8000000000001</v>
+        <v>629.8</v>
       </c>
       <c r="F1296" t="n">
         <v>10233.9</v>
@@ -43921,7 +43921,7 @@
         <v>79.7</v>
       </c>
       <c r="E1318" t="n">
-        <v>874.1999999999999</v>
+        <v>874.2</v>
       </c>
       <c r="F1318" t="n">
         <v>11809</v>
@@ -44017,7 +44017,7 @@
         </is>
       </c>
       <c r="D1321" t="n">
-        <v>68.10000000000001</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="E1321" t="n">
         <v>837.9</v>
@@ -44251,7 +44251,7 @@
         <v>72</v>
       </c>
       <c r="E1328" t="n">
-        <v>899.9000000000001</v>
+        <v>899.9</v>
       </c>
       <c r="F1328" t="n">
         <v>10504</v>
@@ -44413,7 +44413,7 @@
         </is>
       </c>
       <c r="D1333" t="n">
-        <v>62.40000000000001</v>
+        <v>62.4</v>
       </c>
       <c r="E1333" t="n">
         <v>954.8000000000001</v>
@@ -44515,7 +44515,7 @@
         <v>86</v>
       </c>
       <c r="E1336" t="n">
-        <v>985.9000000000001</v>
+        <v>985.9</v>
       </c>
       <c r="F1336" t="n">
         <v>10590</v>
@@ -46393,7 +46393,7 @@
         </is>
       </c>
       <c r="D1393" t="n">
-        <v>73.10000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="E1393" t="n">
         <v>1489.5</v>

--- a/datos/vistas_negocio/Fact_Global_Master.xlsx
+++ b/datos/vistas_negocio/Fact_Global_Master.xlsx
@@ -41080,7 +41080,7 @@
         </is>
       </c>
       <c r="D1232" t="n">
-        <v>70.09999999999999</v>
+        <v>70.10000000000001</v>
       </c>
       <c r="E1232" t="n">
         <v>121.1</v>
@@ -43195,7 +43195,7 @@
         <v>69.40000000000001</v>
       </c>
       <c r="E1296" t="n">
-        <v>629.8</v>
+        <v>629.8000000000001</v>
       </c>
       <c r="F1296" t="n">
         <v>10233.9</v>
@@ -43621,7 +43621,7 @@
         </is>
       </c>
       <c r="D1309" t="n">
-        <v>48.4</v>
+        <v>48.40000000000001</v>
       </c>
       <c r="E1309" t="n">
         <v>782.9</v>
@@ -43921,7 +43921,7 @@
         <v>79.7</v>
       </c>
       <c r="E1318" t="n">
-        <v>874.2</v>
+        <v>874.1999999999999</v>
       </c>
       <c r="F1318" t="n">
         <v>11809</v>
@@ -44251,7 +44251,7 @@
         <v>72</v>
       </c>
       <c r="E1328" t="n">
-        <v>899.9</v>
+        <v>899.9000000000001</v>
       </c>
       <c r="F1328" t="n">
         <v>10504</v>
@@ -44347,7 +44347,7 @@
         </is>
       </c>
       <c r="D1331" t="n">
-        <v>55.6</v>
+        <v>55.59999999999999</v>
       </c>
       <c r="E1331" t="n">
         <v>994.4</v>
@@ -44413,7 +44413,7 @@
         </is>
       </c>
       <c r="D1333" t="n">
-        <v>62.4</v>
+        <v>62.40000000000001</v>
       </c>
       <c r="E1333" t="n">
         <v>954.8000000000001</v>
@@ -44515,7 +44515,7 @@
         <v>86</v>
       </c>
       <c r="E1336" t="n">
-        <v>985.9</v>
+        <v>985.9000000000001</v>
       </c>
       <c r="F1336" t="n">
         <v>10590</v>
@@ -46393,7 +46393,7 @@
         </is>
       </c>
       <c r="D1393" t="n">
-        <v>73.09999999999999</v>
+        <v>73.10000000000001</v>
       </c>
       <c r="E1393" t="n">
         <v>1489.5</v>
@@ -46558,7 +46558,7 @@
         </is>
       </c>
       <c r="D1398" t="n">
-        <v>75.39999999999999</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="E1398" t="n">
         <v>1658.7</v>
@@ -49231,7 +49231,7 @@
         </is>
       </c>
       <c r="D1479" t="n">
-        <v>68.40000000000001</v>
+        <v>68.39999999999999</v>
       </c>
       <c r="E1479" t="n">
         <v>1916.7</v>

--- a/datos/vistas_negocio/Fact_Global_Master.xlsx
+++ b/datos/vistas_negocio/Fact_Global_Master.xlsx
@@ -41080,7 +41080,7 @@
         </is>
       </c>
       <c r="D1232" t="n">
-        <v>70.10000000000001</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="E1232" t="n">
         <v>121.1</v>
@@ -43621,7 +43621,7 @@
         </is>
       </c>
       <c r="D1309" t="n">
-        <v>48.40000000000001</v>
+        <v>48.4</v>
       </c>
       <c r="E1309" t="n">
         <v>782.9</v>
@@ -47845,7 +47845,7 @@
         </is>
       </c>
       <c r="D1437" t="n">
-        <v>62.1</v>
+        <v>62.09999999999999</v>
       </c>
       <c r="E1437" t="n">
         <v>1675.9</v>

--- a/datos/vistas_negocio/Fact_Global_Master.xlsx
+++ b/datos/vistas_negocio/Fact_Global_Master.xlsx
@@ -43195,7 +43195,7 @@
         <v>69.40000000000001</v>
       </c>
       <c r="E1296" t="n">
-        <v>629.8000000000001</v>
+        <v>629.8</v>
       </c>
       <c r="F1296" t="n">
         <v>10233.9</v>
@@ -43621,7 +43621,7 @@
         </is>
       </c>
       <c r="D1309" t="n">
-        <v>48.4</v>
+        <v>48.40000000000001</v>
       </c>
       <c r="E1309" t="n">
         <v>782.9</v>
@@ -43921,7 +43921,7 @@
         <v>79.7</v>
       </c>
       <c r="E1318" t="n">
-        <v>874.1999999999999</v>
+        <v>874.2</v>
       </c>
       <c r="F1318" t="n">
         <v>11809</v>
@@ -44251,7 +44251,7 @@
         <v>72</v>
       </c>
       <c r="E1328" t="n">
-        <v>899.9000000000001</v>
+        <v>899.9</v>
       </c>
       <c r="F1328" t="n">
         <v>10504</v>
@@ -44413,7 +44413,7 @@
         </is>
       </c>
       <c r="D1333" t="n">
-        <v>62.40000000000001</v>
+        <v>62.4</v>
       </c>
       <c r="E1333" t="n">
         <v>954.8000000000001</v>
@@ -44515,7 +44515,7 @@
         <v>86</v>
       </c>
       <c r="E1336" t="n">
-        <v>985.9000000000001</v>
+        <v>985.9</v>
       </c>
       <c r="F1336" t="n">
         <v>10590</v>
@@ -46558,7 +46558,7 @@
         </is>
       </c>
       <c r="D1398" t="n">
-        <v>75.40000000000001</v>
+        <v>75.39999999999999</v>
       </c>
       <c r="E1398" t="n">
         <v>1658.7</v>
@@ -49231,7 +49231,7 @@
         </is>
       </c>
       <c r="D1479" t="n">
-        <v>68.39999999999999</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="E1479" t="n">
         <v>1916.7</v>

--- a/datos/vistas_negocio/Fact_Global_Master.xlsx
+++ b/datos/vistas_negocio/Fact_Global_Master.xlsx
@@ -43621,7 +43621,7 @@
         </is>
       </c>
       <c r="D1309" t="n">
-        <v>48.40000000000001</v>
+        <v>48.4</v>
       </c>
       <c r="E1309" t="n">
         <v>782.9</v>
@@ -43921,7 +43921,7 @@
         <v>79.7</v>
       </c>
       <c r="E1318" t="n">
-        <v>874.2</v>
+        <v>874.1999999999999</v>
       </c>
       <c r="F1318" t="n">
         <v>11809</v>
@@ -44347,7 +44347,7 @@
         </is>
       </c>
       <c r="D1331" t="n">
-        <v>55.59999999999999</v>
+        <v>55.6</v>
       </c>
       <c r="E1331" t="n">
         <v>994.4</v>
@@ -44413,7 +44413,7 @@
         </is>
       </c>
       <c r="D1333" t="n">
-        <v>62.4</v>
+        <v>62.40000000000001</v>
       </c>
       <c r="E1333" t="n">
         <v>954.8000000000001</v>
@@ -47845,7 +47845,7 @@
         </is>
       </c>
       <c r="D1437" t="n">
-        <v>62.09999999999999</v>
+        <v>62.1</v>
       </c>
       <c r="E1437" t="n">
         <v>1675.9</v>
@@ -49231,7 +49231,7 @@
         </is>
       </c>
       <c r="D1479" t="n">
-        <v>68.40000000000001</v>
+        <v>68.39999999999999</v>
       </c>
       <c r="E1479" t="n">
         <v>1916.7</v>

--- a/datos/vistas_negocio/Fact_Global_Master.xlsx
+++ b/datos/vistas_negocio/Fact_Global_Master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1497"/>
+  <dimension ref="A1:I1505"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41080,7 +41080,7 @@
         </is>
       </c>
       <c r="D1232" t="n">
-        <v>70.09999999999999</v>
+        <v>70.10000000000001</v>
       </c>
       <c r="E1232" t="n">
         <v>121.1</v>
@@ -43195,7 +43195,7 @@
         <v>69.40000000000001</v>
       </c>
       <c r="E1296" t="n">
-        <v>629.8</v>
+        <v>629.8000000000001</v>
       </c>
       <c r="F1296" t="n">
         <v>10233.9</v>
@@ -43621,7 +43621,7 @@
         </is>
       </c>
       <c r="D1309" t="n">
-        <v>48.4</v>
+        <v>48.40000000000001</v>
       </c>
       <c r="E1309" t="n">
         <v>782.9</v>
@@ -44017,7 +44017,7 @@
         </is>
       </c>
       <c r="D1321" t="n">
-        <v>68.09999999999999</v>
+        <v>68.10000000000001</v>
       </c>
       <c r="E1321" t="n">
         <v>837.9</v>
@@ -44251,7 +44251,7 @@
         <v>72</v>
       </c>
       <c r="E1328" t="n">
-        <v>899.9</v>
+        <v>899.9000000000001</v>
       </c>
       <c r="F1328" t="n">
         <v>10504</v>
@@ -44347,7 +44347,7 @@
         </is>
       </c>
       <c r="D1331" t="n">
-        <v>55.6</v>
+        <v>55.59999999999999</v>
       </c>
       <c r="E1331" t="n">
         <v>994.4</v>
@@ -44515,7 +44515,7 @@
         <v>86</v>
       </c>
       <c r="E1336" t="n">
-        <v>985.9</v>
+        <v>985.9000000000001</v>
       </c>
       <c r="F1336" t="n">
         <v>10590</v>
@@ -46393,7 +46393,7 @@
         </is>
       </c>
       <c r="D1393" t="n">
-        <v>73.10000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="E1393" t="n">
         <v>1489.5</v>
@@ -46558,7 +46558,7 @@
         </is>
       </c>
       <c r="D1398" t="n">
-        <v>75.39999999999999</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="E1398" t="n">
         <v>1658.7</v>
@@ -47845,7 +47845,7 @@
         </is>
       </c>
       <c r="D1437" t="n">
-        <v>62.1</v>
+        <v>62.09999999999999</v>
       </c>
       <c r="E1437" t="n">
         <v>1675.9</v>
@@ -49231,7 +49231,7 @@
         </is>
       </c>
       <c r="D1479" t="n">
-        <v>68.39999999999999</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="E1479" t="n">
         <v>1916.7</v>
@@ -49840,6 +49840,270 @@
         <v>1</v>
       </c>
       <c r="I1497" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1498">
+      <c r="A1498" t="inlineStr">
+        <is>
+          <t>5f452f5e66dd374930eb2b71</t>
+        </is>
+      </c>
+      <c r="B1498" t="n">
+        <v>35</v>
+      </c>
+      <c r="C1498" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1498" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="E1498" t="n">
+        <v>2602.3</v>
+      </c>
+      <c r="F1498" t="n">
+        <v>13313.4</v>
+      </c>
+      <c r="G1498" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1498" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1498" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1499">
+      <c r="A1499" t="inlineStr">
+        <is>
+          <t>5f453062ec331549297ee6b8</t>
+        </is>
+      </c>
+      <c r="B1499" t="n">
+        <v>35</v>
+      </c>
+      <c r="C1499" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1499" t="n">
+        <v>42</v>
+      </c>
+      <c r="E1499" t="n">
+        <v>2488.5</v>
+      </c>
+      <c r="F1499" t="n">
+        <v>13179.5</v>
+      </c>
+      <c r="G1499" t="n">
+        <v>7</v>
+      </c>
+      <c r="H1499" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1499" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1500">
+      <c r="A1500" t="inlineStr">
+        <is>
+          <t>5f4530beec331549297ee6d6</t>
+        </is>
+      </c>
+      <c r="B1500" t="n">
+        <v>35</v>
+      </c>
+      <c r="C1500" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1500" t="n">
+        <v>65.10000000000001</v>
+      </c>
+      <c r="E1500" t="n">
+        <v>2422.2</v>
+      </c>
+      <c r="F1500" t="n">
+        <v>12287.3</v>
+      </c>
+      <c r="G1500" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1500" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1500" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1501">
+      <c r="A1501" t="inlineStr">
+        <is>
+          <t>5f4531e9764e7d491e029746</t>
+        </is>
+      </c>
+      <c r="B1501" t="n">
+        <v>35</v>
+      </c>
+      <c r="C1501" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1501" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="E1501" t="n">
+        <v>2170</v>
+      </c>
+      <c r="F1501" t="n">
+        <v>11834.6</v>
+      </c>
+      <c r="G1501" t="n">
+        <v>8</v>
+      </c>
+      <c r="H1501" t="n">
+        <v>7</v>
+      </c>
+      <c r="I1501" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1502">
+      <c r="A1502" t="inlineStr">
+        <is>
+          <t>5f45324dec331549297ee971</t>
+        </is>
+      </c>
+      <c r="B1502" t="n">
+        <v>35</v>
+      </c>
+      <c r="C1502" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1502" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="E1502" t="n">
+        <v>2545.5</v>
+      </c>
+      <c r="F1502" t="n">
+        <v>13480.3</v>
+      </c>
+      <c r="G1502" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1502" t="n">
+        <v>3</v>
+      </c>
+      <c r="I1502" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1503">
+      <c r="A1503" t="inlineStr">
+        <is>
+          <t>5f47ab5b9e2edb0bb831c703</t>
+        </is>
+      </c>
+      <c r="B1503" t="n">
+        <v>35</v>
+      </c>
+      <c r="C1503" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1503" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="E1503" t="n">
+        <v>2141.9</v>
+      </c>
+      <c r="F1503" t="n">
+        <v>10975.8</v>
+      </c>
+      <c r="G1503" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1503" t="n">
+        <v>8</v>
+      </c>
+      <c r="I1503" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1504">
+      <c r="A1504" t="inlineStr">
+        <is>
+          <t>5f47aeb6c387a50bca03dd55</t>
+        </is>
+      </c>
+      <c r="B1504" t="n">
+        <v>35</v>
+      </c>
+      <c r="C1504" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1504" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="E1504" t="n">
+        <v>2241.6</v>
+      </c>
+      <c r="F1504" t="n">
+        <v>11845.7</v>
+      </c>
+      <c r="G1504" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1504" t="n">
+        <v>6</v>
+      </c>
+      <c r="I1504" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1505">
+      <c r="A1505" t="inlineStr">
+        <is>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
+        </is>
+      </c>
+      <c r="B1505" t="n">
+        <v>35</v>
+      </c>
+      <c r="C1505" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1505" t="n">
+        <v>81.3</v>
+      </c>
+      <c r="E1505" t="n">
+        <v>2636.1</v>
+      </c>
+      <c r="F1505" t="n">
+        <v>10171.1</v>
+      </c>
+      <c r="G1505" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1505" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1505" t="n">
         <v>8</v>
       </c>
     </row>

--- a/datos/vistas_negocio/Fact_Global_Master.xlsx
+++ b/datos/vistas_negocio/Fact_Global_Master.xlsx
@@ -41080,7 +41080,7 @@
         </is>
       </c>
       <c r="D1232" t="n">
-        <v>70.10000000000001</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="E1232" t="n">
         <v>121.1</v>
@@ -43195,7 +43195,7 @@
         <v>69.40000000000001</v>
       </c>
       <c r="E1296" t="n">
-        <v>629.8000000000001</v>
+        <v>629.8</v>
       </c>
       <c r="F1296" t="n">
         <v>10233.9</v>
@@ -43621,7 +43621,7 @@
         </is>
       </c>
       <c r="D1309" t="n">
-        <v>48.40000000000001</v>
+        <v>48.4</v>
       </c>
       <c r="E1309" t="n">
         <v>782.9</v>
@@ -44251,7 +44251,7 @@
         <v>72</v>
       </c>
       <c r="E1328" t="n">
-        <v>899.9000000000001</v>
+        <v>899.9</v>
       </c>
       <c r="F1328" t="n">
         <v>10504</v>
@@ -44347,7 +44347,7 @@
         </is>
       </c>
       <c r="D1331" t="n">
-        <v>55.59999999999999</v>
+        <v>55.6</v>
       </c>
       <c r="E1331" t="n">
         <v>994.4</v>
@@ -44413,7 +44413,7 @@
         </is>
       </c>
       <c r="D1333" t="n">
-        <v>62.40000000000001</v>
+        <v>62.4</v>
       </c>
       <c r="E1333" t="n">
         <v>954.8000000000001</v>
@@ -44515,7 +44515,7 @@
         <v>86</v>
       </c>
       <c r="E1336" t="n">
-        <v>985.9000000000001</v>
+        <v>985.9</v>
       </c>
       <c r="F1336" t="n">
         <v>10590</v>
@@ -46558,7 +46558,7 @@
         </is>
       </c>
       <c r="D1398" t="n">
-        <v>75.40000000000001</v>
+        <v>75.39999999999999</v>
       </c>
       <c r="E1398" t="n">
         <v>1658.7</v>
@@ -47845,7 +47845,7 @@
         </is>
       </c>
       <c r="D1437" t="n">
-        <v>62.09999999999999</v>
+        <v>62.1</v>
       </c>
       <c r="E1437" t="n">
         <v>1675.9</v>
@@ -49231,7 +49231,7 @@
         </is>
       </c>
       <c r="D1479" t="n">
-        <v>68.40000000000001</v>
+        <v>68.39999999999999</v>
       </c>
       <c r="E1479" t="n">
         <v>1916.7</v>

--- a/datos/vistas_negocio/Fact_Global_Master.xlsx
+++ b/datos/vistas_negocio/Fact_Global_Master.xlsx
@@ -46393,7 +46393,7 @@
         </is>
       </c>
       <c r="D1393" t="n">
-        <v>73.09999999999999</v>
+        <v>73.10000000000001</v>
       </c>
       <c r="E1393" t="n">
         <v>1489.5</v>
@@ -46558,7 +46558,7 @@
         </is>
       </c>
       <c r="D1398" t="n">
-        <v>75.39999999999999</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="E1398" t="n">
         <v>1658.7</v>
@@ -47845,7 +47845,7 @@
         </is>
       </c>
       <c r="D1437" t="n">
-        <v>62.1</v>
+        <v>62.09999999999999</v>
       </c>
       <c r="E1437" t="n">
         <v>1675.9</v>
@@ -49231,7 +49231,7 @@
         </is>
       </c>
       <c r="D1479" t="n">
-        <v>68.39999999999999</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="E1479" t="n">
         <v>1916.7</v>
@@ -49528,7 +49528,7 @@
         </is>
       </c>
       <c r="D1488" t="n">
-        <v>44.90000000000001</v>
+        <v>44.9</v>
       </c>
       <c r="E1488" t="n">
         <v>2144.5</v>

--- a/datos/vistas_negocio/Fact_Global_Master.xlsx
+++ b/datos/vistas_negocio/Fact_Global_Master.xlsx
@@ -41080,7 +41080,7 @@
         </is>
       </c>
       <c r="D1232" t="n">
-        <v>70.09999999999999</v>
+        <v>70.10000000000001</v>
       </c>
       <c r="E1232" t="n">
         <v>121.1</v>
@@ -43195,7 +43195,7 @@
         <v>69.40000000000001</v>
       </c>
       <c r="E1296" t="n">
-        <v>629.8</v>
+        <v>629.8000000000001</v>
       </c>
       <c r="F1296" t="n">
         <v>10233.9</v>
@@ -43621,7 +43621,7 @@
         </is>
       </c>
       <c r="D1309" t="n">
-        <v>48.4</v>
+        <v>48.40000000000001</v>
       </c>
       <c r="E1309" t="n">
         <v>782.9</v>
@@ -43921,7 +43921,7 @@
         <v>79.7</v>
       </c>
       <c r="E1318" t="n">
-        <v>874.1999999999999</v>
+        <v>874.2</v>
       </c>
       <c r="F1318" t="n">
         <v>11809</v>
@@ -44251,7 +44251,7 @@
         <v>72</v>
       </c>
       <c r="E1328" t="n">
-        <v>899.9</v>
+        <v>899.9000000000001</v>
       </c>
       <c r="F1328" t="n">
         <v>10504</v>
@@ -44413,7 +44413,7 @@
         </is>
       </c>
       <c r="D1333" t="n">
-        <v>62.4</v>
+        <v>62.40000000000001</v>
       </c>
       <c r="E1333" t="n">
         <v>954.8000000000001</v>
@@ -44515,7 +44515,7 @@
         <v>86</v>
       </c>
       <c r="E1336" t="n">
-        <v>985.9</v>
+        <v>985.9000000000001</v>
       </c>
       <c r="F1336" t="n">
         <v>10590</v>
@@ -46393,7 +46393,7 @@
         </is>
       </c>
       <c r="D1393" t="n">
-        <v>73.10000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="E1393" t="n">
         <v>1489.5</v>
@@ -47845,7 +47845,7 @@
         </is>
       </c>
       <c r="D1437" t="n">
-        <v>62.09999999999999</v>
+        <v>62.1</v>
       </c>
       <c r="E1437" t="n">
         <v>1675.9</v>
@@ -49231,7 +49231,7 @@
         </is>
       </c>
       <c r="D1479" t="n">
-        <v>68.40000000000001</v>
+        <v>68.39999999999999</v>
       </c>
       <c r="E1479" t="n">
         <v>1916.7</v>
@@ -49528,7 +49528,7 @@
         </is>
       </c>
       <c r="D1488" t="n">
-        <v>44.9</v>
+        <v>44.90000000000001</v>
       </c>
       <c r="E1488" t="n">
         <v>2144.5</v>

--- a/datos/vistas_negocio/Fact_Global_Master.xlsx
+++ b/datos/vistas_negocio/Fact_Global_Master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1505"/>
+  <dimension ref="A1:I1513"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41080,7 +41080,7 @@
         </is>
       </c>
       <c r="D1232" t="n">
-        <v>70.10000000000001</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="E1232" t="n">
         <v>121.1</v>
@@ -43621,7 +43621,7 @@
         </is>
       </c>
       <c r="D1309" t="n">
-        <v>48.40000000000001</v>
+        <v>48.4</v>
       </c>
       <c r="E1309" t="n">
         <v>782.9</v>
@@ -44017,7 +44017,7 @@
         </is>
       </c>
       <c r="D1321" t="n">
-        <v>68.10000000000001</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="E1321" t="n">
         <v>837.9</v>
@@ -44347,7 +44347,7 @@
         </is>
       </c>
       <c r="D1331" t="n">
-        <v>55.6</v>
+        <v>55.59999999999999</v>
       </c>
       <c r="E1331" t="n">
         <v>994.4</v>
@@ -46393,7 +46393,7 @@
         </is>
       </c>
       <c r="D1393" t="n">
-        <v>73.09999999999999</v>
+        <v>73.10000000000001</v>
       </c>
       <c r="E1393" t="n">
         <v>1489.5</v>
@@ -46558,7 +46558,7 @@
         </is>
       </c>
       <c r="D1398" t="n">
-        <v>75.40000000000001</v>
+        <v>75.39999999999999</v>
       </c>
       <c r="E1398" t="n">
         <v>1658.7</v>
@@ -47845,7 +47845,7 @@
         </is>
       </c>
       <c r="D1437" t="n">
-        <v>62.1</v>
+        <v>62.09999999999999</v>
       </c>
       <c r="E1437" t="n">
         <v>1675.9</v>
@@ -49231,7 +49231,7 @@
         </is>
       </c>
       <c r="D1479" t="n">
-        <v>68.39999999999999</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="E1479" t="n">
         <v>1916.7</v>
@@ -50104,6 +50104,270 @@
         <v>1</v>
       </c>
       <c r="I1505" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1506">
+      <c r="A1506" t="inlineStr">
+        <is>
+          <t>5f452f5e66dd374930eb2b71</t>
+        </is>
+      </c>
+      <c r="B1506" t="n">
+        <v>36</v>
+      </c>
+      <c r="C1506" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1506" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="E1506" t="n">
+        <v>2672.9</v>
+      </c>
+      <c r="F1506" t="n">
+        <v>13384</v>
+      </c>
+      <c r="G1506" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1506" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1506" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1507">
+      <c r="A1507" t="inlineStr">
+        <is>
+          <t>5f453062ec331549297ee6b8</t>
+        </is>
+      </c>
+      <c r="B1507" t="n">
+        <v>36</v>
+      </c>
+      <c r="C1507" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1507" t="n">
+        <v>76.40000000000001</v>
+      </c>
+      <c r="E1507" t="n">
+        <v>2564.9</v>
+      </c>
+      <c r="F1507" t="n">
+        <v>13255.9</v>
+      </c>
+      <c r="G1507" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1507" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1507" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1508">
+      <c r="A1508" t="inlineStr">
+        <is>
+          <t>5f4530beec331549297ee6d6</t>
+        </is>
+      </c>
+      <c r="B1508" t="n">
+        <v>36</v>
+      </c>
+      <c r="C1508" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1508" t="n">
+        <v>60.3</v>
+      </c>
+      <c r="E1508" t="n">
+        <v>2482.5</v>
+      </c>
+      <c r="F1508" t="n">
+        <v>12347.6</v>
+      </c>
+      <c r="G1508" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1508" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1508" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1509">
+      <c r="A1509" t="inlineStr">
+        <is>
+          <t>5f4531e9764e7d491e029746</t>
+        </is>
+      </c>
+      <c r="B1509" t="n">
+        <v>36</v>
+      </c>
+      <c r="C1509" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1509" t="n">
+        <v>60.4</v>
+      </c>
+      <c r="E1509" t="n">
+        <v>2230.4</v>
+      </c>
+      <c r="F1509" t="n">
+        <v>11895</v>
+      </c>
+      <c r="G1509" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1509" t="n">
+        <v>7</v>
+      </c>
+      <c r="I1509" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1510">
+      <c r="A1510" t="inlineStr">
+        <is>
+          <t>5f45324dec331549297ee971</t>
+        </is>
+      </c>
+      <c r="B1510" t="n">
+        <v>36</v>
+      </c>
+      <c r="C1510" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1510" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="E1510" t="n">
+        <v>2599.4</v>
+      </c>
+      <c r="F1510" t="n">
+        <v>13534.2</v>
+      </c>
+      <c r="G1510" t="n">
+        <v>7</v>
+      </c>
+      <c r="H1510" t="n">
+        <v>3</v>
+      </c>
+      <c r="I1510" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1511">
+      <c r="A1511" t="inlineStr">
+        <is>
+          <t>5f47ab5b9e2edb0bb831c703</t>
+        </is>
+      </c>
+      <c r="B1511" t="n">
+        <v>36</v>
+      </c>
+      <c r="C1511" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1511" t="n">
+        <v>75.80000000000001</v>
+      </c>
+      <c r="E1511" t="n">
+        <v>2217.7</v>
+      </c>
+      <c r="F1511" t="n">
+        <v>11051.6</v>
+      </c>
+      <c r="G1511" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1511" t="n">
+        <v>8</v>
+      </c>
+      <c r="I1511" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1512">
+      <c r="A1512" t="inlineStr">
+        <is>
+          <t>5f47aeb6c387a50bca03dd55</t>
+        </is>
+      </c>
+      <c r="B1512" t="n">
+        <v>36</v>
+      </c>
+      <c r="C1512" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1512" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="E1512" t="n">
+        <v>2294.8</v>
+      </c>
+      <c r="F1512" t="n">
+        <v>11898.9</v>
+      </c>
+      <c r="G1512" t="n">
+        <v>8</v>
+      </c>
+      <c r="H1512" t="n">
+        <v>6</v>
+      </c>
+      <c r="I1512" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1513">
+      <c r="A1513" t="inlineStr">
+        <is>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
+        </is>
+      </c>
+      <c r="B1513" t="n">
+        <v>36</v>
+      </c>
+      <c r="C1513" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1513" t="n">
+        <v>87.59999999999999</v>
+      </c>
+      <c r="E1513" t="n">
+        <v>2723.7</v>
+      </c>
+      <c r="F1513" t="n">
+        <v>10258.7</v>
+      </c>
+      <c r="G1513" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1513" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1513" t="n">
         <v>8</v>
       </c>
     </row>

--- a/datos/vistas_negocio/Fact_Global_Master.xlsx
+++ b/datos/vistas_negocio/Fact_Global_Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1473"/>
+  <dimension ref="A1:I1505"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40639,19 +40639,19 @@
         </is>
       </c>
       <c r="D1219" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="E1219" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="F1219" t="n">
-        <v>10723</v>
+        <v>10732</v>
       </c>
       <c r="G1219" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H1219" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I1219" t="n">
         <v>3</v>
@@ -40672,13 +40672,13 @@
         </is>
       </c>
       <c r="D1220" t="n">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E1220" t="n">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="F1220" t="n">
-        <v>9936.1</v>
+        <v>9930.1</v>
       </c>
       <c r="G1220" t="n">
         <v>2</v>
@@ -40705,19 +40705,19 @@
         </is>
       </c>
       <c r="D1221" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="E1221" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="F1221" t="n">
-        <v>9707.6</v>
+        <v>9713.6</v>
       </c>
       <c r="G1221" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H1221" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I1221" t="n">
         <v>5</v>
@@ -40738,13 +40738,13 @@
         </is>
       </c>
       <c r="D1222" t="n">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="E1222" t="n">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="F1222" t="n">
-        <v>11013.8</v>
+        <v>11000.8</v>
       </c>
       <c r="G1222" t="n">
         <v>1</v>
@@ -40771,19 +40771,19 @@
         </is>
       </c>
       <c r="D1223" t="n">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="E1223" t="n">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="F1223" t="n">
-        <v>8888.9</v>
+        <v>8880.9</v>
       </c>
       <c r="G1223" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1223" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I1223" t="n">
         <v>7</v>
@@ -40813,10 +40813,10 @@
         <v>9655.1</v>
       </c>
       <c r="G1224" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1224" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I1224" t="n">
         <v>6</v>
@@ -40837,13 +40837,13 @@
         </is>
       </c>
       <c r="D1225" t="n">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="E1225" t="n">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="F1225" t="n">
-        <v>7604</v>
+        <v>7591</v>
       </c>
       <c r="G1225" t="n">
         <v>3</v>
@@ -40906,16 +40906,16 @@
         <v>93.3</v>
       </c>
       <c r="E1227" t="n">
-        <v>125.3</v>
+        <v>134.3</v>
       </c>
       <c r="F1227" t="n">
-        <v>10816.3</v>
+        <v>10825.3</v>
       </c>
       <c r="G1227" t="n">
         <v>2</v>
       </c>
       <c r="H1227" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I1227" t="n">
         <v>2</v>
@@ -40939,10 +40939,10 @@
         <v>63.40000000000001</v>
       </c>
       <c r="E1228" t="n">
-        <v>134.4</v>
+        <v>128.4</v>
       </c>
       <c r="F1228" t="n">
-        <v>9999.5</v>
+        <v>9993.5</v>
       </c>
       <c r="G1228" t="n">
         <v>4</v>
@@ -40972,10 +40972,10 @@
         <v>103</v>
       </c>
       <c r="E1229" t="n">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="F1229" t="n">
-        <v>9810.6</v>
+        <v>9816.6</v>
       </c>
       <c r="G1229" t="n">
         <v>1</v>
@@ -41005,16 +41005,16 @@
         <v>60.2</v>
       </c>
       <c r="E1230" t="n">
-        <v>139.2</v>
+        <v>126.2</v>
       </c>
       <c r="F1230" t="n">
-        <v>11074</v>
+        <v>11061</v>
       </c>
       <c r="G1230" t="n">
         <v>5</v>
       </c>
       <c r="H1230" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I1230" t="n">
         <v>1</v>
@@ -41038,10 +41038,10 @@
         <v>44.6</v>
       </c>
       <c r="E1231" t="n">
-        <v>99.59999999999999</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="F1231" t="n">
-        <v>8933.5</v>
+        <v>8925.5</v>
       </c>
       <c r="G1231" t="n">
         <v>7</v>
@@ -41080,7 +41080,7 @@
         <v>3</v>
       </c>
       <c r="H1232" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I1232" t="n">
         <v>6</v>
@@ -41104,16 +41104,16 @@
         <v>57.8</v>
       </c>
       <c r="E1233" t="n">
-        <v>126.8</v>
+        <v>113.8</v>
       </c>
       <c r="F1233" t="n">
-        <v>7661.8</v>
+        <v>7648.8</v>
       </c>
       <c r="G1233" t="n">
         <v>6</v>
       </c>
       <c r="H1233" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I1233" t="n">
         <v>8</v>
@@ -41170,16 +41170,16 @@
         <v>66.8</v>
       </c>
       <c r="E1235" t="n">
-        <v>192.1</v>
+        <v>201.1</v>
       </c>
       <c r="F1235" t="n">
-        <v>10883.1</v>
+        <v>10892.1</v>
       </c>
       <c r="G1235" t="n">
         <v>3</v>
       </c>
       <c r="H1235" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1235" t="n">
         <v>2</v>
@@ -41203,16 +41203,16 @@
         <v>73</v>
       </c>
       <c r="E1236" t="n">
-        <v>207.4</v>
+        <v>201.4</v>
       </c>
       <c r="F1236" t="n">
-        <v>10072.5</v>
+        <v>10066.5</v>
       </c>
       <c r="G1236" t="n">
         <v>1</v>
       </c>
       <c r="H1236" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I1236" t="n">
         <v>4</v>
@@ -41236,10 +41236,10 @@
         <v>63.6</v>
       </c>
       <c r="E1237" t="n">
-        <v>209.6</v>
+        <v>215.6</v>
       </c>
       <c r="F1237" t="n">
-        <v>9874.200000000001</v>
+        <v>9880.200000000001</v>
       </c>
       <c r="G1237" t="n">
         <v>4</v>
@@ -41269,16 +41269,16 @@
         <v>70</v>
       </c>
       <c r="E1238" t="n">
-        <v>209.2</v>
+        <v>196.2</v>
       </c>
       <c r="F1238" t="n">
-        <v>11144</v>
+        <v>11131</v>
       </c>
       <c r="G1238" t="n">
         <v>2</v>
       </c>
       <c r="H1238" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I1238" t="n">
         <v>1</v>
@@ -41302,10 +41302,10 @@
         <v>40.5</v>
       </c>
       <c r="E1239" t="n">
-        <v>140.1</v>
+        <v>132.1</v>
       </c>
       <c r="F1239" t="n">
-        <v>8974</v>
+        <v>8966</v>
       </c>
       <c r="G1239" t="n">
         <v>8</v>
@@ -41368,10 +41368,10 @@
         <v>43.5</v>
       </c>
       <c r="E1241" t="n">
-        <v>170.3</v>
+        <v>157.3</v>
       </c>
       <c r="F1241" t="n">
-        <v>7705.3</v>
+        <v>7692.3</v>
       </c>
       <c r="G1241" t="n">
         <v>7</v>
@@ -41434,16 +41434,16 @@
         <v>55.1</v>
       </c>
       <c r="E1243" t="n">
-        <v>247.2</v>
+        <v>256.2</v>
       </c>
       <c r="F1243" t="n">
-        <v>10938.2</v>
+        <v>10947.2</v>
       </c>
       <c r="G1243" t="n">
         <v>6</v>
       </c>
       <c r="H1243" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1243" t="n">
         <v>2</v>
@@ -41467,10 +41467,10 @@
         <v>58.8</v>
       </c>
       <c r="E1244" t="n">
-        <v>266.2</v>
+        <v>260.2</v>
       </c>
       <c r="F1244" t="n">
-        <v>10131.3</v>
+        <v>10125.3</v>
       </c>
       <c r="G1244" t="n">
         <v>3</v>
@@ -41500,10 +41500,10 @@
         <v>86.2</v>
       </c>
       <c r="E1245" t="n">
-        <v>295.8</v>
+        <v>301.8</v>
       </c>
       <c r="F1245" t="n">
-        <v>9960.4</v>
+        <v>9966.4</v>
       </c>
       <c r="G1245" t="n">
         <v>1</v>
@@ -41533,16 +41533,16 @@
         <v>56.8</v>
       </c>
       <c r="E1246" t="n">
-        <v>266</v>
+        <v>253</v>
       </c>
       <c r="F1246" t="n">
-        <v>11200.8</v>
+        <v>11187.8</v>
       </c>
       <c r="G1246" t="n">
         <v>5</v>
       </c>
       <c r="H1246" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1246" t="n">
         <v>1</v>
@@ -41566,10 +41566,10 @@
         <v>53.5</v>
       </c>
       <c r="E1247" t="n">
-        <v>193.6</v>
+        <v>185.6</v>
       </c>
       <c r="F1247" t="n">
-        <v>9027.5</v>
+        <v>9019.5</v>
       </c>
       <c r="G1247" t="n">
         <v>7</v>
@@ -41632,10 +41632,10 @@
         <v>71.5</v>
       </c>
       <c r="E1249" t="n">
-        <v>241.8</v>
+        <v>228.8</v>
       </c>
       <c r="F1249" t="n">
-        <v>7776.8</v>
+        <v>7763.8</v>
       </c>
       <c r="G1249" t="n">
         <v>2</v>
@@ -41698,16 +41698,16 @@
         <v>70.40000000000001</v>
       </c>
       <c r="E1251" t="n">
-        <v>317.6</v>
+        <v>326.6</v>
       </c>
       <c r="F1251" t="n">
-        <v>11008.6</v>
+        <v>11017.6</v>
       </c>
       <c r="G1251" t="n">
         <v>5</v>
       </c>
       <c r="H1251" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1251" t="n">
         <v>2</v>
@@ -41731,16 +41731,16 @@
         <v>57.1</v>
       </c>
       <c r="E1252" t="n">
-        <v>323.3</v>
+        <v>317.3</v>
       </c>
       <c r="F1252" t="n">
-        <v>10188.4</v>
+        <v>10182.4</v>
       </c>
       <c r="G1252" t="n">
         <v>6</v>
       </c>
       <c r="H1252" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1252" t="n">
         <v>4</v>
@@ -41764,10 +41764,10 @@
         <v>82.7</v>
       </c>
       <c r="E1253" t="n">
-        <v>378.5</v>
+        <v>384.5</v>
       </c>
       <c r="F1253" t="n">
-        <v>10043.1</v>
+        <v>10049.1</v>
       </c>
       <c r="G1253" t="n">
         <v>2</v>
@@ -41797,10 +41797,10 @@
         <v>86.5</v>
       </c>
       <c r="E1254" t="n">
-        <v>352.5</v>
+        <v>339.5</v>
       </c>
       <c r="F1254" t="n">
-        <v>11287.3</v>
+        <v>11274.3</v>
       </c>
       <c r="G1254" t="n">
         <v>1</v>
@@ -41830,10 +41830,10 @@
         <v>75.8</v>
       </c>
       <c r="E1255" t="n">
-        <v>269.4</v>
+        <v>261.4</v>
       </c>
       <c r="F1255" t="n">
-        <v>9103.299999999999</v>
+        <v>9095.299999999999</v>
       </c>
       <c r="G1255" t="n">
         <v>4</v>
@@ -41896,10 +41896,10 @@
         <v>55.6</v>
       </c>
       <c r="E1257" t="n">
-        <v>297.4</v>
+        <v>284.4</v>
       </c>
       <c r="F1257" t="n">
-        <v>7832.4</v>
+        <v>7819.4</v>
       </c>
       <c r="G1257" t="n">
         <v>7</v>
@@ -41962,10 +41962,10 @@
         <v>45.6</v>
       </c>
       <c r="E1259" t="n">
-        <v>363.2</v>
+        <v>372.2</v>
       </c>
       <c r="F1259" t="n">
-        <v>11054.2</v>
+        <v>11063.2</v>
       </c>
       <c r="G1259" t="n">
         <v>5</v>
@@ -41995,10 +41995,10 @@
         <v>56.1</v>
       </c>
       <c r="E1260" t="n">
-        <v>379.4</v>
+        <v>373.4</v>
       </c>
       <c r="F1260" t="n">
-        <v>10244.5</v>
+        <v>10238.5</v>
       </c>
       <c r="G1260" t="n">
         <v>3</v>
@@ -42028,10 +42028,10 @@
         <v>61.7</v>
       </c>
       <c r="E1261" t="n">
-        <v>440.2</v>
+        <v>446.2</v>
       </c>
       <c r="F1261" t="n">
-        <v>10104.8</v>
+        <v>10110.8</v>
       </c>
       <c r="G1261" t="n">
         <v>1</v>
@@ -42061,10 +42061,10 @@
         <v>58.3</v>
       </c>
       <c r="E1262" t="n">
-        <v>410.8</v>
+        <v>397.8</v>
       </c>
       <c r="F1262" t="n">
-        <v>11345.6</v>
+        <v>11332.6</v>
       </c>
       <c r="G1262" t="n">
         <v>2</v>
@@ -42094,10 +42094,10 @@
         <v>47.9</v>
       </c>
       <c r="E1263" t="n">
-        <v>317.3</v>
+        <v>309.3</v>
       </c>
       <c r="F1263" t="n">
-        <v>9151.200000000001</v>
+        <v>9143.200000000001</v>
       </c>
       <c r="G1263" t="n">
         <v>4</v>
@@ -42160,10 +42160,10 @@
         <v>34.2</v>
       </c>
       <c r="E1265" t="n">
-        <v>331.6</v>
+        <v>318.6</v>
       </c>
       <c r="F1265" t="n">
-        <v>7866.6</v>
+        <v>7853.6</v>
       </c>
       <c r="G1265" t="n">
         <v>6</v>
@@ -42202,7 +42202,7 @@
         <v>3</v>
       </c>
       <c r="H1266" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I1266" t="n">
         <v>3</v>
@@ -42226,10 +42226,10 @@
         <v>59.40000000000001</v>
       </c>
       <c r="E1267" t="n">
-        <v>422.6</v>
+        <v>431.6</v>
       </c>
       <c r="F1267" t="n">
-        <v>11113.6</v>
+        <v>11122.6</v>
       </c>
       <c r="G1267" t="n">
         <v>5</v>
@@ -42259,10 +42259,10 @@
         <v>78.59999999999999</v>
       </c>
       <c r="E1268" t="n">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="F1268" t="n">
-        <v>10323.1</v>
+        <v>10317.1</v>
       </c>
       <c r="G1268" t="n">
         <v>1</v>
@@ -42292,10 +42292,10 @@
         <v>46</v>
       </c>
       <c r="E1269" t="n">
-        <v>486.2</v>
+        <v>492.2</v>
       </c>
       <c r="F1269" t="n">
-        <v>10150.8</v>
+        <v>10156.8</v>
       </c>
       <c r="G1269" t="n">
         <v>8</v>
@@ -42325,10 +42325,10 @@
         <v>70.09999999999999</v>
       </c>
       <c r="E1270" t="n">
-        <v>480.9</v>
+        <v>467.9</v>
       </c>
       <c r="F1270" t="n">
-        <v>11415.7</v>
+        <v>11402.7</v>
       </c>
       <c r="G1270" t="n">
         <v>4</v>
@@ -42358,16 +42358,16 @@
         <v>52.5</v>
       </c>
       <c r="E1271" t="n">
-        <v>369.8</v>
+        <v>361.8</v>
       </c>
       <c r="F1271" t="n">
-        <v>9203.700000000001</v>
+        <v>9195.700000000001</v>
       </c>
       <c r="G1271" t="n">
         <v>7</v>
       </c>
       <c r="H1271" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I1271" t="n">
         <v>7</v>
@@ -42424,10 +42424,10 @@
         <v>58.2</v>
       </c>
       <c r="E1273" t="n">
-        <v>389.8</v>
+        <v>376.8</v>
       </c>
       <c r="F1273" t="n">
-        <v>7924.8</v>
+        <v>7911.8</v>
       </c>
       <c r="G1273" t="n">
         <v>6</v>
@@ -42466,7 +42466,7 @@
         <v>7</v>
       </c>
       <c r="H1274" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I1274" t="n">
         <v>3</v>
@@ -42490,16 +42490,16 @@
         <v>51.1</v>
       </c>
       <c r="E1275" t="n">
-        <v>473.7</v>
+        <v>482.7</v>
       </c>
       <c r="F1275" t="n">
-        <v>11164.7</v>
+        <v>11173.7</v>
       </c>
       <c r="G1275" t="n">
         <v>8</v>
       </c>
       <c r="H1275" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I1275" t="n">
         <v>2</v>
@@ -42523,10 +42523,10 @@
         <v>62.1</v>
       </c>
       <c r="E1276" t="n">
-        <v>520.1</v>
+        <v>514.1</v>
       </c>
       <c r="F1276" t="n">
-        <v>10385.2</v>
+        <v>10379.2</v>
       </c>
       <c r="G1276" t="n">
         <v>3</v>
@@ -42556,10 +42556,10 @@
         <v>69.5</v>
       </c>
       <c r="E1277" t="n">
-        <v>555.7</v>
+        <v>561.7</v>
       </c>
       <c r="F1277" t="n">
-        <v>10220.3</v>
+        <v>10226.3</v>
       </c>
       <c r="G1277" t="n">
         <v>1</v>
@@ -42589,10 +42589,10 @@
         <v>59.5</v>
       </c>
       <c r="E1278" t="n">
-        <v>540.4</v>
+        <v>527.4</v>
       </c>
       <c r="F1278" t="n">
-        <v>11475.2</v>
+        <v>11462.2</v>
       </c>
       <c r="G1278" t="n">
         <v>5</v>
@@ -42622,16 +42622,16 @@
         <v>54.1</v>
       </c>
       <c r="E1279" t="n">
-        <v>423.9</v>
+        <v>415.9</v>
       </c>
       <c r="F1279" t="n">
-        <v>9257.799999999999</v>
+        <v>9249.799999999999</v>
       </c>
       <c r="G1279" t="n">
         <v>6</v>
       </c>
       <c r="H1279" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I1279" t="n">
         <v>7</v>
@@ -42664,7 +42664,7 @@
         <v>2</v>
       </c>
       <c r="H1280" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I1280" t="n">
         <v>6</v>
@@ -42688,10 +42688,10 @@
         <v>60</v>
       </c>
       <c r="E1281" t="n">
-        <v>449.8</v>
+        <v>436.8</v>
       </c>
       <c r="F1281" t="n">
-        <v>7984.8</v>
+        <v>7971.8</v>
       </c>
       <c r="G1281" t="n">
         <v>4</v>
@@ -42754,10 +42754,10 @@
         <v>67</v>
       </c>
       <c r="E1283" t="n">
-        <v>540.7</v>
+        <v>549.7</v>
       </c>
       <c r="F1283" t="n">
-        <v>11231.7</v>
+        <v>11240.7</v>
       </c>
       <c r="G1283" t="n">
         <v>4</v>
@@ -42787,10 +42787,10 @@
         <v>55.4</v>
       </c>
       <c r="E1284" t="n">
-        <v>575.5</v>
+        <v>569.5</v>
       </c>
       <c r="F1284" t="n">
-        <v>10440.6</v>
+        <v>10434.6</v>
       </c>
       <c r="G1284" t="n">
         <v>7</v>
@@ -42820,10 +42820,10 @@
         <v>57.6</v>
       </c>
       <c r="E1285" t="n">
-        <v>613.3000000000001</v>
+        <v>619.3000000000001</v>
       </c>
       <c r="F1285" t="n">
-        <v>10277.9</v>
+        <v>10283.9</v>
       </c>
       <c r="G1285" t="n">
         <v>6</v>
@@ -42853,10 +42853,10 @@
         <v>66.3</v>
       </c>
       <c r="E1286" t="n">
-        <v>606.7</v>
+        <v>593.7</v>
       </c>
       <c r="F1286" t="n">
-        <v>11541.5</v>
+        <v>11528.5</v>
       </c>
       <c r="G1286" t="n">
         <v>5</v>
@@ -42886,10 +42886,10 @@
         <v>52.1</v>
       </c>
       <c r="E1287" t="n">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="F1287" t="n">
-        <v>9309.9</v>
+        <v>9301.9</v>
       </c>
       <c r="G1287" t="n">
         <v>8</v>
@@ -42952,10 +42952,10 @@
         <v>76.89999999999999</v>
       </c>
       <c r="E1289" t="n">
-        <v>526.7</v>
+        <v>513.7</v>
       </c>
       <c r="F1289" t="n">
-        <v>8061.7</v>
+        <v>8048.7</v>
       </c>
       <c r="G1289" t="n">
         <v>3</v>
@@ -42994,10 +42994,10 @@
         <v>1</v>
       </c>
       <c r="H1290" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I1290" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1291">
@@ -43018,10 +43018,10 @@
         <v>54.8</v>
       </c>
       <c r="E1291" t="n">
-        <v>595.5</v>
+        <v>604.5</v>
       </c>
       <c r="F1291" t="n">
-        <v>11286.5</v>
+        <v>11295.5</v>
       </c>
       <c r="G1291" t="n">
         <v>7</v>
@@ -43030,7 +43030,7 @@
         <v>5</v>
       </c>
       <c r="I1291" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1292">
@@ -43051,10 +43051,10 @@
         <v>68.8</v>
       </c>
       <c r="E1292" t="n">
-        <v>644.3</v>
+        <v>638.3</v>
       </c>
       <c r="F1292" t="n">
-        <v>10509.4</v>
+        <v>10503.4</v>
       </c>
       <c r="G1292" t="n">
         <v>3</v>
@@ -43084,10 +43084,10 @@
         <v>60.2</v>
       </c>
       <c r="E1293" t="n">
-        <v>673.5</v>
+        <v>679.5</v>
       </c>
       <c r="F1293" t="n">
-        <v>10338.1</v>
+        <v>10344.1</v>
       </c>
       <c r="G1293" t="n">
         <v>6</v>
@@ -43117,10 +43117,10 @@
         <v>62.8</v>
       </c>
       <c r="E1294" t="n">
-        <v>669.5</v>
+        <v>656.5</v>
       </c>
       <c r="F1294" t="n">
-        <v>11604.3</v>
+        <v>11591.3</v>
       </c>
       <c r="G1294" t="n">
         <v>5</v>
@@ -43150,10 +43150,10 @@
         <v>50.9</v>
       </c>
       <c r="E1295" t="n">
-        <v>526.9</v>
+        <v>518.9</v>
       </c>
       <c r="F1295" t="n">
-        <v>9360.799999999999</v>
+        <v>9352.799999999999</v>
       </c>
       <c r="G1295" t="n">
         <v>8</v>
@@ -43183,7 +43183,7 @@
         <v>69.40000000000001</v>
       </c>
       <c r="E1296" t="n">
-        <v>629.8</v>
+        <v>629.8000000000001</v>
       </c>
       <c r="F1296" t="n">
         <v>10233.9</v>
@@ -43216,16 +43216,16 @@
         <v>66.3</v>
       </c>
       <c r="E1297" t="n">
-        <v>593</v>
+        <v>580</v>
       </c>
       <c r="F1297" t="n">
-        <v>8128</v>
+        <v>8115</v>
       </c>
       <c r="G1297" t="n">
         <v>4</v>
       </c>
       <c r="H1297" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1297" t="n">
         <v>8</v>
@@ -43282,16 +43282,16 @@
         <v>89.2</v>
       </c>
       <c r="E1299" t="n">
-        <v>684.7</v>
+        <v>693.7</v>
       </c>
       <c r="F1299" t="n">
-        <v>11375.7</v>
+        <v>11384.7</v>
       </c>
       <c r="G1299" t="n">
         <v>2</v>
       </c>
       <c r="H1299" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I1299" t="n">
         <v>2</v>
@@ -43315,16 +43315,16 @@
         <v>79.3</v>
       </c>
       <c r="E1300" t="n">
-        <v>723.6</v>
+        <v>717.6</v>
       </c>
       <c r="F1300" t="n">
-        <v>10588.7</v>
+        <v>10582.7</v>
       </c>
       <c r="G1300" t="n">
         <v>3</v>
       </c>
       <c r="H1300" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I1300" t="n">
         <v>4</v>
@@ -43348,10 +43348,10 @@
         <v>61</v>
       </c>
       <c r="E1301" t="n">
-        <v>734.5</v>
+        <v>740.5</v>
       </c>
       <c r="F1301" t="n">
-        <v>10399.1</v>
+        <v>10405.1</v>
       </c>
       <c r="G1301" t="n">
         <v>6</v>
@@ -43381,16 +43381,16 @@
         <v>57.4</v>
       </c>
       <c r="E1302" t="n">
-        <v>726.9</v>
+        <v>713.9</v>
       </c>
       <c r="F1302" t="n">
-        <v>11661.7</v>
+        <v>11648.7</v>
       </c>
       <c r="G1302" t="n">
         <v>7</v>
       </c>
       <c r="H1302" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I1302" t="n">
         <v>1</v>
@@ -43414,10 +43414,10 @@
         <v>46.4</v>
       </c>
       <c r="E1303" t="n">
-        <v>573.3</v>
+        <v>565.3</v>
       </c>
       <c r="F1303" t="n">
-        <v>9407.200000000001</v>
+        <v>9399.200000000001</v>
       </c>
       <c r="G1303" t="n">
         <v>8</v>
@@ -43480,16 +43480,16 @@
         <v>95.2</v>
       </c>
       <c r="E1305" t="n">
-        <v>688.2</v>
+        <v>675.2</v>
       </c>
       <c r="F1305" t="n">
-        <v>8223.200000000001</v>
+        <v>8210.200000000001</v>
       </c>
       <c r="G1305" t="n">
         <v>1</v>
       </c>
       <c r="H1305" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I1305" t="n">
         <v>8</v>
@@ -43546,16 +43546,16 @@
         <v>78.59999999999999</v>
       </c>
       <c r="E1307" t="n">
-        <v>763.3</v>
+        <v>772.3</v>
       </c>
       <c r="F1307" t="n">
-        <v>11454.3</v>
+        <v>11463.3</v>
       </c>
       <c r="G1307" t="n">
         <v>2</v>
       </c>
       <c r="H1307" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I1307" t="n">
         <v>2</v>
@@ -43579,10 +43579,10 @@
         <v>76.90000000000001</v>
       </c>
       <c r="E1308" t="n">
-        <v>800.5</v>
+        <v>794.5</v>
       </c>
       <c r="F1308" t="n">
-        <v>10665.6</v>
+        <v>10659.6</v>
       </c>
       <c r="G1308" t="n">
         <v>4</v>
@@ -43612,16 +43612,16 @@
         <v>48.4</v>
       </c>
       <c r="E1309" t="n">
-        <v>782.9</v>
+        <v>788.9</v>
       </c>
       <c r="F1309" t="n">
-        <v>10447.5</v>
+        <v>10453.5</v>
       </c>
       <c r="G1309" t="n">
         <v>8</v>
       </c>
       <c r="H1309" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I1309" t="n">
         <v>5</v>
@@ -43645,16 +43645,16 @@
         <v>67.59999999999999</v>
       </c>
       <c r="E1310" t="n">
-        <v>794.5</v>
+        <v>781.5</v>
       </c>
       <c r="F1310" t="n">
-        <v>11729.3</v>
+        <v>11716.3</v>
       </c>
       <c r="G1310" t="n">
         <v>5</v>
       </c>
       <c r="H1310" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I1310" t="n">
         <v>1</v>
@@ -43678,10 +43678,10 @@
         <v>58.1</v>
       </c>
       <c r="E1311" t="n">
-        <v>631.4</v>
+        <v>623.4</v>
       </c>
       <c r="F1311" t="n">
-        <v>9465.299999999999</v>
+        <v>9457.299999999999</v>
       </c>
       <c r="G1311" t="n">
         <v>7</v>
@@ -43744,16 +43744,16 @@
         <v>81.59999999999999</v>
       </c>
       <c r="E1313" t="n">
-        <v>769.8</v>
+        <v>756.8</v>
       </c>
       <c r="F1313" t="n">
-        <v>8304.799999999999</v>
+        <v>8291.799999999999</v>
       </c>
       <c r="G1313" t="n">
         <v>1</v>
       </c>
       <c r="H1313" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I1313" t="n">
         <v>8</v>
@@ -43810,16 +43810,16 @@
         <v>69.8</v>
       </c>
       <c r="E1315" t="n">
-        <v>833.1</v>
+        <v>842.1</v>
       </c>
       <c r="F1315" t="n">
-        <v>11524.1</v>
+        <v>11533.1</v>
       </c>
       <c r="G1315" t="n">
         <v>2</v>
       </c>
       <c r="H1315" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I1315" t="n">
         <v>2</v>
@@ -43843,16 +43843,16 @@
         <v>68.3</v>
       </c>
       <c r="E1316" t="n">
-        <v>868.8</v>
+        <v>862.8</v>
       </c>
       <c r="F1316" t="n">
-        <v>10733.9</v>
+        <v>10727.9</v>
       </c>
       <c r="G1316" t="n">
         <v>3</v>
       </c>
       <c r="H1316" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1316" t="n">
         <v>4</v>
@@ -43876,10 +43876,10 @@
         <v>52.1</v>
       </c>
       <c r="E1317" t="n">
-        <v>835</v>
+        <v>841</v>
       </c>
       <c r="F1317" t="n">
-        <v>10499.6</v>
+        <v>10505.6</v>
       </c>
       <c r="G1317" t="n">
         <v>8</v>
@@ -43909,16 +43909,16 @@
         <v>79.7</v>
       </c>
       <c r="E1318" t="n">
-        <v>874.1999999999999</v>
+        <v>861.2</v>
       </c>
       <c r="F1318" t="n">
-        <v>11809</v>
+        <v>11796</v>
       </c>
       <c r="G1318" t="n">
         <v>1</v>
       </c>
       <c r="H1318" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1318" t="n">
         <v>1</v>
@@ -43942,10 +43942,10 @@
         <v>58</v>
       </c>
       <c r="E1319" t="n">
-        <v>689.4</v>
+        <v>681.4</v>
       </c>
       <c r="F1319" t="n">
-        <v>9523.299999999999</v>
+        <v>9515.299999999999</v>
       </c>
       <c r="G1319" t="n">
         <v>7</v>
@@ -43984,7 +43984,7 @@
         <v>6</v>
       </c>
       <c r="H1320" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I1320" t="n">
         <v>6</v>
@@ -44005,19 +44005,19 @@
         </is>
       </c>
       <c r="D1321" t="n">
-        <v>68.09999999999999</v>
+        <v>68.10000000000001</v>
       </c>
       <c r="E1321" t="n">
-        <v>837.9</v>
+        <v>824.9</v>
       </c>
       <c r="F1321" t="n">
-        <v>8372.9</v>
+        <v>8359.9</v>
       </c>
       <c r="G1321" t="n">
         <v>4</v>
       </c>
       <c r="H1321" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I1321" t="n">
         <v>8</v>
@@ -44074,16 +44074,16 @@
         <v>105.7</v>
       </c>
       <c r="E1323" t="n">
-        <v>938.8</v>
+        <v>947.8</v>
       </c>
       <c r="F1323" t="n">
-        <v>11629.8</v>
+        <v>11638.8</v>
       </c>
       <c r="G1323" t="n">
         <v>1</v>
       </c>
       <c r="H1323" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1323" t="n">
         <v>2</v>
@@ -44107,10 +44107,10 @@
         <v>58.4</v>
       </c>
       <c r="E1324" t="n">
-        <v>927.2</v>
+        <v>921.2</v>
       </c>
       <c r="F1324" t="n">
-        <v>10792.3</v>
+        <v>10786.3</v>
       </c>
       <c r="G1324" t="n">
         <v>7</v>
@@ -44140,10 +44140,10 @@
         <v>57.4</v>
       </c>
       <c r="E1325" t="n">
-        <v>892.4</v>
+        <v>898.4</v>
       </c>
       <c r="F1325" t="n">
-        <v>10557</v>
+        <v>10563</v>
       </c>
       <c r="G1325" t="n">
         <v>8</v>
@@ -44173,16 +44173,16 @@
         <v>83.40000000000001</v>
       </c>
       <c r="E1326" t="n">
-        <v>957.6</v>
+        <v>944.6</v>
       </c>
       <c r="F1326" t="n">
-        <v>11892.4</v>
+        <v>11879.4</v>
       </c>
       <c r="G1326" t="n">
         <v>3</v>
       </c>
       <c r="H1326" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1326" t="n">
         <v>1</v>
@@ -44206,10 +44206,10 @@
         <v>74.3</v>
       </c>
       <c r="E1327" t="n">
-        <v>763.7</v>
+        <v>755.7</v>
       </c>
       <c r="F1327" t="n">
-        <v>9597.6</v>
+        <v>9589.6</v>
       </c>
       <c r="G1327" t="n">
         <v>4</v>
@@ -44239,7 +44239,7 @@
         <v>72</v>
       </c>
       <c r="E1328" t="n">
-        <v>899.9</v>
+        <v>899.9000000000001</v>
       </c>
       <c r="F1328" t="n">
         <v>10504</v>
@@ -44272,10 +44272,10 @@
         <v>87.09999999999999</v>
       </c>
       <c r="E1329" t="n">
-        <v>925</v>
+        <v>912</v>
       </c>
       <c r="F1329" t="n">
-        <v>8460</v>
+        <v>8447</v>
       </c>
       <c r="G1329" t="n">
         <v>2</v>
@@ -44338,10 +44338,10 @@
         <v>55.59999999999999</v>
       </c>
       <c r="E1331" t="n">
-        <v>994.4</v>
+        <v>1003.4</v>
       </c>
       <c r="F1331" t="n">
-        <v>11685.4</v>
+        <v>11694.4</v>
       </c>
       <c r="G1331" t="n">
         <v>7</v>
@@ -44371,16 +44371,16 @@
         <v>50.59999999999999</v>
       </c>
       <c r="E1332" t="n">
-        <v>977.8</v>
+        <v>971.8</v>
       </c>
       <c r="F1332" t="n">
-        <v>10842.9</v>
+        <v>10836.9</v>
       </c>
       <c r="G1332" t="n">
         <v>8</v>
       </c>
       <c r="H1332" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I1332" t="n">
         <v>4</v>
@@ -44404,10 +44404,10 @@
         <v>62.40000000000001</v>
       </c>
       <c r="E1333" t="n">
-        <v>954.8000000000001</v>
+        <v>960.8000000000001</v>
       </c>
       <c r="F1333" t="n">
-        <v>10619.4</v>
+        <v>10625.4</v>
       </c>
       <c r="G1333" t="n">
         <v>4</v>
@@ -44437,10 +44437,10 @@
         <v>81.90000000000001</v>
       </c>
       <c r="E1334" t="n">
-        <v>1039.5</v>
+        <v>1026.5</v>
       </c>
       <c r="F1334" t="n">
-        <v>11974.3</v>
+        <v>11961.3</v>
       </c>
       <c r="G1334" t="n">
         <v>2</v>
@@ -44470,10 +44470,10 @@
         <v>63.3</v>
       </c>
       <c r="E1335" t="n">
-        <v>827</v>
+        <v>819</v>
       </c>
       <c r="F1335" t="n">
-        <v>9660.9</v>
+        <v>9652.9</v>
       </c>
       <c r="G1335" t="n">
         <v>3</v>
@@ -44503,7 +44503,7 @@
         <v>86</v>
       </c>
       <c r="E1336" t="n">
-        <v>985.9</v>
+        <v>985.9000000000001</v>
       </c>
       <c r="F1336" t="n">
         <v>10590</v>
@@ -44536,16 +44536,16 @@
         <v>58.1</v>
       </c>
       <c r="E1337" t="n">
-        <v>983.1</v>
+        <v>970.1</v>
       </c>
       <c r="F1337" t="n">
-        <v>8518.1</v>
+        <v>8505.1</v>
       </c>
       <c r="G1337" t="n">
         <v>6</v>
       </c>
       <c r="H1337" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I1337" t="n">
         <v>8</v>
@@ -44602,10 +44602,10 @@
         <v>88.7</v>
       </c>
       <c r="E1339" t="n">
-        <v>1083.1</v>
+        <v>1092.1</v>
       </c>
       <c r="F1339" t="n">
-        <v>11774.1</v>
+        <v>11783.1</v>
       </c>
       <c r="G1339" t="n">
         <v>1</v>
@@ -44635,16 +44635,16 @@
         <v>76.8</v>
       </c>
       <c r="E1340" t="n">
-        <v>1054.6</v>
+        <v>1048.6</v>
       </c>
       <c r="F1340" t="n">
-        <v>10919.7</v>
+        <v>10913.7</v>
       </c>
       <c r="G1340" t="n">
         <v>3</v>
       </c>
       <c r="H1340" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1340" t="n">
         <v>4</v>
@@ -44668,10 +44668,10 @@
         <v>45</v>
       </c>
       <c r="E1341" t="n">
-        <v>999.8000000000001</v>
+        <v>1005.8</v>
       </c>
       <c r="F1341" t="n">
-        <v>10664.4</v>
+        <v>10670.4</v>
       </c>
       <c r="G1341" t="n">
         <v>8</v>
@@ -44701,10 +44701,10 @@
         <v>81.2</v>
       </c>
       <c r="E1342" t="n">
-        <v>1120.7</v>
+        <v>1107.7</v>
       </c>
       <c r="F1342" t="n">
-        <v>12055.5</v>
+        <v>12042.5</v>
       </c>
       <c r="G1342" t="n">
         <v>2</v>
@@ -44734,10 +44734,10 @@
         <v>63.7</v>
       </c>
       <c r="E1343" t="n">
-        <v>890.7</v>
+        <v>882.7</v>
       </c>
       <c r="F1343" t="n">
-        <v>9724.6</v>
+        <v>9716.6</v>
       </c>
       <c r="G1343" t="n">
         <v>6</v>
@@ -44776,7 +44776,7 @@
         <v>4</v>
       </c>
       <c r="H1344" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1344" t="n">
         <v>6</v>
@@ -44800,10 +44800,10 @@
         <v>60.2</v>
       </c>
       <c r="E1345" t="n">
-        <v>1043.3</v>
+        <v>1030.3</v>
       </c>
       <c r="F1345" t="n">
-        <v>8578.299999999999</v>
+        <v>8565.299999999999</v>
       </c>
       <c r="G1345" t="n">
         <v>7</v>
@@ -44866,10 +44866,10 @@
         <v>59.9</v>
       </c>
       <c r="E1347" t="n">
-        <v>1143</v>
+        <v>1152</v>
       </c>
       <c r="F1347" t="n">
-        <v>11834</v>
+        <v>11843</v>
       </c>
       <c r="G1347" t="n">
         <v>6</v>
@@ -44899,10 +44899,10 @@
         <v>70.2</v>
       </c>
       <c r="E1348" t="n">
-        <v>1124.8</v>
+        <v>1118.8</v>
       </c>
       <c r="F1348" t="n">
-        <v>10989.9</v>
+        <v>10983.9</v>
       </c>
       <c r="G1348" t="n">
         <v>4</v>
@@ -44932,10 +44932,10 @@
         <v>0</v>
       </c>
       <c r="E1349" t="n">
-        <v>999.8000000000001</v>
+        <v>1005.8</v>
       </c>
       <c r="F1349" t="n">
-        <v>10664.4</v>
+        <v>10670.4</v>
       </c>
       <c r="G1349" t="n">
         <v>8</v>
@@ -44965,10 +44965,10 @@
         <v>94</v>
       </c>
       <c r="E1350" t="n">
-        <v>1214.7</v>
+        <v>1201.7</v>
       </c>
       <c r="F1350" t="n">
-        <v>12149.5</v>
+        <v>12136.5</v>
       </c>
       <c r="G1350" t="n">
         <v>1</v>
@@ -44998,10 +44998,10 @@
         <v>61.6</v>
       </c>
       <c r="E1351" t="n">
-        <v>952.3</v>
+        <v>944.3</v>
       </c>
       <c r="F1351" t="n">
-        <v>9786.200000000001</v>
+        <v>9778.200000000001</v>
       </c>
       <c r="G1351" t="n">
         <v>5</v>
@@ -45064,10 +45064,10 @@
         <v>89.5</v>
       </c>
       <c r="E1353" t="n">
-        <v>1132.8</v>
+        <v>1119.8</v>
       </c>
       <c r="F1353" t="n">
-        <v>8667.799999999999</v>
+        <v>8654.799999999999</v>
       </c>
       <c r="G1353" t="n">
         <v>2</v>
@@ -45127,13 +45127,13 @@
         </is>
       </c>
       <c r="D1355" t="n">
-        <v>45.8</v>
+        <v>35.8</v>
       </c>
       <c r="E1355" t="n">
-        <v>1188.8</v>
+        <v>1187.8</v>
       </c>
       <c r="F1355" t="n">
-        <v>11879.8</v>
+        <v>11878.8</v>
       </c>
       <c r="G1355" t="n">
         <v>8</v>
@@ -45163,10 +45163,10 @@
         <v>59.2</v>
       </c>
       <c r="E1356" t="n">
-        <v>1184</v>
+        <v>1178</v>
       </c>
       <c r="F1356" t="n">
-        <v>11049.1</v>
+        <v>11043.1</v>
       </c>
       <c r="G1356" t="n">
         <v>6</v>
@@ -45196,10 +45196,10 @@
         <v>82.2</v>
       </c>
       <c r="E1357" t="n">
-        <v>1082</v>
+        <v>1088</v>
       </c>
       <c r="F1357" t="n">
-        <v>10746.6</v>
+        <v>10752.6</v>
       </c>
       <c r="G1357" t="n">
         <v>2</v>
@@ -45229,10 +45229,10 @@
         <v>63</v>
       </c>
       <c r="E1358" t="n">
-        <v>1277.7</v>
+        <v>1264.7</v>
       </c>
       <c r="F1358" t="n">
-        <v>12212.5</v>
+        <v>12199.5</v>
       </c>
       <c r="G1358" t="n">
         <v>5</v>
@@ -45262,10 +45262,10 @@
         <v>56.6</v>
       </c>
       <c r="E1359" t="n">
-        <v>1008.9</v>
+        <v>1000.9</v>
       </c>
       <c r="F1359" t="n">
-        <v>9842.799999999999</v>
+        <v>9834.799999999999</v>
       </c>
       <c r="G1359" t="n">
         <v>7</v>
@@ -45328,10 +45328,10 @@
         <v>87.3</v>
       </c>
       <c r="E1361" t="n">
-        <v>1220.1</v>
+        <v>1207.1</v>
       </c>
       <c r="F1361" t="n">
-        <v>8755.1</v>
+        <v>8742.1</v>
       </c>
       <c r="G1361" t="n">
         <v>1</v>
@@ -45394,16 +45394,16 @@
         <v>76.5</v>
       </c>
       <c r="E1363" t="n">
-        <v>1265.3</v>
+        <v>1264.3</v>
       </c>
       <c r="F1363" t="n">
-        <v>11956.3</v>
+        <v>11955.3</v>
       </c>
       <c r="G1363" t="n">
         <v>2</v>
       </c>
       <c r="H1363" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I1363" t="n">
         <v>2</v>
@@ -45427,16 +45427,16 @@
         <v>75.2</v>
       </c>
       <c r="E1364" t="n">
-        <v>1259.2</v>
+        <v>1253.2</v>
       </c>
       <c r="F1364" t="n">
-        <v>11124.3</v>
+        <v>11118.3</v>
       </c>
       <c r="G1364" t="n">
         <v>3</v>
       </c>
       <c r="H1364" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I1364" t="n">
         <v>4</v>
@@ -45460,10 +45460,10 @@
         <v>46.7</v>
       </c>
       <c r="E1365" t="n">
-        <v>1128.7</v>
+        <v>1134.7</v>
       </c>
       <c r="F1365" t="n">
-        <v>10793.3</v>
+        <v>10799.3</v>
       </c>
       <c r="G1365" t="n">
         <v>8</v>
@@ -45493,10 +45493,10 @@
         <v>79.40000000000001</v>
       </c>
       <c r="E1366" t="n">
-        <v>1357.1</v>
+        <v>1344.1</v>
       </c>
       <c r="F1366" t="n">
-        <v>12291.9</v>
+        <v>12278.9</v>
       </c>
       <c r="G1366" t="n">
         <v>1</v>
@@ -45526,10 +45526,10 @@
         <v>56.59999999999999</v>
       </c>
       <c r="E1367" t="n">
-        <v>1065.5</v>
+        <v>1057.5</v>
       </c>
       <c r="F1367" t="n">
-        <v>9899.4</v>
+        <v>9891.4</v>
       </c>
       <c r="G1367" t="n">
         <v>6</v>
@@ -45568,7 +45568,7 @@
         <v>5</v>
       </c>
       <c r="H1368" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I1368" t="n">
         <v>5</v>
@@ -45592,16 +45592,16 @@
         <v>54.8</v>
       </c>
       <c r="E1369" t="n">
-        <v>1274.9</v>
+        <v>1261.9</v>
       </c>
       <c r="F1369" t="n">
-        <v>8809.9</v>
+        <v>8796.9</v>
       </c>
       <c r="G1369" t="n">
         <v>7</v>
       </c>
       <c r="H1369" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I1369" t="n">
         <v>8</v>
@@ -45658,10 +45658,10 @@
         <v>65.2</v>
       </c>
       <c r="E1371" t="n">
-        <v>1330.5</v>
+        <v>1329.5</v>
       </c>
       <c r="F1371" t="n">
-        <v>12021.5</v>
+        <v>12020.5</v>
       </c>
       <c r="G1371" t="n">
         <v>7</v>
@@ -45691,16 +45691,16 @@
         <v>97.59999999999999</v>
       </c>
       <c r="E1372" t="n">
-        <v>1356.8</v>
+        <v>1350.8</v>
       </c>
       <c r="F1372" t="n">
-        <v>11221.9</v>
+        <v>11215.9</v>
       </c>
       <c r="G1372" t="n">
         <v>1</v>
       </c>
       <c r="H1372" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I1372" t="n">
         <v>4</v>
@@ -45724,10 +45724,10 @@
         <v>63.3</v>
       </c>
       <c r="E1373" t="n">
-        <v>1192</v>
+        <v>1198</v>
       </c>
       <c r="F1373" t="n">
-        <v>10856.6</v>
+        <v>10862.6</v>
       </c>
       <c r="G1373" t="n">
         <v>8</v>
@@ -45757,10 +45757,10 @@
         <v>79.3</v>
       </c>
       <c r="E1374" t="n">
-        <v>1436.4</v>
+        <v>1423.4</v>
       </c>
       <c r="F1374" t="n">
-        <v>12371.2</v>
+        <v>12358.2</v>
       </c>
       <c r="G1374" t="n">
         <v>5</v>
@@ -45790,10 +45790,10 @@
         <v>81.7</v>
       </c>
       <c r="E1375" t="n">
-        <v>1147.2</v>
+        <v>1139.2</v>
       </c>
       <c r="F1375" t="n">
-        <v>9981.1</v>
+        <v>9973.1</v>
       </c>
       <c r="G1375" t="n">
         <v>4</v>
@@ -45856,16 +45856,16 @@
         <v>82.59999999999999</v>
       </c>
       <c r="E1377" t="n">
-        <v>1357.5</v>
+        <v>1344.5</v>
       </c>
       <c r="F1377" t="n">
-        <v>8892.5</v>
+        <v>8879.5</v>
       </c>
       <c r="G1377" t="n">
         <v>3</v>
       </c>
       <c r="H1377" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I1377" t="n">
         <v>8</v>
@@ -45922,16 +45922,16 @@
         <v>80.3</v>
       </c>
       <c r="E1379" t="n">
-        <v>1410.8</v>
+        <v>1409.8</v>
       </c>
       <c r="F1379" t="n">
-        <v>12101.8</v>
+        <v>12100.8</v>
       </c>
       <c r="G1379" t="n">
         <v>2</v>
       </c>
       <c r="H1379" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1379" t="n">
         <v>3</v>
@@ -45955,10 +45955,10 @@
         <v>60.3</v>
       </c>
       <c r="E1380" t="n">
-        <v>1417.1</v>
+        <v>1411.1</v>
       </c>
       <c r="F1380" t="n">
-        <v>11282.2</v>
+        <v>11276.2</v>
       </c>
       <c r="G1380" t="n">
         <v>6</v>
@@ -45988,10 +45988,10 @@
         <v>67.59999999999999</v>
       </c>
       <c r="E1381" t="n">
-        <v>1259.6</v>
+        <v>1265.6</v>
       </c>
       <c r="F1381" t="n">
-        <v>10924.2</v>
+        <v>10930.2</v>
       </c>
       <c r="G1381" t="n">
         <v>4</v>
@@ -46021,10 +46021,10 @@
         <v>70.2</v>
       </c>
       <c r="E1382" t="n">
-        <v>1506.6</v>
+        <v>1493.6</v>
       </c>
       <c r="F1382" t="n">
-        <v>12441.4</v>
+        <v>12428.4</v>
       </c>
       <c r="G1382" t="n">
         <v>3</v>
@@ -46054,10 +46054,10 @@
         <v>61.2</v>
       </c>
       <c r="E1383" t="n">
-        <v>1208.4</v>
+        <v>1200.4</v>
       </c>
       <c r="F1383" t="n">
-        <v>10042.3</v>
+        <v>10034.3</v>
       </c>
       <c r="G1383" t="n">
         <v>5</v>
@@ -46120,16 +46120,16 @@
         <v>58.9</v>
       </c>
       <c r="E1385" t="n">
-        <v>1416.4</v>
+        <v>1403.4</v>
       </c>
       <c r="F1385" t="n">
-        <v>8951.4</v>
+        <v>8938.4</v>
       </c>
       <c r="G1385" t="n">
         <v>7</v>
       </c>
       <c r="H1385" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1385" t="n">
         <v>8</v>
@@ -46186,16 +46186,16 @@
         <v>77.2</v>
       </c>
       <c r="E1387" t="n">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="F1387" t="n">
-        <v>12179</v>
+        <v>12178</v>
       </c>
       <c r="G1387" t="n">
         <v>4</v>
       </c>
       <c r="H1387" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I1387" t="n">
         <v>3</v>
@@ -46219,10 +46219,10 @@
         <v>80.3</v>
       </c>
       <c r="E1388" t="n">
-        <v>1497.4</v>
+        <v>1491.4</v>
       </c>
       <c r="F1388" t="n">
-        <v>11362.5</v>
+        <v>11356.5</v>
       </c>
       <c r="G1388" t="n">
         <v>3</v>
@@ -46252,10 +46252,10 @@
         <v>50.6</v>
       </c>
       <c r="E1389" t="n">
-        <v>1310.2</v>
+        <v>1316.2</v>
       </c>
       <c r="F1389" t="n">
-        <v>10974.8</v>
+        <v>10980.8</v>
       </c>
       <c r="G1389" t="n">
         <v>7</v>
@@ -46285,10 +46285,10 @@
         <v>76.7</v>
       </c>
       <c r="E1390" t="n">
-        <v>1583.3</v>
+        <v>1570.3</v>
       </c>
       <c r="F1390" t="n">
-        <v>12518.1</v>
+        <v>12505.1</v>
       </c>
       <c r="G1390" t="n">
         <v>5</v>
@@ -46318,10 +46318,10 @@
         <v>48.7</v>
       </c>
       <c r="E1391" t="n">
-        <v>1257.1</v>
+        <v>1249.1</v>
       </c>
       <c r="F1391" t="n">
-        <v>10091</v>
+        <v>10083</v>
       </c>
       <c r="G1391" t="n">
         <v>8</v>
@@ -46384,16 +46384,16 @@
         <v>73.10000000000001</v>
       </c>
       <c r="E1393" t="n">
-        <v>1489.5</v>
+        <v>1476.5</v>
       </c>
       <c r="F1393" t="n">
-        <v>9024.5</v>
+        <v>9011.5</v>
       </c>
       <c r="G1393" t="n">
         <v>6</v>
       </c>
       <c r="H1393" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I1393" t="n">
         <v>8</v>
@@ -46426,7 +46426,7 @@
         <v>3</v>
       </c>
       <c r="H1394" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1394" t="n">
         <v>2</v>
@@ -46450,10 +46450,10 @@
         <v>84.09999999999999</v>
       </c>
       <c r="E1395" t="n">
-        <v>1572.1</v>
+        <v>1571.1</v>
       </c>
       <c r="F1395" t="n">
-        <v>12263.1</v>
+        <v>12262.1</v>
       </c>
       <c r="G1395" t="n">
         <v>1</v>
@@ -46483,10 +46483,10 @@
         <v>59.3</v>
       </c>
       <c r="E1396" t="n">
-        <v>1556.7</v>
+        <v>1550.7</v>
       </c>
       <c r="F1396" t="n">
-        <v>11421.8</v>
+        <v>11415.8</v>
       </c>
       <c r="G1396" t="n">
         <v>8</v>
@@ -46516,10 +46516,10 @@
         <v>71.5</v>
       </c>
       <c r="E1397" t="n">
-        <v>1381.7</v>
+        <v>1387.7</v>
       </c>
       <c r="F1397" t="n">
-        <v>11046.3</v>
+        <v>11052.3</v>
       </c>
       <c r="G1397" t="n">
         <v>6</v>
@@ -46549,10 +46549,10 @@
         <v>75.39999999999999</v>
       </c>
       <c r="E1398" t="n">
-        <v>1658.7</v>
+        <v>1645.7</v>
       </c>
       <c r="F1398" t="n">
-        <v>12593.5</v>
+        <v>12580.5</v>
       </c>
       <c r="G1398" t="n">
         <v>4</v>
@@ -46582,10 +46582,10 @@
         <v>62.7</v>
       </c>
       <c r="E1399" t="n">
-        <v>1319.8</v>
+        <v>1311.8</v>
       </c>
       <c r="F1399" t="n">
-        <v>10153.7</v>
+        <v>10145.7</v>
       </c>
       <c r="G1399" t="n">
         <v>7</v>
@@ -46648,16 +46648,16 @@
         <v>79.09999999999999</v>
       </c>
       <c r="E1401" t="n">
-        <v>1568.6</v>
+        <v>1555.6</v>
       </c>
       <c r="F1401" t="n">
-        <v>9103.6</v>
+        <v>9090.6</v>
       </c>
       <c r="G1401" t="n">
         <v>2</v>
       </c>
       <c r="H1401" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1401" t="n">
         <v>8</v>
@@ -46690,7 +46690,7 @@
         <v>2</v>
       </c>
       <c r="H1402" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I1402" t="n">
         <v>2</v>
@@ -46714,16 +46714,16 @@
         <v>62.7</v>
       </c>
       <c r="E1403" t="n">
-        <v>1634.8</v>
+        <v>1633.8</v>
       </c>
       <c r="F1403" t="n">
-        <v>12325.8</v>
+        <v>12324.8</v>
       </c>
       <c r="G1403" t="n">
         <v>5</v>
       </c>
       <c r="H1403" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1403" t="n">
         <v>3</v>
@@ -46747,10 +46747,10 @@
         <v>49.2</v>
       </c>
       <c r="E1404" t="n">
-        <v>1605.9</v>
+        <v>1599.9</v>
       </c>
       <c r="F1404" t="n">
-        <v>11471</v>
+        <v>11465</v>
       </c>
       <c r="G1404" t="n">
         <v>6</v>
@@ -46780,10 +46780,10 @@
         <v>43.9</v>
       </c>
       <c r="E1405" t="n">
-        <v>1425.6</v>
+        <v>1431.6</v>
       </c>
       <c r="F1405" t="n">
-        <v>11090.2</v>
+        <v>11096.2</v>
       </c>
       <c r="G1405" t="n">
         <v>7</v>
@@ -46813,10 +46813,10 @@
         <v>71.2</v>
       </c>
       <c r="E1406" t="n">
-        <v>1729.9</v>
+        <v>1716.9</v>
       </c>
       <c r="F1406" t="n">
-        <v>12664.7</v>
+        <v>12651.7</v>
       </c>
       <c r="G1406" t="n">
         <v>3</v>
@@ -46846,10 +46846,10 @@
         <v>64.09999999999999</v>
       </c>
       <c r="E1407" t="n">
-        <v>1383.9</v>
+        <v>1375.9</v>
       </c>
       <c r="F1407" t="n">
-        <v>10217.8</v>
+        <v>10209.8</v>
       </c>
       <c r="G1407" t="n">
         <v>4</v>
@@ -46912,16 +46912,16 @@
         <v>73.8</v>
       </c>
       <c r="E1409" t="n">
-        <v>1642.4</v>
+        <v>1629.4</v>
       </c>
       <c r="F1409" t="n">
-        <v>9177.4</v>
+        <v>9164.4</v>
       </c>
       <c r="G1409" t="n">
         <v>1</v>
       </c>
       <c r="H1409" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I1409" t="n">
         <v>8</v>
@@ -46978,16 +46978,16 @@
         <v>62.3</v>
       </c>
       <c r="E1411" t="n">
-        <v>1697.1</v>
+        <v>1696.1</v>
       </c>
       <c r="F1411" t="n">
-        <v>12388.1</v>
+        <v>12387.1</v>
       </c>
       <c r="G1411" t="n">
         <v>4</v>
       </c>
       <c r="H1411" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1411" t="n">
         <v>3</v>
@@ -47011,10 +47011,10 @@
         <v>50.4</v>
       </c>
       <c r="E1412" t="n">
-        <v>1656.3</v>
+        <v>1650.3</v>
       </c>
       <c r="F1412" t="n">
-        <v>11521.4</v>
+        <v>11515.4</v>
       </c>
       <c r="G1412" t="n">
         <v>7</v>
@@ -47044,10 +47044,10 @@
         <v>48.8</v>
       </c>
       <c r="E1413" t="n">
-        <v>1474.4</v>
+        <v>1480.4</v>
       </c>
       <c r="F1413" t="n">
-        <v>11139</v>
+        <v>11145</v>
       </c>
       <c r="G1413" t="n">
         <v>8</v>
@@ -47077,10 +47077,10 @@
         <v>75</v>
       </c>
       <c r="E1414" t="n">
-        <v>1804.9</v>
+        <v>1791.9</v>
       </c>
       <c r="F1414" t="n">
-        <v>12739.7</v>
+        <v>12726.7</v>
       </c>
       <c r="G1414" t="n">
         <v>2</v>
@@ -47110,10 +47110,10 @@
         <v>64.5</v>
       </c>
       <c r="E1415" t="n">
-        <v>1448.4</v>
+        <v>1440.4</v>
       </c>
       <c r="F1415" t="n">
-        <v>10282.3</v>
+        <v>10274.3</v>
       </c>
       <c r="G1415" t="n">
         <v>3</v>
@@ -47176,16 +47176,16 @@
         <v>57.7</v>
       </c>
       <c r="E1417" t="n">
-        <v>1700.1</v>
+        <v>1687.1</v>
       </c>
       <c r="F1417" t="n">
-        <v>9235.1</v>
+        <v>9222.1</v>
       </c>
       <c r="G1417" t="n">
         <v>6</v>
       </c>
       <c r="H1417" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1417" t="n">
         <v>8</v>
@@ -47242,10 +47242,10 @@
         <v>75.59999999999999</v>
       </c>
       <c r="E1419" t="n">
-        <v>1772.7</v>
+        <v>1771.7</v>
       </c>
       <c r="F1419" t="n">
-        <v>12463.7</v>
+        <v>12462.7</v>
       </c>
       <c r="G1419" t="n">
         <v>3</v>
@@ -47275,10 +47275,10 @@
         <v>50.9</v>
       </c>
       <c r="E1420" t="n">
-        <v>1707.2</v>
+        <v>1701.2</v>
       </c>
       <c r="F1420" t="n">
-        <v>11572.3</v>
+        <v>11566.3</v>
       </c>
       <c r="G1420" t="n">
         <v>8</v>
@@ -47308,10 +47308,10 @@
         <v>65.3</v>
       </c>
       <c r="E1421" t="n">
-        <v>1539.7</v>
+        <v>1545.7</v>
       </c>
       <c r="F1421" t="n">
-        <v>11204.3</v>
+        <v>11210.3</v>
       </c>
       <c r="G1421" t="n">
         <v>4</v>
@@ -47341,10 +47341,10 @@
         <v>58.4</v>
       </c>
       <c r="E1422" t="n">
-        <v>1863.3</v>
+        <v>1850.3</v>
       </c>
       <c r="F1422" t="n">
-        <v>12798.1</v>
+        <v>12785.1</v>
       </c>
       <c r="G1422" t="n">
         <v>6</v>
@@ -47374,10 +47374,10 @@
         <v>58.6</v>
       </c>
       <c r="E1423" t="n">
-        <v>1507</v>
+        <v>1499</v>
       </c>
       <c r="F1423" t="n">
-        <v>10340.9</v>
+        <v>10332.9</v>
       </c>
       <c r="G1423" t="n">
         <v>5</v>
@@ -47440,10 +47440,10 @@
         <v>96</v>
       </c>
       <c r="E1425" t="n">
-        <v>1796.1</v>
+        <v>1783.1</v>
       </c>
       <c r="F1425" t="n">
-        <v>9331.1</v>
+        <v>9318.1</v>
       </c>
       <c r="G1425" t="n">
         <v>1</v>
@@ -47506,10 +47506,10 @@
         <v>66.59999999999999</v>
       </c>
       <c r="E1427" t="n">
-        <v>1839.3</v>
+        <v>1838.3</v>
       </c>
       <c r="F1427" t="n">
-        <v>12530.3</v>
+        <v>12529.3</v>
       </c>
       <c r="G1427" t="n">
         <v>4</v>
@@ -47539,16 +47539,16 @@
         <v>60.1</v>
       </c>
       <c r="E1428" t="n">
-        <v>1767.3</v>
+        <v>1761.3</v>
       </c>
       <c r="F1428" t="n">
-        <v>11632.4</v>
+        <v>11626.4</v>
       </c>
       <c r="G1428" t="n">
         <v>6</v>
       </c>
       <c r="H1428" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I1428" t="n">
         <v>4</v>
@@ -47572,10 +47572,10 @@
         <v>74.09999999999999</v>
       </c>
       <c r="E1429" t="n">
-        <v>1613.8</v>
+        <v>1619.8</v>
       </c>
       <c r="F1429" t="n">
-        <v>11278.4</v>
+        <v>11284.4</v>
       </c>
       <c r="G1429" t="n">
         <v>3</v>
@@ -47605,10 +47605,10 @@
         <v>57.4</v>
       </c>
       <c r="E1430" t="n">
-        <v>1920.7</v>
+        <v>1907.7</v>
       </c>
       <c r="F1430" t="n">
-        <v>12855.5</v>
+        <v>12842.5</v>
       </c>
       <c r="G1430" t="n">
         <v>7</v>
@@ -47638,10 +47638,10 @@
         <v>0</v>
       </c>
       <c r="E1431" t="n">
-        <v>1507</v>
+        <v>1499</v>
       </c>
       <c r="F1431" t="n">
-        <v>10340.9</v>
+        <v>10332.9</v>
       </c>
       <c r="G1431" t="n">
         <v>8</v>
@@ -47680,7 +47680,7 @@
         <v>5</v>
       </c>
       <c r="H1432" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I1432" t="n">
         <v>5</v>
@@ -47704,10 +47704,10 @@
         <v>76</v>
       </c>
       <c r="E1433" t="n">
-        <v>1872.1</v>
+        <v>1859.1</v>
       </c>
       <c r="F1433" t="n">
-        <v>9407.1</v>
+        <v>9394.1</v>
       </c>
       <c r="G1433" t="n">
         <v>2</v>
@@ -47746,7 +47746,7 @@
         <v>6</v>
       </c>
       <c r="H1434" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I1434" t="n">
         <v>2</v>
@@ -47770,10 +47770,10 @@
         <v>92.90000000000001</v>
       </c>
       <c r="E1435" t="n">
-        <v>1932.2</v>
+        <v>1931.2</v>
       </c>
       <c r="F1435" t="n">
-        <v>12623.2</v>
+        <v>12622.2</v>
       </c>
       <c r="G1435" t="n">
         <v>2</v>
@@ -47803,10 +47803,10 @@
         <v>51.6</v>
       </c>
       <c r="E1436" t="n">
-        <v>1818.9</v>
+        <v>1812.9</v>
       </c>
       <c r="F1436" t="n">
-        <v>11684</v>
+        <v>11678</v>
       </c>
       <c r="G1436" t="n">
         <v>8</v>
@@ -47833,13 +47833,13 @@
         </is>
       </c>
       <c r="D1437" t="n">
-        <v>62.09999999999999</v>
+        <v>62.1</v>
       </c>
       <c r="E1437" t="n">
-        <v>1675.9</v>
+        <v>1681.9</v>
       </c>
       <c r="F1437" t="n">
-        <v>11340.5</v>
+        <v>11346.5</v>
       </c>
       <c r="G1437" t="n">
         <v>7</v>
@@ -47869,10 +47869,10 @@
         <v>86.7</v>
       </c>
       <c r="E1438" t="n">
-        <v>2007.4</v>
+        <v>1994.4</v>
       </c>
       <c r="F1438" t="n">
-        <v>12942.2</v>
+        <v>12929.2</v>
       </c>
       <c r="G1438" t="n">
         <v>4</v>
@@ -47902,10 +47902,10 @@
         <v>88.2</v>
       </c>
       <c r="E1439" t="n">
-        <v>1595.2</v>
+        <v>1587.2</v>
       </c>
       <c r="F1439" t="n">
-        <v>10429.1</v>
+        <v>10421.1</v>
       </c>
       <c r="G1439" t="n">
         <v>3</v>
@@ -47968,16 +47968,16 @@
         <v>100.9</v>
       </c>
       <c r="E1441" t="n">
-        <v>1973</v>
+        <v>1960</v>
       </c>
       <c r="F1441" t="n">
-        <v>9508</v>
+        <v>9495</v>
       </c>
       <c r="G1441" t="n">
         <v>1</v>
       </c>
       <c r="H1441" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I1441" t="n">
         <v>8</v>
@@ -48010,7 +48010,7 @@
         <v>3</v>
       </c>
       <c r="H1442" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1442" t="n">
         <v>2</v>
@@ -48034,16 +48034,16 @@
         <v>73.5</v>
       </c>
       <c r="E1443" t="n">
-        <v>2005.7</v>
+        <v>2004.7</v>
       </c>
       <c r="F1443" t="n">
-        <v>12696.7</v>
+        <v>12695.7</v>
       </c>
       <c r="G1443" t="n">
         <v>4</v>
       </c>
       <c r="H1443" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1443" t="n">
         <v>3</v>
@@ -48067,10 +48067,10 @@
         <v>114.5</v>
       </c>
       <c r="E1444" t="n">
-        <v>1933.4</v>
+        <v>1927.4</v>
       </c>
       <c r="F1444" t="n">
-        <v>11798.5</v>
+        <v>11792.5</v>
       </c>
       <c r="G1444" t="n">
         <v>1</v>
@@ -48100,10 +48100,10 @@
         <v>85.90000000000001</v>
       </c>
       <c r="E1445" t="n">
-        <v>1761.8</v>
+        <v>1767.8</v>
       </c>
       <c r="F1445" t="n">
-        <v>11426.4</v>
+        <v>11432.4</v>
       </c>
       <c r="G1445" t="n">
         <v>2</v>
@@ -48133,16 +48133,16 @@
         <v>48.6</v>
       </c>
       <c r="E1446" t="n">
-        <v>2056</v>
+        <v>2043</v>
       </c>
       <c r="F1446" t="n">
-        <v>12990.8</v>
+        <v>12977.8</v>
       </c>
       <c r="G1446" t="n">
         <v>6</v>
       </c>
       <c r="H1446" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1446" t="n">
         <v>1</v>
@@ -48166,10 +48166,10 @@
         <v>52.8</v>
       </c>
       <c r="E1447" t="n">
-        <v>1648</v>
+        <v>1640</v>
       </c>
       <c r="F1447" t="n">
-        <v>10481.9</v>
+        <v>10473.9</v>
       </c>
       <c r="G1447" t="n">
         <v>5</v>
@@ -48232,16 +48232,16 @@
         <v>43.3</v>
       </c>
       <c r="E1449" t="n">
-        <v>2016.3</v>
+        <v>2003.3</v>
       </c>
       <c r="F1449" t="n">
-        <v>9551.299999999999</v>
+        <v>9538.299999999999</v>
       </c>
       <c r="G1449" t="n">
         <v>8</v>
       </c>
       <c r="H1449" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1449" t="n">
         <v>8</v>
@@ -48298,10 +48298,10 @@
         <v>65.5</v>
       </c>
       <c r="E1451" t="n">
-        <v>2071.2</v>
+        <v>2070.2</v>
       </c>
       <c r="F1451" t="n">
-        <v>12762.2</v>
+        <v>12761.2</v>
       </c>
       <c r="G1451" t="n">
         <v>7</v>
@@ -48331,10 +48331,10 @@
         <v>83.90000000000001</v>
       </c>
       <c r="E1452" t="n">
-        <v>2017.3</v>
+        <v>2011.3</v>
       </c>
       <c r="F1452" t="n">
-        <v>11882.4</v>
+        <v>11876.4</v>
       </c>
       <c r="G1452" t="n">
         <v>3</v>
@@ -48364,10 +48364,10 @@
         <v>66.40000000000001</v>
       </c>
       <c r="E1453" t="n">
-        <v>1828.2</v>
+        <v>1834.2</v>
       </c>
       <c r="F1453" t="n">
-        <v>11492.8</v>
+        <v>11498.8</v>
       </c>
       <c r="G1453" t="n">
         <v>6</v>
@@ -48397,10 +48397,10 @@
         <v>107</v>
       </c>
       <c r="E1454" t="n">
-        <v>2163</v>
+        <v>2150</v>
       </c>
       <c r="F1454" t="n">
-        <v>13097.8</v>
+        <v>13084.8</v>
       </c>
       <c r="G1454" t="n">
         <v>1</v>
@@ -48430,10 +48430,10 @@
         <v>46.5</v>
       </c>
       <c r="E1455" t="n">
-        <v>1694.5</v>
+        <v>1686.5</v>
       </c>
       <c r="F1455" t="n">
-        <v>10528.4</v>
+        <v>10520.4</v>
       </c>
       <c r="G1455" t="n">
         <v>8</v>
@@ -48496,10 +48496,10 @@
         <v>85.59999999999999</v>
       </c>
       <c r="E1457" t="n">
-        <v>2101.9</v>
+        <v>2088.9</v>
       </c>
       <c r="F1457" t="n">
-        <v>9636.9</v>
+        <v>9623.9</v>
       </c>
       <c r="G1457" t="n">
         <v>2</v>
@@ -48562,10 +48562,10 @@
         <v>65.90000000000001</v>
       </c>
       <c r="E1459" t="n">
-        <v>2137.1</v>
+        <v>2136.1</v>
       </c>
       <c r="F1459" t="n">
-        <v>12828.1</v>
+        <v>12827.1</v>
       </c>
       <c r="G1459" t="n">
         <v>5</v>
@@ -48595,10 +48595,10 @@
         <v>70.8</v>
       </c>
       <c r="E1460" t="n">
-        <v>2088.1</v>
+        <v>2082.1</v>
       </c>
       <c r="F1460" t="n">
-        <v>11953.2</v>
+        <v>11947.2</v>
       </c>
       <c r="G1460" t="n">
         <v>4</v>
@@ -48628,10 +48628,10 @@
         <v>60.5</v>
       </c>
       <c r="E1461" t="n">
-        <v>1888.7</v>
+        <v>1894.7</v>
       </c>
       <c r="F1461" t="n">
-        <v>11553.3</v>
+        <v>11559.3</v>
       </c>
       <c r="G1461" t="n">
         <v>7</v>
@@ -48661,10 +48661,10 @@
         <v>64.59999999999999</v>
       </c>
       <c r="E1462" t="n">
-        <v>2227.6</v>
+        <v>2214.6</v>
       </c>
       <c r="F1462" t="n">
-        <v>13162.4</v>
+        <v>13149.4</v>
       </c>
       <c r="G1462" t="n">
         <v>6</v>
@@ -48694,10 +48694,10 @@
         <v>73.7</v>
       </c>
       <c r="E1463" t="n">
-        <v>1768.2</v>
+        <v>1760.2</v>
       </c>
       <c r="F1463" t="n">
-        <v>10602.1</v>
+        <v>10594.1</v>
       </c>
       <c r="G1463" t="n">
         <v>3</v>
@@ -48760,10 +48760,10 @@
         <v>88</v>
       </c>
       <c r="E1465" t="n">
-        <v>2189.9</v>
+        <v>2176.9</v>
       </c>
       <c r="F1465" t="n">
-        <v>9724.9</v>
+        <v>9711.9</v>
       </c>
       <c r="G1465" t="n">
         <v>2</v>
@@ -48782,7 +48782,7 @@
         </is>
       </c>
       <c r="B1466" t="n">
-        <v>31.5</v>
+        <v>32</v>
       </c>
       <c r="C1466" t="inlineStr">
         <is>
@@ -48790,19 +48790,19 @@
         </is>
       </c>
       <c r="D1466" t="n">
-        <v>76.3</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="E1466" t="n">
-        <v>2289</v>
+        <v>2282.8</v>
       </c>
       <c r="F1466" t="n">
-        <v>13000.1</v>
+        <v>12993.9</v>
       </c>
       <c r="G1466" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1466" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1466" t="n">
         <v>2</v>
@@ -48815,7 +48815,7 @@
         </is>
       </c>
       <c r="B1467" t="n">
-        <v>31.5</v>
+        <v>32</v>
       </c>
       <c r="C1467" t="inlineStr">
         <is>
@@ -48823,16 +48823,16 @@
         </is>
       </c>
       <c r="D1467" t="n">
-        <v>73.3</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="E1467" t="n">
-        <v>2210.4</v>
+        <v>2214</v>
       </c>
       <c r="F1467" t="n">
-        <v>12901.4</v>
+        <v>12905</v>
       </c>
       <c r="G1467" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1467" t="n">
         <v>4</v>
@@ -48848,7 +48848,7 @@
         </is>
       </c>
       <c r="B1468" t="n">
-        <v>31.5</v>
+        <v>32</v>
       </c>
       <c r="C1468" t="inlineStr">
         <is>
@@ -48856,16 +48856,16 @@
         </is>
       </c>
       <c r="D1468" t="n">
-        <v>56.5</v>
+        <v>80.8</v>
       </c>
       <c r="E1468" t="n">
-        <v>2144.6</v>
+        <v>2162.9</v>
       </c>
       <c r="F1468" t="n">
-        <v>12009.7</v>
+        <v>12028</v>
       </c>
       <c r="G1468" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H1468" t="n">
         <v>5</v>
@@ -48881,7 +48881,7 @@
         </is>
       </c>
       <c r="B1469" t="n">
-        <v>31.5</v>
+        <v>32</v>
       </c>
       <c r="C1469" t="inlineStr">
         <is>
@@ -48889,16 +48889,16 @@
         </is>
       </c>
       <c r="D1469" t="n">
-        <v>75.09999999999999</v>
+        <v>53</v>
       </c>
       <c r="E1469" t="n">
-        <v>1963.8</v>
+        <v>1947.7</v>
       </c>
       <c r="F1469" t="n">
-        <v>11628.4</v>
+        <v>11612.3</v>
       </c>
       <c r="G1469" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H1469" t="n">
         <v>7</v>
@@ -48914,7 +48914,7 @@
         </is>
       </c>
       <c r="B1470" t="n">
-        <v>31.5</v>
+        <v>32</v>
       </c>
       <c r="C1470" t="inlineStr">
         <is>
@@ -48922,19 +48922,19 @@
         </is>
       </c>
       <c r="D1470" t="n">
-        <v>69.7</v>
+        <v>59.8</v>
       </c>
       <c r="E1470" t="n">
-        <v>2297.3</v>
+        <v>2274.4</v>
       </c>
       <c r="F1470" t="n">
-        <v>13232.1</v>
+        <v>13209.2</v>
       </c>
       <c r="G1470" t="n">
         <v>6</v>
       </c>
       <c r="H1470" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I1470" t="n">
         <v>1</v>
@@ -48947,7 +48947,7 @@
         </is>
       </c>
       <c r="B1471" t="n">
-        <v>31.5</v>
+        <v>32</v>
       </c>
       <c r="C1471" t="inlineStr">
         <is>
@@ -48955,16 +48955,16 @@
         </is>
       </c>
       <c r="D1471" t="n">
-        <v>80.09999999999999</v>
+        <v>68.39999999999999</v>
       </c>
       <c r="E1471" t="n">
-        <v>1848.3</v>
+        <v>1828.6</v>
       </c>
       <c r="F1471" t="n">
-        <v>10682.2</v>
+        <v>10662.5</v>
       </c>
       <c r="G1471" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H1471" t="n">
         <v>8</v>
@@ -48980,7 +48980,7 @@
         </is>
       </c>
       <c r="B1472" t="n">
-        <v>31.5</v>
+        <v>32</v>
       </c>
       <c r="C1472" t="inlineStr">
         <is>
@@ -48988,13 +48988,13 @@
         </is>
       </c>
       <c r="D1472" t="n">
-        <v>44.9</v>
+        <v>48.4</v>
       </c>
       <c r="E1472" t="n">
-        <v>2051.2</v>
+        <v>2054.7</v>
       </c>
       <c r="F1472" t="n">
-        <v>11655.3</v>
+        <v>11658.8</v>
       </c>
       <c r="G1472" t="n">
         <v>8</v>
@@ -49013,7 +49013,7 @@
         </is>
       </c>
       <c r="B1473" t="n">
-        <v>31.5</v>
+        <v>32</v>
       </c>
       <c r="C1473" t="inlineStr">
         <is>
@@ -49021,21 +49021,1077 @@
         </is>
       </c>
       <c r="D1473" t="n">
+        <v>104.8</v>
+      </c>
+      <c r="E1473" t="n">
+        <v>2281.7</v>
+      </c>
+      <c r="F1473" t="n">
+        <v>9816.700000000001</v>
+      </c>
+      <c r="G1473" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1473" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1473" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1474">
+      <c r="A1474" t="inlineStr">
+        <is>
+          <t>5f452f5e66dd374930eb2b71</t>
+        </is>
+      </c>
+      <c r="B1474" t="n">
+        <v>33</v>
+      </c>
+      <c r="C1474" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1474" t="n">
+        <v>76.3</v>
+      </c>
+      <c r="E1474" t="n">
+        <v>2359.1</v>
+      </c>
+      <c r="F1474" t="n">
+        <v>13070.2</v>
+      </c>
+      <c r="G1474" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1474" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1474" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1475">
+      <c r="A1475" t="inlineStr">
+        <is>
+          <t>5f453062ec331549297ee6b8</t>
+        </is>
+      </c>
+      <c r="B1475" t="n">
+        <v>33</v>
+      </c>
+      <c r="C1475" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1475" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="E1475" t="n">
+        <v>2287.3</v>
+      </c>
+      <c r="F1475" t="n">
+        <v>12978.3</v>
+      </c>
+      <c r="G1475" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1475" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1475" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1476">
+      <c r="A1476" t="inlineStr">
+        <is>
+          <t>5f4530beec331549297ee6d6</t>
+        </is>
+      </c>
+      <c r="B1476" t="n">
+        <v>33</v>
+      </c>
+      <c r="C1476" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1476" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="E1476" t="n">
+        <v>2219.4</v>
+      </c>
+      <c r="F1476" t="n">
+        <v>12084.5</v>
+      </c>
+      <c r="G1476" t="n">
+        <v>7</v>
+      </c>
+      <c r="H1476" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1476" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1477">
+      <c r="A1477" t="inlineStr">
+        <is>
+          <t>5f4531e9764e7d491e029746</t>
+        </is>
+      </c>
+      <c r="B1477" t="n">
+        <v>33</v>
+      </c>
+      <c r="C1477" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1477" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="E1477" t="n">
+        <v>2022.8</v>
+      </c>
+      <c r="F1477" t="n">
+        <v>11687.4</v>
+      </c>
+      <c r="G1477" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1477" t="n">
+        <v>7</v>
+      </c>
+      <c r="I1477" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1478">
+      <c r="A1478" t="inlineStr">
+        <is>
+          <t>5f45324dec331549297ee971</t>
+        </is>
+      </c>
+      <c r="B1478" t="n">
+        <v>33</v>
+      </c>
+      <c r="C1478" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1478" t="n">
+        <v>69.7</v>
+      </c>
+      <c r="E1478" t="n">
+        <v>2344.1</v>
+      </c>
+      <c r="F1478" t="n">
+        <v>13278.9</v>
+      </c>
+      <c r="G1478" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1478" t="n">
+        <v>3</v>
+      </c>
+      <c r="I1478" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1479">
+      <c r="A1479" t="inlineStr">
+        <is>
+          <t>5f47ab5b9e2edb0bb831c703</t>
+        </is>
+      </c>
+      <c r="B1479" t="n">
+        <v>33</v>
+      </c>
+      <c r="C1479" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1479" t="n">
+        <v>80.09999999999999</v>
+      </c>
+      <c r="E1479" t="n">
+        <v>1908.7</v>
+      </c>
+      <c r="F1479" t="n">
+        <v>10742.6</v>
+      </c>
+      <c r="G1479" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1479" t="n">
+        <v>8</v>
+      </c>
+      <c r="I1479" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1480">
+      <c r="A1480" t="inlineStr">
+        <is>
+          <t>5f47aeb6c387a50bca03dd55</t>
+        </is>
+      </c>
+      <c r="B1480" t="n">
+        <v>33</v>
+      </c>
+      <c r="C1480" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1480" t="n">
+        <v>44.90000000000001</v>
+      </c>
+      <c r="E1480" t="n">
+        <v>2099.6</v>
+      </c>
+      <c r="F1480" t="n">
+        <v>11703.7</v>
+      </c>
+      <c r="G1480" t="n">
+        <v>8</v>
+      </c>
+      <c r="H1480" t="n">
+        <v>6</v>
+      </c>
+      <c r="I1480" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1481">
+      <c r="A1481" t="inlineStr">
+        <is>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
+        </is>
+      </c>
+      <c r="B1481" t="n">
+        <v>33</v>
+      </c>
+      <c r="C1481" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1481" t="n">
         <v>82.40000000000001</v>
       </c>
-      <c r="E1473" t="n">
-        <v>2272.3</v>
-      </c>
-      <c r="F1473" t="n">
-        <v>9807.299999999999</v>
-      </c>
-      <c r="G1473" t="n">
-        <v>1</v>
-      </c>
-      <c r="H1473" t="n">
-        <v>3</v>
-      </c>
-      <c r="I1473" t="n">
+      <c r="E1481" t="n">
+        <v>2364.1</v>
+      </c>
+      <c r="F1481" t="n">
+        <v>9899.1</v>
+      </c>
+      <c r="G1481" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1481" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1481" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1482">
+      <c r="A1482" t="inlineStr">
+        <is>
+          <t>5f452f5e66dd374930eb2b71</t>
+        </is>
+      </c>
+      <c r="B1482" t="n">
+        <v>34</v>
+      </c>
+      <c r="C1482" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1482" t="n">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="E1482" t="n">
+        <v>2453.2</v>
+      </c>
+      <c r="F1482" t="n">
+        <v>13164.3</v>
+      </c>
+      <c r="G1482" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1482" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1482" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1483">
+      <c r="A1483" t="inlineStr">
+        <is>
+          <t>5f453062ec331549297ee6b8</t>
+        </is>
+      </c>
+      <c r="B1483" t="n">
+        <v>34</v>
+      </c>
+      <c r="C1483" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1483" t="n">
+        <v>94.90000000000001</v>
+      </c>
+      <c r="E1483" t="n">
+        <v>2382.2</v>
+      </c>
+      <c r="F1483" t="n">
+        <v>13073.2</v>
+      </c>
+      <c r="G1483" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1483" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1483" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1484">
+      <c r="A1484" t="inlineStr">
+        <is>
+          <t>5f4530beec331549297ee6d6</t>
+        </is>
+      </c>
+      <c r="B1484" t="n">
+        <v>34</v>
+      </c>
+      <c r="C1484" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1484" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="E1484" t="n">
+        <v>2294.6</v>
+      </c>
+      <c r="F1484" t="n">
+        <v>12159.7</v>
+      </c>
+      <c r="G1484" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1484" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1484" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1485">
+      <c r="A1485" t="inlineStr">
+        <is>
+          <t>5f4531e9764e7d491e029746</t>
+        </is>
+      </c>
+      <c r="B1485" t="n">
+        <v>34</v>
+      </c>
+      <c r="C1485" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1485" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="E1485" t="n">
+        <v>2061.1</v>
+      </c>
+      <c r="F1485" t="n">
+        <v>11725.7</v>
+      </c>
+      <c r="G1485" t="n">
+        <v>8</v>
+      </c>
+      <c r="H1485" t="n">
+        <v>7</v>
+      </c>
+      <c r="I1485" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1486">
+      <c r="A1486" t="inlineStr">
+        <is>
+          <t>5f45324dec331549297ee971</t>
+        </is>
+      </c>
+      <c r="B1486" t="n">
+        <v>34</v>
+      </c>
+      <c r="C1486" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1486" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="E1486" t="n">
+        <v>2397</v>
+      </c>
+      <c r="F1486" t="n">
+        <v>13331.8</v>
+      </c>
+      <c r="G1486" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1486" t="n">
+        <v>3</v>
+      </c>
+      <c r="I1486" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1487">
+      <c r="A1487" t="inlineStr">
+        <is>
+          <t>5f47ab5b9e2edb0bb831c703</t>
+        </is>
+      </c>
+      <c r="B1487" t="n">
+        <v>34</v>
+      </c>
+      <c r="C1487" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1487" t="n">
+        <v>78.7</v>
+      </c>
+      <c r="E1487" t="n">
+        <v>1987.4</v>
+      </c>
+      <c r="F1487" t="n">
+        <v>10821.3</v>
+      </c>
+      <c r="G1487" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1487" t="n">
+        <v>8</v>
+      </c>
+      <c r="I1487" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1488">
+      <c r="A1488" t="inlineStr">
+        <is>
+          <t>5f47aeb6c387a50bca03dd55</t>
+        </is>
+      </c>
+      <c r="B1488" t="n">
+        <v>34</v>
+      </c>
+      <c r="C1488" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1488" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="E1488" t="n">
+        <v>2144</v>
+      </c>
+      <c r="F1488" t="n">
+        <v>11748.1</v>
+      </c>
+      <c r="G1488" t="n">
+        <v>7</v>
+      </c>
+      <c r="H1488" t="n">
+        <v>6</v>
+      </c>
+      <c r="I1488" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1489">
+      <c r="A1489" t="inlineStr">
+        <is>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
+        </is>
+      </c>
+      <c r="B1489" t="n">
+        <v>34</v>
+      </c>
+      <c r="C1489" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1489" t="n">
+        <v>95.3</v>
+      </c>
+      <c r="E1489" t="n">
+        <v>2459.4</v>
+      </c>
+      <c r="F1489" t="n">
+        <v>9994.4</v>
+      </c>
+      <c r="G1489" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1489" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1489" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1490">
+      <c r="A1490" t="inlineStr">
+        <is>
+          <t>5f452f5e66dd374930eb2b71</t>
+        </is>
+      </c>
+      <c r="B1490" t="n">
+        <v>35</v>
+      </c>
+      <c r="C1490" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1490" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="E1490" t="n">
+        <v>2526</v>
+      </c>
+      <c r="F1490" t="n">
+        <v>13237.1</v>
+      </c>
+      <c r="G1490" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1490" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1490" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1491">
+      <c r="A1491" t="inlineStr">
+        <is>
+          <t>5f453062ec331549297ee6b8</t>
+        </is>
+      </c>
+      <c r="B1491" t="n">
+        <v>35</v>
+      </c>
+      <c r="C1491" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1491" t="n">
+        <v>42</v>
+      </c>
+      <c r="E1491" t="n">
+        <v>2424.2</v>
+      </c>
+      <c r="F1491" t="n">
+        <v>13115.2</v>
+      </c>
+      <c r="G1491" t="n">
+        <v>7</v>
+      </c>
+      <c r="H1491" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1491" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1492">
+      <c r="A1492" t="inlineStr">
+        <is>
+          <t>5f4530beec331549297ee6d6</t>
+        </is>
+      </c>
+      <c r="B1492" t="n">
+        <v>35</v>
+      </c>
+      <c r="C1492" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1492" t="n">
+        <v>65.10000000000001</v>
+      </c>
+      <c r="E1492" t="n">
+        <v>2359.7</v>
+      </c>
+      <c r="F1492" t="n">
+        <v>12224.8</v>
+      </c>
+      <c r="G1492" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1492" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1492" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1493">
+      <c r="A1493" t="inlineStr">
+        <is>
+          <t>5f4531e9764e7d491e029746</t>
+        </is>
+      </c>
+      <c r="B1493" t="n">
+        <v>35</v>
+      </c>
+      <c r="C1493" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1493" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="E1493" t="n">
+        <v>2100.9</v>
+      </c>
+      <c r="F1493" t="n">
+        <v>11765.5</v>
+      </c>
+      <c r="G1493" t="n">
+        <v>8</v>
+      </c>
+      <c r="H1493" t="n">
+        <v>7</v>
+      </c>
+      <c r="I1493" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1494">
+      <c r="A1494" t="inlineStr">
+        <is>
+          <t>5f45324dec331549297ee971</t>
+        </is>
+      </c>
+      <c r="B1494" t="n">
+        <v>35</v>
+      </c>
+      <c r="C1494" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1494" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="E1494" t="n">
+        <v>2462.8</v>
+      </c>
+      <c r="F1494" t="n">
+        <v>13397.6</v>
+      </c>
+      <c r="G1494" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1494" t="n">
+        <v>3</v>
+      </c>
+      <c r="I1494" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1495">
+      <c r="A1495" t="inlineStr">
+        <is>
+          <t>5f47ab5b9e2edb0bb831c703</t>
+        </is>
+      </c>
+      <c r="B1495" t="n">
+        <v>35</v>
+      </c>
+      <c r="C1495" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1495" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="E1495" t="n">
+        <v>2053.8</v>
+      </c>
+      <c r="F1495" t="n">
+        <v>10887.7</v>
+      </c>
+      <c r="G1495" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1495" t="n">
+        <v>8</v>
+      </c>
+      <c r="I1495" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1496">
+      <c r="A1496" t="inlineStr">
+        <is>
+          <t>5f47aeb6c387a50bca03dd55</t>
+        </is>
+      </c>
+      <c r="B1496" t="n">
+        <v>35</v>
+      </c>
+      <c r="C1496" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1496" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="E1496" t="n">
+        <v>2196.7</v>
+      </c>
+      <c r="F1496" t="n">
+        <v>11800.8</v>
+      </c>
+      <c r="G1496" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1496" t="n">
+        <v>6</v>
+      </c>
+      <c r="I1496" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1497">
+      <c r="A1497" t="inlineStr">
+        <is>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
+        </is>
+      </c>
+      <c r="B1497" t="n">
+        <v>35</v>
+      </c>
+      <c r="C1497" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1497" t="n">
+        <v>81.3</v>
+      </c>
+      <c r="E1497" t="n">
+        <v>2540.7</v>
+      </c>
+      <c r="F1497" t="n">
+        <v>10075.7</v>
+      </c>
+      <c r="G1497" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1497" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1497" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1498">
+      <c r="A1498" t="inlineStr">
+        <is>
+          <t>5f452f5e66dd374930eb2b71</t>
+        </is>
+      </c>
+      <c r="B1498" t="n">
+        <v>36</v>
+      </c>
+      <c r="C1498" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1498" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="E1498" t="n">
+        <v>2596.6</v>
+      </c>
+      <c r="F1498" t="n">
+        <v>13307.7</v>
+      </c>
+      <c r="G1498" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1498" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1498" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1499">
+      <c r="A1499" t="inlineStr">
+        <is>
+          <t>5f453062ec331549297ee6b8</t>
+        </is>
+      </c>
+      <c r="B1499" t="n">
+        <v>36</v>
+      </c>
+      <c r="C1499" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1499" t="n">
+        <v>76.40000000000001</v>
+      </c>
+      <c r="E1499" t="n">
+        <v>2500.6</v>
+      </c>
+      <c r="F1499" t="n">
+        <v>13191.6</v>
+      </c>
+      <c r="G1499" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1499" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1499" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1500">
+      <c r="A1500" t="inlineStr">
+        <is>
+          <t>5f4530beec331549297ee6d6</t>
+        </is>
+      </c>
+      <c r="B1500" t="n">
+        <v>36</v>
+      </c>
+      <c r="C1500" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1500" t="n">
+        <v>60.3</v>
+      </c>
+      <c r="E1500" t="n">
+        <v>2420</v>
+      </c>
+      <c r="F1500" t="n">
+        <v>12285.1</v>
+      </c>
+      <c r="G1500" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1500" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1500" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1501">
+      <c r="A1501" t="inlineStr">
+        <is>
+          <t>5f4531e9764e7d491e029746</t>
+        </is>
+      </c>
+      <c r="B1501" t="n">
+        <v>36</v>
+      </c>
+      <c r="C1501" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1501" t="n">
+        <v>60.4</v>
+      </c>
+      <c r="E1501" t="n">
+        <v>2161.3</v>
+      </c>
+      <c r="F1501" t="n">
+        <v>11825.9</v>
+      </c>
+      <c r="G1501" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1501" t="n">
+        <v>7</v>
+      </c>
+      <c r="I1501" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1502">
+      <c r="A1502" t="inlineStr">
+        <is>
+          <t>5f45324dec331549297ee971</t>
+        </is>
+      </c>
+      <c r="B1502" t="n">
+        <v>36</v>
+      </c>
+      <c r="C1502" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1502" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="E1502" t="n">
+        <v>2516.7</v>
+      </c>
+      <c r="F1502" t="n">
+        <v>13451.5</v>
+      </c>
+      <c r="G1502" t="n">
+        <v>7</v>
+      </c>
+      <c r="H1502" t="n">
+        <v>3</v>
+      </c>
+      <c r="I1502" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1503">
+      <c r="A1503" t="inlineStr">
+        <is>
+          <t>5f47ab5b9e2edb0bb831c703</t>
+        </is>
+      </c>
+      <c r="B1503" t="n">
+        <v>36</v>
+      </c>
+      <c r="C1503" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1503" t="n">
+        <v>75.80000000000001</v>
+      </c>
+      <c r="E1503" t="n">
+        <v>2129.6</v>
+      </c>
+      <c r="F1503" t="n">
+        <v>10963.5</v>
+      </c>
+      <c r="G1503" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1503" t="n">
+        <v>8</v>
+      </c>
+      <c r="I1503" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1504">
+      <c r="A1504" t="inlineStr">
+        <is>
+          <t>5f47aeb6c387a50bca03dd55</t>
+        </is>
+      </c>
+      <c r="B1504" t="n">
+        <v>36</v>
+      </c>
+      <c r="C1504" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1504" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="E1504" t="n">
+        <v>2249.9</v>
+      </c>
+      <c r="F1504" t="n">
+        <v>11854</v>
+      </c>
+      <c r="G1504" t="n">
+        <v>8</v>
+      </c>
+      <c r="H1504" t="n">
+        <v>6</v>
+      </c>
+      <c r="I1504" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1505">
+      <c r="A1505" t="inlineStr">
+        <is>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
+        </is>
+      </c>
+      <c r="B1505" t="n">
+        <v>36</v>
+      </c>
+      <c r="C1505" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1505" t="n">
+        <v>87.59999999999999</v>
+      </c>
+      <c r="E1505" t="n">
+        <v>2628.3</v>
+      </c>
+      <c r="F1505" t="n">
+        <v>10163.3</v>
+      </c>
+      <c r="G1505" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1505" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1505" t="n">
         <v>8</v>
       </c>
     </row>

--- a/datos/vistas_negocio/Fact_Global_Master.xlsx
+++ b/datos/vistas_negocio/Fact_Global_Master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1505"/>
+  <dimension ref="A1:I1513"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50107,6 +50107,270 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1506">
+      <c r="A1506" t="inlineStr">
+        <is>
+          <t>5f452f5e66dd374930eb2b71</t>
+        </is>
+      </c>
+      <c r="B1506" t="n">
+        <v>37</v>
+      </c>
+      <c r="C1506" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1506" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="E1506" t="n">
+        <v>2654.8</v>
+      </c>
+      <c r="F1506" t="n">
+        <v>13365.9</v>
+      </c>
+      <c r="G1506" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1506" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1506" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1507">
+      <c r="A1507" t="inlineStr">
+        <is>
+          <t>5f453062ec331549297ee6b8</t>
+        </is>
+      </c>
+      <c r="B1507" t="n">
+        <v>37</v>
+      </c>
+      <c r="C1507" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1507" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="E1507" t="n">
+        <v>2549.9</v>
+      </c>
+      <c r="F1507" t="n">
+        <v>13240.9</v>
+      </c>
+      <c r="G1507" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1507" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1507" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1508">
+      <c r="A1508" t="inlineStr">
+        <is>
+          <t>5f4530beec331549297ee6d6</t>
+        </is>
+      </c>
+      <c r="B1508" t="n">
+        <v>37</v>
+      </c>
+      <c r="C1508" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1508" t="n">
+        <v>69.09999999999999</v>
+      </c>
+      <c r="E1508" t="n">
+        <v>2489.1</v>
+      </c>
+      <c r="F1508" t="n">
+        <v>12354.2</v>
+      </c>
+      <c r="G1508" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1508" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1508" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1509">
+      <c r="A1509" t="inlineStr">
+        <is>
+          <t>5f4531e9764e7d491e029746</t>
+        </is>
+      </c>
+      <c r="B1509" t="n">
+        <v>37</v>
+      </c>
+      <c r="C1509" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1509" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="E1509" t="n">
+        <v>2209.7</v>
+      </c>
+      <c r="F1509" t="n">
+        <v>11874.3</v>
+      </c>
+      <c r="G1509" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1509" t="n">
+        <v>7</v>
+      </c>
+      <c r="I1509" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1510">
+      <c r="A1510" t="inlineStr">
+        <is>
+          <t>5f45324dec331549297ee971</t>
+        </is>
+      </c>
+      <c r="B1510" t="n">
+        <v>37</v>
+      </c>
+      <c r="C1510" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1510" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="E1510" t="n">
+        <v>2564.3</v>
+      </c>
+      <c r="F1510" t="n">
+        <v>13499.1</v>
+      </c>
+      <c r="G1510" t="n">
+        <v>7</v>
+      </c>
+      <c r="H1510" t="n">
+        <v>3</v>
+      </c>
+      <c r="I1510" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1511">
+      <c r="A1511" t="inlineStr">
+        <is>
+          <t>5f47ab5b9e2edb0bb831c703</t>
+        </is>
+      </c>
+      <c r="B1511" t="n">
+        <v>37</v>
+      </c>
+      <c r="C1511" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1511" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="E1511" t="n">
+        <v>2164.4</v>
+      </c>
+      <c r="F1511" t="n">
+        <v>10998.3</v>
+      </c>
+      <c r="G1511" t="n">
+        <v>8</v>
+      </c>
+      <c r="H1511" t="n">
+        <v>8</v>
+      </c>
+      <c r="I1511" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1512">
+      <c r="A1512" t="inlineStr">
+        <is>
+          <t>5f47aeb6c387a50bca03dd55</t>
+        </is>
+      </c>
+      <c r="B1512" t="n">
+        <v>37</v>
+      </c>
+      <c r="C1512" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1512" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="E1512" t="n">
+        <v>2323.2</v>
+      </c>
+      <c r="F1512" t="n">
+        <v>11927.3</v>
+      </c>
+      <c r="G1512" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1512" t="n">
+        <v>6</v>
+      </c>
+      <c r="I1512" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1513">
+      <c r="A1513" t="inlineStr">
+        <is>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
+        </is>
+      </c>
+      <c r="B1513" t="n">
+        <v>37</v>
+      </c>
+      <c r="C1513" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1513" t="n">
+        <v>97.7</v>
+      </c>
+      <c r="E1513" t="n">
+        <v>2726</v>
+      </c>
+      <c r="F1513" t="n">
+        <v>10261</v>
+      </c>
+      <c r="G1513" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1513" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1513" t="n">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/vistas_negocio/Fact_Global_Master.xlsx
+++ b/datos/vistas_negocio/Fact_Global_Master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1513"/>
+  <dimension ref="A1:I1521"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50371,6 +50371,270 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1514">
+      <c r="A1514" t="inlineStr">
+        <is>
+          <t>5f452f5e66dd374930eb2b71</t>
+        </is>
+      </c>
+      <c r="B1514" t="n">
+        <v>38</v>
+      </c>
+      <c r="C1514" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1514" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="E1514" t="n">
+        <v>2750.5</v>
+      </c>
+      <c r="F1514" t="n">
+        <v>13461.6</v>
+      </c>
+      <c r="G1514" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1514" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1514" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1515">
+      <c r="A1515" t="inlineStr">
+        <is>
+          <t>5f453062ec331549297ee6b8</t>
+        </is>
+      </c>
+      <c r="B1515" t="n">
+        <v>38</v>
+      </c>
+      <c r="C1515" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1515" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1515" t="n">
+        <v>2549.9</v>
+      </c>
+      <c r="F1515" t="n">
+        <v>13240.9</v>
+      </c>
+      <c r="G1515" t="n">
+        <v>8</v>
+      </c>
+      <c r="H1515" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1515" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1516">
+      <c r="A1516" t="inlineStr">
+        <is>
+          <t>5f4530beec331549297ee6d6</t>
+        </is>
+      </c>
+      <c r="B1516" t="n">
+        <v>38</v>
+      </c>
+      <c r="C1516" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1516" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="E1516" t="n">
+        <v>2529.8</v>
+      </c>
+      <c r="F1516" t="n">
+        <v>12394.9</v>
+      </c>
+      <c r="G1516" t="n">
+        <v>7</v>
+      </c>
+      <c r="H1516" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1516" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1517">
+      <c r="A1517" t="inlineStr">
+        <is>
+          <t>5f4531e9764e7d491e029746</t>
+        </is>
+      </c>
+      <c r="B1517" t="n">
+        <v>38</v>
+      </c>
+      <c r="C1517" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1517" t="n">
+        <v>68.2</v>
+      </c>
+      <c r="E1517" t="n">
+        <v>2277.9</v>
+      </c>
+      <c r="F1517" t="n">
+        <v>11942.5</v>
+      </c>
+      <c r="G1517" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1517" t="n">
+        <v>7</v>
+      </c>
+      <c r="I1517" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1518">
+      <c r="A1518" t="inlineStr">
+        <is>
+          <t>5f45324dec331549297ee971</t>
+        </is>
+      </c>
+      <c r="B1518" t="n">
+        <v>38</v>
+      </c>
+      <c r="C1518" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1518" t="n">
+        <v>66.59999999999999</v>
+      </c>
+      <c r="E1518" t="n">
+        <v>2630.9</v>
+      </c>
+      <c r="F1518" t="n">
+        <v>13565.7</v>
+      </c>
+      <c r="G1518" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1518" t="n">
+        <v>3</v>
+      </c>
+      <c r="I1518" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1519">
+      <c r="A1519" t="inlineStr">
+        <is>
+          <t>5f47ab5b9e2edb0bb831c703</t>
+        </is>
+      </c>
+      <c r="B1519" t="n">
+        <v>38</v>
+      </c>
+      <c r="C1519" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1519" t="n">
+        <v>80.59999999999999</v>
+      </c>
+      <c r="E1519" t="n">
+        <v>2245</v>
+      </c>
+      <c r="F1519" t="n">
+        <v>11078.9</v>
+      </c>
+      <c r="G1519" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1519" t="n">
+        <v>8</v>
+      </c>
+      <c r="I1519" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1520">
+      <c r="A1520" t="inlineStr">
+        <is>
+          <t>5f47aeb6c387a50bca03dd55</t>
+        </is>
+      </c>
+      <c r="B1520" t="n">
+        <v>38</v>
+      </c>
+      <c r="C1520" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1520" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="E1520" t="n">
+        <v>2369.6</v>
+      </c>
+      <c r="F1520" t="n">
+        <v>11973.7</v>
+      </c>
+      <c r="G1520" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1520" t="n">
+        <v>6</v>
+      </c>
+      <c r="I1520" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1521">
+      <c r="A1521" t="inlineStr">
+        <is>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
+        </is>
+      </c>
+      <c r="B1521" t="n">
+        <v>38</v>
+      </c>
+      <c r="C1521" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1521" t="n">
+        <v>80.40000000000001</v>
+      </c>
+      <c r="E1521" t="n">
+        <v>2806.4</v>
+      </c>
+      <c r="F1521" t="n">
+        <v>10341.4</v>
+      </c>
+      <c r="G1521" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1521" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1521" t="n">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/vistas_negocio/Fact_Global_Master.xlsx
+++ b/datos/vistas_negocio/Fact_Global_Master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1521"/>
+  <dimension ref="A1:I1529"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40610,7 +40610,7 @@
         </is>
       </c>
       <c r="B1218" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="C1218" t="inlineStr">
         <is>
@@ -40618,19 +40618,19 @@
         </is>
       </c>
       <c r="D1218" t="n">
-        <v>41</v>
+        <v>6.5</v>
       </c>
       <c r="E1218" t="n">
-        <v>41</v>
+        <v>6.5</v>
       </c>
       <c r="F1218" t="n">
-        <v>10752.1</v>
+        <v>10717.6</v>
       </c>
       <c r="G1218" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H1218" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I1218" t="n">
         <v>2</v>
@@ -40643,7 +40643,7 @@
         </is>
       </c>
       <c r="B1219" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="C1219" t="inlineStr">
         <is>
@@ -40651,19 +40651,19 @@
         </is>
       </c>
       <c r="D1219" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="E1219" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="F1219" t="n">
-        <v>10732</v>
+        <v>10691</v>
       </c>
       <c r="G1219" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H1219" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I1219" t="n">
         <v>3</v>
@@ -40676,7 +40676,7 @@
         </is>
       </c>
       <c r="B1220" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="C1220" t="inlineStr">
         <is>
@@ -40684,19 +40684,19 @@
         </is>
       </c>
       <c r="D1220" t="n">
-        <v>65</v>
+        <v>13.9</v>
       </c>
       <c r="E1220" t="n">
-        <v>65</v>
+        <v>13.9</v>
       </c>
       <c r="F1220" t="n">
-        <v>9930.1</v>
+        <v>9879</v>
       </c>
       <c r="G1220" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H1220" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1220" t="n">
         <v>4</v>
@@ -40709,7 +40709,7 @@
         </is>
       </c>
       <c r="B1221" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="C1221" t="inlineStr">
         <is>
@@ -40717,13 +40717,13 @@
         </is>
       </c>
       <c r="D1221" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="E1221" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="F1221" t="n">
-        <v>9713.6</v>
+        <v>9664.6</v>
       </c>
       <c r="G1221" t="n">
         <v>5</v>
@@ -40742,7 +40742,7 @@
         </is>
       </c>
       <c r="B1222" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="C1222" t="inlineStr">
         <is>
@@ -40750,19 +40750,19 @@
         </is>
       </c>
       <c r="D1222" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="E1222" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="F1222" t="n">
-        <v>11000.8</v>
+        <v>10934.8</v>
       </c>
       <c r="G1222" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H1222" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I1222" t="n">
         <v>1</v>
@@ -40775,7 +40775,7 @@
         </is>
       </c>
       <c r="B1223" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="C1223" t="inlineStr">
         <is>
@@ -40783,19 +40783,19 @@
         </is>
       </c>
       <c r="D1223" t="n">
-        <v>47</v>
+        <v>12.6</v>
       </c>
       <c r="E1223" t="n">
-        <v>47</v>
+        <v>12.6</v>
       </c>
       <c r="F1223" t="n">
-        <v>8880.9</v>
+        <v>8846.5</v>
       </c>
       <c r="G1223" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H1223" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I1223" t="n">
         <v>7</v>
@@ -40808,7 +40808,7 @@
         </is>
       </c>
       <c r="B1224" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="C1224" t="inlineStr">
         <is>
@@ -40816,19 +40816,19 @@
         </is>
       </c>
       <c r="D1224" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="E1224" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="F1224" t="n">
-        <v>9655.1</v>
+        <v>9604.1</v>
       </c>
       <c r="G1224" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1224" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I1224" t="n">
         <v>6</v>
@@ -40841,7 +40841,7 @@
         </is>
       </c>
       <c r="B1225" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="C1225" t="inlineStr">
         <is>
@@ -40849,13 +40849,13 @@
         </is>
       </c>
       <c r="D1225" t="n">
-        <v>56</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="E1225" t="n">
-        <v>56</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="F1225" t="n">
-        <v>7591</v>
+        <v>7544.2</v>
       </c>
       <c r="G1225" t="n">
         <v>3</v>
@@ -40874,7 +40874,7 @@
         </is>
       </c>
       <c r="B1226" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C1226" t="inlineStr">
         <is>
@@ -40882,22 +40882,22 @@
         </is>
       </c>
       <c r="D1226" t="n">
-        <v>44.2</v>
+        <v>41</v>
       </c>
       <c r="E1226" t="n">
-        <v>85.2</v>
+        <v>47.5</v>
       </c>
       <c r="F1226" t="n">
-        <v>10796.3</v>
+        <v>10758.6</v>
       </c>
       <c r="G1226" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H1226" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I1226" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1227">
@@ -40907,7 +40907,7 @@
         </is>
       </c>
       <c r="B1227" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C1227" t="inlineStr">
         <is>
@@ -40915,22 +40915,22 @@
         </is>
       </c>
       <c r="D1227" t="n">
-        <v>93.3</v>
+        <v>41</v>
       </c>
       <c r="E1227" t="n">
-        <v>134.3</v>
+        <v>41</v>
       </c>
       <c r="F1227" t="n">
-        <v>10825.3</v>
+        <v>10732</v>
       </c>
       <c r="G1227" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H1227" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I1227" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1228">
@@ -40940,7 +40940,7 @@
         </is>
       </c>
       <c r="B1228" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C1228" t="inlineStr">
         <is>
@@ -40948,19 +40948,19 @@
         </is>
       </c>
       <c r="D1228" t="n">
-        <v>63.40000000000001</v>
+        <v>65</v>
       </c>
       <c r="E1228" t="n">
-        <v>128.4</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="F1228" t="n">
-        <v>9993.5</v>
+        <v>9944</v>
       </c>
       <c r="G1228" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1228" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I1228" t="n">
         <v>4</v>
@@ -40973,7 +40973,7 @@
         </is>
       </c>
       <c r="B1229" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C1229" t="inlineStr">
         <is>
@@ -40981,19 +40981,19 @@
         </is>
       </c>
       <c r="D1229" t="n">
-        <v>103</v>
+        <v>49</v>
       </c>
       <c r="E1229" t="n">
-        <v>152</v>
+        <v>49</v>
       </c>
       <c r="F1229" t="n">
-        <v>9816.6</v>
+        <v>9713.6</v>
       </c>
       <c r="G1229" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H1229" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I1229" t="n">
         <v>5</v>
@@ -41006,7 +41006,7 @@
         </is>
       </c>
       <c r="B1230" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C1230" t="inlineStr">
         <is>
@@ -41014,19 +41014,19 @@
         </is>
       </c>
       <c r="D1230" t="n">
-        <v>60.2</v>
+        <v>66</v>
       </c>
       <c r="E1230" t="n">
-        <v>126.2</v>
+        <v>66</v>
       </c>
       <c r="F1230" t="n">
-        <v>11061</v>
+        <v>11000.8</v>
       </c>
       <c r="G1230" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H1230" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I1230" t="n">
         <v>1</v>
@@ -41039,7 +41039,7 @@
         </is>
       </c>
       <c r="B1231" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C1231" t="inlineStr">
         <is>
@@ -41047,19 +41047,19 @@
         </is>
       </c>
       <c r="D1231" t="n">
-        <v>44.6</v>
+        <v>47</v>
       </c>
       <c r="E1231" t="n">
-        <v>91.59999999999999</v>
+        <v>59.6</v>
       </c>
       <c r="F1231" t="n">
-        <v>8925.5</v>
+        <v>8893.5</v>
       </c>
       <c r="G1231" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H1231" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I1231" t="n">
         <v>7</v>
@@ -41072,7 +41072,7 @@
         </is>
       </c>
       <c r="B1232" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C1232" t="inlineStr">
         <is>
@@ -41080,16 +41080,16 @@
         </is>
       </c>
       <c r="D1232" t="n">
-        <v>70.09999999999999</v>
+        <v>51</v>
       </c>
       <c r="E1232" t="n">
-        <v>121.1</v>
+        <v>51</v>
       </c>
       <c r="F1232" t="n">
-        <v>9725.200000000001</v>
+        <v>9655.1</v>
       </c>
       <c r="G1232" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1232" t="n">
         <v>5</v>
@@ -41105,7 +41105,7 @@
         </is>
       </c>
       <c r="B1233" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C1233" t="inlineStr">
         <is>
@@ -41113,19 +41113,19 @@
         </is>
       </c>
       <c r="D1233" t="n">
-        <v>57.8</v>
+        <v>56</v>
       </c>
       <c r="E1233" t="n">
-        <v>113.8</v>
+        <v>65.2</v>
       </c>
       <c r="F1233" t="n">
-        <v>7648.8</v>
+        <v>7600.2</v>
       </c>
       <c r="G1233" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H1233" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I1233" t="n">
         <v>8</v>
@@ -41138,7 +41138,7 @@
         </is>
       </c>
       <c r="B1234" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C1234" t="inlineStr">
         <is>
@@ -41146,19 +41146,19 @@
         </is>
       </c>
       <c r="D1234" t="n">
-        <v>62.4</v>
+        <v>44.2</v>
       </c>
       <c r="E1234" t="n">
-        <v>147.6</v>
+        <v>91.7</v>
       </c>
       <c r="F1234" t="n">
-        <v>10858.7</v>
+        <v>10802.8</v>
       </c>
       <c r="G1234" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H1234" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I1234" t="n">
         <v>3</v>
@@ -41171,7 +41171,7 @@
         </is>
       </c>
       <c r="B1235" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C1235" t="inlineStr">
         <is>
@@ -41179,16 +41179,16 @@
         </is>
       </c>
       <c r="D1235" t="n">
-        <v>66.8</v>
+        <v>93.3</v>
       </c>
       <c r="E1235" t="n">
-        <v>201.1</v>
+        <v>134.3</v>
       </c>
       <c r="F1235" t="n">
-        <v>10892.1</v>
+        <v>10825.3</v>
       </c>
       <c r="G1235" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1235" t="n">
         <v>3</v>
@@ -41204,7 +41204,7 @@
         </is>
       </c>
       <c r="B1236" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C1236" t="inlineStr">
         <is>
@@ -41212,16 +41212,16 @@
         </is>
       </c>
       <c r="D1236" t="n">
-        <v>73</v>
+        <v>63.40000000000001</v>
       </c>
       <c r="E1236" t="n">
-        <v>201.4</v>
+        <v>142.3</v>
       </c>
       <c r="F1236" t="n">
-        <v>10066.5</v>
+        <v>10007.4</v>
       </c>
       <c r="G1236" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H1236" t="n">
         <v>2</v>
@@ -41237,7 +41237,7 @@
         </is>
       </c>
       <c r="B1237" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C1237" t="inlineStr">
         <is>
@@ -41245,16 +41245,16 @@
         </is>
       </c>
       <c r="D1237" t="n">
-        <v>63.6</v>
+        <v>103</v>
       </c>
       <c r="E1237" t="n">
-        <v>215.6</v>
+        <v>152</v>
       </c>
       <c r="F1237" t="n">
-        <v>9880.200000000001</v>
+        <v>9816.6</v>
       </c>
       <c r="G1237" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H1237" t="n">
         <v>1</v>
@@ -41270,7 +41270,7 @@
         </is>
       </c>
       <c r="B1238" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C1238" t="inlineStr">
         <is>
@@ -41278,16 +41278,16 @@
         </is>
       </c>
       <c r="D1238" t="n">
-        <v>70</v>
+        <v>60.2</v>
       </c>
       <c r="E1238" t="n">
-        <v>196.2</v>
+        <v>126.2</v>
       </c>
       <c r="F1238" t="n">
-        <v>11131</v>
+        <v>11061</v>
       </c>
       <c r="G1238" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H1238" t="n">
         <v>4</v>
@@ -41303,7 +41303,7 @@
         </is>
       </c>
       <c r="B1239" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C1239" t="inlineStr">
         <is>
@@ -41311,19 +41311,19 @@
         </is>
       </c>
       <c r="D1239" t="n">
-        <v>40.5</v>
+        <v>44.6</v>
       </c>
       <c r="E1239" t="n">
-        <v>132.1</v>
+        <v>104.2</v>
       </c>
       <c r="F1239" t="n">
-        <v>8966</v>
+        <v>8938.1</v>
       </c>
       <c r="G1239" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H1239" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I1239" t="n">
         <v>7</v>
@@ -41336,7 +41336,7 @@
         </is>
       </c>
       <c r="B1240" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C1240" t="inlineStr">
         <is>
@@ -41344,19 +41344,19 @@
         </is>
       </c>
       <c r="D1240" t="n">
-        <v>59.8</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="E1240" t="n">
-        <v>180.9</v>
+        <v>121.1</v>
       </c>
       <c r="F1240" t="n">
-        <v>9785</v>
+        <v>9725.200000000001</v>
       </c>
       <c r="G1240" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H1240" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I1240" t="n">
         <v>6</v>
@@ -41369,7 +41369,7 @@
         </is>
       </c>
       <c r="B1241" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C1241" t="inlineStr">
         <is>
@@ -41377,19 +41377,19 @@
         </is>
       </c>
       <c r="D1241" t="n">
-        <v>43.5</v>
+        <v>57.8</v>
       </c>
       <c r="E1241" t="n">
-        <v>157.3</v>
+        <v>123</v>
       </c>
       <c r="F1241" t="n">
-        <v>7692.3</v>
+        <v>7658</v>
       </c>
       <c r="G1241" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H1241" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I1241" t="n">
         <v>8</v>
@@ -41402,7 +41402,7 @@
         </is>
       </c>
       <c r="B1242" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C1242" t="inlineStr">
         <is>
@@ -41410,16 +41410,16 @@
         </is>
       </c>
       <c r="D1242" t="n">
-        <v>56.9</v>
+        <v>62.4</v>
       </c>
       <c r="E1242" t="n">
-        <v>204.5</v>
+        <v>154.1</v>
       </c>
       <c r="F1242" t="n">
-        <v>10915.6</v>
+        <v>10865.2</v>
       </c>
       <c r="G1242" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1242" t="n">
         <v>7</v>
@@ -41435,7 +41435,7 @@
         </is>
       </c>
       <c r="B1243" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C1243" t="inlineStr">
         <is>
@@ -41443,16 +41443,16 @@
         </is>
       </c>
       <c r="D1243" t="n">
-        <v>55.1</v>
+        <v>66.8</v>
       </c>
       <c r="E1243" t="n">
-        <v>256.2</v>
+        <v>201.1</v>
       </c>
       <c r="F1243" t="n">
-        <v>10947.2</v>
+        <v>10892.1</v>
       </c>
       <c r="G1243" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H1243" t="n">
         <v>3</v>
@@ -41468,7 +41468,7 @@
         </is>
       </c>
       <c r="B1244" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C1244" t="inlineStr">
         <is>
@@ -41476,16 +41476,16 @@
         </is>
       </c>
       <c r="D1244" t="n">
-        <v>58.8</v>
+        <v>73</v>
       </c>
       <c r="E1244" t="n">
-        <v>260.2</v>
+        <v>215.3</v>
       </c>
       <c r="F1244" t="n">
-        <v>10125.3</v>
+        <v>10080.4</v>
       </c>
       <c r="G1244" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H1244" t="n">
         <v>2</v>
@@ -41501,7 +41501,7 @@
         </is>
       </c>
       <c r="B1245" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C1245" t="inlineStr">
         <is>
@@ -41509,16 +41509,16 @@
         </is>
       </c>
       <c r="D1245" t="n">
-        <v>86.2</v>
+        <v>63.6</v>
       </c>
       <c r="E1245" t="n">
-        <v>301.8</v>
+        <v>215.6</v>
       </c>
       <c r="F1245" t="n">
-        <v>9966.4</v>
+        <v>9880.200000000001</v>
       </c>
       <c r="G1245" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H1245" t="n">
         <v>1</v>
@@ -41534,7 +41534,7 @@
         </is>
       </c>
       <c r="B1246" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C1246" t="inlineStr">
         <is>
@@ -41542,16 +41542,16 @@
         </is>
       </c>
       <c r="D1246" t="n">
-        <v>56.8</v>
+        <v>70</v>
       </c>
       <c r="E1246" t="n">
-        <v>253</v>
+        <v>196.2</v>
       </c>
       <c r="F1246" t="n">
-        <v>11187.8</v>
+        <v>11131</v>
       </c>
       <c r="G1246" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H1246" t="n">
         <v>4</v>
@@ -41567,7 +41567,7 @@
         </is>
       </c>
       <c r="B1247" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C1247" t="inlineStr">
         <is>
@@ -41575,16 +41575,16 @@
         </is>
       </c>
       <c r="D1247" t="n">
-        <v>53.5</v>
+        <v>40.5</v>
       </c>
       <c r="E1247" t="n">
-        <v>185.6</v>
+        <v>144.7</v>
       </c>
       <c r="F1247" t="n">
-        <v>9019.5</v>
+        <v>8978.6</v>
       </c>
       <c r="G1247" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H1247" t="n">
         <v>8</v>
@@ -41600,7 +41600,7 @@
         </is>
       </c>
       <c r="B1248" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C1248" t="inlineStr">
         <is>
@@ -41608,19 +41608,19 @@
         </is>
       </c>
       <c r="D1248" t="n">
-        <v>44.2</v>
+        <v>59.8</v>
       </c>
       <c r="E1248" t="n">
-        <v>225.1</v>
+        <v>180.9</v>
       </c>
       <c r="F1248" t="n">
-        <v>9829.200000000001</v>
+        <v>9785</v>
       </c>
       <c r="G1248" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H1248" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I1248" t="n">
         <v>6</v>
@@ -41633,7 +41633,7 @@
         </is>
       </c>
       <c r="B1249" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C1249" t="inlineStr">
         <is>
@@ -41641,19 +41641,19 @@
         </is>
       </c>
       <c r="D1249" t="n">
-        <v>71.5</v>
+        <v>43.5</v>
       </c>
       <c r="E1249" t="n">
-        <v>228.8</v>
+        <v>166.5</v>
       </c>
       <c r="F1249" t="n">
-        <v>7763.8</v>
+        <v>7701.5</v>
       </c>
       <c r="G1249" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H1249" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I1249" t="n">
         <v>8</v>
@@ -41666,7 +41666,7 @@
         </is>
       </c>
       <c r="B1250" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C1250" t="inlineStr">
         <is>
@@ -41674,19 +41674,19 @@
         </is>
       </c>
       <c r="D1250" t="n">
-        <v>49.90000000000001</v>
+        <v>56.9</v>
       </c>
       <c r="E1250" t="n">
-        <v>254.4</v>
+        <v>211</v>
       </c>
       <c r="F1250" t="n">
-        <v>10965.5</v>
+        <v>10922.1</v>
       </c>
       <c r="G1250" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H1250" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I1250" t="n">
         <v>3</v>
@@ -41699,7 +41699,7 @@
         </is>
       </c>
       <c r="B1251" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C1251" t="inlineStr">
         <is>
@@ -41707,16 +41707,16 @@
         </is>
       </c>
       <c r="D1251" t="n">
-        <v>70.40000000000001</v>
+        <v>55.1</v>
       </c>
       <c r="E1251" t="n">
-        <v>326.6</v>
+        <v>256.2</v>
       </c>
       <c r="F1251" t="n">
-        <v>11017.6</v>
+        <v>10947.2</v>
       </c>
       <c r="G1251" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1251" t="n">
         <v>3</v>
@@ -41732,7 +41732,7 @@
         </is>
       </c>
       <c r="B1252" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C1252" t="inlineStr">
         <is>
@@ -41740,19 +41740,19 @@
         </is>
       </c>
       <c r="D1252" t="n">
-        <v>57.1</v>
+        <v>58.8</v>
       </c>
       <c r="E1252" t="n">
-        <v>317.3</v>
+        <v>274.1</v>
       </c>
       <c r="F1252" t="n">
-        <v>10182.4</v>
+        <v>10139.2</v>
       </c>
       <c r="G1252" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H1252" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I1252" t="n">
         <v>4</v>
@@ -41765,7 +41765,7 @@
         </is>
       </c>
       <c r="B1253" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C1253" t="inlineStr">
         <is>
@@ -41773,16 +41773,16 @@
         </is>
       </c>
       <c r="D1253" t="n">
-        <v>82.7</v>
+        <v>86.2</v>
       </c>
       <c r="E1253" t="n">
-        <v>384.5</v>
+        <v>301.8</v>
       </c>
       <c r="F1253" t="n">
-        <v>10049.1</v>
+        <v>9966.4</v>
       </c>
       <c r="G1253" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H1253" t="n">
         <v>1</v>
@@ -41798,7 +41798,7 @@
         </is>
       </c>
       <c r="B1254" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C1254" t="inlineStr">
         <is>
@@ -41806,19 +41806,19 @@
         </is>
       </c>
       <c r="D1254" t="n">
-        <v>86.5</v>
+        <v>56.8</v>
       </c>
       <c r="E1254" t="n">
-        <v>339.5</v>
+        <v>253</v>
       </c>
       <c r="F1254" t="n">
-        <v>11274.3</v>
+        <v>11187.8</v>
       </c>
       <c r="G1254" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H1254" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I1254" t="n">
         <v>1</v>
@@ -41831,7 +41831,7 @@
         </is>
       </c>
       <c r="B1255" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C1255" t="inlineStr">
         <is>
@@ -41839,19 +41839,19 @@
         </is>
       </c>
       <c r="D1255" t="n">
-        <v>75.8</v>
+        <v>53.5</v>
       </c>
       <c r="E1255" t="n">
-        <v>261.4</v>
+        <v>198.2</v>
       </c>
       <c r="F1255" t="n">
-        <v>9095.299999999999</v>
+        <v>9032.1</v>
       </c>
       <c r="G1255" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H1255" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I1255" t="n">
         <v>7</v>
@@ -41864,7 +41864,7 @@
         </is>
       </c>
       <c r="B1256" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C1256" t="inlineStr">
         <is>
@@ -41872,19 +41872,19 @@
         </is>
       </c>
       <c r="D1256" t="n">
-        <v>77.7</v>
+        <v>44.2</v>
       </c>
       <c r="E1256" t="n">
-        <v>302.8</v>
+        <v>225.1</v>
       </c>
       <c r="F1256" t="n">
-        <v>9906.9</v>
+        <v>9829.200000000001</v>
       </c>
       <c r="G1256" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H1256" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I1256" t="n">
         <v>6</v>
@@ -41897,7 +41897,7 @@
         </is>
       </c>
       <c r="B1257" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C1257" t="inlineStr">
         <is>
@@ -41905,19 +41905,19 @@
         </is>
       </c>
       <c r="D1257" t="n">
-        <v>55.6</v>
+        <v>71.5</v>
       </c>
       <c r="E1257" t="n">
-        <v>284.4</v>
+        <v>238</v>
       </c>
       <c r="F1257" t="n">
-        <v>7819.4</v>
+        <v>7773</v>
       </c>
       <c r="G1257" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H1257" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I1257" t="n">
         <v>8</v>
@@ -41930,7 +41930,7 @@
         </is>
       </c>
       <c r="B1258" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C1258" t="inlineStr">
         <is>
@@ -41938,16 +41938,16 @@
         </is>
       </c>
       <c r="D1258" t="n">
-        <v>34.2</v>
+        <v>49.90000000000001</v>
       </c>
       <c r="E1258" t="n">
-        <v>288.6</v>
+        <v>260.9</v>
       </c>
       <c r="F1258" t="n">
-        <v>10999.7</v>
+        <v>10972</v>
       </c>
       <c r="G1258" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H1258" t="n">
         <v>8</v>
@@ -41963,7 +41963,7 @@
         </is>
       </c>
       <c r="B1259" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C1259" t="inlineStr">
         <is>
@@ -41971,13 +41971,13 @@
         </is>
       </c>
       <c r="D1259" t="n">
-        <v>45.6</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="E1259" t="n">
-        <v>372.2</v>
+        <v>326.6</v>
       </c>
       <c r="F1259" t="n">
-        <v>11063.2</v>
+        <v>11017.6</v>
       </c>
       <c r="G1259" t="n">
         <v>5</v>
@@ -41996,7 +41996,7 @@
         </is>
       </c>
       <c r="B1260" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C1260" t="inlineStr">
         <is>
@@ -42004,16 +42004,16 @@
         </is>
       </c>
       <c r="D1260" t="n">
-        <v>56.1</v>
+        <v>57.1</v>
       </c>
       <c r="E1260" t="n">
-        <v>373.4</v>
+        <v>331.2</v>
       </c>
       <c r="F1260" t="n">
-        <v>10238.5</v>
+        <v>10196.3</v>
       </c>
       <c r="G1260" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H1260" t="n">
         <v>3</v>
@@ -42029,7 +42029,7 @@
         </is>
       </c>
       <c r="B1261" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C1261" t="inlineStr">
         <is>
@@ -42037,16 +42037,16 @@
         </is>
       </c>
       <c r="D1261" t="n">
-        <v>61.7</v>
+        <v>82.7</v>
       </c>
       <c r="E1261" t="n">
-        <v>446.2</v>
+        <v>384.5</v>
       </c>
       <c r="F1261" t="n">
-        <v>10110.8</v>
+        <v>10049.1</v>
       </c>
       <c r="G1261" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H1261" t="n">
         <v>1</v>
@@ -42062,7 +42062,7 @@
         </is>
       </c>
       <c r="B1262" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C1262" t="inlineStr">
         <is>
@@ -42070,16 +42070,16 @@
         </is>
       </c>
       <c r="D1262" t="n">
-        <v>58.3</v>
+        <v>86.5</v>
       </c>
       <c r="E1262" t="n">
-        <v>397.8</v>
+        <v>339.5</v>
       </c>
       <c r="F1262" t="n">
-        <v>11332.6</v>
+        <v>11274.3</v>
       </c>
       <c r="G1262" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H1262" t="n">
         <v>2</v>
@@ -42095,7 +42095,7 @@
         </is>
       </c>
       <c r="B1263" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C1263" t="inlineStr">
         <is>
@@ -42103,13 +42103,13 @@
         </is>
       </c>
       <c r="D1263" t="n">
-        <v>47.9</v>
+        <v>75.8</v>
       </c>
       <c r="E1263" t="n">
-        <v>309.3</v>
+        <v>274</v>
       </c>
       <c r="F1263" t="n">
-        <v>9143.200000000001</v>
+        <v>9107.9</v>
       </c>
       <c r="G1263" t="n">
         <v>4</v>
@@ -42128,7 +42128,7 @@
         </is>
       </c>
       <c r="B1264" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C1264" t="inlineStr">
         <is>
@@ -42136,16 +42136,16 @@
         </is>
       </c>
       <c r="D1264" t="n">
-        <v>32.4</v>
+        <v>77.7</v>
       </c>
       <c r="E1264" t="n">
-        <v>335.2</v>
+        <v>302.8</v>
       </c>
       <c r="F1264" t="n">
-        <v>9939.299999999999</v>
+        <v>9906.9</v>
       </c>
       <c r="G1264" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H1264" t="n">
         <v>5</v>
@@ -42161,7 +42161,7 @@
         </is>
       </c>
       <c r="B1265" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C1265" t="inlineStr">
         <is>
@@ -42169,16 +42169,16 @@
         </is>
       </c>
       <c r="D1265" t="n">
-        <v>34.2</v>
+        <v>55.6</v>
       </c>
       <c r="E1265" t="n">
-        <v>318.6</v>
+        <v>293.6</v>
       </c>
       <c r="F1265" t="n">
-        <v>7853.6</v>
+        <v>7828.6</v>
       </c>
       <c r="G1265" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H1265" t="n">
         <v>6</v>
@@ -42194,7 +42194,7 @@
         </is>
       </c>
       <c r="B1266" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C1266" t="inlineStr">
         <is>
@@ -42202,19 +42202,19 @@
         </is>
       </c>
       <c r="D1266" t="n">
-        <v>73.59999999999999</v>
+        <v>34.2</v>
       </c>
       <c r="E1266" t="n">
-        <v>362.2</v>
+        <v>295.1</v>
       </c>
       <c r="F1266" t="n">
-        <v>11073.3</v>
+        <v>11006.2</v>
       </c>
       <c r="G1266" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H1266" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I1266" t="n">
         <v>3</v>
@@ -42227,7 +42227,7 @@
         </is>
       </c>
       <c r="B1267" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C1267" t="inlineStr">
         <is>
@@ -42235,13 +42235,13 @@
         </is>
       </c>
       <c r="D1267" t="n">
-        <v>59.40000000000001</v>
+        <v>45.6</v>
       </c>
       <c r="E1267" t="n">
-        <v>431.6</v>
+        <v>372.2</v>
       </c>
       <c r="F1267" t="n">
-        <v>11122.6</v>
+        <v>11063.2</v>
       </c>
       <c r="G1267" t="n">
         <v>5</v>
@@ -42260,7 +42260,7 @@
         </is>
       </c>
       <c r="B1268" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C1268" t="inlineStr">
         <is>
@@ -42268,16 +42268,16 @@
         </is>
       </c>
       <c r="D1268" t="n">
-        <v>78.59999999999999</v>
+        <v>56.1</v>
       </c>
       <c r="E1268" t="n">
-        <v>452</v>
+        <v>387.3</v>
       </c>
       <c r="F1268" t="n">
-        <v>10317.1</v>
+        <v>10252.4</v>
       </c>
       <c r="G1268" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H1268" t="n">
         <v>3</v>
@@ -42293,7 +42293,7 @@
         </is>
       </c>
       <c r="B1269" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C1269" t="inlineStr">
         <is>
@@ -42301,16 +42301,16 @@
         </is>
       </c>
       <c r="D1269" t="n">
-        <v>46</v>
+        <v>61.7</v>
       </c>
       <c r="E1269" t="n">
-        <v>492.2</v>
+        <v>446.2</v>
       </c>
       <c r="F1269" t="n">
-        <v>10156.8</v>
+        <v>10110.8</v>
       </c>
       <c r="G1269" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H1269" t="n">
         <v>1</v>
@@ -42326,7 +42326,7 @@
         </is>
       </c>
       <c r="B1270" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C1270" t="inlineStr">
         <is>
@@ -42334,16 +42334,16 @@
         </is>
       </c>
       <c r="D1270" t="n">
-        <v>70.09999999999999</v>
+        <v>58.3</v>
       </c>
       <c r="E1270" t="n">
-        <v>467.9</v>
+        <v>397.8</v>
       </c>
       <c r="F1270" t="n">
-        <v>11402.7</v>
+        <v>11332.6</v>
       </c>
       <c r="G1270" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1270" t="n">
         <v>2</v>
@@ -42359,7 +42359,7 @@
         </is>
       </c>
       <c r="B1271" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C1271" t="inlineStr">
         <is>
@@ -42367,19 +42367,19 @@
         </is>
       </c>
       <c r="D1271" t="n">
-        <v>52.5</v>
+        <v>47.9</v>
       </c>
       <c r="E1271" t="n">
-        <v>361.8</v>
+        <v>321.9</v>
       </c>
       <c r="F1271" t="n">
-        <v>9195.700000000001</v>
+        <v>9155.799999999999</v>
       </c>
       <c r="G1271" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H1271" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I1271" t="n">
         <v>7</v>
@@ -42392,7 +42392,7 @@
         </is>
       </c>
       <c r="B1272" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C1272" t="inlineStr">
         <is>
@@ -42400,16 +42400,16 @@
         </is>
       </c>
       <c r="D1272" t="n">
-        <v>74.90000000000001</v>
+        <v>32.4</v>
       </c>
       <c r="E1272" t="n">
-        <v>410.1</v>
+        <v>335.2</v>
       </c>
       <c r="F1272" t="n">
-        <v>10014.2</v>
+        <v>9939.299999999999</v>
       </c>
       <c r="G1272" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H1272" t="n">
         <v>5</v>
@@ -42425,7 +42425,7 @@
         </is>
       </c>
       <c r="B1273" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C1273" t="inlineStr">
         <is>
@@ -42433,13 +42433,13 @@
         </is>
       </c>
       <c r="D1273" t="n">
-        <v>58.2</v>
+        <v>34.2</v>
       </c>
       <c r="E1273" t="n">
-        <v>376.8</v>
+        <v>327.8</v>
       </c>
       <c r="F1273" t="n">
-        <v>7911.8</v>
+        <v>7862.8</v>
       </c>
       <c r="G1273" t="n">
         <v>6</v>
@@ -42458,7 +42458,7 @@
         </is>
       </c>
       <c r="B1274" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C1274" t="inlineStr">
         <is>
@@ -42466,19 +42466,19 @@
         </is>
       </c>
       <c r="D1274" t="n">
-        <v>53.8</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="E1274" t="n">
-        <v>416</v>
+        <v>368.7</v>
       </c>
       <c r="F1274" t="n">
-        <v>11127.1</v>
+        <v>11079.8</v>
       </c>
       <c r="G1274" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H1274" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I1274" t="n">
         <v>3</v>
@@ -42491,7 +42491,7 @@
         </is>
       </c>
       <c r="B1275" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C1275" t="inlineStr">
         <is>
@@ -42499,16 +42499,16 @@
         </is>
       </c>
       <c r="D1275" t="n">
-        <v>51.1</v>
+        <v>59.40000000000001</v>
       </c>
       <c r="E1275" t="n">
-        <v>482.7</v>
+        <v>431.6</v>
       </c>
       <c r="F1275" t="n">
-        <v>11173.7</v>
+        <v>11122.6</v>
       </c>
       <c r="G1275" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H1275" t="n">
         <v>4</v>
@@ -42524,7 +42524,7 @@
         </is>
       </c>
       <c r="B1276" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C1276" t="inlineStr">
         <is>
@@ -42532,16 +42532,16 @@
         </is>
       </c>
       <c r="D1276" t="n">
-        <v>62.1</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="E1276" t="n">
-        <v>514.1</v>
+        <v>465.9</v>
       </c>
       <c r="F1276" t="n">
-        <v>10379.2</v>
+        <v>10331</v>
       </c>
       <c r="G1276" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H1276" t="n">
         <v>3</v>
@@ -42557,7 +42557,7 @@
         </is>
       </c>
       <c r="B1277" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C1277" t="inlineStr">
         <is>
@@ -42565,16 +42565,16 @@
         </is>
       </c>
       <c r="D1277" t="n">
-        <v>69.5</v>
+        <v>46</v>
       </c>
       <c r="E1277" t="n">
-        <v>561.7</v>
+        <v>492.2</v>
       </c>
       <c r="F1277" t="n">
-        <v>10226.3</v>
+        <v>10156.8</v>
       </c>
       <c r="G1277" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H1277" t="n">
         <v>1</v>
@@ -42590,7 +42590,7 @@
         </is>
       </c>
       <c r="B1278" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C1278" t="inlineStr">
         <is>
@@ -42598,16 +42598,16 @@
         </is>
       </c>
       <c r="D1278" t="n">
-        <v>59.5</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="E1278" t="n">
-        <v>527.4</v>
+        <v>467.9</v>
       </c>
       <c r="F1278" t="n">
-        <v>11462.2</v>
+        <v>11402.7</v>
       </c>
       <c r="G1278" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1278" t="n">
         <v>2</v>
@@ -42623,7 +42623,7 @@
         </is>
       </c>
       <c r="B1279" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C1279" t="inlineStr">
         <is>
@@ -42631,19 +42631,19 @@
         </is>
       </c>
       <c r="D1279" t="n">
-        <v>54.1</v>
+        <v>52.5</v>
       </c>
       <c r="E1279" t="n">
-        <v>415.9</v>
+        <v>374.4</v>
       </c>
       <c r="F1279" t="n">
-        <v>9249.799999999999</v>
+        <v>9208.299999999999</v>
       </c>
       <c r="G1279" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H1279" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I1279" t="n">
         <v>7</v>
@@ -42656,7 +42656,7 @@
         </is>
       </c>
       <c r="B1280" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C1280" t="inlineStr">
         <is>
@@ -42664,13 +42664,13 @@
         </is>
       </c>
       <c r="D1280" t="n">
-        <v>69.2</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="E1280" t="n">
-        <v>479.3</v>
+        <v>410.1</v>
       </c>
       <c r="F1280" t="n">
-        <v>10083.4</v>
+        <v>10014.2</v>
       </c>
       <c r="G1280" t="n">
         <v>2</v>
@@ -42689,7 +42689,7 @@
         </is>
       </c>
       <c r="B1281" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C1281" t="inlineStr">
         <is>
@@ -42697,16 +42697,16 @@
         </is>
       </c>
       <c r="D1281" t="n">
-        <v>60</v>
+        <v>58.2</v>
       </c>
       <c r="E1281" t="n">
-        <v>436.8</v>
+        <v>386</v>
       </c>
       <c r="F1281" t="n">
-        <v>7971.8</v>
+        <v>7921</v>
       </c>
       <c r="G1281" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1281" t="n">
         <v>6</v>
@@ -42722,7 +42722,7 @@
         </is>
       </c>
       <c r="B1282" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C1282" t="inlineStr">
         <is>
@@ -42730,19 +42730,19 @@
         </is>
       </c>
       <c r="D1282" t="n">
-        <v>87.8</v>
+        <v>53.8</v>
       </c>
       <c r="E1282" t="n">
-        <v>503.8</v>
+        <v>422.5</v>
       </c>
       <c r="F1282" t="n">
-        <v>11214.9</v>
+        <v>11133.6</v>
       </c>
       <c r="G1282" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H1282" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I1282" t="n">
         <v>3</v>
@@ -42755,7 +42755,7 @@
         </is>
       </c>
       <c r="B1283" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C1283" t="inlineStr">
         <is>
@@ -42763,19 +42763,19 @@
         </is>
       </c>
       <c r="D1283" t="n">
-        <v>67</v>
+        <v>51.1</v>
       </c>
       <c r="E1283" t="n">
-        <v>549.7</v>
+        <v>482.7</v>
       </c>
       <c r="F1283" t="n">
-        <v>11240.7</v>
+        <v>11173.7</v>
       </c>
       <c r="G1283" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H1283" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I1283" t="n">
         <v>2</v>
@@ -42788,7 +42788,7 @@
         </is>
       </c>
       <c r="B1284" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C1284" t="inlineStr">
         <is>
@@ -42796,19 +42796,19 @@
         </is>
       </c>
       <c r="D1284" t="n">
-        <v>55.4</v>
+        <v>62.1</v>
       </c>
       <c r="E1284" t="n">
-        <v>569.5</v>
+        <v>528</v>
       </c>
       <c r="F1284" t="n">
-        <v>10434.6</v>
+        <v>10393.1</v>
       </c>
       <c r="G1284" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H1284" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I1284" t="n">
         <v>4</v>
@@ -42821,7 +42821,7 @@
         </is>
       </c>
       <c r="B1285" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C1285" t="inlineStr">
         <is>
@@ -42829,16 +42829,16 @@
         </is>
       </c>
       <c r="D1285" t="n">
-        <v>57.6</v>
+        <v>69.5</v>
       </c>
       <c r="E1285" t="n">
-        <v>619.3000000000001</v>
+        <v>561.7</v>
       </c>
       <c r="F1285" t="n">
-        <v>10283.9</v>
+        <v>10226.3</v>
       </c>
       <c r="G1285" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H1285" t="n">
         <v>1</v>
@@ -42854,7 +42854,7 @@
         </is>
       </c>
       <c r="B1286" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C1286" t="inlineStr">
         <is>
@@ -42862,19 +42862,19 @@
         </is>
       </c>
       <c r="D1286" t="n">
-        <v>66.3</v>
+        <v>59.5</v>
       </c>
       <c r="E1286" t="n">
-        <v>593.7</v>
+        <v>527.4</v>
       </c>
       <c r="F1286" t="n">
-        <v>11528.5</v>
+        <v>11462.2</v>
       </c>
       <c r="G1286" t="n">
         <v>5</v>
       </c>
       <c r="H1286" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I1286" t="n">
         <v>1</v>
@@ -42887,7 +42887,7 @@
         </is>
       </c>
       <c r="B1287" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C1287" t="inlineStr">
         <is>
@@ -42895,19 +42895,19 @@
         </is>
       </c>
       <c r="D1287" t="n">
-        <v>52.1</v>
+        <v>54.1</v>
       </c>
       <c r="E1287" t="n">
-        <v>468</v>
+        <v>428.5</v>
       </c>
       <c r="F1287" t="n">
-        <v>9301.9</v>
+        <v>9262.4</v>
       </c>
       <c r="G1287" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H1287" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I1287" t="n">
         <v>7</v>
@@ -42920,7 +42920,7 @@
         </is>
       </c>
       <c r="B1288" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C1288" t="inlineStr">
         <is>
@@ -42928,19 +42928,19 @@
         </is>
       </c>
       <c r="D1288" t="n">
-        <v>81.09999999999999</v>
+        <v>69.2</v>
       </c>
       <c r="E1288" t="n">
-        <v>560.4</v>
+        <v>479.3</v>
       </c>
       <c r="F1288" t="n">
-        <v>10164.5</v>
+        <v>10083.4</v>
       </c>
       <c r="G1288" t="n">
         <v>2</v>
       </c>
       <c r="H1288" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I1288" t="n">
         <v>6</v>
@@ -42953,7 +42953,7 @@
         </is>
       </c>
       <c r="B1289" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C1289" t="inlineStr">
         <is>
@@ -42961,16 +42961,16 @@
         </is>
       </c>
       <c r="D1289" t="n">
-        <v>76.89999999999999</v>
+        <v>60</v>
       </c>
       <c r="E1289" t="n">
-        <v>513.7</v>
+        <v>446</v>
       </c>
       <c r="F1289" t="n">
-        <v>8048.7</v>
+        <v>7981</v>
       </c>
       <c r="G1289" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1289" t="n">
         <v>6</v>
@@ -42986,7 +42986,7 @@
         </is>
       </c>
       <c r="B1290" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C1290" t="inlineStr">
         <is>
@@ -42994,19 +42994,19 @@
         </is>
       </c>
       <c r="D1290" t="n">
-        <v>77.90000000000001</v>
+        <v>87.8</v>
       </c>
       <c r="E1290" t="n">
-        <v>581.7</v>
+        <v>510.3</v>
       </c>
       <c r="F1290" t="n">
-        <v>11292.8</v>
+        <v>11221.4</v>
       </c>
       <c r="G1290" t="n">
         <v>1</v>
       </c>
       <c r="H1290" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1290" t="n">
         <v>3</v>
@@ -43019,7 +43019,7 @@
         </is>
       </c>
       <c r="B1291" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C1291" t="inlineStr">
         <is>
@@ -43027,16 +43027,16 @@
         </is>
       </c>
       <c r="D1291" t="n">
-        <v>54.8</v>
+        <v>67</v>
       </c>
       <c r="E1291" t="n">
-        <v>604.5</v>
+        <v>549.7</v>
       </c>
       <c r="F1291" t="n">
-        <v>11295.5</v>
+        <v>11240.7</v>
       </c>
       <c r="G1291" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H1291" t="n">
         <v>5</v>
@@ -43052,7 +43052,7 @@
         </is>
       </c>
       <c r="B1292" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C1292" t="inlineStr">
         <is>
@@ -43060,16 +43060,16 @@
         </is>
       </c>
       <c r="D1292" t="n">
-        <v>68.8</v>
+        <v>55.4</v>
       </c>
       <c r="E1292" t="n">
-        <v>638.3</v>
+        <v>583.4</v>
       </c>
       <c r="F1292" t="n">
-        <v>10503.4</v>
+        <v>10448.5</v>
       </c>
       <c r="G1292" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H1292" t="n">
         <v>3</v>
@@ -43085,7 +43085,7 @@
         </is>
       </c>
       <c r="B1293" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C1293" t="inlineStr">
         <is>
@@ -43093,13 +43093,13 @@
         </is>
       </c>
       <c r="D1293" t="n">
-        <v>60.2</v>
+        <v>57.6</v>
       </c>
       <c r="E1293" t="n">
-        <v>679.5</v>
+        <v>619.3000000000001</v>
       </c>
       <c r="F1293" t="n">
-        <v>10344.1</v>
+        <v>10283.9</v>
       </c>
       <c r="G1293" t="n">
         <v>6</v>
@@ -43118,7 +43118,7 @@
         </is>
       </c>
       <c r="B1294" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C1294" t="inlineStr">
         <is>
@@ -43126,13 +43126,13 @@
         </is>
       </c>
       <c r="D1294" t="n">
-        <v>62.8</v>
+        <v>66.3</v>
       </c>
       <c r="E1294" t="n">
-        <v>656.5</v>
+        <v>593.7</v>
       </c>
       <c r="F1294" t="n">
-        <v>11591.3</v>
+        <v>11528.5</v>
       </c>
       <c r="G1294" t="n">
         <v>5</v>
@@ -43151,7 +43151,7 @@
         </is>
       </c>
       <c r="B1295" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C1295" t="inlineStr">
         <is>
@@ -43159,13 +43159,13 @@
         </is>
       </c>
       <c r="D1295" t="n">
-        <v>50.9</v>
+        <v>52.1</v>
       </c>
       <c r="E1295" t="n">
-        <v>518.9</v>
+        <v>480.6</v>
       </c>
       <c r="F1295" t="n">
-        <v>9352.799999999999</v>
+        <v>9314.5</v>
       </c>
       <c r="G1295" t="n">
         <v>8</v>
@@ -43184,7 +43184,7 @@
         </is>
       </c>
       <c r="B1296" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C1296" t="inlineStr">
         <is>
@@ -43192,13 +43192,13 @@
         </is>
       </c>
       <c r="D1296" t="n">
-        <v>69.40000000000001</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="E1296" t="n">
-        <v>629.8000000000001</v>
+        <v>560.4</v>
       </c>
       <c r="F1296" t="n">
-        <v>10233.9</v>
+        <v>10164.5</v>
       </c>
       <c r="G1296" t="n">
         <v>2</v>
@@ -43217,7 +43217,7 @@
         </is>
       </c>
       <c r="B1297" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C1297" t="inlineStr">
         <is>
@@ -43225,19 +43225,19 @@
         </is>
       </c>
       <c r="D1297" t="n">
-        <v>66.3</v>
+        <v>76.89999999999999</v>
       </c>
       <c r="E1297" t="n">
-        <v>580</v>
+        <v>522.9</v>
       </c>
       <c r="F1297" t="n">
-        <v>8115</v>
+        <v>8057.9</v>
       </c>
       <c r="G1297" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1297" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I1297" t="n">
         <v>8</v>
@@ -43250,7 +43250,7 @@
         </is>
       </c>
       <c r="B1298" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C1298" t="inlineStr">
         <is>
@@ -43258,22 +43258,22 @@
         </is>
       </c>
       <c r="D1298" t="n">
-        <v>68</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="E1298" t="n">
-        <v>649.7</v>
+        <v>588.2</v>
       </c>
       <c r="F1298" t="n">
-        <v>11360.8</v>
+        <v>11299.3</v>
       </c>
       <c r="G1298" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H1298" t="n">
         <v>7</v>
       </c>
       <c r="I1298" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1299">
@@ -43283,7 +43283,7 @@
         </is>
       </c>
       <c r="B1299" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C1299" t="inlineStr">
         <is>
@@ -43291,22 +43291,22 @@
         </is>
       </c>
       <c r="D1299" t="n">
-        <v>89.2</v>
+        <v>54.8</v>
       </c>
       <c r="E1299" t="n">
-        <v>693.7</v>
+        <v>604.5</v>
       </c>
       <c r="F1299" t="n">
-        <v>11384.7</v>
+        <v>11295.5</v>
       </c>
       <c r="G1299" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H1299" t="n">
         <v>5</v>
       </c>
       <c r="I1299" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1300">
@@ -43316,7 +43316,7 @@
         </is>
       </c>
       <c r="B1300" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C1300" t="inlineStr">
         <is>
@@ -43324,19 +43324,19 @@
         </is>
       </c>
       <c r="D1300" t="n">
-        <v>79.3</v>
+        <v>68.8</v>
       </c>
       <c r="E1300" t="n">
-        <v>717.6</v>
+        <v>652.2</v>
       </c>
       <c r="F1300" t="n">
-        <v>10582.7</v>
+        <v>10517.3</v>
       </c>
       <c r="G1300" t="n">
         <v>3</v>
       </c>
       <c r="H1300" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I1300" t="n">
         <v>4</v>
@@ -43349,7 +43349,7 @@
         </is>
       </c>
       <c r="B1301" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C1301" t="inlineStr">
         <is>
@@ -43357,13 +43357,13 @@
         </is>
       </c>
       <c r="D1301" t="n">
-        <v>61</v>
+        <v>60.2</v>
       </c>
       <c r="E1301" t="n">
-        <v>740.5</v>
+        <v>679.5</v>
       </c>
       <c r="F1301" t="n">
-        <v>10405.1</v>
+        <v>10344.1</v>
       </c>
       <c r="G1301" t="n">
         <v>6</v>
@@ -43382,7 +43382,7 @@
         </is>
       </c>
       <c r="B1302" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C1302" t="inlineStr">
         <is>
@@ -43390,19 +43390,19 @@
         </is>
       </c>
       <c r="D1302" t="n">
-        <v>57.4</v>
+        <v>62.8</v>
       </c>
       <c r="E1302" t="n">
-        <v>713.9</v>
+        <v>656.5</v>
       </c>
       <c r="F1302" t="n">
-        <v>11648.7</v>
+        <v>11591.3</v>
       </c>
       <c r="G1302" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H1302" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I1302" t="n">
         <v>1</v>
@@ -43415,7 +43415,7 @@
         </is>
       </c>
       <c r="B1303" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C1303" t="inlineStr">
         <is>
@@ -43423,13 +43423,13 @@
         </is>
       </c>
       <c r="D1303" t="n">
-        <v>46.4</v>
+        <v>50.9</v>
       </c>
       <c r="E1303" t="n">
-        <v>565.3</v>
+        <v>531.5</v>
       </c>
       <c r="F1303" t="n">
-        <v>9399.200000000001</v>
+        <v>9365.4</v>
       </c>
       <c r="G1303" t="n">
         <v>8</v>
@@ -43448,7 +43448,7 @@
         </is>
       </c>
       <c r="B1304" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C1304" t="inlineStr">
         <is>
@@ -43456,16 +43456,16 @@
         </is>
       </c>
       <c r="D1304" t="n">
-        <v>77.2</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="E1304" t="n">
-        <v>707</v>
+        <v>629.8000000000001</v>
       </c>
       <c r="F1304" t="n">
-        <v>10311.1</v>
+        <v>10233.9</v>
       </c>
       <c r="G1304" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1304" t="n">
         <v>4</v>
@@ -43481,7 +43481,7 @@
         </is>
       </c>
       <c r="B1305" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C1305" t="inlineStr">
         <is>
@@ -43489,16 +43489,16 @@
         </is>
       </c>
       <c r="D1305" t="n">
-        <v>95.2</v>
+        <v>66.3</v>
       </c>
       <c r="E1305" t="n">
-        <v>675.2</v>
+        <v>589.2</v>
       </c>
       <c r="F1305" t="n">
-        <v>8210.200000000001</v>
+        <v>8124.2</v>
       </c>
       <c r="G1305" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H1305" t="n">
         <v>6</v>
@@ -43514,7 +43514,7 @@
         </is>
       </c>
       <c r="B1306" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C1306" t="inlineStr">
         <is>
@@ -43522,16 +43522,16 @@
         </is>
       </c>
       <c r="D1306" t="n">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="E1306" t="n">
-        <v>727.7</v>
+        <v>656.2</v>
       </c>
       <c r="F1306" t="n">
-        <v>11438.8</v>
+        <v>11367.3</v>
       </c>
       <c r="G1306" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1306" t="n">
         <v>7</v>
@@ -43547,7 +43547,7 @@
         </is>
       </c>
       <c r="B1307" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C1307" t="inlineStr">
         <is>
@@ -43555,19 +43555,19 @@
         </is>
       </c>
       <c r="D1307" t="n">
-        <v>78.59999999999999</v>
+        <v>89.2</v>
       </c>
       <c r="E1307" t="n">
-        <v>772.3</v>
+        <v>693.7</v>
       </c>
       <c r="F1307" t="n">
-        <v>11463.3</v>
+        <v>11384.7</v>
       </c>
       <c r="G1307" t="n">
         <v>2</v>
       </c>
       <c r="H1307" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I1307" t="n">
         <v>2</v>
@@ -43580,7 +43580,7 @@
         </is>
       </c>
       <c r="B1308" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C1308" t="inlineStr">
         <is>
@@ -43588,19 +43588,19 @@
         </is>
       </c>
       <c r="D1308" t="n">
-        <v>76.90000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="E1308" t="n">
-        <v>794.5</v>
+        <v>731.5</v>
       </c>
       <c r="F1308" t="n">
-        <v>10659.6</v>
+        <v>10596.6</v>
       </c>
       <c r="G1308" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1308" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1308" t="n">
         <v>4</v>
@@ -43613,7 +43613,7 @@
         </is>
       </c>
       <c r="B1309" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C1309" t="inlineStr">
         <is>
@@ -43621,19 +43621,19 @@
         </is>
       </c>
       <c r="D1309" t="n">
-        <v>48.4</v>
+        <v>61</v>
       </c>
       <c r="E1309" t="n">
-        <v>788.9</v>
+        <v>740.5</v>
       </c>
       <c r="F1309" t="n">
-        <v>10453.5</v>
+        <v>10405.1</v>
       </c>
       <c r="G1309" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H1309" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1309" t="n">
         <v>5</v>
@@ -43646,7 +43646,7 @@
         </is>
       </c>
       <c r="B1310" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C1310" t="inlineStr">
         <is>
@@ -43654,16 +43654,16 @@
         </is>
       </c>
       <c r="D1310" t="n">
-        <v>67.59999999999999</v>
+        <v>57.4</v>
       </c>
       <c r="E1310" t="n">
-        <v>781.5</v>
+        <v>713.9</v>
       </c>
       <c r="F1310" t="n">
-        <v>11716.3</v>
+        <v>11648.7</v>
       </c>
       <c r="G1310" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H1310" t="n">
         <v>3</v>
@@ -43679,7 +43679,7 @@
         </is>
       </c>
       <c r="B1311" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C1311" t="inlineStr">
         <is>
@@ -43687,16 +43687,16 @@
         </is>
       </c>
       <c r="D1311" t="n">
-        <v>58.1</v>
+        <v>46.4</v>
       </c>
       <c r="E1311" t="n">
-        <v>623.4</v>
+        <v>577.9</v>
       </c>
       <c r="F1311" t="n">
-        <v>9457.299999999999</v>
+        <v>9411.799999999999</v>
       </c>
       <c r="G1311" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H1311" t="n">
         <v>8</v>
@@ -43712,7 +43712,7 @@
         </is>
       </c>
       <c r="B1312" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C1312" t="inlineStr">
         <is>
@@ -43720,19 +43720,19 @@
         </is>
       </c>
       <c r="D1312" t="n">
-        <v>61.4</v>
+        <v>77.2</v>
       </c>
       <c r="E1312" t="n">
-        <v>768.4</v>
+        <v>707</v>
       </c>
       <c r="F1312" t="n">
-        <v>10372.5</v>
+        <v>10311.1</v>
       </c>
       <c r="G1312" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H1312" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I1312" t="n">
         <v>6</v>
@@ -43745,7 +43745,7 @@
         </is>
       </c>
       <c r="B1313" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C1313" t="inlineStr">
         <is>
@@ -43753,13 +43753,13 @@
         </is>
       </c>
       <c r="D1313" t="n">
-        <v>81.59999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="E1313" t="n">
-        <v>756.8</v>
+        <v>684.4</v>
       </c>
       <c r="F1313" t="n">
-        <v>8291.799999999999</v>
+        <v>8219.4</v>
       </c>
       <c r="G1313" t="n">
         <v>1</v>
@@ -43778,7 +43778,7 @@
         </is>
       </c>
       <c r="B1314" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C1314" t="inlineStr">
         <is>
@@ -43786,16 +43786,16 @@
         </is>
       </c>
       <c r="D1314" t="n">
-        <v>67.5</v>
+        <v>78</v>
       </c>
       <c r="E1314" t="n">
-        <v>795.2</v>
+        <v>734.2</v>
       </c>
       <c r="F1314" t="n">
-        <v>11506.3</v>
+        <v>11445.3</v>
       </c>
       <c r="G1314" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1314" t="n">
         <v>7</v>
@@ -43811,7 +43811,7 @@
         </is>
       </c>
       <c r="B1315" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C1315" t="inlineStr">
         <is>
@@ -43819,19 +43819,19 @@
         </is>
       </c>
       <c r="D1315" t="n">
-        <v>69.8</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="E1315" t="n">
-        <v>842.1</v>
+        <v>772.3</v>
       </c>
       <c r="F1315" t="n">
-        <v>11533.1</v>
+        <v>11463.3</v>
       </c>
       <c r="G1315" t="n">
         <v>2</v>
       </c>
       <c r="H1315" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1315" t="n">
         <v>2</v>
@@ -43844,7 +43844,7 @@
         </is>
       </c>
       <c r="B1316" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C1316" t="inlineStr">
         <is>
@@ -43852,16 +43852,16 @@
         </is>
       </c>
       <c r="D1316" t="n">
-        <v>68.3</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="E1316" t="n">
-        <v>862.8</v>
+        <v>808.4</v>
       </c>
       <c r="F1316" t="n">
-        <v>10727.9</v>
+        <v>10673.5</v>
       </c>
       <c r="G1316" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1316" t="n">
         <v>1</v>
@@ -43877,7 +43877,7 @@
         </is>
       </c>
       <c r="B1317" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C1317" t="inlineStr">
         <is>
@@ -43885,19 +43885,19 @@
         </is>
       </c>
       <c r="D1317" t="n">
-        <v>52.1</v>
+        <v>48.4</v>
       </c>
       <c r="E1317" t="n">
-        <v>841</v>
+        <v>788.9</v>
       </c>
       <c r="F1317" t="n">
-        <v>10505.6</v>
+        <v>10453.5</v>
       </c>
       <c r="G1317" t="n">
         <v>8</v>
       </c>
       <c r="H1317" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I1317" t="n">
         <v>5</v>
@@ -43910,7 +43910,7 @@
         </is>
       </c>
       <c r="B1318" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C1318" t="inlineStr">
         <is>
@@ -43918,19 +43918,19 @@
         </is>
       </c>
       <c r="D1318" t="n">
-        <v>79.7</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="E1318" t="n">
-        <v>861.2</v>
+        <v>781.5</v>
       </c>
       <c r="F1318" t="n">
-        <v>11796</v>
+        <v>11716.3</v>
       </c>
       <c r="G1318" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H1318" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I1318" t="n">
         <v>1</v>
@@ -43943,7 +43943,7 @@
         </is>
       </c>
       <c r="B1319" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C1319" t="inlineStr">
         <is>
@@ -43951,13 +43951,13 @@
         </is>
       </c>
       <c r="D1319" t="n">
-        <v>58</v>
+        <v>58.1</v>
       </c>
       <c r="E1319" t="n">
-        <v>681.4</v>
+        <v>636</v>
       </c>
       <c r="F1319" t="n">
-        <v>9515.299999999999</v>
+        <v>9469.9</v>
       </c>
       <c r="G1319" t="n">
         <v>7</v>
@@ -43976,7 +43976,7 @@
         </is>
       </c>
       <c r="B1320" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C1320" t="inlineStr">
         <is>
@@ -43984,13 +43984,13 @@
         </is>
       </c>
       <c r="D1320" t="n">
-        <v>59.5</v>
+        <v>61.4</v>
       </c>
       <c r="E1320" t="n">
-        <v>827.9</v>
+        <v>768.4</v>
       </c>
       <c r="F1320" t="n">
-        <v>10432</v>
+        <v>10372.5</v>
       </c>
       <c r="G1320" t="n">
         <v>6</v>
@@ -44009,7 +44009,7 @@
         </is>
       </c>
       <c r="B1321" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C1321" t="inlineStr">
         <is>
@@ -44017,16 +44017,16 @@
         </is>
       </c>
       <c r="D1321" t="n">
-        <v>68.10000000000001</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="E1321" t="n">
-        <v>824.9</v>
+        <v>766</v>
       </c>
       <c r="F1321" t="n">
-        <v>8359.9</v>
+        <v>8301</v>
       </c>
       <c r="G1321" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H1321" t="n">
         <v>6</v>
@@ -44042,7 +44042,7 @@
         </is>
       </c>
       <c r="B1322" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C1322" t="inlineStr">
         <is>
@@ -44050,16 +44050,16 @@
         </is>
       </c>
       <c r="D1322" t="n">
-        <v>58.6</v>
+        <v>67.5</v>
       </c>
       <c r="E1322" t="n">
-        <v>853.8</v>
+        <v>801.7</v>
       </c>
       <c r="F1322" t="n">
-        <v>11564.9</v>
+        <v>11512.8</v>
       </c>
       <c r="G1322" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H1322" t="n">
         <v>7</v>
@@ -44075,7 +44075,7 @@
         </is>
       </c>
       <c r="B1323" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C1323" t="inlineStr">
         <is>
@@ -44083,19 +44083,19 @@
         </is>
       </c>
       <c r="D1323" t="n">
-        <v>105.7</v>
+        <v>69.8</v>
       </c>
       <c r="E1323" t="n">
-        <v>947.8</v>
+        <v>842.1</v>
       </c>
       <c r="F1323" t="n">
-        <v>11638.8</v>
+        <v>11533.1</v>
       </c>
       <c r="G1323" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H1323" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I1323" t="n">
         <v>2</v>
@@ -44108,7 +44108,7 @@
         </is>
       </c>
       <c r="B1324" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C1324" t="inlineStr">
         <is>
@@ -44116,19 +44116,19 @@
         </is>
       </c>
       <c r="D1324" t="n">
-        <v>58.4</v>
+        <v>68.3</v>
       </c>
       <c r="E1324" t="n">
-        <v>921.2</v>
+        <v>876.7</v>
       </c>
       <c r="F1324" t="n">
-        <v>10786.3</v>
+        <v>10741.8</v>
       </c>
       <c r="G1324" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H1324" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I1324" t="n">
         <v>4</v>
@@ -44141,7 +44141,7 @@
         </is>
       </c>
       <c r="B1325" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C1325" t="inlineStr">
         <is>
@@ -44149,19 +44149,19 @@
         </is>
       </c>
       <c r="D1325" t="n">
-        <v>57.4</v>
+        <v>52.1</v>
       </c>
       <c r="E1325" t="n">
-        <v>898.4</v>
+        <v>841</v>
       </c>
       <c r="F1325" t="n">
-        <v>10563</v>
+        <v>10505.6</v>
       </c>
       <c r="G1325" t="n">
         <v>8</v>
       </c>
       <c r="H1325" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I1325" t="n">
         <v>5</v>
@@ -44174,7 +44174,7 @@
         </is>
       </c>
       <c r="B1326" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C1326" t="inlineStr">
         <is>
@@ -44182,16 +44182,16 @@
         </is>
       </c>
       <c r="D1326" t="n">
-        <v>83.40000000000001</v>
+        <v>79.7</v>
       </c>
       <c r="E1326" t="n">
-        <v>944.6</v>
+        <v>861.2</v>
       </c>
       <c r="F1326" t="n">
-        <v>11879.4</v>
+        <v>11796</v>
       </c>
       <c r="G1326" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H1326" t="n">
         <v>2</v>
@@ -44207,7 +44207,7 @@
         </is>
       </c>
       <c r="B1327" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C1327" t="inlineStr">
         <is>
@@ -44215,16 +44215,16 @@
         </is>
       </c>
       <c r="D1327" t="n">
-        <v>74.3</v>
+        <v>58</v>
       </c>
       <c r="E1327" t="n">
-        <v>755.7</v>
+        <v>694</v>
       </c>
       <c r="F1327" t="n">
-        <v>9589.6</v>
+        <v>9527.9</v>
       </c>
       <c r="G1327" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H1327" t="n">
         <v>8</v>
@@ -44240,7 +44240,7 @@
         </is>
       </c>
       <c r="B1328" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C1328" t="inlineStr">
         <is>
@@ -44248,19 +44248,19 @@
         </is>
       </c>
       <c r="D1328" t="n">
-        <v>72</v>
+        <v>59.5</v>
       </c>
       <c r="E1328" t="n">
-        <v>899.9000000000001</v>
+        <v>827.9</v>
       </c>
       <c r="F1328" t="n">
-        <v>10504</v>
+        <v>10432</v>
       </c>
       <c r="G1328" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1328" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I1328" t="n">
         <v>6</v>
@@ -44273,7 +44273,7 @@
         </is>
       </c>
       <c r="B1329" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C1329" t="inlineStr">
         <is>
@@ -44281,19 +44281,19 @@
         </is>
       </c>
       <c r="D1329" t="n">
-        <v>87.09999999999999</v>
+        <v>68.10000000000001</v>
       </c>
       <c r="E1329" t="n">
-        <v>912</v>
+        <v>834.1</v>
       </c>
       <c r="F1329" t="n">
-        <v>8447</v>
+        <v>8369.1</v>
       </c>
       <c r="G1329" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1329" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I1329" t="n">
         <v>8</v>
@@ -44306,7 +44306,7 @@
         </is>
       </c>
       <c r="B1330" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C1330" t="inlineStr">
         <is>
@@ -44314,16 +44314,16 @@
         </is>
       </c>
       <c r="D1330" t="n">
-        <v>61.2</v>
+        <v>58.6</v>
       </c>
       <c r="E1330" t="n">
-        <v>915</v>
+        <v>860.3</v>
       </c>
       <c r="F1330" t="n">
-        <v>11626.1</v>
+        <v>11571.4</v>
       </c>
       <c r="G1330" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1330" t="n">
         <v>7</v>
@@ -44339,7 +44339,7 @@
         </is>
       </c>
       <c r="B1331" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C1331" t="inlineStr">
         <is>
@@ -44347,19 +44347,19 @@
         </is>
       </c>
       <c r="D1331" t="n">
-        <v>55.59999999999999</v>
+        <v>105.7</v>
       </c>
       <c r="E1331" t="n">
-        <v>1003.4</v>
+        <v>947.8</v>
       </c>
       <c r="F1331" t="n">
-        <v>11694.4</v>
+        <v>11638.8</v>
       </c>
       <c r="G1331" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H1331" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1331" t="n">
         <v>2</v>
@@ -44372,7 +44372,7 @@
         </is>
       </c>
       <c r="B1332" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C1332" t="inlineStr">
         <is>
@@ -44380,19 +44380,19 @@
         </is>
       </c>
       <c r="D1332" t="n">
-        <v>50.59999999999999</v>
+        <v>58.4</v>
       </c>
       <c r="E1332" t="n">
-        <v>971.8</v>
+        <v>935.1</v>
       </c>
       <c r="F1332" t="n">
-        <v>10836.9</v>
+        <v>10800.2</v>
       </c>
       <c r="G1332" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H1332" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1332" t="n">
         <v>4</v>
@@ -44405,7 +44405,7 @@
         </is>
       </c>
       <c r="B1333" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C1333" t="inlineStr">
         <is>
@@ -44413,16 +44413,16 @@
         </is>
       </c>
       <c r="D1333" t="n">
-        <v>62.40000000000001</v>
+        <v>57.4</v>
       </c>
       <c r="E1333" t="n">
-        <v>960.8000000000001</v>
+        <v>898.4</v>
       </c>
       <c r="F1333" t="n">
-        <v>10625.4</v>
+        <v>10563</v>
       </c>
       <c r="G1333" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H1333" t="n">
         <v>6</v>
@@ -44438,7 +44438,7 @@
         </is>
       </c>
       <c r="B1334" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C1334" t="inlineStr">
         <is>
@@ -44446,19 +44446,19 @@
         </is>
       </c>
       <c r="D1334" t="n">
-        <v>81.90000000000001</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="E1334" t="n">
-        <v>1026.5</v>
+        <v>944.6</v>
       </c>
       <c r="F1334" t="n">
-        <v>11961.3</v>
+        <v>11879.4</v>
       </c>
       <c r="G1334" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1334" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1334" t="n">
         <v>1</v>
@@ -44471,7 +44471,7 @@
         </is>
       </c>
       <c r="B1335" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C1335" t="inlineStr">
         <is>
@@ -44479,16 +44479,16 @@
         </is>
       </c>
       <c r="D1335" t="n">
-        <v>63.3</v>
+        <v>74.3</v>
       </c>
       <c r="E1335" t="n">
-        <v>819</v>
+        <v>768.3</v>
       </c>
       <c r="F1335" t="n">
-        <v>9652.9</v>
+        <v>9602.200000000001</v>
       </c>
       <c r="G1335" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1335" t="n">
         <v>8</v>
@@ -44504,7 +44504,7 @@
         </is>
       </c>
       <c r="B1336" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C1336" t="inlineStr">
         <is>
@@ -44512,19 +44512,19 @@
         </is>
       </c>
       <c r="D1336" t="n">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="E1336" t="n">
-        <v>985.9000000000001</v>
+        <v>899.9000000000001</v>
       </c>
       <c r="F1336" t="n">
-        <v>10590</v>
+        <v>10504</v>
       </c>
       <c r="G1336" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H1336" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I1336" t="n">
         <v>6</v>
@@ -44537,7 +44537,7 @@
         </is>
       </c>
       <c r="B1337" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C1337" t="inlineStr">
         <is>
@@ -44545,19 +44545,19 @@
         </is>
       </c>
       <c r="D1337" t="n">
-        <v>58.1</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="E1337" t="n">
-        <v>970.1</v>
+        <v>921.2</v>
       </c>
       <c r="F1337" t="n">
-        <v>8505.1</v>
+        <v>8456.200000000001</v>
       </c>
       <c r="G1337" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H1337" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I1337" t="n">
         <v>8</v>
@@ -44570,7 +44570,7 @@
         </is>
       </c>
       <c r="B1338" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C1338" t="inlineStr">
         <is>
@@ -44578,13 +44578,13 @@
         </is>
       </c>
       <c r="D1338" t="n">
-        <v>64.2</v>
+        <v>61.2</v>
       </c>
       <c r="E1338" t="n">
-        <v>979.2</v>
+        <v>921.5</v>
       </c>
       <c r="F1338" t="n">
-        <v>11690.3</v>
+        <v>11632.6</v>
       </c>
       <c r="G1338" t="n">
         <v>5</v>
@@ -44603,7 +44603,7 @@
         </is>
       </c>
       <c r="B1339" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C1339" t="inlineStr">
         <is>
@@ -44611,16 +44611,16 @@
         </is>
       </c>
       <c r="D1339" t="n">
-        <v>88.7</v>
+        <v>55.59999999999999</v>
       </c>
       <c r="E1339" t="n">
-        <v>1092.1</v>
+        <v>1003.4</v>
       </c>
       <c r="F1339" t="n">
-        <v>11783.1</v>
+        <v>11694.4</v>
       </c>
       <c r="G1339" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H1339" t="n">
         <v>2</v>
@@ -44636,7 +44636,7 @@
         </is>
       </c>
       <c r="B1340" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C1340" t="inlineStr">
         <is>
@@ -44644,16 +44644,16 @@
         </is>
       </c>
       <c r="D1340" t="n">
-        <v>76.8</v>
+        <v>50.59999999999999</v>
       </c>
       <c r="E1340" t="n">
-        <v>1048.6</v>
+        <v>985.7</v>
       </c>
       <c r="F1340" t="n">
-        <v>10913.7</v>
+        <v>10850.8</v>
       </c>
       <c r="G1340" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H1340" t="n">
         <v>4</v>
@@ -44669,7 +44669,7 @@
         </is>
       </c>
       <c r="B1341" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C1341" t="inlineStr">
         <is>
@@ -44677,16 +44677,16 @@
         </is>
       </c>
       <c r="D1341" t="n">
-        <v>45</v>
+        <v>62.40000000000001</v>
       </c>
       <c r="E1341" t="n">
-        <v>1005.8</v>
+        <v>960.8000000000001</v>
       </c>
       <c r="F1341" t="n">
-        <v>10670.4</v>
+        <v>10625.4</v>
       </c>
       <c r="G1341" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H1341" t="n">
         <v>6</v>
@@ -44702,7 +44702,7 @@
         </is>
       </c>
       <c r="B1342" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C1342" t="inlineStr">
         <is>
@@ -44710,13 +44710,13 @@
         </is>
       </c>
       <c r="D1342" t="n">
-        <v>81.2</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="E1342" t="n">
-        <v>1107.7</v>
+        <v>1026.5</v>
       </c>
       <c r="F1342" t="n">
-        <v>12042.5</v>
+        <v>11961.3</v>
       </c>
       <c r="G1342" t="n">
         <v>2</v>
@@ -44735,7 +44735,7 @@
         </is>
       </c>
       <c r="B1343" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C1343" t="inlineStr">
         <is>
@@ -44743,16 +44743,16 @@
         </is>
       </c>
       <c r="D1343" t="n">
-        <v>63.7</v>
+        <v>63.3</v>
       </c>
       <c r="E1343" t="n">
-        <v>882.7</v>
+        <v>831.6</v>
       </c>
       <c r="F1343" t="n">
-        <v>9716.6</v>
+        <v>9665.5</v>
       </c>
       <c r="G1343" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H1343" t="n">
         <v>8</v>
@@ -44768,7 +44768,7 @@
         </is>
       </c>
       <c r="B1344" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C1344" t="inlineStr">
         <is>
@@ -44776,16 +44776,16 @@
         </is>
       </c>
       <c r="D1344" t="n">
-        <v>67.7</v>
+        <v>86</v>
       </c>
       <c r="E1344" t="n">
-        <v>1053.6</v>
+        <v>985.9000000000001</v>
       </c>
       <c r="F1344" t="n">
-        <v>10657.7</v>
+        <v>10590</v>
       </c>
       <c r="G1344" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H1344" t="n">
         <v>3</v>
@@ -44801,7 +44801,7 @@
         </is>
       </c>
       <c r="B1345" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C1345" t="inlineStr">
         <is>
@@ -44809,16 +44809,16 @@
         </is>
       </c>
       <c r="D1345" t="n">
-        <v>60.2</v>
+        <v>58.1</v>
       </c>
       <c r="E1345" t="n">
-        <v>1030.3</v>
+        <v>979.3</v>
       </c>
       <c r="F1345" t="n">
-        <v>8565.299999999999</v>
+        <v>8514.299999999999</v>
       </c>
       <c r="G1345" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H1345" t="n">
         <v>5</v>
@@ -44834,7 +44834,7 @@
         </is>
       </c>
       <c r="B1346" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C1346" t="inlineStr">
         <is>
@@ -44842,19 +44842,19 @@
         </is>
       </c>
       <c r="D1346" t="n">
-        <v>88.09999999999999</v>
+        <v>64.2</v>
       </c>
       <c r="E1346" t="n">
-        <v>1067.3</v>
+        <v>985.7</v>
       </c>
       <c r="F1346" t="n">
-        <v>11778.4</v>
+        <v>11696.8</v>
       </c>
       <c r="G1346" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1346" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1346" t="n">
         <v>3</v>
@@ -44867,7 +44867,7 @@
         </is>
       </c>
       <c r="B1347" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C1347" t="inlineStr">
         <is>
@@ -44875,16 +44875,16 @@
         </is>
       </c>
       <c r="D1347" t="n">
-        <v>59.9</v>
+        <v>88.7</v>
       </c>
       <c r="E1347" t="n">
-        <v>1152</v>
+        <v>1092.1</v>
       </c>
       <c r="F1347" t="n">
-        <v>11843</v>
+        <v>11783.1</v>
       </c>
       <c r="G1347" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H1347" t="n">
         <v>2</v>
@@ -44900,7 +44900,7 @@
         </is>
       </c>
       <c r="B1348" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C1348" t="inlineStr">
         <is>
@@ -44908,19 +44908,19 @@
         </is>
       </c>
       <c r="D1348" t="n">
-        <v>70.2</v>
+        <v>76.8</v>
       </c>
       <c r="E1348" t="n">
-        <v>1118.8</v>
+        <v>1062.5</v>
       </c>
       <c r="F1348" t="n">
-        <v>10983.9</v>
+        <v>10927.6</v>
       </c>
       <c r="G1348" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1348" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1348" t="n">
         <v>4</v>
@@ -44933,7 +44933,7 @@
         </is>
       </c>
       <c r="B1349" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C1349" t="inlineStr">
         <is>
@@ -44941,7 +44941,7 @@
         </is>
       </c>
       <c r="D1349" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="E1349" t="n">
         <v>1005.8</v>
@@ -44953,10 +44953,10 @@
         <v>8</v>
       </c>
       <c r="H1349" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I1349" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1350">
@@ -44966,7 +44966,7 @@
         </is>
       </c>
       <c r="B1350" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C1350" t="inlineStr">
         <is>
@@ -44974,16 +44974,16 @@
         </is>
       </c>
       <c r="D1350" t="n">
-        <v>94</v>
+        <v>81.2</v>
       </c>
       <c r="E1350" t="n">
-        <v>1201.7</v>
+        <v>1107.7</v>
       </c>
       <c r="F1350" t="n">
-        <v>12136.5</v>
+        <v>12042.5</v>
       </c>
       <c r="G1350" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H1350" t="n">
         <v>1</v>
@@ -44999,7 +44999,7 @@
         </is>
       </c>
       <c r="B1351" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C1351" t="inlineStr">
         <is>
@@ -45007,16 +45007,16 @@
         </is>
       </c>
       <c r="D1351" t="n">
-        <v>61.6</v>
+        <v>63.7</v>
       </c>
       <c r="E1351" t="n">
-        <v>944.3</v>
+        <v>895.3</v>
       </c>
       <c r="F1351" t="n">
-        <v>9778.200000000001</v>
+        <v>9729.200000000001</v>
       </c>
       <c r="G1351" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1351" t="n">
         <v>8</v>
@@ -45032,7 +45032,7 @@
         </is>
       </c>
       <c r="B1352" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C1352" t="inlineStr">
         <is>
@@ -45040,22 +45040,22 @@
         </is>
       </c>
       <c r="D1352" t="n">
-        <v>58.6</v>
+        <v>67.7</v>
       </c>
       <c r="E1352" t="n">
-        <v>1112.2</v>
+        <v>1053.6</v>
       </c>
       <c r="F1352" t="n">
-        <v>10716.3</v>
+        <v>10657.7</v>
       </c>
       <c r="G1352" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H1352" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I1352" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1353">
@@ -45065,7 +45065,7 @@
         </is>
       </c>
       <c r="B1353" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C1353" t="inlineStr">
         <is>
@@ -45073,19 +45073,19 @@
         </is>
       </c>
       <c r="D1353" t="n">
-        <v>89.5</v>
+        <v>60.2</v>
       </c>
       <c r="E1353" t="n">
-        <v>1119.8</v>
+        <v>1039.5</v>
       </c>
       <c r="F1353" t="n">
-        <v>8654.799999999999</v>
+        <v>8574.5</v>
       </c>
       <c r="G1353" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H1353" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I1353" t="n">
         <v>8</v>
@@ -45098,7 +45098,7 @@
         </is>
       </c>
       <c r="B1354" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C1354" t="inlineStr">
         <is>
@@ -45106,16 +45106,16 @@
         </is>
       </c>
       <c r="D1354" t="n">
-        <v>66.7</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="E1354" t="n">
-        <v>1134</v>
+        <v>1073.8</v>
       </c>
       <c r="F1354" t="n">
-        <v>11845.1</v>
+        <v>11784.9</v>
       </c>
       <c r="G1354" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1354" t="n">
         <v>6</v>
@@ -45131,7 +45131,7 @@
         </is>
       </c>
       <c r="B1355" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C1355" t="inlineStr">
         <is>
@@ -45139,19 +45139,19 @@
         </is>
       </c>
       <c r="D1355" t="n">
-        <v>35.8</v>
+        <v>59.9</v>
       </c>
       <c r="E1355" t="n">
-        <v>1187.8</v>
+        <v>1152</v>
       </c>
       <c r="F1355" t="n">
-        <v>11878.8</v>
+        <v>11843</v>
       </c>
       <c r="G1355" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H1355" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I1355" t="n">
         <v>2</v>
@@ -45164,7 +45164,7 @@
         </is>
       </c>
       <c r="B1356" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C1356" t="inlineStr">
         <is>
@@ -45172,19 +45172,19 @@
         </is>
       </c>
       <c r="D1356" t="n">
-        <v>59.2</v>
+        <v>70.2</v>
       </c>
       <c r="E1356" t="n">
-        <v>1178</v>
+        <v>1132.7</v>
       </c>
       <c r="F1356" t="n">
-        <v>11043.1</v>
+        <v>10997.8</v>
       </c>
       <c r="G1356" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H1356" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I1356" t="n">
         <v>4</v>
@@ -45197,7 +45197,7 @@
         </is>
       </c>
       <c r="B1357" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C1357" t="inlineStr">
         <is>
@@ -45205,16 +45205,16 @@
         </is>
       </c>
       <c r="D1357" t="n">
-        <v>82.2</v>
+        <v>0</v>
       </c>
       <c r="E1357" t="n">
-        <v>1088</v>
+        <v>1005.8</v>
       </c>
       <c r="F1357" t="n">
-        <v>10752.6</v>
+        <v>10670.4</v>
       </c>
       <c r="G1357" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H1357" t="n">
         <v>7</v>
@@ -45230,7 +45230,7 @@
         </is>
       </c>
       <c r="B1358" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C1358" t="inlineStr">
         <is>
@@ -45238,16 +45238,16 @@
         </is>
       </c>
       <c r="D1358" t="n">
-        <v>63</v>
+        <v>94</v>
       </c>
       <c r="E1358" t="n">
-        <v>1264.7</v>
+        <v>1201.7</v>
       </c>
       <c r="F1358" t="n">
-        <v>12199.5</v>
+        <v>12136.5</v>
       </c>
       <c r="G1358" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H1358" t="n">
         <v>1</v>
@@ -45263,7 +45263,7 @@
         </is>
       </c>
       <c r="B1359" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C1359" t="inlineStr">
         <is>
@@ -45271,16 +45271,16 @@
         </is>
       </c>
       <c r="D1359" t="n">
-        <v>56.6</v>
+        <v>61.6</v>
       </c>
       <c r="E1359" t="n">
-        <v>1000.9</v>
+        <v>956.9</v>
       </c>
       <c r="F1359" t="n">
-        <v>9834.799999999999</v>
+        <v>9790.799999999999</v>
       </c>
       <c r="G1359" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H1359" t="n">
         <v>8</v>
@@ -45296,7 +45296,7 @@
         </is>
       </c>
       <c r="B1360" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C1360" t="inlineStr">
         <is>
@@ -45304,19 +45304,19 @@
         </is>
       </c>
       <c r="D1360" t="n">
-        <v>78.59999999999999</v>
+        <v>58.6</v>
       </c>
       <c r="E1360" t="n">
-        <v>1190.8</v>
+        <v>1112.2</v>
       </c>
       <c r="F1360" t="n">
-        <v>10794.9</v>
+        <v>10716.3</v>
       </c>
       <c r="G1360" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H1360" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I1360" t="n">
         <v>5</v>
@@ -45329,7 +45329,7 @@
         </is>
       </c>
       <c r="B1361" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C1361" t="inlineStr">
         <is>
@@ -45337,19 +45337,19 @@
         </is>
       </c>
       <c r="D1361" t="n">
-        <v>87.3</v>
+        <v>89.5</v>
       </c>
       <c r="E1361" t="n">
-        <v>1207.1</v>
+        <v>1129</v>
       </c>
       <c r="F1361" t="n">
-        <v>8742.1</v>
+        <v>8664</v>
       </c>
       <c r="G1361" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H1361" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I1361" t="n">
         <v>8</v>
@@ -45362,7 +45362,7 @@
         </is>
       </c>
       <c r="B1362" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C1362" t="inlineStr">
         <is>
@@ -45370,13 +45370,13 @@
         </is>
       </c>
       <c r="D1362" t="n">
-        <v>70.8</v>
+        <v>66.7</v>
       </c>
       <c r="E1362" t="n">
-        <v>1204.8</v>
+        <v>1140.5</v>
       </c>
       <c r="F1362" t="n">
-        <v>11915.9</v>
+        <v>11851.6</v>
       </c>
       <c r="G1362" t="n">
         <v>4</v>
@@ -45395,7 +45395,7 @@
         </is>
       </c>
       <c r="B1363" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C1363" t="inlineStr">
         <is>
@@ -45403,19 +45403,19 @@
         </is>
       </c>
       <c r="D1363" t="n">
-        <v>76.5</v>
+        <v>35.8</v>
       </c>
       <c r="E1363" t="n">
-        <v>1264.3</v>
+        <v>1187.8</v>
       </c>
       <c r="F1363" t="n">
-        <v>11955.3</v>
+        <v>11878.8</v>
       </c>
       <c r="G1363" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H1363" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I1363" t="n">
         <v>2</v>
@@ -45428,7 +45428,7 @@
         </is>
       </c>
       <c r="B1364" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C1364" t="inlineStr">
         <is>
@@ -45436,19 +45436,19 @@
         </is>
       </c>
       <c r="D1364" t="n">
-        <v>75.2</v>
+        <v>59.2</v>
       </c>
       <c r="E1364" t="n">
-        <v>1253.2</v>
+        <v>1191.9</v>
       </c>
       <c r="F1364" t="n">
-        <v>11118.3</v>
+        <v>11057</v>
       </c>
       <c r="G1364" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H1364" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I1364" t="n">
         <v>4</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="B1365" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C1365" t="inlineStr">
         <is>
@@ -45469,16 +45469,16 @@
         </is>
       </c>
       <c r="D1365" t="n">
-        <v>46.7</v>
+        <v>82.2</v>
       </c>
       <c r="E1365" t="n">
-        <v>1134.7</v>
+        <v>1088</v>
       </c>
       <c r="F1365" t="n">
-        <v>10799.3</v>
+        <v>10752.6</v>
       </c>
       <c r="G1365" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H1365" t="n">
         <v>7</v>
@@ -45494,7 +45494,7 @@
         </is>
       </c>
       <c r="B1366" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C1366" t="inlineStr">
         <is>
@@ -45502,16 +45502,16 @@
         </is>
       </c>
       <c r="D1366" t="n">
-        <v>79.40000000000001</v>
+        <v>63</v>
       </c>
       <c r="E1366" t="n">
-        <v>1344.1</v>
+        <v>1264.7</v>
       </c>
       <c r="F1366" t="n">
-        <v>12278.9</v>
+        <v>12199.5</v>
       </c>
       <c r="G1366" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H1366" t="n">
         <v>1</v>
@@ -45527,7 +45527,7 @@
         </is>
       </c>
       <c r="B1367" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C1367" t="inlineStr">
         <is>
@@ -45535,16 +45535,16 @@
         </is>
       </c>
       <c r="D1367" t="n">
-        <v>56.59999999999999</v>
+        <v>56.6</v>
       </c>
       <c r="E1367" t="n">
-        <v>1057.5</v>
+        <v>1013.5</v>
       </c>
       <c r="F1367" t="n">
-        <v>9891.4</v>
+        <v>9847.4</v>
       </c>
       <c r="G1367" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H1367" t="n">
         <v>8</v>
@@ -45560,7 +45560,7 @@
         </is>
       </c>
       <c r="B1368" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C1368" t="inlineStr">
         <is>
@@ -45568,16 +45568,16 @@
         </is>
       </c>
       <c r="D1368" t="n">
-        <v>65.2</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="E1368" t="n">
-        <v>1256</v>
+        <v>1190.8</v>
       </c>
       <c r="F1368" t="n">
-        <v>10860.1</v>
+        <v>10794.9</v>
       </c>
       <c r="G1368" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1368" t="n">
         <v>4</v>
@@ -45593,7 +45593,7 @@
         </is>
       </c>
       <c r="B1369" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C1369" t="inlineStr">
         <is>
@@ -45601,19 +45601,19 @@
         </is>
       </c>
       <c r="D1369" t="n">
-        <v>54.8</v>
+        <v>87.3</v>
       </c>
       <c r="E1369" t="n">
-        <v>1261.9</v>
+        <v>1216.3</v>
       </c>
       <c r="F1369" t="n">
-        <v>8796.9</v>
+        <v>8751.299999999999</v>
       </c>
       <c r="G1369" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H1369" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I1369" t="n">
         <v>8</v>
@@ -45626,7 +45626,7 @@
         </is>
       </c>
       <c r="B1370" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C1370" t="inlineStr">
         <is>
@@ -45634,16 +45634,16 @@
         </is>
       </c>
       <c r="D1370" t="n">
-        <v>93.8</v>
+        <v>70.8</v>
       </c>
       <c r="E1370" t="n">
-        <v>1298.6</v>
+        <v>1211.3</v>
       </c>
       <c r="F1370" t="n">
-        <v>12009.7</v>
+        <v>11922.4</v>
       </c>
       <c r="G1370" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1370" t="n">
         <v>6</v>
@@ -45659,7 +45659,7 @@
         </is>
       </c>
       <c r="B1371" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C1371" t="inlineStr">
         <is>
@@ -45667,16 +45667,16 @@
         </is>
       </c>
       <c r="D1371" t="n">
-        <v>65.2</v>
+        <v>76.5</v>
       </c>
       <c r="E1371" t="n">
-        <v>1329.5</v>
+        <v>1264.3</v>
       </c>
       <c r="F1371" t="n">
-        <v>12020.5</v>
+        <v>11955.3</v>
       </c>
       <c r="G1371" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H1371" t="n">
         <v>4</v>
@@ -45692,7 +45692,7 @@
         </is>
       </c>
       <c r="B1372" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C1372" t="inlineStr">
         <is>
@@ -45700,19 +45700,19 @@
         </is>
       </c>
       <c r="D1372" t="n">
-        <v>97.59999999999999</v>
+        <v>75.2</v>
       </c>
       <c r="E1372" t="n">
-        <v>1350.8</v>
+        <v>1267.1</v>
       </c>
       <c r="F1372" t="n">
-        <v>11215.9</v>
+        <v>11132.2</v>
       </c>
       <c r="G1372" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H1372" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I1372" t="n">
         <v>4</v>
@@ -45725,7 +45725,7 @@
         </is>
       </c>
       <c r="B1373" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C1373" t="inlineStr">
         <is>
@@ -45733,13 +45733,13 @@
         </is>
       </c>
       <c r="D1373" t="n">
-        <v>63.3</v>
+        <v>46.7</v>
       </c>
       <c r="E1373" t="n">
-        <v>1198</v>
+        <v>1134.7</v>
       </c>
       <c r="F1373" t="n">
-        <v>10862.6</v>
+        <v>10799.3</v>
       </c>
       <c r="G1373" t="n">
         <v>8</v>
@@ -45758,7 +45758,7 @@
         </is>
       </c>
       <c r="B1374" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C1374" t="inlineStr">
         <is>
@@ -45766,16 +45766,16 @@
         </is>
       </c>
       <c r="D1374" t="n">
-        <v>79.3</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="E1374" t="n">
-        <v>1423.4</v>
+        <v>1344.1</v>
       </c>
       <c r="F1374" t="n">
-        <v>12358.2</v>
+        <v>12278.9</v>
       </c>
       <c r="G1374" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H1374" t="n">
         <v>1</v>
@@ -45791,7 +45791,7 @@
         </is>
       </c>
       <c r="B1375" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C1375" t="inlineStr">
         <is>
@@ -45799,16 +45799,16 @@
         </is>
       </c>
       <c r="D1375" t="n">
-        <v>81.7</v>
+        <v>56.59999999999999</v>
       </c>
       <c r="E1375" t="n">
-        <v>1139.2</v>
+        <v>1070.1</v>
       </c>
       <c r="F1375" t="n">
-        <v>9973.1</v>
+        <v>9904</v>
       </c>
       <c r="G1375" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1375" t="n">
         <v>8</v>
@@ -45824,7 +45824,7 @@
         </is>
       </c>
       <c r="B1376" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C1376" t="inlineStr">
         <is>
@@ -45832,16 +45832,16 @@
         </is>
       </c>
       <c r="D1376" t="n">
-        <v>67.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="E1376" t="n">
-        <v>1323.4</v>
+        <v>1256</v>
       </c>
       <c r="F1376" t="n">
-        <v>10927.5</v>
+        <v>10860.1</v>
       </c>
       <c r="G1376" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H1376" t="n">
         <v>5</v>
@@ -45857,7 +45857,7 @@
         </is>
       </c>
       <c r="B1377" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C1377" t="inlineStr">
         <is>
@@ -45865,19 +45865,19 @@
         </is>
       </c>
       <c r="D1377" t="n">
-        <v>82.59999999999999</v>
+        <v>54.8</v>
       </c>
       <c r="E1377" t="n">
-        <v>1344.5</v>
+        <v>1271.1</v>
       </c>
       <c r="F1377" t="n">
-        <v>8879.5</v>
+        <v>8806.1</v>
       </c>
       <c r="G1377" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H1377" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I1377" t="n">
         <v>8</v>
@@ -45890,7 +45890,7 @@
         </is>
       </c>
       <c r="B1378" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C1378" t="inlineStr">
         <is>
@@ -45898,22 +45898,22 @@
         </is>
       </c>
       <c r="D1378" t="n">
-        <v>100.5</v>
+        <v>93.8</v>
       </c>
       <c r="E1378" t="n">
-        <v>1399.1</v>
+        <v>1305.1</v>
       </c>
       <c r="F1378" t="n">
-        <v>12110.2</v>
+        <v>12016.2</v>
       </c>
       <c r="G1378" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H1378" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I1378" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1379">
@@ -45923,7 +45923,7 @@
         </is>
       </c>
       <c r="B1379" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C1379" t="inlineStr">
         <is>
@@ -45931,22 +45931,22 @@
         </is>
       </c>
       <c r="D1379" t="n">
-        <v>80.3</v>
+        <v>65.2</v>
       </c>
       <c r="E1379" t="n">
-        <v>1409.8</v>
+        <v>1329.5</v>
       </c>
       <c r="F1379" t="n">
-        <v>12100.8</v>
+        <v>12020.5</v>
       </c>
       <c r="G1379" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H1379" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1379" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1380">
@@ -45956,7 +45956,7 @@
         </is>
       </c>
       <c r="B1380" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C1380" t="inlineStr">
         <is>
@@ -45964,16 +45964,16 @@
         </is>
       </c>
       <c r="D1380" t="n">
-        <v>60.3</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="E1380" t="n">
-        <v>1411.1</v>
+        <v>1364.7</v>
       </c>
       <c r="F1380" t="n">
-        <v>11276.2</v>
+        <v>11229.8</v>
       </c>
       <c r="G1380" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H1380" t="n">
         <v>2</v>
@@ -45989,7 +45989,7 @@
         </is>
       </c>
       <c r="B1381" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C1381" t="inlineStr">
         <is>
@@ -45997,16 +45997,16 @@
         </is>
       </c>
       <c r="D1381" t="n">
-        <v>67.59999999999999</v>
+        <v>63.3</v>
       </c>
       <c r="E1381" t="n">
-        <v>1265.6</v>
+        <v>1198</v>
       </c>
       <c r="F1381" t="n">
-        <v>10930.2</v>
+        <v>10862.6</v>
       </c>
       <c r="G1381" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H1381" t="n">
         <v>7</v>
@@ -46022,7 +46022,7 @@
         </is>
       </c>
       <c r="B1382" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C1382" t="inlineStr">
         <is>
@@ -46030,16 +46030,16 @@
         </is>
       </c>
       <c r="D1382" t="n">
-        <v>70.2</v>
+        <v>79.3</v>
       </c>
       <c r="E1382" t="n">
-        <v>1493.6</v>
+        <v>1423.4</v>
       </c>
       <c r="F1382" t="n">
-        <v>12428.4</v>
+        <v>12358.2</v>
       </c>
       <c r="G1382" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1382" t="n">
         <v>1</v>
@@ -46055,7 +46055,7 @@
         </is>
       </c>
       <c r="B1383" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C1383" t="inlineStr">
         <is>
@@ -46063,16 +46063,16 @@
         </is>
       </c>
       <c r="D1383" t="n">
-        <v>61.2</v>
+        <v>81.7</v>
       </c>
       <c r="E1383" t="n">
-        <v>1200.4</v>
+        <v>1151.8</v>
       </c>
       <c r="F1383" t="n">
-        <v>10034.3</v>
+        <v>9985.700000000001</v>
       </c>
       <c r="G1383" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1383" t="n">
         <v>8</v>
@@ -46088,7 +46088,7 @@
         </is>
       </c>
       <c r="B1384" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C1384" t="inlineStr">
         <is>
@@ -46096,19 +46096,19 @@
         </is>
       </c>
       <c r="D1384" t="n">
-        <v>50.8</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="E1384" t="n">
-        <v>1374.2</v>
+        <v>1323.4</v>
       </c>
       <c r="F1384" t="n">
-        <v>10978.3</v>
+        <v>10927.5</v>
       </c>
       <c r="G1384" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H1384" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I1384" t="n">
         <v>5</v>
@@ -46121,7 +46121,7 @@
         </is>
       </c>
       <c r="B1385" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C1385" t="inlineStr">
         <is>
@@ -46129,19 +46129,19 @@
         </is>
       </c>
       <c r="D1385" t="n">
-        <v>58.9</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="E1385" t="n">
-        <v>1403.4</v>
+        <v>1353.7</v>
       </c>
       <c r="F1385" t="n">
-        <v>8938.4</v>
+        <v>8888.700000000001</v>
       </c>
       <c r="G1385" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H1385" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1385" t="n">
         <v>8</v>
@@ -46154,7 +46154,7 @@
         </is>
       </c>
       <c r="B1386" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C1386" t="inlineStr">
         <is>
@@ -46162,19 +46162,19 @@
         </is>
       </c>
       <c r="D1386" t="n">
-        <v>92</v>
+        <v>100.5</v>
       </c>
       <c r="E1386" t="n">
-        <v>1491.1</v>
+        <v>1405.6</v>
       </c>
       <c r="F1386" t="n">
-        <v>12202.2</v>
+        <v>12116.7</v>
       </c>
       <c r="G1386" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H1386" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I1386" t="n">
         <v>2</v>
@@ -46187,7 +46187,7 @@
         </is>
       </c>
       <c r="B1387" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C1387" t="inlineStr">
         <is>
@@ -46195,16 +46195,16 @@
         </is>
       </c>
       <c r="D1387" t="n">
-        <v>77.2</v>
+        <v>80.3</v>
       </c>
       <c r="E1387" t="n">
-        <v>1487</v>
+        <v>1409.8</v>
       </c>
       <c r="F1387" t="n">
-        <v>12178</v>
+        <v>12100.8</v>
       </c>
       <c r="G1387" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1387" t="n">
         <v>4</v>
@@ -46220,7 +46220,7 @@
         </is>
       </c>
       <c r="B1388" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C1388" t="inlineStr">
         <is>
@@ -46228,16 +46228,16 @@
         </is>
       </c>
       <c r="D1388" t="n">
-        <v>80.3</v>
+        <v>60.3</v>
       </c>
       <c r="E1388" t="n">
-        <v>1491.4</v>
+        <v>1425</v>
       </c>
       <c r="F1388" t="n">
-        <v>11356.5</v>
+        <v>11290.1</v>
       </c>
       <c r="G1388" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H1388" t="n">
         <v>2</v>
@@ -46253,7 +46253,7 @@
         </is>
       </c>
       <c r="B1389" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C1389" t="inlineStr">
         <is>
@@ -46261,16 +46261,16 @@
         </is>
       </c>
       <c r="D1389" t="n">
-        <v>50.6</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="E1389" t="n">
-        <v>1316.2</v>
+        <v>1265.6</v>
       </c>
       <c r="F1389" t="n">
-        <v>10980.8</v>
+        <v>10930.2</v>
       </c>
       <c r="G1389" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H1389" t="n">
         <v>7</v>
@@ -46286,7 +46286,7 @@
         </is>
       </c>
       <c r="B1390" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C1390" t="inlineStr">
         <is>
@@ -46294,16 +46294,16 @@
         </is>
       </c>
       <c r="D1390" t="n">
-        <v>76.7</v>
+        <v>70.2</v>
       </c>
       <c r="E1390" t="n">
-        <v>1570.3</v>
+        <v>1493.6</v>
       </c>
       <c r="F1390" t="n">
-        <v>12505.1</v>
+        <v>12428.4</v>
       </c>
       <c r="G1390" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1390" t="n">
         <v>1</v>
@@ -46319,7 +46319,7 @@
         </is>
       </c>
       <c r="B1391" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C1391" t="inlineStr">
         <is>
@@ -46327,16 +46327,16 @@
         </is>
       </c>
       <c r="D1391" t="n">
-        <v>48.7</v>
+        <v>61.2</v>
       </c>
       <c r="E1391" t="n">
-        <v>1249.1</v>
+        <v>1213</v>
       </c>
       <c r="F1391" t="n">
-        <v>10083</v>
+        <v>10046.9</v>
       </c>
       <c r="G1391" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H1391" t="n">
         <v>8</v>
@@ -46352,7 +46352,7 @@
         </is>
       </c>
       <c r="B1392" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C1392" t="inlineStr">
         <is>
@@ -46360,16 +46360,16 @@
         </is>
       </c>
       <c r="D1392" t="n">
-        <v>92.5</v>
+        <v>50.8</v>
       </c>
       <c r="E1392" t="n">
-        <v>1466.7</v>
+        <v>1374.2</v>
       </c>
       <c r="F1392" t="n">
-        <v>11070.8</v>
+        <v>10978.3</v>
       </c>
       <c r="G1392" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H1392" t="n">
         <v>6</v>
@@ -46385,7 +46385,7 @@
         </is>
       </c>
       <c r="B1393" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C1393" t="inlineStr">
         <is>
@@ -46393,19 +46393,19 @@
         </is>
       </c>
       <c r="D1393" t="n">
-        <v>73.10000000000001</v>
+        <v>58.9</v>
       </c>
       <c r="E1393" t="n">
-        <v>1476.5</v>
+        <v>1412.6</v>
       </c>
       <c r="F1393" t="n">
-        <v>9011.5</v>
+        <v>8947.6</v>
       </c>
       <c r="G1393" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H1393" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I1393" t="n">
         <v>8</v>
@@ -46418,7 +46418,7 @@
         </is>
       </c>
       <c r="B1394" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C1394" t="inlineStr">
         <is>
@@ -46426,16 +46426,16 @@
         </is>
       </c>
       <c r="D1394" t="n">
-        <v>75.59999999999999</v>
+        <v>92</v>
       </c>
       <c r="E1394" t="n">
-        <v>1566.7</v>
+        <v>1497.6</v>
       </c>
       <c r="F1394" t="n">
-        <v>12277.8</v>
+        <v>12208.7</v>
       </c>
       <c r="G1394" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1394" t="n">
         <v>3</v>
@@ -46451,7 +46451,7 @@
         </is>
       </c>
       <c r="B1395" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C1395" t="inlineStr">
         <is>
@@ -46459,19 +46459,19 @@
         </is>
       </c>
       <c r="D1395" t="n">
-        <v>84.09999999999999</v>
+        <v>77.2</v>
       </c>
       <c r="E1395" t="n">
-        <v>1571.1</v>
+        <v>1487</v>
       </c>
       <c r="F1395" t="n">
-        <v>12262.1</v>
+        <v>12178</v>
       </c>
       <c r="G1395" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H1395" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I1395" t="n">
         <v>3</v>
@@ -46484,7 +46484,7 @@
         </is>
       </c>
       <c r="B1396" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C1396" t="inlineStr">
         <is>
@@ -46492,19 +46492,19 @@
         </is>
       </c>
       <c r="D1396" t="n">
-        <v>59.3</v>
+        <v>80.3</v>
       </c>
       <c r="E1396" t="n">
-        <v>1550.7</v>
+        <v>1505.3</v>
       </c>
       <c r="F1396" t="n">
-        <v>11415.8</v>
+        <v>11370.4</v>
       </c>
       <c r="G1396" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H1396" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I1396" t="n">
         <v>4</v>
@@ -46517,7 +46517,7 @@
         </is>
       </c>
       <c r="B1397" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C1397" t="inlineStr">
         <is>
@@ -46525,16 +46525,16 @@
         </is>
       </c>
       <c r="D1397" t="n">
-        <v>71.5</v>
+        <v>50.6</v>
       </c>
       <c r="E1397" t="n">
-        <v>1387.7</v>
+        <v>1316.2</v>
       </c>
       <c r="F1397" t="n">
-        <v>11052.3</v>
+        <v>10980.8</v>
       </c>
       <c r="G1397" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H1397" t="n">
         <v>7</v>
@@ -46550,7 +46550,7 @@
         </is>
       </c>
       <c r="B1398" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C1398" t="inlineStr">
         <is>
@@ -46558,16 +46558,16 @@
         </is>
       </c>
       <c r="D1398" t="n">
-        <v>75.39999999999999</v>
+        <v>76.7</v>
       </c>
       <c r="E1398" t="n">
-        <v>1645.7</v>
+        <v>1570.3</v>
       </c>
       <c r="F1398" t="n">
-        <v>12580.5</v>
+        <v>12505.1</v>
       </c>
       <c r="G1398" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1398" t="n">
         <v>1</v>
@@ -46583,7 +46583,7 @@
         </is>
       </c>
       <c r="B1399" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C1399" t="inlineStr">
         <is>
@@ -46591,16 +46591,16 @@
         </is>
       </c>
       <c r="D1399" t="n">
-        <v>62.7</v>
+        <v>48.7</v>
       </c>
       <c r="E1399" t="n">
-        <v>1311.8</v>
+        <v>1261.7</v>
       </c>
       <c r="F1399" t="n">
-        <v>10145.7</v>
+        <v>10095.6</v>
       </c>
       <c r="G1399" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H1399" t="n">
         <v>8</v>
@@ -46616,7 +46616,7 @@
         </is>
       </c>
       <c r="B1400" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C1400" t="inlineStr">
         <is>
@@ -46624,16 +46624,16 @@
         </is>
       </c>
       <c r="D1400" t="n">
-        <v>72</v>
+        <v>92.5</v>
       </c>
       <c r="E1400" t="n">
-        <v>1538.7</v>
+        <v>1466.7</v>
       </c>
       <c r="F1400" t="n">
-        <v>11142.8</v>
+        <v>11070.8</v>
       </c>
       <c r="G1400" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H1400" t="n">
         <v>6</v>
@@ -46649,7 +46649,7 @@
         </is>
       </c>
       <c r="B1401" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C1401" t="inlineStr">
         <is>
@@ -46657,19 +46657,19 @@
         </is>
       </c>
       <c r="D1401" t="n">
-        <v>79.09999999999999</v>
+        <v>73.10000000000001</v>
       </c>
       <c r="E1401" t="n">
-        <v>1555.6</v>
+        <v>1485.7</v>
       </c>
       <c r="F1401" t="n">
-        <v>9090.6</v>
+        <v>9020.700000000001</v>
       </c>
       <c r="G1401" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H1401" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I1401" t="n">
         <v>8</v>
@@ -46682,7 +46682,7 @@
         </is>
       </c>
       <c r="B1402" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C1402" t="inlineStr">
         <is>
@@ -46690,16 +46690,16 @@
         </is>
       </c>
       <c r="D1402" t="n">
-        <v>73.2</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="E1402" t="n">
-        <v>1639.9</v>
+        <v>1573.2</v>
       </c>
       <c r="F1402" t="n">
-        <v>12351</v>
+        <v>12284.3</v>
       </c>
       <c r="G1402" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1402" t="n">
         <v>2</v>
@@ -46715,7 +46715,7 @@
         </is>
       </c>
       <c r="B1403" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C1403" t="inlineStr">
         <is>
@@ -46723,16 +46723,16 @@
         </is>
       </c>
       <c r="D1403" t="n">
-        <v>62.7</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="E1403" t="n">
-        <v>1633.8</v>
+        <v>1571.1</v>
       </c>
       <c r="F1403" t="n">
-        <v>12324.8</v>
+        <v>12262.1</v>
       </c>
       <c r="G1403" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H1403" t="n">
         <v>3</v>
@@ -46748,7 +46748,7 @@
         </is>
       </c>
       <c r="B1404" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C1404" t="inlineStr">
         <is>
@@ -46756,16 +46756,16 @@
         </is>
       </c>
       <c r="D1404" t="n">
-        <v>49.2</v>
+        <v>59.3</v>
       </c>
       <c r="E1404" t="n">
-        <v>1599.9</v>
+        <v>1564.6</v>
       </c>
       <c r="F1404" t="n">
-        <v>11465</v>
+        <v>11429.7</v>
       </c>
       <c r="G1404" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H1404" t="n">
         <v>5</v>
@@ -46781,7 +46781,7 @@
         </is>
       </c>
       <c r="B1405" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C1405" t="inlineStr">
         <is>
@@ -46789,16 +46789,16 @@
         </is>
       </c>
       <c r="D1405" t="n">
-        <v>43.9</v>
+        <v>71.5</v>
       </c>
       <c r="E1405" t="n">
-        <v>1431.6</v>
+        <v>1387.7</v>
       </c>
       <c r="F1405" t="n">
-        <v>11096.2</v>
+        <v>11052.3</v>
       </c>
       <c r="G1405" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H1405" t="n">
         <v>7</v>
@@ -46814,7 +46814,7 @@
         </is>
       </c>
       <c r="B1406" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C1406" t="inlineStr">
         <is>
@@ -46822,16 +46822,16 @@
         </is>
       </c>
       <c r="D1406" t="n">
-        <v>71.2</v>
+        <v>75.39999999999999</v>
       </c>
       <c r="E1406" t="n">
-        <v>1716.9</v>
+        <v>1645.7</v>
       </c>
       <c r="F1406" t="n">
-        <v>12651.7</v>
+        <v>12580.5</v>
       </c>
       <c r="G1406" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1406" t="n">
         <v>1</v>
@@ -46847,7 +46847,7 @@
         </is>
       </c>
       <c r="B1407" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C1407" t="inlineStr">
         <is>
@@ -46855,16 +46855,16 @@
         </is>
       </c>
       <c r="D1407" t="n">
-        <v>64.09999999999999</v>
+        <v>62.7</v>
       </c>
       <c r="E1407" t="n">
-        <v>1375.9</v>
+        <v>1324.4</v>
       </c>
       <c r="F1407" t="n">
-        <v>10209.8</v>
+        <v>10158.3</v>
       </c>
       <c r="G1407" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H1407" t="n">
         <v>8</v>
@@ -46880,7 +46880,7 @@
         </is>
       </c>
       <c r="B1408" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C1408" t="inlineStr">
         <is>
@@ -46888,16 +46888,16 @@
         </is>
       </c>
       <c r="D1408" t="n">
-        <v>42.9</v>
+        <v>72</v>
       </c>
       <c r="E1408" t="n">
-        <v>1581.6</v>
+        <v>1538.7</v>
       </c>
       <c r="F1408" t="n">
-        <v>11185.7</v>
+        <v>11142.8</v>
       </c>
       <c r="G1408" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H1408" t="n">
         <v>6</v>
@@ -46913,7 +46913,7 @@
         </is>
       </c>
       <c r="B1409" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C1409" t="inlineStr">
         <is>
@@ -46921,16 +46921,16 @@
         </is>
       </c>
       <c r="D1409" t="n">
-        <v>73.8</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="E1409" t="n">
-        <v>1629.4</v>
+        <v>1564.8</v>
       </c>
       <c r="F1409" t="n">
-        <v>9164.4</v>
+        <v>9099.799999999999</v>
       </c>
       <c r="G1409" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H1409" t="n">
         <v>4</v>
@@ -46946,7 +46946,7 @@
         </is>
       </c>
       <c r="B1410" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C1410" t="inlineStr">
         <is>
@@ -46954,16 +46954,16 @@
         </is>
       </c>
       <c r="D1410" t="n">
-        <v>79.3</v>
+        <v>73.2</v>
       </c>
       <c r="E1410" t="n">
-        <v>1719.2</v>
+        <v>1646.4</v>
       </c>
       <c r="F1410" t="n">
-        <v>12430.3</v>
+        <v>12357.5</v>
       </c>
       <c r="G1410" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H1410" t="n">
         <v>2</v>
@@ -46979,7 +46979,7 @@
         </is>
       </c>
       <c r="B1411" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C1411" t="inlineStr">
         <is>
@@ -46987,19 +46987,19 @@
         </is>
       </c>
       <c r="D1411" t="n">
-        <v>62.3</v>
+        <v>62.7</v>
       </c>
       <c r="E1411" t="n">
-        <v>1696.1</v>
+        <v>1633.8</v>
       </c>
       <c r="F1411" t="n">
-        <v>12387.1</v>
+        <v>12324.8</v>
       </c>
       <c r="G1411" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1411" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1411" t="n">
         <v>3</v>
@@ -47012,7 +47012,7 @@
         </is>
       </c>
       <c r="B1412" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C1412" t="inlineStr">
         <is>
@@ -47020,16 +47020,16 @@
         </is>
       </c>
       <c r="D1412" t="n">
-        <v>50.4</v>
+        <v>49.2</v>
       </c>
       <c r="E1412" t="n">
-        <v>1650.3</v>
+        <v>1613.8</v>
       </c>
       <c r="F1412" t="n">
-        <v>11515.4</v>
+        <v>11478.9</v>
       </c>
       <c r="G1412" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H1412" t="n">
         <v>5</v>
@@ -47045,7 +47045,7 @@
         </is>
       </c>
       <c r="B1413" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C1413" t="inlineStr">
         <is>
@@ -47053,16 +47053,16 @@
         </is>
       </c>
       <c r="D1413" t="n">
-        <v>48.8</v>
+        <v>43.9</v>
       </c>
       <c r="E1413" t="n">
-        <v>1480.4</v>
+        <v>1431.6</v>
       </c>
       <c r="F1413" t="n">
-        <v>11145</v>
+        <v>11096.2</v>
       </c>
       <c r="G1413" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H1413" t="n">
         <v>7</v>
@@ -47078,7 +47078,7 @@
         </is>
       </c>
       <c r="B1414" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C1414" t="inlineStr">
         <is>
@@ -47086,16 +47086,16 @@
         </is>
       </c>
       <c r="D1414" t="n">
-        <v>75</v>
+        <v>71.2</v>
       </c>
       <c r="E1414" t="n">
-        <v>1791.9</v>
+        <v>1716.9</v>
       </c>
       <c r="F1414" t="n">
-        <v>12726.7</v>
+        <v>12651.7</v>
       </c>
       <c r="G1414" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1414" t="n">
         <v>1</v>
@@ -47111,7 +47111,7 @@
         </is>
       </c>
       <c r="B1415" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C1415" t="inlineStr">
         <is>
@@ -47119,16 +47119,16 @@
         </is>
       </c>
       <c r="D1415" t="n">
-        <v>64.5</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="E1415" t="n">
-        <v>1440.4</v>
+        <v>1388.5</v>
       </c>
       <c r="F1415" t="n">
-        <v>10274.3</v>
+        <v>10222.4</v>
       </c>
       <c r="G1415" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1415" t="n">
         <v>8</v>
@@ -47144,7 +47144,7 @@
         </is>
       </c>
       <c r="B1416" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C1416" t="inlineStr">
         <is>
@@ -47152,16 +47152,16 @@
         </is>
       </c>
       <c r="D1416" t="n">
-        <v>59.7</v>
+        <v>42.9</v>
       </c>
       <c r="E1416" t="n">
-        <v>1641.3</v>
+        <v>1581.6</v>
       </c>
       <c r="F1416" t="n">
-        <v>11245.4</v>
+        <v>11185.7</v>
       </c>
       <c r="G1416" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H1416" t="n">
         <v>6</v>
@@ -47177,7 +47177,7 @@
         </is>
       </c>
       <c r="B1417" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C1417" t="inlineStr">
         <is>
@@ -47185,19 +47185,19 @@
         </is>
       </c>
       <c r="D1417" t="n">
-        <v>57.7</v>
+        <v>73.8</v>
       </c>
       <c r="E1417" t="n">
-        <v>1687.1</v>
+        <v>1638.6</v>
       </c>
       <c r="F1417" t="n">
-        <v>9222.1</v>
+        <v>9173.6</v>
       </c>
       <c r="G1417" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H1417" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1417" t="n">
         <v>8</v>
@@ -47210,7 +47210,7 @@
         </is>
       </c>
       <c r="B1418" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C1418" t="inlineStr">
         <is>
@@ -47218,16 +47218,16 @@
         </is>
       </c>
       <c r="D1418" t="n">
-        <v>86.3</v>
+        <v>79.3</v>
       </c>
       <c r="E1418" t="n">
-        <v>1805.5</v>
+        <v>1725.7</v>
       </c>
       <c r="F1418" t="n">
-        <v>12516.6</v>
+        <v>12436.8</v>
       </c>
       <c r="G1418" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H1418" t="n">
         <v>2</v>
@@ -47243,7 +47243,7 @@
         </is>
       </c>
       <c r="B1419" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C1419" t="inlineStr">
         <is>
@@ -47251,16 +47251,16 @@
         </is>
       </c>
       <c r="D1419" t="n">
-        <v>75.59999999999999</v>
+        <v>62.3</v>
       </c>
       <c r="E1419" t="n">
-        <v>1771.7</v>
+        <v>1696.1</v>
       </c>
       <c r="F1419" t="n">
-        <v>12462.7</v>
+        <v>12387.1</v>
       </c>
       <c r="G1419" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1419" t="n">
         <v>4</v>
@@ -47276,7 +47276,7 @@
         </is>
       </c>
       <c r="B1420" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C1420" t="inlineStr">
         <is>
@@ -47284,16 +47284,16 @@
         </is>
       </c>
       <c r="D1420" t="n">
-        <v>50.9</v>
+        <v>50.4</v>
       </c>
       <c r="E1420" t="n">
-        <v>1701.2</v>
+        <v>1664.2</v>
       </c>
       <c r="F1420" t="n">
-        <v>11566.3</v>
+        <v>11529.3</v>
       </c>
       <c r="G1420" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H1420" t="n">
         <v>5</v>
@@ -47309,7 +47309,7 @@
         </is>
       </c>
       <c r="B1421" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C1421" t="inlineStr">
         <is>
@@ -47317,16 +47317,16 @@
         </is>
       </c>
       <c r="D1421" t="n">
-        <v>65.3</v>
+        <v>48.8</v>
       </c>
       <c r="E1421" t="n">
-        <v>1545.7</v>
+        <v>1480.4</v>
       </c>
       <c r="F1421" t="n">
-        <v>11210.3</v>
+        <v>11145</v>
       </c>
       <c r="G1421" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H1421" t="n">
         <v>7</v>
@@ -47342,7 +47342,7 @@
         </is>
       </c>
       <c r="B1422" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C1422" t="inlineStr">
         <is>
@@ -47350,16 +47350,16 @@
         </is>
       </c>
       <c r="D1422" t="n">
-        <v>58.4</v>
+        <v>75</v>
       </c>
       <c r="E1422" t="n">
-        <v>1850.3</v>
+        <v>1791.9</v>
       </c>
       <c r="F1422" t="n">
-        <v>12785.1</v>
+        <v>12726.7</v>
       </c>
       <c r="G1422" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H1422" t="n">
         <v>1</v>
@@ -47375,7 +47375,7 @@
         </is>
       </c>
       <c r="B1423" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C1423" t="inlineStr">
         <is>
@@ -47383,16 +47383,16 @@
         </is>
       </c>
       <c r="D1423" t="n">
-        <v>58.6</v>
+        <v>64.5</v>
       </c>
       <c r="E1423" t="n">
-        <v>1499</v>
+        <v>1453</v>
       </c>
       <c r="F1423" t="n">
-        <v>10332.9</v>
+        <v>10286.9</v>
       </c>
       <c r="G1423" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1423" t="n">
         <v>8</v>
@@ -47408,7 +47408,7 @@
         </is>
       </c>
       <c r="B1424" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C1424" t="inlineStr">
         <is>
@@ -47416,16 +47416,16 @@
         </is>
       </c>
       <c r="D1424" t="n">
-        <v>55.3</v>
+        <v>59.7</v>
       </c>
       <c r="E1424" t="n">
-        <v>1696.6</v>
+        <v>1641.3</v>
       </c>
       <c r="F1424" t="n">
-        <v>11300.7</v>
+        <v>11245.4</v>
       </c>
       <c r="G1424" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H1424" t="n">
         <v>6</v>
@@ -47441,7 +47441,7 @@
         </is>
       </c>
       <c r="B1425" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C1425" t="inlineStr">
         <is>
@@ -47449,16 +47449,16 @@
         </is>
       </c>
       <c r="D1425" t="n">
-        <v>96</v>
+        <v>57.7</v>
       </c>
       <c r="E1425" t="n">
-        <v>1783.1</v>
+        <v>1696.3</v>
       </c>
       <c r="F1425" t="n">
-        <v>9318.1</v>
+        <v>9231.299999999999</v>
       </c>
       <c r="G1425" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H1425" t="n">
         <v>3</v>
@@ -47474,7 +47474,7 @@
         </is>
       </c>
       <c r="B1426" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C1426" t="inlineStr">
         <is>
@@ -47482,16 +47482,16 @@
         </is>
       </c>
       <c r="D1426" t="n">
-        <v>84.5</v>
+        <v>86.3</v>
       </c>
       <c r="E1426" t="n">
-        <v>1890</v>
+        <v>1812</v>
       </c>
       <c r="F1426" t="n">
-        <v>12601.1</v>
+        <v>12523.1</v>
       </c>
       <c r="G1426" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H1426" t="n">
         <v>2</v>
@@ -47507,7 +47507,7 @@
         </is>
       </c>
       <c r="B1427" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C1427" t="inlineStr">
         <is>
@@ -47515,16 +47515,16 @@
         </is>
       </c>
       <c r="D1427" t="n">
-        <v>66.59999999999999</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="E1427" t="n">
-        <v>1838.3</v>
+        <v>1771.7</v>
       </c>
       <c r="F1427" t="n">
-        <v>12529.3</v>
+        <v>12462.7</v>
       </c>
       <c r="G1427" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1427" t="n">
         <v>4</v>
@@ -47540,7 +47540,7 @@
         </is>
       </c>
       <c r="B1428" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C1428" t="inlineStr">
         <is>
@@ -47548,19 +47548,19 @@
         </is>
       </c>
       <c r="D1428" t="n">
-        <v>60.1</v>
+        <v>50.9</v>
       </c>
       <c r="E1428" t="n">
-        <v>1761.3</v>
+        <v>1715.1</v>
       </c>
       <c r="F1428" t="n">
-        <v>11626.4</v>
+        <v>11580.2</v>
       </c>
       <c r="G1428" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H1428" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I1428" t="n">
         <v>4</v>
@@ -47573,7 +47573,7 @@
         </is>
       </c>
       <c r="B1429" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C1429" t="inlineStr">
         <is>
@@ -47581,16 +47581,16 @@
         </is>
       </c>
       <c r="D1429" t="n">
-        <v>74.09999999999999</v>
+        <v>65.3</v>
       </c>
       <c r="E1429" t="n">
-        <v>1619.8</v>
+        <v>1545.7</v>
       </c>
       <c r="F1429" t="n">
-        <v>11284.4</v>
+        <v>11210.3</v>
       </c>
       <c r="G1429" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1429" t="n">
         <v>7</v>
@@ -47606,7 +47606,7 @@
         </is>
       </c>
       <c r="B1430" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C1430" t="inlineStr">
         <is>
@@ -47614,16 +47614,16 @@
         </is>
       </c>
       <c r="D1430" t="n">
-        <v>57.4</v>
+        <v>58.4</v>
       </c>
       <c r="E1430" t="n">
-        <v>1907.7</v>
+        <v>1850.3</v>
       </c>
       <c r="F1430" t="n">
-        <v>12842.5</v>
+        <v>12785.1</v>
       </c>
       <c r="G1430" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H1430" t="n">
         <v>1</v>
@@ -47639,7 +47639,7 @@
         </is>
       </c>
       <c r="B1431" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C1431" t="inlineStr">
         <is>
@@ -47647,16 +47647,16 @@
         </is>
       </c>
       <c r="D1431" t="n">
-        <v>0</v>
+        <v>58.6</v>
       </c>
       <c r="E1431" t="n">
-        <v>1499</v>
+        <v>1511.6</v>
       </c>
       <c r="F1431" t="n">
-        <v>10332.9</v>
+        <v>10345.5</v>
       </c>
       <c r="G1431" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H1431" t="n">
         <v>8</v>
@@ -47672,7 +47672,7 @@
         </is>
       </c>
       <c r="B1432" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C1432" t="inlineStr">
         <is>
@@ -47680,19 +47680,19 @@
         </is>
       </c>
       <c r="D1432" t="n">
-        <v>65.90000000000001</v>
+        <v>55.3</v>
       </c>
       <c r="E1432" t="n">
-        <v>1762.5</v>
+        <v>1696.6</v>
       </c>
       <c r="F1432" t="n">
-        <v>11366.6</v>
+        <v>11300.7</v>
       </c>
       <c r="G1432" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H1432" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I1432" t="n">
         <v>5</v>
@@ -47705,7 +47705,7 @@
         </is>
       </c>
       <c r="B1433" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C1433" t="inlineStr">
         <is>
@@ -47713,16 +47713,16 @@
         </is>
       </c>
       <c r="D1433" t="n">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="E1433" t="n">
-        <v>1859.1</v>
+        <v>1792.3</v>
       </c>
       <c r="F1433" t="n">
-        <v>9394.1</v>
+        <v>9327.299999999999</v>
       </c>
       <c r="G1433" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H1433" t="n">
         <v>3</v>
@@ -47738,7 +47738,7 @@
         </is>
       </c>
       <c r="B1434" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C1434" t="inlineStr">
         <is>
@@ -47746,16 +47746,16 @@
         </is>
       </c>
       <c r="D1434" t="n">
-        <v>73.09999999999999</v>
+        <v>84.5</v>
       </c>
       <c r="E1434" t="n">
-        <v>1963.1</v>
+        <v>1896.5</v>
       </c>
       <c r="F1434" t="n">
-        <v>12674.2</v>
+        <v>12607.6</v>
       </c>
       <c r="G1434" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H1434" t="n">
         <v>2</v>
@@ -47771,7 +47771,7 @@
         </is>
       </c>
       <c r="B1435" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C1435" t="inlineStr">
         <is>
@@ -47779,16 +47779,16 @@
         </is>
       </c>
       <c r="D1435" t="n">
-        <v>92.90000000000001</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="E1435" t="n">
-        <v>1931.2</v>
+        <v>1838.3</v>
       </c>
       <c r="F1435" t="n">
-        <v>12622.2</v>
+        <v>12529.3</v>
       </c>
       <c r="G1435" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1435" t="n">
         <v>4</v>
@@ -47804,7 +47804,7 @@
         </is>
       </c>
       <c r="B1436" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C1436" t="inlineStr">
         <is>
@@ -47812,19 +47812,19 @@
         </is>
       </c>
       <c r="D1436" t="n">
-        <v>51.6</v>
+        <v>60.1</v>
       </c>
       <c r="E1436" t="n">
-        <v>1812.9</v>
+        <v>1775.2</v>
       </c>
       <c r="F1436" t="n">
-        <v>11678</v>
+        <v>11640.3</v>
       </c>
       <c r="G1436" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H1436" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I1436" t="n">
         <v>4</v>
@@ -47837,7 +47837,7 @@
         </is>
       </c>
       <c r="B1437" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C1437" t="inlineStr">
         <is>
@@ -47845,16 +47845,16 @@
         </is>
       </c>
       <c r="D1437" t="n">
-        <v>62.1</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="E1437" t="n">
-        <v>1681.9</v>
+        <v>1619.8</v>
       </c>
       <c r="F1437" t="n">
-        <v>11346.5</v>
+        <v>11284.4</v>
       </c>
       <c r="G1437" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H1437" t="n">
         <v>7</v>
@@ -47870,7 +47870,7 @@
         </is>
       </c>
       <c r="B1438" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C1438" t="inlineStr">
         <is>
@@ -47878,16 +47878,16 @@
         </is>
       </c>
       <c r="D1438" t="n">
-        <v>86.7</v>
+        <v>57.4</v>
       </c>
       <c r="E1438" t="n">
-        <v>1994.4</v>
+        <v>1907.7</v>
       </c>
       <c r="F1438" t="n">
-        <v>12929.2</v>
+        <v>12842.5</v>
       </c>
       <c r="G1438" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H1438" t="n">
         <v>1</v>
@@ -47903,7 +47903,7 @@
         </is>
       </c>
       <c r="B1439" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C1439" t="inlineStr">
         <is>
@@ -47911,16 +47911,16 @@
         </is>
       </c>
       <c r="D1439" t="n">
-        <v>88.2</v>
+        <v>0</v>
       </c>
       <c r="E1439" t="n">
-        <v>1587.2</v>
+        <v>1511.6</v>
       </c>
       <c r="F1439" t="n">
-        <v>10421.1</v>
+        <v>10345.5</v>
       </c>
       <c r="G1439" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H1439" t="n">
         <v>8</v>
@@ -47936,7 +47936,7 @@
         </is>
       </c>
       <c r="B1440" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C1440" t="inlineStr">
         <is>
@@ -47944,19 +47944,19 @@
         </is>
       </c>
       <c r="D1440" t="n">
-        <v>73.3</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="E1440" t="n">
-        <v>1835.8</v>
+        <v>1762.5</v>
       </c>
       <c r="F1440" t="n">
-        <v>11439.9</v>
+        <v>11366.6</v>
       </c>
       <c r="G1440" t="n">
         <v>5</v>
       </c>
       <c r="H1440" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I1440" t="n">
         <v>5</v>
@@ -47969,7 +47969,7 @@
         </is>
       </c>
       <c r="B1441" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C1441" t="inlineStr">
         <is>
@@ -47977,16 +47977,16 @@
         </is>
       </c>
       <c r="D1441" t="n">
-        <v>100.9</v>
+        <v>76</v>
       </c>
       <c r="E1441" t="n">
-        <v>1960</v>
+        <v>1868.3</v>
       </c>
       <c r="F1441" t="n">
-        <v>9495</v>
+        <v>9403.299999999999</v>
       </c>
       <c r="G1441" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H1441" t="n">
         <v>3</v>
@@ -48002,7 +48002,7 @@
         </is>
       </c>
       <c r="B1442" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C1442" t="inlineStr">
         <is>
@@ -48010,19 +48010,19 @@
         </is>
       </c>
       <c r="D1442" t="n">
-        <v>82.5</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="E1442" t="n">
-        <v>2045.6</v>
+        <v>1969.6</v>
       </c>
       <c r="F1442" t="n">
-        <v>12756.7</v>
+        <v>12680.7</v>
       </c>
       <c r="G1442" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H1442" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1442" t="n">
         <v>2</v>
@@ -48035,7 +48035,7 @@
         </is>
       </c>
       <c r="B1443" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C1443" t="inlineStr">
         <is>
@@ -48043,19 +48043,19 @@
         </is>
       </c>
       <c r="D1443" t="n">
-        <v>73.5</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="E1443" t="n">
-        <v>2004.7</v>
+        <v>1931.2</v>
       </c>
       <c r="F1443" t="n">
-        <v>12695.7</v>
+        <v>12622.2</v>
       </c>
       <c r="G1443" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1443" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1443" t="n">
         <v>3</v>
@@ -48068,7 +48068,7 @@
         </is>
       </c>
       <c r="B1444" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C1444" t="inlineStr">
         <is>
@@ -48076,19 +48076,19 @@
         </is>
       </c>
       <c r="D1444" t="n">
-        <v>114.5</v>
+        <v>51.6</v>
       </c>
       <c r="E1444" t="n">
-        <v>1927.4</v>
+        <v>1826.8</v>
       </c>
       <c r="F1444" t="n">
-        <v>11792.5</v>
+        <v>11691.9</v>
       </c>
       <c r="G1444" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H1444" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I1444" t="n">
         <v>4</v>
@@ -48101,7 +48101,7 @@
         </is>
       </c>
       <c r="B1445" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C1445" t="inlineStr">
         <is>
@@ -48109,16 +48109,16 @@
         </is>
       </c>
       <c r="D1445" t="n">
-        <v>85.90000000000001</v>
+        <v>62.1</v>
       </c>
       <c r="E1445" t="n">
-        <v>1767.8</v>
+        <v>1681.9</v>
       </c>
       <c r="F1445" t="n">
-        <v>11432.4</v>
+        <v>11346.5</v>
       </c>
       <c r="G1445" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H1445" t="n">
         <v>7</v>
@@ -48134,7 +48134,7 @@
         </is>
       </c>
       <c r="B1446" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C1446" t="inlineStr">
         <is>
@@ -48142,19 +48142,19 @@
         </is>
       </c>
       <c r="D1446" t="n">
-        <v>48.6</v>
+        <v>86.7</v>
       </c>
       <c r="E1446" t="n">
-        <v>2043</v>
+        <v>1994.4</v>
       </c>
       <c r="F1446" t="n">
-        <v>12977.8</v>
+        <v>12929.2</v>
       </c>
       <c r="G1446" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H1446" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1446" t="n">
         <v>1</v>
@@ -48167,7 +48167,7 @@
         </is>
       </c>
       <c r="B1447" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C1447" t="inlineStr">
         <is>
@@ -48175,16 +48175,16 @@
         </is>
       </c>
       <c r="D1447" t="n">
-        <v>52.8</v>
+        <v>88.2</v>
       </c>
       <c r="E1447" t="n">
-        <v>1640</v>
+        <v>1599.8</v>
       </c>
       <c r="F1447" t="n">
-        <v>10473.9</v>
+        <v>10433.7</v>
       </c>
       <c r="G1447" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1447" t="n">
         <v>8</v>
@@ -48200,7 +48200,7 @@
         </is>
       </c>
       <c r="B1448" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C1448" t="inlineStr">
         <is>
@@ -48208,19 +48208,19 @@
         </is>
       </c>
       <c r="D1448" t="n">
-        <v>47.9</v>
+        <v>73.3</v>
       </c>
       <c r="E1448" t="n">
-        <v>1883.7</v>
+        <v>1835.8</v>
       </c>
       <c r="F1448" t="n">
-        <v>11487.8</v>
+        <v>11439.9</v>
       </c>
       <c r="G1448" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H1448" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I1448" t="n">
         <v>5</v>
@@ -48233,7 +48233,7 @@
         </is>
       </c>
       <c r="B1449" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C1449" t="inlineStr">
         <is>
@@ -48241,19 +48241,19 @@
         </is>
       </c>
       <c r="D1449" t="n">
-        <v>43.3</v>
+        <v>100.9</v>
       </c>
       <c r="E1449" t="n">
-        <v>2003.3</v>
+        <v>1969.2</v>
       </c>
       <c r="F1449" t="n">
-        <v>9538.299999999999</v>
+        <v>9504.200000000001</v>
       </c>
       <c r="G1449" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H1449" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1449" t="n">
         <v>8</v>
@@ -48266,7 +48266,7 @@
         </is>
       </c>
       <c r="B1450" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C1450" t="inlineStr">
         <is>
@@ -48274,19 +48274,19 @@
         </is>
       </c>
       <c r="D1450" t="n">
-        <v>66.5</v>
+        <v>82.5</v>
       </c>
       <c r="E1450" t="n">
-        <v>2112.1</v>
+        <v>2052.1</v>
       </c>
       <c r="F1450" t="n">
-        <v>12823.2</v>
+        <v>12763.2</v>
       </c>
       <c r="G1450" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1450" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1450" t="n">
         <v>2</v>
@@ -48299,7 +48299,7 @@
         </is>
       </c>
       <c r="B1451" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C1451" t="inlineStr">
         <is>
@@ -48307,16 +48307,16 @@
         </is>
       </c>
       <c r="D1451" t="n">
-        <v>65.5</v>
+        <v>73.5</v>
       </c>
       <c r="E1451" t="n">
-        <v>2070.2</v>
+        <v>2004.7</v>
       </c>
       <c r="F1451" t="n">
-        <v>12761.2</v>
+        <v>12695.7</v>
       </c>
       <c r="G1451" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H1451" t="n">
         <v>4</v>
@@ -48332,7 +48332,7 @@
         </is>
       </c>
       <c r="B1452" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C1452" t="inlineStr">
         <is>
@@ -48340,16 +48340,16 @@
         </is>
       </c>
       <c r="D1452" t="n">
-        <v>83.90000000000001</v>
+        <v>114.5</v>
       </c>
       <c r="E1452" t="n">
-        <v>2011.3</v>
+        <v>1941.3</v>
       </c>
       <c r="F1452" t="n">
-        <v>11876.4</v>
+        <v>11806.4</v>
       </c>
       <c r="G1452" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H1452" t="n">
         <v>5</v>
@@ -48365,7 +48365,7 @@
         </is>
       </c>
       <c r="B1453" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C1453" t="inlineStr">
         <is>
@@ -48373,16 +48373,16 @@
         </is>
       </c>
       <c r="D1453" t="n">
-        <v>66.40000000000001</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="E1453" t="n">
-        <v>1834.2</v>
+        <v>1767.8</v>
       </c>
       <c r="F1453" t="n">
-        <v>11498.8</v>
+        <v>11432.4</v>
       </c>
       <c r="G1453" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H1453" t="n">
         <v>7</v>
@@ -48398,7 +48398,7 @@
         </is>
       </c>
       <c r="B1454" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C1454" t="inlineStr">
         <is>
@@ -48406,19 +48406,19 @@
         </is>
       </c>
       <c r="D1454" t="n">
-        <v>107</v>
+        <v>48.6</v>
       </c>
       <c r="E1454" t="n">
-        <v>2150</v>
+        <v>2043</v>
       </c>
       <c r="F1454" t="n">
-        <v>13084.8</v>
+        <v>12977.8</v>
       </c>
       <c r="G1454" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H1454" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1454" t="n">
         <v>1</v>
@@ -48431,7 +48431,7 @@
         </is>
       </c>
       <c r="B1455" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C1455" t="inlineStr">
         <is>
@@ -48439,16 +48439,16 @@
         </is>
       </c>
       <c r="D1455" t="n">
-        <v>46.5</v>
+        <v>52.8</v>
       </c>
       <c r="E1455" t="n">
-        <v>1686.5</v>
+        <v>1652.6</v>
       </c>
       <c r="F1455" t="n">
-        <v>10520.4</v>
+        <v>10486.5</v>
       </c>
       <c r="G1455" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H1455" t="n">
         <v>8</v>
@@ -48464,7 +48464,7 @@
         </is>
       </c>
       <c r="B1456" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C1456" t="inlineStr">
         <is>
@@ -48472,16 +48472,16 @@
         </is>
       </c>
       <c r="D1456" t="n">
-        <v>67.40000000000001</v>
+        <v>47.9</v>
       </c>
       <c r="E1456" t="n">
-        <v>1951.1</v>
+        <v>1883.7</v>
       </c>
       <c r="F1456" t="n">
-        <v>11555.2</v>
+        <v>11487.8</v>
       </c>
       <c r="G1456" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H1456" t="n">
         <v>6</v>
@@ -48497,7 +48497,7 @@
         </is>
       </c>
       <c r="B1457" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C1457" t="inlineStr">
         <is>
@@ -48505,16 +48505,16 @@
         </is>
       </c>
       <c r="D1457" t="n">
-        <v>85.59999999999999</v>
+        <v>43.3</v>
       </c>
       <c r="E1457" t="n">
-        <v>2088.9</v>
+        <v>2012.5</v>
       </c>
       <c r="F1457" t="n">
-        <v>9623.9</v>
+        <v>9547.5</v>
       </c>
       <c r="G1457" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H1457" t="n">
         <v>3</v>
@@ -48530,7 +48530,7 @@
         </is>
       </c>
       <c r="B1458" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C1458" t="inlineStr">
         <is>
@@ -48538,16 +48538,16 @@
         </is>
       </c>
       <c r="D1458" t="n">
-        <v>100.6</v>
+        <v>66.5</v>
       </c>
       <c r="E1458" t="n">
-        <v>2212.7</v>
+        <v>2118.6</v>
       </c>
       <c r="F1458" t="n">
-        <v>12923.8</v>
+        <v>12829.7</v>
       </c>
       <c r="G1458" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H1458" t="n">
         <v>2</v>
@@ -48563,7 +48563,7 @@
         </is>
       </c>
       <c r="B1459" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C1459" t="inlineStr">
         <is>
@@ -48571,16 +48571,16 @@
         </is>
       </c>
       <c r="D1459" t="n">
-        <v>65.90000000000001</v>
+        <v>65.5</v>
       </c>
       <c r="E1459" t="n">
-        <v>2136.1</v>
+        <v>2070.2</v>
       </c>
       <c r="F1459" t="n">
-        <v>12827.1</v>
+        <v>12761.2</v>
       </c>
       <c r="G1459" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H1459" t="n">
         <v>4</v>
@@ -48596,7 +48596,7 @@
         </is>
       </c>
       <c r="B1460" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C1460" t="inlineStr">
         <is>
@@ -48604,16 +48604,16 @@
         </is>
       </c>
       <c r="D1460" t="n">
-        <v>70.8</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="E1460" t="n">
-        <v>2082.1</v>
+        <v>2025.2</v>
       </c>
       <c r="F1460" t="n">
-        <v>11947.2</v>
+        <v>11890.3</v>
       </c>
       <c r="G1460" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1460" t="n">
         <v>5</v>
@@ -48629,7 +48629,7 @@
         </is>
       </c>
       <c r="B1461" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C1461" t="inlineStr">
         <is>
@@ -48637,16 +48637,16 @@
         </is>
       </c>
       <c r="D1461" t="n">
-        <v>60.5</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="E1461" t="n">
-        <v>1894.7</v>
+        <v>1834.2</v>
       </c>
       <c r="F1461" t="n">
-        <v>11559.3</v>
+        <v>11498.8</v>
       </c>
       <c r="G1461" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H1461" t="n">
         <v>7</v>
@@ -48662,7 +48662,7 @@
         </is>
       </c>
       <c r="B1462" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C1462" t="inlineStr">
         <is>
@@ -48670,16 +48670,16 @@
         </is>
       </c>
       <c r="D1462" t="n">
-        <v>64.59999999999999</v>
+        <v>107</v>
       </c>
       <c r="E1462" t="n">
-        <v>2214.6</v>
+        <v>2150</v>
       </c>
       <c r="F1462" t="n">
-        <v>13149.4</v>
+        <v>13084.8</v>
       </c>
       <c r="G1462" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H1462" t="n">
         <v>1</v>
@@ -48695,7 +48695,7 @@
         </is>
       </c>
       <c r="B1463" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C1463" t="inlineStr">
         <is>
@@ -48703,16 +48703,16 @@
         </is>
       </c>
       <c r="D1463" t="n">
-        <v>73.7</v>
+        <v>46.5</v>
       </c>
       <c r="E1463" t="n">
-        <v>1760.2</v>
+        <v>1699.1</v>
       </c>
       <c r="F1463" t="n">
-        <v>10594.1</v>
+        <v>10533</v>
       </c>
       <c r="G1463" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H1463" t="n">
         <v>8</v>
@@ -48728,7 +48728,7 @@
         </is>
       </c>
       <c r="B1464" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C1464" t="inlineStr">
         <is>
@@ -48736,16 +48736,16 @@
         </is>
       </c>
       <c r="D1464" t="n">
-        <v>55.2</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="E1464" t="n">
-        <v>2006.3</v>
+        <v>1951.1</v>
       </c>
       <c r="F1464" t="n">
-        <v>11610.4</v>
+        <v>11555.2</v>
       </c>
       <c r="G1464" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H1464" t="n">
         <v>6</v>
@@ -48761,7 +48761,7 @@
         </is>
       </c>
       <c r="B1465" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C1465" t="inlineStr">
         <is>
@@ -48769,13 +48769,13 @@
         </is>
       </c>
       <c r="D1465" t="n">
-        <v>88</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="E1465" t="n">
-        <v>2176.9</v>
+        <v>2098.1</v>
       </c>
       <c r="F1465" t="n">
-        <v>9711.9</v>
+        <v>9633.1</v>
       </c>
       <c r="G1465" t="n">
         <v>2</v>
@@ -48794,7 +48794,7 @@
         </is>
       </c>
       <c r="B1466" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C1466" t="inlineStr">
         <is>
@@ -48802,16 +48802,16 @@
         </is>
       </c>
       <c r="D1466" t="n">
-        <v>70.09999999999999</v>
+        <v>100.6</v>
       </c>
       <c r="E1466" t="n">
-        <v>2282.8</v>
+        <v>2219.2</v>
       </c>
       <c r="F1466" t="n">
-        <v>12993.9</v>
+        <v>12930.3</v>
       </c>
       <c r="G1466" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H1466" t="n">
         <v>1</v>
@@ -48827,7 +48827,7 @@
         </is>
       </c>
       <c r="B1467" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C1467" t="inlineStr">
         <is>
@@ -48835,16 +48835,16 @@
         </is>
       </c>
       <c r="D1467" t="n">
-        <v>77.90000000000001</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="E1467" t="n">
-        <v>2214</v>
+        <v>2136.1</v>
       </c>
       <c r="F1467" t="n">
-        <v>12905</v>
+        <v>12827.1</v>
       </c>
       <c r="G1467" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1467" t="n">
         <v>4</v>
@@ -48860,7 +48860,7 @@
         </is>
       </c>
       <c r="B1468" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C1468" t="inlineStr">
         <is>
@@ -48868,16 +48868,16 @@
         </is>
       </c>
       <c r="D1468" t="n">
-        <v>80.8</v>
+        <v>70.8</v>
       </c>
       <c r="E1468" t="n">
-        <v>2162.9</v>
+        <v>2096</v>
       </c>
       <c r="F1468" t="n">
-        <v>12028</v>
+        <v>11961.1</v>
       </c>
       <c r="G1468" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1468" t="n">
         <v>5</v>
@@ -48893,7 +48893,7 @@
         </is>
       </c>
       <c r="B1469" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C1469" t="inlineStr">
         <is>
@@ -48901,13 +48901,13 @@
         </is>
       </c>
       <c r="D1469" t="n">
-        <v>53</v>
+        <v>60.5</v>
       </c>
       <c r="E1469" t="n">
-        <v>1947.7</v>
+        <v>1894.7</v>
       </c>
       <c r="F1469" t="n">
-        <v>11612.3</v>
+        <v>11559.3</v>
       </c>
       <c r="G1469" t="n">
         <v>7</v>
@@ -48926,7 +48926,7 @@
         </is>
       </c>
       <c r="B1470" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C1470" t="inlineStr">
         <is>
@@ -48934,19 +48934,19 @@
         </is>
       </c>
       <c r="D1470" t="n">
-        <v>59.8</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="E1470" t="n">
-        <v>2274.4</v>
+        <v>2214.6</v>
       </c>
       <c r="F1470" t="n">
-        <v>13209.2</v>
+        <v>13149.4</v>
       </c>
       <c r="G1470" t="n">
         <v>6</v>
       </c>
       <c r="H1470" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I1470" t="n">
         <v>1</v>
@@ -48959,7 +48959,7 @@
         </is>
       </c>
       <c r="B1471" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C1471" t="inlineStr">
         <is>
@@ -48967,16 +48967,16 @@
         </is>
       </c>
       <c r="D1471" t="n">
-        <v>68.39999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="E1471" t="n">
-        <v>1828.6</v>
+        <v>1772.8</v>
       </c>
       <c r="F1471" t="n">
-        <v>10662.5</v>
+        <v>10606.7</v>
       </c>
       <c r="G1471" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1471" t="n">
         <v>8</v>
@@ -48992,7 +48992,7 @@
         </is>
       </c>
       <c r="B1472" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C1472" t="inlineStr">
         <is>
@@ -49000,13 +49000,13 @@
         </is>
       </c>
       <c r="D1472" t="n">
-        <v>48.4</v>
+        <v>55.2</v>
       </c>
       <c r="E1472" t="n">
-        <v>2054.7</v>
+        <v>2006.3</v>
       </c>
       <c r="F1472" t="n">
-        <v>11658.8</v>
+        <v>11610.4</v>
       </c>
       <c r="G1472" t="n">
         <v>8</v>
@@ -49025,7 +49025,7 @@
         </is>
       </c>
       <c r="B1473" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C1473" t="inlineStr">
         <is>
@@ -49033,19 +49033,19 @@
         </is>
       </c>
       <c r="D1473" t="n">
-        <v>104.8</v>
+        <v>88</v>
       </c>
       <c r="E1473" t="n">
-        <v>2281.7</v>
+        <v>2186.1</v>
       </c>
       <c r="F1473" t="n">
-        <v>9816.700000000001</v>
+        <v>9721.1</v>
       </c>
       <c r="G1473" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H1473" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I1473" t="n">
         <v>8</v>
@@ -49058,7 +49058,7 @@
         </is>
       </c>
       <c r="B1474" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C1474" t="inlineStr">
         <is>
@@ -49066,16 +49066,16 @@
         </is>
       </c>
       <c r="D1474" t="n">
-        <v>76.3</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="E1474" t="n">
-        <v>2359.1</v>
+        <v>2289.3</v>
       </c>
       <c r="F1474" t="n">
-        <v>13070.2</v>
+        <v>13000.4</v>
       </c>
       <c r="G1474" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1474" t="n">
         <v>2</v>
@@ -49091,7 +49091,7 @@
         </is>
       </c>
       <c r="B1475" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C1475" t="inlineStr">
         <is>
@@ -49099,16 +49099,16 @@
         </is>
       </c>
       <c r="D1475" t="n">
-        <v>73.3</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="E1475" t="n">
-        <v>2287.3</v>
+        <v>2214</v>
       </c>
       <c r="F1475" t="n">
-        <v>12978.3</v>
+        <v>12905</v>
       </c>
       <c r="G1475" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1475" t="n">
         <v>4</v>
@@ -49124,7 +49124,7 @@
         </is>
       </c>
       <c r="B1476" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C1476" t="inlineStr">
         <is>
@@ -49132,16 +49132,16 @@
         </is>
       </c>
       <c r="D1476" t="n">
-        <v>56.5</v>
+        <v>80.8</v>
       </c>
       <c r="E1476" t="n">
-        <v>2219.4</v>
+        <v>2176.8</v>
       </c>
       <c r="F1476" t="n">
-        <v>12084.5</v>
+        <v>12041.9</v>
       </c>
       <c r="G1476" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H1476" t="n">
         <v>5</v>
@@ -49157,7 +49157,7 @@
         </is>
       </c>
       <c r="B1477" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C1477" t="inlineStr">
         <is>
@@ -49165,16 +49165,16 @@
         </is>
       </c>
       <c r="D1477" t="n">
-        <v>75.09999999999999</v>
+        <v>53</v>
       </c>
       <c r="E1477" t="n">
-        <v>2022.8</v>
+        <v>1947.7</v>
       </c>
       <c r="F1477" t="n">
-        <v>11687.4</v>
+        <v>11612.3</v>
       </c>
       <c r="G1477" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H1477" t="n">
         <v>7</v>
@@ -49190,7 +49190,7 @@
         </is>
       </c>
       <c r="B1478" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C1478" t="inlineStr">
         <is>
@@ -49198,13 +49198,13 @@
         </is>
       </c>
       <c r="D1478" t="n">
-        <v>69.7</v>
+        <v>59.8</v>
       </c>
       <c r="E1478" t="n">
-        <v>2344.1</v>
+        <v>2274.4</v>
       </c>
       <c r="F1478" t="n">
-        <v>13278.9</v>
+        <v>13209.2</v>
       </c>
       <c r="G1478" t="n">
         <v>6</v>
@@ -49223,7 +49223,7 @@
         </is>
       </c>
       <c r="B1479" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C1479" t="inlineStr">
         <is>
@@ -49231,16 +49231,16 @@
         </is>
       </c>
       <c r="D1479" t="n">
-        <v>80.09999999999999</v>
+        <v>68.39999999999999</v>
       </c>
       <c r="E1479" t="n">
-        <v>1908.7</v>
+        <v>1841.2</v>
       </c>
       <c r="F1479" t="n">
-        <v>10742.6</v>
+        <v>10675.1</v>
       </c>
       <c r="G1479" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H1479" t="n">
         <v>8</v>
@@ -49256,7 +49256,7 @@
         </is>
       </c>
       <c r="B1480" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C1480" t="inlineStr">
         <is>
@@ -49264,13 +49264,13 @@
         </is>
       </c>
       <c r="D1480" t="n">
-        <v>44.90000000000001</v>
+        <v>48.4</v>
       </c>
       <c r="E1480" t="n">
-        <v>2099.6</v>
+        <v>2054.7</v>
       </c>
       <c r="F1480" t="n">
-        <v>11703.7</v>
+        <v>11658.8</v>
       </c>
       <c r="G1480" t="n">
         <v>8</v>
@@ -49289,7 +49289,7 @@
         </is>
       </c>
       <c r="B1481" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C1481" t="inlineStr">
         <is>
@@ -49297,13 +49297,13 @@
         </is>
       </c>
       <c r="D1481" t="n">
-        <v>82.40000000000001</v>
+        <v>104.8</v>
       </c>
       <c r="E1481" t="n">
-        <v>2364.1</v>
+        <v>2290.9</v>
       </c>
       <c r="F1481" t="n">
-        <v>9899.1</v>
+        <v>9825.9</v>
       </c>
       <c r="G1481" t="n">
         <v>1</v>
@@ -49322,7 +49322,7 @@
         </is>
       </c>
       <c r="B1482" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C1482" t="inlineStr">
         <is>
@@ -49330,13 +49330,13 @@
         </is>
       </c>
       <c r="D1482" t="n">
-        <v>94.09999999999999</v>
+        <v>76.3</v>
       </c>
       <c r="E1482" t="n">
-        <v>2453.2</v>
+        <v>2365.6</v>
       </c>
       <c r="F1482" t="n">
-        <v>13164.3</v>
+        <v>13076.7</v>
       </c>
       <c r="G1482" t="n">
         <v>3</v>
@@ -49355,7 +49355,7 @@
         </is>
       </c>
       <c r="B1483" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C1483" t="inlineStr">
         <is>
@@ -49363,16 +49363,16 @@
         </is>
       </c>
       <c r="D1483" t="n">
-        <v>94.90000000000001</v>
+        <v>73.3</v>
       </c>
       <c r="E1483" t="n">
-        <v>2382.2</v>
+        <v>2287.3</v>
       </c>
       <c r="F1483" t="n">
-        <v>13073.2</v>
+        <v>12978.3</v>
       </c>
       <c r="G1483" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H1483" t="n">
         <v>4</v>
@@ -49388,7 +49388,7 @@
         </is>
       </c>
       <c r="B1484" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C1484" t="inlineStr">
         <is>
@@ -49396,16 +49396,16 @@
         </is>
       </c>
       <c r="D1484" t="n">
-        <v>75.2</v>
+        <v>56.5</v>
       </c>
       <c r="E1484" t="n">
-        <v>2294.6</v>
+        <v>2233.3</v>
       </c>
       <c r="F1484" t="n">
-        <v>12159.7</v>
+        <v>12098.4</v>
       </c>
       <c r="G1484" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H1484" t="n">
         <v>5</v>
@@ -49421,7 +49421,7 @@
         </is>
       </c>
       <c r="B1485" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C1485" t="inlineStr">
         <is>
@@ -49429,16 +49429,16 @@
         </is>
       </c>
       <c r="D1485" t="n">
-        <v>38.3</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="E1485" t="n">
-        <v>2061.1</v>
+        <v>2022.8</v>
       </c>
       <c r="F1485" t="n">
-        <v>11725.7</v>
+        <v>11687.4</v>
       </c>
       <c r="G1485" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H1485" t="n">
         <v>7</v>
@@ -49454,7 +49454,7 @@
         </is>
       </c>
       <c r="B1486" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C1486" t="inlineStr">
         <is>
@@ -49462,13 +49462,13 @@
         </is>
       </c>
       <c r="D1486" t="n">
-        <v>52.9</v>
+        <v>69.7</v>
       </c>
       <c r="E1486" t="n">
-        <v>2397</v>
+        <v>2344.1</v>
       </c>
       <c r="F1486" t="n">
-        <v>13331.8</v>
+        <v>13278.9</v>
       </c>
       <c r="G1486" t="n">
         <v>6</v>
@@ -49487,7 +49487,7 @@
         </is>
       </c>
       <c r="B1487" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C1487" t="inlineStr">
         <is>
@@ -49495,16 +49495,16 @@
         </is>
       </c>
       <c r="D1487" t="n">
-        <v>78.7</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="E1487" t="n">
-        <v>1987.4</v>
+        <v>1921.3</v>
       </c>
       <c r="F1487" t="n">
-        <v>10821.3</v>
+        <v>10755.2</v>
       </c>
       <c r="G1487" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1487" t="n">
         <v>8</v>
@@ -49520,7 +49520,7 @@
         </is>
       </c>
       <c r="B1488" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C1488" t="inlineStr">
         <is>
@@ -49528,16 +49528,16 @@
         </is>
       </c>
       <c r="D1488" t="n">
-        <v>44.4</v>
+        <v>44.90000000000001</v>
       </c>
       <c r="E1488" t="n">
-        <v>2144</v>
+        <v>2099.6</v>
       </c>
       <c r="F1488" t="n">
-        <v>11748.1</v>
+        <v>11703.7</v>
       </c>
       <c r="G1488" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H1488" t="n">
         <v>6</v>
@@ -49553,7 +49553,7 @@
         </is>
       </c>
       <c r="B1489" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C1489" t="inlineStr">
         <is>
@@ -49561,13 +49561,13 @@
         </is>
       </c>
       <c r="D1489" t="n">
-        <v>95.3</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="E1489" t="n">
-        <v>2459.4</v>
+        <v>2373.3</v>
       </c>
       <c r="F1489" t="n">
-        <v>9994.4</v>
+        <v>9908.299999999999</v>
       </c>
       <c r="G1489" t="n">
         <v>1</v>
@@ -49586,7 +49586,7 @@
         </is>
       </c>
       <c r="B1490" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C1490" t="inlineStr">
         <is>
@@ -49594,16 +49594,16 @@
         </is>
       </c>
       <c r="D1490" t="n">
-        <v>72.8</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="E1490" t="n">
-        <v>2526</v>
+        <v>2459.7</v>
       </c>
       <c r="F1490" t="n">
-        <v>13237.1</v>
+        <v>13170.8</v>
       </c>
       <c r="G1490" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1490" t="n">
         <v>2</v>
@@ -49619,7 +49619,7 @@
         </is>
       </c>
       <c r="B1491" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C1491" t="inlineStr">
         <is>
@@ -49627,16 +49627,16 @@
         </is>
       </c>
       <c r="D1491" t="n">
-        <v>42</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="E1491" t="n">
-        <v>2424.2</v>
+        <v>2382.2</v>
       </c>
       <c r="F1491" t="n">
-        <v>13115.2</v>
+        <v>13073.2</v>
       </c>
       <c r="G1491" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H1491" t="n">
         <v>4</v>
@@ -49652,7 +49652,7 @@
         </is>
       </c>
       <c r="B1492" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C1492" t="inlineStr">
         <is>
@@ -49660,13 +49660,13 @@
         </is>
       </c>
       <c r="D1492" t="n">
-        <v>65.10000000000001</v>
+        <v>75.2</v>
       </c>
       <c r="E1492" t="n">
-        <v>2359.7</v>
+        <v>2308.5</v>
       </c>
       <c r="F1492" t="n">
-        <v>12224.8</v>
+        <v>12173.6</v>
       </c>
       <c r="G1492" t="n">
         <v>5</v>
@@ -49685,7 +49685,7 @@
         </is>
       </c>
       <c r="B1493" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C1493" t="inlineStr">
         <is>
@@ -49693,13 +49693,13 @@
         </is>
       </c>
       <c r="D1493" t="n">
-        <v>39.8</v>
+        <v>38.3</v>
       </c>
       <c r="E1493" t="n">
-        <v>2100.9</v>
+        <v>2061.1</v>
       </c>
       <c r="F1493" t="n">
-        <v>11765.5</v>
+        <v>11725.7</v>
       </c>
       <c r="G1493" t="n">
         <v>8</v>
@@ -49718,7 +49718,7 @@
         </is>
       </c>
       <c r="B1494" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C1494" t="inlineStr">
         <is>
@@ -49726,16 +49726,16 @@
         </is>
       </c>
       <c r="D1494" t="n">
-        <v>65.8</v>
+        <v>52.9</v>
       </c>
       <c r="E1494" t="n">
-        <v>2462.8</v>
+        <v>2397</v>
       </c>
       <c r="F1494" t="n">
-        <v>13397.6</v>
+        <v>13331.8</v>
       </c>
       <c r="G1494" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1494" t="n">
         <v>3</v>
@@ -49751,7 +49751,7 @@
         </is>
       </c>
       <c r="B1495" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C1495" t="inlineStr">
         <is>
@@ -49759,16 +49759,16 @@
         </is>
       </c>
       <c r="D1495" t="n">
-        <v>66.40000000000001</v>
+        <v>78.7</v>
       </c>
       <c r="E1495" t="n">
-        <v>2053.8</v>
+        <v>2000</v>
       </c>
       <c r="F1495" t="n">
-        <v>10887.7</v>
+        <v>10833.9</v>
       </c>
       <c r="G1495" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1495" t="n">
         <v>8</v>
@@ -49784,7 +49784,7 @@
         </is>
       </c>
       <c r="B1496" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C1496" t="inlineStr">
         <is>
@@ -49792,16 +49792,16 @@
         </is>
       </c>
       <c r="D1496" t="n">
-        <v>52.7</v>
+        <v>44.4</v>
       </c>
       <c r="E1496" t="n">
-        <v>2196.7</v>
+        <v>2144</v>
       </c>
       <c r="F1496" t="n">
-        <v>11800.8</v>
+        <v>11748.1</v>
       </c>
       <c r="G1496" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H1496" t="n">
         <v>6</v>
@@ -49817,7 +49817,7 @@
         </is>
       </c>
       <c r="B1497" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C1497" t="inlineStr">
         <is>
@@ -49825,13 +49825,13 @@
         </is>
       </c>
       <c r="D1497" t="n">
-        <v>81.3</v>
+        <v>95.3</v>
       </c>
       <c r="E1497" t="n">
-        <v>2540.7</v>
+        <v>2468.6</v>
       </c>
       <c r="F1497" t="n">
-        <v>10075.7</v>
+        <v>10003.6</v>
       </c>
       <c r="G1497" t="n">
         <v>1</v>
@@ -49850,7 +49850,7 @@
         </is>
       </c>
       <c r="B1498" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C1498" t="inlineStr">
         <is>
@@ -49858,16 +49858,16 @@
         </is>
       </c>
       <c r="D1498" t="n">
-        <v>70.59999999999999</v>
+        <v>72.8</v>
       </c>
       <c r="E1498" t="n">
-        <v>2596.6</v>
+        <v>2532.5</v>
       </c>
       <c r="F1498" t="n">
-        <v>13307.7</v>
+        <v>13243.6</v>
       </c>
       <c r="G1498" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1498" t="n">
         <v>2</v>
@@ -49883,7 +49883,7 @@
         </is>
       </c>
       <c r="B1499" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C1499" t="inlineStr">
         <is>
@@ -49891,16 +49891,16 @@
         </is>
       </c>
       <c r="D1499" t="n">
-        <v>76.40000000000001</v>
+        <v>42</v>
       </c>
       <c r="E1499" t="n">
-        <v>2500.6</v>
+        <v>2424.2</v>
       </c>
       <c r="F1499" t="n">
-        <v>13191.6</v>
+        <v>13115.2</v>
       </c>
       <c r="G1499" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H1499" t="n">
         <v>4</v>
@@ -49916,7 +49916,7 @@
         </is>
       </c>
       <c r="B1500" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C1500" t="inlineStr">
         <is>
@@ -49924,16 +49924,16 @@
         </is>
       </c>
       <c r="D1500" t="n">
-        <v>60.3</v>
+        <v>65.10000000000001</v>
       </c>
       <c r="E1500" t="n">
-        <v>2420</v>
+        <v>2373.6</v>
       </c>
       <c r="F1500" t="n">
-        <v>12285.1</v>
+        <v>12238.7</v>
       </c>
       <c r="G1500" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H1500" t="n">
         <v>5</v>
@@ -49949,7 +49949,7 @@
         </is>
       </c>
       <c r="B1501" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C1501" t="inlineStr">
         <is>
@@ -49957,16 +49957,16 @@
         </is>
       </c>
       <c r="D1501" t="n">
-        <v>60.4</v>
+        <v>39.8</v>
       </c>
       <c r="E1501" t="n">
-        <v>2161.3</v>
+        <v>2100.9</v>
       </c>
       <c r="F1501" t="n">
-        <v>11825.9</v>
+        <v>11765.5</v>
       </c>
       <c r="G1501" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H1501" t="n">
         <v>7</v>
@@ -49982,7 +49982,7 @@
         </is>
       </c>
       <c r="B1502" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C1502" t="inlineStr">
         <is>
@@ -49990,16 +49990,16 @@
         </is>
       </c>
       <c r="D1502" t="n">
-        <v>53.9</v>
+        <v>65.8</v>
       </c>
       <c r="E1502" t="n">
-        <v>2516.7</v>
+        <v>2462.8</v>
       </c>
       <c r="F1502" t="n">
-        <v>13451.5</v>
+        <v>13397.6</v>
       </c>
       <c r="G1502" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H1502" t="n">
         <v>3</v>
@@ -50015,7 +50015,7 @@
         </is>
       </c>
       <c r="B1503" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C1503" t="inlineStr">
         <is>
@@ -50023,13 +50023,13 @@
         </is>
       </c>
       <c r="D1503" t="n">
-        <v>75.80000000000001</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="E1503" t="n">
-        <v>2129.6</v>
+        <v>2066.4</v>
       </c>
       <c r="F1503" t="n">
-        <v>10963.5</v>
+        <v>10900.3</v>
       </c>
       <c r="G1503" t="n">
         <v>3</v>
@@ -50048,7 +50048,7 @@
         </is>
       </c>
       <c r="B1504" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C1504" t="inlineStr">
         <is>
@@ -50056,16 +50056,16 @@
         </is>
       </c>
       <c r="D1504" t="n">
-        <v>53.2</v>
+        <v>52.7</v>
       </c>
       <c r="E1504" t="n">
-        <v>2249.9</v>
+        <v>2196.7</v>
       </c>
       <c r="F1504" t="n">
-        <v>11854</v>
+        <v>11800.8</v>
       </c>
       <c r="G1504" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H1504" t="n">
         <v>6</v>
@@ -50081,7 +50081,7 @@
         </is>
       </c>
       <c r="B1505" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C1505" t="inlineStr">
         <is>
@@ -50089,13 +50089,13 @@
         </is>
       </c>
       <c r="D1505" t="n">
-        <v>87.59999999999999</v>
+        <v>81.3</v>
       </c>
       <c r="E1505" t="n">
-        <v>2628.3</v>
+        <v>2549.9</v>
       </c>
       <c r="F1505" t="n">
-        <v>10163.3</v>
+        <v>10084.9</v>
       </c>
       <c r="G1505" t="n">
         <v>1</v>
@@ -50114,7 +50114,7 @@
         </is>
       </c>
       <c r="B1506" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C1506" t="inlineStr">
         <is>
@@ -50122,13 +50122,13 @@
         </is>
       </c>
       <c r="D1506" t="n">
-        <v>58.2</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="E1506" t="n">
-        <v>2654.8</v>
+        <v>2603.1</v>
       </c>
       <c r="F1506" t="n">
-        <v>13365.9</v>
+        <v>13314.2</v>
       </c>
       <c r="G1506" t="n">
         <v>4</v>
@@ -50147,7 +50147,7 @@
         </is>
       </c>
       <c r="B1507" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C1507" t="inlineStr">
         <is>
@@ -50155,16 +50155,16 @@
         </is>
       </c>
       <c r="D1507" t="n">
-        <v>49.3</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="E1507" t="n">
-        <v>2549.9</v>
+        <v>2500.6</v>
       </c>
       <c r="F1507" t="n">
-        <v>13240.9</v>
+        <v>13191.6</v>
       </c>
       <c r="G1507" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H1507" t="n">
         <v>4</v>
@@ -50180,7 +50180,7 @@
         </is>
       </c>
       <c r="B1508" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C1508" t="inlineStr">
         <is>
@@ -50188,16 +50188,16 @@
         </is>
       </c>
       <c r="D1508" t="n">
-        <v>69.09999999999999</v>
+        <v>60.3</v>
       </c>
       <c r="E1508" t="n">
-        <v>2489.1</v>
+        <v>2433.9</v>
       </c>
       <c r="F1508" t="n">
-        <v>12354.2</v>
+        <v>12299</v>
       </c>
       <c r="G1508" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H1508" t="n">
         <v>5</v>
@@ -50213,7 +50213,7 @@
         </is>
       </c>
       <c r="B1509" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C1509" t="inlineStr">
         <is>
@@ -50221,16 +50221,16 @@
         </is>
       </c>
       <c r="D1509" t="n">
-        <v>48.4</v>
+        <v>60.4</v>
       </c>
       <c r="E1509" t="n">
-        <v>2209.7</v>
+        <v>2161.3</v>
       </c>
       <c r="F1509" t="n">
-        <v>11874.3</v>
+        <v>11825.9</v>
       </c>
       <c r="G1509" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H1509" t="n">
         <v>7</v>
@@ -50246,7 +50246,7 @@
         </is>
       </c>
       <c r="B1510" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C1510" t="inlineStr">
         <is>
@@ -50254,13 +50254,13 @@
         </is>
       </c>
       <c r="D1510" t="n">
-        <v>47.6</v>
+        <v>53.9</v>
       </c>
       <c r="E1510" t="n">
-        <v>2564.3</v>
+        <v>2516.7</v>
       </c>
       <c r="F1510" t="n">
-        <v>13499.1</v>
+        <v>13451.5</v>
       </c>
       <c r="G1510" t="n">
         <v>7</v>
@@ -50279,7 +50279,7 @@
         </is>
       </c>
       <c r="B1511" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C1511" t="inlineStr">
         <is>
@@ -50287,16 +50287,16 @@
         </is>
       </c>
       <c r="D1511" t="n">
-        <v>34.8</v>
+        <v>75.80000000000001</v>
       </c>
       <c r="E1511" t="n">
-        <v>2164.4</v>
+        <v>2142.2</v>
       </c>
       <c r="F1511" t="n">
-        <v>10998.3</v>
+        <v>10976.1</v>
       </c>
       <c r="G1511" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H1511" t="n">
         <v>8</v>
@@ -50312,7 +50312,7 @@
         </is>
       </c>
       <c r="B1512" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C1512" t="inlineStr">
         <is>
@@ -50320,16 +50320,16 @@
         </is>
       </c>
       <c r="D1512" t="n">
-        <v>73.3</v>
+        <v>53.2</v>
       </c>
       <c r="E1512" t="n">
-        <v>2323.2</v>
+        <v>2249.9</v>
       </c>
       <c r="F1512" t="n">
-        <v>11927.3</v>
+        <v>11854</v>
       </c>
       <c r="G1512" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H1512" t="n">
         <v>6</v>
@@ -50345,7 +50345,7 @@
         </is>
       </c>
       <c r="B1513" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C1513" t="inlineStr">
         <is>
@@ -50353,13 +50353,13 @@
         </is>
       </c>
       <c r="D1513" t="n">
-        <v>97.7</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="E1513" t="n">
-        <v>2726</v>
+        <v>2637.5</v>
       </c>
       <c r="F1513" t="n">
-        <v>10261</v>
+        <v>10172.5</v>
       </c>
       <c r="G1513" t="n">
         <v>1</v>
@@ -50378,7 +50378,7 @@
         </is>
       </c>
       <c r="B1514" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C1514" t="inlineStr">
         <is>
@@ -50386,16 +50386,16 @@
         </is>
       </c>
       <c r="D1514" t="n">
-        <v>95.7</v>
+        <v>58.2</v>
       </c>
       <c r="E1514" t="n">
-        <v>2750.5</v>
+        <v>2661.3</v>
       </c>
       <c r="F1514" t="n">
-        <v>13461.6</v>
+        <v>13372.4</v>
       </c>
       <c r="G1514" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H1514" t="n">
         <v>2</v>
@@ -50411,7 +50411,7 @@
         </is>
       </c>
       <c r="B1515" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C1515" t="inlineStr">
         <is>
@@ -50419,7 +50419,7 @@
         </is>
       </c>
       <c r="D1515" t="n">
-        <v>0</v>
+        <v>49.3</v>
       </c>
       <c r="E1515" t="n">
         <v>2549.9</v>
@@ -50428,7 +50428,7 @@
         <v>13240.9</v>
       </c>
       <c r="G1515" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H1515" t="n">
         <v>4</v>
@@ -50444,7 +50444,7 @@
         </is>
       </c>
       <c r="B1516" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C1516" t="inlineStr">
         <is>
@@ -50452,16 +50452,16 @@
         </is>
       </c>
       <c r="D1516" t="n">
-        <v>40.7</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="E1516" t="n">
-        <v>2529.8</v>
+        <v>2503</v>
       </c>
       <c r="F1516" t="n">
-        <v>12394.9</v>
+        <v>12368.1</v>
       </c>
       <c r="G1516" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H1516" t="n">
         <v>5</v>
@@ -50477,7 +50477,7 @@
         </is>
       </c>
       <c r="B1517" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C1517" t="inlineStr">
         <is>
@@ -50485,16 +50485,16 @@
         </is>
       </c>
       <c r="D1517" t="n">
-        <v>68.2</v>
+        <v>48.4</v>
       </c>
       <c r="E1517" t="n">
-        <v>2277.9</v>
+        <v>2209.7</v>
       </c>
       <c r="F1517" t="n">
-        <v>11942.5</v>
+        <v>11874.3</v>
       </c>
       <c r="G1517" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1517" t="n">
         <v>7</v>
@@ -50510,7 +50510,7 @@
         </is>
       </c>
       <c r="B1518" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C1518" t="inlineStr">
         <is>
@@ -50518,16 +50518,16 @@
         </is>
       </c>
       <c r="D1518" t="n">
-        <v>66.59999999999999</v>
+        <v>47.6</v>
       </c>
       <c r="E1518" t="n">
-        <v>2630.9</v>
+        <v>2564.3</v>
       </c>
       <c r="F1518" t="n">
-        <v>13565.7</v>
+        <v>13499.1</v>
       </c>
       <c r="G1518" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H1518" t="n">
         <v>3</v>
@@ -50543,7 +50543,7 @@
         </is>
       </c>
       <c r="B1519" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C1519" t="inlineStr">
         <is>
@@ -50551,16 +50551,16 @@
         </is>
       </c>
       <c r="D1519" t="n">
-        <v>80.59999999999999</v>
+        <v>34.8</v>
       </c>
       <c r="E1519" t="n">
-        <v>2245</v>
+        <v>2177</v>
       </c>
       <c r="F1519" t="n">
-        <v>11078.9</v>
+        <v>11010.9</v>
       </c>
       <c r="G1519" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H1519" t="n">
         <v>8</v>
@@ -50576,7 +50576,7 @@
         </is>
       </c>
       <c r="B1520" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C1520" t="inlineStr">
         <is>
@@ -50584,16 +50584,16 @@
         </is>
       </c>
       <c r="D1520" t="n">
-        <v>46.4</v>
+        <v>73.3</v>
       </c>
       <c r="E1520" t="n">
-        <v>2369.6</v>
+        <v>2323.2</v>
       </c>
       <c r="F1520" t="n">
-        <v>11973.7</v>
+        <v>11927.3</v>
       </c>
       <c r="G1520" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H1520" t="n">
         <v>6</v>
@@ -50609,29 +50609,293 @@
         </is>
       </c>
       <c r="B1521" t="n">
+        <v>37</v>
+      </c>
+      <c r="C1521" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1521" t="n">
+        <v>97.7</v>
+      </c>
+      <c r="E1521" t="n">
+        <v>2735.2</v>
+      </c>
+      <c r="F1521" t="n">
+        <v>10270.2</v>
+      </c>
+      <c r="G1521" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1521" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1521" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1522">
+      <c r="A1522" t="inlineStr">
+        <is>
+          <t>5f452f5e66dd374930eb2b71</t>
+        </is>
+      </c>
+      <c r="B1522" t="n">
         <v>38</v>
       </c>
-      <c r="C1521" t="inlineStr">
+      <c r="C1522" t="inlineStr">
         <is>
           <t>2025/26</t>
         </is>
       </c>
-      <c r="D1521" t="n">
+      <c r="D1522" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="E1522" t="n">
+        <v>2757</v>
+      </c>
+      <c r="F1522" t="n">
+        <v>13468.1</v>
+      </c>
+      <c r="G1522" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1522" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1522" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1523">
+      <c r="A1523" t="inlineStr">
+        <is>
+          <t>5f453062ec331549297ee6b8</t>
+        </is>
+      </c>
+      <c r="B1523" t="n">
+        <v>38</v>
+      </c>
+      <c r="C1523" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1523" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1523" t="n">
+        <v>2549.9</v>
+      </c>
+      <c r="F1523" t="n">
+        <v>13240.9</v>
+      </c>
+      <c r="G1523" t="n">
+        <v>8</v>
+      </c>
+      <c r="H1523" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1523" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1524">
+      <c r="A1524" t="inlineStr">
+        <is>
+          <t>5f4530beec331549297ee6d6</t>
+        </is>
+      </c>
+      <c r="B1524" t="n">
+        <v>38</v>
+      </c>
+      <c r="C1524" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1524" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="E1524" t="n">
+        <v>2543.7</v>
+      </c>
+      <c r="F1524" t="n">
+        <v>12408.8</v>
+      </c>
+      <c r="G1524" t="n">
+        <v>7</v>
+      </c>
+      <c r="H1524" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1524" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1525">
+      <c r="A1525" t="inlineStr">
+        <is>
+          <t>5f4531e9764e7d491e029746</t>
+        </is>
+      </c>
+      <c r="B1525" t="n">
+        <v>38</v>
+      </c>
+      <c r="C1525" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1525" t="n">
+        <v>68.2</v>
+      </c>
+      <c r="E1525" t="n">
+        <v>2277.9</v>
+      </c>
+      <c r="F1525" t="n">
+        <v>11942.5</v>
+      </c>
+      <c r="G1525" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1525" t="n">
+        <v>7</v>
+      </c>
+      <c r="I1525" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1526">
+      <c r="A1526" t="inlineStr">
+        <is>
+          <t>5f45324dec331549297ee971</t>
+        </is>
+      </c>
+      <c r="B1526" t="n">
+        <v>38</v>
+      </c>
+      <c r="C1526" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1526" t="n">
+        <v>66.59999999999999</v>
+      </c>
+      <c r="E1526" t="n">
+        <v>2630.9</v>
+      </c>
+      <c r="F1526" t="n">
+        <v>13565.7</v>
+      </c>
+      <c r="G1526" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1526" t="n">
+        <v>3</v>
+      </c>
+      <c r="I1526" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1527">
+      <c r="A1527" t="inlineStr">
+        <is>
+          <t>5f47ab5b9e2edb0bb831c703</t>
+        </is>
+      </c>
+      <c r="B1527" t="n">
+        <v>38</v>
+      </c>
+      <c r="C1527" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1527" t="n">
+        <v>80.59999999999999</v>
+      </c>
+      <c r="E1527" t="n">
+        <v>2257.6</v>
+      </c>
+      <c r="F1527" t="n">
+        <v>11091.5</v>
+      </c>
+      <c r="G1527" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1527" t="n">
+        <v>8</v>
+      </c>
+      <c r="I1527" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1528">
+      <c r="A1528" t="inlineStr">
+        <is>
+          <t>5f47aeb6c387a50bca03dd55</t>
+        </is>
+      </c>
+      <c r="B1528" t="n">
+        <v>38</v>
+      </c>
+      <c r="C1528" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1528" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="E1528" t="n">
+        <v>2369.6</v>
+      </c>
+      <c r="F1528" t="n">
+        <v>11973.7</v>
+      </c>
+      <c r="G1528" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1528" t="n">
+        <v>6</v>
+      </c>
+      <c r="I1528" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1529">
+      <c r="A1529" t="inlineStr">
+        <is>
+          <t>62d5bd9ad8106d3355b5bdc1</t>
+        </is>
+      </c>
+      <c r="B1529" t="n">
+        <v>38</v>
+      </c>
+      <c r="C1529" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="D1529" t="n">
         <v>80.40000000000001</v>
       </c>
-      <c r="E1521" t="n">
-        <v>2806.4</v>
-      </c>
-      <c r="F1521" t="n">
-        <v>10341.4</v>
-      </c>
-      <c r="G1521" t="n">
-        <v>3</v>
-      </c>
-      <c r="H1521" t="n">
-        <v>1</v>
-      </c>
-      <c r="I1521" t="n">
+      <c r="E1529" t="n">
+        <v>2815.6</v>
+      </c>
+      <c r="F1529" t="n">
+        <v>10350.6</v>
+      </c>
+      <c r="G1529" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1529" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1529" t="n">
         <v>8</v>
       </c>
     </row>

--- a/datos/vistas_negocio/Fact_Global_Master.xlsx
+++ b/datos/vistas_negocio/Fact_Global_Master.xlsx
@@ -41146,13 +41146,13 @@
         </is>
       </c>
       <c r="D1234" t="n">
-        <v>44.2</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="E1234" t="n">
-        <v>91.7</v>
+        <v>133.1</v>
       </c>
       <c r="F1234" t="n">
-        <v>10802.8</v>
+        <v>10844.2</v>
       </c>
       <c r="G1234" t="n">
         <v>8</v>
@@ -41179,16 +41179,16 @@
         </is>
       </c>
       <c r="D1235" t="n">
-        <v>93.3</v>
+        <v>160.4</v>
       </c>
       <c r="E1235" t="n">
-        <v>134.3</v>
+        <v>201.4</v>
       </c>
       <c r="F1235" t="n">
-        <v>10825.3</v>
+        <v>10892.4</v>
       </c>
       <c r="G1235" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H1235" t="n">
         <v>3</v>
@@ -41212,19 +41212,19 @@
         </is>
       </c>
       <c r="D1236" t="n">
-        <v>63.40000000000001</v>
+        <v>140.6</v>
       </c>
       <c r="E1236" t="n">
-        <v>142.3</v>
+        <v>219.5</v>
       </c>
       <c r="F1236" t="n">
-        <v>10007.4</v>
+        <v>10084.6</v>
       </c>
       <c r="G1236" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1236" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1236" t="n">
         <v>4</v>
@@ -41245,19 +41245,19 @@
         </is>
       </c>
       <c r="D1237" t="n">
-        <v>103</v>
+        <v>159.3</v>
       </c>
       <c r="E1237" t="n">
-        <v>152</v>
+        <v>208.3</v>
       </c>
       <c r="F1237" t="n">
-        <v>9816.6</v>
+        <v>9872.9</v>
       </c>
       <c r="G1237" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H1237" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1237" t="n">
         <v>5</v>
@@ -41278,16 +41278,16 @@
         </is>
       </c>
       <c r="D1238" t="n">
-        <v>60.2</v>
+        <v>134.8</v>
       </c>
       <c r="E1238" t="n">
-        <v>126.2</v>
+        <v>200.8</v>
       </c>
       <c r="F1238" t="n">
-        <v>11061</v>
+        <v>11135.6</v>
       </c>
       <c r="G1238" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1238" t="n">
         <v>4</v>
@@ -41311,13 +41311,13 @@
         </is>
       </c>
       <c r="D1239" t="n">
-        <v>44.6</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="E1239" t="n">
-        <v>104.2</v>
+        <v>151</v>
       </c>
       <c r="F1239" t="n">
-        <v>8938.1</v>
+        <v>8984.9</v>
       </c>
       <c r="G1239" t="n">
         <v>7</v>
@@ -41344,16 +41344,16 @@
         </is>
       </c>
       <c r="D1240" t="n">
-        <v>70.09999999999999</v>
+        <v>114.6</v>
       </c>
       <c r="E1240" t="n">
-        <v>121.1</v>
+        <v>165.6</v>
       </c>
       <c r="F1240" t="n">
-        <v>9725.200000000001</v>
+        <v>9769.700000000001</v>
       </c>
       <c r="G1240" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H1240" t="n">
         <v>6</v>
@@ -41377,16 +41377,16 @@
         </is>
       </c>
       <c r="D1241" t="n">
-        <v>57.8</v>
+        <v>121.9</v>
       </c>
       <c r="E1241" t="n">
-        <v>123</v>
+        <v>187.1</v>
       </c>
       <c r="F1241" t="n">
-        <v>7658</v>
+        <v>7722.1</v>
       </c>
       <c r="G1241" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H1241" t="n">
         <v>5</v>
@@ -41410,16 +41410,16 @@
         </is>
       </c>
       <c r="D1242" t="n">
-        <v>62.4</v>
+        <v>151.1</v>
       </c>
       <c r="E1242" t="n">
-        <v>154.1</v>
+        <v>284.2</v>
       </c>
       <c r="F1242" t="n">
-        <v>10865.2</v>
+        <v>10995.3</v>
       </c>
       <c r="G1242" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H1242" t="n">
         <v>7</v>
@@ -41443,19 +41443,19 @@
         </is>
       </c>
       <c r="D1243" t="n">
-        <v>66.8</v>
+        <v>136.7</v>
       </c>
       <c r="E1243" t="n">
-        <v>201.1</v>
+        <v>338.1</v>
       </c>
       <c r="F1243" t="n">
-        <v>10892.1</v>
+        <v>11029.1</v>
       </c>
       <c r="G1243" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1243" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1243" t="n">
         <v>2</v>
@@ -41476,19 +41476,19 @@
         </is>
       </c>
       <c r="D1244" t="n">
-        <v>73</v>
+        <v>125.3</v>
       </c>
       <c r="E1244" t="n">
-        <v>215.3</v>
+        <v>344.8</v>
       </c>
       <c r="F1244" t="n">
-        <v>10080.4</v>
+        <v>10209.9</v>
       </c>
       <c r="G1244" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H1244" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I1244" t="n">
         <v>4</v>
@@ -41509,19 +41509,19 @@
         </is>
       </c>
       <c r="D1245" t="n">
-        <v>63.6</v>
+        <v>145</v>
       </c>
       <c r="E1245" t="n">
-        <v>215.6</v>
+        <v>353.3</v>
       </c>
       <c r="F1245" t="n">
-        <v>9880.200000000001</v>
+        <v>10017.9</v>
       </c>
       <c r="G1245" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1245" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1245" t="n">
         <v>5</v>
@@ -41542,19 +41542,19 @@
         </is>
       </c>
       <c r="D1246" t="n">
-        <v>70</v>
+        <v>170.6</v>
       </c>
       <c r="E1246" t="n">
-        <v>196.2</v>
+        <v>371.4</v>
       </c>
       <c r="F1246" t="n">
-        <v>11131</v>
+        <v>11306.2</v>
       </c>
       <c r="G1246" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H1246" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I1246" t="n">
         <v>1</v>
@@ -41575,13 +41575,13 @@
         </is>
       </c>
       <c r="D1247" t="n">
-        <v>40.5</v>
+        <v>110.2</v>
       </c>
       <c r="E1247" t="n">
-        <v>144.7</v>
+        <v>261.2</v>
       </c>
       <c r="F1247" t="n">
-        <v>8978.6</v>
+        <v>9095.1</v>
       </c>
       <c r="G1247" t="n">
         <v>8</v>
@@ -41608,19 +41608,19 @@
         </is>
       </c>
       <c r="D1248" t="n">
-        <v>59.8</v>
+        <v>120.2</v>
       </c>
       <c r="E1248" t="n">
-        <v>180.9</v>
+        <v>285.8</v>
       </c>
       <c r="F1248" t="n">
-        <v>9785</v>
+        <v>9889.9</v>
       </c>
       <c r="G1248" t="n">
         <v>6</v>
       </c>
       <c r="H1248" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I1248" t="n">
         <v>6</v>
@@ -41641,19 +41641,19 @@
         </is>
       </c>
       <c r="D1249" t="n">
-        <v>43.5</v>
+        <v>118.4</v>
       </c>
       <c r="E1249" t="n">
-        <v>166.5</v>
+        <v>305.5</v>
       </c>
       <c r="F1249" t="n">
-        <v>7701.5</v>
+        <v>7840.5</v>
       </c>
       <c r="G1249" t="n">
         <v>7</v>
       </c>
       <c r="H1249" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I1249" t="n">
         <v>8</v>
@@ -41677,16 +41677,16 @@
         <v>56.9</v>
       </c>
       <c r="E1250" t="n">
-        <v>211</v>
+        <v>341.1</v>
       </c>
       <c r="F1250" t="n">
-        <v>10922.1</v>
+        <v>11052.2</v>
       </c>
       <c r="G1250" t="n">
         <v>4</v>
       </c>
       <c r="H1250" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I1250" t="n">
         <v>3</v>
@@ -41710,16 +41710,16 @@
         <v>55.1</v>
       </c>
       <c r="E1251" t="n">
-        <v>256.2</v>
+        <v>393.2</v>
       </c>
       <c r="F1251" t="n">
-        <v>10947.2</v>
+        <v>11084.2</v>
       </c>
       <c r="G1251" t="n">
         <v>6</v>
       </c>
       <c r="H1251" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1251" t="n">
         <v>2</v>
@@ -41743,16 +41743,16 @@
         <v>58.8</v>
       </c>
       <c r="E1252" t="n">
-        <v>274.1</v>
+        <v>403.6</v>
       </c>
       <c r="F1252" t="n">
-        <v>10139.2</v>
+        <v>10268.7</v>
       </c>
       <c r="G1252" t="n">
         <v>3</v>
       </c>
       <c r="H1252" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I1252" t="n">
         <v>4</v>
@@ -41776,10 +41776,10 @@
         <v>86.2</v>
       </c>
       <c r="E1253" t="n">
-        <v>301.8</v>
+        <v>439.5</v>
       </c>
       <c r="F1253" t="n">
-        <v>9966.4</v>
+        <v>10104.1</v>
       </c>
       <c r="G1253" t="n">
         <v>1</v>
@@ -41809,16 +41809,16 @@
         <v>56.8</v>
       </c>
       <c r="E1254" t="n">
-        <v>253</v>
+        <v>428.2</v>
       </c>
       <c r="F1254" t="n">
-        <v>11187.8</v>
+        <v>11363</v>
       </c>
       <c r="G1254" t="n">
         <v>5</v>
       </c>
       <c r="H1254" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I1254" t="n">
         <v>1</v>
@@ -41842,10 +41842,10 @@
         <v>53.5</v>
       </c>
       <c r="E1255" t="n">
-        <v>198.2</v>
+        <v>314.7</v>
       </c>
       <c r="F1255" t="n">
-        <v>9032.1</v>
+        <v>9148.6</v>
       </c>
       <c r="G1255" t="n">
         <v>7</v>
@@ -41875,16 +41875,16 @@
         <v>44.2</v>
       </c>
       <c r="E1256" t="n">
-        <v>225.1</v>
+        <v>330</v>
       </c>
       <c r="F1256" t="n">
-        <v>9829.200000000001</v>
+        <v>9934.1</v>
       </c>
       <c r="G1256" t="n">
         <v>8</v>
       </c>
       <c r="H1256" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1256" t="n">
         <v>6</v>
@@ -41908,10 +41908,10 @@
         <v>71.5</v>
       </c>
       <c r="E1257" t="n">
-        <v>238</v>
+        <v>377</v>
       </c>
       <c r="F1257" t="n">
-        <v>7773</v>
+        <v>7912</v>
       </c>
       <c r="G1257" t="n">
         <v>2</v>
@@ -41941,16 +41941,16 @@
         <v>49.90000000000001</v>
       </c>
       <c r="E1258" t="n">
-        <v>260.9</v>
+        <v>391</v>
       </c>
       <c r="F1258" t="n">
-        <v>10972</v>
+        <v>11102.1</v>
       </c>
       <c r="G1258" t="n">
         <v>8</v>
       </c>
       <c r="H1258" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I1258" t="n">
         <v>3</v>
@@ -41974,16 +41974,16 @@
         <v>70.40000000000001</v>
       </c>
       <c r="E1259" t="n">
-        <v>326.6</v>
+        <v>463.6</v>
       </c>
       <c r="F1259" t="n">
-        <v>11017.6</v>
+        <v>11154.6</v>
       </c>
       <c r="G1259" t="n">
         <v>5</v>
       </c>
       <c r="H1259" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1259" t="n">
         <v>2</v>
@@ -42007,16 +42007,16 @@
         <v>57.1</v>
       </c>
       <c r="E1260" t="n">
-        <v>331.2</v>
+        <v>460.7</v>
       </c>
       <c r="F1260" t="n">
-        <v>10196.3</v>
+        <v>10325.8</v>
       </c>
       <c r="G1260" t="n">
         <v>6</v>
       </c>
       <c r="H1260" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1260" t="n">
         <v>4</v>
@@ -42040,10 +42040,10 @@
         <v>82.7</v>
       </c>
       <c r="E1261" t="n">
-        <v>384.5</v>
+        <v>522.2</v>
       </c>
       <c r="F1261" t="n">
-        <v>10049.1</v>
+        <v>10186.8</v>
       </c>
       <c r="G1261" t="n">
         <v>2</v>
@@ -42073,10 +42073,10 @@
         <v>86.5</v>
       </c>
       <c r="E1262" t="n">
-        <v>339.5</v>
+        <v>514.7</v>
       </c>
       <c r="F1262" t="n">
-        <v>11274.3</v>
+        <v>11449.5</v>
       </c>
       <c r="G1262" t="n">
         <v>1</v>
@@ -42106,16 +42106,16 @@
         <v>75.8</v>
       </c>
       <c r="E1263" t="n">
-        <v>274</v>
+        <v>390.5</v>
       </c>
       <c r="F1263" t="n">
-        <v>9107.9</v>
+        <v>9224.4</v>
       </c>
       <c r="G1263" t="n">
         <v>4</v>
       </c>
       <c r="H1263" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I1263" t="n">
         <v>7</v>
@@ -42139,16 +42139,16 @@
         <v>77.7</v>
       </c>
       <c r="E1264" t="n">
-        <v>302.8</v>
+        <v>407.7</v>
       </c>
       <c r="F1264" t="n">
-        <v>9906.9</v>
+        <v>10011.8</v>
       </c>
       <c r="G1264" t="n">
         <v>3</v>
       </c>
       <c r="H1264" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I1264" t="n">
         <v>6</v>
@@ -42172,16 +42172,16 @@
         <v>55.6</v>
       </c>
       <c r="E1265" t="n">
-        <v>293.6</v>
+        <v>432.6</v>
       </c>
       <c r="F1265" t="n">
-        <v>7828.6</v>
+        <v>7967.6</v>
       </c>
       <c r="G1265" t="n">
         <v>7</v>
       </c>
       <c r="H1265" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I1265" t="n">
         <v>8</v>
@@ -42205,10 +42205,10 @@
         <v>34.2</v>
       </c>
       <c r="E1266" t="n">
-        <v>295.1</v>
+        <v>425.2</v>
       </c>
       <c r="F1266" t="n">
-        <v>11006.2</v>
+        <v>11136.3</v>
       </c>
       <c r="G1266" t="n">
         <v>6</v>
@@ -42238,10 +42238,10 @@
         <v>45.6</v>
       </c>
       <c r="E1267" t="n">
-        <v>372.2</v>
+        <v>509.2</v>
       </c>
       <c r="F1267" t="n">
-        <v>11063.2</v>
+        <v>11200.2</v>
       </c>
       <c r="G1267" t="n">
         <v>5</v>
@@ -42271,10 +42271,10 @@
         <v>56.1</v>
       </c>
       <c r="E1268" t="n">
-        <v>387.3</v>
+        <v>516.8</v>
       </c>
       <c r="F1268" t="n">
-        <v>10252.4</v>
+        <v>10381.9</v>
       </c>
       <c r="G1268" t="n">
         <v>3</v>
@@ -42304,10 +42304,10 @@
         <v>61.7</v>
       </c>
       <c r="E1269" t="n">
-        <v>446.2</v>
+        <v>583.9</v>
       </c>
       <c r="F1269" t="n">
-        <v>10110.8</v>
+        <v>10248.5</v>
       </c>
       <c r="G1269" t="n">
         <v>1</v>
@@ -42337,10 +42337,10 @@
         <v>58.3</v>
       </c>
       <c r="E1270" t="n">
-        <v>397.8</v>
+        <v>573</v>
       </c>
       <c r="F1270" t="n">
-        <v>11332.6</v>
+        <v>11507.8</v>
       </c>
       <c r="G1270" t="n">
         <v>2</v>
@@ -42370,10 +42370,10 @@
         <v>47.9</v>
       </c>
       <c r="E1271" t="n">
-        <v>321.9</v>
+        <v>438.4</v>
       </c>
       <c r="F1271" t="n">
-        <v>9155.799999999999</v>
+        <v>9272.299999999999</v>
       </c>
       <c r="G1271" t="n">
         <v>4</v>
@@ -42403,16 +42403,16 @@
         <v>32.4</v>
       </c>
       <c r="E1272" t="n">
-        <v>335.2</v>
+        <v>440.1</v>
       </c>
       <c r="F1272" t="n">
-        <v>9939.299999999999</v>
+        <v>10044.2</v>
       </c>
       <c r="G1272" t="n">
         <v>8</v>
       </c>
       <c r="H1272" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I1272" t="n">
         <v>6</v>
@@ -42436,16 +42436,16 @@
         <v>34.2</v>
       </c>
       <c r="E1273" t="n">
-        <v>327.8</v>
+        <v>466.8</v>
       </c>
       <c r="F1273" t="n">
-        <v>7862.8</v>
+        <v>8001.8</v>
       </c>
       <c r="G1273" t="n">
         <v>6</v>
       </c>
       <c r="H1273" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I1273" t="n">
         <v>8</v>
@@ -42469,16 +42469,16 @@
         <v>73.59999999999999</v>
       </c>
       <c r="E1274" t="n">
-        <v>368.7</v>
+        <v>498.8</v>
       </c>
       <c r="F1274" t="n">
-        <v>11079.8</v>
+        <v>11209.9</v>
       </c>
       <c r="G1274" t="n">
         <v>3</v>
       </c>
       <c r="H1274" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I1274" t="n">
         <v>3</v>
@@ -42502,10 +42502,10 @@
         <v>59.40000000000001</v>
       </c>
       <c r="E1275" t="n">
-        <v>431.6</v>
+        <v>568.6</v>
       </c>
       <c r="F1275" t="n">
-        <v>11122.6</v>
+        <v>11259.6</v>
       </c>
       <c r="G1275" t="n">
         <v>5</v>
@@ -42535,10 +42535,10 @@
         <v>78.59999999999999</v>
       </c>
       <c r="E1276" t="n">
-        <v>465.9</v>
+        <v>595.4</v>
       </c>
       <c r="F1276" t="n">
-        <v>10331</v>
+        <v>10460.5</v>
       </c>
       <c r="G1276" t="n">
         <v>1</v>
@@ -42568,16 +42568,16 @@
         <v>46</v>
       </c>
       <c r="E1277" t="n">
-        <v>492.2</v>
+        <v>629.9</v>
       </c>
       <c r="F1277" t="n">
-        <v>10156.8</v>
+        <v>10294.5</v>
       </c>
       <c r="G1277" t="n">
         <v>8</v>
       </c>
       <c r="H1277" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1277" t="n">
         <v>5</v>
@@ -42601,16 +42601,16 @@
         <v>70.09999999999999</v>
       </c>
       <c r="E1278" t="n">
-        <v>467.9</v>
+        <v>643.1</v>
       </c>
       <c r="F1278" t="n">
-        <v>11402.7</v>
+        <v>11577.9</v>
       </c>
       <c r="G1278" t="n">
         <v>4</v>
       </c>
       <c r="H1278" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1278" t="n">
         <v>1</v>
@@ -42634,16 +42634,16 @@
         <v>52.5</v>
       </c>
       <c r="E1279" t="n">
-        <v>374.4</v>
+        <v>490.9</v>
       </c>
       <c r="F1279" t="n">
-        <v>9208.299999999999</v>
+        <v>9324.799999999999</v>
       </c>
       <c r="G1279" t="n">
         <v>7</v>
       </c>
       <c r="H1279" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I1279" t="n">
         <v>7</v>
@@ -42667,16 +42667,16 @@
         <v>74.90000000000001</v>
       </c>
       <c r="E1280" t="n">
-        <v>410.1</v>
+        <v>515</v>
       </c>
       <c r="F1280" t="n">
-        <v>10014.2</v>
+        <v>10119.1</v>
       </c>
       <c r="G1280" t="n">
         <v>2</v>
       </c>
       <c r="H1280" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I1280" t="n">
         <v>6</v>
@@ -42700,16 +42700,16 @@
         <v>58.2</v>
       </c>
       <c r="E1281" t="n">
-        <v>386</v>
+        <v>525</v>
       </c>
       <c r="F1281" t="n">
-        <v>7921</v>
+        <v>8060</v>
       </c>
       <c r="G1281" t="n">
         <v>6</v>
       </c>
       <c r="H1281" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I1281" t="n">
         <v>8</v>
@@ -42733,16 +42733,16 @@
         <v>53.8</v>
       </c>
       <c r="E1282" t="n">
-        <v>422.5</v>
+        <v>552.6</v>
       </c>
       <c r="F1282" t="n">
-        <v>11133.6</v>
+        <v>11263.7</v>
       </c>
       <c r="G1282" t="n">
         <v>7</v>
       </c>
       <c r="H1282" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I1282" t="n">
         <v>3</v>
@@ -42766,10 +42766,10 @@
         <v>51.1</v>
       </c>
       <c r="E1283" t="n">
-        <v>482.7</v>
+        <v>619.7</v>
       </c>
       <c r="F1283" t="n">
-        <v>11173.7</v>
+        <v>11310.7</v>
       </c>
       <c r="G1283" t="n">
         <v>8</v>
@@ -42799,16 +42799,16 @@
         <v>62.1</v>
       </c>
       <c r="E1284" t="n">
-        <v>528</v>
+        <v>657.5</v>
       </c>
       <c r="F1284" t="n">
-        <v>10393.1</v>
+        <v>10522.6</v>
       </c>
       <c r="G1284" t="n">
         <v>3</v>
       </c>
       <c r="H1284" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I1284" t="n">
         <v>4</v>
@@ -42832,16 +42832,16 @@
         <v>69.5</v>
       </c>
       <c r="E1285" t="n">
-        <v>561.7</v>
+        <v>699.4</v>
       </c>
       <c r="F1285" t="n">
-        <v>10226.3</v>
+        <v>10364</v>
       </c>
       <c r="G1285" t="n">
         <v>1</v>
       </c>
       <c r="H1285" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1285" t="n">
         <v>5</v>
@@ -42865,16 +42865,16 @@
         <v>59.5</v>
       </c>
       <c r="E1286" t="n">
-        <v>527.4</v>
+        <v>702.6</v>
       </c>
       <c r="F1286" t="n">
-        <v>11462.2</v>
+        <v>11637.4</v>
       </c>
       <c r="G1286" t="n">
         <v>5</v>
       </c>
       <c r="H1286" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I1286" t="n">
         <v>1</v>
@@ -42898,16 +42898,16 @@
         <v>54.1</v>
       </c>
       <c r="E1287" t="n">
-        <v>428.5</v>
+        <v>545</v>
       </c>
       <c r="F1287" t="n">
-        <v>9262.4</v>
+        <v>9378.9</v>
       </c>
       <c r="G1287" t="n">
         <v>6</v>
       </c>
       <c r="H1287" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I1287" t="n">
         <v>7</v>
@@ -42931,16 +42931,16 @@
         <v>69.2</v>
       </c>
       <c r="E1288" t="n">
-        <v>479.3</v>
+        <v>584.2</v>
       </c>
       <c r="F1288" t="n">
-        <v>10083.4</v>
+        <v>10188.3</v>
       </c>
       <c r="G1288" t="n">
         <v>2</v>
       </c>
       <c r="H1288" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I1288" t="n">
         <v>6</v>
@@ -42964,16 +42964,16 @@
         <v>60</v>
       </c>
       <c r="E1289" t="n">
-        <v>446</v>
+        <v>585</v>
       </c>
       <c r="F1289" t="n">
-        <v>7981</v>
+        <v>8120</v>
       </c>
       <c r="G1289" t="n">
         <v>4</v>
       </c>
       <c r="H1289" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I1289" t="n">
         <v>8</v>
@@ -42997,10 +42997,10 @@
         <v>87.8</v>
       </c>
       <c r="E1290" t="n">
-        <v>510.3</v>
+        <v>640.4</v>
       </c>
       <c r="F1290" t="n">
-        <v>11221.4</v>
+        <v>11351.5</v>
       </c>
       <c r="G1290" t="n">
         <v>1</v>
@@ -43030,16 +43030,16 @@
         <v>67</v>
       </c>
       <c r="E1291" t="n">
-        <v>549.7</v>
+        <v>686.7</v>
       </c>
       <c r="F1291" t="n">
-        <v>11240.7</v>
+        <v>11377.7</v>
       </c>
       <c r="G1291" t="n">
         <v>4</v>
       </c>
       <c r="H1291" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I1291" t="n">
         <v>2</v>
@@ -43063,10 +43063,10 @@
         <v>55.4</v>
       </c>
       <c r="E1292" t="n">
-        <v>583.4</v>
+        <v>712.9</v>
       </c>
       <c r="F1292" t="n">
-        <v>10448.5</v>
+        <v>10578</v>
       </c>
       <c r="G1292" t="n">
         <v>7</v>
@@ -43096,16 +43096,16 @@
         <v>57.6</v>
       </c>
       <c r="E1293" t="n">
-        <v>619.3000000000001</v>
+        <v>757</v>
       </c>
       <c r="F1293" t="n">
-        <v>10283.9</v>
+        <v>10421.6</v>
       </c>
       <c r="G1293" t="n">
         <v>6</v>
       </c>
       <c r="H1293" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1293" t="n">
         <v>5</v>
@@ -43129,16 +43129,16 @@
         <v>66.3</v>
       </c>
       <c r="E1294" t="n">
-        <v>593.7</v>
+        <v>768.9</v>
       </c>
       <c r="F1294" t="n">
-        <v>11528.5</v>
+        <v>11703.7</v>
       </c>
       <c r="G1294" t="n">
         <v>5</v>
       </c>
       <c r="H1294" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1294" t="n">
         <v>1</v>
@@ -43162,10 +43162,10 @@
         <v>52.1</v>
       </c>
       <c r="E1295" t="n">
-        <v>480.6</v>
+        <v>597.1</v>
       </c>
       <c r="F1295" t="n">
-        <v>9314.5</v>
+        <v>9431</v>
       </c>
       <c r="G1295" t="n">
         <v>8</v>
@@ -43195,16 +43195,16 @@
         <v>81.09999999999999</v>
       </c>
       <c r="E1296" t="n">
-        <v>560.4</v>
+        <v>665.3</v>
       </c>
       <c r="F1296" t="n">
-        <v>10164.5</v>
+        <v>10269.4</v>
       </c>
       <c r="G1296" t="n">
         <v>2</v>
       </c>
       <c r="H1296" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I1296" t="n">
         <v>6</v>
@@ -43228,10 +43228,10 @@
         <v>76.89999999999999</v>
       </c>
       <c r="E1297" t="n">
-        <v>522.9</v>
+        <v>661.9</v>
       </c>
       <c r="F1297" t="n">
-        <v>8057.9</v>
+        <v>8196.9</v>
       </c>
       <c r="G1297" t="n">
         <v>3</v>
@@ -43261,10 +43261,10 @@
         <v>77.90000000000001</v>
       </c>
       <c r="E1298" t="n">
-        <v>588.2</v>
+        <v>718.3</v>
       </c>
       <c r="F1298" t="n">
-        <v>11299.3</v>
+        <v>11429.4</v>
       </c>
       <c r="G1298" t="n">
         <v>1</v>
@@ -43273,7 +43273,7 @@
         <v>7</v>
       </c>
       <c r="I1298" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1299">
@@ -43294,19 +43294,19 @@
         <v>54.8</v>
       </c>
       <c r="E1299" t="n">
-        <v>604.5</v>
+        <v>741.5</v>
       </c>
       <c r="F1299" t="n">
-        <v>11295.5</v>
+        <v>11432.5</v>
       </c>
       <c r="G1299" t="n">
         <v>7</v>
       </c>
       <c r="H1299" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I1299" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1300">
@@ -43327,10 +43327,10 @@
         <v>68.8</v>
       </c>
       <c r="E1300" t="n">
-        <v>652.2</v>
+        <v>781.7</v>
       </c>
       <c r="F1300" t="n">
-        <v>10517.3</v>
+        <v>10646.8</v>
       </c>
       <c r="G1300" t="n">
         <v>3</v>
@@ -43360,16 +43360,16 @@
         <v>60.2</v>
       </c>
       <c r="E1301" t="n">
-        <v>679.5</v>
+        <v>817.2</v>
       </c>
       <c r="F1301" t="n">
-        <v>10344.1</v>
+        <v>10481.8</v>
       </c>
       <c r="G1301" t="n">
         <v>6</v>
       </c>
       <c r="H1301" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1301" t="n">
         <v>5</v>
@@ -43393,16 +43393,16 @@
         <v>62.8</v>
       </c>
       <c r="E1302" t="n">
-        <v>656.5</v>
+        <v>831.7</v>
       </c>
       <c r="F1302" t="n">
-        <v>11591.3</v>
+        <v>11766.5</v>
       </c>
       <c r="G1302" t="n">
         <v>5</v>
       </c>
       <c r="H1302" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1302" t="n">
         <v>1</v>
@@ -43426,10 +43426,10 @@
         <v>50.9</v>
       </c>
       <c r="E1303" t="n">
-        <v>531.5</v>
+        <v>648</v>
       </c>
       <c r="F1303" t="n">
-        <v>9365.4</v>
+        <v>9481.9</v>
       </c>
       <c r="G1303" t="n">
         <v>8</v>
@@ -43459,16 +43459,16 @@
         <v>69.40000000000001</v>
       </c>
       <c r="E1304" t="n">
-        <v>629.8000000000001</v>
+        <v>734.7</v>
       </c>
       <c r="F1304" t="n">
-        <v>10233.9</v>
+        <v>10338.8</v>
       </c>
       <c r="G1304" t="n">
         <v>2</v>
       </c>
       <c r="H1304" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I1304" t="n">
         <v>6</v>
@@ -43492,10 +43492,10 @@
         <v>66.3</v>
       </c>
       <c r="E1305" t="n">
-        <v>589.2</v>
+        <v>728.2</v>
       </c>
       <c r="F1305" t="n">
-        <v>8124.2</v>
+        <v>8263.200000000001</v>
       </c>
       <c r="G1305" t="n">
         <v>4</v>
@@ -43525,10 +43525,10 @@
         <v>68</v>
       </c>
       <c r="E1306" t="n">
-        <v>656.2</v>
+        <v>786.3</v>
       </c>
       <c r="F1306" t="n">
-        <v>11367.3</v>
+        <v>11497.4</v>
       </c>
       <c r="G1306" t="n">
         <v>5</v>
@@ -43558,16 +43558,16 @@
         <v>89.2</v>
       </c>
       <c r="E1307" t="n">
-        <v>693.7</v>
+        <v>830.7</v>
       </c>
       <c r="F1307" t="n">
-        <v>11384.7</v>
+        <v>11521.7</v>
       </c>
       <c r="G1307" t="n">
         <v>2</v>
       </c>
       <c r="H1307" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I1307" t="n">
         <v>2</v>
@@ -43591,16 +43591,16 @@
         <v>79.3</v>
       </c>
       <c r="E1308" t="n">
-        <v>731.5</v>
+        <v>861</v>
       </c>
       <c r="F1308" t="n">
-        <v>10596.6</v>
+        <v>10726.1</v>
       </c>
       <c r="G1308" t="n">
         <v>3</v>
       </c>
       <c r="H1308" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I1308" t="n">
         <v>4</v>
@@ -43624,16 +43624,16 @@
         <v>61</v>
       </c>
       <c r="E1309" t="n">
-        <v>740.5</v>
+        <v>878.2</v>
       </c>
       <c r="F1309" t="n">
-        <v>10405.1</v>
+        <v>10542.8</v>
       </c>
       <c r="G1309" t="n">
         <v>6</v>
       </c>
       <c r="H1309" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1309" t="n">
         <v>5</v>
@@ -43657,16 +43657,16 @@
         <v>57.4</v>
       </c>
       <c r="E1310" t="n">
-        <v>713.9</v>
+        <v>889.1</v>
       </c>
       <c r="F1310" t="n">
-        <v>11648.7</v>
+        <v>11823.9</v>
       </c>
       <c r="G1310" t="n">
         <v>7</v>
       </c>
       <c r="H1310" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I1310" t="n">
         <v>1</v>
@@ -43690,10 +43690,10 @@
         <v>46.4</v>
       </c>
       <c r="E1311" t="n">
-        <v>577.9</v>
+        <v>694.4</v>
       </c>
       <c r="F1311" t="n">
-        <v>9411.799999999999</v>
+        <v>9528.299999999999</v>
       </c>
       <c r="G1311" t="n">
         <v>8</v>
@@ -43723,16 +43723,16 @@
         <v>77.2</v>
       </c>
       <c r="E1312" t="n">
-        <v>707</v>
+        <v>811.9</v>
       </c>
       <c r="F1312" t="n">
-        <v>10311.1</v>
+        <v>10416</v>
       </c>
       <c r="G1312" t="n">
         <v>4</v>
       </c>
       <c r="H1312" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I1312" t="n">
         <v>6</v>
@@ -43756,16 +43756,16 @@
         <v>95.2</v>
       </c>
       <c r="E1313" t="n">
-        <v>684.4</v>
+        <v>823.4</v>
       </c>
       <c r="F1313" t="n">
-        <v>8219.4</v>
+        <v>8358.4</v>
       </c>
       <c r="G1313" t="n">
         <v>1</v>
       </c>
       <c r="H1313" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I1313" t="n">
         <v>8</v>
@@ -43789,10 +43789,10 @@
         <v>78</v>
       </c>
       <c r="E1314" t="n">
-        <v>734.2</v>
+        <v>864.3</v>
       </c>
       <c r="F1314" t="n">
-        <v>11445.3</v>
+        <v>11575.4</v>
       </c>
       <c r="G1314" t="n">
         <v>3</v>
@@ -43822,10 +43822,10 @@
         <v>78.59999999999999</v>
       </c>
       <c r="E1315" t="n">
-        <v>772.3</v>
+        <v>909.3</v>
       </c>
       <c r="F1315" t="n">
-        <v>11463.3</v>
+        <v>11600.3</v>
       </c>
       <c r="G1315" t="n">
         <v>2</v>
@@ -43855,16 +43855,16 @@
         <v>76.90000000000001</v>
       </c>
       <c r="E1316" t="n">
-        <v>808.4</v>
+        <v>937.9</v>
       </c>
       <c r="F1316" t="n">
-        <v>10673.5</v>
+        <v>10803</v>
       </c>
       <c r="G1316" t="n">
         <v>4</v>
       </c>
       <c r="H1316" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1316" t="n">
         <v>4</v>
@@ -43888,16 +43888,16 @@
         <v>48.4</v>
       </c>
       <c r="E1317" t="n">
-        <v>788.9</v>
+        <v>926.6</v>
       </c>
       <c r="F1317" t="n">
-        <v>10453.5</v>
+        <v>10591.2</v>
       </c>
       <c r="G1317" t="n">
         <v>8</v>
       </c>
       <c r="H1317" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I1317" t="n">
         <v>5</v>
@@ -43921,16 +43921,16 @@
         <v>67.59999999999999</v>
       </c>
       <c r="E1318" t="n">
-        <v>781.5</v>
+        <v>956.7</v>
       </c>
       <c r="F1318" t="n">
-        <v>11716.3</v>
+        <v>11891.5</v>
       </c>
       <c r="G1318" t="n">
         <v>5</v>
       </c>
       <c r="H1318" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I1318" t="n">
         <v>1</v>
@@ -43954,10 +43954,10 @@
         <v>58.1</v>
       </c>
       <c r="E1319" t="n">
-        <v>636</v>
+        <v>752.5</v>
       </c>
       <c r="F1319" t="n">
-        <v>9469.9</v>
+        <v>9586.4</v>
       </c>
       <c r="G1319" t="n">
         <v>7</v>
@@ -43987,16 +43987,16 @@
         <v>61.4</v>
       </c>
       <c r="E1320" t="n">
-        <v>768.4</v>
+        <v>873.3</v>
       </c>
       <c r="F1320" t="n">
-        <v>10372.5</v>
+        <v>10477.4</v>
       </c>
       <c r="G1320" t="n">
         <v>6</v>
       </c>
       <c r="H1320" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I1320" t="n">
         <v>6</v>
@@ -44020,16 +44020,16 @@
         <v>81.59999999999999</v>
       </c>
       <c r="E1321" t="n">
-        <v>766</v>
+        <v>905</v>
       </c>
       <c r="F1321" t="n">
-        <v>8301</v>
+        <v>8440</v>
       </c>
       <c r="G1321" t="n">
         <v>1</v>
       </c>
       <c r="H1321" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I1321" t="n">
         <v>8</v>
@@ -44053,10 +44053,10 @@
         <v>67.5</v>
       </c>
       <c r="E1322" t="n">
-        <v>801.7</v>
+        <v>931.8</v>
       </c>
       <c r="F1322" t="n">
-        <v>11512.8</v>
+        <v>11642.9</v>
       </c>
       <c r="G1322" t="n">
         <v>5</v>
@@ -44086,10 +44086,10 @@
         <v>69.8</v>
       </c>
       <c r="E1323" t="n">
-        <v>842.1</v>
+        <v>979.1</v>
       </c>
       <c r="F1323" t="n">
-        <v>11533.1</v>
+        <v>11670.1</v>
       </c>
       <c r="G1323" t="n">
         <v>2</v>
@@ -44119,16 +44119,16 @@
         <v>68.3</v>
       </c>
       <c r="E1324" t="n">
-        <v>876.7</v>
+        <v>1006.2</v>
       </c>
       <c r="F1324" t="n">
-        <v>10741.8</v>
+        <v>10871.3</v>
       </c>
       <c r="G1324" t="n">
         <v>3</v>
       </c>
       <c r="H1324" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1324" t="n">
         <v>4</v>
@@ -44152,10 +44152,10 @@
         <v>52.1</v>
       </c>
       <c r="E1325" t="n">
-        <v>841</v>
+        <v>978.7</v>
       </c>
       <c r="F1325" t="n">
-        <v>10505.6</v>
+        <v>10643.3</v>
       </c>
       <c r="G1325" t="n">
         <v>8</v>
@@ -44185,16 +44185,16 @@
         <v>79.7</v>
       </c>
       <c r="E1326" t="n">
-        <v>861.2</v>
+        <v>1036.4</v>
       </c>
       <c r="F1326" t="n">
-        <v>11796</v>
+        <v>11971.2</v>
       </c>
       <c r="G1326" t="n">
         <v>1</v>
       </c>
       <c r="H1326" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1326" t="n">
         <v>1</v>
@@ -44218,10 +44218,10 @@
         <v>58</v>
       </c>
       <c r="E1327" t="n">
-        <v>694</v>
+        <v>810.5</v>
       </c>
       <c r="F1327" t="n">
-        <v>9527.9</v>
+        <v>9644.4</v>
       </c>
       <c r="G1327" t="n">
         <v>7</v>
@@ -44251,10 +44251,10 @@
         <v>59.5</v>
       </c>
       <c r="E1328" t="n">
-        <v>827.9</v>
+        <v>932.8</v>
       </c>
       <c r="F1328" t="n">
-        <v>10432</v>
+        <v>10536.9</v>
       </c>
       <c r="G1328" t="n">
         <v>6</v>
@@ -44284,10 +44284,10 @@
         <v>68.10000000000001</v>
       </c>
       <c r="E1329" t="n">
-        <v>834.1</v>
+        <v>973.1</v>
       </c>
       <c r="F1329" t="n">
-        <v>8369.1</v>
+        <v>8508.1</v>
       </c>
       <c r="G1329" t="n">
         <v>4</v>
@@ -44317,10 +44317,10 @@
         <v>58.6</v>
       </c>
       <c r="E1330" t="n">
-        <v>860.3</v>
+        <v>990.4</v>
       </c>
       <c r="F1330" t="n">
-        <v>11571.4</v>
+        <v>11701.5</v>
       </c>
       <c r="G1330" t="n">
         <v>6</v>
@@ -44350,16 +44350,16 @@
         <v>105.7</v>
       </c>
       <c r="E1331" t="n">
-        <v>947.8</v>
+        <v>1084.8</v>
       </c>
       <c r="F1331" t="n">
-        <v>11638.8</v>
+        <v>11775.8</v>
       </c>
       <c r="G1331" t="n">
         <v>1</v>
       </c>
       <c r="H1331" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1331" t="n">
         <v>2</v>
@@ -44383,10 +44383,10 @@
         <v>58.4</v>
       </c>
       <c r="E1332" t="n">
-        <v>935.1</v>
+        <v>1064.6</v>
       </c>
       <c r="F1332" t="n">
-        <v>10800.2</v>
+        <v>10929.7</v>
       </c>
       <c r="G1332" t="n">
         <v>7</v>
@@ -44416,16 +44416,16 @@
         <v>57.4</v>
       </c>
       <c r="E1333" t="n">
-        <v>898.4</v>
+        <v>1036.1</v>
       </c>
       <c r="F1333" t="n">
-        <v>10563</v>
+        <v>10700.7</v>
       </c>
       <c r="G1333" t="n">
         <v>8</v>
       </c>
       <c r="H1333" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I1333" t="n">
         <v>5</v>
@@ -44449,16 +44449,16 @@
         <v>83.40000000000001</v>
       </c>
       <c r="E1334" t="n">
-        <v>944.6</v>
+        <v>1119.8</v>
       </c>
       <c r="F1334" t="n">
-        <v>11879.4</v>
+        <v>12054.6</v>
       </c>
       <c r="G1334" t="n">
         <v>3</v>
       </c>
       <c r="H1334" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1334" t="n">
         <v>1</v>
@@ -44482,10 +44482,10 @@
         <v>74.3</v>
       </c>
       <c r="E1335" t="n">
-        <v>768.3</v>
+        <v>884.8</v>
       </c>
       <c r="F1335" t="n">
-        <v>9602.200000000001</v>
+        <v>9718.700000000001</v>
       </c>
       <c r="G1335" t="n">
         <v>4</v>
@@ -44515,16 +44515,16 @@
         <v>72</v>
       </c>
       <c r="E1336" t="n">
-        <v>899.9000000000001</v>
+        <v>1004.8</v>
       </c>
       <c r="F1336" t="n">
-        <v>10504</v>
+        <v>10608.9</v>
       </c>
       <c r="G1336" t="n">
         <v>5</v>
       </c>
       <c r="H1336" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I1336" t="n">
         <v>6</v>
@@ -44548,10 +44548,10 @@
         <v>87.09999999999999</v>
       </c>
       <c r="E1337" t="n">
-        <v>921.2</v>
+        <v>1060.2</v>
       </c>
       <c r="F1337" t="n">
-        <v>8456.200000000001</v>
+        <v>8595.200000000001</v>
       </c>
       <c r="G1337" t="n">
         <v>2</v>
@@ -44581,10 +44581,10 @@
         <v>61.2</v>
       </c>
       <c r="E1338" t="n">
-        <v>921.5</v>
+        <v>1051.6</v>
       </c>
       <c r="F1338" t="n">
-        <v>11632.6</v>
+        <v>11762.7</v>
       </c>
       <c r="G1338" t="n">
         <v>5</v>
@@ -44614,10 +44614,10 @@
         <v>55.59999999999999</v>
       </c>
       <c r="E1339" t="n">
-        <v>1003.4</v>
+        <v>1140.4</v>
       </c>
       <c r="F1339" t="n">
-        <v>11694.4</v>
+        <v>11831.4</v>
       </c>
       <c r="G1339" t="n">
         <v>7</v>
@@ -44647,10 +44647,10 @@
         <v>50.59999999999999</v>
       </c>
       <c r="E1340" t="n">
-        <v>985.7</v>
+        <v>1115.2</v>
       </c>
       <c r="F1340" t="n">
-        <v>10850.8</v>
+        <v>10980.3</v>
       </c>
       <c r="G1340" t="n">
         <v>8</v>
@@ -44680,16 +44680,16 @@
         <v>62.40000000000001</v>
       </c>
       <c r="E1341" t="n">
-        <v>960.8000000000001</v>
+        <v>1098.5</v>
       </c>
       <c r="F1341" t="n">
-        <v>10625.4</v>
+        <v>10763.1</v>
       </c>
       <c r="G1341" t="n">
         <v>4</v>
       </c>
       <c r="H1341" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I1341" t="n">
         <v>5</v>
@@ -44713,10 +44713,10 @@
         <v>81.90000000000001</v>
       </c>
       <c r="E1342" t="n">
-        <v>1026.5</v>
+        <v>1201.7</v>
       </c>
       <c r="F1342" t="n">
-        <v>11961.3</v>
+        <v>12136.5</v>
       </c>
       <c r="G1342" t="n">
         <v>2</v>
@@ -44746,10 +44746,10 @@
         <v>63.3</v>
       </c>
       <c r="E1343" t="n">
-        <v>831.6</v>
+        <v>948.1</v>
       </c>
       <c r="F1343" t="n">
-        <v>9665.5</v>
+        <v>9782</v>
       </c>
       <c r="G1343" t="n">
         <v>3</v>
@@ -44779,16 +44779,16 @@
         <v>86</v>
       </c>
       <c r="E1344" t="n">
-        <v>985.9000000000001</v>
+        <v>1090.8</v>
       </c>
       <c r="F1344" t="n">
-        <v>10590</v>
+        <v>10694.9</v>
       </c>
       <c r="G1344" t="n">
         <v>1</v>
       </c>
       <c r="H1344" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I1344" t="n">
         <v>6</v>
@@ -44812,16 +44812,16 @@
         <v>58.1</v>
       </c>
       <c r="E1345" t="n">
-        <v>979.3</v>
+        <v>1118.3</v>
       </c>
       <c r="F1345" t="n">
-        <v>8514.299999999999</v>
+        <v>8653.299999999999</v>
       </c>
       <c r="G1345" t="n">
         <v>6</v>
       </c>
       <c r="H1345" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I1345" t="n">
         <v>8</v>
@@ -44845,10 +44845,10 @@
         <v>64.2</v>
       </c>
       <c r="E1346" t="n">
-        <v>985.7</v>
+        <v>1115.8</v>
       </c>
       <c r="F1346" t="n">
-        <v>11696.8</v>
+        <v>11826.9</v>
       </c>
       <c r="G1346" t="n">
         <v>5</v>
@@ -44878,10 +44878,10 @@
         <v>88.7</v>
       </c>
       <c r="E1347" t="n">
-        <v>1092.1</v>
+        <v>1229.1</v>
       </c>
       <c r="F1347" t="n">
-        <v>11783.1</v>
+        <v>11920.1</v>
       </c>
       <c r="G1347" t="n">
         <v>1</v>
@@ -44911,10 +44911,10 @@
         <v>76.8</v>
       </c>
       <c r="E1348" t="n">
-        <v>1062.5</v>
+        <v>1192</v>
       </c>
       <c r="F1348" t="n">
-        <v>10927.6</v>
+        <v>11057.1</v>
       </c>
       <c r="G1348" t="n">
         <v>3</v>
@@ -44944,10 +44944,10 @@
         <v>45</v>
       </c>
       <c r="E1349" t="n">
-        <v>1005.8</v>
+        <v>1143.5</v>
       </c>
       <c r="F1349" t="n">
-        <v>10670.4</v>
+        <v>10808.1</v>
       </c>
       <c r="G1349" t="n">
         <v>8</v>
@@ -44977,10 +44977,10 @@
         <v>81.2</v>
       </c>
       <c r="E1350" t="n">
-        <v>1107.7</v>
+        <v>1282.9</v>
       </c>
       <c r="F1350" t="n">
-        <v>12042.5</v>
+        <v>12217.7</v>
       </c>
       <c r="G1350" t="n">
         <v>2</v>
@@ -45010,10 +45010,10 @@
         <v>63.7</v>
       </c>
       <c r="E1351" t="n">
-        <v>895.3</v>
+        <v>1011.8</v>
       </c>
       <c r="F1351" t="n">
-        <v>9729.200000000001</v>
+        <v>9845.700000000001</v>
       </c>
       <c r="G1351" t="n">
         <v>6</v>
@@ -45043,16 +45043,16 @@
         <v>67.7</v>
       </c>
       <c r="E1352" t="n">
-        <v>1053.6</v>
+        <v>1158.5</v>
       </c>
       <c r="F1352" t="n">
-        <v>10657.7</v>
+        <v>10762.6</v>
       </c>
       <c r="G1352" t="n">
         <v>4</v>
       </c>
       <c r="H1352" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I1352" t="n">
         <v>6</v>
@@ -45076,16 +45076,16 @@
         <v>60.2</v>
       </c>
       <c r="E1353" t="n">
-        <v>1039.5</v>
+        <v>1178.5</v>
       </c>
       <c r="F1353" t="n">
-        <v>8574.5</v>
+        <v>8713.5</v>
       </c>
       <c r="G1353" t="n">
         <v>7</v>
       </c>
       <c r="H1353" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I1353" t="n">
         <v>8</v>
@@ -45109,10 +45109,10 @@
         <v>88.09999999999999</v>
       </c>
       <c r="E1354" t="n">
-        <v>1073.8</v>
+        <v>1203.9</v>
       </c>
       <c r="F1354" t="n">
-        <v>11784.9</v>
+        <v>11915</v>
       </c>
       <c r="G1354" t="n">
         <v>3</v>
@@ -45142,10 +45142,10 @@
         <v>59.9</v>
       </c>
       <c r="E1355" t="n">
-        <v>1152</v>
+        <v>1289</v>
       </c>
       <c r="F1355" t="n">
-        <v>11843</v>
+        <v>11980</v>
       </c>
       <c r="G1355" t="n">
         <v>6</v>
@@ -45175,16 +45175,16 @@
         <v>70.2</v>
       </c>
       <c r="E1356" t="n">
-        <v>1132.7</v>
+        <v>1262.2</v>
       </c>
       <c r="F1356" t="n">
-        <v>10997.8</v>
+        <v>11127.3</v>
       </c>
       <c r="G1356" t="n">
         <v>4</v>
       </c>
       <c r="H1356" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1356" t="n">
         <v>4</v>
@@ -45208,10 +45208,10 @@
         <v>0</v>
       </c>
       <c r="E1357" t="n">
-        <v>1005.8</v>
+        <v>1143.5</v>
       </c>
       <c r="F1357" t="n">
-        <v>10670.4</v>
+        <v>10808.1</v>
       </c>
       <c r="G1357" t="n">
         <v>8</v>
@@ -45241,10 +45241,10 @@
         <v>94</v>
       </c>
       <c r="E1358" t="n">
-        <v>1201.7</v>
+        <v>1376.9</v>
       </c>
       <c r="F1358" t="n">
-        <v>12136.5</v>
+        <v>12311.7</v>
       </c>
       <c r="G1358" t="n">
         <v>1</v>
@@ -45274,10 +45274,10 @@
         <v>61.6</v>
       </c>
       <c r="E1359" t="n">
-        <v>956.9</v>
+        <v>1073.4</v>
       </c>
       <c r="F1359" t="n">
-        <v>9790.799999999999</v>
+        <v>9907.299999999999</v>
       </c>
       <c r="G1359" t="n">
         <v>5</v>
@@ -45307,10 +45307,10 @@
         <v>58.6</v>
       </c>
       <c r="E1360" t="n">
-        <v>1112.2</v>
+        <v>1217.1</v>
       </c>
       <c r="F1360" t="n">
-        <v>10716.3</v>
+        <v>10821.2</v>
       </c>
       <c r="G1360" t="n">
         <v>7</v>
@@ -45340,16 +45340,16 @@
         <v>89.5</v>
       </c>
       <c r="E1361" t="n">
-        <v>1129</v>
+        <v>1268</v>
       </c>
       <c r="F1361" t="n">
-        <v>8664</v>
+        <v>8803</v>
       </c>
       <c r="G1361" t="n">
         <v>2</v>
       </c>
       <c r="H1361" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1361" t="n">
         <v>8</v>
@@ -45373,10 +45373,10 @@
         <v>66.7</v>
       </c>
       <c r="E1362" t="n">
-        <v>1140.5</v>
+        <v>1270.6</v>
       </c>
       <c r="F1362" t="n">
-        <v>11851.6</v>
+        <v>11981.7</v>
       </c>
       <c r="G1362" t="n">
         <v>4</v>
@@ -45406,16 +45406,16 @@
         <v>35.8</v>
       </c>
       <c r="E1363" t="n">
-        <v>1187.8</v>
+        <v>1324.8</v>
       </c>
       <c r="F1363" t="n">
-        <v>11878.8</v>
+        <v>12015.8</v>
       </c>
       <c r="G1363" t="n">
         <v>8</v>
       </c>
       <c r="H1363" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I1363" t="n">
         <v>2</v>
@@ -45439,16 +45439,16 @@
         <v>59.2</v>
       </c>
       <c r="E1364" t="n">
-        <v>1191.9</v>
+        <v>1321.4</v>
       </c>
       <c r="F1364" t="n">
-        <v>11057</v>
+        <v>11186.5</v>
       </c>
       <c r="G1364" t="n">
         <v>6</v>
       </c>
       <c r="H1364" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1364" t="n">
         <v>4</v>
@@ -45472,10 +45472,10 @@
         <v>82.2</v>
       </c>
       <c r="E1365" t="n">
-        <v>1088</v>
+        <v>1225.7</v>
       </c>
       <c r="F1365" t="n">
-        <v>10752.6</v>
+        <v>10890.3</v>
       </c>
       <c r="G1365" t="n">
         <v>2</v>
@@ -45505,10 +45505,10 @@
         <v>63</v>
       </c>
       <c r="E1366" t="n">
-        <v>1264.7</v>
+        <v>1439.9</v>
       </c>
       <c r="F1366" t="n">
-        <v>12199.5</v>
+        <v>12374.7</v>
       </c>
       <c r="G1366" t="n">
         <v>5</v>
@@ -45538,10 +45538,10 @@
         <v>56.6</v>
       </c>
       <c r="E1367" t="n">
-        <v>1013.5</v>
+        <v>1130</v>
       </c>
       <c r="F1367" t="n">
-        <v>9847.4</v>
+        <v>9963.9</v>
       </c>
       <c r="G1367" t="n">
         <v>7</v>
@@ -45571,16 +45571,16 @@
         <v>78.59999999999999</v>
       </c>
       <c r="E1368" t="n">
-        <v>1190.8</v>
+        <v>1295.7</v>
       </c>
       <c r="F1368" t="n">
-        <v>10794.9</v>
+        <v>10899.8</v>
       </c>
       <c r="G1368" t="n">
         <v>3</v>
       </c>
       <c r="H1368" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I1368" t="n">
         <v>5</v>
@@ -45604,10 +45604,10 @@
         <v>87.3</v>
       </c>
       <c r="E1369" t="n">
-        <v>1216.3</v>
+        <v>1355.3</v>
       </c>
       <c r="F1369" t="n">
-        <v>8751.299999999999</v>
+        <v>8890.299999999999</v>
       </c>
       <c r="G1369" t="n">
         <v>1</v>
@@ -45637,10 +45637,10 @@
         <v>70.8</v>
       </c>
       <c r="E1370" t="n">
-        <v>1211.3</v>
+        <v>1341.4</v>
       </c>
       <c r="F1370" t="n">
-        <v>11922.4</v>
+        <v>12052.5</v>
       </c>
       <c r="G1370" t="n">
         <v>4</v>
@@ -45670,16 +45670,16 @@
         <v>76.5</v>
       </c>
       <c r="E1371" t="n">
-        <v>1264.3</v>
+        <v>1401.3</v>
       </c>
       <c r="F1371" t="n">
-        <v>11955.3</v>
+        <v>12092.3</v>
       </c>
       <c r="G1371" t="n">
         <v>2</v>
       </c>
       <c r="H1371" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1371" t="n">
         <v>2</v>
@@ -45703,16 +45703,16 @@
         <v>75.2</v>
       </c>
       <c r="E1372" t="n">
-        <v>1267.1</v>
+        <v>1396.6</v>
       </c>
       <c r="F1372" t="n">
-        <v>11132.2</v>
+        <v>11261.7</v>
       </c>
       <c r="G1372" t="n">
         <v>3</v>
       </c>
       <c r="H1372" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1372" t="n">
         <v>4</v>
@@ -45736,10 +45736,10 @@
         <v>46.7</v>
       </c>
       <c r="E1373" t="n">
-        <v>1134.7</v>
+        <v>1272.4</v>
       </c>
       <c r="F1373" t="n">
-        <v>10799.3</v>
+        <v>10937</v>
       </c>
       <c r="G1373" t="n">
         <v>8</v>
@@ -45769,10 +45769,10 @@
         <v>79.40000000000001</v>
       </c>
       <c r="E1374" t="n">
-        <v>1344.1</v>
+        <v>1519.3</v>
       </c>
       <c r="F1374" t="n">
-        <v>12278.9</v>
+        <v>12454.1</v>
       </c>
       <c r="G1374" t="n">
         <v>1</v>
@@ -45802,10 +45802,10 @@
         <v>56.59999999999999</v>
       </c>
       <c r="E1375" t="n">
-        <v>1070.1</v>
+        <v>1186.6</v>
       </c>
       <c r="F1375" t="n">
-        <v>9904</v>
+        <v>10020.5</v>
       </c>
       <c r="G1375" t="n">
         <v>6</v>
@@ -45835,10 +45835,10 @@
         <v>65.2</v>
       </c>
       <c r="E1376" t="n">
-        <v>1256</v>
+        <v>1360.9</v>
       </c>
       <c r="F1376" t="n">
-        <v>10860.1</v>
+        <v>10965</v>
       </c>
       <c r="G1376" t="n">
         <v>5</v>
@@ -45868,10 +45868,10 @@
         <v>54.8</v>
       </c>
       <c r="E1377" t="n">
-        <v>1271.1</v>
+        <v>1410.1</v>
       </c>
       <c r="F1377" t="n">
-        <v>8806.1</v>
+        <v>8945.1</v>
       </c>
       <c r="G1377" t="n">
         <v>7</v>
@@ -45901,16 +45901,16 @@
         <v>93.8</v>
       </c>
       <c r="E1378" t="n">
-        <v>1305.1</v>
+        <v>1435.2</v>
       </c>
       <c r="F1378" t="n">
-        <v>12016.2</v>
+        <v>12146.3</v>
       </c>
       <c r="G1378" t="n">
         <v>2</v>
       </c>
       <c r="H1378" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I1378" t="n">
         <v>3</v>
@@ -45934,10 +45934,10 @@
         <v>65.2</v>
       </c>
       <c r="E1379" t="n">
-        <v>1329.5</v>
+        <v>1466.5</v>
       </c>
       <c r="F1379" t="n">
-        <v>12020.5</v>
+        <v>12157.5</v>
       </c>
       <c r="G1379" t="n">
         <v>7</v>
@@ -45967,10 +45967,10 @@
         <v>97.59999999999999</v>
       </c>
       <c r="E1380" t="n">
-        <v>1364.7</v>
+        <v>1494.2</v>
       </c>
       <c r="F1380" t="n">
-        <v>11229.8</v>
+        <v>11359.3</v>
       </c>
       <c r="G1380" t="n">
         <v>1</v>
@@ -46000,10 +46000,10 @@
         <v>63.3</v>
       </c>
       <c r="E1381" t="n">
-        <v>1198</v>
+        <v>1335.7</v>
       </c>
       <c r="F1381" t="n">
-        <v>10862.6</v>
+        <v>11000.3</v>
       </c>
       <c r="G1381" t="n">
         <v>8</v>
@@ -46033,10 +46033,10 @@
         <v>79.3</v>
       </c>
       <c r="E1382" t="n">
-        <v>1423.4</v>
+        <v>1598.6</v>
       </c>
       <c r="F1382" t="n">
-        <v>12358.2</v>
+        <v>12533.4</v>
       </c>
       <c r="G1382" t="n">
         <v>5</v>
@@ -46066,10 +46066,10 @@
         <v>81.7</v>
       </c>
       <c r="E1383" t="n">
-        <v>1151.8</v>
+        <v>1268.3</v>
       </c>
       <c r="F1383" t="n">
-        <v>9985.700000000001</v>
+        <v>10102.2</v>
       </c>
       <c r="G1383" t="n">
         <v>4</v>
@@ -46099,16 +46099,16 @@
         <v>67.40000000000001</v>
       </c>
       <c r="E1384" t="n">
-        <v>1323.4</v>
+        <v>1428.3</v>
       </c>
       <c r="F1384" t="n">
-        <v>10927.5</v>
+        <v>11032.4</v>
       </c>
       <c r="G1384" t="n">
         <v>6</v>
       </c>
       <c r="H1384" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I1384" t="n">
         <v>5</v>
@@ -46132,10 +46132,10 @@
         <v>82.59999999999999</v>
       </c>
       <c r="E1385" t="n">
-        <v>1353.7</v>
+        <v>1492.7</v>
       </c>
       <c r="F1385" t="n">
-        <v>8888.700000000001</v>
+        <v>9027.700000000001</v>
       </c>
       <c r="G1385" t="n">
         <v>3</v>
@@ -46165,10 +46165,10 @@
         <v>100.5</v>
       </c>
       <c r="E1386" t="n">
-        <v>1405.6</v>
+        <v>1535.7</v>
       </c>
       <c r="F1386" t="n">
-        <v>12116.7</v>
+        <v>12246.8</v>
       </c>
       <c r="G1386" t="n">
         <v>1</v>
@@ -46198,10 +46198,10 @@
         <v>80.3</v>
       </c>
       <c r="E1387" t="n">
-        <v>1409.8</v>
+        <v>1546.8</v>
       </c>
       <c r="F1387" t="n">
-        <v>12100.8</v>
+        <v>12237.8</v>
       </c>
       <c r="G1387" t="n">
         <v>2</v>
@@ -46231,10 +46231,10 @@
         <v>60.3</v>
       </c>
       <c r="E1388" t="n">
-        <v>1425</v>
+        <v>1554.5</v>
       </c>
       <c r="F1388" t="n">
-        <v>11290.1</v>
+        <v>11419.6</v>
       </c>
       <c r="G1388" t="n">
         <v>6</v>
@@ -46264,10 +46264,10 @@
         <v>67.59999999999999</v>
       </c>
       <c r="E1389" t="n">
-        <v>1265.6</v>
+        <v>1403.3</v>
       </c>
       <c r="F1389" t="n">
-        <v>10930.2</v>
+        <v>11067.9</v>
       </c>
       <c r="G1389" t="n">
         <v>4</v>
@@ -46297,10 +46297,10 @@
         <v>70.2</v>
       </c>
       <c r="E1390" t="n">
-        <v>1493.6</v>
+        <v>1668.8</v>
       </c>
       <c r="F1390" t="n">
-        <v>12428.4</v>
+        <v>12603.6</v>
       </c>
       <c r="G1390" t="n">
         <v>3</v>
@@ -46330,10 +46330,10 @@
         <v>61.2</v>
       </c>
       <c r="E1391" t="n">
-        <v>1213</v>
+        <v>1329.5</v>
       </c>
       <c r="F1391" t="n">
-        <v>10046.9</v>
+        <v>10163.4</v>
       </c>
       <c r="G1391" t="n">
         <v>5</v>
@@ -46363,10 +46363,10 @@
         <v>50.8</v>
       </c>
       <c r="E1392" t="n">
-        <v>1374.2</v>
+        <v>1479.1</v>
       </c>
       <c r="F1392" t="n">
-        <v>10978.3</v>
+        <v>11083.2</v>
       </c>
       <c r="G1392" t="n">
         <v>8</v>
@@ -46396,10 +46396,10 @@
         <v>58.9</v>
       </c>
       <c r="E1393" t="n">
-        <v>1412.6</v>
+        <v>1551.6</v>
       </c>
       <c r="F1393" t="n">
-        <v>8947.6</v>
+        <v>9086.6</v>
       </c>
       <c r="G1393" t="n">
         <v>7</v>
@@ -46429,10 +46429,10 @@
         <v>92</v>
       </c>
       <c r="E1394" t="n">
-        <v>1497.6</v>
+        <v>1627.7</v>
       </c>
       <c r="F1394" t="n">
-        <v>12208.7</v>
+        <v>12338.8</v>
       </c>
       <c r="G1394" t="n">
         <v>2</v>
@@ -46462,16 +46462,16 @@
         <v>77.2</v>
       </c>
       <c r="E1395" t="n">
-        <v>1487</v>
+        <v>1624</v>
       </c>
       <c r="F1395" t="n">
-        <v>12178</v>
+        <v>12315</v>
       </c>
       <c r="G1395" t="n">
         <v>4</v>
       </c>
       <c r="H1395" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I1395" t="n">
         <v>3</v>
@@ -46495,10 +46495,10 @@
         <v>80.3</v>
       </c>
       <c r="E1396" t="n">
-        <v>1505.3</v>
+        <v>1634.8</v>
       </c>
       <c r="F1396" t="n">
-        <v>11370.4</v>
+        <v>11499.9</v>
       </c>
       <c r="G1396" t="n">
         <v>3</v>
@@ -46528,10 +46528,10 @@
         <v>50.6</v>
       </c>
       <c r="E1397" t="n">
-        <v>1316.2</v>
+        <v>1453.9</v>
       </c>
       <c r="F1397" t="n">
-        <v>10980.8</v>
+        <v>11118.5</v>
       </c>
       <c r="G1397" t="n">
         <v>7</v>
@@ -46561,10 +46561,10 @@
         <v>76.7</v>
       </c>
       <c r="E1398" t="n">
-        <v>1570.3</v>
+        <v>1745.5</v>
       </c>
       <c r="F1398" t="n">
-        <v>12505.1</v>
+        <v>12680.3</v>
       </c>
       <c r="G1398" t="n">
         <v>5</v>
@@ -46594,10 +46594,10 @@
         <v>48.7</v>
       </c>
       <c r="E1399" t="n">
-        <v>1261.7</v>
+        <v>1378.2</v>
       </c>
       <c r="F1399" t="n">
-        <v>10095.6</v>
+        <v>10212.1</v>
       </c>
       <c r="G1399" t="n">
         <v>8</v>
@@ -46627,10 +46627,10 @@
         <v>92.5</v>
       </c>
       <c r="E1400" t="n">
-        <v>1466.7</v>
+        <v>1571.6</v>
       </c>
       <c r="F1400" t="n">
-        <v>11070.8</v>
+        <v>11175.7</v>
       </c>
       <c r="G1400" t="n">
         <v>1</v>
@@ -46660,16 +46660,16 @@
         <v>73.10000000000001</v>
       </c>
       <c r="E1401" t="n">
-        <v>1485.7</v>
+        <v>1624.7</v>
       </c>
       <c r="F1401" t="n">
-        <v>9020.700000000001</v>
+        <v>9159.700000000001</v>
       </c>
       <c r="G1401" t="n">
         <v>6</v>
       </c>
       <c r="H1401" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I1401" t="n">
         <v>8</v>
@@ -46693,16 +46693,16 @@
         <v>75.59999999999999</v>
       </c>
       <c r="E1402" t="n">
-        <v>1573.2</v>
+        <v>1703.3</v>
       </c>
       <c r="F1402" t="n">
-        <v>12284.3</v>
+        <v>12414.4</v>
       </c>
       <c r="G1402" t="n">
         <v>3</v>
       </c>
       <c r="H1402" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I1402" t="n">
         <v>2</v>
@@ -46726,16 +46726,16 @@
         <v>84.09999999999999</v>
       </c>
       <c r="E1403" t="n">
-        <v>1571.1</v>
+        <v>1708.1</v>
       </c>
       <c r="F1403" t="n">
-        <v>12262.1</v>
+        <v>12399.1</v>
       </c>
       <c r="G1403" t="n">
         <v>1</v>
       </c>
       <c r="H1403" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I1403" t="n">
         <v>3</v>
@@ -46759,10 +46759,10 @@
         <v>59.3</v>
       </c>
       <c r="E1404" t="n">
-        <v>1564.6</v>
+        <v>1694.1</v>
       </c>
       <c r="F1404" t="n">
-        <v>11429.7</v>
+        <v>11559.2</v>
       </c>
       <c r="G1404" t="n">
         <v>8</v>
@@ -46792,10 +46792,10 @@
         <v>71.5</v>
       </c>
       <c r="E1405" t="n">
-        <v>1387.7</v>
+        <v>1525.4</v>
       </c>
       <c r="F1405" t="n">
-        <v>11052.3</v>
+        <v>11190</v>
       </c>
       <c r="G1405" t="n">
         <v>6</v>
@@ -46825,10 +46825,10 @@
         <v>75.39999999999999</v>
       </c>
       <c r="E1406" t="n">
-        <v>1645.7</v>
+        <v>1820.9</v>
       </c>
       <c r="F1406" t="n">
-        <v>12580.5</v>
+        <v>12755.7</v>
       </c>
       <c r="G1406" t="n">
         <v>4</v>
@@ -46858,10 +46858,10 @@
         <v>62.7</v>
       </c>
       <c r="E1407" t="n">
-        <v>1324.4</v>
+        <v>1440.9</v>
       </c>
       <c r="F1407" t="n">
-        <v>10158.3</v>
+        <v>10274.8</v>
       </c>
       <c r="G1407" t="n">
         <v>7</v>
@@ -46891,10 +46891,10 @@
         <v>72</v>
       </c>
       <c r="E1408" t="n">
-        <v>1538.7</v>
+        <v>1643.6</v>
       </c>
       <c r="F1408" t="n">
-        <v>11142.8</v>
+        <v>11247.7</v>
       </c>
       <c r="G1408" t="n">
         <v>5</v>
@@ -46924,16 +46924,16 @@
         <v>79.09999999999999</v>
       </c>
       <c r="E1409" t="n">
-        <v>1564.8</v>
+        <v>1703.8</v>
       </c>
       <c r="F1409" t="n">
-        <v>9099.799999999999</v>
+        <v>9238.799999999999</v>
       </c>
       <c r="G1409" t="n">
         <v>2</v>
       </c>
       <c r="H1409" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1409" t="n">
         <v>8</v>
@@ -46957,16 +46957,16 @@
         <v>73.2</v>
       </c>
       <c r="E1410" t="n">
-        <v>1646.4</v>
+        <v>1776.5</v>
       </c>
       <c r="F1410" t="n">
-        <v>12357.5</v>
+        <v>12487.6</v>
       </c>
       <c r="G1410" t="n">
         <v>2</v>
       </c>
       <c r="H1410" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I1410" t="n">
         <v>2</v>
@@ -46990,10 +46990,10 @@
         <v>62.7</v>
       </c>
       <c r="E1411" t="n">
-        <v>1633.8</v>
+        <v>1770.8</v>
       </c>
       <c r="F1411" t="n">
-        <v>12324.8</v>
+        <v>12461.8</v>
       </c>
       <c r="G1411" t="n">
         <v>5</v>
@@ -47023,10 +47023,10 @@
         <v>49.2</v>
       </c>
       <c r="E1412" t="n">
-        <v>1613.8</v>
+        <v>1743.3</v>
       </c>
       <c r="F1412" t="n">
-        <v>11478.9</v>
+        <v>11608.4</v>
       </c>
       <c r="G1412" t="n">
         <v>6</v>
@@ -47056,10 +47056,10 @@
         <v>43.9</v>
       </c>
       <c r="E1413" t="n">
-        <v>1431.6</v>
+        <v>1569.3</v>
       </c>
       <c r="F1413" t="n">
-        <v>11096.2</v>
+        <v>11233.9</v>
       </c>
       <c r="G1413" t="n">
         <v>7</v>
@@ -47089,10 +47089,10 @@
         <v>71.2</v>
       </c>
       <c r="E1414" t="n">
-        <v>1716.9</v>
+        <v>1892.1</v>
       </c>
       <c r="F1414" t="n">
-        <v>12651.7</v>
+        <v>12826.9</v>
       </c>
       <c r="G1414" t="n">
         <v>3</v>
@@ -47122,10 +47122,10 @@
         <v>64.09999999999999</v>
       </c>
       <c r="E1415" t="n">
-        <v>1388.5</v>
+        <v>1505</v>
       </c>
       <c r="F1415" t="n">
-        <v>10222.4</v>
+        <v>10338.9</v>
       </c>
       <c r="G1415" t="n">
         <v>4</v>
@@ -47155,10 +47155,10 @@
         <v>42.9</v>
       </c>
       <c r="E1416" t="n">
-        <v>1581.6</v>
+        <v>1686.5</v>
       </c>
       <c r="F1416" t="n">
-        <v>11185.7</v>
+        <v>11290.6</v>
       </c>
       <c r="G1416" t="n">
         <v>8</v>
@@ -47188,16 +47188,16 @@
         <v>73.8</v>
       </c>
       <c r="E1417" t="n">
-        <v>1638.6</v>
+        <v>1777.6</v>
       </c>
       <c r="F1417" t="n">
-        <v>9173.6</v>
+        <v>9312.6</v>
       </c>
       <c r="G1417" t="n">
         <v>1</v>
       </c>
       <c r="H1417" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I1417" t="n">
         <v>8</v>
@@ -47221,10 +47221,10 @@
         <v>79.3</v>
       </c>
       <c r="E1418" t="n">
-        <v>1725.7</v>
+        <v>1855.8</v>
       </c>
       <c r="F1418" t="n">
-        <v>12436.8</v>
+        <v>12566.9</v>
       </c>
       <c r="G1418" t="n">
         <v>1</v>
@@ -47254,10 +47254,10 @@
         <v>62.3</v>
       </c>
       <c r="E1419" t="n">
-        <v>1696.1</v>
+        <v>1833.1</v>
       </c>
       <c r="F1419" t="n">
-        <v>12387.1</v>
+        <v>12524.1</v>
       </c>
       <c r="G1419" t="n">
         <v>4</v>
@@ -47287,10 +47287,10 @@
         <v>50.4</v>
       </c>
       <c r="E1420" t="n">
-        <v>1664.2</v>
+        <v>1793.7</v>
       </c>
       <c r="F1420" t="n">
-        <v>11529.3</v>
+        <v>11658.8</v>
       </c>
       <c r="G1420" t="n">
         <v>7</v>
@@ -47320,10 +47320,10 @@
         <v>48.8</v>
       </c>
       <c r="E1421" t="n">
-        <v>1480.4</v>
+        <v>1618.1</v>
       </c>
       <c r="F1421" t="n">
-        <v>11145</v>
+        <v>11282.7</v>
       </c>
       <c r="G1421" t="n">
         <v>8</v>
@@ -47353,10 +47353,10 @@
         <v>75</v>
       </c>
       <c r="E1422" t="n">
-        <v>1791.9</v>
+        <v>1967.1</v>
       </c>
       <c r="F1422" t="n">
-        <v>12726.7</v>
+        <v>12901.9</v>
       </c>
       <c r="G1422" t="n">
         <v>2</v>
@@ -47386,10 +47386,10 @@
         <v>64.5</v>
       </c>
       <c r="E1423" t="n">
-        <v>1453</v>
+        <v>1569.5</v>
       </c>
       <c r="F1423" t="n">
-        <v>10286.9</v>
+        <v>10403.4</v>
       </c>
       <c r="G1423" t="n">
         <v>3</v>
@@ -47419,10 +47419,10 @@
         <v>59.7</v>
       </c>
       <c r="E1424" t="n">
-        <v>1641.3</v>
+        <v>1746.2</v>
       </c>
       <c r="F1424" t="n">
-        <v>11245.4</v>
+        <v>11350.3</v>
       </c>
       <c r="G1424" t="n">
         <v>5</v>
@@ -47452,10 +47452,10 @@
         <v>57.7</v>
       </c>
       <c r="E1425" t="n">
-        <v>1696.3</v>
+        <v>1835.3</v>
       </c>
       <c r="F1425" t="n">
-        <v>9231.299999999999</v>
+        <v>9370.299999999999</v>
       </c>
       <c r="G1425" t="n">
         <v>6</v>
@@ -47485,10 +47485,10 @@
         <v>86.3</v>
       </c>
       <c r="E1426" t="n">
-        <v>1812</v>
+        <v>1942.1</v>
       </c>
       <c r="F1426" t="n">
-        <v>12523.1</v>
+        <v>12653.2</v>
       </c>
       <c r="G1426" t="n">
         <v>2</v>
@@ -47518,10 +47518,10 @@
         <v>75.59999999999999</v>
       </c>
       <c r="E1427" t="n">
-        <v>1771.7</v>
+        <v>1908.7</v>
       </c>
       <c r="F1427" t="n">
-        <v>12462.7</v>
+        <v>12599.7</v>
       </c>
       <c r="G1427" t="n">
         <v>3</v>
@@ -47551,10 +47551,10 @@
         <v>50.9</v>
       </c>
       <c r="E1428" t="n">
-        <v>1715.1</v>
+        <v>1844.6</v>
       </c>
       <c r="F1428" t="n">
-        <v>11580.2</v>
+        <v>11709.7</v>
       </c>
       <c r="G1428" t="n">
         <v>8</v>
@@ -47584,10 +47584,10 @@
         <v>65.3</v>
       </c>
       <c r="E1429" t="n">
-        <v>1545.7</v>
+        <v>1683.4</v>
       </c>
       <c r="F1429" t="n">
-        <v>11210.3</v>
+        <v>11348</v>
       </c>
       <c r="G1429" t="n">
         <v>4</v>
@@ -47617,10 +47617,10 @@
         <v>58.4</v>
       </c>
       <c r="E1430" t="n">
-        <v>1850.3</v>
+        <v>2025.5</v>
       </c>
       <c r="F1430" t="n">
-        <v>12785.1</v>
+        <v>12960.3</v>
       </c>
       <c r="G1430" t="n">
         <v>6</v>
@@ -47650,10 +47650,10 @@
         <v>58.6</v>
       </c>
       <c r="E1431" t="n">
-        <v>1511.6</v>
+        <v>1628.1</v>
       </c>
       <c r="F1431" t="n">
-        <v>10345.5</v>
+        <v>10462</v>
       </c>
       <c r="G1431" t="n">
         <v>5</v>
@@ -47683,10 +47683,10 @@
         <v>55.3</v>
       </c>
       <c r="E1432" t="n">
-        <v>1696.6</v>
+        <v>1801.5</v>
       </c>
       <c r="F1432" t="n">
-        <v>11300.7</v>
+        <v>11405.6</v>
       </c>
       <c r="G1432" t="n">
         <v>7</v>
@@ -47716,10 +47716,10 @@
         <v>96</v>
       </c>
       <c r="E1433" t="n">
-        <v>1792.3</v>
+        <v>1931.3</v>
       </c>
       <c r="F1433" t="n">
-        <v>9327.299999999999</v>
+        <v>9466.299999999999</v>
       </c>
       <c r="G1433" t="n">
         <v>1</v>
@@ -47749,10 +47749,10 @@
         <v>84.5</v>
       </c>
       <c r="E1434" t="n">
-        <v>1896.5</v>
+        <v>2026.6</v>
       </c>
       <c r="F1434" t="n">
-        <v>12607.6</v>
+        <v>12737.7</v>
       </c>
       <c r="G1434" t="n">
         <v>1</v>
@@ -47782,10 +47782,10 @@
         <v>66.59999999999999</v>
       </c>
       <c r="E1435" t="n">
-        <v>1838.3</v>
+        <v>1975.3</v>
       </c>
       <c r="F1435" t="n">
-        <v>12529.3</v>
+        <v>12666.3</v>
       </c>
       <c r="G1435" t="n">
         <v>4</v>
@@ -47815,10 +47815,10 @@
         <v>60.1</v>
       </c>
       <c r="E1436" t="n">
-        <v>1775.2</v>
+        <v>1904.7</v>
       </c>
       <c r="F1436" t="n">
-        <v>11640.3</v>
+        <v>11769.8</v>
       </c>
       <c r="G1436" t="n">
         <v>6</v>
@@ -47848,10 +47848,10 @@
         <v>74.09999999999999</v>
       </c>
       <c r="E1437" t="n">
-        <v>1619.8</v>
+        <v>1757.5</v>
       </c>
       <c r="F1437" t="n">
-        <v>11284.4</v>
+        <v>11422.1</v>
       </c>
       <c r="G1437" t="n">
         <v>3</v>
@@ -47881,10 +47881,10 @@
         <v>57.4</v>
       </c>
       <c r="E1438" t="n">
-        <v>1907.7</v>
+        <v>2082.9</v>
       </c>
       <c r="F1438" t="n">
-        <v>12842.5</v>
+        <v>13017.7</v>
       </c>
       <c r="G1438" t="n">
         <v>7</v>
@@ -47914,10 +47914,10 @@
         <v>0</v>
       </c>
       <c r="E1439" t="n">
-        <v>1511.6</v>
+        <v>1628.1</v>
       </c>
       <c r="F1439" t="n">
-        <v>10345.5</v>
+        <v>10462</v>
       </c>
       <c r="G1439" t="n">
         <v>8</v>
@@ -47947,10 +47947,10 @@
         <v>65.90000000000001</v>
       </c>
       <c r="E1440" t="n">
-        <v>1762.5</v>
+        <v>1867.4</v>
       </c>
       <c r="F1440" t="n">
-        <v>11366.6</v>
+        <v>11471.5</v>
       </c>
       <c r="G1440" t="n">
         <v>5</v>
@@ -47980,10 +47980,10 @@
         <v>76</v>
       </c>
       <c r="E1441" t="n">
-        <v>1868.3</v>
+        <v>2007.3</v>
       </c>
       <c r="F1441" t="n">
-        <v>9403.299999999999</v>
+        <v>9542.299999999999</v>
       </c>
       <c r="G1441" t="n">
         <v>2</v>
@@ -48013,16 +48013,16 @@
         <v>73.09999999999999</v>
       </c>
       <c r="E1442" t="n">
-        <v>1969.6</v>
+        <v>2099.7</v>
       </c>
       <c r="F1442" t="n">
-        <v>12680.7</v>
+        <v>12810.8</v>
       </c>
       <c r="G1442" t="n">
         <v>6</v>
       </c>
       <c r="H1442" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I1442" t="n">
         <v>2</v>
@@ -48046,10 +48046,10 @@
         <v>92.90000000000001</v>
       </c>
       <c r="E1443" t="n">
-        <v>1931.2</v>
+        <v>2068.2</v>
       </c>
       <c r="F1443" t="n">
-        <v>12622.2</v>
+        <v>12759.2</v>
       </c>
       <c r="G1443" t="n">
         <v>2</v>
@@ -48079,16 +48079,16 @@
         <v>51.6</v>
       </c>
       <c r="E1444" t="n">
-        <v>1826.8</v>
+        <v>1956.3</v>
       </c>
       <c r="F1444" t="n">
-        <v>11691.9</v>
+        <v>11821.4</v>
       </c>
       <c r="G1444" t="n">
         <v>8</v>
       </c>
       <c r="H1444" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I1444" t="n">
         <v>4</v>
@@ -48112,10 +48112,10 @@
         <v>62.1</v>
       </c>
       <c r="E1445" t="n">
-        <v>1681.9</v>
+        <v>1819.6</v>
       </c>
       <c r="F1445" t="n">
-        <v>11346.5</v>
+        <v>11484.2</v>
       </c>
       <c r="G1445" t="n">
         <v>7</v>
@@ -48145,10 +48145,10 @@
         <v>86.7</v>
       </c>
       <c r="E1446" t="n">
-        <v>1994.4</v>
+        <v>2169.6</v>
       </c>
       <c r="F1446" t="n">
-        <v>12929.2</v>
+        <v>13104.4</v>
       </c>
       <c r="G1446" t="n">
         <v>4</v>
@@ -48178,10 +48178,10 @@
         <v>88.2</v>
       </c>
       <c r="E1447" t="n">
-        <v>1599.8</v>
+        <v>1716.3</v>
       </c>
       <c r="F1447" t="n">
-        <v>10433.7</v>
+        <v>10550.2</v>
       </c>
       <c r="G1447" t="n">
         <v>3</v>
@@ -48211,16 +48211,16 @@
         <v>73.3</v>
       </c>
       <c r="E1448" t="n">
-        <v>1835.8</v>
+        <v>1940.7</v>
       </c>
       <c r="F1448" t="n">
-        <v>11439.9</v>
+        <v>11544.8</v>
       </c>
       <c r="G1448" t="n">
         <v>5</v>
       </c>
       <c r="H1448" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I1448" t="n">
         <v>5</v>
@@ -48244,16 +48244,16 @@
         <v>100.9</v>
       </c>
       <c r="E1449" t="n">
-        <v>1969.2</v>
+        <v>2108.2</v>
       </c>
       <c r="F1449" t="n">
-        <v>9504.200000000001</v>
+        <v>9643.200000000001</v>
       </c>
       <c r="G1449" t="n">
         <v>1</v>
       </c>
       <c r="H1449" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I1449" t="n">
         <v>8</v>
@@ -48277,16 +48277,16 @@
         <v>82.5</v>
       </c>
       <c r="E1450" t="n">
-        <v>2052.1</v>
+        <v>2182.2</v>
       </c>
       <c r="F1450" t="n">
-        <v>12763.2</v>
+        <v>12893.3</v>
       </c>
       <c r="G1450" t="n">
         <v>3</v>
       </c>
       <c r="H1450" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1450" t="n">
         <v>2</v>
@@ -48310,10 +48310,10 @@
         <v>73.5</v>
       </c>
       <c r="E1451" t="n">
-        <v>2004.7</v>
+        <v>2141.7</v>
       </c>
       <c r="F1451" t="n">
-        <v>12695.7</v>
+        <v>12832.7</v>
       </c>
       <c r="G1451" t="n">
         <v>4</v>
@@ -48343,10 +48343,10 @@
         <v>114.5</v>
       </c>
       <c r="E1452" t="n">
-        <v>1941.3</v>
+        <v>2070.8</v>
       </c>
       <c r="F1452" t="n">
-        <v>11806.4</v>
+        <v>11935.9</v>
       </c>
       <c r="G1452" t="n">
         <v>1</v>
@@ -48376,10 +48376,10 @@
         <v>85.90000000000001</v>
       </c>
       <c r="E1453" t="n">
-        <v>1767.8</v>
+        <v>1905.5</v>
       </c>
       <c r="F1453" t="n">
-        <v>11432.4</v>
+        <v>11570.1</v>
       </c>
       <c r="G1453" t="n">
         <v>2</v>
@@ -48409,16 +48409,16 @@
         <v>48.6</v>
       </c>
       <c r="E1454" t="n">
-        <v>2043</v>
+        <v>2218.2</v>
       </c>
       <c r="F1454" t="n">
-        <v>12977.8</v>
+        <v>13153</v>
       </c>
       <c r="G1454" t="n">
         <v>6</v>
       </c>
       <c r="H1454" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1454" t="n">
         <v>1</v>
@@ -48442,10 +48442,10 @@
         <v>52.8</v>
       </c>
       <c r="E1455" t="n">
-        <v>1652.6</v>
+        <v>1769.1</v>
       </c>
       <c r="F1455" t="n">
-        <v>10486.5</v>
+        <v>10603</v>
       </c>
       <c r="G1455" t="n">
         <v>5</v>
@@ -48475,10 +48475,10 @@
         <v>47.9</v>
       </c>
       <c r="E1456" t="n">
-        <v>1883.7</v>
+        <v>1988.6</v>
       </c>
       <c r="F1456" t="n">
-        <v>11487.8</v>
+        <v>11592.7</v>
       </c>
       <c r="G1456" t="n">
         <v>7</v>
@@ -48508,10 +48508,10 @@
         <v>43.3</v>
       </c>
       <c r="E1457" t="n">
-        <v>2012.5</v>
+        <v>2151.5</v>
       </c>
       <c r="F1457" t="n">
-        <v>9547.5</v>
+        <v>9686.5</v>
       </c>
       <c r="G1457" t="n">
         <v>8</v>
@@ -48541,10 +48541,10 @@
         <v>66.5</v>
       </c>
       <c r="E1458" t="n">
-        <v>2118.6</v>
+        <v>2248.7</v>
       </c>
       <c r="F1458" t="n">
-        <v>12829.7</v>
+        <v>12959.8</v>
       </c>
       <c r="G1458" t="n">
         <v>5</v>
@@ -48574,10 +48574,10 @@
         <v>65.5</v>
       </c>
       <c r="E1459" t="n">
-        <v>2070.2</v>
+        <v>2207.2</v>
       </c>
       <c r="F1459" t="n">
-        <v>12761.2</v>
+        <v>12898.2</v>
       </c>
       <c r="G1459" t="n">
         <v>7</v>
@@ -48607,10 +48607,10 @@
         <v>83.90000000000001</v>
       </c>
       <c r="E1460" t="n">
-        <v>2025.2</v>
+        <v>2154.7</v>
       </c>
       <c r="F1460" t="n">
-        <v>11890.3</v>
+        <v>12019.8</v>
       </c>
       <c r="G1460" t="n">
         <v>3</v>
@@ -48640,10 +48640,10 @@
         <v>66.40000000000001</v>
       </c>
       <c r="E1461" t="n">
-        <v>1834.2</v>
+        <v>1971.9</v>
       </c>
       <c r="F1461" t="n">
-        <v>11498.8</v>
+        <v>11636.5</v>
       </c>
       <c r="G1461" t="n">
         <v>6</v>
@@ -48673,10 +48673,10 @@
         <v>107</v>
       </c>
       <c r="E1462" t="n">
-        <v>2150</v>
+        <v>2325.2</v>
       </c>
       <c r="F1462" t="n">
-        <v>13084.8</v>
+        <v>13260</v>
       </c>
       <c r="G1462" t="n">
         <v>1</v>
@@ -48706,10 +48706,10 @@
         <v>46.5</v>
       </c>
       <c r="E1463" t="n">
-        <v>1699.1</v>
+        <v>1815.6</v>
       </c>
       <c r="F1463" t="n">
-        <v>10533</v>
+        <v>10649.5</v>
       </c>
       <c r="G1463" t="n">
         <v>8</v>
@@ -48739,10 +48739,10 @@
         <v>67.40000000000001</v>
       </c>
       <c r="E1464" t="n">
-        <v>1951.1</v>
+        <v>2056</v>
       </c>
       <c r="F1464" t="n">
-        <v>11555.2</v>
+        <v>11660.1</v>
       </c>
       <c r="G1464" t="n">
         <v>4</v>
@@ -48772,10 +48772,10 @@
         <v>85.59999999999999</v>
       </c>
       <c r="E1465" t="n">
-        <v>2098.1</v>
+        <v>2237.1</v>
       </c>
       <c r="F1465" t="n">
-        <v>9633.1</v>
+        <v>9772.1</v>
       </c>
       <c r="G1465" t="n">
         <v>2</v>
@@ -48805,16 +48805,16 @@
         <v>100.6</v>
       </c>
       <c r="E1466" t="n">
-        <v>2219.2</v>
+        <v>2349.3</v>
       </c>
       <c r="F1466" t="n">
-        <v>12930.3</v>
+        <v>13060.4</v>
       </c>
       <c r="G1466" t="n">
         <v>1</v>
       </c>
       <c r="H1466" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1466" t="n">
         <v>2</v>
@@ -48838,10 +48838,10 @@
         <v>65.90000000000001</v>
       </c>
       <c r="E1467" t="n">
-        <v>2136.1</v>
+        <v>2273.1</v>
       </c>
       <c r="F1467" t="n">
-        <v>12827.1</v>
+        <v>12964.1</v>
       </c>
       <c r="G1467" t="n">
         <v>5</v>
@@ -48871,10 +48871,10 @@
         <v>70.8</v>
       </c>
       <c r="E1468" t="n">
-        <v>2096</v>
+        <v>2225.5</v>
       </c>
       <c r="F1468" t="n">
-        <v>11961.1</v>
+        <v>12090.6</v>
       </c>
       <c r="G1468" t="n">
         <v>4</v>
@@ -48904,10 +48904,10 @@
         <v>60.5</v>
       </c>
       <c r="E1469" t="n">
-        <v>1894.7</v>
+        <v>2032.4</v>
       </c>
       <c r="F1469" t="n">
-        <v>11559.3</v>
+        <v>11697</v>
       </c>
       <c r="G1469" t="n">
         <v>7</v>
@@ -48937,16 +48937,16 @@
         <v>64.59999999999999</v>
       </c>
       <c r="E1470" t="n">
-        <v>2214.6</v>
+        <v>2389.8</v>
       </c>
       <c r="F1470" t="n">
-        <v>13149.4</v>
+        <v>13324.6</v>
       </c>
       <c r="G1470" t="n">
         <v>6</v>
       </c>
       <c r="H1470" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1470" t="n">
         <v>1</v>
@@ -48970,10 +48970,10 @@
         <v>73.7</v>
       </c>
       <c r="E1471" t="n">
-        <v>1772.8</v>
+        <v>1889.3</v>
       </c>
       <c r="F1471" t="n">
-        <v>10606.7</v>
+        <v>10723.2</v>
       </c>
       <c r="G1471" t="n">
         <v>3</v>
@@ -49003,10 +49003,10 @@
         <v>55.2</v>
       </c>
       <c r="E1472" t="n">
-        <v>2006.3</v>
+        <v>2111.2</v>
       </c>
       <c r="F1472" t="n">
-        <v>11610.4</v>
+        <v>11715.3</v>
       </c>
       <c r="G1472" t="n">
         <v>8</v>
@@ -49036,10 +49036,10 @@
         <v>88</v>
       </c>
       <c r="E1473" t="n">
-        <v>2186.1</v>
+        <v>2325.1</v>
       </c>
       <c r="F1473" t="n">
-        <v>9721.1</v>
+        <v>9860.1</v>
       </c>
       <c r="G1473" t="n">
         <v>2</v>
@@ -49069,16 +49069,16 @@
         <v>70.09999999999999</v>
       </c>
       <c r="E1474" t="n">
-        <v>2289.3</v>
+        <v>2419.4</v>
       </c>
       <c r="F1474" t="n">
-        <v>13000.4</v>
+        <v>13130.5</v>
       </c>
       <c r="G1474" t="n">
         <v>4</v>
       </c>
       <c r="H1474" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I1474" t="n">
         <v>2</v>
@@ -49102,10 +49102,10 @@
         <v>77.90000000000001</v>
       </c>
       <c r="E1475" t="n">
-        <v>2214</v>
+        <v>2351</v>
       </c>
       <c r="F1475" t="n">
-        <v>12905</v>
+        <v>13042</v>
       </c>
       <c r="G1475" t="n">
         <v>3</v>
@@ -49135,10 +49135,10 @@
         <v>80.8</v>
       </c>
       <c r="E1476" t="n">
-        <v>2176.8</v>
+        <v>2306.3</v>
       </c>
       <c r="F1476" t="n">
-        <v>12041.9</v>
+        <v>12171.4</v>
       </c>
       <c r="G1476" t="n">
         <v>2</v>
@@ -49168,10 +49168,10 @@
         <v>53</v>
       </c>
       <c r="E1477" t="n">
-        <v>1947.7</v>
+        <v>2085.4</v>
       </c>
       <c r="F1477" t="n">
-        <v>11612.3</v>
+        <v>11750</v>
       </c>
       <c r="G1477" t="n">
         <v>7</v>
@@ -49201,16 +49201,16 @@
         <v>59.8</v>
       </c>
       <c r="E1478" t="n">
-        <v>2274.4</v>
+        <v>2449.6</v>
       </c>
       <c r="F1478" t="n">
-        <v>13209.2</v>
+        <v>13384.4</v>
       </c>
       <c r="G1478" t="n">
         <v>6</v>
       </c>
       <c r="H1478" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I1478" t="n">
         <v>1</v>
@@ -49234,10 +49234,10 @@
         <v>68.39999999999999</v>
       </c>
       <c r="E1479" t="n">
-        <v>1841.2</v>
+        <v>1957.7</v>
       </c>
       <c r="F1479" t="n">
-        <v>10675.1</v>
+        <v>10791.6</v>
       </c>
       <c r="G1479" t="n">
         <v>5</v>
@@ -49267,10 +49267,10 @@
         <v>48.4</v>
       </c>
       <c r="E1480" t="n">
-        <v>2054.7</v>
+        <v>2159.6</v>
       </c>
       <c r="F1480" t="n">
-        <v>11658.8</v>
+        <v>11763.7</v>
       </c>
       <c r="G1480" t="n">
         <v>8</v>
@@ -49300,16 +49300,16 @@
         <v>104.8</v>
       </c>
       <c r="E1481" t="n">
-        <v>2290.9</v>
+        <v>2429.9</v>
       </c>
       <c r="F1481" t="n">
-        <v>9825.9</v>
+        <v>9964.9</v>
       </c>
       <c r="G1481" t="n">
         <v>1</v>
       </c>
       <c r="H1481" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1481" t="n">
         <v>8</v>
@@ -49333,16 +49333,16 @@
         <v>76.3</v>
       </c>
       <c r="E1482" t="n">
-        <v>2365.6</v>
+        <v>2495.7</v>
       </c>
       <c r="F1482" t="n">
-        <v>13076.7</v>
+        <v>13206.8</v>
       </c>
       <c r="G1482" t="n">
         <v>3</v>
       </c>
       <c r="H1482" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I1482" t="n">
         <v>2</v>
@@ -49366,10 +49366,10 @@
         <v>73.3</v>
       </c>
       <c r="E1483" t="n">
-        <v>2287.3</v>
+        <v>2424.3</v>
       </c>
       <c r="F1483" t="n">
-        <v>12978.3</v>
+        <v>13115.3</v>
       </c>
       <c r="G1483" t="n">
         <v>5</v>
@@ -49399,10 +49399,10 @@
         <v>56.5</v>
       </c>
       <c r="E1484" t="n">
-        <v>2233.3</v>
+        <v>2362.8</v>
       </c>
       <c r="F1484" t="n">
-        <v>12098.4</v>
+        <v>12227.9</v>
       </c>
       <c r="G1484" t="n">
         <v>7</v>
@@ -49432,10 +49432,10 @@
         <v>75.09999999999999</v>
       </c>
       <c r="E1485" t="n">
-        <v>2022.8</v>
+        <v>2160.5</v>
       </c>
       <c r="F1485" t="n">
-        <v>11687.4</v>
+        <v>11825.1</v>
       </c>
       <c r="G1485" t="n">
         <v>4</v>
@@ -49444,7 +49444,7 @@
         <v>7</v>
       </c>
       <c r="I1485" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1486">
@@ -49465,16 +49465,16 @@
         <v>69.7</v>
       </c>
       <c r="E1486" t="n">
-        <v>2344.1</v>
+        <v>2519.3</v>
       </c>
       <c r="F1486" t="n">
-        <v>13278.9</v>
+        <v>13454.1</v>
       </c>
       <c r="G1486" t="n">
         <v>6</v>
       </c>
       <c r="H1486" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I1486" t="n">
         <v>1</v>
@@ -49498,10 +49498,10 @@
         <v>80.09999999999999</v>
       </c>
       <c r="E1487" t="n">
-        <v>1921.3</v>
+        <v>2037.8</v>
       </c>
       <c r="F1487" t="n">
-        <v>10755.2</v>
+        <v>10871.7</v>
       </c>
       <c r="G1487" t="n">
         <v>2</v>
@@ -49531,10 +49531,10 @@
         <v>44.90000000000001</v>
       </c>
       <c r="E1488" t="n">
-        <v>2099.6</v>
+        <v>2204.5</v>
       </c>
       <c r="F1488" t="n">
-        <v>11703.7</v>
+        <v>11808.6</v>
       </c>
       <c r="G1488" t="n">
         <v>8</v>
@@ -49543,7 +49543,7 @@
         <v>6</v>
       </c>
       <c r="I1488" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1489">
@@ -49564,16 +49564,16 @@
         <v>82.40000000000001</v>
       </c>
       <c r="E1489" t="n">
-        <v>2373.3</v>
+        <v>2512.3</v>
       </c>
       <c r="F1489" t="n">
-        <v>9908.299999999999</v>
+        <v>10047.3</v>
       </c>
       <c r="G1489" t="n">
         <v>1</v>
       </c>
       <c r="H1489" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1489" t="n">
         <v>8</v>
@@ -49597,10 +49597,10 @@
         <v>94.09999999999999</v>
       </c>
       <c r="E1490" t="n">
-        <v>2459.7</v>
+        <v>2589.8</v>
       </c>
       <c r="F1490" t="n">
-        <v>13170.8</v>
+        <v>13300.9</v>
       </c>
       <c r="G1490" t="n">
         <v>3</v>
@@ -49630,10 +49630,10 @@
         <v>94.90000000000001</v>
       </c>
       <c r="E1491" t="n">
-        <v>2382.2</v>
+        <v>2519.2</v>
       </c>
       <c r="F1491" t="n">
-        <v>13073.2</v>
+        <v>13210.2</v>
       </c>
       <c r="G1491" t="n">
         <v>2</v>
@@ -49663,10 +49663,10 @@
         <v>75.2</v>
       </c>
       <c r="E1492" t="n">
-        <v>2308.5</v>
+        <v>2438</v>
       </c>
       <c r="F1492" t="n">
-        <v>12173.6</v>
+        <v>12303.1</v>
       </c>
       <c r="G1492" t="n">
         <v>5</v>
@@ -49696,10 +49696,10 @@
         <v>38.3</v>
       </c>
       <c r="E1493" t="n">
-        <v>2061.1</v>
+        <v>2198.8</v>
       </c>
       <c r="F1493" t="n">
-        <v>11725.7</v>
+        <v>11863.4</v>
       </c>
       <c r="G1493" t="n">
         <v>8</v>
@@ -49708,7 +49708,7 @@
         <v>7</v>
       </c>
       <c r="I1493" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1494">
@@ -49729,10 +49729,10 @@
         <v>52.9</v>
       </c>
       <c r="E1494" t="n">
-        <v>2397</v>
+        <v>2572.2</v>
       </c>
       <c r="F1494" t="n">
-        <v>13331.8</v>
+        <v>13507</v>
       </c>
       <c r="G1494" t="n">
         <v>6</v>
@@ -49762,10 +49762,10 @@
         <v>78.7</v>
       </c>
       <c r="E1495" t="n">
-        <v>2000</v>
+        <v>2116.5</v>
       </c>
       <c r="F1495" t="n">
-        <v>10833.9</v>
+        <v>10950.4</v>
       </c>
       <c r="G1495" t="n">
         <v>4</v>
@@ -49795,10 +49795,10 @@
         <v>44.4</v>
       </c>
       <c r="E1496" t="n">
-        <v>2144</v>
+        <v>2248.9</v>
       </c>
       <c r="F1496" t="n">
-        <v>11748.1</v>
+        <v>11853</v>
       </c>
       <c r="G1496" t="n">
         <v>7</v>
@@ -49807,7 +49807,7 @@
         <v>6</v>
       </c>
       <c r="I1496" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1497">
@@ -49828,10 +49828,10 @@
         <v>95.3</v>
       </c>
       <c r="E1497" t="n">
-        <v>2468.6</v>
+        <v>2607.6</v>
       </c>
       <c r="F1497" t="n">
-        <v>10003.6</v>
+        <v>10142.6</v>
       </c>
       <c r="G1497" t="n">
         <v>1</v>
@@ -49861,10 +49861,10 @@
         <v>72.8</v>
       </c>
       <c r="E1498" t="n">
-        <v>2532.5</v>
+        <v>2662.6</v>
       </c>
       <c r="F1498" t="n">
-        <v>13243.6</v>
+        <v>13373.7</v>
       </c>
       <c r="G1498" t="n">
         <v>2</v>
@@ -49894,10 +49894,10 @@
         <v>42</v>
       </c>
       <c r="E1499" t="n">
-        <v>2424.2</v>
+        <v>2561.2</v>
       </c>
       <c r="F1499" t="n">
-        <v>13115.2</v>
+        <v>13252.2</v>
       </c>
       <c r="G1499" t="n">
         <v>7</v>
@@ -49927,10 +49927,10 @@
         <v>65.10000000000001</v>
       </c>
       <c r="E1500" t="n">
-        <v>2373.6</v>
+        <v>2503.1</v>
       </c>
       <c r="F1500" t="n">
-        <v>12238.7</v>
+        <v>12368.2</v>
       </c>
       <c r="G1500" t="n">
         <v>5</v>
@@ -49960,10 +49960,10 @@
         <v>39.8</v>
       </c>
       <c r="E1501" t="n">
-        <v>2100.9</v>
+        <v>2238.6</v>
       </c>
       <c r="F1501" t="n">
-        <v>11765.5</v>
+        <v>11903.2</v>
       </c>
       <c r="G1501" t="n">
         <v>8</v>
@@ -49993,10 +49993,10 @@
         <v>65.8</v>
       </c>
       <c r="E1502" t="n">
-        <v>2462.8</v>
+        <v>2638</v>
       </c>
       <c r="F1502" t="n">
-        <v>13397.6</v>
+        <v>13572.8</v>
       </c>
       <c r="G1502" t="n">
         <v>4</v>
@@ -50026,10 +50026,10 @@
         <v>66.40000000000001</v>
       </c>
       <c r="E1503" t="n">
-        <v>2066.4</v>
+        <v>2182.9</v>
       </c>
       <c r="F1503" t="n">
-        <v>10900.3</v>
+        <v>11016.8</v>
       </c>
       <c r="G1503" t="n">
         <v>3</v>
@@ -50059,10 +50059,10 @@
         <v>52.7</v>
       </c>
       <c r="E1504" t="n">
-        <v>2196.7</v>
+        <v>2301.6</v>
       </c>
       <c r="F1504" t="n">
-        <v>11800.8</v>
+        <v>11905.7</v>
       </c>
       <c r="G1504" t="n">
         <v>6</v>
@@ -50092,10 +50092,10 @@
         <v>81.3</v>
       </c>
       <c r="E1505" t="n">
-        <v>2549.9</v>
+        <v>2688.9</v>
       </c>
       <c r="F1505" t="n">
-        <v>10084.9</v>
+        <v>10223.9</v>
       </c>
       <c r="G1505" t="n">
         <v>1</v>
@@ -50125,10 +50125,10 @@
         <v>70.59999999999999</v>
       </c>
       <c r="E1506" t="n">
-        <v>2603.1</v>
+        <v>2733.2</v>
       </c>
       <c r="F1506" t="n">
-        <v>13314.2</v>
+        <v>13444.3</v>
       </c>
       <c r="G1506" t="n">
         <v>4</v>
@@ -50158,10 +50158,10 @@
         <v>76.40000000000001</v>
       </c>
       <c r="E1507" t="n">
-        <v>2500.6</v>
+        <v>2637.6</v>
       </c>
       <c r="F1507" t="n">
-        <v>13191.6</v>
+        <v>13328.6</v>
       </c>
       <c r="G1507" t="n">
         <v>2</v>
@@ -50191,10 +50191,10 @@
         <v>60.3</v>
       </c>
       <c r="E1508" t="n">
-        <v>2433.9</v>
+        <v>2563.4</v>
       </c>
       <c r="F1508" t="n">
-        <v>12299</v>
+        <v>12428.5</v>
       </c>
       <c r="G1508" t="n">
         <v>6</v>
@@ -50224,10 +50224,10 @@
         <v>60.4</v>
       </c>
       <c r="E1509" t="n">
-        <v>2161.3</v>
+        <v>2299</v>
       </c>
       <c r="F1509" t="n">
-        <v>11825.9</v>
+        <v>11963.6</v>
       </c>
       <c r="G1509" t="n">
         <v>5</v>
@@ -50236,7 +50236,7 @@
         <v>7</v>
       </c>
       <c r="I1509" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1510">
@@ -50257,10 +50257,10 @@
         <v>53.9</v>
       </c>
       <c r="E1510" t="n">
-        <v>2516.7</v>
+        <v>2691.9</v>
       </c>
       <c r="F1510" t="n">
-        <v>13451.5</v>
+        <v>13626.7</v>
       </c>
       <c r="G1510" t="n">
         <v>7</v>
@@ -50290,10 +50290,10 @@
         <v>75.80000000000001</v>
       </c>
       <c r="E1511" t="n">
-        <v>2142.2</v>
+        <v>2258.7</v>
       </c>
       <c r="F1511" t="n">
-        <v>10976.1</v>
+        <v>11092.6</v>
       </c>
       <c r="G1511" t="n">
         <v>3</v>
@@ -50323,10 +50323,10 @@
         <v>53.2</v>
       </c>
       <c r="E1512" t="n">
-        <v>2249.9</v>
+        <v>2354.8</v>
       </c>
       <c r="F1512" t="n">
-        <v>11854</v>
+        <v>11958.9</v>
       </c>
       <c r="G1512" t="n">
         <v>8</v>
@@ -50335,7 +50335,7 @@
         <v>6</v>
       </c>
       <c r="I1512" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1513">
@@ -50356,10 +50356,10 @@
         <v>87.59999999999999</v>
       </c>
       <c r="E1513" t="n">
-        <v>2637.5</v>
+        <v>2776.5</v>
       </c>
       <c r="F1513" t="n">
-        <v>10172.5</v>
+        <v>10311.5</v>
       </c>
       <c r="G1513" t="n">
         <v>1</v>
@@ -50389,10 +50389,10 @@
         <v>58.2</v>
       </c>
       <c r="E1514" t="n">
-        <v>2661.3</v>
+        <v>2791.4</v>
       </c>
       <c r="F1514" t="n">
-        <v>13372.4</v>
+        <v>13502.5</v>
       </c>
       <c r="G1514" t="n">
         <v>4</v>
@@ -50422,10 +50422,10 @@
         <v>49.3</v>
       </c>
       <c r="E1515" t="n">
-        <v>2549.9</v>
+        <v>2686.9</v>
       </c>
       <c r="F1515" t="n">
-        <v>13240.9</v>
+        <v>13377.9</v>
       </c>
       <c r="G1515" t="n">
         <v>5</v>
@@ -50455,10 +50455,10 @@
         <v>69.09999999999999</v>
       </c>
       <c r="E1516" t="n">
-        <v>2503</v>
+        <v>2632.5</v>
       </c>
       <c r="F1516" t="n">
-        <v>12368.1</v>
+        <v>12497.6</v>
       </c>
       <c r="G1516" t="n">
         <v>3</v>
@@ -50488,10 +50488,10 @@
         <v>48.4</v>
       </c>
       <c r="E1517" t="n">
-        <v>2209.7</v>
+        <v>2347.4</v>
       </c>
       <c r="F1517" t="n">
-        <v>11874.3</v>
+        <v>12012</v>
       </c>
       <c r="G1517" t="n">
         <v>6</v>
@@ -50521,10 +50521,10 @@
         <v>47.6</v>
       </c>
       <c r="E1518" t="n">
-        <v>2564.3</v>
+        <v>2739.5</v>
       </c>
       <c r="F1518" t="n">
-        <v>13499.1</v>
+        <v>13674.3</v>
       </c>
       <c r="G1518" t="n">
         <v>7</v>
@@ -50554,10 +50554,10 @@
         <v>34.8</v>
       </c>
       <c r="E1519" t="n">
-        <v>2177</v>
+        <v>2293.5</v>
       </c>
       <c r="F1519" t="n">
-        <v>11010.9</v>
+        <v>11127.4</v>
       </c>
       <c r="G1519" t="n">
         <v>8</v>
@@ -50587,10 +50587,10 @@
         <v>73.3</v>
       </c>
       <c r="E1520" t="n">
-        <v>2323.2</v>
+        <v>2428.1</v>
       </c>
       <c r="F1520" t="n">
-        <v>11927.3</v>
+        <v>12032.2</v>
       </c>
       <c r="G1520" t="n">
         <v>2</v>
@@ -50620,10 +50620,10 @@
         <v>97.7</v>
       </c>
       <c r="E1521" t="n">
-        <v>2735.2</v>
+        <v>2874.2</v>
       </c>
       <c r="F1521" t="n">
-        <v>10270.2</v>
+        <v>10409.2</v>
       </c>
       <c r="G1521" t="n">
         <v>1</v>
@@ -50653,10 +50653,10 @@
         <v>95.7</v>
       </c>
       <c r="E1522" t="n">
-        <v>2757</v>
+        <v>2887.1</v>
       </c>
       <c r="F1522" t="n">
-        <v>13468.1</v>
+        <v>13598.2</v>
       </c>
       <c r="G1522" t="n">
         <v>1</v>
@@ -50686,10 +50686,10 @@
         <v>0</v>
       </c>
       <c r="E1523" t="n">
-        <v>2549.9</v>
+        <v>2686.9</v>
       </c>
       <c r="F1523" t="n">
-        <v>13240.9</v>
+        <v>13377.9</v>
       </c>
       <c r="G1523" t="n">
         <v>8</v>
@@ -50719,10 +50719,10 @@
         <v>40.7</v>
       </c>
       <c r="E1524" t="n">
-        <v>2543.7</v>
+        <v>2673.2</v>
       </c>
       <c r="F1524" t="n">
-        <v>12408.8</v>
+        <v>12538.3</v>
       </c>
       <c r="G1524" t="n">
         <v>7</v>
@@ -50752,10 +50752,10 @@
         <v>68.2</v>
       </c>
       <c r="E1525" t="n">
-        <v>2277.9</v>
+        <v>2415.6</v>
       </c>
       <c r="F1525" t="n">
-        <v>11942.5</v>
+        <v>12080.2</v>
       </c>
       <c r="G1525" t="n">
         <v>4</v>
@@ -50764,7 +50764,7 @@
         <v>7</v>
       </c>
       <c r="I1525" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1526">
@@ -50785,10 +50785,10 @@
         <v>66.59999999999999</v>
       </c>
       <c r="E1526" t="n">
-        <v>2630.9</v>
+        <v>2806.1</v>
       </c>
       <c r="F1526" t="n">
-        <v>13565.7</v>
+        <v>13740.9</v>
       </c>
       <c r="G1526" t="n">
         <v>5</v>
@@ -50818,10 +50818,10 @@
         <v>80.59999999999999</v>
       </c>
       <c r="E1527" t="n">
-        <v>2257.6</v>
+        <v>2374.1</v>
       </c>
       <c r="F1527" t="n">
-        <v>11091.5</v>
+        <v>11208</v>
       </c>
       <c r="G1527" t="n">
         <v>2</v>
@@ -50851,10 +50851,10 @@
         <v>46.4</v>
       </c>
       <c r="E1528" t="n">
-        <v>2369.6</v>
+        <v>2474.5</v>
       </c>
       <c r="F1528" t="n">
-        <v>11973.7</v>
+        <v>12078.6</v>
       </c>
       <c r="G1528" t="n">
         <v>6</v>
@@ -50863,7 +50863,7 @@
         <v>6</v>
       </c>
       <c r="I1528" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1529">
@@ -50884,10 +50884,10 @@
         <v>80.40000000000001</v>
       </c>
       <c r="E1529" t="n">
-        <v>2815.6</v>
+        <v>2954.6</v>
       </c>
       <c r="F1529" t="n">
-        <v>10350.6</v>
+        <v>10489.6</v>
       </c>
       <c r="G1529" t="n">
         <v>3</v>
